--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU142"/>
+  <dimension ref="A1:AU136"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G12">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G13">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G16">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G29">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G30">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>2026-10-16 12:00:00</t>
+          <t>2026-10-16 11:30:00</t>
         </is>
       </c>
     </row>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G31">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G32">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N32">
@@ -5646,7 +5646,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G33">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G34">
@@ -5847,7 +5847,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N34">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G35">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>2026-10-16 12:00:00</t>
+          <t>2026-10-16 12:30:00</t>
         </is>
       </c>
     </row>
@@ -6130,12 +6130,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G36">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>2026-10-16 12:00:00</t>
+          <t>2026-10-16 12:30:00</t>
         </is>
       </c>
     </row>
@@ -6293,12 +6293,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G37">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-10-16 12:00:00</t>
+          <t>2026-10-16 12:45:00</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="G38">
@@ -6499,7 +6499,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N38">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>2026-10-16 12:00:00</t>
+          <t>2026-10-16 13:00:00</t>
         </is>
       </c>
     </row>
@@ -6619,12 +6619,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G39">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>2026-10-16 12:00:00</t>
+          <t>2026-10-16 13:00:00</t>
         </is>
       </c>
     </row>
@@ -6782,27 +6782,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G40">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>2026-10-16 12:00:00</t>
+          <t>2026-10-16 13:00:00</t>
         </is>
       </c>
     </row>
@@ -6945,27 +6945,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G41">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:00</t>
+          <t>2026-10-16 13:00:00</t>
         </is>
       </c>
     </row>
@@ -7108,12 +7108,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G42">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:00</t>
+          <t>2026-10-16 13:00:00</t>
         </is>
       </c>
     </row>
@@ -7271,12 +7271,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G43">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>2026-10-16 12:45:00</t>
+          <t>2026-10-16 13:00:00</t>
         </is>
       </c>
     </row>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G44">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G45">
@@ -7765,22 +7765,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G46">
@@ -7928,22 +7928,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G47">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G48">
@@ -8237,7 +8237,7 @@
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>2026-10-16 13:00:00</t>
+          <t>2026-10-16 13:30:00</t>
         </is>
       </c>
     </row>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G49">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>2026-10-16 13:00:00</t>
+          <t>2026-10-16 13:30:00</t>
         </is>
       </c>
     </row>
@@ -8412,12 +8412,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G50">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>2026-10-16 13:00:00</t>
+          <t>2026-10-16 13:30:00</t>
         </is>
       </c>
     </row>
@@ -8575,12 +8575,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G51">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>2026-10-16 13:00:00</t>
+          <t>2026-10-16 13:30:00</t>
         </is>
       </c>
     </row>
@@ -8738,12 +8738,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G52">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>2026-10-16 13:00:00</t>
+          <t>2026-10-16 13:30:00</t>
         </is>
       </c>
     </row>
@@ -8901,12 +8901,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G53">
@@ -9052,7 +9052,7 @@
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>2026-10-16 13:00:00</t>
+          <t>2026-10-16 13:30:00</t>
         </is>
       </c>
     </row>
@@ -9064,12 +9064,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G54">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>2026-10-16 13:30:00</t>
+          <t>2026-10-16 13:45:00</t>
         </is>
       </c>
     </row>
@@ -9227,12 +9227,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G55">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>2026-10-16 13:30:00</t>
+          <t>2026-10-16 14:00:00</t>
         </is>
       </c>
     </row>
@@ -9390,12 +9390,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G56">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>2026-10-16 13:30:00</t>
+          <t>2026-10-16 14:00:00</t>
         </is>
       </c>
     </row>
@@ -9553,27 +9553,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G57">
@@ -9704,7 +9704,7 @@
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>2026-10-16 13:30:00</t>
+          <t>2026-10-16 14:00:00</t>
         </is>
       </c>
     </row>
@@ -9716,12 +9716,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Horsens</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G58">
@@ -9867,7 +9867,7 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>2026-10-16 13:30:00</t>
+          <t>2026-10-16 14:00:00</t>
         </is>
       </c>
     </row>
@@ -9879,12 +9879,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>2026-10-16 13:30:00</t>
+          <t>2026-10-16 14:30:00</t>
         </is>
       </c>
     </row>
@@ -10042,12 +10042,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G60">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>2026-10-16 13:45:00</t>
+          <t>2026-10-16 15:00:00</t>
         </is>
       </c>
     </row>
@@ -10205,12 +10205,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G61">
@@ -10356,7 +10356,7 @@
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>2026-10-16 14:00:00</t>
+          <t>2026-10-16 15:00:00</t>
         </is>
       </c>
     </row>
@@ -10368,12 +10368,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G62">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>2026-10-16 14:00:00</t>
+          <t>2026-10-16 15:00:00</t>
         </is>
       </c>
     </row>
@@ -10531,27 +10531,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G63">
@@ -10682,7 +10682,7 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>2026-10-16 14:00:00</t>
+          <t>2026-10-16 15:00:00</t>
         </is>
       </c>
     </row>
@@ -10694,12 +10694,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Horsens</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G64">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>2026-10-16 14:00:00</t>
+          <t>2026-10-16 15:00:00</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="O65">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="P65">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q65">
         <v>0</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>2026-10-16 14:30:00</t>
+          <t>2026-10-16 15:00:00</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G66">
@@ -11188,7 +11188,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G67">
@@ -11351,7 +11351,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G68">
@@ -11514,7 +11514,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G69">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G70">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G71">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G72">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G73">
@@ -12312,7 +12312,7 @@
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>2026-10-16 15:00:00</t>
+          <t>2026-10-16 15:30:00</t>
         </is>
       </c>
     </row>
@@ -12324,12 +12324,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="G74">
@@ -12475,7 +12475,7 @@
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>2026-10-16 15:00:00</t>
+          <t>2026-10-16 15:30:00</t>
         </is>
       </c>
     </row>
@@ -12487,12 +12487,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G75">
@@ -12638,7 +12638,7 @@
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>2026-10-16 15:00:00</t>
+          <t>2026-10-16 15:30:00</t>
         </is>
       </c>
     </row>
@@ -12650,12 +12650,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G76">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>2026-10-16 15:00:00</t>
+          <t>2026-10-16 15:30:00</t>
         </is>
       </c>
     </row>
@@ -12813,12 +12813,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G77">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>2026-10-16 15:00:00</t>
+          <t>2026-10-16 15:30:00</t>
         </is>
       </c>
     </row>
@@ -12976,12 +12976,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G78">
@@ -13127,7 +13127,7 @@
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>2026-10-16 15:00:00</t>
+          <t>2026-10-16 15:30:00</t>
         </is>
       </c>
     </row>
@@ -13144,7 +13144,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G79">
@@ -13307,7 +13307,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G80">
@@ -13470,7 +13470,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13557,10 +13557,10 @@
         <v>0</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD81">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE81">
         <v>0</v>
@@ -13628,12 +13628,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G82">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>2026-10-16 15:30:00</t>
+          <t>2026-10-16 15:45:00</t>
         </is>
       </c>
     </row>
@@ -13791,12 +13791,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -13942,7 +13942,7 @@
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>2026-10-16 15:30:00</t>
+          <t>2026-10-16 15:45:00</t>
         </is>
       </c>
     </row>
@@ -13954,27 +13954,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G84">
@@ -14105,7 +14105,7 @@
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>2026-10-16 15:30:00</t>
+          <t>2026-10-16 15:45:00</t>
         </is>
       </c>
     </row>
@@ -14117,27 +14117,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G85">
@@ -14268,7 +14268,7 @@
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>2026-10-16 15:30:00</t>
+          <t>2026-10-16 15:45:00</t>
         </is>
       </c>
     </row>
@@ -14280,27 +14280,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G86">
@@ -14431,7 +14431,7 @@
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>2026-10-16 15:30:00</t>
+          <t>2026-10-16 15:45:00</t>
         </is>
       </c>
     </row>
@@ -14443,27 +14443,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O87">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="P87">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -14535,10 +14535,10 @@
         <v>0</v>
       </c>
       <c r="AC87">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD87">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE87">
         <v>0</v>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>2026-10-16 15:30:00</t>
+          <t>2026-10-16 15:45:00</t>
         </is>
       </c>
     </row>
@@ -14611,22 +14611,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G88">
@@ -14774,22 +14774,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G89">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G90">
@@ -15100,7 +15100,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G91">
@@ -15263,7 +15263,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G92">
@@ -15426,22 +15426,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,13 +15468,13 @@
         </is>
       </c>
       <c r="N93">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O93">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q93">
         <v>0</v>
@@ -15584,12 +15584,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G94">
@@ -15735,7 +15735,7 @@
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>2026-10-16 15:45:00</t>
+          <t>2026-10-16 16:00:00</t>
         </is>
       </c>
     </row>
@@ -15747,27 +15747,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G95">
@@ -15898,7 +15898,7 @@
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>2026-10-16 15:45:00</t>
+          <t>2026-10-16 16:00:00</t>
         </is>
       </c>
     </row>
@@ -15910,27 +15910,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G96">
@@ -16061,7 +16061,7 @@
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>2026-10-16 15:45:00</t>
+          <t>2026-10-16 16:00:00</t>
         </is>
       </c>
     </row>
@@ -16073,12 +16073,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G97">
@@ -16224,7 +16224,7 @@
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>2026-10-16 15:45:00</t>
+          <t>2026-10-16 17:30:00</t>
         </is>
       </c>
     </row>
@@ -16236,12 +16236,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G98">
@@ -16387,7 +16387,7 @@
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>2026-10-16 15:45:00</t>
+          <t>2026-10-16 18:00:00</t>
         </is>
       </c>
     </row>
@@ -16399,27 +16399,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O99">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P99">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16550,7 +16550,7 @@
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>2026-10-16 15:45:00</t>
+          <t>2026-10-16 19:30:00</t>
         </is>
       </c>
     </row>
@@ -16562,12 +16562,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G100">
@@ -16713,7 +16713,7 @@
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>2026-10-16 16:00:00</t>
+          <t>2026-10-16 20:00:00</t>
         </is>
       </c>
     </row>
@@ -16725,27 +16725,27 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G101">
@@ -16876,7 +16876,7 @@
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>2026-10-16 16:00:00</t>
+          <t>2026-10-16 20:00:00</t>
         </is>
       </c>
     </row>
@@ -16888,27 +16888,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G102">
@@ -17039,7 +17039,7 @@
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>2026-10-16 16:00:00</t>
+          <t>2026-10-16 20:30:00</t>
         </is>
       </c>
     </row>
@@ -17051,27 +17051,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G103">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>2026-10-16 17:30:00</t>
+          <t>2026-10-16 21:00:00</t>
         </is>
       </c>
     </row>
@@ -17214,27 +17214,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G104">
@@ -17365,7 +17365,7 @@
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>2026-10-16 18:00:00</t>
+          <t>2026-10-16 21:00:00</t>
         </is>
       </c>
     </row>
@@ -17377,27 +17377,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G105">
@@ -17528,7 +17528,7 @@
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>2026-10-16 19:30:00</t>
+          <t>2026-10-16 21:00:00</t>
         </is>
       </c>
     </row>
@@ -17540,27 +17540,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G106">
@@ -17691,7 +17691,7 @@
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>2026-10-16 20:00:00</t>
+          <t>2026-10-16 21:00:00</t>
         </is>
       </c>
     </row>
@@ -17703,12 +17703,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="G107">
@@ -17854,7 +17854,7 @@
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>2026-10-16 20:00:00</t>
+          <t>2026-10-16 21:00:00</t>
         </is>
       </c>
     </row>
@@ -17866,27 +17866,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G108">
@@ -18017,7 +18017,7 @@
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>2026-10-16 20:30:00</t>
+          <t>2026-10-16 21:00:00</t>
         </is>
       </c>
     </row>
@@ -18034,7 +18034,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G109">
@@ -18197,7 +18197,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G110">
@@ -18360,7 +18360,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G111">
@@ -18523,7 +18523,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G112">
@@ -18686,22 +18686,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G114">
@@ -19012,22 +19012,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G115">
@@ -19175,22 +19175,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G116">
@@ -19338,22 +19338,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G117">
@@ -19501,22 +19501,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G118">
@@ -19664,22 +19664,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G119">
@@ -19827,22 +19827,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G120">
@@ -19990,22 +19990,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G121">
@@ -20153,22 +20153,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G122">
@@ -20316,22 +20316,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G123">
@@ -20479,22 +20479,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G124">
@@ -20642,22 +20642,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G125">
@@ -20805,7 +20805,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G126">
@@ -20968,7 +20968,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G127">
@@ -21131,7 +21131,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G128">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G129">
@@ -21457,7 +21457,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G130">
@@ -21620,7 +21620,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G131">
@@ -21783,22 +21783,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G133">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G134">
@@ -22267,27 +22267,27 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G135">
@@ -22418,7 +22418,7 @@
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>2026-10-16 21:00:00</t>
+          <t>2026-10-16 22:00:00</t>
         </is>
       </c>
     </row>
@@ -22430,27 +22430,27 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G136">
@@ -22580,984 +22580,6 @@
         <v>0</v>
       </c>
       <c r="AU136" t="inlineStr">
-        <is>
-          <t>2026-10-16 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Napredak</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>Dubočica</t>
-        </is>
-      </c>
-      <c r="G137">
-        <v>0</v>
-      </c>
-      <c r="H137">
-        <v>0</v>
-      </c>
-      <c r="I137">
-        <v>0</v>
-      </c>
-      <c r="J137">
-        <v>0</v>
-      </c>
-      <c r="K137">
-        <v>0</v>
-      </c>
-      <c r="L137">
-        <v>0</v>
-      </c>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N137">
-        <v>0</v>
-      </c>
-      <c r="O137">
-        <v>0</v>
-      </c>
-      <c r="P137">
-        <v>0</v>
-      </c>
-      <c r="Q137">
-        <v>0</v>
-      </c>
-      <c r="R137">
-        <v>0</v>
-      </c>
-      <c r="S137">
-        <v>0</v>
-      </c>
-      <c r="T137">
-        <v>0</v>
-      </c>
-      <c r="U137">
-        <v>0</v>
-      </c>
-      <c r="V137">
-        <v>0</v>
-      </c>
-      <c r="W137">
-        <v>0</v>
-      </c>
-      <c r="X137">
-        <v>0</v>
-      </c>
-      <c r="Y137">
-        <v>0</v>
-      </c>
-      <c r="Z137">
-        <v>0</v>
-      </c>
-      <c r="AA137">
-        <v>0</v>
-      </c>
-      <c r="AB137">
-        <v>0</v>
-      </c>
-      <c r="AC137">
-        <v>0</v>
-      </c>
-      <c r="AD137">
-        <v>0</v>
-      </c>
-      <c r="AE137">
-        <v>0</v>
-      </c>
-      <c r="AF137">
-        <v>0</v>
-      </c>
-      <c r="AG137">
-        <v>0</v>
-      </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ137">
-        <v>0</v>
-      </c>
-      <c r="AK137">
-        <v>0</v>
-      </c>
-      <c r="AL137">
-        <v>0</v>
-      </c>
-      <c r="AM137">
-        <v>-1</v>
-      </c>
-      <c r="AN137">
-        <v>-1</v>
-      </c>
-      <c r="AO137">
-        <v>-1</v>
-      </c>
-      <c r="AP137">
-        <v>-1</v>
-      </c>
-      <c r="AQ137">
-        <v>0</v>
-      </c>
-      <c r="AR137">
-        <v>0</v>
-      </c>
-      <c r="AS137">
-        <v>0</v>
-      </c>
-      <c r="AT137">
-        <v>0</v>
-      </c>
-      <c r="AU137" t="inlineStr">
-        <is>
-          <t>2026-10-16 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Javor Ivanjica</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>Bor</t>
-        </is>
-      </c>
-      <c r="G138">
-        <v>0</v>
-      </c>
-      <c r="H138">
-        <v>0</v>
-      </c>
-      <c r="I138">
-        <v>0</v>
-      </c>
-      <c r="J138">
-        <v>0</v>
-      </c>
-      <c r="K138">
-        <v>0</v>
-      </c>
-      <c r="L138">
-        <v>0</v>
-      </c>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N138">
-        <v>0</v>
-      </c>
-      <c r="O138">
-        <v>0</v>
-      </c>
-      <c r="P138">
-        <v>0</v>
-      </c>
-      <c r="Q138">
-        <v>0</v>
-      </c>
-      <c r="R138">
-        <v>0</v>
-      </c>
-      <c r="S138">
-        <v>0</v>
-      </c>
-      <c r="T138">
-        <v>0</v>
-      </c>
-      <c r="U138">
-        <v>0</v>
-      </c>
-      <c r="V138">
-        <v>0</v>
-      </c>
-      <c r="W138">
-        <v>0</v>
-      </c>
-      <c r="X138">
-        <v>0</v>
-      </c>
-      <c r="Y138">
-        <v>0</v>
-      </c>
-      <c r="Z138">
-        <v>0</v>
-      </c>
-      <c r="AA138">
-        <v>0</v>
-      </c>
-      <c r="AB138">
-        <v>0</v>
-      </c>
-      <c r="AC138">
-        <v>0</v>
-      </c>
-      <c r="AD138">
-        <v>0</v>
-      </c>
-      <c r="AE138">
-        <v>0</v>
-      </c>
-      <c r="AF138">
-        <v>0</v>
-      </c>
-      <c r="AG138">
-        <v>0</v>
-      </c>
-      <c r="AH138" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI138" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ138">
-        <v>0</v>
-      </c>
-      <c r="AK138">
-        <v>0</v>
-      </c>
-      <c r="AL138">
-        <v>0</v>
-      </c>
-      <c r="AM138">
-        <v>-1</v>
-      </c>
-      <c r="AN138">
-        <v>-1</v>
-      </c>
-      <c r="AO138">
-        <v>-1</v>
-      </c>
-      <c r="AP138">
-        <v>-1</v>
-      </c>
-      <c r="AQ138">
-        <v>0</v>
-      </c>
-      <c r="AR138">
-        <v>0</v>
-      </c>
-      <c r="AS138">
-        <v>0</v>
-      </c>
-      <c r="AT138">
-        <v>0</v>
-      </c>
-      <c r="AU138" t="inlineStr">
-        <is>
-          <t>2026-10-16 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Jedinstvo Ub</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Grafičar</t>
-        </is>
-      </c>
-      <c r="G139">
-        <v>0</v>
-      </c>
-      <c r="H139">
-        <v>0</v>
-      </c>
-      <c r="I139">
-        <v>0</v>
-      </c>
-      <c r="J139">
-        <v>0</v>
-      </c>
-      <c r="K139">
-        <v>0</v>
-      </c>
-      <c r="L139">
-        <v>0</v>
-      </c>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N139">
-        <v>0</v>
-      </c>
-      <c r="O139">
-        <v>0</v>
-      </c>
-      <c r="P139">
-        <v>0</v>
-      </c>
-      <c r="Q139">
-        <v>0</v>
-      </c>
-      <c r="R139">
-        <v>0</v>
-      </c>
-      <c r="S139">
-        <v>0</v>
-      </c>
-      <c r="T139">
-        <v>0</v>
-      </c>
-      <c r="U139">
-        <v>0</v>
-      </c>
-      <c r="V139">
-        <v>0</v>
-      </c>
-      <c r="W139">
-        <v>0</v>
-      </c>
-      <c r="X139">
-        <v>0</v>
-      </c>
-      <c r="Y139">
-        <v>0</v>
-      </c>
-      <c r="Z139">
-        <v>0</v>
-      </c>
-      <c r="AA139">
-        <v>0</v>
-      </c>
-      <c r="AB139">
-        <v>0</v>
-      </c>
-      <c r="AC139">
-        <v>0</v>
-      </c>
-      <c r="AD139">
-        <v>0</v>
-      </c>
-      <c r="AE139">
-        <v>0</v>
-      </c>
-      <c r="AF139">
-        <v>0</v>
-      </c>
-      <c r="AG139">
-        <v>0</v>
-      </c>
-      <c r="AH139" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI139" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ139">
-        <v>0</v>
-      </c>
-      <c r="AK139">
-        <v>0</v>
-      </c>
-      <c r="AL139">
-        <v>0</v>
-      </c>
-      <c r="AM139">
-        <v>-1</v>
-      </c>
-      <c r="AN139">
-        <v>-1</v>
-      </c>
-      <c r="AO139">
-        <v>-1</v>
-      </c>
-      <c r="AP139">
-        <v>-1</v>
-      </c>
-      <c r="AQ139">
-        <v>0</v>
-      </c>
-      <c r="AR139">
-        <v>0</v>
-      </c>
-      <c r="AS139">
-        <v>0</v>
-      </c>
-      <c r="AT139">
-        <v>0</v>
-      </c>
-      <c r="AU139" t="inlineStr">
-        <is>
-          <t>2026-10-16 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Semendrija 1924</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>Naftagas</t>
-        </is>
-      </c>
-      <c r="G140">
-        <v>0</v>
-      </c>
-      <c r="H140">
-        <v>0</v>
-      </c>
-      <c r="I140">
-        <v>0</v>
-      </c>
-      <c r="J140">
-        <v>0</v>
-      </c>
-      <c r="K140">
-        <v>0</v>
-      </c>
-      <c r="L140">
-        <v>0</v>
-      </c>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N140">
-        <v>0</v>
-      </c>
-      <c r="O140">
-        <v>0</v>
-      </c>
-      <c r="P140">
-        <v>0</v>
-      </c>
-      <c r="Q140">
-        <v>0</v>
-      </c>
-      <c r="R140">
-        <v>0</v>
-      </c>
-      <c r="S140">
-        <v>0</v>
-      </c>
-      <c r="T140">
-        <v>0</v>
-      </c>
-      <c r="U140">
-        <v>0</v>
-      </c>
-      <c r="V140">
-        <v>0</v>
-      </c>
-      <c r="W140">
-        <v>0</v>
-      </c>
-      <c r="X140">
-        <v>0</v>
-      </c>
-      <c r="Y140">
-        <v>0</v>
-      </c>
-      <c r="Z140">
-        <v>0</v>
-      </c>
-      <c r="AA140">
-        <v>0</v>
-      </c>
-      <c r="AB140">
-        <v>0</v>
-      </c>
-      <c r="AC140">
-        <v>0</v>
-      </c>
-      <c r="AD140">
-        <v>0</v>
-      </c>
-      <c r="AE140">
-        <v>0</v>
-      </c>
-      <c r="AF140">
-        <v>0</v>
-      </c>
-      <c r="AG140">
-        <v>0</v>
-      </c>
-      <c r="AH140" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI140" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ140">
-        <v>0</v>
-      </c>
-      <c r="AK140">
-        <v>0</v>
-      </c>
-      <c r="AL140">
-        <v>0</v>
-      </c>
-      <c r="AM140">
-        <v>-1</v>
-      </c>
-      <c r="AN140">
-        <v>-1</v>
-      </c>
-      <c r="AO140">
-        <v>-1</v>
-      </c>
-      <c r="AP140">
-        <v>-1</v>
-      </c>
-      <c r="AQ140">
-        <v>0</v>
-      </c>
-      <c r="AR140">
-        <v>0</v>
-      </c>
-      <c r="AS140">
-        <v>0</v>
-      </c>
-      <c r="AT140">
-        <v>0</v>
-      </c>
-      <c r="AU140" t="inlineStr">
-        <is>
-          <t>2026-10-16 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Gimnasia y Tiro</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>Atlanta</t>
-        </is>
-      </c>
-      <c r="G141">
-        <v>0</v>
-      </c>
-      <c r="H141">
-        <v>0</v>
-      </c>
-      <c r="I141">
-        <v>0</v>
-      </c>
-      <c r="J141">
-        <v>0</v>
-      </c>
-      <c r="K141">
-        <v>0</v>
-      </c>
-      <c r="L141">
-        <v>0</v>
-      </c>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N141">
-        <v>0</v>
-      </c>
-      <c r="O141">
-        <v>0</v>
-      </c>
-      <c r="P141">
-        <v>0</v>
-      </c>
-      <c r="Q141">
-        <v>0</v>
-      </c>
-      <c r="R141">
-        <v>0</v>
-      </c>
-      <c r="S141">
-        <v>0</v>
-      </c>
-      <c r="T141">
-        <v>0</v>
-      </c>
-      <c r="U141">
-        <v>0</v>
-      </c>
-      <c r="V141">
-        <v>0</v>
-      </c>
-      <c r="W141">
-        <v>0</v>
-      </c>
-      <c r="X141">
-        <v>0</v>
-      </c>
-      <c r="Y141">
-        <v>0</v>
-      </c>
-      <c r="Z141">
-        <v>0</v>
-      </c>
-      <c r="AA141">
-        <v>0</v>
-      </c>
-      <c r="AB141">
-        <v>0</v>
-      </c>
-      <c r="AC141">
-        <v>0</v>
-      </c>
-      <c r="AD141">
-        <v>0</v>
-      </c>
-      <c r="AE141">
-        <v>0</v>
-      </c>
-      <c r="AF141">
-        <v>0</v>
-      </c>
-      <c r="AG141">
-        <v>0</v>
-      </c>
-      <c r="AH141" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI141" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ141">
-        <v>0</v>
-      </c>
-      <c r="AK141">
-        <v>0</v>
-      </c>
-      <c r="AL141">
-        <v>0</v>
-      </c>
-      <c r="AM141">
-        <v>-1</v>
-      </c>
-      <c r="AN141">
-        <v>-1</v>
-      </c>
-      <c r="AO141">
-        <v>-1</v>
-      </c>
-      <c r="AP141">
-        <v>-1</v>
-      </c>
-      <c r="AQ141">
-        <v>0</v>
-      </c>
-      <c r="AR141">
-        <v>0</v>
-      </c>
-      <c r="AS141">
-        <v>0</v>
-      </c>
-      <c r="AT141">
-        <v>0</v>
-      </c>
-      <c r="AU141" t="inlineStr">
-        <is>
-          <t>2026-10-16 22:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Canada Canadian Premier League</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Vancouver FC</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>HFX Wanderers FC</t>
-        </is>
-      </c>
-      <c r="G142">
-        <v>0</v>
-      </c>
-      <c r="H142">
-        <v>0</v>
-      </c>
-      <c r="I142">
-        <v>0</v>
-      </c>
-      <c r="J142">
-        <v>0</v>
-      </c>
-      <c r="K142">
-        <v>0</v>
-      </c>
-      <c r="L142">
-        <v>0</v>
-      </c>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N142">
-        <v>0</v>
-      </c>
-      <c r="O142">
-        <v>0</v>
-      </c>
-      <c r="P142">
-        <v>0</v>
-      </c>
-      <c r="Q142">
-        <v>0</v>
-      </c>
-      <c r="R142">
-        <v>0</v>
-      </c>
-      <c r="S142">
-        <v>0</v>
-      </c>
-      <c r="T142">
-        <v>0</v>
-      </c>
-      <c r="U142">
-        <v>0</v>
-      </c>
-      <c r="V142">
-        <v>0</v>
-      </c>
-      <c r="W142">
-        <v>0</v>
-      </c>
-      <c r="X142">
-        <v>0</v>
-      </c>
-      <c r="Y142">
-        <v>0</v>
-      </c>
-      <c r="Z142">
-        <v>0</v>
-      </c>
-      <c r="AA142">
-        <v>0</v>
-      </c>
-      <c r="AB142">
-        <v>0</v>
-      </c>
-      <c r="AC142">
-        <v>0</v>
-      </c>
-      <c r="AD142">
-        <v>0</v>
-      </c>
-      <c r="AE142">
-        <v>0</v>
-      </c>
-      <c r="AF142">
-        <v>0</v>
-      </c>
-      <c r="AG142">
-        <v>0</v>
-      </c>
-      <c r="AH142" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI142" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ142">
-        <v>0</v>
-      </c>
-      <c r="AK142">
-        <v>0</v>
-      </c>
-      <c r="AL142">
-        <v>0</v>
-      </c>
-      <c r="AM142">
-        <v>-1</v>
-      </c>
-      <c r="AN142">
-        <v>-1</v>
-      </c>
-      <c r="AO142">
-        <v>-1</v>
-      </c>
-      <c r="AP142">
-        <v>-1</v>
-      </c>
-      <c r="AQ142">
-        <v>0</v>
-      </c>
-      <c r="AR142">
-        <v>0</v>
-      </c>
-      <c r="AS142">
-        <v>0</v>
-      </c>
-      <c r="AT142">
-        <v>0</v>
-      </c>
-      <c r="AU142" t="inlineStr">
         <is>
           <t>2026-10-16 23:00:00</t>
         </is>

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb II</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Dinamo Zagreb II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G23">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G108">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G109">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G114">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G120">

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Dinamo Zagreb II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb II</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G23">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G114">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G120">

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Adhyaksa</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Adhyaksa</t>
         </is>
       </c>
       <c r="G11">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G13">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G16">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb II</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Dinamo Zagreb II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G23">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G47">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G62">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G63">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G64">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G65">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G66">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G85">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G86">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G87">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G89">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G90">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G91">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G92">
@@ -19539,7 +19539,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N118">

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G65">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G66">
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>5.02</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O68">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="Q68">
         <v>0</v>
@@ -11438,10 +11438,10 @@
         <v>0</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE68">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G91">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G92">

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10617,10 +10617,10 @@
         <v>0</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC63">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -10780,10 +10780,10 @@
         <v>0</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G65">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G66">
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q79">
         <v>0</v>
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O84">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -14040,10 +14040,10 @@
         <v>0</v>
       </c>
       <c r="AA84">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC84">
         <v>0</v>
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O88">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q90">
         <v>0</v>
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>6.32</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Q91">
         <v>0</v>
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O92">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q92">
         <v>0</v>
@@ -15957,13 +15957,13 @@
         </is>
       </c>
       <c r="N96">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="O96">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P96">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q96">
         <v>0</v>
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O100">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="P100">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q100">
         <v>0</v>
@@ -16648,10 +16648,10 @@
         <v>0</v>
       </c>
       <c r="AA100">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB100">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC100">
         <v>0</v>

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU136"/>
+  <dimension ref="A1:AU131"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.81</v>
+        <v>2.07</v>
       </c>
       <c r="O62">
-        <v>3.13</v>
+        <v>3.52</v>
       </c>
       <c r="P62">
-        <v>2.51</v>
+        <v>3.31</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -10454,10 +10454,10 @@
         <v>0</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.07</v>
+        <v>2.69</v>
       </c>
       <c r="O63">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="P63">
-        <v>3.31</v>
+        <v>2.44</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10617,10 +10617,10 @@
         <v>0</v>
       </c>
       <c r="AA63">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AB63">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AC63">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="O64">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P64">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -10780,10 +10780,10 @@
         <v>0</v>
       </c>
       <c r="AA64">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB64">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G65">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -19175,22 +19175,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G116">
@@ -19338,22 +19338,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G117">
@@ -19501,22 +19501,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G118">
@@ -19539,7 +19539,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N118">
@@ -19664,22 +19664,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G119">
@@ -19827,22 +19827,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G120">
@@ -19990,22 +19990,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G121">
@@ -20153,7 +20153,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G122">
@@ -20316,7 +20316,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G123">
@@ -20479,7 +20479,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G124">
@@ -20642,7 +20642,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G125">
@@ -20805,22 +20805,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G129">
@@ -21452,27 +21452,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G130">
@@ -21603,7 +21603,7 @@
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>2026-10-16 21:00:00</t>
+          <t>2026-10-16 22:00:00</t>
         </is>
       </c>
     </row>
@@ -21615,27 +21615,27 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G131">
@@ -21765,821 +21765,6 @@
         <v>0</v>
       </c>
       <c r="AU131" t="inlineStr">
-        <is>
-          <t>2026-10-16 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Javor Ivanjica</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>Bor</t>
-        </is>
-      </c>
-      <c r="G132">
-        <v>0</v>
-      </c>
-      <c r="H132">
-        <v>0</v>
-      </c>
-      <c r="I132">
-        <v>0</v>
-      </c>
-      <c r="J132">
-        <v>0</v>
-      </c>
-      <c r="K132">
-        <v>0</v>
-      </c>
-      <c r="L132">
-        <v>0</v>
-      </c>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N132">
-        <v>0</v>
-      </c>
-      <c r="O132">
-        <v>0</v>
-      </c>
-      <c r="P132">
-        <v>0</v>
-      </c>
-      <c r="Q132">
-        <v>0</v>
-      </c>
-      <c r="R132">
-        <v>0</v>
-      </c>
-      <c r="S132">
-        <v>0</v>
-      </c>
-      <c r="T132">
-        <v>0</v>
-      </c>
-      <c r="U132">
-        <v>0</v>
-      </c>
-      <c r="V132">
-        <v>0</v>
-      </c>
-      <c r="W132">
-        <v>0</v>
-      </c>
-      <c r="X132">
-        <v>0</v>
-      </c>
-      <c r="Y132">
-        <v>0</v>
-      </c>
-      <c r="Z132">
-        <v>0</v>
-      </c>
-      <c r="AA132">
-        <v>0</v>
-      </c>
-      <c r="AB132">
-        <v>0</v>
-      </c>
-      <c r="AC132">
-        <v>0</v>
-      </c>
-      <c r="AD132">
-        <v>0</v>
-      </c>
-      <c r="AE132">
-        <v>0</v>
-      </c>
-      <c r="AF132">
-        <v>0</v>
-      </c>
-      <c r="AG132">
-        <v>0</v>
-      </c>
-      <c r="AH132" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI132" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ132">
-        <v>0</v>
-      </c>
-      <c r="AK132">
-        <v>0</v>
-      </c>
-      <c r="AL132">
-        <v>0</v>
-      </c>
-      <c r="AM132">
-        <v>-1</v>
-      </c>
-      <c r="AN132">
-        <v>-1</v>
-      </c>
-      <c r="AO132">
-        <v>-1</v>
-      </c>
-      <c r="AP132">
-        <v>-1</v>
-      </c>
-      <c r="AQ132">
-        <v>0</v>
-      </c>
-      <c r="AR132">
-        <v>0</v>
-      </c>
-      <c r="AS132">
-        <v>0</v>
-      </c>
-      <c r="AT132">
-        <v>0</v>
-      </c>
-      <c r="AU132" t="inlineStr">
-        <is>
-          <t>2026-10-16 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Jedinstvo Ub</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>Grafičar</t>
-        </is>
-      </c>
-      <c r="G133">
-        <v>0</v>
-      </c>
-      <c r="H133">
-        <v>0</v>
-      </c>
-      <c r="I133">
-        <v>0</v>
-      </c>
-      <c r="J133">
-        <v>0</v>
-      </c>
-      <c r="K133">
-        <v>0</v>
-      </c>
-      <c r="L133">
-        <v>0</v>
-      </c>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N133">
-        <v>0</v>
-      </c>
-      <c r="O133">
-        <v>0</v>
-      </c>
-      <c r="P133">
-        <v>0</v>
-      </c>
-      <c r="Q133">
-        <v>0</v>
-      </c>
-      <c r="R133">
-        <v>0</v>
-      </c>
-      <c r="S133">
-        <v>0</v>
-      </c>
-      <c r="T133">
-        <v>0</v>
-      </c>
-      <c r="U133">
-        <v>0</v>
-      </c>
-      <c r="V133">
-        <v>0</v>
-      </c>
-      <c r="W133">
-        <v>0</v>
-      </c>
-      <c r="X133">
-        <v>0</v>
-      </c>
-      <c r="Y133">
-        <v>0</v>
-      </c>
-      <c r="Z133">
-        <v>0</v>
-      </c>
-      <c r="AA133">
-        <v>0</v>
-      </c>
-      <c r="AB133">
-        <v>0</v>
-      </c>
-      <c r="AC133">
-        <v>0</v>
-      </c>
-      <c r="AD133">
-        <v>0</v>
-      </c>
-      <c r="AE133">
-        <v>0</v>
-      </c>
-      <c r="AF133">
-        <v>0</v>
-      </c>
-      <c r="AG133">
-        <v>0</v>
-      </c>
-      <c r="AH133" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI133" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ133">
-        <v>0</v>
-      </c>
-      <c r="AK133">
-        <v>0</v>
-      </c>
-      <c r="AL133">
-        <v>0</v>
-      </c>
-      <c r="AM133">
-        <v>-1</v>
-      </c>
-      <c r="AN133">
-        <v>-1</v>
-      </c>
-      <c r="AO133">
-        <v>-1</v>
-      </c>
-      <c r="AP133">
-        <v>-1</v>
-      </c>
-      <c r="AQ133">
-        <v>0</v>
-      </c>
-      <c r="AR133">
-        <v>0</v>
-      </c>
-      <c r="AS133">
-        <v>0</v>
-      </c>
-      <c r="AT133">
-        <v>0</v>
-      </c>
-      <c r="AU133" t="inlineStr">
-        <is>
-          <t>2026-10-16 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Semendrija 1924</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>Naftagas</t>
-        </is>
-      </c>
-      <c r="G134">
-        <v>0</v>
-      </c>
-      <c r="H134">
-        <v>0</v>
-      </c>
-      <c r="I134">
-        <v>0</v>
-      </c>
-      <c r="J134">
-        <v>0</v>
-      </c>
-      <c r="K134">
-        <v>0</v>
-      </c>
-      <c r="L134">
-        <v>0</v>
-      </c>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N134">
-        <v>0</v>
-      </c>
-      <c r="O134">
-        <v>0</v>
-      </c>
-      <c r="P134">
-        <v>0</v>
-      </c>
-      <c r="Q134">
-        <v>0</v>
-      </c>
-      <c r="R134">
-        <v>0</v>
-      </c>
-      <c r="S134">
-        <v>0</v>
-      </c>
-      <c r="T134">
-        <v>0</v>
-      </c>
-      <c r="U134">
-        <v>0</v>
-      </c>
-      <c r="V134">
-        <v>0</v>
-      </c>
-      <c r="W134">
-        <v>0</v>
-      </c>
-      <c r="X134">
-        <v>0</v>
-      </c>
-      <c r="Y134">
-        <v>0</v>
-      </c>
-      <c r="Z134">
-        <v>0</v>
-      </c>
-      <c r="AA134">
-        <v>0</v>
-      </c>
-      <c r="AB134">
-        <v>0</v>
-      </c>
-      <c r="AC134">
-        <v>0</v>
-      </c>
-      <c r="AD134">
-        <v>0</v>
-      </c>
-      <c r="AE134">
-        <v>0</v>
-      </c>
-      <c r="AF134">
-        <v>0</v>
-      </c>
-      <c r="AG134">
-        <v>0</v>
-      </c>
-      <c r="AH134" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI134" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ134">
-        <v>0</v>
-      </c>
-      <c r="AK134">
-        <v>0</v>
-      </c>
-      <c r="AL134">
-        <v>0</v>
-      </c>
-      <c r="AM134">
-        <v>-1</v>
-      </c>
-      <c r="AN134">
-        <v>-1</v>
-      </c>
-      <c r="AO134">
-        <v>-1</v>
-      </c>
-      <c r="AP134">
-        <v>-1</v>
-      </c>
-      <c r="AQ134">
-        <v>0</v>
-      </c>
-      <c r="AR134">
-        <v>0</v>
-      </c>
-      <c r="AS134">
-        <v>0</v>
-      </c>
-      <c r="AT134">
-        <v>0</v>
-      </c>
-      <c r="AU134" t="inlineStr">
-        <is>
-          <t>2026-10-16 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Gimnasia y Tiro</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>Atlanta</t>
-        </is>
-      </c>
-      <c r="G135">
-        <v>0</v>
-      </c>
-      <c r="H135">
-        <v>0</v>
-      </c>
-      <c r="I135">
-        <v>0</v>
-      </c>
-      <c r="J135">
-        <v>0</v>
-      </c>
-      <c r="K135">
-        <v>0</v>
-      </c>
-      <c r="L135">
-        <v>0</v>
-      </c>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N135">
-        <v>0</v>
-      </c>
-      <c r="O135">
-        <v>0</v>
-      </c>
-      <c r="P135">
-        <v>0</v>
-      </c>
-      <c r="Q135">
-        <v>0</v>
-      </c>
-      <c r="R135">
-        <v>0</v>
-      </c>
-      <c r="S135">
-        <v>0</v>
-      </c>
-      <c r="T135">
-        <v>0</v>
-      </c>
-      <c r="U135">
-        <v>0</v>
-      </c>
-      <c r="V135">
-        <v>0</v>
-      </c>
-      <c r="W135">
-        <v>0</v>
-      </c>
-      <c r="X135">
-        <v>0</v>
-      </c>
-      <c r="Y135">
-        <v>0</v>
-      </c>
-      <c r="Z135">
-        <v>0</v>
-      </c>
-      <c r="AA135">
-        <v>0</v>
-      </c>
-      <c r="AB135">
-        <v>0</v>
-      </c>
-      <c r="AC135">
-        <v>0</v>
-      </c>
-      <c r="AD135">
-        <v>0</v>
-      </c>
-      <c r="AE135">
-        <v>0</v>
-      </c>
-      <c r="AF135">
-        <v>0</v>
-      </c>
-      <c r="AG135">
-        <v>0</v>
-      </c>
-      <c r="AH135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ135">
-        <v>0</v>
-      </c>
-      <c r="AK135">
-        <v>0</v>
-      </c>
-      <c r="AL135">
-        <v>0</v>
-      </c>
-      <c r="AM135">
-        <v>-1</v>
-      </c>
-      <c r="AN135">
-        <v>-1</v>
-      </c>
-      <c r="AO135">
-        <v>-1</v>
-      </c>
-      <c r="AP135">
-        <v>-1</v>
-      </c>
-      <c r="AQ135">
-        <v>0</v>
-      </c>
-      <c r="AR135">
-        <v>0</v>
-      </c>
-      <c r="AS135">
-        <v>0</v>
-      </c>
-      <c r="AT135">
-        <v>0</v>
-      </c>
-      <c r="AU135" t="inlineStr">
-        <is>
-          <t>2026-10-16 22:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Canada Canadian Premier League</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Vancouver FC</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>HFX Wanderers FC</t>
-        </is>
-      </c>
-      <c r="G136">
-        <v>0</v>
-      </c>
-      <c r="H136">
-        <v>0</v>
-      </c>
-      <c r="I136">
-        <v>0</v>
-      </c>
-      <c r="J136">
-        <v>0</v>
-      </c>
-      <c r="K136">
-        <v>0</v>
-      </c>
-      <c r="L136">
-        <v>0</v>
-      </c>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N136">
-        <v>0</v>
-      </c>
-      <c r="O136">
-        <v>0</v>
-      </c>
-      <c r="P136">
-        <v>0</v>
-      </c>
-      <c r="Q136">
-        <v>0</v>
-      </c>
-      <c r="R136">
-        <v>0</v>
-      </c>
-      <c r="S136">
-        <v>0</v>
-      </c>
-      <c r="T136">
-        <v>0</v>
-      </c>
-      <c r="U136">
-        <v>0</v>
-      </c>
-      <c r="V136">
-        <v>0</v>
-      </c>
-      <c r="W136">
-        <v>0</v>
-      </c>
-      <c r="X136">
-        <v>0</v>
-      </c>
-      <c r="Y136">
-        <v>0</v>
-      </c>
-      <c r="Z136">
-        <v>0</v>
-      </c>
-      <c r="AA136">
-        <v>0</v>
-      </c>
-      <c r="AB136">
-        <v>0</v>
-      </c>
-      <c r="AC136">
-        <v>0</v>
-      </c>
-      <c r="AD136">
-        <v>0</v>
-      </c>
-      <c r="AE136">
-        <v>0</v>
-      </c>
-      <c r="AF136">
-        <v>0</v>
-      </c>
-      <c r="AG136">
-        <v>0</v>
-      </c>
-      <c r="AH136" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI136" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ136">
-        <v>0</v>
-      </c>
-      <c r="AK136">
-        <v>0</v>
-      </c>
-      <c r="AL136">
-        <v>0</v>
-      </c>
-      <c r="AM136">
-        <v>-1</v>
-      </c>
-      <c r="AN136">
-        <v>-1</v>
-      </c>
-      <c r="AO136">
-        <v>-1</v>
-      </c>
-      <c r="AP136">
-        <v>-1</v>
-      </c>
-      <c r="AQ136">
-        <v>0</v>
-      </c>
-      <c r="AR136">
-        <v>0</v>
-      </c>
-      <c r="AS136">
-        <v>0</v>
-      </c>
-      <c r="AT136">
-        <v>0</v>
-      </c>
-      <c r="AU136" t="inlineStr">
         <is>
           <t>2026-10-16 23:00:00</t>
         </is>

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>3.46</v>
+        <v>6.32</v>
       </c>
       <c r="O90">
-        <v>3.54</v>
+        <v>4.55</v>
       </c>
       <c r="P90">
-        <v>1.87</v>
+        <v>1.37</v>
       </c>
       <c r="Q90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>6.32</v>
+        <v>2.8</v>
       </c>
       <c r="O91">
-        <v>4.55</v>
+        <v>3.38</v>
       </c>
       <c r="P91">
-        <v>1.37</v>
+        <v>2.21</v>
       </c>
       <c r="Q91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.8</v>
+        <v>3.46</v>
       </c>
       <c r="O92">
-        <v>3.38</v>
+        <v>3.54</v>
       </c>
       <c r="P92">
-        <v>2.21</v>
+        <v>1.87</v>
       </c>
       <c r="Q92">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G103">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G104">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G105">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G106">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G114">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G116">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G118">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G120">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G123">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G126">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G129">

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU131"/>
+  <dimension ref="A1:AU129"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G118">
@@ -19664,22 +19664,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,13 +19706,13 @@
         </is>
       </c>
       <c r="N119">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O119">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P119">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="Q119">
         <v>0</v>
@@ -19827,7 +19827,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G120">
@@ -19990,22 +19990,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G123">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G127">
@@ -21126,27 +21126,27 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G128">
@@ -21277,7 +21277,7 @@
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>2026-10-16 21:00:00</t>
+          <t>2026-10-16 22:00:00</t>
         </is>
       </c>
     </row>
@@ -21289,27 +21289,27 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G129">
@@ -21439,332 +21439,6 @@
         <v>0</v>
       </c>
       <c r="AU129" t="inlineStr">
-        <is>
-          <t>2026-10-16 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>Gimnasia y Tiro</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>Atlanta</t>
-        </is>
-      </c>
-      <c r="G130">
-        <v>0</v>
-      </c>
-      <c r="H130">
-        <v>0</v>
-      </c>
-      <c r="I130">
-        <v>0</v>
-      </c>
-      <c r="J130">
-        <v>0</v>
-      </c>
-      <c r="K130">
-        <v>0</v>
-      </c>
-      <c r="L130">
-        <v>0</v>
-      </c>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N130">
-        <v>0</v>
-      </c>
-      <c r="O130">
-        <v>0</v>
-      </c>
-      <c r="P130">
-        <v>0</v>
-      </c>
-      <c r="Q130">
-        <v>0</v>
-      </c>
-      <c r="R130">
-        <v>0</v>
-      </c>
-      <c r="S130">
-        <v>0</v>
-      </c>
-      <c r="T130">
-        <v>0</v>
-      </c>
-      <c r="U130">
-        <v>0</v>
-      </c>
-      <c r="V130">
-        <v>0</v>
-      </c>
-      <c r="W130">
-        <v>0</v>
-      </c>
-      <c r="X130">
-        <v>0</v>
-      </c>
-      <c r="Y130">
-        <v>0</v>
-      </c>
-      <c r="Z130">
-        <v>0</v>
-      </c>
-      <c r="AA130">
-        <v>0</v>
-      </c>
-      <c r="AB130">
-        <v>0</v>
-      </c>
-      <c r="AC130">
-        <v>0</v>
-      </c>
-      <c r="AD130">
-        <v>0</v>
-      </c>
-      <c r="AE130">
-        <v>0</v>
-      </c>
-      <c r="AF130">
-        <v>0</v>
-      </c>
-      <c r="AG130">
-        <v>0</v>
-      </c>
-      <c r="AH130" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI130" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ130">
-        <v>0</v>
-      </c>
-      <c r="AK130">
-        <v>0</v>
-      </c>
-      <c r="AL130">
-        <v>0</v>
-      </c>
-      <c r="AM130">
-        <v>-1</v>
-      </c>
-      <c r="AN130">
-        <v>-1</v>
-      </c>
-      <c r="AO130">
-        <v>-1</v>
-      </c>
-      <c r="AP130">
-        <v>-1</v>
-      </c>
-      <c r="AQ130">
-        <v>0</v>
-      </c>
-      <c r="AR130">
-        <v>0</v>
-      </c>
-      <c r="AS130">
-        <v>0</v>
-      </c>
-      <c r="AT130">
-        <v>0</v>
-      </c>
-      <c r="AU130" t="inlineStr">
-        <is>
-          <t>2026-10-16 22:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Canada Canadian Premier League</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>Vancouver FC</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>HFX Wanderers FC</t>
-        </is>
-      </c>
-      <c r="G131">
-        <v>0</v>
-      </c>
-      <c r="H131">
-        <v>0</v>
-      </c>
-      <c r="I131">
-        <v>0</v>
-      </c>
-      <c r="J131">
-        <v>0</v>
-      </c>
-      <c r="K131">
-        <v>0</v>
-      </c>
-      <c r="L131">
-        <v>0</v>
-      </c>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N131">
-        <v>0</v>
-      </c>
-      <c r="O131">
-        <v>0</v>
-      </c>
-      <c r="P131">
-        <v>0</v>
-      </c>
-      <c r="Q131">
-        <v>0</v>
-      </c>
-      <c r="R131">
-        <v>0</v>
-      </c>
-      <c r="S131">
-        <v>0</v>
-      </c>
-      <c r="T131">
-        <v>0</v>
-      </c>
-      <c r="U131">
-        <v>0</v>
-      </c>
-      <c r="V131">
-        <v>0</v>
-      </c>
-      <c r="W131">
-        <v>0</v>
-      </c>
-      <c r="X131">
-        <v>0</v>
-      </c>
-      <c r="Y131">
-        <v>0</v>
-      </c>
-      <c r="Z131">
-        <v>0</v>
-      </c>
-      <c r="AA131">
-        <v>0</v>
-      </c>
-      <c r="AB131">
-        <v>0</v>
-      </c>
-      <c r="AC131">
-        <v>0</v>
-      </c>
-      <c r="AD131">
-        <v>0</v>
-      </c>
-      <c r="AE131">
-        <v>0</v>
-      </c>
-      <c r="AF131">
-        <v>0</v>
-      </c>
-      <c r="AG131">
-        <v>0</v>
-      </c>
-      <c r="AH131" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI131" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ131">
-        <v>0</v>
-      </c>
-      <c r="AK131">
-        <v>0</v>
-      </c>
-      <c r="AL131">
-        <v>0</v>
-      </c>
-      <c r="AM131">
-        <v>-1</v>
-      </c>
-      <c r="AN131">
-        <v>-1</v>
-      </c>
-      <c r="AO131">
-        <v>-1</v>
-      </c>
-      <c r="AP131">
-        <v>-1</v>
-      </c>
-      <c r="AQ131">
-        <v>0</v>
-      </c>
-      <c r="AR131">
-        <v>0</v>
-      </c>
-      <c r="AS131">
-        <v>0</v>
-      </c>
-      <c r="AT131">
-        <v>0</v>
-      </c>
-      <c r="AU131" t="inlineStr">
         <is>
           <t>2026-10-16 23:00:00</t>
         </is>

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q54">
         <v>0</v>

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -13714,10 +13714,10 @@
         <v>0</v>
       </c>
       <c r="AA82">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC82">
         <v>0</v>

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU129"/>
+  <dimension ref="A1:AU127"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8667,10 +8667,10 @@
         <v>0</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE51">
         <v>0</v>
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -12736,10 +12736,10 @@
         <v>0</v>
       </c>
       <c r="AA76">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC76">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G116">
@@ -19338,22 +19338,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O117">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P117">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="Q117">
         <v>0</v>
@@ -19501,7 +19501,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G118">
@@ -19664,22 +19664,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,13 +19706,13 @@
         </is>
       </c>
       <c r="N119">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O119">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="P119">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="Q119">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G123">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G125">
@@ -20800,27 +20800,27 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G126">
@@ -20951,7 +20951,7 @@
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>2026-10-16 21:00:00</t>
+          <t>2026-10-16 22:00:00</t>
         </is>
       </c>
     </row>
@@ -20963,27 +20963,27 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G127">
@@ -21113,332 +21113,6 @@
         <v>0</v>
       </c>
       <c r="AU127" t="inlineStr">
-        <is>
-          <t>2026-10-16 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>Gimnasia y Tiro</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Atlanta</t>
-        </is>
-      </c>
-      <c r="G128">
-        <v>0</v>
-      </c>
-      <c r="H128">
-        <v>0</v>
-      </c>
-      <c r="I128">
-        <v>0</v>
-      </c>
-      <c r="J128">
-        <v>0</v>
-      </c>
-      <c r="K128">
-        <v>0</v>
-      </c>
-      <c r="L128">
-        <v>0</v>
-      </c>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N128">
-        <v>0</v>
-      </c>
-      <c r="O128">
-        <v>0</v>
-      </c>
-      <c r="P128">
-        <v>0</v>
-      </c>
-      <c r="Q128">
-        <v>0</v>
-      </c>
-      <c r="R128">
-        <v>0</v>
-      </c>
-      <c r="S128">
-        <v>0</v>
-      </c>
-      <c r="T128">
-        <v>0</v>
-      </c>
-      <c r="U128">
-        <v>0</v>
-      </c>
-      <c r="V128">
-        <v>0</v>
-      </c>
-      <c r="W128">
-        <v>0</v>
-      </c>
-      <c r="X128">
-        <v>0</v>
-      </c>
-      <c r="Y128">
-        <v>0</v>
-      </c>
-      <c r="Z128">
-        <v>0</v>
-      </c>
-      <c r="AA128">
-        <v>0</v>
-      </c>
-      <c r="AB128">
-        <v>0</v>
-      </c>
-      <c r="AC128">
-        <v>0</v>
-      </c>
-      <c r="AD128">
-        <v>0</v>
-      </c>
-      <c r="AE128">
-        <v>0</v>
-      </c>
-      <c r="AF128">
-        <v>0</v>
-      </c>
-      <c r="AG128">
-        <v>0</v>
-      </c>
-      <c r="AH128" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI128" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ128">
-        <v>0</v>
-      </c>
-      <c r="AK128">
-        <v>0</v>
-      </c>
-      <c r="AL128">
-        <v>0</v>
-      </c>
-      <c r="AM128">
-        <v>-1</v>
-      </c>
-      <c r="AN128">
-        <v>-1</v>
-      </c>
-      <c r="AO128">
-        <v>-1</v>
-      </c>
-      <c r="AP128">
-        <v>-1</v>
-      </c>
-      <c r="AQ128">
-        <v>0</v>
-      </c>
-      <c r="AR128">
-        <v>0</v>
-      </c>
-      <c r="AS128">
-        <v>0</v>
-      </c>
-      <c r="AT128">
-        <v>0</v>
-      </c>
-      <c r="AU128" t="inlineStr">
-        <is>
-          <t>2026-10-16 22:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Canada Canadian Premier League</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Vancouver FC</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>HFX Wanderers FC</t>
-        </is>
-      </c>
-      <c r="G129">
-        <v>0</v>
-      </c>
-      <c r="H129">
-        <v>0</v>
-      </c>
-      <c r="I129">
-        <v>0</v>
-      </c>
-      <c r="J129">
-        <v>0</v>
-      </c>
-      <c r="K129">
-        <v>0</v>
-      </c>
-      <c r="L129">
-        <v>0</v>
-      </c>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N129">
-        <v>0</v>
-      </c>
-      <c r="O129">
-        <v>0</v>
-      </c>
-      <c r="P129">
-        <v>0</v>
-      </c>
-      <c r="Q129">
-        <v>0</v>
-      </c>
-      <c r="R129">
-        <v>0</v>
-      </c>
-      <c r="S129">
-        <v>0</v>
-      </c>
-      <c r="T129">
-        <v>0</v>
-      </c>
-      <c r="U129">
-        <v>0</v>
-      </c>
-      <c r="V129">
-        <v>0</v>
-      </c>
-      <c r="W129">
-        <v>0</v>
-      </c>
-      <c r="X129">
-        <v>0</v>
-      </c>
-      <c r="Y129">
-        <v>0</v>
-      </c>
-      <c r="Z129">
-        <v>0</v>
-      </c>
-      <c r="AA129">
-        <v>0</v>
-      </c>
-      <c r="AB129">
-        <v>0</v>
-      </c>
-      <c r="AC129">
-        <v>0</v>
-      </c>
-      <c r="AD129">
-        <v>0</v>
-      </c>
-      <c r="AE129">
-        <v>0</v>
-      </c>
-      <c r="AF129">
-        <v>0</v>
-      </c>
-      <c r="AG129">
-        <v>0</v>
-      </c>
-      <c r="AH129" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI129" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ129">
-        <v>0</v>
-      </c>
-      <c r="AK129">
-        <v>0</v>
-      </c>
-      <c r="AL129">
-        <v>0</v>
-      </c>
-      <c r="AM129">
-        <v>-1</v>
-      </c>
-      <c r="AN129">
-        <v>-1</v>
-      </c>
-      <c r="AO129">
-        <v>-1</v>
-      </c>
-      <c r="AP129">
-        <v>-1</v>
-      </c>
-      <c r="AQ129">
-        <v>0</v>
-      </c>
-      <c r="AR129">
-        <v>0</v>
-      </c>
-      <c r="AS129">
-        <v>0</v>
-      </c>
-      <c r="AT129">
-        <v>0</v>
-      </c>
-      <c r="AU129" t="inlineStr">
         <is>
           <t>2026-10-16 23:00:00</t>
         </is>

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G16">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G26">

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G9">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G10">

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -807,34 +807,34 @@
         <v>4.35</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA3">
         <v>1.63</v>
@@ -843,19 +843,19 @@
         <v>2.1</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1785,55 +1785,55 @@
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G26">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G45">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="O51">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P51">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8667,10 +8667,10 @@
         <v>0</v>
       </c>
       <c r="AC51">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD51">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -8830,10 +8830,10 @@
         <v>0</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE52">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G69">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G70">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G71">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G72">

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -1296,55 +1296,55 @@
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>5.87</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9645,10 +9645,10 @@
         <v>0</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE57">
         <v>0</v>
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O78">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q78">
         <v>0</v>
@@ -13062,10 +13062,10 @@
         <v>0</v>
       </c>
       <c r="AA78">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB78">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC78">
         <v>0</v>

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G12">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G13">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G16">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G108">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G109">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G112">

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU127"/>
+  <dimension ref="A1:AU126"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -644,55 +644,55 @@
         <v>2.88</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X21">
         <v>0</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5697,55 +5697,55 @@
         <v>5.36</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6023,55 +6023,55 @@
         <v>1.8</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6340,34 +6340,34 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X37">
         <v>0</v>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6512,55 +6512,55 @@
         <v>3.09</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6675,55 +6675,55 @@
         <v>2.98</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7164,55 +7164,55 @@
         <v>2.61</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.18</v>
+        <v>3.2</v>
       </c>
       <c r="O49">
+        <v>3.64</v>
+      </c>
+      <c r="P49">
+        <v>2.03</v>
+      </c>
+      <c r="Q49">
         <v>3.62</v>
       </c>
-      <c r="P49">
-        <v>2.9</v>
-      </c>
-      <c r="Q49">
-        <v>0</v>
-      </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O50">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="P50">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8794,40 +8794,40 @@
         <v>1.93</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AC52">
         <v>1.98</v>
@@ -8836,13 +8836,13 @@
         <v>1.72</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9120,55 +9120,55 @@
         <v>1.8</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z56">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK56">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9772,55 +9772,55 @@
         <v>2.38</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK58">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9935,55 +9935,55 @@
         <v>9.300000000000001</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10261,55 +10261,55 @@
         <v>2.72</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y61">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA61">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK61">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10424,34 +10424,34 @@
         <v>3.31</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA62">
         <v>1.8</v>
@@ -10460,19 +10460,19 @@
         <v>2</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK62">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.69</v>
+        <v>2.16</v>
       </c>
       <c r="O63">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="P63">
-        <v>2.44</v>
+        <v>3.31</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AA63">
-        <v>1.88</v>
+        <v>2.14</v>
       </c>
       <c r="AB63">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.16</v>
+        <v>2.69</v>
       </c>
       <c r="O64">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="P64">
-        <v>3.31</v>
+        <v>2.44</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK64">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="Q65">
         <v>0</v>
@@ -11076,55 +11076,55 @@
         <v>2.51</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S66">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T66">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U66">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V66">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W66">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X66">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y66">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z66">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC66">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD66">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE66">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF66">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK66">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11402,40 +11402,40 @@
         <v>4.07</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC68">
         <v>2</v>
@@ -11444,13 +11444,13 @@
         <v>1.71</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK68">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>5.66</v>
       </c>
       <c r="O69">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S69">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T69">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U69">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V69">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W69">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X69">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y69">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z69">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AA69">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD69">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE69">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF69">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG69">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK69">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T70">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U70">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V70">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W70">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X70">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z70">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC70">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD70">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE70">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF70">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK70">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q71">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R71">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S71">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T71">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="U71">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V71">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W71">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X71">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y71">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z71">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AA71">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AB71">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="AC71">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD71">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AE71">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF71">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG71">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK71">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O72">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q72">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S72">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T72">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U72">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V72">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W72">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X72">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y72">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z72">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA72">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AC72">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD72">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE72">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF72">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG72">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK72">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O73">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S73">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T73">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U73">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="V73">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W73">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X73">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z73">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA73">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB73">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC73">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD73">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE73">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF73">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG73">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK73">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P75">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q75">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R75">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S75">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T75">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U75">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="V75">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W75">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y75">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z75">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA75">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC75">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD75">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF75">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG75">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK75">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12706,34 +12706,34 @@
         <v>1.73</v>
       </c>
       <c r="Q76">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="R76">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S76">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T76">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U76">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V76">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W76">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X76">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y76">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z76">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA76">
         <v>1.9</v>
@@ -12742,19 +12742,19 @@
         <v>1.9</v>
       </c>
       <c r="AC76">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD76">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF76">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG76">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK76">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -13032,34 +13032,34 @@
         <v>2.88</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S78">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T78">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U78">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V78">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W78">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y78">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z78">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA78">
         <v>1.78</v>
@@ -13068,19 +13068,19 @@
         <v>1.9</v>
       </c>
       <c r="AC78">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AD78">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF78">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG78">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK78">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13195,55 +13195,55 @@
         <v>2.98</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R79">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S79">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T79">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U79">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V79">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W79">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y79">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z79">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC79">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD79">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF79">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG79">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK79">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13521,40 +13521,40 @@
         <v>3.55</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T81">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U81">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V81">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="W81">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X81">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z81">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AA81">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AC81">
         <v>1.95</v>
@@ -13563,13 +13563,13 @@
         <v>1.77</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG81">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK81">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13684,34 +13684,34 @@
         <v>2.74</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S82">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T82">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U82">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V82">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W82">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X82">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z82">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA82">
         <v>1.98</v>
@@ -13720,19 +13720,19 @@
         <v>1.79</v>
       </c>
       <c r="AC82">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD82">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG82">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK82">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13847,55 +13847,55 @@
         <v>2.13</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W83">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG83">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK83">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -15477,55 +15477,55 @@
         <v>3</v>
       </c>
       <c r="Q93">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R93">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S93">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T93">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U93">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V93">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W93">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X93">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y93">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z93">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA93">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB93">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AC93">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD93">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE93">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF93">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG93">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK93">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15803,55 +15803,55 @@
         <v>0</v>
       </c>
       <c r="Q95">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="R95">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S95">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T95">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U95">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V95">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W95">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X95">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y95">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z95">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA95">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB95">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC95">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="AD95">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE95">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF95">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG95">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK95">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O97">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G109">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G114">
@@ -19175,22 +19175,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O116">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P116">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -19338,22 +19338,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O117">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="P117">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="Q117">
         <v>0</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G124">
@@ -20637,27 +20637,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G125">
@@ -20788,7 +20788,7 @@
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>2026-10-16 21:00:00</t>
+          <t>2026-10-16 22:00:00</t>
         </is>
       </c>
     </row>
@@ -20800,12 +20800,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G126">
@@ -20950,169 +20950,6 @@
         <v>0</v>
       </c>
       <c r="AU126" t="inlineStr">
-        <is>
-          <t>2026-10-16 22:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Canada Canadian Premier League</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>Vancouver FC</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>HFX Wanderers FC</t>
-        </is>
-      </c>
-      <c r="G127">
-        <v>0</v>
-      </c>
-      <c r="H127">
-        <v>0</v>
-      </c>
-      <c r="I127">
-        <v>0</v>
-      </c>
-      <c r="J127">
-        <v>0</v>
-      </c>
-      <c r="K127">
-        <v>0</v>
-      </c>
-      <c r="L127">
-        <v>0</v>
-      </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N127">
-        <v>0</v>
-      </c>
-      <c r="O127">
-        <v>0</v>
-      </c>
-      <c r="P127">
-        <v>0</v>
-      </c>
-      <c r="Q127">
-        <v>0</v>
-      </c>
-      <c r="R127">
-        <v>0</v>
-      </c>
-      <c r="S127">
-        <v>0</v>
-      </c>
-      <c r="T127">
-        <v>0</v>
-      </c>
-      <c r="U127">
-        <v>0</v>
-      </c>
-      <c r="V127">
-        <v>0</v>
-      </c>
-      <c r="W127">
-        <v>0</v>
-      </c>
-      <c r="X127">
-        <v>0</v>
-      </c>
-      <c r="Y127">
-        <v>0</v>
-      </c>
-      <c r="Z127">
-        <v>0</v>
-      </c>
-      <c r="AA127">
-        <v>0</v>
-      </c>
-      <c r="AB127">
-        <v>0</v>
-      </c>
-      <c r="AC127">
-        <v>0</v>
-      </c>
-      <c r="AD127">
-        <v>0</v>
-      </c>
-      <c r="AE127">
-        <v>0</v>
-      </c>
-      <c r="AF127">
-        <v>0</v>
-      </c>
-      <c r="AG127">
-        <v>0</v>
-      </c>
-      <c r="AH127" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI127" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ127">
-        <v>0</v>
-      </c>
-      <c r="AK127">
-        <v>0</v>
-      </c>
-      <c r="AL127">
-        <v>0</v>
-      </c>
-      <c r="AM127">
-        <v>-1</v>
-      </c>
-      <c r="AN127">
-        <v>-1</v>
-      </c>
-      <c r="AO127">
-        <v>-1</v>
-      </c>
-      <c r="AP127">
-        <v>-1</v>
-      </c>
-      <c r="AQ127">
-        <v>0</v>
-      </c>
-      <c r="AR127">
-        <v>0</v>
-      </c>
-      <c r="AS127">
-        <v>0</v>
-      </c>
-      <c r="AT127">
-        <v>0</v>
-      </c>
-      <c r="AU127" t="inlineStr">
         <is>
           <t>2026-10-16 23:00:00</t>
         </is>

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -9609,40 +9609,40 @@
         <v>1.46</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z57">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AC57">
         <v>2.2</v>
@@ -9651,13 +9651,13 @@
         <v>1.58</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF57">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG57">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK57">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.74</v>
+        <v>2.81</v>
       </c>
       <c r="O65">
-        <v>3.7</v>
+        <v>3.13</v>
       </c>
       <c r="P65">
-        <v>4.38</v>
+        <v>2.51</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.81</v>
+        <v>1.74</v>
       </c>
       <c r="O66">
-        <v>3.13</v>
+        <v>3.7</v>
       </c>
       <c r="P66">
-        <v>2.51</v>
+        <v>4.38</v>
       </c>
       <c r="Q66">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="R66">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S66">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T66">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U66">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V66">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W66">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X66">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y66">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z66">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AA66">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AB66">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC66">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD66">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE66">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF66">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG66">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK66">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,80 +11556,80 @@
         </is>
       </c>
       <c r="N69">
-        <v>5.66</v>
+        <v>3.35</v>
       </c>
       <c r="O69">
+        <v>3.8</v>
+      </c>
+      <c r="P69">
+        <v>1.92</v>
+      </c>
+      <c r="Q69">
+        <v>3.5</v>
+      </c>
+      <c r="R69">
+        <v>2.45</v>
+      </c>
+      <c r="S69">
+        <v>1.25</v>
+      </c>
+      <c r="T69">
+        <v>3.7</v>
+      </c>
+      <c r="U69">
+        <v>2.2</v>
+      </c>
+      <c r="V69">
+        <v>1.62</v>
+      </c>
+      <c r="W69">
+        <v>1.15</v>
+      </c>
+      <c r="X69">
+        <v>1.02</v>
+      </c>
+      <c r="Y69">
+        <v>1.12</v>
+      </c>
+      <c r="Z69">
         <v>4.7</v>
       </c>
-      <c r="P69">
-        <v>1.45</v>
-      </c>
-      <c r="Q69">
-        <v>5</v>
-      </c>
-      <c r="R69">
-        <v>2.62</v>
-      </c>
-      <c r="S69">
-        <v>1.17</v>
-      </c>
-      <c r="T69">
-        <v>4</v>
-      </c>
-      <c r="U69">
-        <v>1.95</v>
-      </c>
-      <c r="V69">
-        <v>1.72</v>
-      </c>
-      <c r="W69">
+      <c r="AA69">
+        <v>1.47</v>
+      </c>
+      <c r="AB69">
+        <v>2.35</v>
+      </c>
+      <c r="AC69">
+        <v>2.27</v>
+      </c>
+      <c r="AD69">
+        <v>1.58</v>
+      </c>
+      <c r="AE69">
         <v>1.2</v>
       </c>
-      <c r="X69">
-        <v>1.01</v>
-      </c>
-      <c r="Y69">
-        <v>1.08</v>
-      </c>
-      <c r="Z69">
-        <v>5.65</v>
-      </c>
-      <c r="AA69">
-        <v>1.35</v>
-      </c>
-      <c r="AB69">
-        <v>2.74</v>
-      </c>
-      <c r="AC69">
-        <v>1.98</v>
-      </c>
-      <c r="AD69">
-        <v>1.76</v>
-      </c>
-      <c r="AE69">
+      <c r="AF69">
+        <v>1.44</v>
+      </c>
+      <c r="AG69">
+        <v>2.5</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ69">
+        <v>1.22</v>
+      </c>
+      <c r="AK69">
         <v>1.28</v>
-      </c>
-      <c r="AF69">
-        <v>1.5</v>
-      </c>
-      <c r="AG69">
-        <v>2.45</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ69">
-        <v>1.18</v>
-      </c>
-      <c r="AK69">
-        <v>1.12</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,80 +11719,80 @@
         </is>
       </c>
       <c r="N70">
-        <v>3.35</v>
+        <v>5.66</v>
       </c>
       <c r="O70">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="P70">
-        <v>1.92</v>
+        <v>1.45</v>
       </c>
       <c r="Q70">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="R70">
+        <v>2.62</v>
+      </c>
+      <c r="S70">
+        <v>1.17</v>
+      </c>
+      <c r="T70">
+        <v>4</v>
+      </c>
+      <c r="U70">
+        <v>1.95</v>
+      </c>
+      <c r="V70">
+        <v>1.72</v>
+      </c>
+      <c r="W70">
+        <v>1.2</v>
+      </c>
+      <c r="X70">
+        <v>1.01</v>
+      </c>
+      <c r="Y70">
+        <v>1.08</v>
+      </c>
+      <c r="Z70">
+        <v>5.65</v>
+      </c>
+      <c r="AA70">
+        <v>1.35</v>
+      </c>
+      <c r="AB70">
+        <v>2.74</v>
+      </c>
+      <c r="AC70">
+        <v>1.98</v>
+      </c>
+      <c r="AD70">
+        <v>1.76</v>
+      </c>
+      <c r="AE70">
+        <v>1.28</v>
+      </c>
+      <c r="AF70">
+        <v>1.5</v>
+      </c>
+      <c r="AG70">
         <v>2.45</v>
       </c>
-      <c r="S70">
-        <v>1.25</v>
-      </c>
-      <c r="T70">
-        <v>3.7</v>
-      </c>
-      <c r="U70">
-        <v>2.2</v>
-      </c>
-      <c r="V70">
-        <v>1.62</v>
-      </c>
-      <c r="W70">
-        <v>1.15</v>
-      </c>
-      <c r="X70">
-        <v>1.02</v>
-      </c>
-      <c r="Y70">
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ70">
+        <v>1.18</v>
+      </c>
+      <c r="AK70">
         <v>1.12</v>
-      </c>
-      <c r="Z70">
-        <v>4.7</v>
-      </c>
-      <c r="AA70">
-        <v>1.47</v>
-      </c>
-      <c r="AB70">
-        <v>2.35</v>
-      </c>
-      <c r="AC70">
-        <v>2.27</v>
-      </c>
-      <c r="AD70">
-        <v>1.58</v>
-      </c>
-      <c r="AE70">
-        <v>1.2</v>
-      </c>
-      <c r="AF70">
-        <v>1.44</v>
-      </c>
-      <c r="AG70">
-        <v>2.5</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ70">
-        <v>1.22</v>
-      </c>
-      <c r="AK70">
-        <v>1.28</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -14010,34 +14010,34 @@
         <v>2.14</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S84">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T84">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U84">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V84">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W84">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X84">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y84">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z84">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA84">
         <v>1.83</v>
@@ -14046,19 +14046,19 @@
         <v>1.97</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD84">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF84">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG84">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK84">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -14336,55 +14336,55 @@
         <v>4.98</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S86">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T86">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U86">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V86">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W86">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X86">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z86">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG86">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK86">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -14662,55 +14662,55 @@
         <v>2.48</v>
       </c>
       <c r="Q88">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R88">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S88">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T88">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U88">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V88">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W88">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X88">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y88">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z88">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA88">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB88">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC88">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD88">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE88">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF88">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG88">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK88">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14825,55 +14825,55 @@
         <v>2.26</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R89">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S89">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T89">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U89">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V89">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W89">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X89">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y89">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z89">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA89">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB89">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC89">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD89">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE89">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF89">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG89">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK89">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14988,55 +14988,55 @@
         <v>1.37</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S90">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T90">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U90">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V90">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W90">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X90">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y90">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z90">
-        <v>0</v>
+        <v>5.46</v>
       </c>
       <c r="AA90">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB90">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AC90">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AD90">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE90">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF90">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG90">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AK90">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15151,55 +15151,55 @@
         <v>2.21</v>
       </c>
       <c r="Q91">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R91">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S91">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T91">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U91">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V91">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W91">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X91">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y91">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z91">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA91">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB91">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC91">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD91">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE91">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF91">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG91">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK91">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15314,55 +15314,55 @@
         <v>1.87</v>
       </c>
       <c r="Q92">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R92">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S92">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T92">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U92">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V92">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W92">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X92">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y92">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z92">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA92">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB92">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC92">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD92">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE92">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF92">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG92">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK92">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -16129,55 +16129,55 @@
         <v>4.28</v>
       </c>
       <c r="Q97">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R97">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S97">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T97">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U97">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V97">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W97">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X97">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y97">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z97">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AA97">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB97">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC97">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="AD97">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE97">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF97">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG97">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK97">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16618,34 +16618,34 @@
         <v>3.03</v>
       </c>
       <c r="Q100">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R100">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S100">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T100">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U100">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="V100">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W100">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y100">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z100">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="AA100">
         <v>1.87</v>
@@ -16654,19 +16654,19 @@
         <v>1.8</v>
       </c>
       <c r="AC100">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD100">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE100">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF100">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG100">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK100">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G103">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G104">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G105">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G109">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G114">

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -635,28 +635,28 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="O2">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="P2">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="Q2">
         <v>2.8</v>
       </c>
       <c r="R2">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S2">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T2">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="U2">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="V2">
         <v>1.38</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AK2">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1948,10 +1948,10 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="R10">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S10">
         <v>1.3</v>
@@ -1960,13 +1960,13 @@
         <v>3</v>
       </c>
       <c r="U10">
-        <v>2.75</v>
+        <v>2.51</v>
       </c>
       <c r="V10">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W10">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
         <v>1.01</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AK10">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.81</v>
+        <v>2.16</v>
       </c>
       <c r="O65">
+        <v>3.28</v>
+      </c>
+      <c r="P65">
+        <v>3.31</v>
+      </c>
+      <c r="Q65">
+        <v>2.78</v>
+      </c>
+      <c r="R65">
+        <v>2.1</v>
+      </c>
+      <c r="S65">
+        <v>1.36</v>
+      </c>
+      <c r="T65">
+        <v>2.75</v>
+      </c>
+      <c r="U65">
+        <v>2.9</v>
+      </c>
+      <c r="V65">
+        <v>1.34</v>
+      </c>
+      <c r="W65">
+        <v>1.07</v>
+      </c>
+      <c r="X65">
+        <v>1.01</v>
+      </c>
+      <c r="Y65">
+        <v>1.31</v>
+      </c>
+      <c r="Z65">
         <v>3.13</v>
       </c>
-      <c r="P65">
-        <v>2.51</v>
-      </c>
-      <c r="Q65">
-        <v>3.56</v>
-      </c>
-      <c r="R65">
-        <v>1.96</v>
-      </c>
-      <c r="S65">
-        <v>1.44</v>
-      </c>
-      <c r="T65">
-        <v>2.62</v>
-      </c>
-      <c r="U65">
-        <v>3.1</v>
-      </c>
-      <c r="V65">
-        <v>1.33</v>
-      </c>
-      <c r="W65">
-        <v>1.06</v>
-      </c>
-      <c r="X65">
-        <v>1.04</v>
-      </c>
-      <c r="Y65">
-        <v>1.39</v>
-      </c>
-      <c r="Z65">
-        <v>2.59</v>
-      </c>
       <c r="AA65">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="AB65">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="AC65">
-        <v>4.1</v>
+        <v>3.81</v>
       </c>
       <c r="AD65">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AE65">
         <v>1.02</v>
       </c>
       <c r="AF65">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AG65">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK65">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.16</v>
+        <v>2.69</v>
       </c>
       <c r="O66">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="P66">
-        <v>3.31</v>
+        <v>2.44</v>
       </c>
       <c r="Q66">
-        <v>2.78</v>
+        <v>3.34</v>
       </c>
       <c r="R66">
         <v>2.1</v>
       </c>
       <c r="S66">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T66">
+        <v>3</v>
+      </c>
+      <c r="U66">
         <v>2.75</v>
       </c>
-      <c r="U66">
-        <v>2.9</v>
-      </c>
       <c r="V66">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="W66">
         <v>1.07</v>
       </c>
       <c r="X66">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y66">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="Z66">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="AA66">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AB66">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="AC66">
-        <v>3.81</v>
+        <v>3.2</v>
       </c>
       <c r="AD66">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AE66">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF66">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AG66">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK66">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,80 +11230,80 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.69</v>
+        <v>2.81</v>
       </c>
       <c r="O67">
-        <v>3.4</v>
+        <v>3.13</v>
       </c>
       <c r="P67">
-        <v>2.44</v>
+        <v>2.51</v>
       </c>
       <c r="Q67">
-        <v>3.34</v>
+        <v>3.56</v>
       </c>
       <c r="R67">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="S67">
+        <v>1.44</v>
+      </c>
+      <c r="T67">
+        <v>2.62</v>
+      </c>
+      <c r="U67">
+        <v>3.1</v>
+      </c>
+      <c r="V67">
         <v>1.33</v>
       </c>
-      <c r="T67">
-        <v>3</v>
-      </c>
-      <c r="U67">
-        <v>2.75</v>
-      </c>
-      <c r="V67">
+      <c r="W67">
+        <v>1.06</v>
+      </c>
+      <c r="X67">
+        <v>1.04</v>
+      </c>
+      <c r="Y67">
+        <v>1.39</v>
+      </c>
+      <c r="Z67">
+        <v>2.59</v>
+      </c>
+      <c r="AA67">
+        <v>2.38</v>
+      </c>
+      <c r="AB67">
+        <v>1.58</v>
+      </c>
+      <c r="AC67">
+        <v>4.1</v>
+      </c>
+      <c r="AD67">
+        <v>1.16</v>
+      </c>
+      <c r="AE67">
+        <v>1.02</v>
+      </c>
+      <c r="AF67">
+        <v>1.91</v>
+      </c>
+      <c r="AG67">
+        <v>1.8</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ67">
+        <v>1.33</v>
+      </c>
+      <c r="AK67">
         <v>1.4</v>
-      </c>
-      <c r="W67">
-        <v>1.07</v>
-      </c>
-      <c r="X67">
-        <v>1</v>
-      </c>
-      <c r="Y67">
-        <v>1.26</v>
-      </c>
-      <c r="Z67">
-        <v>3.2</v>
-      </c>
-      <c r="AA67">
-        <v>1.88</v>
-      </c>
-      <c r="AB67">
-        <v>1.91</v>
-      </c>
-      <c r="AC67">
-        <v>3.2</v>
-      </c>
-      <c r="AD67">
-        <v>1.26</v>
-      </c>
-      <c r="AE67">
-        <v>1.06</v>
-      </c>
-      <c r="AF67">
-        <v>1.71</v>
-      </c>
-      <c r="AG67">
-        <v>2.02</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ67">
-        <v>1.28</v>
-      </c>
-      <c r="AK67">
-        <v>1.43</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,34 +15142,34 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.58</v>
+        <v>6.32</v>
       </c>
       <c r="O91">
-        <v>3.46</v>
+        <v>4.55</v>
       </c>
       <c r="P91">
-        <v>2.26</v>
+        <v>1.37</v>
       </c>
       <c r="Q91">
-        <v>3.56</v>
+        <v>5.8</v>
       </c>
       <c r="R91">
-        <v>2.29</v>
+        <v>2.62</v>
       </c>
       <c r="S91">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T91">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="U91">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="V91">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="W91">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X91">
         <v>1.02</v>
@@ -15178,28 +15178,28 @@
         <v>1.13</v>
       </c>
       <c r="Z91">
-        <v>4.5</v>
+        <v>5.46</v>
       </c>
       <c r="AA91">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AB91">
-        <v>2.27</v>
+        <v>2.68</v>
       </c>
       <c r="AC91">
-        <v>2.33</v>
+        <v>2.11</v>
       </c>
       <c r="AD91">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AE91">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AF91">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG91">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.29</v>
+        <v>2.8</v>
       </c>
       <c r="AK91">
-        <v>1.35</v>
+        <v>1.05</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,34 +15305,34 @@
         </is>
       </c>
       <c r="N92">
-        <v>6.32</v>
+        <v>2.58</v>
       </c>
       <c r="O92">
-        <v>4.55</v>
+        <v>3.46</v>
       </c>
       <c r="P92">
-        <v>1.37</v>
+        <v>2.26</v>
       </c>
       <c r="Q92">
-        <v>5.8</v>
+        <v>3.56</v>
       </c>
       <c r="R92">
-        <v>2.62</v>
+        <v>2.29</v>
       </c>
       <c r="S92">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T92">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="U92">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="V92">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="W92">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X92">
         <v>1.02</v>
@@ -15341,28 +15341,28 @@
         <v>1.13</v>
       </c>
       <c r="Z92">
-        <v>5.46</v>
+        <v>4.5</v>
       </c>
       <c r="AA92">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="AB92">
-        <v>2.68</v>
+        <v>2.27</v>
       </c>
       <c r="AC92">
-        <v>2.11</v>
+        <v>2.33</v>
       </c>
       <c r="AD92">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AE92">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AF92">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG92">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>2.8</v>
+        <v>1.29</v>
       </c>
       <c r="AK92">
-        <v>1.05</v>
+        <v>1.35</v>
       </c>
       <c r="AL92">
         <v>0</v>

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -798,19 +798,19 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="O3">
-        <v>4.02</v>
+        <v>3.68</v>
       </c>
       <c r="P3">
-        <v>4.35</v>
+        <v>3.3</v>
       </c>
       <c r="Q3">
         <v>2.49</v>
       </c>
       <c r="R3">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S3">
         <v>1.29</v>
@@ -819,7 +819,7 @@
         <v>3.4</v>
       </c>
       <c r="U3">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="V3">
         <v>1.48</v>
@@ -834,22 +834,22 @@
         <v>1.18</v>
       </c>
       <c r="Z3">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AA3">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AB3">
         <v>2.1</v>
       </c>
       <c r="AC3">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="AD3">
         <v>1.43</v>
       </c>
       <c r="AE3">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF3">
         <v>1.55</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK3">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1296,52 +1296,52 @@
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="R6">
-        <v>2.21</v>
+        <v>2.12</v>
       </c>
       <c r="S6">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T6">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U6">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="V6">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z6">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="AA6">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AB6">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AC6">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="AD6">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE6">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF6">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG6">
         <v>1.95</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK6">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G13">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G14">
@@ -3741,55 +3741,55 @@
         <v>0</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -6696,34 +6696,34 @@
         <v>1.17</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>5.72</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.18</v>
+        <v>3.2</v>
       </c>
       <c r="O50">
+        <v>3.64</v>
+      </c>
+      <c r="P50">
+        <v>2.03</v>
+      </c>
+      <c r="Q50">
         <v>3.62</v>
       </c>
-      <c r="P50">
-        <v>2.9</v>
-      </c>
-      <c r="Q50">
-        <v>0</v>
-      </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,80 +8622,80 @@
         </is>
       </c>
       <c r="N51">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="O51">
-        <v>3.64</v>
+        <v>4.2</v>
       </c>
       <c r="P51">
-        <v>2.03</v>
+        <v>4.63</v>
       </c>
       <c r="Q51">
-        <v>3.62</v>
+        <v>1.95</v>
       </c>
       <c r="R51">
-        <v>2.28</v>
+        <v>2.48</v>
       </c>
       <c r="S51">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="T51">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="U51">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="V51">
-        <v>1.52</v>
+        <v>1.69</v>
       </c>
       <c r="W51">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X51">
         <v>1.01</v>
       </c>
       <c r="Y51">
+        <v>1.1</v>
+      </c>
+      <c r="Z51">
+        <v>5.1</v>
+      </c>
+      <c r="AA51">
+        <v>1.42</v>
+      </c>
+      <c r="AB51">
+        <v>2.49</v>
+      </c>
+      <c r="AC51">
+        <v>2.12</v>
+      </c>
+      <c r="AD51">
+        <v>1.66</v>
+      </c>
+      <c r="AE51">
+        <v>1.24</v>
+      </c>
+      <c r="AF51">
+        <v>1.55</v>
+      </c>
+      <c r="AG51">
+        <v>2.26</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
         <v>1.14</v>
       </c>
-      <c r="Z51">
-        <v>4.35</v>
-      </c>
-      <c r="AA51">
-        <v>1.6</v>
-      </c>
-      <c r="AB51">
-        <v>2.23</v>
-      </c>
-      <c r="AC51">
-        <v>2.42</v>
-      </c>
-      <c r="AD51">
-        <v>1.44</v>
-      </c>
-      <c r="AE51">
-        <v>1.15</v>
-      </c>
-      <c r="AF51">
-        <v>1.51</v>
-      </c>
-      <c r="AG51">
-        <v>2.39</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.24</v>
-      </c>
       <c r="AK51">
-        <v>1.33</v>
+        <v>2.5</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -11402,55 +11402,55 @@
         <v>4.38</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK68">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q79">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.31</v>
+        <v>6.32</v>
       </c>
       <c r="O90">
-        <v>3.54</v>
+        <v>4.55</v>
       </c>
       <c r="P90">
-        <v>2.48</v>
+        <v>1.37</v>
       </c>
       <c r="Q90">
-        <v>2.75</v>
+        <v>5.8</v>
       </c>
       <c r="R90">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="S90">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T90">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="U90">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="V90">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="W90">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X90">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y90">
         <v>1.13</v>
       </c>
       <c r="Z90">
-        <v>4.6</v>
+        <v>5.46</v>
       </c>
       <c r="AA90">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB90">
-        <v>2.28</v>
+        <v>2.68</v>
       </c>
       <c r="AC90">
-        <v>2.29</v>
+        <v>2.11</v>
       </c>
       <c r="AD90">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AE90">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AF90">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AG90">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.44</v>
+        <v>2.8</v>
       </c>
       <c r="AK90">
-        <v>1.47</v>
+        <v>1.05</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>6.32</v>
+        <v>2.31</v>
       </c>
       <c r="O91">
-        <v>4.55</v>
+        <v>3.54</v>
       </c>
       <c r="P91">
-        <v>1.37</v>
+        <v>2.48</v>
       </c>
       <c r="Q91">
-        <v>5.8</v>
+        <v>2.75</v>
       </c>
       <c r="R91">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="S91">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T91">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="U91">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="V91">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="W91">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X91">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y91">
         <v>1.13</v>
       </c>
       <c r="Z91">
-        <v>5.46</v>
+        <v>4.6</v>
       </c>
       <c r="AA91">
+        <v>1.5</v>
+      </c>
+      <c r="AB91">
+        <v>2.28</v>
+      </c>
+      <c r="AC91">
+        <v>2.29</v>
+      </c>
+      <c r="AD91">
+        <v>1.53</v>
+      </c>
+      <c r="AE91">
+        <v>1.18</v>
+      </c>
+      <c r="AF91">
         <v>1.44</v>
       </c>
-      <c r="AB91">
-        <v>2.68</v>
-      </c>
-      <c r="AC91">
-        <v>2.11</v>
-      </c>
-      <c r="AD91">
-        <v>1.7</v>
-      </c>
-      <c r="AE91">
-        <v>1.28</v>
-      </c>
-      <c r="AF91">
-        <v>1.62</v>
-      </c>
       <c r="AG91">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>2.8</v>
+        <v>1.44</v>
       </c>
       <c r="AK91">
-        <v>1.05</v>
+        <v>1.47</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -16292,55 +16292,55 @@
         <v>2.15</v>
       </c>
       <c r="Q98">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R98">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S98">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T98">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U98">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V98">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W98">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X98">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y98">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z98">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA98">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB98">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC98">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD98">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE98">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF98">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG98">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK98">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17137,10 +17137,10 @@
         <v>0</v>
       </c>
       <c r="AA103">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB103">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC103">
         <v>0</v>
@@ -18767,10 +18767,10 @@
         <v>0</v>
       </c>
       <c r="AA113">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB113">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC113">
         <v>0</v>

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -3895,28 +3895,28 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="O22">
-        <v>10.7</v>
+        <v>6.6</v>
       </c>
       <c r="P22">
-        <v>20</v>
+        <v>10.5</v>
       </c>
       <c r="Q22">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="R22">
-        <v>3.22</v>
+        <v>3.46</v>
       </c>
       <c r="S22">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="T22">
-        <v>4.95</v>
+        <v>4.4</v>
       </c>
       <c r="U22">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="V22">
         <v>1.85</v>
@@ -3934,25 +3934,25 @@
         <v>7.2</v>
       </c>
       <c r="AA22">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AB22">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AC22">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AD22">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AE22">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AF22">
         <v>1.93</v>
       </c>
       <c r="AG22">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AK22">
-        <v>6.75</v>
+        <v>5.45</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -5045,55 +5045,55 @@
         <v>0</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>7.49</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O31">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="P31">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5688,34 +5688,34 @@
         </is>
       </c>
       <c r="N33">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="O33">
-        <v>11</v>
+        <v>6.4</v>
       </c>
       <c r="P33">
         <v>1.12</v>
       </c>
       <c r="Q33">
-        <v>10.7</v>
+        <v>11</v>
       </c>
       <c r="R33">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="S33">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T33">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="U33">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="V33">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="W33">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X33">
         <v>1.01</v>
@@ -5724,28 +5724,28 @@
         <v>1.05</v>
       </c>
       <c r="Z33">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AA33">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AB33">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AC33">
+        <v>1.83</v>
+      </c>
+      <c r="AD33">
         <v>1.84</v>
       </c>
-      <c r="AD33">
-        <v>1.91</v>
-      </c>
       <c r="AE33">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AF33">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AG33">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AK33">
         <v>1.03</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -5890,10 +5890,10 @@
         <v>0</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC34">
         <v>0</v>
@@ -6014,31 +6014,31 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="O35">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="P35">
-        <v>5.36</v>
+        <v>4.8</v>
       </c>
       <c r="Q35">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="R35">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="S35">
         <v>1.33</v>
       </c>
       <c r="T35">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U35">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="V35">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W35">
         <v>1.07</v>
@@ -6053,19 +6053,19 @@
         <v>3.63</v>
       </c>
       <c r="AA35">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AB35">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AC35">
-        <v>3.09</v>
+        <v>3.05</v>
       </c>
       <c r="AD35">
         <v>1.35</v>
       </c>
       <c r="AE35">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF35">
         <v>1.8</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK35">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6349,71 +6349,71 @@
         <v>1.8</v>
       </c>
       <c r="Q37">
-        <v>4.63</v>
+        <v>4.5</v>
       </c>
       <c r="R37">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S37">
         <v>1.33</v>
       </c>
       <c r="T37">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="U37">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="V37">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W37">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X37">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y37">
+        <v>1.22</v>
+      </c>
+      <c r="Z37">
+        <v>3.77</v>
+      </c>
+      <c r="AA37">
+        <v>1.77</v>
+      </c>
+      <c r="AB37">
+        <v>1.9</v>
+      </c>
+      <c r="AC37">
+        <v>2.83</v>
+      </c>
+      <c r="AD37">
+        <v>1.33</v>
+      </c>
+      <c r="AE37">
+        <v>1.09</v>
+      </c>
+      <c r="AF37">
+        <v>1.67</v>
+      </c>
+      <c r="AG37">
+        <v>2.05</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ37">
         <v>1.25</v>
       </c>
-      <c r="Z37">
-        <v>3.28</v>
-      </c>
-      <c r="AA37">
-        <v>1.84</v>
-      </c>
-      <c r="AB37">
-        <v>1.83</v>
-      </c>
-      <c r="AC37">
-        <v>3.05</v>
-      </c>
-      <c r="AD37">
-        <v>1.28</v>
-      </c>
-      <c r="AE37">
-        <v>1.08</v>
-      </c>
-      <c r="AF37">
-        <v>1.75</v>
-      </c>
-      <c r="AG37">
-        <v>1.95</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ37">
-        <v>1.21</v>
-      </c>
       <c r="AK37">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6847,7 +6847,7 @@
         <v>1.25</v>
       </c>
       <c r="T40">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="U40">
         <v>2.39</v>
@@ -6856,7 +6856,7 @@
         <v>1.53</v>
       </c>
       <c r="W40">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X40">
         <v>1.01</v>
@@ -6871,7 +6871,7 @@
         <v>1.57</v>
       </c>
       <c r="AB40">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AC40">
         <v>2.52</v>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AK40">
         <v>1.67</v>
@@ -6992,31 +6992,31 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.42</v>
+        <v>2.25</v>
       </c>
       <c r="O41">
-        <v>3.36</v>
+        <v>3.2</v>
       </c>
       <c r="P41">
-        <v>2.98</v>
+        <v>2.69</v>
       </c>
       <c r="Q41">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="R41">
-        <v>1.98</v>
+        <v>2.13</v>
       </c>
       <c r="S41">
         <v>1.41</v>
       </c>
       <c r="T41">
-        <v>2.63</v>
+        <v>2.79</v>
       </c>
       <c r="U41">
-        <v>3.02</v>
+        <v>3.09</v>
       </c>
       <c r="V41">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W41">
         <v>1.03</v>
@@ -7025,22 +7025,22 @@
         <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z41">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="AA41">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="AB41">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AC41">
-        <v>3.58</v>
+        <v>3.66</v>
       </c>
       <c r="AD41">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AE41">
         <v>1.03</v>
@@ -7049,7 +7049,7 @@
         <v>1.81</v>
       </c>
       <c r="AG41">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK41">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7653,10 +7653,10 @@
         <v>1.31</v>
       </c>
       <c r="Q45">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="R45">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="S45">
         <v>1.23</v>
@@ -7665,7 +7665,7 @@
         <v>3.48</v>
       </c>
       <c r="U45">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="V45">
         <v>1.6</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.6</v>
+        <v>2.18</v>
       </c>
       <c r="O51">
-        <v>4.2</v>
+        <v>3.62</v>
       </c>
       <c r="P51">
-        <v>4.63</v>
+        <v>2.9</v>
       </c>
       <c r="Q51">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R51">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S51">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="T51">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U51">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="V51">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="W51">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X51">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y51">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z51">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AA51">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AB51">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AC51">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD51">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE51">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AF51">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG51">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK51">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.18</v>
+        <v>1.6</v>
       </c>
       <c r="O52">
-        <v>3.62</v>
+        <v>4.2</v>
       </c>
       <c r="P52">
-        <v>2.9</v>
+        <v>4.63</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL52">
         <v>0</v>

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -3898,10 +3898,10 @@
         <v>1.12</v>
       </c>
       <c r="O22">
-        <v>6.6</v>
+        <v>10.7</v>
       </c>
       <c r="P22">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="Q22">
         <v>1.41</v>
@@ -3925,7 +3925,7 @@
         <v>1.22</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
         <v>1.03</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="O31">
         <v>3.62</v>
       </c>
       <c r="P31">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="O33">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="P33">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Q33">
         <v>11</v>
@@ -5703,10 +5703,10 @@
         <v>3.3</v>
       </c>
       <c r="S33">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T33">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="U33">
         <v>1.85</v>
@@ -5733,10 +5733,10 @@
         <v>3.2</v>
       </c>
       <c r="AC33">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AD33">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AE33">
         <v>1.33</v>
@@ -6032,13 +6032,13 @@
         <v>1.33</v>
       </c>
       <c r="T35">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U35">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V35">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W35">
         <v>1.07</v>
@@ -6841,7 +6841,7 @@
         <v>2.54</v>
       </c>
       <c r="R40">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="S40">
         <v>1.25</v>
@@ -6850,7 +6850,7 @@
         <v>3.5</v>
       </c>
       <c r="U40">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="V40">
         <v>1.53</v>
@@ -6865,16 +6865,16 @@
         <v>1.14</v>
       </c>
       <c r="Z40">
-        <v>4.61</v>
+        <v>4.67</v>
       </c>
       <c r="AA40">
         <v>1.57</v>
       </c>
       <c r="AB40">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AC40">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="AD40">
         <v>1.44</v>
@@ -7490,10 +7490,10 @@
         <v>2.61</v>
       </c>
       <c r="Q44">
-        <v>2.83</v>
+        <v>2.6</v>
       </c>
       <c r="R44">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="S44">
         <v>1.22</v>
@@ -7502,43 +7502,43 @@
         <v>3.8</v>
       </c>
       <c r="U44">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="V44">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="W44">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="X44">
         <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Z44">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AA44">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="AB44">
-        <v>2.31</v>
+        <v>2.46</v>
       </c>
       <c r="AC44">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AD44">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="AE44">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AF44">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AG44">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK44">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -9446,22 +9446,22 @@
         <v>1.8</v>
       </c>
       <c r="Q56">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="R56">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="S56">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T56">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U56">
         <v>2.1</v>
       </c>
       <c r="V56">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W56">
         <v>1.17</v>
@@ -9470,31 +9470,31 @@
         <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z56">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AA56">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AB56">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="AC56">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AD56">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AE56">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF56">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG56">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="AK56">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="O62">
-        <v>4.02</v>
+        <v>4.16</v>
       </c>
       <c r="P62">
-        <v>3.41</v>
+        <v>3.84</v>
       </c>
       <c r="Q62">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="R62">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="S62">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T62">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U62">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="V62">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="W62">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z62">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AA62">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB62">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AC62">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AD62">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AE62">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AF62">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AG62">
-        <v>2.81</v>
+        <v>2.67</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK62">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="O64">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="P64">
-        <v>3.31</v>
+        <v>3.2</v>
       </c>
       <c r="Q64">
         <v>2.61</v>
@@ -10777,22 +10777,22 @@
         <v>1.22</v>
       </c>
       <c r="Z64">
-        <v>3.5</v>
+        <v>3.79</v>
       </c>
       <c r="AA64">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB64">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC64">
         <v>2.88</v>
       </c>
       <c r="AD64">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AE64">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF64">
         <v>1.67</v>
@@ -10811,7 +10811,7 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK64">
         <v>1.7</v>
@@ -10904,16 +10904,16 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="O65">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="P65">
-        <v>3.31</v>
+        <v>3.2</v>
       </c>
       <c r="Q65">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="R65">
         <v>2.1</v>
@@ -10922,46 +10922,46 @@
         <v>1.36</v>
       </c>
       <c r="T65">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="U65">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="V65">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="W65">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X65">
         <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z65">
-        <v>3.13</v>
+        <v>3.33</v>
       </c>
       <c r="AA65">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="AB65">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="AC65">
-        <v>3.81</v>
+        <v>3.5</v>
       </c>
       <c r="AD65">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE65">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF65">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AG65">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK65">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.69</v>
+        <v>2.45</v>
       </c>
       <c r="O66">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P66">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="Q66">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="R66">
         <v>2.1</v>
       </c>
       <c r="S66">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="T66">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U66">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="V66">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W66">
         <v>1.07</v>
       </c>
       <c r="X66">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y66">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z66">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA66">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AB66">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="AC66">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD66">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE66">
         <v>1.06</v>
       </c>
       <c r="AF66">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AG66">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK66">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,25 +11230,25 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="O67">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="P67">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="Q67">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="R67">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="S67">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="T67">
-        <v>2.62</v>
+        <v>2.39</v>
       </c>
       <c r="U67">
         <v>3.1</v>
@@ -11260,34 +11260,34 @@
         <v>1.06</v>
       </c>
       <c r="X67">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y67">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="Z67">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="AA67">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AB67">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AC67">
-        <v>4.1</v>
+        <v>4.75</v>
       </c>
       <c r="AD67">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AE67">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF67">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG67">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11393,31 +11393,31 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="O68">
-        <v>3.7</v>
+        <v>3.94</v>
       </c>
       <c r="P68">
-        <v>4.38</v>
+        <v>4.31</v>
       </c>
       <c r="Q68">
-        <v>2.21</v>
+        <v>2.31</v>
       </c>
       <c r="R68">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S68">
         <v>1.3</v>
       </c>
       <c r="T68">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U68">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="V68">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="W68">
         <v>1.08</v>
@@ -11426,31 +11426,31 @@
         <v>1.03</v>
       </c>
       <c r="Y68">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z68">
-        <v>3.84</v>
+        <v>4.29</v>
       </c>
       <c r="AA68">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AB68">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AC68">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="AD68">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AE68">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AF68">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AG68">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK68">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="O69">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="P69">
-        <v>5.02</v>
+        <v>7</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11719,19 +11719,19 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="O70">
-        <v>4.23</v>
+        <v>4.2</v>
       </c>
       <c r="P70">
-        <v>4.07</v>
+        <v>4.33</v>
       </c>
       <c r="Q70">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="R70">
-        <v>2.68</v>
+        <v>2.43</v>
       </c>
       <c r="S70">
         <v>1.22</v>
@@ -11740,10 +11740,10 @@
         <v>3.55</v>
       </c>
       <c r="U70">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="V70">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="W70">
         <v>1.14</v>
@@ -11755,22 +11755,22 @@
         <v>1.08</v>
       </c>
       <c r="Z70">
-        <v>5.55</v>
+        <v>5.6</v>
       </c>
       <c r="AA70">
         <v>1.39</v>
       </c>
       <c r="AB70">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AC70">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AD70">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AE70">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AF70">
         <v>1.44</v>
@@ -12869,22 +12869,22 @@
         <v>3.61</v>
       </c>
       <c r="Q77">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="R77">
         <v>2.14</v>
       </c>
       <c r="S77">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T77">
-        <v>2.8</v>
+        <v>3.03</v>
       </c>
       <c r="U77">
-        <v>2.64</v>
+        <v>2.82</v>
       </c>
       <c r="V77">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W77">
         <v>1.07</v>
@@ -12893,25 +12893,25 @@
         <v>1</v>
       </c>
       <c r="Y77">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z77">
-        <v>3.34</v>
+        <v>3.48</v>
       </c>
       <c r="AA77">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AB77">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AC77">
-        <v>2.97</v>
+        <v>3.22</v>
       </c>
       <c r="AD77">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE77">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF77">
         <v>1.73</v>
@@ -13023,25 +13023,25 @@
         </is>
       </c>
       <c r="N78">
-        <v>4.14</v>
+        <v>3.9</v>
       </c>
       <c r="O78">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P78">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="Q78">
         <v>4.68</v>
       </c>
       <c r="R78">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="S78">
         <v>1.33</v>
       </c>
       <c r="T78">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="U78">
         <v>2.56</v>
@@ -13065,7 +13065,7 @@
         <v>1.9</v>
       </c>
       <c r="AB78">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AC78">
         <v>2.92</v>
@@ -13080,7 +13080,7 @@
         <v>1.75</v>
       </c>
       <c r="AG78">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13355,74 +13355,74 @@
         <v>3.4</v>
       </c>
       <c r="P80">
+        <v>2.8</v>
+      </c>
+      <c r="Q80">
         <v>2.88</v>
       </c>
-      <c r="Q80">
-        <v>2.76</v>
-      </c>
       <c r="R80">
-        <v>2.17</v>
+        <v>2.36</v>
       </c>
       <c r="S80">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T80">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="U80">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V80">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W80">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X80">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y80">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="Z80">
-        <v>3.95</v>
+        <v>4.33</v>
       </c>
       <c r="AA80">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AB80">
-        <v>1.9</v>
+        <v>2.22</v>
       </c>
       <c r="AC80">
-        <v>2.69</v>
+        <v>2.86</v>
       </c>
       <c r="AD80">
+        <v>1.43</v>
+      </c>
+      <c r="AE80">
+        <v>1.14</v>
+      </c>
+      <c r="AF80">
+        <v>1.55</v>
+      </c>
+      <c r="AG80">
+        <v>2.25</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ80">
         <v>1.36</v>
       </c>
-      <c r="AE80">
-        <v>1.1</v>
-      </c>
-      <c r="AF80">
-        <v>1.57</v>
-      </c>
-      <c r="AG80">
-        <v>2.26</v>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI80" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ80">
-        <v>1.3</v>
-      </c>
       <c r="AK80">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13838,34 +13838,34 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="O83">
-        <v>4.26</v>
+        <v>4.1</v>
       </c>
       <c r="P83">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="Q83">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="R83">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="S83">
         <v>1.2</v>
       </c>
       <c r="T83">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="U83">
         <v>2.04</v>
       </c>
       <c r="V83">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="W83">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X83">
         <v>1.01</v>
@@ -13877,25 +13877,25 @@
         <v>6.2</v>
       </c>
       <c r="AA83">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB83">
-        <v>2.78</v>
+        <v>3.2</v>
       </c>
       <c r="AC83">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AD83">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AE83">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AF83">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AG83">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -14164,28 +14164,28 @@
         </is>
       </c>
       <c r="N85">
-        <v>3.55</v>
+        <v>2.97</v>
       </c>
       <c r="O85">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P85">
-        <v>2.13</v>
+        <v>2.36</v>
       </c>
       <c r="Q85">
         <v>3.2</v>
       </c>
       <c r="R85">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S85">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T85">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="U85">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="V85">
         <v>1.44</v>
@@ -14200,19 +14200,19 @@
         <v>1.2</v>
       </c>
       <c r="Z85">
-        <v>3.94</v>
+        <v>4.1</v>
       </c>
       <c r="AA85">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="AB85">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AC85">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="AD85">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AE85">
         <v>1.1</v>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AK85">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="O86">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="P86">
-        <v>4.98</v>
+        <v>4.8</v>
       </c>
       <c r="Q86">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="R86">
-        <v>2.33</v>
+        <v>2.17</v>
       </c>
       <c r="S86">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T86">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="U86">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="V86">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W86">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X86">
         <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z86">
-        <v>3.98</v>
+        <v>3.95</v>
       </c>
       <c r="AA86">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AB86">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AC86">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="AD86">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE86">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF86">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG86">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK86">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14490,61 +14490,61 @@
         </is>
       </c>
       <c r="N87">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O87">
-        <v>3.52</v>
+        <v>3.25</v>
       </c>
       <c r="P87">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="Q87">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="R87">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="S87">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T87">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U87">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="V87">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W87">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X87">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z87">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="AA87">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AB87">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AC87">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="AD87">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AE87">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF87">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AG87">
         <v>2.1</v>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK87">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="O88">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P88">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="Q88">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R88">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S88">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T88">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U88">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V88">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W88">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X88">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y88">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z88">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA88">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB88">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC88">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD88">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE88">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF88">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG88">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK88">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="O89">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="P89">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="R89">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S89">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T89">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="U89">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V89">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W89">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X89">
         <v>0</v>
       </c>
       <c r="Y89">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z89">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA89">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB89">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC89">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD89">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE89">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF89">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG89">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK89">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="O95">
-        <v>3.54</v>
+        <v>3.75</v>
       </c>
       <c r="P95">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="Q95">
         <v>2.95</v>
@@ -15812,19 +15812,19 @@
         <v>1.25</v>
       </c>
       <c r="T95">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="U95">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V95">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W95">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X95">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y95">
         <v>1.11</v>
@@ -15833,41 +15833,41 @@
         <v>4.8</v>
       </c>
       <c r="AA95">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AB95">
         <v>2.44</v>
       </c>
       <c r="AC95">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AD95">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="AE95">
         <v>1.24</v>
       </c>
       <c r="AF95">
+        <v>1.4</v>
+      </c>
+      <c r="AG95">
+        <v>2.75</v>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ95">
         <v>1.44</v>
       </c>
-      <c r="AG95">
-        <v>2.6</v>
-      </c>
-      <c r="AH95" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI95" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ95">
-        <v>1.3</v>
-      </c>
       <c r="AK95">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15957,13 +15957,13 @@
         </is>
       </c>
       <c r="N96">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O96">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P96">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q96">
         <v>0</v>
@@ -16135,49 +16135,49 @@
         <v>2.11</v>
       </c>
       <c r="S97">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T97">
-        <v>2.92</v>
+        <v>3.11</v>
       </c>
       <c r="U97">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V97">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W97">
         <v>1.1</v>
       </c>
       <c r="X97">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y97">
         <v>1.27</v>
       </c>
       <c r="Z97">
-        <v>3.34</v>
+        <v>3.74</v>
       </c>
       <c r="AA97">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AB97">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AC97">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="AD97">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE97">
         <v>1.08</v>
       </c>
       <c r="AF97">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG97">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O113">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P113">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -18767,10 +18767,10 @@
         <v>0</v>
       </c>
       <c r="AA113">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB113">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC113">
         <v>0</v>

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -653,16 +653,16 @@
         <v>1.33</v>
       </c>
       <c r="T2">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="U2">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="V2">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W2">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X2">
         <v>1.01</v>
@@ -1954,7 +1954,7 @@
         <v>2.1</v>
       </c>
       <c r="S10">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T10">
         <v>3</v>
@@ -1966,7 +1966,7 @@
         <v>1.42</v>
       </c>
       <c r="W10">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X10">
         <v>1.01</v>
@@ -5051,19 +5051,19 @@
         <v>2.14</v>
       </c>
       <c r="S29">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T29">
-        <v>2.73</v>
+        <v>3.15</v>
       </c>
       <c r="U29">
-        <v>2.45</v>
+        <v>2.69</v>
       </c>
       <c r="V29">
         <v>1.44</v>
       </c>
       <c r="W29">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X29">
         <v>1.01</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="O34">
         <v>3.24</v>
       </c>
       <c r="P34">
-        <v>2.94</v>
+        <v>3.12</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -6355,7 +6355,7 @@
         <v>2.2</v>
       </c>
       <c r="S37">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T37">
         <v>3.1</v>
@@ -6370,19 +6370,19 @@
         <v>1.08</v>
       </c>
       <c r="X37">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z37">
-        <v>3.77</v>
+        <v>3.7</v>
       </c>
       <c r="AA37">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AB37">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC37">
         <v>2.83</v>
@@ -6391,7 +6391,7 @@
         <v>1.33</v>
       </c>
       <c r="AE37">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF37">
         <v>1.67</v>
@@ -6853,7 +6853,7 @@
         <v>2.37</v>
       </c>
       <c r="V40">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W40">
         <v>1.14</v>
@@ -7490,10 +7490,10 @@
         <v>2.61</v>
       </c>
       <c r="Q44">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="R44">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="S44">
         <v>1.22</v>
@@ -7505,34 +7505,34 @@
         <v>2.15</v>
       </c>
       <c r="V44">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W44">
         <v>1.18</v>
       </c>
       <c r="X44">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y44">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Z44">
-        <v>5.3</v>
+        <v>5.66</v>
       </c>
       <c r="AA44">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AB44">
-        <v>2.46</v>
+        <v>2.63</v>
       </c>
       <c r="AC44">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AD44">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AE44">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AF44">
         <v>1.4</v>
@@ -7644,31 +7644,31 @@
         </is>
       </c>
       <c r="N45">
-        <v>8.75</v>
+        <v>7.25</v>
       </c>
       <c r="O45">
-        <v>5.25</v>
+        <v>4.75</v>
       </c>
       <c r="P45">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="Q45">
         <v>7.5</v>
       </c>
       <c r="R45">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="S45">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="T45">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="U45">
         <v>2.25</v>
       </c>
       <c r="V45">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="W45">
         <v>1.13</v>
@@ -7677,47 +7677,47 @@
         <v>1.03</v>
       </c>
       <c r="Y45">
+        <v>1.19</v>
+      </c>
+      <c r="Z45">
+        <v>4.33</v>
+      </c>
+      <c r="AA45">
+        <v>1.52</v>
+      </c>
+      <c r="AB45">
+        <v>2.24</v>
+      </c>
+      <c r="AC45">
+        <v>2.59</v>
+      </c>
+      <c r="AD45">
+        <v>1.47</v>
+      </c>
+      <c r="AE45">
+        <v>1.17</v>
+      </c>
+      <c r="AF45">
+        <v>1.85</v>
+      </c>
+      <c r="AG45">
+        <v>1.85</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ45">
         <v>1.13</v>
       </c>
-      <c r="Z45">
-        <v>4.6</v>
-      </c>
-      <c r="AA45">
-        <v>1.49</v>
-      </c>
-      <c r="AB45">
-        <v>2.3</v>
-      </c>
-      <c r="AC45">
-        <v>2.31</v>
-      </c>
-      <c r="AD45">
-        <v>1.56</v>
-      </c>
-      <c r="AE45">
-        <v>1.19</v>
-      </c>
-      <c r="AF45">
-        <v>1.9</v>
-      </c>
-      <c r="AG45">
-        <v>1.8</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ45">
-        <v>1.11</v>
-      </c>
       <c r="AK45">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>3.2</v>
+        <v>2.87</v>
       </c>
       <c r="O50">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="P50">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="Q50">
         <v>3.62</v>
@@ -8474,19 +8474,19 @@
         <v>2.28</v>
       </c>
       <c r="S50">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T50">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U50">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="V50">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W50">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X50">
         <v>1.01</v>
@@ -8498,10 +8498,10 @@
         <v>4.35</v>
       </c>
       <c r="AA50">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AB50">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AC50">
         <v>2.42</v>
@@ -8661,10 +8661,10 @@
         <v>0</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC51">
         <v>0</v>
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="O52">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="P52">
-        <v>4.63</v>
+        <v>4.6</v>
       </c>
       <c r="Q52">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="R52">
-        <v>2.48</v>
+        <v>2.57</v>
       </c>
       <c r="S52">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T52">
         <v>4</v>
       </c>
       <c r="U52">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V52">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="W52">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="X52">
         <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z52">
-        <v>5.1</v>
+        <v>5.45</v>
       </c>
       <c r="AA52">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AB52">
-        <v>2.49</v>
+        <v>2.66</v>
       </c>
       <c r="AC52">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="AD52">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AE52">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AF52">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AG52">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>1.14</v>
       </c>
       <c r="AK52">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,31 +8948,31 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="O53">
-        <v>3.86</v>
+        <v>3.7</v>
       </c>
       <c r="P53">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="Q53">
-        <v>3.13</v>
+        <v>2.9</v>
       </c>
       <c r="R53">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S53">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T53">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="U53">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="V53">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="W53">
         <v>1.15</v>
@@ -8987,19 +8987,19 @@
         <v>5.65</v>
       </c>
       <c r="AA53">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AB53">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AC53">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AD53">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AE53">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AF53">
         <v>1.4</v>
@@ -9021,7 +9021,7 @@
         <v>1.23</v>
       </c>
       <c r="AK53">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>3.32</v>
+        <v>2.9</v>
       </c>
       <c r="O54">
         <v>4</v>
       </c>
       <c r="P54">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="Q54">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="R54">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="S54">
+        <v>1.14</v>
+      </c>
+      <c r="T54">
+        <v>4.15</v>
+      </c>
+      <c r="U54">
+        <v>1.91</v>
+      </c>
+      <c r="V54">
+        <v>1.8</v>
+      </c>
+      <c r="W54">
         <v>1.18</v>
-      </c>
-      <c r="T54">
-        <v>3.98</v>
-      </c>
-      <c r="U54">
-        <v>1.95</v>
-      </c>
-      <c r="V54">
-        <v>1.74</v>
-      </c>
-      <c r="W54">
-        <v>1.17</v>
       </c>
       <c r="X54">
         <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z54">
-        <v>6.05</v>
+        <v>6.4</v>
       </c>
       <c r="AA54">
+        <v>1.3</v>
+      </c>
+      <c r="AB54">
+        <v>2.97</v>
+      </c>
+      <c r="AC54">
+        <v>1.94</v>
+      </c>
+      <c r="AD54">
+        <v>1.92</v>
+      </c>
+      <c r="AE54">
         <v>1.33</v>
       </c>
-      <c r="AB54">
-        <v>2.83</v>
-      </c>
-      <c r="AC54">
-        <v>1.98</v>
-      </c>
-      <c r="AD54">
-        <v>1.72</v>
-      </c>
-      <c r="AE54">
-        <v>1.3</v>
-      </c>
       <c r="AF54">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AG54">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>1.25</v>
       </c>
       <c r="AK54">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9606,16 +9606,16 @@
         <v>3.6</v>
       </c>
       <c r="P57">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q57">
-        <v>2.57</v>
+        <v>2.42</v>
       </c>
       <c r="R57">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="S57">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T57">
         <v>3.08</v>
@@ -9624,10 +9624,10 @@
         <v>2.45</v>
       </c>
       <c r="V57">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W57">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X57">
         <v>1.01</v>
@@ -9639,25 +9639,25 @@
         <v>3.58</v>
       </c>
       <c r="AA57">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AB57">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="AC57">
-        <v>2.78</v>
+        <v>2.98</v>
       </c>
       <c r="AD57">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="AE57">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF57">
         <v>1.64</v>
       </c>
       <c r="AG57">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AK57">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O58">
         <v>3.6</v>
       </c>
       <c r="P58">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q58">
         <v>2.67</v>
@@ -9778,19 +9778,19 @@
         <v>2.31</v>
       </c>
       <c r="S58">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T58">
-        <v>3.34</v>
+        <v>3.75</v>
       </c>
       <c r="U58">
         <v>2.22</v>
       </c>
       <c r="V58">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="W58">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X58">
         <v>1.03</v>
@@ -9929,16 +9929,16 @@
         <v>5.87</v>
       </c>
       <c r="O59">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="P59">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="Q59">
         <v>5.5</v>
       </c>
       <c r="R59">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="S59">
         <v>1.2</v>
@@ -9959,31 +9959,31 @@
         <v>1.02</v>
       </c>
       <c r="Y59">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="Z59">
-        <v>5.1</v>
+        <v>5.01</v>
       </c>
       <c r="AA59">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="AB59">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AC59">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="AD59">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AE59">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AF59">
         <v>1.6</v>
       </c>
       <c r="AG59">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -10252,19 +10252,19 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O61">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="P61">
-        <v>9.300000000000001</v>
+        <v>7</v>
       </c>
       <c r="Q61">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="R61">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="S61">
         <v>1.22</v>
@@ -10273,10 +10273,10 @@
         <v>4</v>
       </c>
       <c r="U61">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="V61">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="W61">
         <v>1.18</v>
@@ -10288,28 +10288,28 @@
         <v>1.08</v>
       </c>
       <c r="Z61">
-        <v>6.5</v>
+        <v>6.54</v>
       </c>
       <c r="AA61">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB61">
-        <v>2.87</v>
+        <v>2.74</v>
       </c>
       <c r="AC61">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="AD61">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AE61">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AF61">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AG61">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AK61">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10587,25 +10587,25 @@
         <v>2.72</v>
       </c>
       <c r="Q63">
-        <v>2.73</v>
+        <v>2.87</v>
       </c>
       <c r="R63">
-        <v>2.36</v>
+        <v>2.49</v>
       </c>
       <c r="S63">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T63">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="U63">
         <v>2.2</v>
       </c>
       <c r="V63">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W63">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X63">
         <v>1.02</v>
@@ -10617,41 +10617,41 @@
         <v>4.95</v>
       </c>
       <c r="AA63">
+        <v>1.51</v>
+      </c>
+      <c r="AB63">
+        <v>2.5</v>
+      </c>
+      <c r="AC63">
+        <v>2.25</v>
+      </c>
+      <c r="AD63">
+        <v>1.62</v>
+      </c>
+      <c r="AE63">
+        <v>1.25</v>
+      </c>
+      <c r="AF63">
         <v>1.44</v>
       </c>
-      <c r="AB63">
-        <v>2.43</v>
-      </c>
-      <c r="AC63">
-        <v>2.15</v>
-      </c>
-      <c r="AD63">
-        <v>1.6</v>
-      </c>
-      <c r="AE63">
+      <c r="AG63">
+        <v>2.5</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ63">
         <v>1.22</v>
       </c>
-      <c r="AF63">
-        <v>1.41</v>
-      </c>
-      <c r="AG63">
-        <v>2.66</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ63">
-        <v>1.19</v>
-      </c>
       <c r="AK63">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -12534,65 +12534,65 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="O75">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="P75">
-        <v>4.27</v>
+        <v>3.7</v>
       </c>
       <c r="Q75">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="R75">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="S75">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T75">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="U75">
-        <v>2.74</v>
+        <v>2.52</v>
       </c>
       <c r="V75">
         <v>1.44</v>
       </c>
       <c r="W75">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X75">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y75">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z75">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AA75">
+        <v>1.84</v>
+      </c>
+      <c r="AB75">
+        <v>1.85</v>
+      </c>
+      <c r="AC75">
+        <v>3</v>
+      </c>
+      <c r="AD75">
+        <v>1.33</v>
+      </c>
+      <c r="AE75">
+        <v>1.08</v>
+      </c>
+      <c r="AF75">
         <v>1.7</v>
       </c>
-      <c r="AB75">
+      <c r="AG75">
         <v>2</v>
       </c>
-      <c r="AC75">
-        <v>3.14</v>
-      </c>
-      <c r="AD75">
-        <v>1.39</v>
-      </c>
-      <c r="AE75">
-        <v>1.12</v>
-      </c>
-      <c r="AF75">
-        <v>1.61</v>
-      </c>
-      <c r="AG75">
-        <v>2.18</v>
-      </c>
       <c r="AH75" t="inlineStr">
         <is>
           <t>[]</t>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK75">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="O79">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P79">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="Q79">
         <v>0</v>
@@ -13225,10 +13225,10 @@
         <v>0</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC79">
         <v>0</v>
@@ -13515,61 +13515,61 @@
         <v>2.2</v>
       </c>
       <c r="O81">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P81">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="Q81">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="R81">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S81">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T81">
-        <v>3.5</v>
+        <v>3.32</v>
       </c>
       <c r="U81">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="V81">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W81">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X81">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y81">
         <v>1.18</v>
       </c>
       <c r="Z81">
-        <v>4.71</v>
+        <v>4.33</v>
       </c>
       <c r="AA81">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AB81">
+        <v>2.08</v>
+      </c>
+      <c r="AC81">
+        <v>2.7</v>
+      </c>
+      <c r="AD81">
+        <v>1.4</v>
+      </c>
+      <c r="AE81">
+        <v>1.13</v>
+      </c>
+      <c r="AF81">
+        <v>1.57</v>
+      </c>
+      <c r="AG81">
         <v>2.3</v>
-      </c>
-      <c r="AC81">
-        <v>2.59</v>
-      </c>
-      <c r="AD81">
-        <v>1.5</v>
-      </c>
-      <c r="AE81">
-        <v>1.19</v>
-      </c>
-      <c r="AF81">
-        <v>1.53</v>
-      </c>
-      <c r="AG81">
-        <v>2.4</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>1.25</v>
       </c>
       <c r="AK81">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13841,10 +13841,10 @@
         <v>1.93</v>
       </c>
       <c r="O83">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P83">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="Q83">
         <v>2.27</v>
@@ -13886,7 +13886,7 @@
         <v>1.93</v>
       </c>
       <c r="AD83">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AE83">
         <v>1.37</v>
@@ -13895,7 +13895,7 @@
         <v>1.29</v>
       </c>
       <c r="AG83">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>1.26</v>
       </c>
       <c r="AK83">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="O84">
-        <v>3.26</v>
+        <v>3.15</v>
       </c>
       <c r="P84">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="Q84">
-        <v>2.87</v>
+        <v>3.04</v>
       </c>
       <c r="R84">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S84">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="T84">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="U84">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="V84">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W84">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X84">
         <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="Z84">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="AA84">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AB84">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AC84">
-        <v>2.88</v>
+        <v>3.28</v>
       </c>
       <c r="AD84">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AE84">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF84">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AG84">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK84">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -15966,55 +15966,55 @@
         <v>2.39</v>
       </c>
       <c r="Q96">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R96">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S96">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T96">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="U96">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V96">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W96">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X96">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y96">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z96">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA96">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB96">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC96">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD96">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE96">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF96">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG96">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK96">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>3.11</v>
+        <v>3.14</v>
       </c>
       <c r="O98">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="P98">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="Q98">
         <v>3.78</v>
@@ -16313,7 +16313,7 @@
         <v>1.08</v>
       </c>
       <c r="X98">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y98">
         <v>1.19</v>
@@ -16322,10 +16322,10 @@
         <v>3.8</v>
       </c>
       <c r="AA98">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AB98">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="AC98">
         <v>2.66</v>
@@ -16337,10 +16337,10 @@
         <v>1.1</v>
       </c>
       <c r="AF98">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG98">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16455,16 +16455,16 @@
         <v>4.28</v>
       </c>
       <c r="Q99">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="R99">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="S99">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T99">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="U99">
         <v>3.18</v>
@@ -16473,28 +16473,28 @@
         <v>1.27</v>
       </c>
       <c r="W99">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X99">
         <v>1.03</v>
       </c>
       <c r="Y99">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z99">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="AA99">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="AB99">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AC99">
-        <v>4.09</v>
+        <v>4.16</v>
       </c>
       <c r="AD99">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AE99">
         <v>1.02</v>
@@ -16503,7 +16503,7 @@
         <v>2.01</v>
       </c>
       <c r="AG99">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK99">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="O102">
-        <v>3.53</v>
+        <v>3.48</v>
       </c>
       <c r="P102">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -16974,10 +16974,10 @@
         <v>3.63</v>
       </c>
       <c r="AA102">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AB102">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AC102">
         <v>3.28</v>
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="O103">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="P103">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q104">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="R104">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S104">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T104">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U104">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V104">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W104">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X104">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y104">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z104">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AA104">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB104">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC104">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD104">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE104">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF104">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG104">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK104">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O110">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q110">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R110">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S110">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T110">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U110">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="V110">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W110">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X110">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y110">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z110">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA110">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AB110">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC110">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD110">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE110">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF110">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG110">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK110">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O112">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="Q112">
         <v>0</v>

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -801,10 +801,10 @@
         <v>2.05</v>
       </c>
       <c r="O3">
-        <v>3.68</v>
+        <v>3.61</v>
       </c>
       <c r="P3">
-        <v>3.3</v>
+        <v>2.81</v>
       </c>
       <c r="Q3">
         <v>2.49</v>
@@ -819,13 +819,13 @@
         <v>3.4</v>
       </c>
       <c r="U3">
-        <v>2.54</v>
+        <v>2.3</v>
       </c>
       <c r="V3">
         <v>1.48</v>
       </c>
       <c r="W3">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X3">
         <v>1.01</v>
@@ -837,7 +837,7 @@
         <v>4.5</v>
       </c>
       <c r="AA3">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB3">
         <v>2.1</v>
@@ -846,7 +846,7 @@
         <v>2.75</v>
       </c>
       <c r="AD3">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE3">
         <v>1.13</v>
@@ -1305,7 +1305,7 @@
         <v>1.35</v>
       </c>
       <c r="T6">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U6">
         <v>2.47</v>
@@ -1323,7 +1323,7 @@
         <v>1.24</v>
       </c>
       <c r="Z6">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AA6">
         <v>1.79</v>
@@ -1332,13 +1332,13 @@
         <v>1.93</v>
       </c>
       <c r="AC6">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="AD6">
         <v>1.4</v>
       </c>
       <c r="AE6">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF6">
         <v>1.7</v>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK6">
         <v>2.05</v>
@@ -3741,10 +3741,10 @@
         <v>0</v>
       </c>
       <c r="Q21">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="R21">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S21">
         <v>1.29</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O33">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="P33">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Q33">
         <v>11</v>
@@ -6355,7 +6355,7 @@
         <v>2.2</v>
       </c>
       <c r="S37">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="T37">
         <v>3.1</v>
@@ -6675,10 +6675,10 @@
         <v>1.39</v>
       </c>
       <c r="Q39">
-        <v>5</v>
+        <v>5.65</v>
       </c>
       <c r="R39">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="S39">
         <v>1.2</v>
@@ -6687,10 +6687,10 @@
         <v>4</v>
       </c>
       <c r="U39">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="V39">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W39">
         <v>1.17</v>
@@ -7001,7 +7001,7 @@
         <v>2.69</v>
       </c>
       <c r="Q41">
-        <v>3.1</v>
+        <v>2.72</v>
       </c>
       <c r="R41">
         <v>2.13</v>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK41">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>7.25</v>
+        <v>6.1</v>
       </c>
       <c r="O45">
-        <v>4.75</v>
+        <v>4.3</v>
       </c>
       <c r="P45">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Q45">
         <v>7.5</v>
@@ -8785,7 +8785,7 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="O52">
         <v>4.4</v>
@@ -8812,7 +8812,7 @@
         <v>1.71</v>
       </c>
       <c r="W52">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="X52">
         <v>1.01</v>
@@ -9612,7 +9612,7 @@
         <v>2.42</v>
       </c>
       <c r="R57">
-        <v>2.13</v>
+        <v>2.33</v>
       </c>
       <c r="S57">
         <v>1.3</v>
@@ -9642,10 +9642,10 @@
         <v>1.7</v>
       </c>
       <c r="AB57">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AC57">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="AD57">
         <v>1.39</v>
@@ -9763,7 +9763,7 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O58">
         <v>3.6</v>
@@ -9938,7 +9938,7 @@
         <v>5.5</v>
       </c>
       <c r="R59">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S59">
         <v>1.2</v>
@@ -9968,7 +9968,7 @@
         <v>1.54</v>
       </c>
       <c r="AB59">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AC59">
         <v>2.34</v>
@@ -10089,31 +10089,31 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="O60">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="P60">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="Q60">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="R60">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="S60">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T60">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="U60">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="V60">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W60">
         <v>1.11</v>
@@ -10122,31 +10122,31 @@
         <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z60">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="AA60">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AB60">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="AC60">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="AD60">
         <v>1.38</v>
       </c>
       <c r="AE60">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF60">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG60">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK60">
         <v>1.4</v>
@@ -10255,19 +10255,19 @@
         <v>1.3</v>
       </c>
       <c r="O61">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="P61">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="Q61">
         <v>1.65</v>
       </c>
       <c r="R61">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="S61">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T61">
         <v>4</v>
@@ -10418,10 +10418,10 @@
         <v>1.75</v>
       </c>
       <c r="O62">
-        <v>4.16</v>
+        <v>4.05</v>
       </c>
       <c r="P62">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="Q62">
         <v>2.18</v>
@@ -10436,10 +10436,10 @@
         <v>4</v>
       </c>
       <c r="U62">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="V62">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="W62">
         <v>1.2</v>
@@ -11079,7 +11079,7 @@
         <v>3.3</v>
       </c>
       <c r="R66">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S66">
         <v>1.41</v>
@@ -11230,7 +11230,7 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="O67">
         <v>3</v>
@@ -11393,19 +11393,19 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="O68">
-        <v>3.94</v>
+        <v>3.88</v>
       </c>
       <c r="P68">
-        <v>4.31</v>
+        <v>4.33</v>
       </c>
       <c r="Q68">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="R68">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="S68">
         <v>1.3</v>
@@ -11414,37 +11414,37 @@
         <v>3.3</v>
       </c>
       <c r="U68">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="V68">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="W68">
         <v>1.08</v>
       </c>
       <c r="X68">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y68">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z68">
-        <v>4.29</v>
+        <v>4.36</v>
       </c>
       <c r="AA68">
         <v>1.67</v>
       </c>
       <c r="AB68">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AC68">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AD68">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE68">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF68">
         <v>1.65</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="O69">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="P69">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>5.66</v>
+        <v>4.6</v>
       </c>
       <c r="O71">
         <v>4.7</v>
       </c>
       <c r="P71">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="Q71">
         <v>5</v>
@@ -11897,13 +11897,13 @@
         <v>2.62</v>
       </c>
       <c r="S71">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T71">
         <v>4</v>
       </c>
       <c r="U71">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="V71">
         <v>1.72</v>
@@ -11915,25 +11915,25 @@
         <v>1.01</v>
       </c>
       <c r="Y71">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z71">
-        <v>5.65</v>
+        <v>6.06</v>
       </c>
       <c r="AA71">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AB71">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AC71">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AD71">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AE71">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AF71">
         <v>1.5</v>
@@ -11952,7 +11952,7 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AK71">
         <v>1.12</v>
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="O72">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="P72">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="Q72">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="R72">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="S72">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="T72">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="U72">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="V72">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="W72">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X72">
         <v>1.01</v>
       </c>
       <c r="Y72">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Z72">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AA72">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AB72">
-        <v>3.21</v>
+        <v>3.28</v>
       </c>
       <c r="AC72">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AD72">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="AE72">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AF72">
         <v>1.3</v>
       </c>
       <c r="AG72">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12208,19 +12208,19 @@
         </is>
       </c>
       <c r="N73">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="O73">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P73">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="Q73">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="R73">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="S73">
         <v>1.25</v>
@@ -12229,13 +12229,13 @@
         <v>3.7</v>
       </c>
       <c r="U73">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="V73">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W73">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X73">
         <v>1.02</v>
@@ -12244,28 +12244,28 @@
         <v>1.12</v>
       </c>
       <c r="Z73">
-        <v>4.7</v>
+        <v>5.25</v>
       </c>
       <c r="AA73">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AB73">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AC73">
         <v>2.27</v>
       </c>
       <c r="AD73">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AE73">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF73">
         <v>1.44</v>
       </c>
       <c r="AG73">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK73">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12371,31 +12371,31 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="O74">
+        <v>4.25</v>
+      </c>
+      <c r="P74">
+        <v>3.8</v>
+      </c>
+      <c r="Q74">
+        <v>2.03</v>
+      </c>
+      <c r="R74">
+        <v>2.45</v>
+      </c>
+      <c r="S74">
+        <v>1.14</v>
+      </c>
+      <c r="T74">
         <v>4.1</v>
       </c>
-      <c r="P74">
-        <v>4.04</v>
-      </c>
-      <c r="Q74">
-        <v>2.17</v>
-      </c>
-      <c r="R74">
-        <v>2.48</v>
-      </c>
-      <c r="S74">
-        <v>1.22</v>
-      </c>
-      <c r="T74">
-        <v>4</v>
-      </c>
       <c r="U74">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V74">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="W74">
         <v>1.2</v>
@@ -12404,31 +12404,31 @@
         <v>1.01</v>
       </c>
       <c r="Y74">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Z74">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="AA74">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AB74">
-        <v>2.59</v>
+        <v>2.87</v>
       </c>
       <c r="AC74">
-        <v>2.06</v>
+        <v>1.87</v>
       </c>
       <c r="AD74">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="AE74">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AF74">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AG74">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,7 +12441,7 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK74">
         <v>2.05</v>
@@ -12543,7 +12543,7 @@
         <v>3.7</v>
       </c>
       <c r="Q75">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="R75">
         <v>2.2</v>
@@ -12573,10 +12573,10 @@
         <v>3.6</v>
       </c>
       <c r="AA75">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="AB75">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AC75">
         <v>3</v>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK75">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -13189,7 +13189,7 @@
         <v>2.2</v>
       </c>
       <c r="O79">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P79">
         <v>2.7</v>
@@ -13376,7 +13376,7 @@
         <v>1.5</v>
       </c>
       <c r="W80">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X80">
         <v>1.01</v>
@@ -13422,7 +13422,7 @@
         <v>1.36</v>
       </c>
       <c r="AK80">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -14182,7 +14182,7 @@
         <v>1.3</v>
       </c>
       <c r="T85">
-        <v>3.05</v>
+        <v>3.34</v>
       </c>
       <c r="U85">
         <v>2.55</v>
@@ -14209,7 +14209,7 @@
         <v>2.12</v>
       </c>
       <c r="AC85">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="AD85">
         <v>1.38</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,80 +14327,80 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.53</v>
+        <v>3.2</v>
       </c>
       <c r="O86">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="P86">
-        <v>4.8</v>
+        <v>2.02</v>
       </c>
       <c r="Q86">
-        <v>2.05</v>
+        <v>3.25</v>
       </c>
       <c r="R86">
-        <v>2.17</v>
+        <v>2.24</v>
       </c>
       <c r="S86">
+        <v>1.35</v>
+      </c>
+      <c r="T86">
+        <v>3</v>
+      </c>
+      <c r="U86">
+        <v>2.62</v>
+      </c>
+      <c r="V86">
+        <v>1.4</v>
+      </c>
+      <c r="W86">
+        <v>1.1</v>
+      </c>
+      <c r="X86">
+        <v>1.01</v>
+      </c>
+      <c r="Y86">
+        <v>1.24</v>
+      </c>
+      <c r="Z86">
+        <v>3.34</v>
+      </c>
+      <c r="AA86">
+        <v>1.95</v>
+      </c>
+      <c r="AB86">
+        <v>1.85</v>
+      </c>
+      <c r="AC86">
+        <v>3.14</v>
+      </c>
+      <c r="AD86">
+        <v>1.27</v>
+      </c>
+      <c r="AE86">
+        <v>1.06</v>
+      </c>
+      <c r="AF86">
+        <v>1.69</v>
+      </c>
+      <c r="AG86">
+        <v>2.1</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ86">
+        <v>1.28</v>
+      </c>
+      <c r="AK86">
         <v>1.32</v>
-      </c>
-      <c r="T86">
-        <v>3.08</v>
-      </c>
-      <c r="U86">
-        <v>2.53</v>
-      </c>
-      <c r="V86">
-        <v>1.44</v>
-      </c>
-      <c r="W86">
-        <v>1.11</v>
-      </c>
-      <c r="X86">
-        <v>1.02</v>
-      </c>
-      <c r="Y86">
-        <v>1.19</v>
-      </c>
-      <c r="Z86">
-        <v>3.95</v>
-      </c>
-      <c r="AA86">
-        <v>1.77</v>
-      </c>
-      <c r="AB86">
-        <v>2.05</v>
-      </c>
-      <c r="AC86">
-        <v>2.88</v>
-      </c>
-      <c r="AD86">
-        <v>1.4</v>
-      </c>
-      <c r="AE86">
-        <v>1.1</v>
-      </c>
-      <c r="AF86">
-        <v>1.75</v>
-      </c>
-      <c r="AG86">
-        <v>1.97</v>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI86" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ86">
-        <v>1.19</v>
-      </c>
-      <c r="AK86">
-        <v>2.26</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="O87">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="P87">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="Q87">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="R87">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="S87">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T87">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="U87">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="V87">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="W87">
         <v>1.1</v>
       </c>
       <c r="X87">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y87">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z87">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="AA87">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AB87">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="AC87">
-        <v>3.14</v>
+        <v>2.7</v>
       </c>
       <c r="AD87">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="AE87">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF87">
         <v>1.69</v>
       </c>
       <c r="AG87">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK87">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
+        <v>1.53</v>
+      </c>
+      <c r="O88">
         <v>3.8</v>
       </c>
-      <c r="O88">
-        <v>3.6</v>
-      </c>
       <c r="P88">
-        <v>1.75</v>
+        <v>4.8</v>
       </c>
       <c r="Q88">
-        <v>4.6</v>
+        <v>2.05</v>
       </c>
       <c r="R88">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="S88">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T88">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="U88">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="V88">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W88">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X88">
         <v>1.02</v>
       </c>
       <c r="Y88">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z88">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="AA88">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AB88">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AC88">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AD88">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE88">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF88">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AG88">
-        <v>2.07</v>
+        <v>1.97</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AK88">
-        <v>1.2</v>
+        <v>2.26</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14988,10 +14988,10 @@
         <v>1.37</v>
       </c>
       <c r="Q90">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="R90">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="S90">
         <v>1.22</v>
@@ -15000,7 +15000,7 @@
         <v>3.9</v>
       </c>
       <c r="U90">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="V90">
         <v>1.75</v>
@@ -15009,34 +15009,34 @@
         <v>1.18</v>
       </c>
       <c r="X90">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y90">
         <v>1.13</v>
       </c>
       <c r="Z90">
-        <v>5.46</v>
+        <v>5.6</v>
       </c>
       <c r="AA90">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AB90">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="AC90">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="AD90">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AE90">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AF90">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AG90">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15052,7 +15052,7 @@
         <v>2.8</v>
       </c>
       <c r="AK90">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15151,19 +15151,19 @@
         <v>2.48</v>
       </c>
       <c r="Q91">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="R91">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="S91">
         <v>1.25</v>
       </c>
       <c r="T91">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="U91">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V91">
         <v>1.6</v>
@@ -15172,28 +15172,28 @@
         <v>1.15</v>
       </c>
       <c r="X91">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y91">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z91">
-        <v>4.6</v>
+        <v>4.98</v>
       </c>
       <c r="AA91">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AB91">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="AC91">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="AD91">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AE91">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AF91">
         <v>1.44</v>
@@ -15215,7 +15215,7 @@
         <v>1.44</v>
       </c>
       <c r="AK91">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15314,22 +15314,22 @@
         <v>2.26</v>
       </c>
       <c r="Q92">
-        <v>3.56</v>
+        <v>3.3</v>
       </c>
       <c r="R92">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="S92">
         <v>1.25</v>
       </c>
       <c r="T92">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U92">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V92">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W92">
         <v>1.15</v>
@@ -15338,22 +15338,22 @@
         <v>1.02</v>
       </c>
       <c r="Y92">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="Z92">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA92">
+        <v>1.57</v>
+      </c>
+      <c r="AB92">
+        <v>2.35</v>
+      </c>
+      <c r="AC92">
+        <v>2.42</v>
+      </c>
+      <c r="AD92">
         <v>1.54</v>
-      </c>
-      <c r="AB92">
-        <v>2.27</v>
-      </c>
-      <c r="AC92">
-        <v>2.33</v>
-      </c>
-      <c r="AD92">
-        <v>1.48</v>
       </c>
       <c r="AE92">
         <v>1.16</v>
@@ -15362,7 +15362,7 @@
         <v>1.53</v>
       </c>
       <c r="AG92">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15477,10 +15477,10 @@
         <v>2.21</v>
       </c>
       <c r="Q93">
-        <v>3.54</v>
+        <v>3.75</v>
       </c>
       <c r="R93">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S93">
         <v>1.3</v>
@@ -15489,7 +15489,7 @@
         <v>3.25</v>
       </c>
       <c r="U93">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="V93">
         <v>1.44</v>
@@ -15498,34 +15498,34 @@
         <v>1.11</v>
       </c>
       <c r="X93">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y93">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z93">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AA93">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB93">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AC93">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AD93">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AE93">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF93">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG93">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK93">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15640,22 +15640,22 @@
         <v>1.87</v>
       </c>
       <c r="Q94">
-        <v>3.95</v>
+        <v>3.98</v>
       </c>
       <c r="R94">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="S94">
         <v>1.25</v>
       </c>
       <c r="T94">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U94">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="V94">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W94">
         <v>1.12</v>
@@ -15664,10 +15664,10 @@
         <v>1.03</v>
       </c>
       <c r="Y94">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="Z94">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="AA94">
         <v>1.57</v>
@@ -15794,31 +15794,31 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="O95">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P95">
         <v>2.6</v>
       </c>
       <c r="Q95">
-        <v>2.95</v>
+        <v>3.02</v>
       </c>
       <c r="R95">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="S95">
         <v>1.25</v>
       </c>
       <c r="T95">
-        <v>3.8</v>
+        <v>3.34</v>
       </c>
       <c r="U95">
         <v>2.25</v>
       </c>
       <c r="V95">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W95">
         <v>1.13</v>
@@ -15830,22 +15830,22 @@
         <v>1.11</v>
       </c>
       <c r="Z95">
-        <v>4.8</v>
+        <v>4.95</v>
       </c>
       <c r="AA95">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AB95">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AC95">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="AD95">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="AE95">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF95">
         <v>1.4</v>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AK95">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -16190,7 +16190,7 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK97">
         <v>1.73</v>
@@ -18085,55 +18085,55 @@
         <v>0</v>
       </c>
       <c r="Q109">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="R109">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S109">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T109">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U109">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V109">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W109">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X109">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y109">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z109">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA109">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AB109">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AC109">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD109">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE109">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF109">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG109">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK109">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL109">
         <v>0</v>

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="O31">
         <v>3.62</v>
       </c>
       <c r="P31">
-        <v>2.39</v>
+        <v>2.49</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5727,7 +5727,7 @@
         <v>6.4</v>
       </c>
       <c r="AA33">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AB33">
         <v>3.2</v>
@@ -5857,7 +5857,7 @@
         <v>3.24</v>
       </c>
       <c r="P34">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -6087,7 +6087,7 @@
         <v>1.18</v>
       </c>
       <c r="AK35">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK37">
         <v>1.2</v>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK44">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -8465,7 +8465,7 @@
         <v>3.5</v>
       </c>
       <c r="P50">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q50">
         <v>3.62</v>
@@ -8498,10 +8498,10 @@
         <v>4.35</v>
       </c>
       <c r="AA50">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AB50">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AC50">
         <v>2.42</v>
@@ -8532,7 +8532,7 @@
         <v>1.24</v>
       </c>
       <c r="AK50">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8661,10 +8661,10 @@
         <v>0</v>
       </c>
       <c r="AA51">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB51">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC51">
         <v>0</v>
@@ -8806,7 +8806,7 @@
         <v>4</v>
       </c>
       <c r="U52">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="V52">
         <v>1.71</v>
@@ -8839,10 +8839,10 @@
         <v>1.27</v>
       </c>
       <c r="AF52">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG52">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>2.5</v>
       </c>
       <c r="O53">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P53">
         <v>2.2</v>
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.23</v>
+        <v>1.58</v>
       </c>
       <c r="AK53">
         <v>1.41</v>
@@ -9123,19 +9123,19 @@
         <v>3.36</v>
       </c>
       <c r="R54">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="S54">
         <v>1.14</v>
       </c>
       <c r="T54">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="U54">
         <v>1.91</v>
       </c>
       <c r="V54">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="W54">
         <v>1.18</v>
@@ -9159,7 +9159,7 @@
         <v>1.94</v>
       </c>
       <c r="AD54">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="AE54">
         <v>1.33</v>
@@ -9452,7 +9452,7 @@
         <v>2.4</v>
       </c>
       <c r="S56">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T56">
         <v>4</v>
@@ -9639,7 +9639,7 @@
         <v>3.58</v>
       </c>
       <c r="AA57">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AB57">
         <v>2.04</v>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK57">
         <v>1.69</v>
@@ -9935,10 +9935,10 @@
         <v>1.49</v>
       </c>
       <c r="Q59">
-        <v>5.5</v>
+        <v>4.53</v>
       </c>
       <c r="R59">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S59">
         <v>1.2</v>
@@ -9968,7 +9968,7 @@
         <v>1.54</v>
       </c>
       <c r="AB59">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AC59">
         <v>2.34</v>
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK59">
         <v>1.11</v>
@@ -10273,10 +10273,10 @@
         <v>4</v>
       </c>
       <c r="U61">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="V61">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="W61">
         <v>1.18</v>
@@ -10297,10 +10297,10 @@
         <v>2.74</v>
       </c>
       <c r="AC61">
-        <v>2.13</v>
+        <v>2.01</v>
       </c>
       <c r="AD61">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AE61">
         <v>1.27</v>
@@ -10325,7 +10325,7 @@
         <v>1.04</v>
       </c>
       <c r="AK61">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10651,7 +10651,7 @@
         <v>1.22</v>
       </c>
       <c r="AK63">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10913,10 +10913,10 @@
         <v>3.2</v>
       </c>
       <c r="Q65">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="R65">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S65">
         <v>1.36</v>
@@ -10925,7 +10925,7 @@
         <v>2.83</v>
       </c>
       <c r="U65">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="V65">
         <v>1.4</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,80 +11067,80 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.45</v>
+        <v>1.65</v>
       </c>
       <c r="O66">
-        <v>3.25</v>
+        <v>3.88</v>
       </c>
       <c r="P66">
-        <v>2.45</v>
+        <v>4.33</v>
       </c>
       <c r="Q66">
+        <v>2.2</v>
+      </c>
+      <c r="R66">
+        <v>2.41</v>
+      </c>
+      <c r="S66">
+        <v>1.3</v>
+      </c>
+      <c r="T66">
         <v>3.3</v>
       </c>
-      <c r="R66">
+      <c r="U66">
+        <v>2.52</v>
+      </c>
+      <c r="V66">
+        <v>1.51</v>
+      </c>
+      <c r="W66">
+        <v>1.08</v>
+      </c>
+      <c r="X66">
+        <v>1.04</v>
+      </c>
+      <c r="Y66">
+        <v>1.21</v>
+      </c>
+      <c r="Z66">
+        <v>4.36</v>
+      </c>
+      <c r="AA66">
+        <v>1.67</v>
+      </c>
+      <c r="AB66">
+        <v>2</v>
+      </c>
+      <c r="AC66">
+        <v>2.75</v>
+      </c>
+      <c r="AD66">
+        <v>1.4</v>
+      </c>
+      <c r="AE66">
+        <v>1.13</v>
+      </c>
+      <c r="AF66">
+        <v>1.65</v>
+      </c>
+      <c r="AG66">
+        <v>2.1</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ66">
+        <v>1.2</v>
+      </c>
+      <c r="AK66">
         <v>2.05</v>
-      </c>
-      <c r="S66">
-        <v>1.41</v>
-      </c>
-      <c r="T66">
-        <v>2.8</v>
-      </c>
-      <c r="U66">
-        <v>2.68</v>
-      </c>
-      <c r="V66">
-        <v>1.39</v>
-      </c>
-      <c r="W66">
-        <v>1.07</v>
-      </c>
-      <c r="X66">
-        <v>1.03</v>
-      </c>
-      <c r="Y66">
-        <v>1.3</v>
-      </c>
-      <c r="Z66">
-        <v>3.3</v>
-      </c>
-      <c r="AA66">
-        <v>1.91</v>
-      </c>
-      <c r="AB66">
-        <v>1.77</v>
-      </c>
-      <c r="AC66">
-        <v>3.5</v>
-      </c>
-      <c r="AD66">
-        <v>1.25</v>
-      </c>
-      <c r="AE66">
-        <v>1.06</v>
-      </c>
-      <c r="AF66">
-        <v>1.75</v>
-      </c>
-      <c r="AG66">
-        <v>1.95</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ66">
-        <v>1.33</v>
-      </c>
-      <c r="AK66">
-        <v>1.4</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11263,31 +11263,31 @@
         <v>1.05</v>
       </c>
       <c r="Y67">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Z67">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="AA67">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AB67">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC67">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="AD67">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE67">
         <v>1.03</v>
       </c>
       <c r="AF67">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG67">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK67">
         <v>1.4</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,80 +11393,80 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.65</v>
+        <v>2.55</v>
       </c>
       <c r="O68">
-        <v>3.88</v>
+        <v>3.25</v>
       </c>
       <c r="P68">
-        <v>4.33</v>
+        <v>2.45</v>
       </c>
       <c r="Q68">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="R68">
-        <v>2.41</v>
+        <v>2.05</v>
       </c>
       <c r="S68">
+        <v>1.41</v>
+      </c>
+      <c r="T68">
+        <v>2.8</v>
+      </c>
+      <c r="U68">
+        <v>2.68</v>
+      </c>
+      <c r="V68">
+        <v>1.39</v>
+      </c>
+      <c r="W68">
+        <v>1.07</v>
+      </c>
+      <c r="X68">
+        <v>1.03</v>
+      </c>
+      <c r="Y68">
         <v>1.3</v>
       </c>
-      <c r="T68">
+      <c r="Z68">
         <v>3.3</v>
       </c>
-      <c r="U68">
-        <v>2.52</v>
-      </c>
-      <c r="V68">
-        <v>1.51</v>
-      </c>
-      <c r="W68">
-        <v>1.08</v>
-      </c>
-      <c r="X68">
-        <v>1.04</v>
-      </c>
-      <c r="Y68">
-        <v>1.21</v>
-      </c>
-      <c r="Z68">
-        <v>4.36</v>
-      </c>
       <c r="AA68">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AB68">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AC68">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="AD68">
+        <v>1.25</v>
+      </c>
+      <c r="AE68">
+        <v>1.06</v>
+      </c>
+      <c r="AF68">
+        <v>1.75</v>
+      </c>
+      <c r="AG68">
+        <v>1.95</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ68">
         <v>1.4</v>
       </c>
-      <c r="AE68">
-        <v>1.13</v>
-      </c>
-      <c r="AF68">
-        <v>1.65</v>
-      </c>
-      <c r="AG68">
-        <v>2.1</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ68">
-        <v>1.2</v>
-      </c>
       <c r="AK68">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11728,7 +11728,7 @@
         <v>4.33</v>
       </c>
       <c r="Q70">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="R70">
         <v>2.43</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="O71">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="P71">
-        <v>1.48</v>
+        <v>1.95</v>
       </c>
       <c r="Q71">
-        <v>5</v>
+        <v>3.28</v>
       </c>
       <c r="R71">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="S71">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T71">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="U71">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="V71">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="W71">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="X71">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z71">
-        <v>6.06</v>
+        <v>5.25</v>
       </c>
       <c r="AA71">
+        <v>1.53</v>
+      </c>
+      <c r="AB71">
+        <v>2.4</v>
+      </c>
+      <c r="AC71">
+        <v>2.27</v>
+      </c>
+      <c r="AD71">
+        <v>1.57</v>
+      </c>
+      <c r="AE71">
+        <v>1.25</v>
+      </c>
+      <c r="AF71">
         <v>1.44</v>
       </c>
-      <c r="AB71">
-        <v>2.7</v>
-      </c>
-      <c r="AC71">
-        <v>1.95</v>
-      </c>
-      <c r="AD71">
-        <v>1.73</v>
-      </c>
-      <c r="AE71">
-        <v>1.3</v>
-      </c>
-      <c r="AF71">
-        <v>1.5</v>
-      </c>
       <c r="AG71">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AK71">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.05</v>
+        <v>4.6</v>
       </c>
       <c r="O72">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="P72">
-        <v>2.7</v>
+        <v>1.48</v>
       </c>
       <c r="Q72">
-        <v>2.33</v>
+        <v>5</v>
       </c>
       <c r="R72">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="S72">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T72">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="U72">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="V72">
-        <v>1.88</v>
+        <v>1.72</v>
       </c>
       <c r="W72">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X72">
         <v>1.01</v>
       </c>
       <c r="Y72">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="Z72">
-        <v>7.2</v>
+        <v>6.06</v>
       </c>
       <c r="AA72">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AB72">
-        <v>3.28</v>
+        <v>2.7</v>
       </c>
       <c r="AC72">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AD72">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="AE72">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AF72">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AG72">
-        <v>3.5</v>
+        <v>2.45</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AK72">
-        <v>1.65</v>
+        <v>1.12</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,65 +12208,65 @@
         </is>
       </c>
       <c r="N73">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="O73">
+        <v>4.1</v>
+      </c>
+      <c r="P73">
+        <v>2.7</v>
+      </c>
+      <c r="Q73">
+        <v>2.33</v>
+      </c>
+      <c r="R73">
+        <v>2.5</v>
+      </c>
+      <c r="S73">
+        <v>1.17</v>
+      </c>
+      <c r="T73">
+        <v>4.5</v>
+      </c>
+      <c r="U73">
+        <v>1.9</v>
+      </c>
+      <c r="V73">
+        <v>1.88</v>
+      </c>
+      <c r="W73">
+        <v>1.22</v>
+      </c>
+      <c r="X73">
+        <v>1.01</v>
+      </c>
+      <c r="Y73">
+        <v>1.03</v>
+      </c>
+      <c r="Z73">
+        <v>7.2</v>
+      </c>
+      <c r="AA73">
+        <v>1.25</v>
+      </c>
+      <c r="AB73">
+        <v>3.28</v>
+      </c>
+      <c r="AC73">
+        <v>1.82</v>
+      </c>
+      <c r="AD73">
+        <v>1.96</v>
+      </c>
+      <c r="AE73">
+        <v>1.39</v>
+      </c>
+      <c r="AF73">
+        <v>1.3</v>
+      </c>
+      <c r="AG73">
         <v>3.5</v>
       </c>
-      <c r="P73">
-        <v>1.95</v>
-      </c>
-      <c r="Q73">
-        <v>3.28</v>
-      </c>
-      <c r="R73">
-        <v>2.3</v>
-      </c>
-      <c r="S73">
-        <v>1.25</v>
-      </c>
-      <c r="T73">
-        <v>3.7</v>
-      </c>
-      <c r="U73">
-        <v>2.13</v>
-      </c>
-      <c r="V73">
-        <v>1.61</v>
-      </c>
-      <c r="W73">
-        <v>1.13</v>
-      </c>
-      <c r="X73">
-        <v>1.02</v>
-      </c>
-      <c r="Y73">
-        <v>1.12</v>
-      </c>
-      <c r="Z73">
-        <v>5.25</v>
-      </c>
-      <c r="AA73">
-        <v>1.53</v>
-      </c>
-      <c r="AB73">
-        <v>2.4</v>
-      </c>
-      <c r="AC73">
-        <v>2.27</v>
-      </c>
-      <c r="AD73">
-        <v>1.57</v>
-      </c>
-      <c r="AE73">
-        <v>1.25</v>
-      </c>
-      <c r="AF73">
-        <v>1.44</v>
-      </c>
-      <c r="AG73">
-        <v>2.55</v>
-      </c>
       <c r="AH73" t="inlineStr">
         <is>
           <t>[]</t>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK73">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12543,7 +12543,7 @@
         <v>3.7</v>
       </c>
       <c r="Q75">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="R75">
         <v>2.2</v>
@@ -12561,22 +12561,22 @@
         <v>1.44</v>
       </c>
       <c r="W75">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X75">
         <v>1.02</v>
       </c>
       <c r="Y75">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z75">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA75">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AB75">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AC75">
         <v>3</v>
@@ -12585,13 +12585,13 @@
         <v>1.33</v>
       </c>
       <c r="AE75">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF75">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG75">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK75">
         <v>1.83</v>
@@ -12930,7 +12930,7 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK77">
         <v>1.79</v>
@@ -13035,7 +13035,7 @@
         <v>4.68</v>
       </c>
       <c r="R78">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="S78">
         <v>1.33</v>
@@ -13225,10 +13225,10 @@
         <v>0</v>
       </c>
       <c r="AA79">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AB79">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AC79">
         <v>0</v>
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="O80">
         <v>3.4</v>
       </c>
       <c r="P80">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="Q80">
         <v>2.88</v>
@@ -13376,7 +13376,7 @@
         <v>1.5</v>
       </c>
       <c r="W80">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X80">
         <v>1.01</v>
@@ -13388,7 +13388,7 @@
         <v>4.33</v>
       </c>
       <c r="AA80">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB80">
         <v>2.22</v>
@@ -13403,10 +13403,10 @@
         <v>1.14</v>
       </c>
       <c r="AF80">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG80">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13847,7 +13847,7 @@
         <v>2.9</v>
       </c>
       <c r="Q83">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="R83">
         <v>2.47</v>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK83">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14040,10 +14040,10 @@
         <v>3.08</v>
       </c>
       <c r="AA84">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB84">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC84">
         <v>3.28</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,61 +14327,61 @@
         </is>
       </c>
       <c r="N86">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="O86">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="P86">
-        <v>2.02</v>
+        <v>1.77</v>
       </c>
       <c r="Q86">
-        <v>3.25</v>
+        <v>4.68</v>
       </c>
       <c r="R86">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="S86">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="T86">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="U86">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="V86">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W86">
         <v>1.1</v>
       </c>
       <c r="X86">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y86">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="Z86">
-        <v>3.34</v>
+        <v>3.75</v>
       </c>
       <c r="AA86">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AB86">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AC86">
-        <v>3.14</v>
+        <v>2.69</v>
       </c>
       <c r="AD86">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AE86">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF86">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AG86">
         <v>2.1</v>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK86">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>3.8</v>
+        <v>1.53</v>
       </c>
       <c r="O87">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="P87">
-        <v>1.75</v>
+        <v>4.8</v>
       </c>
       <c r="Q87">
-        <v>4.6</v>
+        <v>2.05</v>
       </c>
       <c r="R87">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="S87">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T87">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="U87">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="V87">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W87">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X87">
         <v>1.02</v>
       </c>
       <c r="Y87">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z87">
-        <v>3.8</v>
+        <v>4.02</v>
       </c>
       <c r="AA87">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB87">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="AC87">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="AD87">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AE87">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF87">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AG87">
-        <v>2.07</v>
+        <v>1.97</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AK87">
-        <v>1.2</v>
+        <v>2.26</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,80 +14653,80 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.53</v>
+        <v>3</v>
       </c>
       <c r="O88">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="P88">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="Q88">
-        <v>2.05</v>
+        <v>3.25</v>
       </c>
       <c r="R88">
-        <v>2.17</v>
+        <v>2.24</v>
       </c>
       <c r="S88">
+        <v>1.35</v>
+      </c>
+      <c r="T88">
+        <v>3</v>
+      </c>
+      <c r="U88">
+        <v>2.62</v>
+      </c>
+      <c r="V88">
+        <v>1.4</v>
+      </c>
+      <c r="W88">
+        <v>1.1</v>
+      </c>
+      <c r="X88">
+        <v>1.01</v>
+      </c>
+      <c r="Y88">
+        <v>1.24</v>
+      </c>
+      <c r="Z88">
+        <v>3.34</v>
+      </c>
+      <c r="AA88">
+        <v>1.85</v>
+      </c>
+      <c r="AB88">
+        <v>1.86</v>
+      </c>
+      <c r="AC88">
+        <v>3.14</v>
+      </c>
+      <c r="AD88">
+        <v>1.27</v>
+      </c>
+      <c r="AE88">
+        <v>1.06</v>
+      </c>
+      <c r="AF88">
+        <v>1.69</v>
+      </c>
+      <c r="AG88">
+        <v>2.1</v>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ88">
+        <v>1.28</v>
+      </c>
+      <c r="AK88">
         <v>1.32</v>
-      </c>
-      <c r="T88">
-        <v>3.08</v>
-      </c>
-      <c r="U88">
-        <v>2.53</v>
-      </c>
-      <c r="V88">
-        <v>1.44</v>
-      </c>
-      <c r="W88">
-        <v>1.11</v>
-      </c>
-      <c r="X88">
-        <v>1.02</v>
-      </c>
-      <c r="Y88">
-        <v>1.19</v>
-      </c>
-      <c r="Z88">
-        <v>3.95</v>
-      </c>
-      <c r="AA88">
-        <v>1.77</v>
-      </c>
-      <c r="AB88">
-        <v>2.05</v>
-      </c>
-      <c r="AC88">
-        <v>2.88</v>
-      </c>
-      <c r="AD88">
-        <v>1.4</v>
-      </c>
-      <c r="AE88">
-        <v>1.1</v>
-      </c>
-      <c r="AF88">
-        <v>1.75</v>
-      </c>
-      <c r="AG88">
-        <v>1.97</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI88" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ88">
-        <v>1.19</v>
-      </c>
-      <c r="AK88">
-        <v>2.26</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14816,61 +14816,61 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="O89">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="P89">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q89">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R89">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="S89">
+        <v>1.2</v>
+      </c>
+      <c r="T89">
+        <v>3.78</v>
+      </c>
+      <c r="U89">
+        <v>2.2</v>
+      </c>
+      <c r="V89">
+        <v>1.6</v>
+      </c>
+      <c r="W89">
+        <v>1.14</v>
+      </c>
+      <c r="X89">
+        <v>0</v>
+      </c>
+      <c r="Y89">
+        <v>1.15</v>
+      </c>
+      <c r="Z89">
+        <v>5.25</v>
+      </c>
+      <c r="AA89">
+        <v>1.49</v>
+      </c>
+      <c r="AB89">
+        <v>2.57</v>
+      </c>
+      <c r="AC89">
+        <v>2.26</v>
+      </c>
+      <c r="AD89">
+        <v>1.64</v>
+      </c>
+      <c r="AE89">
         <v>1.25</v>
       </c>
-      <c r="T89">
-        <v>3.65</v>
-      </c>
-      <c r="U89">
-        <v>2.17</v>
-      </c>
-      <c r="V89">
-        <v>1.62</v>
-      </c>
-      <c r="W89">
-        <v>1.16</v>
-      </c>
-      <c r="X89">
-        <v>0</v>
-      </c>
-      <c r="Y89">
-        <v>1.14</v>
-      </c>
-      <c r="Z89">
-        <v>4.6</v>
-      </c>
-      <c r="AA89">
-        <v>1.5</v>
-      </c>
-      <c r="AB89">
-        <v>2.4</v>
-      </c>
-      <c r="AC89">
-        <v>2.25</v>
-      </c>
-      <c r="AD89">
-        <v>1.62</v>
-      </c>
-      <c r="AE89">
-        <v>1.22</v>
-      </c>
       <c r="AF89">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG89">
         <v>2.18</v>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK89">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -15797,7 +15797,7 @@
         <v>2.53</v>
       </c>
       <c r="O95">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P95">
         <v>2.6</v>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AK95">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -16138,7 +16138,7 @@
         <v>1.36</v>
       </c>
       <c r="T97">
-        <v>3.11</v>
+        <v>2.92</v>
       </c>
       <c r="U97">
         <v>2.75</v>
@@ -16156,7 +16156,7 @@
         <v>1.27</v>
       </c>
       <c r="Z97">
-        <v>3.74</v>
+        <v>3.34</v>
       </c>
       <c r="AA97">
         <v>1.94</v>
@@ -16165,7 +16165,7 @@
         <v>1.94</v>
       </c>
       <c r="AC97">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="AD97">
         <v>1.36</v>
@@ -16174,7 +16174,7 @@
         <v>1.08</v>
       </c>
       <c r="AF97">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG97">
         <v>2.05</v>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK97">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16292,22 +16292,22 @@
         <v>2.3</v>
       </c>
       <c r="Q98">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="R98">
         <v>2.2</v>
       </c>
       <c r="S98">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="T98">
-        <v>3.08</v>
+        <v>2.87</v>
       </c>
       <c r="U98">
         <v>2.44</v>
       </c>
       <c r="V98">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W98">
         <v>1.08</v>
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O102">
         <v>3.48</v>
       </c>
       <c r="P102">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
@@ -16974,7 +16974,7 @@
         <v>3.63</v>
       </c>
       <c r="AA102">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB102">
         <v>1.92</v>
@@ -18239,7 +18239,7 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="O110">
         <v>2.85</v>
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="O112">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="P112">
-        <v>4.17</v>
+        <v>3.5</v>
       </c>
       <c r="Q112">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R112">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S112">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T112">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U112">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V112">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W112">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X112">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y112">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z112">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA112">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB112">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC112">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AD112">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE112">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF112">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG112">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK112">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18767,10 +18767,10 @@
         <v>0</v>
       </c>
       <c r="AA113">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB113">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC113">
         <v>0</v>

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -3901,7 +3901,7 @@
         <v>10.7</v>
       </c>
       <c r="P22">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Q22">
         <v>1.41</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O33">
         <v>7.8</v>
       </c>
       <c r="P33">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Q33">
         <v>11</v>
@@ -5761,7 +5761,7 @@
         <v>1.06</v>
       </c>
       <c r="AK33">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -8462,10 +8462,10 @@
         <v>2.87</v>
       </c>
       <c r="O50">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P50">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q50">
         <v>3.62</v>
@@ -8507,7 +8507,7 @@
         <v>2.42</v>
       </c>
       <c r="AD50">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE50">
         <v>1.15</v>
@@ -8785,7 +8785,7 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="O52">
         <v>4.4</v>
@@ -8827,7 +8827,7 @@
         <v>1.37</v>
       </c>
       <c r="AB52">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AC52">
         <v>2.02</v>
@@ -8842,7 +8842,7 @@
         <v>1.44</v>
       </c>
       <c r="AG52">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,80 +10904,80 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="O65">
-        <v>3.1</v>
+        <v>3.88</v>
       </c>
       <c r="P65">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="Q65">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="R65">
+        <v>2.42</v>
+      </c>
+      <c r="S65">
+        <v>1.3</v>
+      </c>
+      <c r="T65">
+        <v>3.3</v>
+      </c>
+      <c r="U65">
+        <v>2.52</v>
+      </c>
+      <c r="V65">
+        <v>1.51</v>
+      </c>
+      <c r="W65">
+        <v>1.08</v>
+      </c>
+      <c r="X65">
+        <v>1.03</v>
+      </c>
+      <c r="Y65">
+        <v>1.2</v>
+      </c>
+      <c r="Z65">
+        <v>4.36</v>
+      </c>
+      <c r="AA65">
+        <v>1.67</v>
+      </c>
+      <c r="AB65">
+        <v>2.18</v>
+      </c>
+      <c r="AC65">
+        <v>2.75</v>
+      </c>
+      <c r="AD65">
+        <v>1.4</v>
+      </c>
+      <c r="AE65">
+        <v>1.13</v>
+      </c>
+      <c r="AF65">
+        <v>1.65</v>
+      </c>
+      <c r="AG65">
+        <v>2.1</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ65">
+        <v>1.2</v>
+      </c>
+      <c r="AK65">
         <v>2.05</v>
-      </c>
-      <c r="S65">
-        <v>1.36</v>
-      </c>
-      <c r="T65">
-        <v>2.83</v>
-      </c>
-      <c r="U65">
-        <v>2.75</v>
-      </c>
-      <c r="V65">
-        <v>1.4</v>
-      </c>
-      <c r="W65">
-        <v>1.05</v>
-      </c>
-      <c r="X65">
-        <v>1.01</v>
-      </c>
-      <c r="Y65">
-        <v>1.28</v>
-      </c>
-      <c r="Z65">
-        <v>3.33</v>
-      </c>
-      <c r="AA65">
-        <v>2.02</v>
-      </c>
-      <c r="AB65">
-        <v>1.74</v>
-      </c>
-      <c r="AC65">
-        <v>3.5</v>
-      </c>
-      <c r="AD65">
-        <v>1.22</v>
-      </c>
-      <c r="AE65">
-        <v>1.03</v>
-      </c>
-      <c r="AF65">
-        <v>1.8</v>
-      </c>
-      <c r="AG65">
-        <v>1.9</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ65">
-        <v>1.28</v>
-      </c>
-      <c r="AK65">
-        <v>1.7</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,80 +11067,80 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.65</v>
+        <v>2.55</v>
       </c>
       <c r="O66">
-        <v>3.88</v>
+        <v>3.25</v>
       </c>
       <c r="P66">
-        <v>4.33</v>
+        <v>2.45</v>
       </c>
       <c r="Q66">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="R66">
-        <v>2.41</v>
+        <v>2.05</v>
       </c>
       <c r="S66">
+        <v>1.4</v>
+      </c>
+      <c r="T66">
+        <v>2.8</v>
+      </c>
+      <c r="U66">
+        <v>2.7</v>
+      </c>
+      <c r="V66">
+        <v>1.39</v>
+      </c>
+      <c r="W66">
+        <v>1.07</v>
+      </c>
+      <c r="X66">
+        <v>1.03</v>
+      </c>
+      <c r="Y66">
         <v>1.3</v>
       </c>
-      <c r="T66">
+      <c r="Z66">
         <v>3.3</v>
       </c>
-      <c r="U66">
-        <v>2.52</v>
-      </c>
-      <c r="V66">
-        <v>1.51</v>
-      </c>
-      <c r="W66">
-        <v>1.08</v>
-      </c>
-      <c r="X66">
-        <v>1.04</v>
-      </c>
-      <c r="Y66">
-        <v>1.21</v>
-      </c>
-      <c r="Z66">
-        <v>4.36</v>
-      </c>
       <c r="AA66">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AB66">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AC66">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="AD66">
+        <v>1.25</v>
+      </c>
+      <c r="AE66">
+        <v>1.06</v>
+      </c>
+      <c r="AF66">
+        <v>1.75</v>
+      </c>
+      <c r="AG66">
+        <v>1.95</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ66">
         <v>1.4</v>
       </c>
-      <c r="AE66">
-        <v>1.13</v>
-      </c>
-      <c r="AF66">
-        <v>1.65</v>
-      </c>
-      <c r="AG66">
-        <v>2.1</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ66">
-        <v>1.2</v>
-      </c>
       <c r="AK66">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
+        <v>2.15</v>
+      </c>
+      <c r="O67">
+        <v>3.1</v>
+      </c>
+      <c r="P67">
+        <v>3.2</v>
+      </c>
+      <c r="Q67">
         <v>2.75</v>
       </c>
-      <c r="O67">
-        <v>3</v>
-      </c>
-      <c r="P67">
-        <v>2.45</v>
-      </c>
-      <c r="Q67">
+      <c r="R67">
+        <v>2.05</v>
+      </c>
+      <c r="S67">
+        <v>1.36</v>
+      </c>
+      <c r="T67">
+        <v>2.83</v>
+      </c>
+      <c r="U67">
+        <v>2.75</v>
+      </c>
+      <c r="V67">
+        <v>1.4</v>
+      </c>
+      <c r="W67">
+        <v>1.05</v>
+      </c>
+      <c r="X67">
+        <v>1.01</v>
+      </c>
+      <c r="Y67">
+        <v>1.28</v>
+      </c>
+      <c r="Z67">
+        <v>3.33</v>
+      </c>
+      <c r="AA67">
+        <v>2.02</v>
+      </c>
+      <c r="AB67">
+        <v>1.74</v>
+      </c>
+      <c r="AC67">
         <v>3.5</v>
       </c>
-      <c r="R67">
-        <v>1.95</v>
-      </c>
-      <c r="S67">
-        <v>1.49</v>
-      </c>
-      <c r="T67">
-        <v>2.39</v>
-      </c>
-      <c r="U67">
-        <v>3.1</v>
-      </c>
-      <c r="V67">
-        <v>1.33</v>
-      </c>
-      <c r="W67">
-        <v>1.06</v>
-      </c>
-      <c r="X67">
-        <v>1.05</v>
-      </c>
-      <c r="Y67">
-        <v>1.4</v>
-      </c>
-      <c r="Z67">
-        <v>2.75</v>
-      </c>
-      <c r="AA67">
-        <v>2.21</v>
-      </c>
-      <c r="AB67">
-        <v>1.57</v>
-      </c>
-      <c r="AC67">
-        <v>4.6</v>
-      </c>
       <c r="AD67">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE67">
         <v>1.03</v>
       </c>
       <c r="AF67">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AG67">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AK67">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="O68">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P68">
         <v>2.45</v>
       </c>
       <c r="Q68">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R68">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="S68">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="T68">
-        <v>2.8</v>
+        <v>2.39</v>
       </c>
       <c r="U68">
-        <v>2.68</v>
+        <v>3.1</v>
       </c>
       <c r="V68">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="W68">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X68">
+        <v>1.05</v>
+      </c>
+      <c r="Y68">
+        <v>1.4</v>
+      </c>
+      <c r="Z68">
+        <v>2.75</v>
+      </c>
+      <c r="AA68">
+        <v>2.21</v>
+      </c>
+      <c r="AB68">
+        <v>1.57</v>
+      </c>
+      <c r="AC68">
+        <v>4.6</v>
+      </c>
+      <c r="AD68">
+        <v>1.17</v>
+      </c>
+      <c r="AE68">
         <v>1.03</v>
       </c>
-      <c r="Y68">
-        <v>1.3</v>
-      </c>
-      <c r="Z68">
-        <v>3.3</v>
-      </c>
-      <c r="AA68">
-        <v>2.05</v>
-      </c>
-      <c r="AB68">
-        <v>1.75</v>
-      </c>
-      <c r="AC68">
-        <v>3.5</v>
-      </c>
-      <c r="AD68">
-        <v>1.25</v>
-      </c>
-      <c r="AE68">
-        <v>1.06</v>
-      </c>
       <c r="AF68">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AG68">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
+        <v>1.36</v>
+      </c>
+      <c r="AK68">
         <v>1.4</v>
-      </c>
-      <c r="AK68">
-        <v>1.5</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11562,7 +11562,7 @@
         <v>4.33</v>
       </c>
       <c r="P69">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11792,7 +11792,7 @@
         <v>1.25</v>
       </c>
       <c r="AK70">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -13032,7 +13032,7 @@
         <v>1.79</v>
       </c>
       <c r="Q78">
-        <v>4.68</v>
+        <v>4.4</v>
       </c>
       <c r="R78">
         <v>2.2</v>
@@ -13050,7 +13050,7 @@
         <v>1.44</v>
       </c>
       <c r="W78">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X78">
         <v>1.03</v>
@@ -13844,25 +13844,25 @@
         <v>4</v>
       </c>
       <c r="P83">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="Q83">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R83">
-        <v>2.47</v>
+        <v>2.52</v>
       </c>
       <c r="S83">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T83">
         <v>4.8</v>
       </c>
       <c r="U83">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="V83">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="W83">
         <v>1.21</v>
@@ -13886,13 +13886,13 @@
         <v>1.93</v>
       </c>
       <c r="AD83">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="AE83">
         <v>1.37</v>
       </c>
       <c r="AF83">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AG83">
         <v>3</v>
@@ -13911,7 +13911,7 @@
         <v>1.25</v>
       </c>
       <c r="AK83">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
+        <v>1.53</v>
+      </c>
+      <c r="O86">
         <v>3.9</v>
       </c>
-      <c r="O86">
-        <v>3.6</v>
-      </c>
       <c r="P86">
-        <v>1.77</v>
+        <v>4.8</v>
       </c>
       <c r="Q86">
-        <v>4.68</v>
+        <v>2.05</v>
       </c>
       <c r="R86">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="S86">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T86">
-        <v>3.22</v>
+        <v>3.08</v>
       </c>
       <c r="U86">
-        <v>2.38</v>
+        <v>2.53</v>
       </c>
       <c r="V86">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W86">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X86">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y86">
         <v>1.19</v>
       </c>
       <c r="Z86">
-        <v>3.75</v>
+        <v>4.02</v>
       </c>
       <c r="AA86">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB86">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AC86">
-        <v>2.69</v>
+        <v>2.83</v>
       </c>
       <c r="AD86">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AE86">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF86">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AG86">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AK86">
-        <v>1.21</v>
+        <v>2.26</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="O87">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="P87">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="Q87">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="R87">
-        <v>2.17</v>
+        <v>2.71</v>
       </c>
       <c r="S87">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="T87">
-        <v>3.08</v>
+        <v>3.78</v>
       </c>
       <c r="U87">
-        <v>2.53</v>
+        <v>2.2</v>
       </c>
       <c r="V87">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="W87">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X87">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y87">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z87">
-        <v>4.02</v>
+        <v>5.25</v>
       </c>
       <c r="AA87">
-        <v>1.75</v>
+        <v>1.49</v>
       </c>
       <c r="AB87">
-        <v>2.08</v>
+        <v>2.57</v>
       </c>
       <c r="AC87">
-        <v>2.83</v>
+        <v>2.26</v>
       </c>
       <c r="AD87">
-        <v>1.42</v>
+        <v>1.64</v>
       </c>
       <c r="AE87">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AF87">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AG87">
-        <v>1.97</v>
+        <v>2.18</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK87">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,61 +14653,61 @@
         </is>
       </c>
       <c r="N88">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="O88">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P88">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="Q88">
-        <v>3.25</v>
+        <v>4.68</v>
       </c>
       <c r="R88">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="S88">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="T88">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="U88">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="V88">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W88">
         <v>1.1</v>
       </c>
       <c r="X88">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y88">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="Z88">
-        <v>3.34</v>
+        <v>3.75</v>
       </c>
       <c r="AA88">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AB88">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="AC88">
-        <v>3.14</v>
+        <v>2.69</v>
       </c>
       <c r="AD88">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AE88">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF88">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AG88">
         <v>2.1</v>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK88">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.44</v>
+        <v>3</v>
       </c>
       <c r="O89">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="P89">
-        <v>5.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q89">
-        <v>1.89</v>
+        <v>3.25</v>
       </c>
       <c r="R89">
-        <v>2.71</v>
+        <v>2.24</v>
       </c>
       <c r="S89">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="T89">
-        <v>3.78</v>
+        <v>3</v>
       </c>
       <c r="U89">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="V89">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="W89">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X89">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="Z89">
-        <v>5.25</v>
+        <v>3.34</v>
       </c>
       <c r="AA89">
-        <v>1.49</v>
+        <v>1.85</v>
       </c>
       <c r="AB89">
-        <v>2.57</v>
+        <v>1.86</v>
       </c>
       <c r="AC89">
-        <v>2.26</v>
+        <v>3.14</v>
       </c>
       <c r="AD89">
-        <v>1.64</v>
+        <v>1.27</v>
       </c>
       <c r="AE89">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AF89">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="AG89">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK89">
-        <v>2.5</v>
+        <v>1.32</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -15864,7 +15864,7 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AK95">
         <v>1.5</v>

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -7490,46 +7490,46 @@
         <v>2.61</v>
       </c>
       <c r="Q44">
-        <v>2.72</v>
+        <v>2.59</v>
       </c>
       <c r="R44">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="S44">
         <v>1.22</v>
       </c>
       <c r="T44">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U44">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="V44">
         <v>1.66</v>
       </c>
       <c r="W44">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="X44">
         <v>1.02</v>
       </c>
       <c r="Y44">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z44">
-        <v>5.66</v>
+        <v>5.7</v>
       </c>
       <c r="AA44">
         <v>1.47</v>
       </c>
       <c r="AB44">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="AC44">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="AD44">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AE44">
         <v>1.27</v>
@@ -7538,7 +7538,7 @@
         <v>1.4</v>
       </c>
       <c r="AG44">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK44">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="O53">
         <v>3.6</v>
       </c>
       <c r="P53">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="Q53">
         <v>2.9</v>
@@ -9117,7 +9117,7 @@
         <v>4</v>
       </c>
       <c r="P54">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="Q54">
         <v>3.36</v>
@@ -9606,7 +9606,7 @@
         <v>3.6</v>
       </c>
       <c r="P57">
-        <v>3.2</v>
+        <v>3.36</v>
       </c>
       <c r="Q57">
         <v>2.42</v>
@@ -9624,10 +9624,10 @@
         <v>2.45</v>
       </c>
       <c r="V57">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W57">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X57">
         <v>1.01</v>
@@ -9926,10 +9926,10 @@
         </is>
       </c>
       <c r="N59">
-        <v>5.87</v>
+        <v>5.4</v>
       </c>
       <c r="O59">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="P59">
         <v>1.49</v>
@@ -10276,7 +10276,7 @@
         <v>2.05</v>
       </c>
       <c r="V61">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="W61">
         <v>1.18</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="O66">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P66">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="Q66">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="R66">
         <v>2.05</v>
       </c>
       <c r="S66">
+        <v>1.36</v>
+      </c>
+      <c r="T66">
+        <v>2.83</v>
+      </c>
+      <c r="U66">
+        <v>2.75</v>
+      </c>
+      <c r="V66">
         <v>1.4</v>
       </c>
-      <c r="T66">
-        <v>2.8</v>
-      </c>
-      <c r="U66">
-        <v>2.7</v>
-      </c>
-      <c r="V66">
-        <v>1.39</v>
-      </c>
       <c r="W66">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X66">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z66">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="AA66">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AB66">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AC66">
         <v>3.5</v>
       </c>
       <c r="AD66">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE66">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF66">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG66">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AK66">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="O67">
+        <v>3</v>
+      </c>
+      <c r="P67">
+        <v>2.45</v>
+      </c>
+      <c r="Q67">
+        <v>3.5</v>
+      </c>
+      <c r="R67">
+        <v>1.95</v>
+      </c>
+      <c r="S67">
+        <v>1.49</v>
+      </c>
+      <c r="T67">
+        <v>2.39</v>
+      </c>
+      <c r="U67">
         <v>3.1</v>
       </c>
-      <c r="P67">
-        <v>3.2</v>
-      </c>
-      <c r="Q67">
+      <c r="V67">
+        <v>1.33</v>
+      </c>
+      <c r="W67">
+        <v>1.06</v>
+      </c>
+      <c r="X67">
+        <v>1.05</v>
+      </c>
+      <c r="Y67">
+        <v>1.4</v>
+      </c>
+      <c r="Z67">
         <v>2.75</v>
       </c>
-      <c r="R67">
-        <v>2.05</v>
-      </c>
-      <c r="S67">
-        <v>1.36</v>
-      </c>
-      <c r="T67">
-        <v>2.83</v>
-      </c>
-      <c r="U67">
-        <v>2.75</v>
-      </c>
-      <c r="V67">
-        <v>1.4</v>
-      </c>
-      <c r="W67">
-        <v>1.05</v>
-      </c>
-      <c r="X67">
-        <v>1.01</v>
-      </c>
-      <c r="Y67">
-        <v>1.28</v>
-      </c>
-      <c r="Z67">
-        <v>3.33</v>
-      </c>
       <c r="AA67">
-        <v>2.02</v>
+        <v>2.21</v>
       </c>
       <c r="AB67">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="AC67">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="AD67">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AE67">
         <v>1.03</v>
       </c>
       <c r="AF67">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AG67">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AK67">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,80 +11393,80 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="O68">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P68">
         <v>2.45</v>
       </c>
       <c r="Q68">
+        <v>3.3</v>
+      </c>
+      <c r="R68">
+        <v>2.05</v>
+      </c>
+      <c r="S68">
+        <v>1.4</v>
+      </c>
+      <c r="T68">
+        <v>2.8</v>
+      </c>
+      <c r="U68">
+        <v>2.7</v>
+      </c>
+      <c r="V68">
+        <v>1.39</v>
+      </c>
+      <c r="W68">
+        <v>1.07</v>
+      </c>
+      <c r="X68">
+        <v>1.03</v>
+      </c>
+      <c r="Y68">
+        <v>1.3</v>
+      </c>
+      <c r="Z68">
+        <v>3.3</v>
+      </c>
+      <c r="AA68">
+        <v>2.05</v>
+      </c>
+      <c r="AB68">
+        <v>1.75</v>
+      </c>
+      <c r="AC68">
         <v>3.5</v>
       </c>
-      <c r="R68">
+      <c r="AD68">
+        <v>1.25</v>
+      </c>
+      <c r="AE68">
+        <v>1.06</v>
+      </c>
+      <c r="AF68">
+        <v>1.75</v>
+      </c>
+      <c r="AG68">
         <v>1.95</v>
       </c>
-      <c r="S68">
-        <v>1.49</v>
-      </c>
-      <c r="T68">
-        <v>2.39</v>
-      </c>
-      <c r="U68">
-        <v>3.1</v>
-      </c>
-      <c r="V68">
-        <v>1.33</v>
-      </c>
-      <c r="W68">
-        <v>1.06</v>
-      </c>
-      <c r="X68">
-        <v>1.05</v>
-      </c>
-      <c r="Y68">
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ68">
         <v>1.4</v>
       </c>
-      <c r="Z68">
-        <v>2.75</v>
-      </c>
-      <c r="AA68">
-        <v>2.21</v>
-      </c>
-      <c r="AB68">
-        <v>1.57</v>
-      </c>
-      <c r="AC68">
-        <v>4.6</v>
-      </c>
-      <c r="AD68">
-        <v>1.17</v>
-      </c>
-      <c r="AE68">
-        <v>1.03</v>
-      </c>
-      <c r="AF68">
-        <v>1.93</v>
-      </c>
-      <c r="AG68">
-        <v>1.78</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ68">
-        <v>1.36</v>
-      </c>
       <c r="AK68">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -12543,22 +12543,22 @@
         <v>3.7</v>
       </c>
       <c r="Q75">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="R75">
         <v>2.2</v>
       </c>
       <c r="S75">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T75">
         <v>3.2</v>
       </c>
       <c r="U75">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="V75">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W75">
         <v>1.07</v>
@@ -12576,7 +12576,7 @@
         <v>1.76</v>
       </c>
       <c r="AB75">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AC75">
         <v>3</v>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK75">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="O80">
         <v>3.4</v>
       </c>
       <c r="P80">
-        <v>2.74</v>
+        <v>2.81</v>
       </c>
       <c r="Q80">
         <v>2.88</v>
@@ -13566,7 +13566,7 @@
         <v>1.13</v>
       </c>
       <c r="AF81">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG81">
         <v>2.3</v>
@@ -14074,7 +14074,7 @@
         <v>1.3</v>
       </c>
       <c r="AK84">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.53</v>
+        <v>3.9</v>
       </c>
       <c r="O86">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P86">
-        <v>4.8</v>
+        <v>1.77</v>
       </c>
       <c r="Q86">
-        <v>2.05</v>
+        <v>4.68</v>
       </c>
       <c r="R86">
-        <v>2.17</v>
+        <v>2.26</v>
       </c>
       <c r="S86">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="T86">
-        <v>3.08</v>
+        <v>3.22</v>
       </c>
       <c r="U86">
-        <v>2.53</v>
+        <v>2.38</v>
       </c>
       <c r="V86">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W86">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X86">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y86">
         <v>1.19</v>
       </c>
       <c r="Z86">
-        <v>4.02</v>
+        <v>3.75</v>
       </c>
       <c r="AA86">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB86">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AC86">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="AD86">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE86">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF86">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AG86">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AK86">
-        <v>2.26</v>
+        <v>1.21</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.44</v>
+        <v>3</v>
       </c>
       <c r="O87">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="P87">
-        <v>5.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q87">
-        <v>1.89</v>
+        <v>3.25</v>
       </c>
       <c r="R87">
-        <v>2.71</v>
+        <v>2.24</v>
       </c>
       <c r="S87">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="T87">
-        <v>3.78</v>
+        <v>3</v>
       </c>
       <c r="U87">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="V87">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="W87">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X87">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="Z87">
-        <v>5.25</v>
+        <v>3.34</v>
       </c>
       <c r="AA87">
-        <v>1.49</v>
+        <v>1.85</v>
       </c>
       <c r="AB87">
-        <v>2.57</v>
+        <v>1.86</v>
       </c>
       <c r="AC87">
-        <v>2.26</v>
+        <v>3.14</v>
       </c>
       <c r="AD87">
-        <v>1.64</v>
+        <v>1.27</v>
       </c>
       <c r="AE87">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AF87">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="AG87">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK87">
-        <v>2.5</v>
+        <v>1.32</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
+        <v>1.53</v>
+      </c>
+      <c r="O88">
         <v>3.9</v>
       </c>
-      <c r="O88">
-        <v>3.6</v>
-      </c>
       <c r="P88">
-        <v>1.77</v>
+        <v>4.8</v>
       </c>
       <c r="Q88">
-        <v>4.68</v>
+        <v>2.05</v>
       </c>
       <c r="R88">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="S88">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T88">
-        <v>3.22</v>
+        <v>3.08</v>
       </c>
       <c r="U88">
-        <v>2.38</v>
+        <v>2.53</v>
       </c>
       <c r="V88">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W88">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X88">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y88">
         <v>1.19</v>
       </c>
       <c r="Z88">
-        <v>3.75</v>
+        <v>4.02</v>
       </c>
       <c r="AA88">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB88">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AC88">
-        <v>2.69</v>
+        <v>2.83</v>
       </c>
       <c r="AD88">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AE88">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF88">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AG88">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AK88">
-        <v>1.21</v>
+        <v>2.26</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>3</v>
+        <v>1.44</v>
       </c>
       <c r="O89">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="P89">
-        <v>2.1</v>
+        <v>5.25</v>
       </c>
       <c r="Q89">
-        <v>3.25</v>
+        <v>1.89</v>
       </c>
       <c r="R89">
-        <v>2.24</v>
+        <v>2.71</v>
       </c>
       <c r="S89">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="T89">
-        <v>3</v>
+        <v>3.78</v>
       </c>
       <c r="U89">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="V89">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="W89">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X89">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y89">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="Z89">
-        <v>3.34</v>
+        <v>5.25</v>
       </c>
       <c r="AA89">
-        <v>1.85</v>
+        <v>1.49</v>
       </c>
       <c r="AB89">
-        <v>1.86</v>
+        <v>2.57</v>
       </c>
       <c r="AC89">
-        <v>3.14</v>
+        <v>2.26</v>
       </c>
       <c r="AD89">
-        <v>1.27</v>
+        <v>1.64</v>
       </c>
       <c r="AE89">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="AF89">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="AG89">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK89">
-        <v>1.32</v>
+        <v>2.5</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -17104,7 +17104,7 @@
         <v>4</v>
       </c>
       <c r="P103">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -18085,10 +18085,10 @@
         <v>0</v>
       </c>
       <c r="Q109">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="R109">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="S109">
         <v>1.25</v>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK109">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18239,28 +18239,28 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="O110">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="P110">
         <v>2.75</v>
       </c>
       <c r="Q110">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R110">
         <v>1.83</v>
       </c>
       <c r="S110">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="T110">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="U110">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="V110">
         <v>1.22</v>
@@ -18278,25 +18278,25 @@
         <v>2.37</v>
       </c>
       <c r="AA110">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AB110">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AC110">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AD110">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AE110">
         <v>1.04</v>
       </c>
       <c r="AF110">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AG110">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O3">
-        <v>3.61</v>
+        <v>3.7</v>
       </c>
       <c r="P3">
-        <v>2.81</v>
+        <v>3.15</v>
       </c>
       <c r="Q3">
         <v>2.49</v>
@@ -813,46 +813,46 @@
         <v>2.3</v>
       </c>
       <c r="S3">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T3">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U3">
         <v>2.3</v>
       </c>
       <c r="V3">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W3">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X3">
         <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z3">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA3">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB3">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC3">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AD3">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AE3">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF3">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG3">
         <v>2.3</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK3">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3901,7 +3901,7 @@
         <v>10.7</v>
       </c>
       <c r="P22">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Q22">
         <v>1.41</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -5045,55 +5045,55 @@
         <v>0</v>
       </c>
       <c r="Q29">
-        <v>7.49</v>
+        <v>0</v>
       </c>
       <c r="R29">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S29">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T29">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U29">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="V29">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W29">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X29">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y29">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z29">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AA29">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB29">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC29">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AD29">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE29">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF29">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG29">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK29">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O33">
         <v>7.8</v>
       </c>
       <c r="P33">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Q33">
         <v>11</v>
@@ -5709,13 +5709,13 @@
         <v>4.2</v>
       </c>
       <c r="U33">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="V33">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="W33">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X33">
         <v>1.01</v>
@@ -5730,7 +5730,7 @@
         <v>1.36</v>
       </c>
       <c r="AB33">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AC33">
         <v>1.88</v>
@@ -5860,34 +5860,34 @@
         <v>3.1</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA34">
         <v>2.05</v>
@@ -5896,19 +5896,19 @@
         <v>1.75</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6032,7 +6032,7 @@
         <v>1.33</v>
       </c>
       <c r="T35">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U35">
         <v>2.75</v>
@@ -6044,7 +6044,7 @@
         <v>1.07</v>
       </c>
       <c r="X35">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
         <v>1.27</v>
@@ -6071,7 +6071,7 @@
         <v>1.8</v>
       </c>
       <c r="AG35">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8142,55 +8142,55 @@
         <v>0</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8827,7 +8827,7 @@
         <v>1.37</v>
       </c>
       <c r="AB52">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AC52">
         <v>2.02</v>
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="O53">
         <v>3.6</v>
       </c>
       <c r="P53">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="Q53">
         <v>2.9</v>
@@ -8993,7 +8993,7 @@
         <v>2.7</v>
       </c>
       <c r="AC53">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="AD53">
         <v>1.73</v>
@@ -9627,7 +9627,7 @@
         <v>1.47</v>
       </c>
       <c r="W57">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X57">
         <v>1.01</v>
@@ -9657,7 +9657,7 @@
         <v>1.64</v>
       </c>
       <c r="AG57">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9763,10 +9763,10 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O58">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P58">
         <v>2.8</v>
@@ -9787,13 +9787,13 @@
         <v>2.22</v>
       </c>
       <c r="V58">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W58">
         <v>1.14</v>
       </c>
       <c r="X58">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y58">
         <v>1.13</v>
@@ -10095,7 +10095,7 @@
         <v>3.5</v>
       </c>
       <c r="P60">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="Q60">
         <v>3.05</v>
@@ -10128,7 +10128,7 @@
         <v>3.9</v>
       </c>
       <c r="AA60">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AB60">
         <v>2.05</v>
@@ -10255,10 +10255,10 @@
         <v>1.3</v>
       </c>
       <c r="O61">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="P61">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="Q61">
         <v>1.65</v>
@@ -10617,10 +10617,10 @@
         <v>4.95</v>
       </c>
       <c r="AA63">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AB63">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AC63">
         <v>2.25</v>
@@ -10940,7 +10940,7 @@
         <v>1.2</v>
       </c>
       <c r="Z65">
-        <v>4.36</v>
+        <v>4.37</v>
       </c>
       <c r="AA65">
         <v>1.67</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="O66">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P66">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="Q66">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="R66">
         <v>2.05</v>
       </c>
       <c r="S66">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T66">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="U66">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="V66">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W66">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X66">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y66">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z66">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="AA66">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AB66">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AC66">
         <v>3.5</v>
       </c>
       <c r="AD66">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE66">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF66">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG66">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AK66">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
+        <v>2.15</v>
+      </c>
+      <c r="O67">
+        <v>3.1</v>
+      </c>
+      <c r="P67">
+        <v>3.3</v>
+      </c>
+      <c r="Q67">
         <v>2.75</v>
       </c>
-      <c r="O67">
-        <v>3</v>
-      </c>
-      <c r="P67">
-        <v>2.45</v>
-      </c>
-      <c r="Q67">
+      <c r="R67">
+        <v>2.05</v>
+      </c>
+      <c r="S67">
+        <v>1.36</v>
+      </c>
+      <c r="T67">
+        <v>2.82</v>
+      </c>
+      <c r="U67">
+        <v>2.75</v>
+      </c>
+      <c r="V67">
+        <v>1.4</v>
+      </c>
+      <c r="W67">
+        <v>1.05</v>
+      </c>
+      <c r="X67">
+        <v>1.01</v>
+      </c>
+      <c r="Y67">
+        <v>1.28</v>
+      </c>
+      <c r="Z67">
+        <v>3.32</v>
+      </c>
+      <c r="AA67">
+        <v>2.02</v>
+      </c>
+      <c r="AB67">
+        <v>1.74</v>
+      </c>
+      <c r="AC67">
         <v>3.5</v>
       </c>
-      <c r="R67">
-        <v>1.95</v>
-      </c>
-      <c r="S67">
-        <v>1.49</v>
-      </c>
-      <c r="T67">
-        <v>2.39</v>
-      </c>
-      <c r="U67">
-        <v>3.1</v>
-      </c>
-      <c r="V67">
-        <v>1.33</v>
-      </c>
-      <c r="W67">
-        <v>1.06</v>
-      </c>
-      <c r="X67">
-        <v>1.05</v>
-      </c>
-      <c r="Y67">
-        <v>1.4</v>
-      </c>
-      <c r="Z67">
-        <v>2.75</v>
-      </c>
-      <c r="AA67">
-        <v>2.21</v>
-      </c>
-      <c r="AB67">
-        <v>1.57</v>
-      </c>
-      <c r="AC67">
-        <v>4.6</v>
-      </c>
       <c r="AD67">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE67">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF67">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AG67">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AK67">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="O68">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P68">
         <v>2.45</v>
       </c>
       <c r="Q68">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R68">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="S68">
+        <v>1.49</v>
+      </c>
+      <c r="T68">
+        <v>2.39</v>
+      </c>
+      <c r="U68">
+        <v>3.1</v>
+      </c>
+      <c r="V68">
+        <v>1.33</v>
+      </c>
+      <c r="W68">
+        <v>1.06</v>
+      </c>
+      <c r="X68">
+        <v>1.05</v>
+      </c>
+      <c r="Y68">
         <v>1.4</v>
       </c>
-      <c r="T68">
-        <v>2.8</v>
-      </c>
-      <c r="U68">
-        <v>2.7</v>
-      </c>
-      <c r="V68">
-        <v>1.39</v>
-      </c>
-      <c r="W68">
-        <v>1.07</v>
-      </c>
-      <c r="X68">
+      <c r="Z68">
+        <v>2.75</v>
+      </c>
+      <c r="AA68">
+        <v>2.21</v>
+      </c>
+      <c r="AB68">
+        <v>1.57</v>
+      </c>
+      <c r="AC68">
+        <v>4.6</v>
+      </c>
+      <c r="AD68">
+        <v>1.17</v>
+      </c>
+      <c r="AE68">
         <v>1.03</v>
       </c>
-      <c r="Y68">
-        <v>1.3</v>
-      </c>
-      <c r="Z68">
-        <v>3.3</v>
-      </c>
-      <c r="AA68">
-        <v>2.05</v>
-      </c>
-      <c r="AB68">
-        <v>1.75</v>
-      </c>
-      <c r="AC68">
-        <v>3.5</v>
-      </c>
-      <c r="AD68">
-        <v>1.25</v>
-      </c>
-      <c r="AE68">
-        <v>1.06</v>
-      </c>
       <c r="AF68">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AG68">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
+        <v>1.36</v>
+      </c>
+      <c r="AK68">
         <v>1.4</v>
-      </c>
-      <c r="AK68">
-        <v>1.5</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11562,7 +11562,7 @@
         <v>4.33</v>
       </c>
       <c r="P69">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11595,10 +11595,10 @@
         <v>0</v>
       </c>
       <c r="AA69">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC69">
         <v>0</v>
@@ -11891,10 +11891,10 @@
         <v>1.95</v>
       </c>
       <c r="Q71">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="R71">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S71">
         <v>1.25</v>
@@ -11903,7 +11903,7 @@
         <v>3.7</v>
       </c>
       <c r="U71">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="V71">
         <v>1.61</v>
@@ -11924,7 +11924,7 @@
         <v>1.53</v>
       </c>
       <c r="AB71">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="AC71">
         <v>2.27</v>
@@ -11955,7 +11955,7 @@
         <v>1.18</v>
       </c>
       <c r="AK71">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12045,22 +12045,22 @@
         </is>
       </c>
       <c r="N72">
-        <v>4.6</v>
+        <v>5.66</v>
       </c>
       <c r="O72">
         <v>4.7</v>
       </c>
       <c r="P72">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Q72">
-        <v>5</v>
+        <v>4.18</v>
       </c>
       <c r="R72">
-        <v>2.62</v>
+        <v>2.43</v>
       </c>
       <c r="S72">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T72">
         <v>4</v>
@@ -12072,7 +12072,7 @@
         <v>1.72</v>
       </c>
       <c r="W72">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X72">
         <v>1.01</v>
@@ -12084,10 +12084,10 @@
         <v>6.06</v>
       </c>
       <c r="AA72">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB72">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="AC72">
         <v>1.95</v>
@@ -12217,10 +12217,10 @@
         <v>2.7</v>
       </c>
       <c r="Q73">
-        <v>2.33</v>
+        <v>2.52</v>
       </c>
       <c r="R73">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="S73">
         <v>1.17</v>
@@ -12232,7 +12232,7 @@
         <v>1.9</v>
       </c>
       <c r="V73">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="W73">
         <v>1.22</v>
@@ -12256,7 +12256,7 @@
         <v>1.82</v>
       </c>
       <c r="AD73">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="AE73">
         <v>1.39</v>
@@ -12377,19 +12377,19 @@
         <v>4.25</v>
       </c>
       <c r="P74">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="Q74">
         <v>2.03</v>
       </c>
       <c r="R74">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="S74">
         <v>1.14</v>
       </c>
       <c r="T74">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="U74">
         <v>2.05</v>
@@ -12410,10 +12410,10 @@
         <v>7</v>
       </c>
       <c r="AA74">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB74">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="AC74">
         <v>1.87</v>
@@ -12441,7 +12441,7 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK74">
         <v>2.05</v>
@@ -12604,7 +12604,7 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK75">
         <v>1.85</v>
@@ -12917,7 +12917,7 @@
         <v>1.73</v>
       </c>
       <c r="AG77">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>2.2</v>
       </c>
       <c r="O79">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P79">
         <v>2.7</v>
@@ -13518,7 +13518,7 @@
         <v>3.4</v>
       </c>
       <c r="P81">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="Q81">
         <v>2.8</v>
@@ -14182,7 +14182,7 @@
         <v>1.3</v>
       </c>
       <c r="T85">
-        <v>3.34</v>
+        <v>3.05</v>
       </c>
       <c r="U85">
         <v>2.55</v>
@@ -14209,7 +14209,7 @@
         <v>2.12</v>
       </c>
       <c r="AC85">
-        <v>2.84</v>
+        <v>2.76</v>
       </c>
       <c r="AD85">
         <v>1.38</v>
@@ -14221,7 +14221,7 @@
         <v>1.6</v>
       </c>
       <c r="AG85">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -15006,7 +15006,7 @@
         <v>1.75</v>
       </c>
       <c r="W90">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X90">
         <v>1.01</v>
@@ -15154,22 +15154,22 @@
         <v>2.88</v>
       </c>
       <c r="R91">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="S91">
         <v>1.25</v>
       </c>
       <c r="T91">
-        <v>3.75</v>
+        <v>3.52</v>
       </c>
       <c r="U91">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="V91">
         <v>1.6</v>
       </c>
       <c r="W91">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X91">
         <v>1.01</v>
@@ -15215,7 +15215,7 @@
         <v>1.44</v>
       </c>
       <c r="AK91">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15338,7 +15338,7 @@
         <v>1.02</v>
       </c>
       <c r="Y92">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="Z92">
         <v>4.8</v>
@@ -15353,7 +15353,7 @@
         <v>2.42</v>
       </c>
       <c r="AD92">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="AE92">
         <v>1.16</v>
@@ -15362,7 +15362,7 @@
         <v>1.53</v>
       </c>
       <c r="AG92">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
         <v>2.25</v>
       </c>
       <c r="S93">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T93">
         <v>3.25</v>
@@ -15640,19 +15640,19 @@
         <v>1.87</v>
       </c>
       <c r="Q94">
-        <v>3.98</v>
+        <v>3.6</v>
       </c>
       <c r="R94">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="S94">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T94">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="U94">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="V94">
         <v>1.5</v>
@@ -15661,31 +15661,31 @@
         <v>1.12</v>
       </c>
       <c r="X94">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y94">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z94">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="AA94">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AB94">
         <v>2.2</v>
       </c>
       <c r="AC94">
-        <v>2.43</v>
+        <v>2.51</v>
       </c>
       <c r="AD94">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AE94">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF94">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG94">
         <v>2.38</v>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK94">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15818,7 +15818,7 @@
         <v>2.25</v>
       </c>
       <c r="V95">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W95">
         <v>1.13</v>
@@ -16135,10 +16135,10 @@
         <v>2.11</v>
       </c>
       <c r="S97">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T97">
-        <v>2.92</v>
+        <v>3.09</v>
       </c>
       <c r="U97">
         <v>2.75</v>
@@ -16159,25 +16159,25 @@
         <v>3.34</v>
       </c>
       <c r="AA97">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AB97">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AC97">
-        <v>3.27</v>
+        <v>3.32</v>
       </c>
       <c r="AD97">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE97">
         <v>1.08</v>
       </c>
       <c r="AF97">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG97">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16316,10 +16316,10 @@
         <v>1.01</v>
       </c>
       <c r="Y98">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="Z98">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="AA98">
         <v>1.65</v>
@@ -16353,7 +16353,7 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK98">
         <v>1.33</v>
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="O99">
-        <v>3.32</v>
+        <v>3.1</v>
       </c>
       <c r="P99">
-        <v>4.28</v>
+        <v>4.2</v>
       </c>
       <c r="Q99">
         <v>2.48</v>
@@ -16781,55 +16781,55 @@
         <v>0</v>
       </c>
       <c r="Q101">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="R101">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S101">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T101">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U101">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V101">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W101">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X101">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y101">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z101">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="AA101">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB101">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC101">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD101">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE101">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF101">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AG101">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK101">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -17267,7 +17267,7 @@
         <v>3.2</v>
       </c>
       <c r="P104">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="Q104">
         <v>3.09</v>
@@ -17276,10 +17276,10 @@
         <v>2.14</v>
       </c>
       <c r="S104">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T104">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="U104">
         <v>2.9</v>
@@ -17288,7 +17288,7 @@
         <v>1.36</v>
       </c>
       <c r="W104">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X104">
         <v>1.01</v>
@@ -17300,7 +17300,7 @@
         <v>3.13</v>
       </c>
       <c r="AA104">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AB104">
         <v>1.7</v>
@@ -17318,7 +17318,7 @@
         <v>1.8</v>
       </c>
       <c r="AG104">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>1.33</v>
       </c>
       <c r="AK104">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="O105">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q105">
         <v>0</v>

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU113"/>
+  <dimension ref="A1:AU110"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1308,7 +1308,7 @@
         <v>3.3</v>
       </c>
       <c r="U6">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="V6">
         <v>1.46</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK6">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -3934,10 +3934,10 @@
         <v>7.2</v>
       </c>
       <c r="AA22">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AB22">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AC22">
         <v>1.81</v>
@@ -4058,10 +4058,10 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="O23">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P23">
         <v>3.35</v>
@@ -5045,55 +5045,55 @@
         <v>0</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>7.49</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="O34">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="P34">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q34">
         <v>2.77</v>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O41">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P41">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q41">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="R41">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="S41">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T41">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="U41">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="V41">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W41">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X41">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y41">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z41">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AA41">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AB41">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC41">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="AD41">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE41">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF41">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG41">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK41">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7113,22 +7113,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G43">
@@ -7439,22 +7439,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O44">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P44">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="Q44">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="R44">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="S44">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T44">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U44">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V44">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="W44">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X44">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y44">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z44">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA44">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AB44">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AC44">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AD44">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE44">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AF44">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG44">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK44">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>6.1</v>
+        <v>2.33</v>
       </c>
       <c r="O45">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="P45">
-        <v>1.38</v>
+        <v>2.61</v>
       </c>
       <c r="Q45">
-        <v>7.5</v>
+        <v>2.58</v>
       </c>
       <c r="R45">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="S45">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T45">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U45">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="V45">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="W45">
+        <v>1.12</v>
+      </c>
+      <c r="X45">
+        <v>1.02</v>
+      </c>
+      <c r="Y45">
         <v>1.13</v>
       </c>
-      <c r="X45">
-        <v>1.03</v>
-      </c>
-      <c r="Y45">
-        <v>1.19</v>
-      </c>
       <c r="Z45">
-        <v>4.33</v>
+        <v>5.7</v>
       </c>
       <c r="AA45">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AB45">
-        <v>2.24</v>
+        <v>2.66</v>
       </c>
       <c r="AC45">
-        <v>2.59</v>
+        <v>2.1</v>
       </c>
       <c r="AD45">
-        <v>1.47</v>
+        <v>1.63</v>
       </c>
       <c r="AE45">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AF45">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="AG45">
-        <v>1.85</v>
+        <v>2.7</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AK45">
-        <v>1.08</v>
+        <v>1.67</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,80 +7807,80 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.92</v>
+        <v>5.6</v>
       </c>
       <c r="O46">
-        <v>3.48</v>
+        <v>4.15</v>
       </c>
       <c r="P46">
-        <v>3</v>
+        <v>1.42</v>
       </c>
       <c r="Q46">
-        <v>2.51</v>
+        <v>7.5</v>
       </c>
       <c r="R46">
-        <v>2.21</v>
+        <v>2.55</v>
       </c>
       <c r="S46">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="T46">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="U46">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="V46">
+        <v>1.52</v>
+      </c>
+      <c r="W46">
+        <v>1.13</v>
+      </c>
+      <c r="X46">
+        <v>1.03</v>
+      </c>
+      <c r="Y46">
+        <v>1.19</v>
+      </c>
+      <c r="Z46">
+        <v>4.33</v>
+      </c>
+      <c r="AA46">
+        <v>1.52</v>
+      </c>
+      <c r="AB46">
+        <v>2.24</v>
+      </c>
+      <c r="AC46">
+        <v>2.59</v>
+      </c>
+      <c r="AD46">
         <v>1.47</v>
       </c>
-      <c r="W46">
+      <c r="AE46">
+        <v>1.17</v>
+      </c>
+      <c r="AF46">
+        <v>1.85</v>
+      </c>
+      <c r="AG46">
+        <v>1.85</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ46">
+        <v>1.13</v>
+      </c>
+      <c r="AK46">
         <v>1.08</v>
-      </c>
-      <c r="X46">
-        <v>1.02</v>
-      </c>
-      <c r="Y46">
-        <v>1.15</v>
-      </c>
-      <c r="Z46">
-        <v>4.3</v>
-      </c>
-      <c r="AA46">
-        <v>1.61</v>
-      </c>
-      <c r="AB46">
-        <v>2.13</v>
-      </c>
-      <c r="AC46">
-        <v>2.52</v>
-      </c>
-      <c r="AD46">
-        <v>1.41</v>
-      </c>
-      <c r="AE46">
-        <v>1.13</v>
-      </c>
-      <c r="AF46">
-        <v>1.53</v>
-      </c>
-      <c r="AG46">
-        <v>2.29</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ46">
-        <v>1.2</v>
-      </c>
-      <c r="AK46">
-        <v>1.67</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,19 +7970,19 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="O47">
-        <v>3.8</v>
+        <v>3.48</v>
       </c>
       <c r="P47">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="Q47">
-        <v>2.19</v>
+        <v>2.51</v>
       </c>
       <c r="R47">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="S47">
         <v>1.27</v>
@@ -7991,43 +7991,43 @@
         <v>3.18</v>
       </c>
       <c r="U47">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V47">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W47">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X47">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z47">
-        <v>3.92</v>
+        <v>4.3</v>
       </c>
       <c r="AA47">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AB47">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="AC47">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="AD47">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AE47">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF47">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AG47">
-        <v>2.05</v>
+        <v>2.29</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK47">
-        <v>2.02</v>
+        <v>1.67</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q48">
-        <v>1.86</v>
+        <v>2.19</v>
       </c>
       <c r="R48">
-        <v>2.52</v>
+        <v>2.23</v>
       </c>
       <c r="S48">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="T48">
-        <v>3.68</v>
+        <v>3.18</v>
       </c>
       <c r="U48">
-        <v>2.12</v>
+        <v>2.34</v>
       </c>
       <c r="V48">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="W48">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X48">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y48">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="Z48">
-        <v>5.2</v>
+        <v>3.92</v>
       </c>
       <c r="AA48">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="AB48">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="AC48">
-        <v>2.13</v>
+        <v>2.62</v>
       </c>
       <c r="AD48">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="AE48">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AF48">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AG48">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AK48">
-        <v>2.56</v>
+        <v>2.02</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O49">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P49">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q49">
-        <v>3.14</v>
+        <v>1.86</v>
       </c>
       <c r="R49">
-        <v>2.19</v>
+        <v>2.52</v>
       </c>
       <c r="S49">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T49">
-        <v>3.3</v>
+        <v>3.68</v>
       </c>
       <c r="U49">
-        <v>2.27</v>
+        <v>2.12</v>
       </c>
       <c r="V49">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="W49">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X49">
         <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z49">
-        <v>4.25</v>
+        <v>5.2</v>
       </c>
       <c r="AA49">
-        <v>1.66</v>
+        <v>1.47</v>
       </c>
       <c r="AB49">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="AC49">
-        <v>2.52</v>
+        <v>2.13</v>
       </c>
       <c r="AD49">
-        <v>1.41</v>
+        <v>1.61</v>
       </c>
       <c r="AE49">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AF49">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="AG49">
-        <v>2.34</v>
+        <v>2.19</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AK49">
-        <v>1.38</v>
+        <v>2.56</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8412,12 +8412,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.87</v>
+        <v>2.53</v>
       </c>
       <c r="O50">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P50">
-        <v>2.05</v>
+        <v>2.31</v>
       </c>
       <c r="Q50">
-        <v>3.62</v>
+        <v>3.14</v>
       </c>
       <c r="R50">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
       <c r="S50">
         <v>1.25</v>
       </c>
       <c r="T50">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U50">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="V50">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W50">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z50">
-        <v>4.35</v>
+        <v>4.25</v>
       </c>
       <c r="AA50">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AB50">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AC50">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="AD50">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AE50">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF50">
         <v>1.51</v>
       </c>
       <c r="AG50">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AK50">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8563,7 +8563,7 @@
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>2026-10-16 13:30:00</t>
+          <t>2026-10-16 13:00:00</t>
         </is>
       </c>
     </row>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.18</v>
+        <v>2.87</v>
       </c>
       <c r="O51">
+        <v>3.6</v>
+      </c>
+      <c r="P51">
+        <v>2.05</v>
+      </c>
+      <c r="Q51">
         <v>3.62</v>
       </c>
-      <c r="P51">
-        <v>2.9</v>
-      </c>
-      <c r="Q51">
-        <v>0</v>
-      </c>
       <c r="R51">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AA51">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB51">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.48</v>
+        <v>2.18</v>
       </c>
       <c r="O52">
-        <v>4.4</v>
+        <v>3.62</v>
       </c>
       <c r="P52">
-        <v>4.6</v>
+        <v>2.9</v>
       </c>
       <c r="Q52">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="R52">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="S52">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T52">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U52">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V52">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="W52">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X52">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y52">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z52">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="AA52">
-        <v>1.37</v>
+        <v>1.65</v>
       </c>
       <c r="AB52">
-        <v>2.66</v>
+        <v>2.2</v>
       </c>
       <c r="AC52">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD52">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE52">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AF52">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG52">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK52">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.43</v>
+        <v>1.48</v>
       </c>
       <c r="O53">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="P53">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="Q53">
-        <v>2.9</v>
+        <v>1.93</v>
       </c>
       <c r="R53">
-        <v>2.45</v>
+        <v>2.57</v>
       </c>
       <c r="S53">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T53">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="U53">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="V53">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="W53">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X53">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z53">
-        <v>5.65</v>
+        <v>5.45</v>
       </c>
       <c r="AA53">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AB53">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="AC53">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AD53">
         <v>1.73</v>
       </c>
       <c r="AE53">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AF53">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG53">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.58</v>
+        <v>1.14</v>
       </c>
       <c r="AK53">
-        <v>1.41</v>
+        <v>2.4</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
+        <v>2.47</v>
+      </c>
+      <c r="O54">
+        <v>3.6</v>
+      </c>
+      <c r="P54">
+        <v>2.2</v>
+      </c>
+      <c r="Q54">
         <v>2.9</v>
       </c>
-      <c r="O54">
-        <v>4</v>
-      </c>
-      <c r="P54">
-        <v>2.01</v>
-      </c>
-      <c r="Q54">
-        <v>3.36</v>
-      </c>
       <c r="R54">
-        <v>2.71</v>
+        <v>2.45</v>
       </c>
       <c r="S54">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T54">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="U54">
-        <v>1.91</v>
+        <v>2.09</v>
       </c>
       <c r="V54">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="W54">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X54">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y54">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z54">
-        <v>6.4</v>
+        <v>5.65</v>
       </c>
       <c r="AA54">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AB54">
-        <v>2.97</v>
+        <v>2.7</v>
       </c>
       <c r="AC54">
-        <v>1.94</v>
+        <v>2.07</v>
       </c>
       <c r="AD54">
-        <v>1.97</v>
+        <v>1.73</v>
       </c>
       <c r="AE54">
         <v>1.33</v>
       </c>
       <c r="AF54">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AG54">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="AK54">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9232,7 +9232,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9390,12 +9390,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O56">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P56">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q56">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R56">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S56">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T56">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U56">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V56">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="W56">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X56">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y56">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z56">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA56">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AB56">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AC56">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD56">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE56">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF56">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG56">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK56">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9541,7 +9541,7 @@
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>2026-10-16 13:45:00</t>
+          <t>2026-10-16 13:30:00</t>
         </is>
       </c>
     </row>
@@ -9553,12 +9553,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
+        <v>2.81</v>
+      </c>
+      <c r="O57">
+        <v>3.51</v>
+      </c>
+      <c r="P57">
+        <v>1.87</v>
+      </c>
+      <c r="Q57">
+        <v>3.6</v>
+      </c>
+      <c r="R57">
+        <v>2.4</v>
+      </c>
+      <c r="S57">
+        <v>1.22</v>
+      </c>
+      <c r="T57">
+        <v>4</v>
+      </c>
+      <c r="U57">
         <v>2.1</v>
       </c>
-      <c r="O57">
-        <v>3.6</v>
-      </c>
-      <c r="P57">
-        <v>3.36</v>
-      </c>
-      <c r="Q57">
-        <v>2.42</v>
-      </c>
-      <c r="R57">
-        <v>2.33</v>
-      </c>
-      <c r="S57">
-        <v>1.3</v>
-      </c>
-      <c r="T57">
-        <v>3.08</v>
-      </c>
-      <c r="U57">
-        <v>2.45</v>
-      </c>
       <c r="V57">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="W57">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X57">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="Z57">
-        <v>3.58</v>
+        <v>5.5</v>
       </c>
       <c r="AA57">
-        <v>1.8</v>
+        <v>1.45</v>
       </c>
       <c r="AB57">
-        <v>2.04</v>
+        <v>2.6</v>
       </c>
       <c r="AC57">
-        <v>2.97</v>
+        <v>2.1</v>
       </c>
       <c r="AD57">
-        <v>1.39</v>
+        <v>1.63</v>
       </c>
       <c r="AE57">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AF57">
-        <v>1.64</v>
+        <v>1.4</v>
       </c>
       <c r="AG57">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,11 +9670,11 @@
         </is>
       </c>
       <c r="AJ57">
+        <v>1.2</v>
+      </c>
+      <c r="AK57">
         <v>1.25</v>
       </c>
-      <c r="AK57">
-        <v>1.69</v>
-      </c>
       <c r="AL57">
         <v>0</v>
       </c>
@@ -9704,7 +9704,7 @@
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>2026-10-16 14:00:00</t>
+          <t>2026-10-16 13:45:00</t>
         </is>
       </c>
     </row>
@@ -9721,7 +9721,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G58">
@@ -9766,61 +9766,61 @@
         <v>2.1</v>
       </c>
       <c r="O58">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P58">
-        <v>2.8</v>
+        <v>3.36</v>
       </c>
       <c r="Q58">
-        <v>2.67</v>
+        <v>2.42</v>
       </c>
       <c r="R58">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="S58">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T58">
-        <v>3.75</v>
+        <v>3.08</v>
       </c>
       <c r="U58">
-        <v>2.22</v>
+        <v>2.45</v>
       </c>
       <c r="V58">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="W58">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X58">
         <v>1.01</v>
       </c>
       <c r="Y58">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="Z58">
-        <v>4.6</v>
+        <v>3.58</v>
       </c>
       <c r="AA58">
-        <v>1.49</v>
+        <v>1.72</v>
       </c>
       <c r="AB58">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="AC58">
-        <v>2.29</v>
+        <v>2.8</v>
       </c>
       <c r="AD58">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AE58">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF58">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="AG58">
-        <v>2.53</v>
+        <v>2.15</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK58">
-        <v>1.54</v>
+        <v>1.69</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9884,22 +9884,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>5.4</v>
+        <v>2.1</v>
       </c>
       <c r="O59">
-        <v>4.45</v>
+        <v>3.5</v>
       </c>
       <c r="P59">
+        <v>2.8</v>
+      </c>
+      <c r="Q59">
+        <v>2.67</v>
+      </c>
+      <c r="R59">
+        <v>2.31</v>
+      </c>
+      <c r="S59">
+        <v>1.22</v>
+      </c>
+      <c r="T59">
+        <v>3.75</v>
+      </c>
+      <c r="U59">
+        <v>2.22</v>
+      </c>
+      <c r="V59">
+        <v>1.57</v>
+      </c>
+      <c r="W59">
+        <v>1.14</v>
+      </c>
+      <c r="X59">
+        <v>1.01</v>
+      </c>
+      <c r="Y59">
+        <v>1.13</v>
+      </c>
+      <c r="Z59">
+        <v>4.6</v>
+      </c>
+      <c r="AA59">
         <v>1.49</v>
       </c>
-      <c r="Q59">
-        <v>4.53</v>
-      </c>
-      <c r="R59">
-        <v>2.38</v>
-      </c>
-      <c r="S59">
-        <v>1.2</v>
-      </c>
-      <c r="T59">
-        <v>4</v>
-      </c>
-      <c r="U59">
-        <v>2.2</v>
-      </c>
-      <c r="V59">
-        <v>1.6</v>
-      </c>
-      <c r="W59">
-        <v>1.13</v>
-      </c>
-      <c r="X59">
-        <v>1.02</v>
-      </c>
-      <c r="Y59">
-        <v>1.16</v>
-      </c>
-      <c r="Z59">
-        <v>5.01</v>
-      </c>
-      <c r="AA59">
-        <v>1.54</v>
-      </c>
       <c r="AB59">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AC59">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="AD59">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AE59">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AF59">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AG59">
-        <v>2.15</v>
+        <v>2.53</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>1.2</v>
       </c>
       <c r="AK59">
-        <v>1.11</v>
+        <v>1.54</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10047,22 +10047,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Horsens</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.77</v>
+        <v>5.4</v>
       </c>
       <c r="O60">
-        <v>3.5</v>
+        <v>4.45</v>
       </c>
       <c r="P60">
-        <v>2.37</v>
+        <v>1.49</v>
       </c>
       <c r="Q60">
-        <v>3.05</v>
+        <v>4.53</v>
       </c>
       <c r="R60">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="S60">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T60">
-        <v>3.19</v>
+        <v>4</v>
       </c>
       <c r="U60">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="V60">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="W60">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X60">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y60">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z60">
-        <v>3.9</v>
+        <v>5.01</v>
       </c>
       <c r="AA60">
-        <v>1.81</v>
+        <v>1.54</v>
       </c>
       <c r="AB60">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AC60">
-        <v>2.9</v>
+        <v>2.34</v>
       </c>
       <c r="AD60">
-        <v>1.38</v>
+        <v>1.59</v>
       </c>
       <c r="AE60">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AF60">
         <v>1.6</v>
       </c>
       <c r="AG60">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK60">
-        <v>1.4</v>
+        <v>1.11</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10205,12 +10205,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Horsens</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
+        <v>2.77</v>
+      </c>
+      <c r="O61">
+        <v>3.5</v>
+      </c>
+      <c r="P61">
+        <v>2.37</v>
+      </c>
+      <c r="Q61">
+        <v>3.05</v>
+      </c>
+      <c r="R61">
+        <v>2.12</v>
+      </c>
+      <c r="S61">
         <v>1.3</v>
       </c>
-      <c r="O61">
-        <v>5.25</v>
-      </c>
-      <c r="P61">
-        <v>7</v>
-      </c>
-      <c r="Q61">
-        <v>1.65</v>
-      </c>
-      <c r="R61">
-        <v>2.75</v>
-      </c>
-      <c r="S61">
-        <v>1.2</v>
-      </c>
       <c r="T61">
-        <v>4</v>
+        <v>3.21</v>
       </c>
       <c r="U61">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="V61">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="W61">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X61">
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="Z61">
-        <v>6.54</v>
+        <v>3.95</v>
       </c>
       <c r="AA61">
-        <v>1.36</v>
+        <v>1.81</v>
       </c>
       <c r="AB61">
-        <v>2.74</v>
+        <v>1.95</v>
       </c>
       <c r="AC61">
-        <v>2.01</v>
+        <v>2.9</v>
       </c>
       <c r="AD61">
-        <v>1.75</v>
+        <v>1.39</v>
       </c>
       <c r="AE61">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="AF61">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG61">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="AK61">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10356,7 +10356,7 @@
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>2026-10-16 14:30:00</t>
+          <t>2026-10-16 14:00:00</t>
         </is>
       </c>
     </row>
@@ -10368,12 +10368,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.75</v>
+        <v>1.3</v>
       </c>
       <c r="O62">
-        <v>4.05</v>
+        <v>5.25</v>
       </c>
       <c r="P62">
-        <v>3.8</v>
+        <v>7</v>
       </c>
       <c r="Q62">
-        <v>2.18</v>
+        <v>1.65</v>
       </c>
       <c r="R62">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="S62">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T62">
         <v>4</v>
       </c>
       <c r="U62">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="V62">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="W62">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z62">
-        <v>6</v>
+        <v>6.54</v>
       </c>
       <c r="AA62">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB62">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="AC62">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AD62">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AE62">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AF62">
-        <v>1.39</v>
+        <v>1.62</v>
       </c>
       <c r="AG62">
-        <v>2.67</v>
+        <v>2.03</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="AK62">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>2026-10-16 15:00:00</t>
+          <t>2026-10-16 14:30:00</t>
         </is>
       </c>
     </row>
@@ -10536,7 +10536,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.47</v>
+        <v>1.75</v>
       </c>
       <c r="O63">
-        <v>3.6</v>
+        <v>4.05</v>
       </c>
       <c r="P63">
-        <v>2.72</v>
+        <v>3.8</v>
       </c>
       <c r="Q63">
-        <v>2.87</v>
+        <v>2.18</v>
       </c>
       <c r="R63">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="S63">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T63">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U63">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="V63">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="W63">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X63">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y63">
         <v>1.11</v>
       </c>
       <c r="Z63">
-        <v>4.95</v>
+        <v>6</v>
       </c>
       <c r="AA63">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AB63">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="AC63">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AD63">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="AE63">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AF63">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AG63">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK63">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,65 +10741,65 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.95</v>
+        <v>2.47</v>
       </c>
       <c r="O64">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P64">
-        <v>3.2</v>
+        <v>2.72</v>
       </c>
       <c r="Q64">
-        <v>2.61</v>
+        <v>2.87</v>
       </c>
       <c r="R64">
-        <v>2.18</v>
+        <v>2.49</v>
       </c>
       <c r="S64">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T64">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="U64">
+        <v>2.2</v>
+      </c>
+      <c r="V64">
+        <v>1.62</v>
+      </c>
+      <c r="W64">
+        <v>1.14</v>
+      </c>
+      <c r="X64">
+        <v>1.02</v>
+      </c>
+      <c r="Y64">
+        <v>1.11</v>
+      </c>
+      <c r="Z64">
+        <v>4.95</v>
+      </c>
+      <c r="AA64">
+        <v>1.53</v>
+      </c>
+      <c r="AB64">
+        <v>2.4</v>
+      </c>
+      <c r="AC64">
+        <v>2.25</v>
+      </c>
+      <c r="AD64">
+        <v>1.62</v>
+      </c>
+      <c r="AE64">
+        <v>1.25</v>
+      </c>
+      <c r="AF64">
+        <v>1.44</v>
+      </c>
+      <c r="AG64">
         <v>2.5</v>
       </c>
-      <c r="V64">
-        <v>1.44</v>
-      </c>
-      <c r="W64">
-        <v>1.1</v>
-      </c>
-      <c r="X64">
-        <v>1.01</v>
-      </c>
-      <c r="Y64">
-        <v>1.22</v>
-      </c>
-      <c r="Z64">
-        <v>3.79</v>
-      </c>
-      <c r="AA64">
-        <v>1.85</v>
-      </c>
-      <c r="AB64">
-        <v>1.95</v>
-      </c>
-      <c r="AC64">
-        <v>2.88</v>
-      </c>
-      <c r="AD64">
-        <v>1.37</v>
-      </c>
-      <c r="AE64">
-        <v>1.13</v>
-      </c>
-      <c r="AF64">
-        <v>1.67</v>
-      </c>
-      <c r="AG64">
-        <v>2.1</v>
-      </c>
       <c r="AH64" t="inlineStr">
         <is>
           <t>[]</t>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK64">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,61 +10904,61 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="O65">
-        <v>3.88</v>
+        <v>3.3</v>
       </c>
       <c r="P65">
-        <v>4.33</v>
+        <v>3.2</v>
       </c>
       <c r="Q65">
-        <v>2.2</v>
+        <v>2.61</v>
       </c>
       <c r="R65">
-        <v>2.42</v>
+        <v>2.18</v>
       </c>
       <c r="S65">
         <v>1.3</v>
       </c>
       <c r="T65">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U65">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="V65">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W65">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X65">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z65">
-        <v>4.37</v>
+        <v>3.79</v>
       </c>
       <c r="AA65">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AB65">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AC65">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AD65">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE65">
         <v>1.13</v>
       </c>
       <c r="AF65">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG65">
         <v>2.1</v>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK65">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,16 +11067,16 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="O66">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P66">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="Q66">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R66">
         <v>2.05</v>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
+        <v>1.5</v>
+      </c>
+      <c r="AK66">
         <v>1.4</v>
-      </c>
-      <c r="AK66">
-        <v>1.5</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11236,7 +11236,7 @@
         <v>3.1</v>
       </c>
       <c r="P67">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Q67">
         <v>2.75</v>
@@ -11402,7 +11402,7 @@
         <v>2.45</v>
       </c>
       <c r="Q68">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="R68">
         <v>1.95</v>
@@ -11411,7 +11411,7 @@
         <v>1.49</v>
       </c>
       <c r="T68">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="U68">
         <v>3.1</v>
@@ -11432,13 +11432,13 @@
         <v>2.75</v>
       </c>
       <c r="AA68">
-        <v>2.21</v>
+        <v>2.31</v>
       </c>
       <c r="AB68">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC68">
-        <v>4.6</v>
+        <v>4.15</v>
       </c>
       <c r="AD68">
         <v>1.17</v>
@@ -11447,10 +11447,10 @@
         <v>1.03</v>
       </c>
       <c r="AF68">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AG68">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="O69">
-        <v>4.33</v>
+        <v>3.88</v>
       </c>
       <c r="P69">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S69">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T69">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U69">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="V69">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W69">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X69">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y69">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z69">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="AA69">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AB69">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD69">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE69">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF69">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG69">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK69">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11677,7 +11677,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="O70">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="P70">
-        <v>4.33</v>
+        <v>6</v>
       </c>
       <c r="Q70">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="R70">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S70">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T70">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="U70">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="V70">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="W70">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X70">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y70">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z70">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AA70">
-        <v>1.39</v>
+        <v>1.61</v>
       </c>
       <c r="AB70">
-        <v>2.59</v>
+        <v>2.25</v>
       </c>
       <c r="AC70">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD70">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE70">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AF70">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG70">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK70">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11840,7 +11840,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>3.1</v>
+        <v>1.65</v>
       </c>
       <c r="O71">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="P71">
-        <v>1.95</v>
+        <v>4.5</v>
       </c>
       <c r="Q71">
-        <v>3.8</v>
+        <v>2.09</v>
       </c>
       <c r="R71">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="S71">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T71">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="U71">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="V71">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="W71">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X71">
         <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Z71">
-        <v>5.25</v>
+        <v>5.6</v>
       </c>
       <c r="AA71">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="AB71">
-        <v>2.34</v>
+        <v>2.59</v>
       </c>
       <c r="AC71">
-        <v>2.27</v>
+        <v>2.12</v>
       </c>
       <c r="AD71">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AE71">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AF71">
         <v>1.44</v>
       </c>
       <c r="AG71">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK71">
-        <v>1.3</v>
+        <v>2.15</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,80 +12045,80 @@
         </is>
       </c>
       <c r="N72">
-        <v>5.66</v>
+        <v>3.1</v>
       </c>
       <c r="O72">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="P72">
-        <v>1.47</v>
+        <v>1.95</v>
       </c>
       <c r="Q72">
-        <v>4.18</v>
+        <v>3.8</v>
       </c>
       <c r="R72">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="S72">
+        <v>1.25</v>
+      </c>
+      <c r="T72">
+        <v>3.7</v>
+      </c>
+      <c r="U72">
+        <v>2.2</v>
+      </c>
+      <c r="V72">
+        <v>1.61</v>
+      </c>
+      <c r="W72">
+        <v>1.13</v>
+      </c>
+      <c r="X72">
+        <v>1.02</v>
+      </c>
+      <c r="Y72">
+        <v>1.12</v>
+      </c>
+      <c r="Z72">
+        <v>5.25</v>
+      </c>
+      <c r="AA72">
+        <v>1.53</v>
+      </c>
+      <c r="AB72">
+        <v>2.34</v>
+      </c>
+      <c r="AC72">
+        <v>2.27</v>
+      </c>
+      <c r="AD72">
+        <v>1.57</v>
+      </c>
+      <c r="AE72">
+        <v>1.25</v>
+      </c>
+      <c r="AF72">
+        <v>1.44</v>
+      </c>
+      <c r="AG72">
+        <v>2.55</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ72">
         <v>1.18</v>
       </c>
-      <c r="T72">
-        <v>4</v>
-      </c>
-      <c r="U72">
-        <v>2.06</v>
-      </c>
-      <c r="V72">
-        <v>1.72</v>
-      </c>
-      <c r="W72">
-        <v>1.17</v>
-      </c>
-      <c r="X72">
-        <v>1.01</v>
-      </c>
-      <c r="Y72">
-        <v>1.11</v>
-      </c>
-      <c r="Z72">
-        <v>6.06</v>
-      </c>
-      <c r="AA72">
-        <v>1.4</v>
-      </c>
-      <c r="AB72">
-        <v>2.87</v>
-      </c>
-      <c r="AC72">
-        <v>1.95</v>
-      </c>
-      <c r="AD72">
-        <v>1.73</v>
-      </c>
-      <c r="AE72">
+      <c r="AK72">
         <v>1.3</v>
-      </c>
-      <c r="AF72">
-        <v>1.5</v>
-      </c>
-      <c r="AG72">
-        <v>2.45</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ72">
-        <v>1.14</v>
-      </c>
-      <c r="AK72">
-        <v>1.12</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.05</v>
+        <v>5.66</v>
       </c>
       <c r="O73">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="P73">
-        <v>2.7</v>
+        <v>1.47</v>
       </c>
       <c r="Q73">
-        <v>2.52</v>
+        <v>4.18</v>
       </c>
       <c r="R73">
-        <v>2.63</v>
+        <v>2.43</v>
       </c>
       <c r="S73">
+        <v>1.18</v>
+      </c>
+      <c r="T73">
+        <v>4</v>
+      </c>
+      <c r="U73">
+        <v>2.06</v>
+      </c>
+      <c r="V73">
+        <v>1.72</v>
+      </c>
+      <c r="W73">
         <v>1.17</v>
-      </c>
-      <c r="T73">
-        <v>4.5</v>
-      </c>
-      <c r="U73">
-        <v>1.9</v>
-      </c>
-      <c r="V73">
-        <v>1.8</v>
-      </c>
-      <c r="W73">
-        <v>1.22</v>
       </c>
       <c r="X73">
         <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="Z73">
-        <v>7.2</v>
+        <v>6.06</v>
       </c>
       <c r="AA73">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AB73">
-        <v>3.28</v>
+        <v>2.87</v>
       </c>
       <c r="AC73">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AD73">
-        <v>1.99</v>
+        <v>1.73</v>
       </c>
       <c r="AE73">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AF73">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AG73">
-        <v>3.5</v>
+        <v>2.45</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AK73">
-        <v>1.65</v>
+        <v>1.12</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.68</v>
+        <v>2.05</v>
       </c>
       <c r="O74">
-        <v>4.25</v>
+        <v>4.1</v>
       </c>
       <c r="P74">
-        <v>3.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q74">
-        <v>2.03</v>
+        <v>2.52</v>
       </c>
       <c r="R74">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="S74">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T74">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="U74">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="V74">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="W74">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X74">
         <v>1.01</v>
       </c>
       <c r="Y74">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Z74">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AA74">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AB74">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="AC74">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AD74">
-        <v>1.86</v>
+        <v>1.99</v>
       </c>
       <c r="AE74">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AF74">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AG74">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK74">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12487,12 +12487,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,81 +12534,81 @@
         </is>
       </c>
       <c r="N75">
+        <v>1.68</v>
+      </c>
+      <c r="O75">
+        <v>4.25</v>
+      </c>
+      <c r="P75">
+        <v>3.75</v>
+      </c>
+      <c r="Q75">
+        <v>2.03</v>
+      </c>
+      <c r="R75">
+        <v>2.6</v>
+      </c>
+      <c r="S75">
+        <v>1.14</v>
+      </c>
+      <c r="T75">
+        <v>4.4</v>
+      </c>
+      <c r="U75">
+        <v>2.05</v>
+      </c>
+      <c r="V75">
+        <v>1.73</v>
+      </c>
+      <c r="W75">
+        <v>1.2</v>
+      </c>
+      <c r="X75">
+        <v>1.01</v>
+      </c>
+      <c r="Y75">
+        <v>1.07</v>
+      </c>
+      <c r="Z75">
+        <v>7</v>
+      </c>
+      <c r="AA75">
+        <v>1.36</v>
+      </c>
+      <c r="AB75">
+        <v>3.1</v>
+      </c>
+      <c r="AC75">
         <v>1.87</v>
       </c>
-      <c r="O75">
-        <v>3.4</v>
-      </c>
-      <c r="P75">
-        <v>3.7</v>
-      </c>
-      <c r="Q75">
-        <v>2.45</v>
-      </c>
-      <c r="R75">
-        <v>2.2</v>
-      </c>
-      <c r="S75">
+      <c r="AD75">
+        <v>1.86</v>
+      </c>
+      <c r="AE75">
+        <v>1.33</v>
+      </c>
+      <c r="AF75">
         <v>1.36</v>
       </c>
-      <c r="T75">
-        <v>3.2</v>
-      </c>
-      <c r="U75">
-        <v>2.5</v>
-      </c>
-      <c r="V75">
-        <v>1.45</v>
-      </c>
-      <c r="W75">
-        <v>1.07</v>
-      </c>
-      <c r="X75">
-        <v>1.02</v>
-      </c>
-      <c r="Y75">
+      <c r="AG75">
+        <v>2.9</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ75">
         <v>1.22</v>
       </c>
-      <c r="Z75">
-        <v>3.8</v>
-      </c>
-      <c r="AA75">
-        <v>1.76</v>
-      </c>
-      <c r="AB75">
-        <v>1.92</v>
-      </c>
-      <c r="AC75">
-        <v>3</v>
-      </c>
-      <c r="AD75">
-        <v>1.33</v>
-      </c>
-      <c r="AE75">
-        <v>1.1</v>
-      </c>
-      <c r="AF75">
-        <v>1.67</v>
-      </c>
-      <c r="AG75">
+      <c r="AK75">
         <v>2.05</v>
       </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ75">
-        <v>1.25</v>
-      </c>
-      <c r="AK75">
-        <v>1.85</v>
-      </c>
       <c r="AL75">
         <v>0</v>
       </c>
@@ -12638,7 +12638,7 @@
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>2026-10-16 15:30:00</t>
+          <t>2026-10-16 15:00:00</t>
         </is>
       </c>
     </row>
@@ -12655,7 +12655,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q76">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R76">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S76">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T76">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U76">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V76">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W76">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X76">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y76">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z76">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA76">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC76">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD76">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF76">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG76">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK76">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12818,7 +12818,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.87</v>
+        <v>2.14</v>
       </c>
       <c r="O77">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="P77">
-        <v>3.61</v>
+        <v>2.94</v>
       </c>
       <c r="Q77">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="R77">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S77">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T77">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="U77">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="V77">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W77">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y77">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z77">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AA77">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB77">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC77">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AD77">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE77">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF77">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG77">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK77">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12981,7 +12981,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,80 +13023,80 @@
         </is>
       </c>
       <c r="N78">
-        <v>3.9</v>
+        <v>1.87</v>
       </c>
       <c r="O78">
         <v>3.4</v>
       </c>
       <c r="P78">
+        <v>3.61</v>
+      </c>
+      <c r="Q78">
+        <v>2.41</v>
+      </c>
+      <c r="R78">
+        <v>2.14</v>
+      </c>
+      <c r="S78">
+        <v>1.36</v>
+      </c>
+      <c r="T78">
+        <v>3.03</v>
+      </c>
+      <c r="U78">
+        <v>2.82</v>
+      </c>
+      <c r="V78">
+        <v>1.4</v>
+      </c>
+      <c r="W78">
+        <v>1.07</v>
+      </c>
+      <c r="X78">
+        <v>1</v>
+      </c>
+      <c r="Y78">
+        <v>1.28</v>
+      </c>
+      <c r="Z78">
+        <v>3.48</v>
+      </c>
+      <c r="AA78">
+        <v>1.83</v>
+      </c>
+      <c r="AB78">
+        <v>1.9</v>
+      </c>
+      <c r="AC78">
+        <v>3.22</v>
+      </c>
+      <c r="AD78">
+        <v>1.32</v>
+      </c>
+      <c r="AE78">
+        <v>1.11</v>
+      </c>
+      <c r="AF78">
+        <v>1.73</v>
+      </c>
+      <c r="AG78">
+        <v>1.97</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ78">
+        <v>1.25</v>
+      </c>
+      <c r="AK78">
         <v>1.79</v>
-      </c>
-      <c r="Q78">
-        <v>4.4</v>
-      </c>
-      <c r="R78">
-        <v>2.2</v>
-      </c>
-      <c r="S78">
-        <v>1.33</v>
-      </c>
-      <c r="T78">
-        <v>2.76</v>
-      </c>
-      <c r="U78">
-        <v>2.56</v>
-      </c>
-      <c r="V78">
-        <v>1.44</v>
-      </c>
-      <c r="W78">
-        <v>1.1</v>
-      </c>
-      <c r="X78">
-        <v>1.03</v>
-      </c>
-      <c r="Y78">
-        <v>1.24</v>
-      </c>
-      <c r="Z78">
-        <v>3.6</v>
-      </c>
-      <c r="AA78">
-        <v>1.9</v>
-      </c>
-      <c r="AB78">
-        <v>1.84</v>
-      </c>
-      <c r="AC78">
-        <v>2.92</v>
-      </c>
-      <c r="AD78">
-        <v>1.3</v>
-      </c>
-      <c r="AE78">
-        <v>1.08</v>
-      </c>
-      <c r="AF78">
-        <v>1.75</v>
-      </c>
-      <c r="AG78">
-        <v>1.95</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ78">
-        <v>1.21</v>
-      </c>
-      <c r="AK78">
-        <v>1.22</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13144,7 +13144,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
+        <v>3.9</v>
+      </c>
+      <c r="O79">
+        <v>3.4</v>
+      </c>
+      <c r="P79">
+        <v>1.79</v>
+      </c>
+      <c r="Q79">
+        <v>4.4</v>
+      </c>
+      <c r="R79">
         <v>2.2</v>
       </c>
-      <c r="O79">
-        <v>3.5</v>
-      </c>
-      <c r="P79">
-        <v>2.7</v>
-      </c>
-      <c r="Q79">
-        <v>0</v>
-      </c>
-      <c r="R79">
-        <v>0</v>
-      </c>
       <c r="S79">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T79">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U79">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V79">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W79">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y79">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z79">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA79">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AB79">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="AC79">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD79">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF79">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG79">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK79">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13307,7 +13307,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="O80">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P80">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="Q80">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R80">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S80">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T80">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U80">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V80">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W80">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X80">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y80">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z80">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AA80">
         <v>1.65</v>
       </c>
       <c r="AB80">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AC80">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="AD80">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE80">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF80">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG80">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK80">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13470,7 +13470,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,31 +13512,31 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="O81">
         <v>3.4</v>
       </c>
       <c r="P81">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="Q81">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R81">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="S81">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T81">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="U81">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="V81">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W81">
         <v>1.11</v>
@@ -13545,25 +13545,25 @@
         <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z81">
         <v>4.33</v>
       </c>
       <c r="AA81">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AB81">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="AC81">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
       <c r="AD81">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE81">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF81">
         <v>1.53</v>
@@ -13582,7 +13582,7 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK81">
         <v>1.57</v>
@@ -13633,7 +13633,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S82">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T82">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U82">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V82">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W82">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X82">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z82">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA82">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC82">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD82">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG82">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK82">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.93</v>
+        <v>2.65</v>
       </c>
       <c r="O83">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="P83">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="Q83">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R83">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S83">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="T83">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="U83">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="V83">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="W83">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X83">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y83">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z83">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AA83">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AB83">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AC83">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD83">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE83">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AF83">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AG83">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK83">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13954,12 +13954,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,80 +14001,80 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.23</v>
+        <v>1.93</v>
       </c>
       <c r="O84">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="P84">
-        <v>2.72</v>
+        <v>2.95</v>
       </c>
       <c r="Q84">
-        <v>3.04</v>
+        <v>2.4</v>
       </c>
       <c r="R84">
-        <v>2.1</v>
+        <v>2.52</v>
       </c>
       <c r="S84">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="T84">
-        <v>2.8</v>
+        <v>4.8</v>
       </c>
       <c r="U84">
-        <v>2.8</v>
+        <v>1.86</v>
       </c>
       <c r="V84">
-        <v>1.36</v>
+        <v>1.85</v>
       </c>
       <c r="W84">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="X84">
         <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>1.31</v>
+        <v>1.06</v>
       </c>
       <c r="Z84">
-        <v>3.08</v>
+        <v>6.2</v>
       </c>
       <c r="AA84">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="AB84">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="AC84">
-        <v>3.28</v>
+        <v>1.93</v>
       </c>
       <c r="AD84">
+        <v>1.84</v>
+      </c>
+      <c r="AE84">
+        <v>1.37</v>
+      </c>
+      <c r="AF84">
+        <v>1.33</v>
+      </c>
+      <c r="AG84">
+        <v>3</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ84">
         <v>1.25</v>
       </c>
-      <c r="AE84">
-        <v>1.11</v>
-      </c>
-      <c r="AF84">
-        <v>1.73</v>
-      </c>
-      <c r="AG84">
-        <v>2.05</v>
-      </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI84" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ84">
-        <v>1.3</v>
-      </c>
       <c r="AK84">
-        <v>1.55</v>
+        <v>1.89</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14105,7 +14105,7 @@
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>2026-10-16 15:45:00</t>
+          <t>2026-10-16 15:30:00</t>
         </is>
       </c>
     </row>
@@ -14122,7 +14122,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,80 +14164,80 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.97</v>
+        <v>2.23</v>
       </c>
       <c r="O85">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="P85">
-        <v>2.36</v>
+        <v>2.72</v>
       </c>
       <c r="Q85">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="R85">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S85">
+        <v>1.37</v>
+      </c>
+      <c r="T85">
+        <v>2.8</v>
+      </c>
+      <c r="U85">
+        <v>2.8</v>
+      </c>
+      <c r="V85">
+        <v>1.36</v>
+      </c>
+      <c r="W85">
+        <v>1.05</v>
+      </c>
+      <c r="X85">
+        <v>1.01</v>
+      </c>
+      <c r="Y85">
+        <v>1.31</v>
+      </c>
+      <c r="Z85">
+        <v>3.08</v>
+      </c>
+      <c r="AA85">
+        <v>2</v>
+      </c>
+      <c r="AB85">
+        <v>1.8</v>
+      </c>
+      <c r="AC85">
+        <v>3.28</v>
+      </c>
+      <c r="AD85">
+        <v>1.25</v>
+      </c>
+      <c r="AE85">
+        <v>1.11</v>
+      </c>
+      <c r="AF85">
+        <v>1.73</v>
+      </c>
+      <c r="AG85">
+        <v>1.98</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ85">
         <v>1.3</v>
       </c>
-      <c r="T85">
-        <v>3.05</v>
-      </c>
-      <c r="U85">
-        <v>2.55</v>
-      </c>
-      <c r="V85">
-        <v>1.44</v>
-      </c>
-      <c r="W85">
-        <v>1.11</v>
-      </c>
-      <c r="X85">
-        <v>1</v>
-      </c>
-      <c r="Y85">
-        <v>1.2</v>
-      </c>
-      <c r="Z85">
-        <v>4.1</v>
-      </c>
-      <c r="AA85">
-        <v>1.84</v>
-      </c>
-      <c r="AB85">
-        <v>2.12</v>
-      </c>
-      <c r="AC85">
-        <v>2.76</v>
-      </c>
-      <c r="AD85">
-        <v>1.38</v>
-      </c>
-      <c r="AE85">
-        <v>1.1</v>
-      </c>
-      <c r="AF85">
-        <v>1.6</v>
-      </c>
-      <c r="AG85">
-        <v>2.25</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI85" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ85">
-        <v>1.34</v>
-      </c>
       <c r="AK85">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14285,22 +14285,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,80 +14327,80 @@
         </is>
       </c>
       <c r="N86">
-        <v>3.9</v>
+        <v>3.01</v>
       </c>
       <c r="O86">
         <v>3.6</v>
       </c>
       <c r="P86">
-        <v>1.77</v>
+        <v>2.31</v>
       </c>
       <c r="Q86">
-        <v>4.68</v>
+        <v>3.2</v>
       </c>
       <c r="R86">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="S86">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="T86">
-        <v>3.22</v>
+        <v>3.16</v>
       </c>
       <c r="U86">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="V86">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W86">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X86">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z86">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AA86">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AB86">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="AC86">
-        <v>2.69</v>
+        <v>2.61</v>
       </c>
       <c r="AD86">
+        <v>1.42</v>
+      </c>
+      <c r="AE86">
+        <v>1.12</v>
+      </c>
+      <c r="AF86">
+        <v>1.53</v>
+      </c>
+      <c r="AG86">
+        <v>2.32</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ86">
+        <v>1.25</v>
+      </c>
+      <c r="AK86">
         <v>1.36</v>
-      </c>
-      <c r="AE86">
-        <v>1.11</v>
-      </c>
-      <c r="AF86">
-        <v>1.66</v>
-      </c>
-      <c r="AG86">
-        <v>2.1</v>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI86" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ86">
-        <v>1.24</v>
-      </c>
-      <c r="AK86">
-        <v>1.21</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,80 +14490,80 @@
         </is>
       </c>
       <c r="N87">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O87">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="P87">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="Q87">
-        <v>3.25</v>
+        <v>4.68</v>
       </c>
       <c r="R87">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="S87">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="T87">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="U87">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="V87">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W87">
         <v>1.1</v>
       </c>
       <c r="X87">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y87">
+        <v>1.19</v>
+      </c>
+      <c r="Z87">
+        <v>3.75</v>
+      </c>
+      <c r="AA87">
+        <v>1.72</v>
+      </c>
+      <c r="AB87">
+        <v>2.05</v>
+      </c>
+      <c r="AC87">
+        <v>2.69</v>
+      </c>
+      <c r="AD87">
+        <v>1.36</v>
+      </c>
+      <c r="AE87">
+        <v>1.11</v>
+      </c>
+      <c r="AF87">
+        <v>1.66</v>
+      </c>
+      <c r="AG87">
+        <v>2.09</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ87">
         <v>1.24</v>
       </c>
-      <c r="Z87">
-        <v>3.34</v>
-      </c>
-      <c r="AA87">
-        <v>1.85</v>
-      </c>
-      <c r="AB87">
-        <v>1.86</v>
-      </c>
-      <c r="AC87">
-        <v>3.14</v>
-      </c>
-      <c r="AD87">
-        <v>1.27</v>
-      </c>
-      <c r="AE87">
-        <v>1.06</v>
-      </c>
-      <c r="AF87">
-        <v>1.69</v>
-      </c>
-      <c r="AG87">
-        <v>2.1</v>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI87" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ87">
-        <v>1.28</v>
-      </c>
       <c r="AK87">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,80 +14653,80 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.53</v>
+        <v>3</v>
       </c>
       <c r="O88">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="P88">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="Q88">
-        <v>2.05</v>
+        <v>3.25</v>
       </c>
       <c r="R88">
-        <v>2.17</v>
+        <v>2.24</v>
       </c>
       <c r="S88">
+        <v>1.35</v>
+      </c>
+      <c r="T88">
+        <v>3</v>
+      </c>
+      <c r="U88">
+        <v>2.62</v>
+      </c>
+      <c r="V88">
+        <v>1.4</v>
+      </c>
+      <c r="W88">
+        <v>1.1</v>
+      </c>
+      <c r="X88">
+        <v>1.01</v>
+      </c>
+      <c r="Y88">
+        <v>1.24</v>
+      </c>
+      <c r="Z88">
+        <v>3.34</v>
+      </c>
+      <c r="AA88">
+        <v>1.9</v>
+      </c>
+      <c r="AB88">
+        <v>1.86</v>
+      </c>
+      <c r="AC88">
+        <v>3.14</v>
+      </c>
+      <c r="AD88">
+        <v>1.27</v>
+      </c>
+      <c r="AE88">
+        <v>1.06</v>
+      </c>
+      <c r="AF88">
+        <v>1.69</v>
+      </c>
+      <c r="AG88">
+        <v>2.1</v>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ88">
+        <v>1.28</v>
+      </c>
+      <c r="AK88">
         <v>1.32</v>
-      </c>
-      <c r="T88">
-        <v>3.08</v>
-      </c>
-      <c r="U88">
-        <v>2.53</v>
-      </c>
-      <c r="V88">
-        <v>1.47</v>
-      </c>
-      <c r="W88">
-        <v>1.11</v>
-      </c>
-      <c r="X88">
-        <v>1.02</v>
-      </c>
-      <c r="Y88">
-        <v>1.19</v>
-      </c>
-      <c r="Z88">
-        <v>4.02</v>
-      </c>
-      <c r="AA88">
-        <v>1.75</v>
-      </c>
-      <c r="AB88">
-        <v>2.08</v>
-      </c>
-      <c r="AC88">
-        <v>2.83</v>
-      </c>
-      <c r="AD88">
-        <v>1.42</v>
-      </c>
-      <c r="AE88">
-        <v>1.1</v>
-      </c>
-      <c r="AF88">
-        <v>1.75</v>
-      </c>
-      <c r="AG88">
-        <v>1.97</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI88" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ88">
-        <v>1.19</v>
-      </c>
-      <c r="AK88">
-        <v>2.26</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,80 +14816,80 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="O89">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="P89">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Q89">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="R89">
-        <v>2.71</v>
+        <v>2.17</v>
       </c>
       <c r="S89">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="T89">
-        <v>3.78</v>
+        <v>3.08</v>
       </c>
       <c r="U89">
-        <v>2.2</v>
+        <v>2.53</v>
       </c>
       <c r="V89">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="W89">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X89">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y89">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z89">
-        <v>5.25</v>
+        <v>4.02</v>
       </c>
       <c r="AA89">
-        <v>1.49</v>
+        <v>1.75</v>
       </c>
       <c r="AB89">
-        <v>2.57</v>
+        <v>2.08</v>
       </c>
       <c r="AC89">
+        <v>2.83</v>
+      </c>
+      <c r="AD89">
+        <v>1.42</v>
+      </c>
+      <c r="AE89">
+        <v>1.1</v>
+      </c>
+      <c r="AF89">
+        <v>1.75</v>
+      </c>
+      <c r="AG89">
+        <v>1.97</v>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ89">
+        <v>1.19</v>
+      </c>
+      <c r="AK89">
         <v>2.26</v>
-      </c>
-      <c r="AD89">
-        <v>1.64</v>
-      </c>
-      <c r="AE89">
-        <v>1.25</v>
-      </c>
-      <c r="AF89">
-        <v>1.61</v>
-      </c>
-      <c r="AG89">
-        <v>2.18</v>
-      </c>
-      <c r="AH89" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI89" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ89">
-        <v>1.2</v>
-      </c>
-      <c r="AK89">
-        <v>2.5</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>6.32</v>
+        <v>1.5</v>
       </c>
       <c r="O90">
-        <v>4.55</v>
+        <v>4.2</v>
       </c>
       <c r="P90">
-        <v>1.37</v>
+        <v>4.8</v>
       </c>
       <c r="Q90">
-        <v>5.5</v>
+        <v>1.95</v>
       </c>
       <c r="R90">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="S90">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T90">
         <v>3.9</v>
       </c>
       <c r="U90">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="V90">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="W90">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X90">
         <v>1.01</v>
       </c>
       <c r="Y90">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z90">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="AA90">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AB90">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="AC90">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AD90">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AE90">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF90">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG90">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="AK90">
-        <v>1.11</v>
+        <v>2.5</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.31</v>
+        <v>6.32</v>
       </c>
       <c r="O91">
-        <v>3.54</v>
+        <v>4.55</v>
       </c>
       <c r="P91">
-        <v>2.48</v>
+        <v>1.37</v>
       </c>
       <c r="Q91">
-        <v>2.88</v>
+        <v>5.5</v>
       </c>
       <c r="R91">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="S91">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T91">
-        <v>3.52</v>
+        <v>3.9</v>
       </c>
       <c r="U91">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="V91">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="W91">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X91">
         <v>1.01</v>
       </c>
       <c r="Y91">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z91">
-        <v>4.98</v>
+        <v>5.6</v>
       </c>
       <c r="AA91">
+        <v>1.42</v>
+      </c>
+      <c r="AB91">
+        <v>2.74</v>
+      </c>
+      <c r="AC91">
+        <v>2.07</v>
+      </c>
+      <c r="AD91">
+        <v>1.73</v>
+      </c>
+      <c r="AE91">
+        <v>1.29</v>
+      </c>
+      <c r="AF91">
         <v>1.55</v>
       </c>
-      <c r="AB91">
-        <v>2.4</v>
-      </c>
-      <c r="AC91">
-        <v>2.34</v>
-      </c>
-      <c r="AD91">
-        <v>1.57</v>
-      </c>
-      <c r="AE91">
-        <v>1.23</v>
-      </c>
-      <c r="AF91">
-        <v>1.44</v>
-      </c>
       <c r="AG91">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.44</v>
+        <v>2.8</v>
       </c>
       <c r="AK91">
-        <v>1.53</v>
+        <v>1.11</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,80 +15305,80 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.58</v>
+        <v>2.31</v>
       </c>
       <c r="O92">
-        <v>3.46</v>
+        <v>3.54</v>
       </c>
       <c r="P92">
-        <v>2.26</v>
+        <v>2.48</v>
       </c>
       <c r="Q92">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="R92">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="S92">
         <v>1.25</v>
       </c>
       <c r="T92">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="U92">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="V92">
+        <v>1.6</v>
+      </c>
+      <c r="W92">
+        <v>1.14</v>
+      </c>
+      <c r="X92">
+        <v>1.01</v>
+      </c>
+      <c r="Y92">
+        <v>1.15</v>
+      </c>
+      <c r="Z92">
+        <v>4.98</v>
+      </c>
+      <c r="AA92">
+        <v>1.55</v>
+      </c>
+      <c r="AB92">
+        <v>2.4</v>
+      </c>
+      <c r="AC92">
+        <v>2.34</v>
+      </c>
+      <c r="AD92">
         <v>1.57</v>
       </c>
-      <c r="W92">
-        <v>1.15</v>
-      </c>
-      <c r="X92">
-        <v>1.02</v>
-      </c>
-      <c r="Y92">
-        <v>1.13</v>
-      </c>
-      <c r="Z92">
-        <v>4.8</v>
-      </c>
-      <c r="AA92">
-        <v>1.57</v>
-      </c>
-      <c r="AB92">
-        <v>2.35</v>
-      </c>
-      <c r="AC92">
-        <v>2.42</v>
-      </c>
-      <c r="AD92">
-        <v>1.47</v>
-      </c>
       <c r="AE92">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AF92">
+        <v>1.44</v>
+      </c>
+      <c r="AG92">
+        <v>2.5</v>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ92">
+        <v>1.44</v>
+      </c>
+      <c r="AK92">
         <v>1.53</v>
-      </c>
-      <c r="AG92">
-        <v>2.4</v>
-      </c>
-      <c r="AH92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ92">
-        <v>1.29</v>
-      </c>
-      <c r="AK92">
-        <v>1.35</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.8</v>
+        <v>2.58</v>
       </c>
       <c r="O93">
-        <v>3.38</v>
+        <v>3.46</v>
       </c>
       <c r="P93">
-        <v>2.21</v>
+        <v>2.26</v>
       </c>
       <c r="Q93">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="R93">
+        <v>2.3</v>
+      </c>
+      <c r="S93">
+        <v>1.25</v>
+      </c>
+      <c r="T93">
+        <v>3.5</v>
+      </c>
+      <c r="U93">
         <v>2.25</v>
       </c>
-      <c r="S93">
-        <v>1.31</v>
-      </c>
-      <c r="T93">
-        <v>3.25</v>
-      </c>
-      <c r="U93">
-        <v>2.63</v>
-      </c>
       <c r="V93">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="W93">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X93">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y93">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="Z93">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="AA93">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AB93">
-        <v>1.93</v>
+        <v>2.35</v>
       </c>
       <c r="AC93">
-        <v>2.88</v>
+        <v>2.42</v>
       </c>
       <c r="AD93">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="AE93">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="AF93">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG93">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>1.29</v>
       </c>
       <c r="AK93">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>3.46</v>
+        <v>2.8</v>
       </c>
       <c r="O94">
-        <v>3.54</v>
+        <v>3.38</v>
       </c>
       <c r="P94">
-        <v>1.87</v>
+        <v>2.21</v>
       </c>
       <c r="Q94">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="R94">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="S94">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T94">
         <v>3.25</v>
       </c>
       <c r="U94">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="V94">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W94">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X94">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y94">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z94">
-        <v>4.25</v>
+        <v>3.7</v>
       </c>
       <c r="AA94">
+        <v>1.75</v>
+      </c>
+      <c r="AB94">
+        <v>1.93</v>
+      </c>
+      <c r="AC94">
+        <v>2.88</v>
+      </c>
+      <c r="AD94">
+        <v>1.39</v>
+      </c>
+      <c r="AE94">
+        <v>1.08</v>
+      </c>
+      <c r="AF94">
         <v>1.62</v>
       </c>
-      <c r="AB94">
-        <v>2.2</v>
-      </c>
-      <c r="AC94">
-        <v>2.51</v>
-      </c>
-      <c r="AD94">
-        <v>1.41</v>
-      </c>
-      <c r="AE94">
-        <v>1.12</v>
-      </c>
-      <c r="AF94">
-        <v>1.53</v>
-      </c>
       <c r="AG94">
-        <v>2.38</v>
+        <v>2.07</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK94">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15752,22 +15752,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,80 +15794,80 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.53</v>
+        <v>3.46</v>
       </c>
       <c r="O95">
-        <v>3.75</v>
+        <v>3.54</v>
       </c>
       <c r="P95">
-        <v>2.6</v>
+        <v>1.87</v>
       </c>
       <c r="Q95">
-        <v>3.02</v>
+        <v>3.6</v>
       </c>
       <c r="R95">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="S95">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T95">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="U95">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V95">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="W95">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X95">
         <v>1.02</v>
       </c>
       <c r="Y95">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="Z95">
-        <v>4.95</v>
+        <v>4.25</v>
       </c>
       <c r="AA95">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="AB95">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AC95">
-        <v>2.24</v>
+        <v>2.51</v>
       </c>
       <c r="AD95">
-        <v>1.76</v>
+        <v>1.41</v>
       </c>
       <c r="AE95">
+        <v>1.12</v>
+      </c>
+      <c r="AF95">
+        <v>1.53</v>
+      </c>
+      <c r="AG95">
+        <v>2.38</v>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ95">
         <v>1.25</v>
       </c>
-      <c r="AF95">
-        <v>1.4</v>
-      </c>
-      <c r="AG95">
-        <v>2.75</v>
-      </c>
-      <c r="AH95" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI95" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ95">
-        <v>1.3</v>
-      </c>
       <c r="AK95">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15910,27 +15910,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,34 +15957,34 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.42</v>
+        <v>2.53</v>
       </c>
       <c r="O96">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P96">
-        <v>2.39</v>
+        <v>2.6</v>
       </c>
       <c r="Q96">
         <v>3.02</v>
       </c>
       <c r="R96">
+        <v>2.38</v>
+      </c>
+      <c r="S96">
+        <v>1.25</v>
+      </c>
+      <c r="T96">
+        <v>3.34</v>
+      </c>
+      <c r="U96">
         <v>2.25</v>
       </c>
-      <c r="S96">
-        <v>1.23</v>
-      </c>
-      <c r="T96">
-        <v>3.46</v>
-      </c>
-      <c r="U96">
-        <v>2.23</v>
-      </c>
       <c r="V96">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="W96">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X96">
         <v>1.02</v>
@@ -15993,28 +15993,28 @@
         <v>1.13</v>
       </c>
       <c r="Z96">
-        <v>4.5</v>
+        <v>4.95</v>
       </c>
       <c r="AA96">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="AB96">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AC96">
-        <v>2.43</v>
+        <v>2.24</v>
       </c>
       <c r="AD96">
-        <v>1.44</v>
+        <v>1.76</v>
       </c>
       <c r="AE96">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AF96">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AG96">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK96">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16061,7 +16061,7 @@
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>2026-10-16 16:00:00</t>
+          <t>2026-10-16 15:45:00</t>
         </is>
       </c>
     </row>
@@ -16078,22 +16078,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,80 +16120,80 @@
         </is>
       </c>
       <c r="N97">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O97">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q97">
-        <v>2.49</v>
+        <v>3.02</v>
       </c>
       <c r="R97">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="S97">
-        <v>1.39</v>
+        <v>1.23</v>
       </c>
       <c r="T97">
-        <v>3.09</v>
+        <v>3.46</v>
       </c>
       <c r="U97">
-        <v>2.75</v>
+        <v>2.23</v>
       </c>
       <c r="V97">
+        <v>1.53</v>
+      </c>
+      <c r="W97">
+        <v>1.12</v>
+      </c>
+      <c r="X97">
+        <v>1.02</v>
+      </c>
+      <c r="Y97">
+        <v>1.13</v>
+      </c>
+      <c r="Z97">
+        <v>4.5</v>
+      </c>
+      <c r="AA97">
+        <v>1.57</v>
+      </c>
+      <c r="AB97">
+        <v>2.2</v>
+      </c>
+      <c r="AC97">
+        <v>2.43</v>
+      </c>
+      <c r="AD97">
+        <v>1.44</v>
+      </c>
+      <c r="AE97">
+        <v>1.14</v>
+      </c>
+      <c r="AF97">
+        <v>1.48</v>
+      </c>
+      <c r="AG97">
+        <v>2.45</v>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ97">
+        <v>1.21</v>
+      </c>
+      <c r="AK97">
         <v>1.42</v>
-      </c>
-      <c r="W97">
-        <v>1.1</v>
-      </c>
-      <c r="X97">
-        <v>1.03</v>
-      </c>
-      <c r="Y97">
-        <v>1.27</v>
-      </c>
-      <c r="Z97">
-        <v>3.34</v>
-      </c>
-      <c r="AA97">
-        <v>1.95</v>
-      </c>
-      <c r="AB97">
-        <v>1.93</v>
-      </c>
-      <c r="AC97">
-        <v>3.32</v>
-      </c>
-      <c r="AD97">
-        <v>1.35</v>
-      </c>
-      <c r="AE97">
-        <v>1.08</v>
-      </c>
-      <c r="AF97">
-        <v>1.7</v>
-      </c>
-      <c r="AG97">
-        <v>2</v>
-      </c>
-      <c r="AH97" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI97" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ97">
-        <v>1.3</v>
-      </c>
-      <c r="AK97">
-        <v>1.7</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16241,7 +16241,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="O98">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="P98">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q98">
-        <v>3.75</v>
+        <v>2.49</v>
       </c>
       <c r="R98">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="S98">
+        <v>1.39</v>
+      </c>
+      <c r="T98">
+        <v>3.09</v>
+      </c>
+      <c r="U98">
+        <v>2.75</v>
+      </c>
+      <c r="V98">
+        <v>1.42</v>
+      </c>
+      <c r="W98">
+        <v>1.1</v>
+      </c>
+      <c r="X98">
+        <v>1.03</v>
+      </c>
+      <c r="Y98">
+        <v>1.27</v>
+      </c>
+      <c r="Z98">
+        <v>3.34</v>
+      </c>
+      <c r="AA98">
+        <v>1.95</v>
+      </c>
+      <c r="AB98">
+        <v>1.93</v>
+      </c>
+      <c r="AC98">
+        <v>3.32</v>
+      </c>
+      <c r="AD98">
         <v>1.35</v>
       </c>
-      <c r="T98">
-        <v>2.87</v>
-      </c>
-      <c r="U98">
-        <v>2.44</v>
-      </c>
-      <c r="V98">
-        <v>1.47</v>
-      </c>
-      <c r="W98">
+      <c r="AE98">
         <v>1.08</v>
       </c>
-      <c r="X98">
-        <v>1.01</v>
-      </c>
-      <c r="Y98">
-        <v>1.24</v>
-      </c>
-      <c r="Z98">
-        <v>3.55</v>
-      </c>
-      <c r="AA98">
-        <v>1.65</v>
-      </c>
-      <c r="AB98">
-        <v>2.1</v>
-      </c>
-      <c r="AC98">
-        <v>2.66</v>
-      </c>
-      <c r="AD98">
-        <v>1.4</v>
-      </c>
-      <c r="AE98">
-        <v>1.1</v>
-      </c>
       <c r="AF98">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG98">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK98">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16399,27 +16399,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.77</v>
+        <v>3.14</v>
       </c>
       <c r="O99">
-        <v>3.1</v>
+        <v>3.56</v>
       </c>
       <c r="P99">
-        <v>4.2</v>
+        <v>2.12</v>
       </c>
       <c r="Q99">
-        <v>2.48</v>
+        <v>3.75</v>
       </c>
       <c r="R99">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S99">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="T99">
-        <v>2.62</v>
+        <v>2.87</v>
       </c>
       <c r="U99">
-        <v>3.18</v>
+        <v>2.44</v>
       </c>
       <c r="V99">
-        <v>1.27</v>
+        <v>1.47</v>
       </c>
       <c r="W99">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X99">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y99">
+        <v>1.24</v>
+      </c>
+      <c r="Z99">
+        <v>3.55</v>
+      </c>
+      <c r="AA99">
+        <v>1.8</v>
+      </c>
+      <c r="AB99">
+        <v>2</v>
+      </c>
+      <c r="AC99">
+        <v>2.66</v>
+      </c>
+      <c r="AD99">
         <v>1.4</v>
       </c>
-      <c r="Z99">
-        <v>2.82</v>
-      </c>
-      <c r="AA99">
-        <v>2.28</v>
-      </c>
-      <c r="AB99">
-        <v>1.61</v>
-      </c>
-      <c r="AC99">
-        <v>4.16</v>
-      </c>
-      <c r="AD99">
-        <v>1.21</v>
-      </c>
       <c r="AE99">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="AF99">
-        <v>2.01</v>
+        <v>1.62</v>
       </c>
       <c r="AG99">
-        <v>1.68</v>
+        <v>2.25</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>1.25</v>
       </c>
       <c r="AK99">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16550,7 +16550,7 @@
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>2026-10-16 17:30:00</t>
+          <t>2026-10-16 16:00:00</t>
         </is>
       </c>
     </row>
@@ -16562,12 +16562,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O100">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P100">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q100">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R100">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S100">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T100">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U100">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V100">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W100">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X100">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y100">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z100">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AA100">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB100">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC100">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="AD100">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE100">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF100">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG100">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK100">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16713,7 +16713,7 @@
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>2026-10-16 18:00:00</t>
+          <t>2026-10-16 17:30:00</t>
         </is>
       </c>
     </row>
@@ -16725,12 +16725,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G101">
@@ -16781,55 +16781,55 @@
         <v>0</v>
       </c>
       <c r="Q101">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="R101">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="S101">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T101">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U101">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="V101">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W101">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X101">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y101">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z101">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="AA101">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB101">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC101">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD101">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE101">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF101">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AG101">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK101">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16876,7 +16876,7 @@
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>2026-10-16 19:30:00</t>
+          <t>2026-10-16 18:00:00</t>
         </is>
       </c>
     </row>
@@ -16888,12 +16888,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O102">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P102">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q102">
-        <v>2.88</v>
+        <v>9.5</v>
       </c>
       <c r="R102">
-        <v>2.25</v>
+        <v>2.59</v>
       </c>
       <c r="S102">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T102">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="U102">
-        <v>2.57</v>
+        <v>2.26</v>
       </c>
       <c r="V102">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W102">
         <v>1.08</v>
       </c>
       <c r="X102">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y102">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="Z102">
-        <v>3.63</v>
+        <v>4.03</v>
       </c>
       <c r="AA102">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB102">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="AC102">
-        <v>3.28</v>
+        <v>2.75</v>
       </c>
       <c r="AD102">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AE102">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF102">
-        <v>1.7</v>
+        <v>2.24</v>
       </c>
       <c r="AG102">
-        <v>2.05</v>
+        <v>1.58</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.36</v>
+        <v>1.08</v>
       </c>
       <c r="AK102">
-        <v>1.57</v>
+        <v>1.04</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17039,7 +17039,7 @@
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>2026-10-16 20:00:00</t>
+          <t>2026-10-16 19:30:00</t>
         </is>
       </c>
     </row>
@@ -17056,7 +17056,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="O103">
-        <v>4</v>
+        <v>3.48</v>
       </c>
       <c r="P103">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="Q103">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R103">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S103">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T103">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U103">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="V103">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W103">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X103">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y103">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z103">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="AA103">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="AB103">
-        <v>2.75</v>
+        <v>1.92</v>
       </c>
       <c r="AC103">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD103">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE103">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF103">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG103">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK103">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17214,12 +17214,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="O104">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="P104">
-        <v>2.87</v>
+        <v>3.8</v>
       </c>
       <c r="Q104">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="R104">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S104">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T104">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U104">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V104">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W104">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X104">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y104">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z104">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="AA104">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="AB104">
-        <v>1.7</v>
+        <v>2.75</v>
       </c>
       <c r="AC104">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD104">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE104">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF104">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG104">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK104">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17365,7 +17365,7 @@
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>2026-10-16 20:30:00</t>
+          <t>2026-10-16 20:00:00</t>
         </is>
       </c>
     </row>
@@ -17377,27 +17377,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>4.54</v>
+        <v>2.24</v>
       </c>
       <c r="O105">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="P105">
+        <v>2.87</v>
+      </c>
+      <c r="Q105">
+        <v>3.09</v>
+      </c>
+      <c r="R105">
+        <v>2.14</v>
+      </c>
+      <c r="S105">
+        <v>1.44</v>
+      </c>
+      <c r="T105">
+        <v>2.53</v>
+      </c>
+      <c r="U105">
+        <v>2.9</v>
+      </c>
+      <c r="V105">
+        <v>1.36</v>
+      </c>
+      <c r="W105">
+        <v>1.05</v>
+      </c>
+      <c r="X105">
+        <v>1.01</v>
+      </c>
+      <c r="Y105">
+        <v>1.35</v>
+      </c>
+      <c r="Z105">
+        <v>3.13</v>
+      </c>
+      <c r="AA105">
+        <v>2.1</v>
+      </c>
+      <c r="AB105">
         <v>1.7</v>
       </c>
-      <c r="Q105">
-        <v>0</v>
-      </c>
-      <c r="R105">
-        <v>0</v>
-      </c>
-      <c r="S105">
-        <v>0</v>
-      </c>
-      <c r="T105">
-        <v>0</v>
-      </c>
-      <c r="U105">
-        <v>0</v>
-      </c>
-      <c r="V105">
-        <v>0</v>
-      </c>
-      <c r="W105">
-        <v>0</v>
-      </c>
-      <c r="X105">
-        <v>0</v>
-      </c>
-      <c r="Y105">
-        <v>0</v>
-      </c>
-      <c r="Z105">
-        <v>0</v>
-      </c>
-      <c r="AA105">
-        <v>0</v>
-      </c>
-      <c r="AB105">
-        <v>0</v>
-      </c>
       <c r="AC105">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD105">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE105">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF105">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG105">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK105">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17528,7 +17528,7 @@
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>2026-10-16 21:00:00</t>
+          <t>2026-10-16 20:30:00</t>
         </is>
       </c>
     </row>
@@ -17545,22 +17545,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="G106">
@@ -17596,55 +17596,55 @@
         <v>0</v>
       </c>
       <c r="Q106">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R106">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S106">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T106">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U106">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V106">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W106">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X106">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z106">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA106">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AB106">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AC106">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD106">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE106">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF106">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG106">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK106">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17708,22 +17708,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O107">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P107">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q107">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R107">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S107">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T107">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U107">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="V107">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W107">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X107">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y107">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z107">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA107">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB107">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC107">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AD107">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE107">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF107">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG107">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK107">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17871,22 +17871,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,13 +17913,13 @@
         </is>
       </c>
       <c r="N108">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O108">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P108">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="Q108">
         <v>0</v>
@@ -18029,12 +18029,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,65 +18076,65 @@
         </is>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q109">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="R109">
-        <v>2.4</v>
+        <v>1.83</v>
       </c>
       <c r="S109">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="T109">
-        <v>3.6</v>
+        <v>2.25</v>
       </c>
       <c r="U109">
-        <v>2.15</v>
+        <v>3.75</v>
       </c>
       <c r="V109">
-        <v>1.6</v>
+        <v>1.22</v>
       </c>
       <c r="W109">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="X109">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="Y109">
-        <v>1.13</v>
+        <v>1.65</v>
       </c>
       <c r="Z109">
-        <v>4.55</v>
+        <v>2.2</v>
       </c>
       <c r="AA109">
+        <v>2.87</v>
+      </c>
+      <c r="AB109">
+        <v>1.35</v>
+      </c>
+      <c r="AC109">
+        <v>6.3</v>
+      </c>
+      <c r="AD109">
+        <v>1.1</v>
+      </c>
+      <c r="AE109">
+        <v>1.03</v>
+      </c>
+      <c r="AF109">
+        <v>2.34</v>
+      </c>
+      <c r="AG109">
         <v>1.52</v>
       </c>
-      <c r="AB109">
-        <v>2.31</v>
-      </c>
-      <c r="AC109">
-        <v>2.28</v>
-      </c>
-      <c r="AD109">
-        <v>1.5</v>
-      </c>
-      <c r="AE109">
-        <v>1.18</v>
-      </c>
-      <c r="AF109">
-        <v>1.5</v>
-      </c>
-      <c r="AG109">
-        <v>2.38</v>
-      </c>
       <c r="AH109" t="inlineStr">
         <is>
           <t>[]</t>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AK109">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18180,7 +18180,7 @@
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>2026-10-16 21:00:00</t>
+          <t>2026-10-16 22:00:00</t>
         </is>
       </c>
     </row>
@@ -18192,12 +18192,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.6</v>
+        <v>2.02</v>
       </c>
       <c r="O110">
-        <v>2.75</v>
+        <v>3.44</v>
       </c>
       <c r="P110">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="Q110">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R110">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S110">
+        <v>0</v>
+      </c>
+      <c r="T110">
+        <v>0</v>
+      </c>
+      <c r="U110">
+        <v>0</v>
+      </c>
+      <c r="V110">
+        <v>0</v>
+      </c>
+      <c r="W110">
+        <v>0</v>
+      </c>
+      <c r="X110">
+        <v>0</v>
+      </c>
+      <c r="Y110">
+        <v>0</v>
+      </c>
+      <c r="Z110">
+        <v>0</v>
+      </c>
+      <c r="AA110">
         <v>1.53</v>
       </c>
-      <c r="T110">
-        <v>2.38</v>
-      </c>
-      <c r="U110">
-        <v>3.82</v>
-      </c>
-      <c r="V110">
-        <v>1.22</v>
-      </c>
-      <c r="W110">
-        <v>1.03</v>
-      </c>
-      <c r="X110">
-        <v>1.06</v>
-      </c>
-      <c r="Y110">
-        <v>1.56</v>
-      </c>
-      <c r="Z110">
+      <c r="AB110">
         <v>2.37</v>
       </c>
-      <c r="AA110">
-        <v>2.62</v>
-      </c>
-      <c r="AB110">
-        <v>1.38</v>
-      </c>
       <c r="AC110">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AD110">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE110">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF110">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG110">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK110">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18342,495 +18342,6 @@
         <v>0</v>
       </c>
       <c r="AU110" t="inlineStr">
-        <is>
-          <t>2026-10-16 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Boston Legacy W</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>Racing Louisville</t>
-        </is>
-      </c>
-      <c r="G111">
-        <v>0</v>
-      </c>
-      <c r="H111">
-        <v>0</v>
-      </c>
-      <c r="I111">
-        <v>0</v>
-      </c>
-      <c r="J111">
-        <v>0</v>
-      </c>
-      <c r="K111">
-        <v>0</v>
-      </c>
-      <c r="L111">
-        <v>0</v>
-      </c>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N111">
-        <v>1.5</v>
-      </c>
-      <c r="O111">
-        <v>4.15</v>
-      </c>
-      <c r="P111">
-        <v>4.96</v>
-      </c>
-      <c r="Q111">
-        <v>0</v>
-      </c>
-      <c r="R111">
-        <v>0</v>
-      </c>
-      <c r="S111">
-        <v>0</v>
-      </c>
-      <c r="T111">
-        <v>0</v>
-      </c>
-      <c r="U111">
-        <v>0</v>
-      </c>
-      <c r="V111">
-        <v>0</v>
-      </c>
-      <c r="W111">
-        <v>0</v>
-      </c>
-      <c r="X111">
-        <v>0</v>
-      </c>
-      <c r="Y111">
-        <v>0</v>
-      </c>
-      <c r="Z111">
-        <v>0</v>
-      </c>
-      <c r="AA111">
-        <v>0</v>
-      </c>
-      <c r="AB111">
-        <v>0</v>
-      </c>
-      <c r="AC111">
-        <v>0</v>
-      </c>
-      <c r="AD111">
-        <v>0</v>
-      </c>
-      <c r="AE111">
-        <v>0</v>
-      </c>
-      <c r="AF111">
-        <v>0</v>
-      </c>
-      <c r="AG111">
-        <v>0</v>
-      </c>
-      <c r="AH111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ111">
-        <v>0</v>
-      </c>
-      <c r="AK111">
-        <v>0</v>
-      </c>
-      <c r="AL111">
-        <v>0</v>
-      </c>
-      <c r="AM111">
-        <v>-1</v>
-      </c>
-      <c r="AN111">
-        <v>-1</v>
-      </c>
-      <c r="AO111">
-        <v>-1</v>
-      </c>
-      <c r="AP111">
-        <v>-1</v>
-      </c>
-      <c r="AQ111">
-        <v>0</v>
-      </c>
-      <c r="AR111">
-        <v>0</v>
-      </c>
-      <c r="AS111">
-        <v>0</v>
-      </c>
-      <c r="AT111">
-        <v>0</v>
-      </c>
-      <c r="AU111" t="inlineStr">
-        <is>
-          <t>2026-10-16 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Gimnasia y Tiro</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>Atlanta</t>
-        </is>
-      </c>
-      <c r="G112">
-        <v>0</v>
-      </c>
-      <c r="H112">
-        <v>0</v>
-      </c>
-      <c r="I112">
-        <v>0</v>
-      </c>
-      <c r="J112">
-        <v>0</v>
-      </c>
-      <c r="K112">
-        <v>0</v>
-      </c>
-      <c r="L112">
-        <v>0</v>
-      </c>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N112">
-        <v>2.1</v>
-      </c>
-      <c r="O112">
-        <v>2.85</v>
-      </c>
-      <c r="P112">
-        <v>3.5</v>
-      </c>
-      <c r="Q112">
-        <v>3</v>
-      </c>
-      <c r="R112">
-        <v>1.83</v>
-      </c>
-      <c r="S112">
-        <v>1.57</v>
-      </c>
-      <c r="T112">
-        <v>2.25</v>
-      </c>
-      <c r="U112">
-        <v>3.75</v>
-      </c>
-      <c r="V112">
-        <v>1.22</v>
-      </c>
-      <c r="W112">
-        <v>1.04</v>
-      </c>
-      <c r="X112">
-        <v>1.14</v>
-      </c>
-      <c r="Y112">
-        <v>1.65</v>
-      </c>
-      <c r="Z112">
-        <v>2.2</v>
-      </c>
-      <c r="AA112">
-        <v>2.87</v>
-      </c>
-      <c r="AB112">
-        <v>1.35</v>
-      </c>
-      <c r="AC112">
-        <v>6.3</v>
-      </c>
-      <c r="AD112">
-        <v>1.1</v>
-      </c>
-      <c r="AE112">
-        <v>1.03</v>
-      </c>
-      <c r="AF112">
-        <v>2.34</v>
-      </c>
-      <c r="AG112">
-        <v>1.52</v>
-      </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI112" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ112">
-        <v>1.4</v>
-      </c>
-      <c r="AK112">
-        <v>1.57</v>
-      </c>
-      <c r="AL112">
-        <v>0</v>
-      </c>
-      <c r="AM112">
-        <v>-1</v>
-      </c>
-      <c r="AN112">
-        <v>-1</v>
-      </c>
-      <c r="AO112">
-        <v>-1</v>
-      </c>
-      <c r="AP112">
-        <v>-1</v>
-      </c>
-      <c r="AQ112">
-        <v>0</v>
-      </c>
-      <c r="AR112">
-        <v>0</v>
-      </c>
-      <c r="AS112">
-        <v>0</v>
-      </c>
-      <c r="AT112">
-        <v>0</v>
-      </c>
-      <c r="AU112" t="inlineStr">
-        <is>
-          <t>2026-10-16 22:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Canada Canadian Premier League</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Vancouver FC</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>HFX Wanderers FC</t>
-        </is>
-      </c>
-      <c r="G113">
-        <v>0</v>
-      </c>
-      <c r="H113">
-        <v>0</v>
-      </c>
-      <c r="I113">
-        <v>0</v>
-      </c>
-      <c r="J113">
-        <v>0</v>
-      </c>
-      <c r="K113">
-        <v>0</v>
-      </c>
-      <c r="L113">
-        <v>0</v>
-      </c>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N113">
-        <v>2.02</v>
-      </c>
-      <c r="O113">
-        <v>3.44</v>
-      </c>
-      <c r="P113">
-        <v>3.1</v>
-      </c>
-      <c r="Q113">
-        <v>0</v>
-      </c>
-      <c r="R113">
-        <v>0</v>
-      </c>
-      <c r="S113">
-        <v>0</v>
-      </c>
-      <c r="T113">
-        <v>0</v>
-      </c>
-      <c r="U113">
-        <v>0</v>
-      </c>
-      <c r="V113">
-        <v>0</v>
-      </c>
-      <c r="W113">
-        <v>0</v>
-      </c>
-      <c r="X113">
-        <v>0</v>
-      </c>
-      <c r="Y113">
-        <v>0</v>
-      </c>
-      <c r="Z113">
-        <v>0</v>
-      </c>
-      <c r="AA113">
-        <v>1.53</v>
-      </c>
-      <c r="AB113">
-        <v>2.37</v>
-      </c>
-      <c r="AC113">
-        <v>0</v>
-      </c>
-      <c r="AD113">
-        <v>0</v>
-      </c>
-      <c r="AE113">
-        <v>0</v>
-      </c>
-      <c r="AF113">
-        <v>0</v>
-      </c>
-      <c r="AG113">
-        <v>0</v>
-      </c>
-      <c r="AH113" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI113" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ113">
-        <v>0</v>
-      </c>
-      <c r="AK113">
-        <v>0</v>
-      </c>
-      <c r="AL113">
-        <v>0</v>
-      </c>
-      <c r="AM113">
-        <v>-1</v>
-      </c>
-      <c r="AN113">
-        <v>-1</v>
-      </c>
-      <c r="AO113">
-        <v>-1</v>
-      </c>
-      <c r="AP113">
-        <v>-1</v>
-      </c>
-      <c r="AQ113">
-        <v>0</v>
-      </c>
-      <c r="AR113">
-        <v>0</v>
-      </c>
-      <c r="AS113">
-        <v>0</v>
-      </c>
-      <c r="AT113">
-        <v>0</v>
-      </c>
-      <c r="AU113" t="inlineStr">
         <is>
           <t>2026-10-16 23:00:00</t>
         </is>

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -3611,7 +3611,7 @@
         <v>1.38</v>
       </c>
       <c r="AB20">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AC20">
         <v>2.01</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.08</v>
+        <v>2.29</v>
       </c>
       <c r="O23">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="P23">
-        <v>3.35</v>
+        <v>2.73</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -5051,13 +5051,13 @@
         <v>2.14</v>
       </c>
       <c r="S29">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T29">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="U29">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="V29">
         <v>1.44</v>
@@ -5730,7 +5730,7 @@
         <v>1.36</v>
       </c>
       <c r="AB33">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AC33">
         <v>1.88</v>
@@ -5890,10 +5890,10 @@
         <v>3.25</v>
       </c>
       <c r="AA34">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB34">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC34">
         <v>3.62</v>
@@ -6029,7 +6029,7 @@
         <v>2.14</v>
       </c>
       <c r="S35">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T35">
         <v>2.88</v>
@@ -6044,7 +6044,7 @@
         <v>1.07</v>
       </c>
       <c r="X35">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y35">
         <v>1.27</v>
@@ -6071,7 +6071,7 @@
         <v>1.8</v>
       </c>
       <c r="AG35">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6349,10 +6349,10 @@
         <v>1.8</v>
       </c>
       <c r="Q37">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="R37">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="S37">
         <v>1.36</v>
@@ -6361,28 +6361,28 @@
         <v>3.1</v>
       </c>
       <c r="U37">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="V37">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W37">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X37">
         <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z37">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AA37">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB37">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC37">
         <v>2.83</v>
@@ -6391,7 +6391,7 @@
         <v>1.33</v>
       </c>
       <c r="AE37">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF37">
         <v>1.67</v>
@@ -6527,7 +6527,7 @@
         <v>2.19</v>
       </c>
       <c r="V38">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W38">
         <v>1.13</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK38">
         <v>2</v>
@@ -6841,7 +6841,7 @@
         <v>2.54</v>
       </c>
       <c r="R40">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="S40">
         <v>1.25</v>
@@ -6868,10 +6868,10 @@
         <v>4.67</v>
       </c>
       <c r="AA40">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AB40">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC40">
         <v>2.49</v>
@@ -7717,7 +7717,7 @@
         <v>1.25</v>
       </c>
       <c r="AK45">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O47">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P47">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q47">
-        <v>2.51</v>
+        <v>1.83</v>
       </c>
       <c r="R47">
-        <v>2.21</v>
+        <v>2.44</v>
       </c>
       <c r="S47">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="T47">
-        <v>3.18</v>
+        <v>3.75</v>
       </c>
       <c r="U47">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="V47">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="W47">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="X47">
         <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z47">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="AA47">
-        <v>1.61</v>
+        <v>1.42</v>
       </c>
       <c r="AB47">
-        <v>2.13</v>
+        <v>2.49</v>
       </c>
       <c r="AC47">
-        <v>2.52</v>
+        <v>2.1</v>
       </c>
       <c r="AD47">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="AE47">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AF47">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG47">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK47">
-        <v>1.67</v>
+        <v>2.75</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,19 +8133,19 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="O48">
-        <v>3.8</v>
+        <v>3.48</v>
       </c>
       <c r="P48">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="Q48">
-        <v>2.19</v>
+        <v>2.51</v>
       </c>
       <c r="R48">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="S48">
         <v>1.27</v>
@@ -8154,43 +8154,43 @@
         <v>3.18</v>
       </c>
       <c r="U48">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V48">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W48">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X48">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z48">
-        <v>3.92</v>
+        <v>4.3</v>
       </c>
       <c r="AA48">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AB48">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AC48">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="AD48">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AE48">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF48">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AG48">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AK48">
-        <v>2.02</v>
+        <v>1.67</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q49">
-        <v>1.86</v>
+        <v>2.19</v>
       </c>
       <c r="R49">
-        <v>2.52</v>
+        <v>2.23</v>
       </c>
       <c r="S49">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="T49">
-        <v>3.68</v>
+        <v>3.18</v>
       </c>
       <c r="U49">
-        <v>2.12</v>
+        <v>2.34</v>
       </c>
       <c r="V49">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="W49">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X49">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y49">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="Z49">
-        <v>5.2</v>
+        <v>3.92</v>
       </c>
       <c r="AA49">
-        <v>1.47</v>
+        <v>1.66</v>
       </c>
       <c r="AB49">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="AC49">
-        <v>2.13</v>
+        <v>2.62</v>
       </c>
       <c r="AD49">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="AE49">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AF49">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AG49">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AK49">
-        <v>2.56</v>
+        <v>2.02</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8474,7 +8474,7 @@
         <v>2.19</v>
       </c>
       <c r="S50">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T50">
         <v>3.3</v>
@@ -8486,7 +8486,7 @@
         <v>1.51</v>
       </c>
       <c r="W50">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X50">
         <v>1.02</v>
@@ -8513,10 +8513,10 @@
         <v>1.12</v>
       </c>
       <c r="AF50">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AG50">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>1.61</v>
       </c>
       <c r="AB51">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC51">
         <v>2.42</v>
@@ -9111,7 +9111,7 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="O54">
         <v>3.6</v>
@@ -9153,10 +9153,10 @@
         <v>1.44</v>
       </c>
       <c r="AB54">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AC54">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="AD54">
         <v>1.73</v>
@@ -9600,10 +9600,10 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="O57">
-        <v>3.51</v>
+        <v>3.52</v>
       </c>
       <c r="P57">
         <v>1.87</v>
@@ -9763,7 +9763,7 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="O58">
         <v>3.6</v>
@@ -9802,10 +9802,10 @@
         <v>3.58</v>
       </c>
       <c r="AA58">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB58">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="AC58">
         <v>2.8</v>
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK58">
         <v>1.69</v>
@@ -9935,10 +9935,10 @@
         <v>2.8</v>
       </c>
       <c r="Q59">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="R59">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="S59">
         <v>1.22</v>
@@ -9947,7 +9947,7 @@
         <v>3.75</v>
       </c>
       <c r="U59">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V59">
         <v>1.57</v>
@@ -9959,31 +9959,31 @@
         <v>1.01</v>
       </c>
       <c r="Y59">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="Z59">
-        <v>4.6</v>
+        <v>4.79</v>
       </c>
       <c r="AA59">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AB59">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="AC59">
-        <v>2.29</v>
+        <v>2.37</v>
       </c>
       <c r="AD59">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AE59">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF59">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AG59">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK59">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10128,7 +10128,7 @@
         <v>5.01</v>
       </c>
       <c r="AA60">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AB60">
         <v>2.4</v>
@@ -10454,10 +10454,10 @@
         <v>6.54</v>
       </c>
       <c r="AA62">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB62">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AC62">
         <v>2.01</v>
@@ -10578,16 +10578,16 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="O63">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="P63">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="Q63">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="R63">
         <v>2.5</v>
@@ -10596,7 +10596,7 @@
         <v>1.17</v>
       </c>
       <c r="T63">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="U63">
         <v>2.02</v>
@@ -10611,31 +10611,31 @@
         <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z63">
-        <v>6</v>
+        <v>5.89</v>
       </c>
       <c r="AA63">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB63">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AC63">
         <v>1.98</v>
       </c>
       <c r="AD63">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AE63">
         <v>1.32</v>
       </c>
       <c r="AF63">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AG63">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK63">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,19 +10741,19 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="O64">
         <v>3.6</v>
       </c>
       <c r="P64">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="Q64">
-        <v>2.87</v>
+        <v>2.67</v>
       </c>
       <c r="R64">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="S64">
         <v>1.22</v>
@@ -10777,13 +10777,13 @@
         <v>1.11</v>
       </c>
       <c r="Z64">
-        <v>4.95</v>
+        <v>4.85</v>
       </c>
       <c r="AA64">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB64">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AC64">
         <v>2.25</v>
@@ -10811,7 +10811,7 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK64">
         <v>1.57</v>
@@ -10904,22 +10904,22 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O65">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P65">
         <v>3.2</v>
       </c>
       <c r="Q65">
-        <v>2.61</v>
+        <v>2.46</v>
       </c>
       <c r="R65">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="S65">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T65">
         <v>3.1</v>
@@ -10934,28 +10934,28 @@
         <v>1.1</v>
       </c>
       <c r="X65">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y65">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z65">
-        <v>3.79</v>
+        <v>3.6</v>
       </c>
       <c r="AA65">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB65">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC65">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AD65">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AE65">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF65">
         <v>1.67</v>
@@ -10974,7 +10974,7 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK65">
         <v>1.7</v>
@@ -11076,10 +11076,10 @@
         <v>2.37</v>
       </c>
       <c r="Q66">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R66">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S66">
         <v>1.4</v>
@@ -11088,34 +11088,34 @@
         <v>2.8</v>
       </c>
       <c r="U66">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="V66">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W66">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X66">
         <v>1.03</v>
       </c>
       <c r="Y66">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z66">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AA66">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="AB66">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AC66">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AD66">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE66">
         <v>1.06</v>
@@ -11233,13 +11233,13 @@
         <v>2.15</v>
       </c>
       <c r="O67">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P67">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q67">
-        <v>2.75</v>
+        <v>2.57</v>
       </c>
       <c r="R67">
         <v>2.05</v>
@@ -11251,7 +11251,7 @@
         <v>2.82</v>
       </c>
       <c r="U67">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="V67">
         <v>1.4</v>
@@ -11269,10 +11269,10 @@
         <v>3.32</v>
       </c>
       <c r="AA67">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AB67">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AC67">
         <v>3.5</v>
@@ -11393,31 +11393,31 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="O68">
         <v>3</v>
       </c>
       <c r="P68">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="Q68">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="R68">
         <v>1.95</v>
       </c>
       <c r="S68">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T68">
         <v>2.4</v>
       </c>
       <c r="U68">
-        <v>3.1</v>
+        <v>3.33</v>
       </c>
       <c r="V68">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W68">
         <v>1.06</v>
@@ -11435,16 +11435,16 @@
         <v>2.31</v>
       </c>
       <c r="AB68">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC68">
         <v>4.15</v>
       </c>
       <c r="AD68">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE68">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF68">
         <v>1.94</v>
@@ -11556,19 +11556,19 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="O69">
-        <v>3.88</v>
+        <v>3.7</v>
       </c>
       <c r="P69">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q69">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="R69">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="S69">
         <v>1.3</v>
@@ -11598,10 +11598,10 @@
         <v>1.67</v>
       </c>
       <c r="AB69">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AC69">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AD69">
         <v>1.4</v>
@@ -11610,10 +11610,10 @@
         <v>1.13</v>
       </c>
       <c r="AF69">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG69">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK69">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11722,10 +11722,10 @@
         <v>1.44</v>
       </c>
       <c r="O70">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="P70">
-        <v>6</v>
+        <v>4.85</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -11921,10 +11921,10 @@
         <v>5.6</v>
       </c>
       <c r="AA71">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AB71">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="AC71">
         <v>2.12</v>
@@ -12736,7 +12736,7 @@
         <v>3.8</v>
       </c>
       <c r="AA76">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB76">
         <v>1.92</v>
@@ -12767,7 +12767,7 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK76">
         <v>1.92</v>
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="O77">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="P77">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="Q77">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R77">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S77">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T77">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U77">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V77">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W77">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X77">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z77">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA77">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB77">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC77">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD77">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF77">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG77">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK77">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13050,10 +13050,10 @@
         <v>1.4</v>
       </c>
       <c r="W78">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X78">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y78">
         <v>1.28</v>
@@ -13077,10 +13077,10 @@
         <v>1.11</v>
       </c>
       <c r="AF78">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG78">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13225,13 +13225,13 @@
         <v>3.6</v>
       </c>
       <c r="AA79">
+        <v>1.87</v>
+      </c>
+      <c r="AB79">
         <v>1.9</v>
       </c>
-      <c r="AB79">
-        <v>1.84</v>
-      </c>
       <c r="AC79">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="AD79">
         <v>1.3</v>
@@ -13352,7 +13352,7 @@
         <v>2.2</v>
       </c>
       <c r="O80">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P80">
         <v>2.7</v>
@@ -13512,19 +13512,19 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="O81">
         <v>3.4</v>
       </c>
       <c r="P81">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="Q81">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="R81">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="S81">
         <v>1.29</v>
@@ -13545,19 +13545,19 @@
         <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z81">
-        <v>4.33</v>
+        <v>4.27</v>
       </c>
       <c r="AA81">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AB81">
         <v>2.22</v>
       </c>
       <c r="AC81">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="AD81">
         <v>1.43</v>
@@ -13684,10 +13684,10 @@
         <v>2.85</v>
       </c>
       <c r="Q82">
-        <v>2.8</v>
+        <v>2.57</v>
       </c>
       <c r="R82">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="S82">
         <v>1.3</v>
@@ -13714,10 +13714,10 @@
         <v>4.33</v>
       </c>
       <c r="AA82">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AB82">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AC82">
         <v>2.52</v>
@@ -13729,7 +13729,7 @@
         <v>1.13</v>
       </c>
       <c r="AF82">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG82">
         <v>2.3</v>
@@ -13748,7 +13748,7 @@
         <v>1.25</v>
       </c>
       <c r="AK82">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="O83">
         <v>3.1</v>
       </c>
       <c r="P83">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W83">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG83">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK83">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14034,10 +14034,10 @@
         <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Z84">
-        <v>6.2</v>
+        <v>7.5</v>
       </c>
       <c r="AA84">
         <v>1.36</v>
@@ -14046,16 +14046,16 @@
         <v>3.2</v>
       </c>
       <c r="AC84">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AD84">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AE84">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AF84">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AG84">
         <v>3</v>
@@ -14221,7 +14221,7 @@
         <v>1.73</v>
       </c>
       <c r="AG85">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>1.12</v>
       </c>
       <c r="AF86">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AG86">
         <v>2.32</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>3</v>
+        <v>1.55</v>
       </c>
       <c r="O88">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="P88">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="Q88">
-        <v>3.25</v>
+        <v>2.05</v>
       </c>
       <c r="R88">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="S88">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="T88">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="U88">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="V88">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="W88">
+        <v>1.11</v>
+      </c>
+      <c r="X88">
+        <v>1.03</v>
+      </c>
+      <c r="Y88">
+        <v>1.19</v>
+      </c>
+      <c r="Z88">
+        <v>4.02</v>
+      </c>
+      <c r="AA88">
+        <v>1.75</v>
+      </c>
+      <c r="AB88">
+        <v>2.08</v>
+      </c>
+      <c r="AC88">
+        <v>2.83</v>
+      </c>
+      <c r="AD88">
+        <v>1.42</v>
+      </c>
+      <c r="AE88">
         <v>1.1</v>
       </c>
-      <c r="X88">
-        <v>1.01</v>
-      </c>
-      <c r="Y88">
-        <v>1.24</v>
-      </c>
-      <c r="Z88">
-        <v>3.34</v>
-      </c>
-      <c r="AA88">
-        <v>1.9</v>
-      </c>
-      <c r="AB88">
-        <v>1.86</v>
-      </c>
-      <c r="AC88">
-        <v>3.14</v>
-      </c>
-      <c r="AD88">
-        <v>1.27</v>
-      </c>
-      <c r="AE88">
-        <v>1.06</v>
-      </c>
       <c r="AF88">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AG88">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AK88">
-        <v>1.32</v>
+        <v>2.26</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="O89">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="P89">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Q89">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="R89">
-        <v>2.17</v>
+        <v>2.74</v>
       </c>
       <c r="S89">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="T89">
-        <v>3.08</v>
+        <v>3.9</v>
       </c>
       <c r="U89">
-        <v>2.53</v>
+        <v>2.2</v>
       </c>
       <c r="V89">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="W89">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X89">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="Z89">
-        <v>4.02</v>
+        <v>5.2</v>
       </c>
       <c r="AA89">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AB89">
-        <v>2.08</v>
+        <v>2.56</v>
       </c>
       <c r="AC89">
-        <v>2.83</v>
+        <v>2.12</v>
       </c>
       <c r="AD89">
-        <v>1.42</v>
+        <v>1.72</v>
       </c>
       <c r="AE89">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AF89">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AG89">
-        <v>1.97</v>
+        <v>2.35</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK89">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="O90">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="P90">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="Q90">
-        <v>1.95</v>
+        <v>3.25</v>
       </c>
       <c r="R90">
-        <v>2.74</v>
+        <v>2.24</v>
       </c>
       <c r="S90">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="T90">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="U90">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="V90">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="W90">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X90">
         <v>1.01</v>
       </c>
       <c r="Y90">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="Z90">
-        <v>5.2</v>
+        <v>3.34</v>
       </c>
       <c r="AA90">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="AB90">
-        <v>2.56</v>
+        <v>1.86</v>
       </c>
       <c r="AC90">
-        <v>2.12</v>
+        <v>3.14</v>
       </c>
       <c r="AD90">
-        <v>1.72</v>
+        <v>1.27</v>
       </c>
       <c r="AE90">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AF90">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="AG90">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK90">
-        <v>2.5</v>
+        <v>1.32</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,65 +15305,65 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.31</v>
+        <v>2.58</v>
       </c>
       <c r="O92">
-        <v>3.54</v>
+        <v>3.46</v>
       </c>
       <c r="P92">
-        <v>2.48</v>
+        <v>2.26</v>
       </c>
       <c r="Q92">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="R92">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="S92">
         <v>1.25</v>
       </c>
       <c r="T92">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="U92">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="V92">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W92">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X92">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y92">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z92">
-        <v>4.98</v>
+        <v>4.8</v>
       </c>
       <c r="AA92">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AB92">
+        <v>2.35</v>
+      </c>
+      <c r="AC92">
+        <v>2.42</v>
+      </c>
+      <c r="AD92">
+        <v>1.47</v>
+      </c>
+      <c r="AE92">
+        <v>1.16</v>
+      </c>
+      <c r="AF92">
+        <v>1.53</v>
+      </c>
+      <c r="AG92">
         <v>2.4</v>
       </c>
-      <c r="AC92">
-        <v>2.34</v>
-      </c>
-      <c r="AD92">
-        <v>1.57</v>
-      </c>
-      <c r="AE92">
-        <v>1.23</v>
-      </c>
-      <c r="AF92">
-        <v>1.44</v>
-      </c>
-      <c r="AG92">
-        <v>2.5</v>
-      </c>
       <c r="AH92" t="inlineStr">
         <is>
           <t>[]</t>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AK92">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,80 +15468,80 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.58</v>
+        <v>2.31</v>
       </c>
       <c r="O93">
-        <v>3.46</v>
+        <v>3.54</v>
       </c>
       <c r="P93">
-        <v>2.26</v>
+        <v>2.48</v>
       </c>
       <c r="Q93">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="R93">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="S93">
         <v>1.25</v>
       </c>
       <c r="T93">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="U93">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="V93">
+        <v>1.6</v>
+      </c>
+      <c r="W93">
+        <v>1.14</v>
+      </c>
+      <c r="X93">
+        <v>1.01</v>
+      </c>
+      <c r="Y93">
+        <v>1.15</v>
+      </c>
+      <c r="Z93">
+        <v>4.98</v>
+      </c>
+      <c r="AA93">
+        <v>1.55</v>
+      </c>
+      <c r="AB93">
+        <v>2.4</v>
+      </c>
+      <c r="AC93">
+        <v>2.34</v>
+      </c>
+      <c r="AD93">
         <v>1.57</v>
       </c>
-      <c r="W93">
-        <v>1.15</v>
-      </c>
-      <c r="X93">
-        <v>1.02</v>
-      </c>
-      <c r="Y93">
-        <v>1.13</v>
-      </c>
-      <c r="Z93">
-        <v>4.8</v>
-      </c>
-      <c r="AA93">
-        <v>1.57</v>
-      </c>
-      <c r="AB93">
-        <v>2.35</v>
-      </c>
-      <c r="AC93">
-        <v>2.42</v>
-      </c>
-      <c r="AD93">
-        <v>1.47</v>
-      </c>
       <c r="AE93">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AF93">
+        <v>1.44</v>
+      </c>
+      <c r="AG93">
+        <v>2.5</v>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ93">
+        <v>1.44</v>
+      </c>
+      <c r="AK93">
         <v>1.53</v>
-      </c>
-      <c r="AG93">
-        <v>2.4</v>
-      </c>
-      <c r="AH93" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI93" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ93">
-        <v>1.29</v>
-      </c>
-      <c r="AK93">
-        <v>1.35</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -16301,10 +16301,10 @@
         <v>1.39</v>
       </c>
       <c r="T98">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="U98">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="V98">
         <v>1.42</v>
@@ -16316,10 +16316,10 @@
         <v>1.03</v>
       </c>
       <c r="Y98">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z98">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="AA98">
         <v>1.95</v>
@@ -16328,13 +16328,13 @@
         <v>1.93</v>
       </c>
       <c r="AC98">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="AD98">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE98">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF98">
         <v>1.7</v>
@@ -16446,43 +16446,43 @@
         </is>
       </c>
       <c r="N99">
-        <v>3.14</v>
+        <v>3.03</v>
       </c>
       <c r="O99">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="P99">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="Q99">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="R99">
         <v>2.2</v>
       </c>
       <c r="S99">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T99">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="U99">
-        <v>2.44</v>
+        <v>2.57</v>
       </c>
       <c r="V99">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W99">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X99">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y99">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Z99">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="AA99">
         <v>1.8</v>
@@ -16491,10 +16491,10 @@
         <v>2</v>
       </c>
       <c r="AC99">
-        <v>2.66</v>
+        <v>2.83</v>
       </c>
       <c r="AD99">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE99">
         <v>1.1</v>
@@ -16516,7 +16516,7 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK99">
         <v>1.33</v>
@@ -16609,7 +16609,7 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="O100">
         <v>3.2</v>
@@ -17596,55 +17596,55 @@
         <v>0</v>
       </c>
       <c r="Q106">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R106">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S106">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T106">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U106">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="V106">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W106">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X106">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y106">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z106">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AA106">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AB106">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AC106">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD106">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE106">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF106">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG106">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK106">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -18097,13 +18097,13 @@
         <v>2.25</v>
       </c>
       <c r="U109">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="V109">
         <v>1.22</v>
       </c>
       <c r="W109">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X109">
         <v>1.14</v>

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="O2">
         <v>3.25</v>
       </c>
       <c r="P2">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="Q2">
         <v>2.8</v>
@@ -656,7 +656,7 @@
         <v>3</v>
       </c>
       <c r="U2">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="V2">
         <v>1.4</v>
@@ -3623,7 +3623,7 @@
         <v>1.26</v>
       </c>
       <c r="AF20">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AG20">
         <v>2.69</v>
@@ -4067,55 +4067,55 @@
         <v>2.73</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4912,10 +4912,10 @@
         <v>0</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC28">
         <v>0</v>
@@ -6071,7 +6071,7 @@
         <v>1.8</v>
       </c>
       <c r="AG35">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="O39">
-        <v>4.6</v>
+        <v>4.35</v>
       </c>
       <c r="P39">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="Q39">
         <v>5.65</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -8501,7 +8501,7 @@
         <v>1.66</v>
       </c>
       <c r="AB50">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AC50">
         <v>2.52</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9476,10 +9476,10 @@
         <v>0</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC56">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
+        <v>1.73</v>
+      </c>
+      <c r="O67">
+        <v>3.7</v>
+      </c>
+      <c r="P67">
+        <v>3.9</v>
+      </c>
+      <c r="Q67">
+        <v>2.25</v>
+      </c>
+      <c r="R67">
+        <v>2.3</v>
+      </c>
+      <c r="S67">
+        <v>1.3</v>
+      </c>
+      <c r="T67">
+        <v>3.3</v>
+      </c>
+      <c r="U67">
+        <v>2.52</v>
+      </c>
+      <c r="V67">
+        <v>1.51</v>
+      </c>
+      <c r="W67">
+        <v>1.08</v>
+      </c>
+      <c r="X67">
+        <v>1.03</v>
+      </c>
+      <c r="Y67">
+        <v>1.2</v>
+      </c>
+      <c r="Z67">
+        <v>4.37</v>
+      </c>
+      <c r="AA67">
+        <v>1.67</v>
+      </c>
+      <c r="AB67">
         <v>2.15</v>
       </c>
-      <c r="O67">
-        <v>3.3</v>
-      </c>
-      <c r="P67">
-        <v>3.25</v>
-      </c>
-      <c r="Q67">
-        <v>2.57</v>
-      </c>
-      <c r="R67">
-        <v>2.05</v>
-      </c>
-      <c r="S67">
-        <v>1.36</v>
-      </c>
-      <c r="T67">
-        <v>2.82</v>
-      </c>
-      <c r="U67">
-        <v>2.8</v>
-      </c>
-      <c r="V67">
+      <c r="AC67">
+        <v>2.7</v>
+      </c>
+      <c r="AD67">
         <v>1.4</v>
       </c>
-      <c r="W67">
-        <v>1.05</v>
-      </c>
-      <c r="X67">
-        <v>1.01</v>
-      </c>
-      <c r="Y67">
-        <v>1.28</v>
-      </c>
-      <c r="Z67">
-        <v>3.32</v>
-      </c>
-      <c r="AA67">
-        <v>1.97</v>
-      </c>
-      <c r="AB67">
-        <v>1.72</v>
-      </c>
-      <c r="AC67">
-        <v>3.5</v>
-      </c>
-      <c r="AD67">
-        <v>1.22</v>
-      </c>
       <c r="AE67">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AF67">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AG67">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AK67">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="O69">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="P69">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="Q69">
-        <v>2.25</v>
+        <v>2.57</v>
       </c>
       <c r="R69">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="S69">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T69">
-        <v>3.3</v>
+        <v>2.82</v>
       </c>
       <c r="U69">
-        <v>2.52</v>
+        <v>2.8</v>
       </c>
       <c r="V69">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="W69">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X69">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y69">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="Z69">
-        <v>4.37</v>
+        <v>3.32</v>
       </c>
       <c r="AA69">
-        <v>1.67</v>
+        <v>1.97</v>
       </c>
       <c r="AB69">
-        <v>2.15</v>
+        <v>1.72</v>
       </c>
       <c r="AC69">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AD69">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AE69">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AF69">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AG69">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AK69">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11725,7 +11725,7 @@
         <v>4.4</v>
       </c>
       <c r="P70">
-        <v>4.85</v>
+        <v>5.8</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -11758,10 +11758,10 @@
         <v>0</v>
       </c>
       <c r="AA70">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AB70">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AC70">
         <v>0</v>
@@ -11912,7 +11912,7 @@
         <v>1.14</v>
       </c>
       <c r="X71">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y71">
         <v>1.08</v>
@@ -11927,7 +11927,7 @@
         <v>2.88</v>
       </c>
       <c r="AC71">
-        <v>2.12</v>
+        <v>2.01</v>
       </c>
       <c r="AD71">
         <v>1.72</v>
@@ -12866,7 +12866,7 @@
         <v>3.1</v>
       </c>
       <c r="P77">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="Q77">
         <v>2.77</v>
@@ -13237,7 +13237,7 @@
         <v>1.3</v>
       </c>
       <c r="AE79">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF79">
         <v>1.75</v>
@@ -13877,10 +13877,10 @@
         <v>2.83</v>
       </c>
       <c r="AA83">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB83">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AC83">
         <v>3.75</v>
@@ -14203,10 +14203,10 @@
         <v>3.08</v>
       </c>
       <c r="AA85">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB85">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC85">
         <v>3.28</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>4</v>
+        <v>1.55</v>
       </c>
       <c r="O87">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P87">
-        <v>1.75</v>
+        <v>5</v>
       </c>
       <c r="Q87">
-        <v>4.68</v>
+        <v>2.05</v>
       </c>
       <c r="R87">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="S87">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T87">
-        <v>3.22</v>
+        <v>3.08</v>
       </c>
       <c r="U87">
-        <v>2.38</v>
+        <v>2.53</v>
       </c>
       <c r="V87">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W87">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X87">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y87">
         <v>1.19</v>
       </c>
       <c r="Z87">
-        <v>3.75</v>
+        <v>4.02</v>
       </c>
       <c r="AA87">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB87">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AC87">
-        <v>2.69</v>
+        <v>2.83</v>
       </c>
       <c r="AD87">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AE87">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF87">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AG87">
-        <v>2.09</v>
+        <v>1.97</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AK87">
-        <v>1.21</v>
+        <v>2.26</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,80 +14653,80 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.55</v>
+        <v>3</v>
       </c>
       <c r="O88">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="P88">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="Q88">
-        <v>2.05</v>
+        <v>3.25</v>
       </c>
       <c r="R88">
-        <v>2.17</v>
+        <v>2.24</v>
       </c>
       <c r="S88">
+        <v>1.35</v>
+      </c>
+      <c r="T88">
+        <v>3</v>
+      </c>
+      <c r="U88">
+        <v>2.62</v>
+      </c>
+      <c r="V88">
+        <v>1.4</v>
+      </c>
+      <c r="W88">
+        <v>1.1</v>
+      </c>
+      <c r="X88">
+        <v>1.01</v>
+      </c>
+      <c r="Y88">
+        <v>1.24</v>
+      </c>
+      <c r="Z88">
+        <v>3.34</v>
+      </c>
+      <c r="AA88">
+        <v>1.9</v>
+      </c>
+      <c r="AB88">
+        <v>1.86</v>
+      </c>
+      <c r="AC88">
+        <v>3.14</v>
+      </c>
+      <c r="AD88">
+        <v>1.27</v>
+      </c>
+      <c r="AE88">
+        <v>1.06</v>
+      </c>
+      <c r="AF88">
+        <v>1.69</v>
+      </c>
+      <c r="AG88">
+        <v>2.1</v>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ88">
+        <v>1.28</v>
+      </c>
+      <c r="AK88">
         <v>1.32</v>
-      </c>
-      <c r="T88">
-        <v>3.08</v>
-      </c>
-      <c r="U88">
-        <v>2.53</v>
-      </c>
-      <c r="V88">
-        <v>1.47</v>
-      </c>
-      <c r="W88">
-        <v>1.11</v>
-      </c>
-      <c r="X88">
-        <v>1.03</v>
-      </c>
-      <c r="Y88">
-        <v>1.19</v>
-      </c>
-      <c r="Z88">
-        <v>4.02</v>
-      </c>
-      <c r="AA88">
-        <v>1.75</v>
-      </c>
-      <c r="AB88">
-        <v>2.08</v>
-      </c>
-      <c r="AC88">
-        <v>2.83</v>
-      </c>
-      <c r="AD88">
-        <v>1.42</v>
-      </c>
-      <c r="AE88">
-        <v>1.1</v>
-      </c>
-      <c r="AF88">
-        <v>1.75</v>
-      </c>
-      <c r="AG88">
-        <v>1.97</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI88" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ88">
-        <v>1.19</v>
-      </c>
-      <c r="AK88">
-        <v>2.26</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
+        <v>4</v>
+      </c>
+      <c r="O89">
+        <v>3.7</v>
+      </c>
+      <c r="P89">
+        <v>1.75</v>
+      </c>
+      <c r="Q89">
+        <v>4.68</v>
+      </c>
+      <c r="R89">
+        <v>2.26</v>
+      </c>
+      <c r="S89">
+        <v>1.28</v>
+      </c>
+      <c r="T89">
+        <v>3.22</v>
+      </c>
+      <c r="U89">
+        <v>2.38</v>
+      </c>
+      <c r="V89">
         <v>1.5</v>
       </c>
-      <c r="O89">
-        <v>4.2</v>
-      </c>
-      <c r="P89">
-        <v>4.8</v>
-      </c>
-      <c r="Q89">
-        <v>1.95</v>
-      </c>
-      <c r="R89">
-        <v>2.74</v>
-      </c>
-      <c r="S89">
-        <v>1.2</v>
-      </c>
-      <c r="T89">
-        <v>3.9</v>
-      </c>
-      <c r="U89">
-        <v>2.2</v>
-      </c>
-      <c r="V89">
-        <v>1.6</v>
-      </c>
       <c r="W89">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X89">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y89">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="Z89">
-        <v>5.2</v>
+        <v>3.75</v>
       </c>
       <c r="AA89">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="AB89">
-        <v>2.56</v>
+        <v>2.05</v>
       </c>
       <c r="AC89">
-        <v>2.12</v>
+        <v>2.69</v>
       </c>
       <c r="AD89">
-        <v>1.72</v>
+        <v>1.36</v>
       </c>
       <c r="AE89">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AF89">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AG89">
-        <v>2.35</v>
+        <v>2.09</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK89">
-        <v>2.5</v>
+        <v>1.21</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="O90">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="P90">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="Q90">
-        <v>3.25</v>
+        <v>1.95</v>
       </c>
       <c r="R90">
-        <v>2.24</v>
+        <v>2.74</v>
       </c>
       <c r="S90">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="T90">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="U90">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="V90">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="W90">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X90">
         <v>1.01</v>
       </c>
       <c r="Y90">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="Z90">
-        <v>3.34</v>
+        <v>5.2</v>
       </c>
       <c r="AA90">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="AB90">
-        <v>1.86</v>
+        <v>2.56</v>
       </c>
       <c r="AC90">
-        <v>3.14</v>
+        <v>2.12</v>
       </c>
       <c r="AD90">
-        <v>1.27</v>
+        <v>1.72</v>
       </c>
       <c r="AE90">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="AF90">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="AG90">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK90">
-        <v>1.32</v>
+        <v>2.5</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         </is>
       </c>
       <c r="N99">
-        <v>3.03</v>
+        <v>2.86</v>
       </c>
       <c r="O99">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="P99">
         <v>2.15</v>
@@ -16467,10 +16467,10 @@
         <v>2.82</v>
       </c>
       <c r="U99">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="V99">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W99">
         <v>1.07</v>
@@ -16479,10 +16479,10 @@
         <v>1.03</v>
       </c>
       <c r="Y99">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z99">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AA99">
         <v>1.8</v>
@@ -16491,16 +16491,16 @@
         <v>2</v>
       </c>
       <c r="AC99">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AD99">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE99">
         <v>1.1</v>
       </c>
       <c r="AF99">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG99">
         <v>2.25</v>
@@ -16519,7 +16519,7 @@
         <v>1.29</v>
       </c>
       <c r="AK99">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="O102">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q102">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="R102">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="S102">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T102">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U102">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="V102">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W102">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X102">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y102">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z102">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="AA102">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB102">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="AC102">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD102">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE102">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF102">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AG102">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK102">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.24</v>
+        <v>2.33</v>
       </c>
       <c r="O105">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="P105">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="Q105">
         <v>3.09</v>

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O3">
         <v>3.7</v>
@@ -852,7 +852,7 @@
         <v>1.17</v>
       </c>
       <c r="AF3">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG3">
         <v>2.3</v>
@@ -1302,28 +1302,28 @@
         <v>2.12</v>
       </c>
       <c r="S6">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T6">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="U6">
         <v>2.5</v>
       </c>
       <c r="V6">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W6">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X6">
         <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Z6">
-        <v>3.9</v>
+        <v>3.71</v>
       </c>
       <c r="AA6">
         <v>1.79</v>
@@ -1332,16 +1332,16 @@
         <v>1.93</v>
       </c>
       <c r="AC6">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="AD6">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE6">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF6">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG6">
         <v>1.95</v>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK6">
         <v>2.1</v>
@@ -3578,10 +3578,10 @@
         <v>3.85</v>
       </c>
       <c r="Q20">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="R20">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="S20">
         <v>1.16</v>
@@ -3611,7 +3611,7 @@
         <v>1.38</v>
       </c>
       <c r="AB20">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AC20">
         <v>2.01</v>
@@ -3898,7 +3898,7 @@
         <v>1.12</v>
       </c>
       <c r="O22">
-        <v>10.7</v>
+        <v>8</v>
       </c>
       <c r="P22">
         <v>15</v>
@@ -4109,7 +4109,7 @@
         <v>1.17</v>
       </c>
       <c r="AE23">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF23">
         <v>1.85</v>
@@ -4882,55 +4882,55 @@
         <v>0</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA28">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AB28">
+        <v>1.71</v>
+      </c>
+      <c r="AC28">
+        <v>3.42</v>
+      </c>
+      <c r="AD28">
+        <v>1.23</v>
+      </c>
+      <c r="AE28">
+        <v>1.05</v>
+      </c>
+      <c r="AF28">
         <v>1.75</v>
       </c>
-      <c r="AC28">
-        <v>0</v>
-      </c>
-      <c r="AD28">
-        <v>0</v>
-      </c>
-      <c r="AE28">
-        <v>0</v>
-      </c>
-      <c r="AF28">
-        <v>0</v>
-      </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5362,10 +5362,10 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="O31">
-        <v>3.62</v>
+        <v>3.75</v>
       </c>
       <c r="P31">
         <v>2.49</v>
@@ -5860,55 +5860,55 @@
         <v>3.15</v>
       </c>
       <c r="Q34">
-        <v>2.77</v>
+        <v>2.55</v>
       </c>
       <c r="R34">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="S34">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T34">
-        <v>2.72</v>
+        <v>2.23</v>
       </c>
       <c r="U34">
-        <v>2.76</v>
+        <v>2.29</v>
       </c>
       <c r="V34">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="W34">
         <v>1.04</v>
       </c>
       <c r="X34">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z34">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="AA34">
         <v>2</v>
       </c>
       <c r="AB34">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC34">
-        <v>3.62</v>
+        <v>2.75</v>
       </c>
       <c r="AD34">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AE34">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF34">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AG34">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AK34">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6293,12 +6293,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="O37">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P37">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q37">
-        <v>4.4</v>
+        <v>1.83</v>
       </c>
       <c r="R37">
-        <v>2.14</v>
+        <v>2.44</v>
       </c>
       <c r="S37">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="T37">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="U37">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="V37">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="W37">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X37">
         <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="Z37">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="AA37">
-        <v>1.8</v>
+        <v>1.42</v>
       </c>
       <c r="AB37">
-        <v>2</v>
+        <v>2.49</v>
       </c>
       <c r="AC37">
-        <v>2.83</v>
+        <v>2.1</v>
       </c>
       <c r="AD37">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="AE37">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="AF37">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG37">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AK37">
-        <v>1.2</v>
+        <v>2.75</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-10-16 12:30:00</t>
+          <t>2026-10-16 12:00:00</t>
         </is>
       </c>
     </row>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.75</v>
+        <v>3.84</v>
       </c>
       <c r="O38">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="P38">
-        <v>3.9</v>
+        <v>1.8</v>
       </c>
       <c r="Q38">
-        <v>2.1</v>
+        <v>4.4</v>
       </c>
       <c r="R38">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="S38">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="T38">
-        <v>3.42</v>
+        <v>3.1</v>
       </c>
       <c r="U38">
-        <v>2.19</v>
+        <v>2.63</v>
       </c>
       <c r="V38">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="W38">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="Z38">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA38">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AB38">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AC38">
-        <v>2.28</v>
+        <v>2.83</v>
       </c>
       <c r="AD38">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AE38">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AF38">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AG38">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AK38">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6619,12 +6619,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>5</v>
+        <v>1.75</v>
       </c>
       <c r="O39">
-        <v>4.35</v>
+        <v>3.5</v>
       </c>
       <c r="P39">
-        <v>1.45</v>
+        <v>3.9</v>
       </c>
       <c r="Q39">
-        <v>5.65</v>
+        <v>2.1</v>
       </c>
       <c r="R39">
-        <v>2.74</v>
+        <v>2.4</v>
       </c>
       <c r="S39">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="T39">
-        <v>4</v>
+        <v>3.42</v>
       </c>
       <c r="U39">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="V39">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="W39">
+        <v>1.13</v>
+      </c>
+      <c r="X39">
+        <v>1.03</v>
+      </c>
+      <c r="Y39">
+        <v>1.13</v>
+      </c>
+      <c r="Z39">
+        <v>4.6</v>
+      </c>
+      <c r="AA39">
+        <v>1.53</v>
+      </c>
+      <c r="AB39">
+        <v>2.29</v>
+      </c>
+      <c r="AC39">
+        <v>2.28</v>
+      </c>
+      <c r="AD39">
+        <v>1.5</v>
+      </c>
+      <c r="AE39">
         <v>1.17</v>
       </c>
-      <c r="X39">
-        <v>1.02</v>
-      </c>
-      <c r="Y39">
-        <v>1.12</v>
-      </c>
-      <c r="Z39">
-        <v>5.72</v>
-      </c>
-      <c r="AA39">
-        <v>1.41</v>
-      </c>
-      <c r="AB39">
-        <v>2.78</v>
-      </c>
-      <c r="AC39">
-        <v>2.11</v>
-      </c>
-      <c r="AD39">
-        <v>1.7</v>
-      </c>
-      <c r="AE39">
-        <v>1.27</v>
-      </c>
       <c r="AF39">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG39">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AK39">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>2026-10-16 12:45:00</t>
+          <t>2026-10-16 12:30:00</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O40">
-        <v>3.54</v>
+        <v>4.35</v>
       </c>
       <c r="P40">
-        <v>3.09</v>
+        <v>1.45</v>
       </c>
       <c r="Q40">
-        <v>2.54</v>
+        <v>5.65</v>
       </c>
       <c r="R40">
-        <v>2.38</v>
+        <v>2.74</v>
       </c>
       <c r="S40">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T40">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U40">
-        <v>2.37</v>
+        <v>2.13</v>
       </c>
       <c r="V40">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="W40">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X40">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z40">
-        <v>4.67</v>
+        <v>5.72</v>
       </c>
       <c r="AA40">
-        <v>1.61</v>
+        <v>1.41</v>
       </c>
       <c r="AB40">
-        <v>2.25</v>
+        <v>2.78</v>
       </c>
       <c r="AC40">
-        <v>2.49</v>
+        <v>2.11</v>
       </c>
       <c r="AD40">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AE40">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AF40">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG40">
-        <v>2.34</v>
+        <v>2.27</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AK40">
-        <v>1.67</v>
+        <v>1.1</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>2026-10-16 13:00:00</t>
+          <t>2026-10-16 12:45:00</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="O41">
-        <v>3.04</v>
+        <v>3.54</v>
       </c>
       <c r="P41">
-        <v>3.12</v>
+        <v>3.09</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="O42">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="P42">
-        <v>2.69</v>
+        <v>3.12</v>
       </c>
       <c r="Q42">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="R42">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="S42">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T42">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="U42">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="V42">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W42">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X42">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y42">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z42">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AA42">
-        <v>2.09</v>
+        <v>2.35</v>
       </c>
       <c r="AB42">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AC42">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="AD42">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE42">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF42">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG42">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK42">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7276,22 +7276,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G44">
@@ -7602,22 +7602,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O45">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P45">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="Q45">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="R45">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="S45">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T45">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U45">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V45">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="W45">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X45">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y45">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z45">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA45">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AB45">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AC45">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD45">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE45">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AF45">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG45">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK45">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>5.6</v>
+        <v>2.33</v>
       </c>
       <c r="O46">
-        <v>4.15</v>
+        <v>3.65</v>
       </c>
       <c r="P46">
-        <v>1.42</v>
+        <v>2.61</v>
       </c>
       <c r="Q46">
-        <v>7.5</v>
+        <v>2.51</v>
       </c>
       <c r="R46">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="S46">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T46">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U46">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="V46">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="W46">
         <v>1.13</v>
       </c>
       <c r="X46">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="Z46">
-        <v>4.33</v>
+        <v>5.72</v>
       </c>
       <c r="AA46">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AB46">
-        <v>2.24</v>
+        <v>2.66</v>
       </c>
       <c r="AC46">
-        <v>2.59</v>
+        <v>2.09</v>
       </c>
       <c r="AD46">
-        <v>1.47</v>
+        <v>1.64</v>
       </c>
       <c r="AE46">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AF46">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="AG46">
-        <v>1.85</v>
+        <v>2.7</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AK46">
-        <v>1.08</v>
+        <v>1.71</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q47">
-        <v>1.83</v>
+        <v>7</v>
       </c>
       <c r="R47">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="S47">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T47">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U47">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="V47">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="W47">
+        <v>1.13</v>
+      </c>
+      <c r="X47">
+        <v>1.03</v>
+      </c>
+      <c r="Y47">
+        <v>1.19</v>
+      </c>
+      <c r="Z47">
+        <v>4.33</v>
+      </c>
+      <c r="AA47">
+        <v>1.52</v>
+      </c>
+      <c r="AB47">
+        <v>2.24</v>
+      </c>
+      <c r="AC47">
+        <v>2.59</v>
+      </c>
+      <c r="AD47">
+        <v>1.47</v>
+      </c>
+      <c r="AE47">
         <v>1.17</v>
       </c>
-      <c r="X47">
-        <v>1.02</v>
-      </c>
-      <c r="Y47">
-        <v>1.1</v>
-      </c>
-      <c r="Z47">
-        <v>5.2</v>
-      </c>
-      <c r="AA47">
-        <v>1.42</v>
-      </c>
-      <c r="AB47">
-        <v>2.49</v>
-      </c>
-      <c r="AC47">
-        <v>2.1</v>
-      </c>
-      <c r="AD47">
-        <v>1.63</v>
-      </c>
-      <c r="AE47">
-        <v>1.23</v>
-      </c>
       <c r="AF47">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AG47">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AK47">
-        <v>2.75</v>
+        <v>1.09</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8163,7 +8163,7 @@
         <v>1.08</v>
       </c>
       <c r="X48">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y48">
         <v>1.15</v>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK48">
         <v>1.67</v>
@@ -8326,7 +8326,7 @@
         <v>1.1</v>
       </c>
       <c r="X49">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y49">
         <v>1.18</v>
@@ -8350,7 +8350,7 @@
         <v>1.12</v>
       </c>
       <c r="AF49">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG49">
         <v>2.05</v>
@@ -8474,7 +8474,7 @@
         <v>2.19</v>
       </c>
       <c r="S50">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T50">
         <v>3.3</v>
@@ -8486,10 +8486,10 @@
         <v>1.51</v>
       </c>
       <c r="W50">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y50">
         <v>1.15</v>
@@ -8948,10 +8948,10 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="O53">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="P53">
         <v>4.6</v>
@@ -9150,7 +9150,7 @@
         <v>5.65</v>
       </c>
       <c r="AA54">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB54">
         <v>2.88</v>
@@ -9286,7 +9286,7 @@
         <v>3.36</v>
       </c>
       <c r="R55">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="S55">
         <v>1.14</v>
@@ -9298,7 +9298,7 @@
         <v>1.91</v>
       </c>
       <c r="V55">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="W55">
         <v>1.18</v>
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="O56">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="P56">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z56">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA56">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AB56">
         <v>1.8</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK56">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9769,7 +9769,7 @@
         <v>3.6</v>
       </c>
       <c r="P58">
-        <v>3.36</v>
+        <v>3.32</v>
       </c>
       <c r="Q58">
         <v>2.42</v>
@@ -9778,28 +9778,28 @@
         <v>2.38</v>
       </c>
       <c r="S58">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T58">
-        <v>3.08</v>
+        <v>3.23</v>
       </c>
       <c r="U58">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="V58">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W58">
         <v>1.11</v>
       </c>
       <c r="X58">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y58">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z58">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="AA58">
         <v>1.75</v>
@@ -9817,10 +9817,10 @@
         <v>1.17</v>
       </c>
       <c r="AF58">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AG58">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9926,19 +9926,19 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O59">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P59">
+        <v>2.75</v>
+      </c>
+      <c r="Q59">
         <v>2.8</v>
       </c>
-      <c r="Q59">
-        <v>2.7</v>
-      </c>
       <c r="R59">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="S59">
         <v>1.22</v>
@@ -9959,10 +9959,10 @@
         <v>1.01</v>
       </c>
       <c r="Y59">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="Z59">
-        <v>4.79</v>
+        <v>4.76</v>
       </c>
       <c r="AA59">
         <v>1.51</v>
@@ -9971,13 +9971,13 @@
         <v>2.26</v>
       </c>
       <c r="AC59">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="AD59">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AE59">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AF59">
         <v>1.46</v>
@@ -9999,7 +9999,7 @@
         <v>1.22</v>
       </c>
       <c r="AK59">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10131,7 +10131,7 @@
         <v>1.5</v>
       </c>
       <c r="AB60">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AC60">
         <v>2.34</v>
@@ -10252,7 +10252,7 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.77</v>
+        <v>2.6</v>
       </c>
       <c r="O61">
         <v>3.5</v>
@@ -10291,19 +10291,19 @@
         <v>3.95</v>
       </c>
       <c r="AA61">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AB61">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC61">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AD61">
         <v>1.39</v>
       </c>
       <c r="AE61">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF61">
         <v>1.6</v>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AK61">
         <v>1.4</v>
@@ -10424,7 +10424,7 @@
         <v>7</v>
       </c>
       <c r="Q62">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="R62">
         <v>2.75</v>
@@ -10433,7 +10433,7 @@
         <v>1.2</v>
       </c>
       <c r="T62">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="U62">
         <v>2.05</v>
@@ -10460,7 +10460,7 @@
         <v>2.88</v>
       </c>
       <c r="AC62">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="AD62">
         <v>1.75</v>
@@ -10469,7 +10469,7 @@
         <v>1.27</v>
       </c>
       <c r="AF62">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG62">
         <v>2.03</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="O64">
         <v>3.6</v>
       </c>
       <c r="P64">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="Q64">
         <v>2.67</v>
@@ -10811,7 +10811,7 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK64">
         <v>1.57</v>
@@ -10904,10 +10904,10 @@
         </is>
       </c>
       <c r="N65">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="O65">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P65">
         <v>3.2</v>
@@ -10919,13 +10919,13 @@
         <v>2.15</v>
       </c>
       <c r="S65">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="T65">
         <v>3.1</v>
       </c>
       <c r="U65">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V65">
         <v>1.44</v>
@@ -10974,7 +10974,7 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK65">
         <v>1.7</v>
@@ -11076,10 +11076,10 @@
         <v>2.37</v>
       </c>
       <c r="Q66">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="R66">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="S66">
         <v>1.4</v>
@@ -11121,10 +11121,10 @@
         <v>1.06</v>
       </c>
       <c r="AF66">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG66">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
         <v>2.25</v>
       </c>
       <c r="R67">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S67">
         <v>1.3</v>
@@ -11260,7 +11260,7 @@
         <v>1.08</v>
       </c>
       <c r="X67">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y67">
         <v>1.2</v>
@@ -11300,7 +11300,7 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK67">
         <v>1.95</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.54</v>
+        <v>2.15</v>
       </c>
       <c r="O68">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="P68">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="Q68">
-        <v>3.4</v>
+        <v>2.57</v>
       </c>
       <c r="R68">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="S68">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="T68">
-        <v>2.4</v>
+        <v>2.82</v>
       </c>
       <c r="U68">
-        <v>3.33</v>
+        <v>2.8</v>
       </c>
       <c r="V68">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="W68">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X68">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="Z68">
-        <v>2.75</v>
+        <v>3.32</v>
       </c>
       <c r="AA68">
-        <v>2.31</v>
+        <v>1.96</v>
       </c>
       <c r="AB68">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AC68">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="AD68">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE68">
         <v>1.04</v>
       </c>
       <c r="AF68">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AG68">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AK68">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.15</v>
+        <v>2.57</v>
       </c>
       <c r="O69">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="P69">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="Q69">
-        <v>2.57</v>
+        <v>3.4</v>
       </c>
       <c r="R69">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="S69">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="T69">
-        <v>2.82</v>
+        <v>2.4</v>
       </c>
       <c r="U69">
-        <v>2.8</v>
+        <v>3.33</v>
       </c>
       <c r="V69">
+        <v>1.3</v>
+      </c>
+      <c r="W69">
+        <v>1.06</v>
+      </c>
+      <c r="X69">
+        <v>1.05</v>
+      </c>
+      <c r="Y69">
         <v>1.4</v>
       </c>
-      <c r="W69">
-        <v>1.05</v>
-      </c>
-      <c r="X69">
-        <v>1.01</v>
-      </c>
-      <c r="Y69">
-        <v>1.28</v>
-      </c>
       <c r="Z69">
-        <v>3.32</v>
+        <v>2.75</v>
       </c>
       <c r="AA69">
-        <v>1.97</v>
+        <v>2.31</v>
       </c>
       <c r="AB69">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AC69">
-        <v>3.5</v>
+        <v>4.15</v>
       </c>
       <c r="AD69">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE69">
         <v>1.04</v>
       </c>
       <c r="AF69">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AG69">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AK69">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11758,10 +11758,10 @@
         <v>0</v>
       </c>
       <c r="AA70">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB70">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC70">
         <v>0</v>
@@ -11891,10 +11891,10 @@
         <v>4.5</v>
       </c>
       <c r="Q71">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="R71">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="S71">
         <v>1.22</v>
@@ -11927,7 +11927,7 @@
         <v>2.88</v>
       </c>
       <c r="AC71">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AD71">
         <v>1.72</v>
@@ -12054,10 +12054,10 @@
         <v>1.95</v>
       </c>
       <c r="Q72">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="R72">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S72">
         <v>1.25</v>
@@ -12087,7 +12087,7 @@
         <v>1.53</v>
       </c>
       <c r="AB72">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="AC72">
         <v>2.27</v>
@@ -12118,7 +12118,7 @@
         <v>1.18</v>
       </c>
       <c r="AK72">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>5.66</v>
+        <v>5</v>
       </c>
       <c r="O73">
         <v>4.7</v>
       </c>
       <c r="P73">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="Q73">
         <v>4.18</v>
@@ -12223,7 +12223,7 @@
         <v>2.43</v>
       </c>
       <c r="S73">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="T73">
         <v>4</v>
@@ -12250,7 +12250,7 @@
         <v>1.4</v>
       </c>
       <c r="AB73">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="AC73">
         <v>1.95</v>
@@ -12374,7 +12374,7 @@
         <v>2.05</v>
       </c>
       <c r="O74">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="P74">
         <v>2.7</v>
@@ -12392,7 +12392,7 @@
         <v>4.5</v>
       </c>
       <c r="U74">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="V74">
         <v>1.8</v>
@@ -12410,10 +12410,10 @@
         <v>7.2</v>
       </c>
       <c r="AA74">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AB74">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AC74">
         <v>1.82</v>
@@ -12537,10 +12537,10 @@
         <v>1.68</v>
       </c>
       <c r="O75">
-        <v>4.25</v>
+        <v>3.9</v>
       </c>
       <c r="P75">
-        <v>3.75</v>
+        <v>4.04</v>
       </c>
       <c r="Q75">
         <v>2.03</v>
@@ -12549,7 +12549,7 @@
         <v>2.6</v>
       </c>
       <c r="S75">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="T75">
         <v>4.4</v>
@@ -12866,7 +12866,7 @@
         <v>3.1</v>
       </c>
       <c r="P77">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="Q77">
         <v>2.77</v>
@@ -13192,7 +13192,7 @@
         <v>3.4</v>
       </c>
       <c r="P79">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="Q79">
         <v>4.4</v>
@@ -13512,19 +13512,19 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="O81">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P81">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="Q81">
         <v>2.89</v>
       </c>
       <c r="R81">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="S81">
         <v>1.29</v>
@@ -13545,19 +13545,19 @@
         <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z81">
-        <v>4.27</v>
+        <v>4.4</v>
       </c>
       <c r="AA81">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AB81">
         <v>2.22</v>
       </c>
       <c r="AC81">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="AD81">
         <v>1.43</v>
@@ -13684,10 +13684,10 @@
         <v>2.85</v>
       </c>
       <c r="Q82">
-        <v>2.57</v>
+        <v>2.8</v>
       </c>
       <c r="R82">
-        <v>2.19</v>
+        <v>2.38</v>
       </c>
       <c r="S82">
         <v>1.3</v>
@@ -13729,7 +13729,7 @@
         <v>1.13</v>
       </c>
       <c r="AF82">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG82">
         <v>2.3</v>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK82">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -14001,7 +14001,7 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="O84">
         <v>4</v>
@@ -14010,10 +14010,10 @@
         <v>2.95</v>
       </c>
       <c r="Q84">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="R84">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="S84">
         <v>1.19</v>
@@ -14034,10 +14034,10 @@
         <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z84">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AA84">
         <v>1.36</v>
@@ -14381,7 +14381,7 @@
         <v>1.12</v>
       </c>
       <c r="AF86">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AG86">
         <v>2.32</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.55</v>
+        <v>4</v>
       </c>
       <c r="O87">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P87">
-        <v>5</v>
+        <v>1.75</v>
       </c>
       <c r="Q87">
-        <v>2.05</v>
+        <v>4.68</v>
       </c>
       <c r="R87">
-        <v>2.17</v>
+        <v>2.26</v>
       </c>
       <c r="S87">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="T87">
-        <v>3.08</v>
+        <v>3.22</v>
       </c>
       <c r="U87">
-        <v>2.53</v>
+        <v>2.38</v>
       </c>
       <c r="V87">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W87">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X87">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y87">
         <v>1.19</v>
       </c>
       <c r="Z87">
-        <v>4.02</v>
+        <v>3.75</v>
       </c>
       <c r="AA87">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB87">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AC87">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="AD87">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE87">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF87">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AG87">
-        <v>1.97</v>
+        <v>2.09</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AK87">
-        <v>2.26</v>
+        <v>1.21</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="O88">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="P88">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="Q88">
-        <v>3.25</v>
+        <v>1.95</v>
       </c>
       <c r="R88">
-        <v>2.24</v>
+        <v>2.74</v>
       </c>
       <c r="S88">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="T88">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="U88">
-        <v>2.62</v>
+        <v>2</v>
       </c>
       <c r="V88">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="W88">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X88">
         <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="Z88">
-        <v>3.34</v>
+        <v>5.2</v>
       </c>
       <c r="AA88">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="AB88">
-        <v>1.86</v>
+        <v>2.56</v>
       </c>
       <c r="AC88">
-        <v>3.14</v>
+        <v>2.12</v>
       </c>
       <c r="AD88">
-        <v>1.27</v>
+        <v>1.72</v>
       </c>
       <c r="AE88">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="AF88">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="AG88">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK88">
-        <v>1.32</v>
+        <v>2.5</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O89">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P89">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="Q89">
-        <v>4.68</v>
+        <v>3.25</v>
       </c>
       <c r="R89">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="S89">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="T89">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="U89">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="V89">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W89">
         <v>1.1</v>
       </c>
       <c r="X89">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="Z89">
-        <v>3.75</v>
+        <v>3.34</v>
       </c>
       <c r="AA89">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AB89">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="AC89">
-        <v>2.69</v>
+        <v>3.14</v>
       </c>
       <c r="AD89">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AE89">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF89">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AG89">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AK89">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.5</v>
+        <v>5.6</v>
       </c>
       <c r="O90">
-        <v>4.2</v>
+        <v>4.55</v>
       </c>
       <c r="P90">
-        <v>4.8</v>
+        <v>1.38</v>
       </c>
       <c r="Q90">
-        <v>1.95</v>
+        <v>5.5</v>
       </c>
       <c r="R90">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="S90">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T90">
         <v>3.9</v>
       </c>
       <c r="U90">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="V90">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="W90">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X90">
         <v>1.01</v>
       </c>
       <c r="Y90">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z90">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AA90">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AB90">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="AC90">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AD90">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AE90">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF90">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG90">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="AK90">
-        <v>2.5</v>
+        <v>1.11</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,80 +15142,80 @@
         </is>
       </c>
       <c r="N91">
-        <v>6.32</v>
+        <v>2.77</v>
       </c>
       <c r="O91">
-        <v>4.55</v>
+        <v>3.4</v>
       </c>
       <c r="P91">
-        <v>1.37</v>
+        <v>2.11</v>
       </c>
       <c r="Q91">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="R91">
-        <v>2.7</v>
+        <v>2.24</v>
       </c>
       <c r="S91">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T91">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="U91">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="V91">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="W91">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X91">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y91">
         <v>1.13</v>
       </c>
       <c r="Z91">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="AA91">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="AB91">
-        <v>2.74</v>
+        <v>2.24</v>
       </c>
       <c r="AC91">
-        <v>2.07</v>
+        <v>2.42</v>
       </c>
       <c r="AD91">
-        <v>1.73</v>
+        <v>1.47</v>
       </c>
       <c r="AE91">
+        <v>1.16</v>
+      </c>
+      <c r="AF91">
+        <v>1.53</v>
+      </c>
+      <c r="AG91">
+        <v>2.38</v>
+      </c>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ91">
         <v>1.29</v>
       </c>
-      <c r="AF91">
-        <v>1.55</v>
-      </c>
-      <c r="AG91">
-        <v>2.3</v>
-      </c>
-      <c r="AH91" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI91" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ91">
-        <v>2.8</v>
-      </c>
       <c r="AK91">
-        <v>1.11</v>
+        <v>1.35</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.58</v>
+        <v>2.3</v>
       </c>
       <c r="O92">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="P92">
-        <v>2.26</v>
+        <v>2.55</v>
       </c>
       <c r="Q92">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="R92">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="S92">
         <v>1.25</v>
       </c>
       <c r="T92">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="U92">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="V92">
+        <v>1.6</v>
+      </c>
+      <c r="W92">
+        <v>1.14</v>
+      </c>
+      <c r="X92">
+        <v>1.01</v>
+      </c>
+      <c r="Y92">
+        <v>1.15</v>
+      </c>
+      <c r="Z92">
+        <v>4.98</v>
+      </c>
+      <c r="AA92">
+        <v>1.53</v>
+      </c>
+      <c r="AB92">
+        <v>2.4</v>
+      </c>
+      <c r="AC92">
+        <v>2.34</v>
+      </c>
+      <c r="AD92">
         <v>1.57</v>
       </c>
-      <c r="W92">
-        <v>1.15</v>
-      </c>
-      <c r="X92">
-        <v>1.02</v>
-      </c>
-      <c r="Y92">
-        <v>1.13</v>
-      </c>
-      <c r="Z92">
-        <v>4.8</v>
-      </c>
-      <c r="AA92">
-        <v>1.57</v>
-      </c>
-      <c r="AB92">
-        <v>2.35</v>
-      </c>
-      <c r="AC92">
-        <v>2.42</v>
-      </c>
-      <c r="AD92">
-        <v>1.47</v>
-      </c>
       <c r="AE92">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AF92">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AG92">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AK92">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.31</v>
+        <v>3.15</v>
       </c>
       <c r="O93">
-        <v>3.54</v>
+        <v>3.45</v>
       </c>
       <c r="P93">
-        <v>2.48</v>
+        <v>1.96</v>
       </c>
       <c r="Q93">
+        <v>3.75</v>
+      </c>
+      <c r="R93">
+        <v>2.25</v>
+      </c>
+      <c r="S93">
+        <v>1.31</v>
+      </c>
+      <c r="T93">
+        <v>3.1</v>
+      </c>
+      <c r="U93">
+        <v>2.63</v>
+      </c>
+      <c r="V93">
+        <v>1.44</v>
+      </c>
+      <c r="W93">
+        <v>1.11</v>
+      </c>
+      <c r="X93">
+        <v>1.03</v>
+      </c>
+      <c r="Y93">
+        <v>1.2</v>
+      </c>
+      <c r="Z93">
+        <v>3.7</v>
+      </c>
+      <c r="AA93">
+        <v>1.75</v>
+      </c>
+      <c r="AB93">
+        <v>1.98</v>
+      </c>
+      <c r="AC93">
         <v>2.88</v>
       </c>
-      <c r="R93">
-        <v>2.46</v>
-      </c>
-      <c r="S93">
-        <v>1.25</v>
-      </c>
-      <c r="T93">
-        <v>3.52</v>
-      </c>
-      <c r="U93">
-        <v>2.15</v>
-      </c>
-      <c r="V93">
-        <v>1.6</v>
-      </c>
-      <c r="W93">
-        <v>1.14</v>
-      </c>
-      <c r="X93">
-        <v>1.01</v>
-      </c>
-      <c r="Y93">
-        <v>1.15</v>
-      </c>
-      <c r="Z93">
-        <v>4.98</v>
-      </c>
-      <c r="AA93">
-        <v>1.55</v>
-      </c>
-      <c r="AB93">
-        <v>2.4</v>
-      </c>
-      <c r="AC93">
-        <v>2.34</v>
-      </c>
       <c r="AD93">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="AE93">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="AF93">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AG93">
-        <v>2.5</v>
+        <v>2.07</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AK93">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.8</v>
+        <v>2.99</v>
       </c>
       <c r="O94">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="P94">
+        <v>1.99</v>
+      </c>
+      <c r="Q94">
+        <v>3.6</v>
+      </c>
+      <c r="R94">
         <v>2.21</v>
       </c>
-      <c r="Q94">
-        <v>3.75</v>
-      </c>
-      <c r="R94">
-        <v>2.25</v>
-      </c>
       <c r="S94">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T94">
         <v>3.25</v>
       </c>
       <c r="U94">
-        <v>2.63</v>
+        <v>2.42</v>
       </c>
       <c r="V94">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W94">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X94">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y94">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z94">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
       <c r="AA94">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AB94">
-        <v>1.93</v>
+        <v>2.22</v>
       </c>
       <c r="AC94">
-        <v>2.88</v>
+        <v>2.52</v>
       </c>
       <c r="AD94">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AE94">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF94">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG94">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>1.29</v>
       </c>
       <c r="AK94">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15752,22 +15752,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>3.46</v>
+        <v>2.53</v>
       </c>
       <c r="O95">
-        <v>3.54</v>
+        <v>3.75</v>
       </c>
       <c r="P95">
-        <v>1.87</v>
+        <v>2.6</v>
       </c>
       <c r="Q95">
-        <v>3.6</v>
+        <v>3.02</v>
       </c>
       <c r="R95">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="S95">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T95">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="U95">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V95">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="W95">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X95">
         <v>1.02</v>
       </c>
       <c r="Y95">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z95">
-        <v>4.25</v>
+        <v>4.95</v>
       </c>
       <c r="AA95">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="AB95">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AC95">
-        <v>2.51</v>
+        <v>2.24</v>
       </c>
       <c r="AD95">
-        <v>1.41</v>
+        <v>1.76</v>
       </c>
       <c r="AE95">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AF95">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AG95">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK95">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15910,27 +15910,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.53</v>
+        <v>2.42</v>
       </c>
       <c r="O96">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P96">
-        <v>2.6</v>
+        <v>2.39</v>
       </c>
       <c r="Q96">
         <v>3.02</v>
       </c>
       <c r="R96">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S96">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T96">
-        <v>3.34</v>
+        <v>3.46</v>
       </c>
       <c r="U96">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="V96">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="W96">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X96">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y96">
         <v>1.13</v>
       </c>
       <c r="Z96">
-        <v>4.95</v>
+        <v>4.5</v>
       </c>
       <c r="AA96">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AB96">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AC96">
-        <v>2.24</v>
+        <v>2.43</v>
       </c>
       <c r="AD96">
-        <v>1.76</v>
+        <v>1.44</v>
       </c>
       <c r="AE96">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AF96">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AG96">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK96">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16061,7 +16061,7 @@
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>2026-10-16 15:45:00</t>
+          <t>2026-10-16 16:00:00</t>
         </is>
       </c>
     </row>
@@ -16078,7 +16078,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.42</v>
+        <v>1.55</v>
       </c>
       <c r="O97">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="P97">
-        <v>2.39</v>
+        <v>5</v>
       </c>
       <c r="Q97">
-        <v>3.02</v>
+        <v>2.05</v>
       </c>
       <c r="R97">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="S97">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="T97">
-        <v>3.46</v>
+        <v>3.08</v>
       </c>
       <c r="U97">
-        <v>2.23</v>
+        <v>2.53</v>
       </c>
       <c r="V97">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="W97">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X97">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y97">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="Z97">
-        <v>4.5</v>
+        <v>4.02</v>
       </c>
       <c r="AA97">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AB97">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AC97">
-        <v>2.43</v>
+        <v>2.83</v>
       </c>
       <c r="AD97">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE97">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF97">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="AG97">
-        <v>2.45</v>
+        <v>1.97</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK97">
-        <v>1.42</v>
+        <v>2.26</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16452,7 +16452,7 @@
         <v>3.48</v>
       </c>
       <c r="P99">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="Q99">
         <v>3.5</v>
@@ -16476,7 +16476,7 @@
         <v>1.07</v>
       </c>
       <c r="X99">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y99">
         <v>1.27</v>
@@ -16488,7 +16488,7 @@
         <v>1.8</v>
       </c>
       <c r="AB99">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AC99">
         <v>2.88</v>
@@ -16503,7 +16503,7 @@
         <v>1.65</v>
       </c>
       <c r="AG99">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK99">
         <v>1.36</v>
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="O100">
         <v>3.2</v>
       </c>
       <c r="P100">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="Q100">
         <v>2.48</v>
@@ -16944,55 +16944,55 @@
         <v>1.3</v>
       </c>
       <c r="Q102">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="R102">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S102">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T102">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U102">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V102">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W102">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X102">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y102">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z102">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="AA102">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AB102">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AC102">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD102">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE102">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF102">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AG102">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK102">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17264,10 +17264,10 @@
         <v>1.67</v>
       </c>
       <c r="O104">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="P104">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17424,10 +17424,10 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.33</v>
+        <v>2.24</v>
       </c>
       <c r="O105">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="P105">
         <v>2.8</v>
@@ -17442,7 +17442,7 @@
         <v>1.44</v>
       </c>
       <c r="T105">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="U105">
         <v>2.9</v>
@@ -17596,55 +17596,55 @@
         <v>0</v>
       </c>
       <c r="Q106">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R106">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S106">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T106">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U106">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V106">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W106">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X106">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y106">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z106">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA106">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AB106">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AC106">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD106">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE106">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF106">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG106">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK106">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -18115,7 +18115,7 @@
         <v>2.2</v>
       </c>
       <c r="AA109">
-        <v>2.87</v>
+        <v>3.04</v>
       </c>
       <c r="AB109">
         <v>1.35</v>

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O2">
         <v>3.25</v>
       </c>
       <c r="P2">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="Q2">
         <v>2.8</v>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -3642,7 +3642,7 @@
         <v>1.16</v>
       </c>
       <c r="AK20">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3762,7 +3762,7 @@
         <v>1.13</v>
       </c>
       <c r="X21">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y21">
         <v>1.21</v>
@@ -3916,10 +3916,10 @@
         <v>4.4</v>
       </c>
       <c r="U22">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="V22">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="W22">
         <v>1.22</v>
@@ -3928,10 +3928,10 @@
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Z22">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="AA22">
         <v>1.3</v>
@@ -3949,10 +3949,10 @@
         <v>1.39</v>
       </c>
       <c r="AF22">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG22">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AK22">
-        <v>5.45</v>
+        <v>5.5</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4097,7 +4097,7 @@
         <v>2.78</v>
       </c>
       <c r="AA23">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AB23">
         <v>1.6</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q29">
         <v>7.49</v>
@@ -5060,7 +5060,7 @@
         <v>2.7</v>
       </c>
       <c r="V29">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W29">
         <v>1.07</v>
@@ -6708,7 +6708,7 @@
         <v>1.53</v>
       </c>
       <c r="AB39">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="AC39">
         <v>2.28</v>
@@ -6723,7 +6723,7 @@
         <v>1.52</v>
       </c>
       <c r="AG39">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6877,7 +6877,7 @@
         <v>2.11</v>
       </c>
       <c r="AD40">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AE40">
         <v>1.27</v>
@@ -6886,7 +6886,7 @@
         <v>1.53</v>
       </c>
       <c r="AG40">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6992,19 +6992,19 @@
         </is>
       </c>
       <c r="N41">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="O41">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="P41">
-        <v>3.09</v>
+        <v>2.95</v>
       </c>
       <c r="Q41">
         <v>2.54</v>
       </c>
       <c r="R41">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S41">
         <v>1.25</v>
@@ -7013,7 +7013,7 @@
         <v>3.5</v>
       </c>
       <c r="U41">
-        <v>2.37</v>
+        <v>2.22</v>
       </c>
       <c r="V41">
         <v>1.57</v>
@@ -7324,7 +7324,7 @@
         <v>3.2</v>
       </c>
       <c r="P43">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="Q43">
         <v>2.72</v>
@@ -8175,7 +8175,7 @@
         <v>1.61</v>
       </c>
       <c r="AB48">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AC48">
         <v>2.52</v>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK48">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8486,7 +8486,7 @@
         <v>1.51</v>
       </c>
       <c r="W50">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X50">
         <v>1.03</v>
@@ -9446,7 +9446,7 @@
         <v>2.28</v>
       </c>
       <c r="Q56">
-        <v>3.64</v>
+        <v>3.81</v>
       </c>
       <c r="R56">
         <v>2.07</v>
@@ -9491,10 +9491,10 @@
         <v>1.06</v>
       </c>
       <c r="AF56">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG56">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>1.24</v>
       </c>
       <c r="AK56">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9763,10 +9763,10 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="O58">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P58">
         <v>3.32</v>
@@ -11758,10 +11758,10 @@
         <v>0</v>
       </c>
       <c r="AA70">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB70">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AC70">
         <v>0</v>
@@ -12208,7 +12208,7 @@
         </is>
       </c>
       <c r="N73">
-        <v>5</v>
+        <v>5.66</v>
       </c>
       <c r="O73">
         <v>4.7</v>
@@ -12534,16 +12534,16 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="O75">
         <v>3.9</v>
       </c>
       <c r="P75">
-        <v>4.04</v>
+        <v>3.85</v>
       </c>
       <c r="Q75">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="R75">
         <v>2.6</v>
@@ -12607,7 +12607,7 @@
         <v>1.22</v>
       </c>
       <c r="AK75">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12697,22 +12697,22 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="O76">
         <v>3.4</v>
       </c>
       <c r="P76">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="Q76">
         <v>2.3</v>
       </c>
       <c r="R76">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="S76">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="T76">
         <v>3.2</v>
@@ -12751,7 +12751,7 @@
         <v>1.1</v>
       </c>
       <c r="AF76">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG76">
         <v>2.05</v>
@@ -12770,7 +12770,7 @@
         <v>1.29</v>
       </c>
       <c r="AK76">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="O78">
         <v>3.4</v>
       </c>
       <c r="P78">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="Q78">
         <v>2.41</v>
@@ -14016,19 +14016,19 @@
         <v>2.53</v>
       </c>
       <c r="S84">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="T84">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="U84">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="V84">
         <v>1.85</v>
       </c>
       <c r="W84">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="X84">
         <v>1.01</v>
@@ -14203,10 +14203,10 @@
         <v>3.08</v>
       </c>
       <c r="AA85">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB85">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC85">
         <v>3.28</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="O87">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="P87">
-        <v>1.75</v>
+        <v>4.8</v>
       </c>
       <c r="Q87">
-        <v>4.68</v>
+        <v>1.95</v>
       </c>
       <c r="R87">
-        <v>2.26</v>
+        <v>2.74</v>
       </c>
       <c r="S87">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="T87">
-        <v>3.22</v>
+        <v>3.9</v>
       </c>
       <c r="U87">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="V87">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="W87">
+        <v>1.17</v>
+      </c>
+      <c r="X87">
+        <v>1.01</v>
+      </c>
+      <c r="Y87">
         <v>1.1</v>
       </c>
-      <c r="X87">
-        <v>1</v>
-      </c>
-      <c r="Y87">
-        <v>1.19</v>
-      </c>
       <c r="Z87">
-        <v>3.75</v>
+        <v>5.2</v>
       </c>
       <c r="AA87">
+        <v>1.4</v>
+      </c>
+      <c r="AB87">
+        <v>2.56</v>
+      </c>
+      <c r="AC87">
+        <v>2.12</v>
+      </c>
+      <c r="AD87">
         <v>1.72</v>
       </c>
-      <c r="AB87">
-        <v>2.05</v>
-      </c>
-      <c r="AC87">
-        <v>2.69</v>
-      </c>
-      <c r="AD87">
-        <v>1.36</v>
-      </c>
       <c r="AE87">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AF87">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AG87">
-        <v>2.09</v>
+        <v>2.35</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK87">
-        <v>1.21</v>
+        <v>2.5</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="O88">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="P88">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="Q88">
-        <v>1.95</v>
+        <v>3.25</v>
       </c>
       <c r="R88">
-        <v>2.74</v>
+        <v>2.24</v>
       </c>
       <c r="S88">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="T88">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="U88">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="V88">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="W88">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X88">
         <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="Z88">
-        <v>5.2</v>
+        <v>3.34</v>
       </c>
       <c r="AA88">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="AB88">
-        <v>2.56</v>
+        <v>1.86</v>
       </c>
       <c r="AC88">
-        <v>2.12</v>
+        <v>3.14</v>
       </c>
       <c r="AD88">
-        <v>1.72</v>
+        <v>1.27</v>
       </c>
       <c r="AE88">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AF88">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="AG88">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK88">
-        <v>2.5</v>
+        <v>1.32</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,80 +14816,80 @@
         </is>
       </c>
       <c r="N89">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O89">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="P89">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="Q89">
-        <v>3.25</v>
+        <v>4.68</v>
       </c>
       <c r="R89">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="S89">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="T89">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="U89">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="V89">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W89">
         <v>1.1</v>
       </c>
       <c r="X89">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y89">
+        <v>1.19</v>
+      </c>
+      <c r="Z89">
+        <v>3.75</v>
+      </c>
+      <c r="AA89">
+        <v>1.72</v>
+      </c>
+      <c r="AB89">
+        <v>2.05</v>
+      </c>
+      <c r="AC89">
+        <v>2.69</v>
+      </c>
+      <c r="AD89">
+        <v>1.36</v>
+      </c>
+      <c r="AE89">
+        <v>1.11</v>
+      </c>
+      <c r="AF89">
+        <v>1.66</v>
+      </c>
+      <c r="AG89">
+        <v>2.09</v>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ89">
         <v>1.24</v>
       </c>
-      <c r="Z89">
-        <v>3.34</v>
-      </c>
-      <c r="AA89">
-        <v>1.9</v>
-      </c>
-      <c r="AB89">
-        <v>1.86</v>
-      </c>
-      <c r="AC89">
-        <v>3.14</v>
-      </c>
-      <c r="AD89">
-        <v>1.27</v>
-      </c>
-      <c r="AE89">
-        <v>1.06</v>
-      </c>
-      <c r="AF89">
-        <v>1.69</v>
-      </c>
-      <c r="AG89">
-        <v>2.1</v>
-      </c>
-      <c r="AH89" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI89" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ89">
-        <v>1.28</v>
-      </c>
       <c r="AK89">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -15818,7 +15818,7 @@
         <v>2.25</v>
       </c>
       <c r="V95">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W95">
         <v>1.14</v>
@@ -15845,7 +15845,7 @@
         <v>1.76</v>
       </c>
       <c r="AE95">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF95">
         <v>1.4</v>

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="O3">
         <v>3.7</v>
@@ -807,7 +807,7 @@
         <v>3.15</v>
       </c>
       <c r="Q3">
-        <v>2.49</v>
+        <v>2.53</v>
       </c>
       <c r="R3">
         <v>2.3</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q6">
         <v>2.16</v>
@@ -1305,7 +1305,7 @@
         <v>1.36</v>
       </c>
       <c r="T6">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="U6">
         <v>2.5</v>
@@ -1323,7 +1323,7 @@
         <v>1.26</v>
       </c>
       <c r="Z6">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="AA6">
         <v>1.79</v>
@@ -1332,7 +1332,7 @@
         <v>1.93</v>
       </c>
       <c r="AC6">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="AD6">
         <v>1.36</v>
@@ -1360,7 +1360,7 @@
         <v>1.22</v>
       </c>
       <c r="AK6">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -4067,7 +4067,7 @@
         <v>2.73</v>
       </c>
       <c r="Q23">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R23">
         <v>1.95</v>
@@ -4079,10 +4079,10 @@
         <v>2.51</v>
       </c>
       <c r="U23">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="V23">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W23">
         <v>1.03</v>
@@ -4091,13 +4091,13 @@
         <v>1.04</v>
       </c>
       <c r="Y23">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="Z23">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AA23">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AB23">
         <v>1.6</v>
@@ -4109,13 +4109,13 @@
         <v>1.17</v>
       </c>
       <c r="AE23">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF23">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG23">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AK23">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4882,55 +4882,55 @@
         <v>0</v>
       </c>
       <c r="Q28">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="R28">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S28">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T28">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U28">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="V28">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W28">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X28">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y28">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z28">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA28">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB28">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC28">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD28">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE28">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF28">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG28">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK28">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -7164,34 +7164,34 @@
         <v>3.12</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X42">
         <v>0</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA42">
         <v>2.35</v>
@@ -7200,19 +7200,19 @@
         <v>1.57</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE42">
         <v>0</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7819,7 +7819,7 @@
         <v>2.51</v>
       </c>
       <c r="R46">
-        <v>2.58</v>
+        <v>2.35</v>
       </c>
       <c r="S46">
         <v>1.22</v>
@@ -8043,7 +8043,7 @@
         <v>1.08</v>
       </c>
       <c r="AK47">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -9280,7 +9280,7 @@
         <v>4</v>
       </c>
       <c r="P55">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="Q55">
         <v>3.36</v>
@@ -9301,7 +9301,7 @@
         <v>1.82</v>
       </c>
       <c r="W55">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X55">
         <v>1.01</v>
@@ -9763,7 +9763,7 @@
         </is>
       </c>
       <c r="N58">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="O58">
         <v>3.55</v>
@@ -9784,13 +9784,13 @@
         <v>3.23</v>
       </c>
       <c r="U58">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="V58">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W58">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X58">
         <v>1</v>
@@ -9926,28 +9926,28 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O59">
         <v>3.6</v>
       </c>
       <c r="P59">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="Q59">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="R59">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="S59">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T59">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U59">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V59">
         <v>1.57</v>
@@ -9962,16 +9962,16 @@
         <v>1.13</v>
       </c>
       <c r="Z59">
-        <v>4.76</v>
+        <v>4.5</v>
       </c>
       <c r="AA59">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="AB59">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="AC59">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="AD59">
         <v>1.53</v>
@@ -9999,7 +9999,7 @@
         <v>1.22</v>
       </c>
       <c r="AK59">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,65 +10904,65 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.02</v>
+        <v>2.7</v>
       </c>
       <c r="O65">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P65">
-        <v>3.2</v>
+        <v>2.37</v>
       </c>
       <c r="Q65">
-        <v>2.46</v>
+        <v>3.02</v>
       </c>
       <c r="R65">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="S65">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T65">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="U65">
-        <v>2.48</v>
+        <v>2.66</v>
       </c>
       <c r="V65">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W65">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X65">
         <v>1.03</v>
       </c>
       <c r="Y65">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z65">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AA65">
-        <v>1.8</v>
+        <v>1.99</v>
       </c>
       <c r="AB65">
+        <v>1.83</v>
+      </c>
+      <c r="AC65">
+        <v>3.4</v>
+      </c>
+      <c r="AD65">
+        <v>1.29</v>
+      </c>
+      <c r="AE65">
+        <v>1.06</v>
+      </c>
+      <c r="AF65">
+        <v>1.7</v>
+      </c>
+      <c r="AG65">
         <v>2</v>
       </c>
-      <c r="AC65">
-        <v>3.1</v>
-      </c>
-      <c r="AD65">
-        <v>1.33</v>
-      </c>
-      <c r="AE65">
-        <v>1.08</v>
-      </c>
-      <c r="AF65">
-        <v>1.67</v>
-      </c>
-      <c r="AG65">
-        <v>2.1</v>
-      </c>
       <c r="AH65" t="inlineStr">
         <is>
           <t>[]</t>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AK65">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="O66">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P66">
-        <v>2.37</v>
+        <v>2.99</v>
       </c>
       <c r="Q66">
-        <v>3.02</v>
+        <v>2.57</v>
       </c>
       <c r="R66">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="S66">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T66">
+        <v>2.82</v>
+      </c>
+      <c r="U66">
         <v>2.8</v>
-      </c>
-      <c r="U66">
-        <v>2.66</v>
       </c>
       <c r="V66">
         <v>1.4</v>
       </c>
       <c r="W66">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X66">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z66">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="AA66">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AB66">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AC66">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="AD66">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AE66">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF66">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AG66">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="AK66">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.73</v>
+        <v>2.13</v>
       </c>
       <c r="O67">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="P67">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="Q67">
-        <v>2.25</v>
+        <v>2.46</v>
       </c>
       <c r="R67">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S67">
         <v>1.3</v>
       </c>
       <c r="T67">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U67">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="V67">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W67">
+        <v>1.1</v>
+      </c>
+      <c r="X67">
+        <v>1.03</v>
+      </c>
+      <c r="Y67">
+        <v>1.25</v>
+      </c>
+      <c r="Z67">
+        <v>3.6</v>
+      </c>
+      <c r="AA67">
+        <v>1.8</v>
+      </c>
+      <c r="AB67">
+        <v>2</v>
+      </c>
+      <c r="AC67">
+        <v>3.1</v>
+      </c>
+      <c r="AD67">
+        <v>1.33</v>
+      </c>
+      <c r="AE67">
         <v>1.08</v>
       </c>
-      <c r="X67">
-        <v>1.01</v>
-      </c>
-      <c r="Y67">
-        <v>1.2</v>
-      </c>
-      <c r="Z67">
-        <v>4.37</v>
-      </c>
-      <c r="AA67">
+      <c r="AF67">
         <v>1.67</v>
       </c>
-      <c r="AB67">
-        <v>2.15</v>
-      </c>
-      <c r="AC67">
-        <v>2.7</v>
-      </c>
-      <c r="AD67">
-        <v>1.4</v>
-      </c>
-      <c r="AE67">
-        <v>1.13</v>
-      </c>
-      <c r="AF67">
-        <v>1.62</v>
-      </c>
       <c r="AG67">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK67">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,80 +11393,80 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.15</v>
+        <v>2.61</v>
       </c>
       <c r="O68">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="P68">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="Q68">
-        <v>2.57</v>
+        <v>3.48</v>
       </c>
       <c r="R68">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="S68">
+        <v>1.49</v>
+      </c>
+      <c r="T68">
+        <v>2.39</v>
+      </c>
+      <c r="U68">
+        <v>3.33</v>
+      </c>
+      <c r="V68">
+        <v>1.3</v>
+      </c>
+      <c r="W68">
+        <v>1.06</v>
+      </c>
+      <c r="X68">
+        <v>1.05</v>
+      </c>
+      <c r="Y68">
+        <v>1.41</v>
+      </c>
+      <c r="Z68">
+        <v>2.75</v>
+      </c>
+      <c r="AA68">
+        <v>2.31</v>
+      </c>
+      <c r="AB68">
+        <v>1.57</v>
+      </c>
+      <c r="AC68">
+        <v>4.15</v>
+      </c>
+      <c r="AD68">
+        <v>1.17</v>
+      </c>
+      <c r="AE68">
+        <v>1.03</v>
+      </c>
+      <c r="AF68">
+        <v>1.94</v>
+      </c>
+      <c r="AG68">
+        <v>1.77</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ68">
         <v>1.36</v>
       </c>
-      <c r="T68">
-        <v>2.82</v>
-      </c>
-      <c r="U68">
-        <v>2.8</v>
-      </c>
-      <c r="V68">
+      <c r="AK68">
         <v>1.4</v>
-      </c>
-      <c r="W68">
-        <v>1.05</v>
-      </c>
-      <c r="X68">
-        <v>1.01</v>
-      </c>
-      <c r="Y68">
-        <v>1.28</v>
-      </c>
-      <c r="Z68">
-        <v>3.32</v>
-      </c>
-      <c r="AA68">
-        <v>1.96</v>
-      </c>
-      <c r="AB68">
-        <v>1.72</v>
-      </c>
-      <c r="AC68">
-        <v>3.5</v>
-      </c>
-      <c r="AD68">
-        <v>1.22</v>
-      </c>
-      <c r="AE68">
-        <v>1.04</v>
-      </c>
-      <c r="AF68">
-        <v>1.8</v>
-      </c>
-      <c r="AG68">
-        <v>1.9</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ68">
-        <v>1.28</v>
-      </c>
-      <c r="AK68">
-        <v>1.71</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,80 +11556,80 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.57</v>
+        <v>1.73</v>
       </c>
       <c r="O69">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="P69">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="Q69">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="R69">
+        <v>2.2</v>
+      </c>
+      <c r="S69">
+        <v>1.3</v>
+      </c>
+      <c r="T69">
+        <v>3.3</v>
+      </c>
+      <c r="U69">
+        <v>2.53</v>
+      </c>
+      <c r="V69">
+        <v>1.51</v>
+      </c>
+      <c r="W69">
+        <v>1.08</v>
+      </c>
+      <c r="X69">
+        <v>1.01</v>
+      </c>
+      <c r="Y69">
+        <v>1.21</v>
+      </c>
+      <c r="Z69">
+        <v>4.33</v>
+      </c>
+      <c r="AA69">
+        <v>1.67</v>
+      </c>
+      <c r="AB69">
+        <v>2.15</v>
+      </c>
+      <c r="AC69">
+        <v>2.75</v>
+      </c>
+      <c r="AD69">
+        <v>1.4</v>
+      </c>
+      <c r="AE69">
+        <v>1.13</v>
+      </c>
+      <c r="AF69">
+        <v>1.62</v>
+      </c>
+      <c r="AG69">
+        <v>2.15</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ69">
+        <v>1.2</v>
+      </c>
+      <c r="AK69">
         <v>1.95</v>
-      </c>
-      <c r="S69">
-        <v>1.48</v>
-      </c>
-      <c r="T69">
-        <v>2.4</v>
-      </c>
-      <c r="U69">
-        <v>3.33</v>
-      </c>
-      <c r="V69">
-        <v>1.3</v>
-      </c>
-      <c r="W69">
-        <v>1.06</v>
-      </c>
-      <c r="X69">
-        <v>1.05</v>
-      </c>
-      <c r="Y69">
-        <v>1.4</v>
-      </c>
-      <c r="Z69">
-        <v>2.75</v>
-      </c>
-      <c r="AA69">
-        <v>2.31</v>
-      </c>
-      <c r="AB69">
-        <v>1.57</v>
-      </c>
-      <c r="AC69">
-        <v>4.15</v>
-      </c>
-      <c r="AD69">
-        <v>1.18</v>
-      </c>
-      <c r="AE69">
-        <v>1.04</v>
-      </c>
-      <c r="AF69">
-        <v>1.94</v>
-      </c>
-      <c r="AG69">
-        <v>1.77</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ69">
-        <v>1.36</v>
-      </c>
-      <c r="AK69">
-        <v>1.4</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="O81">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P81">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="Q81">
         <v>2.89</v>
@@ -14004,13 +14004,13 @@
         <v>1.92</v>
       </c>
       <c r="O84">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P84">
         <v>2.95</v>
       </c>
       <c r="Q84">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="R84">
         <v>2.53</v>
@@ -14034,7 +14034,7 @@
         <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z84">
         <v>8</v>
@@ -14046,13 +14046,13 @@
         <v>3.2</v>
       </c>
       <c r="AC84">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AD84">
         <v>1.9</v>
       </c>
       <c r="AE84">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AF84">
         <v>1.36</v>
@@ -14074,7 +14074,7 @@
         <v>1.25</v>
       </c>
       <c r="AK84">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
+        <v>4</v>
+      </c>
+      <c r="O87">
+        <v>3.7</v>
+      </c>
+      <c r="P87">
+        <v>1.75</v>
+      </c>
+      <c r="Q87">
+        <v>4.33</v>
+      </c>
+      <c r="R87">
+        <v>2.26</v>
+      </c>
+      <c r="S87">
+        <v>1.28</v>
+      </c>
+      <c r="T87">
+        <v>3.22</v>
+      </c>
+      <c r="U87">
+        <v>2.4</v>
+      </c>
+      <c r="V87">
         <v>1.5</v>
       </c>
-      <c r="O87">
-        <v>4.2</v>
-      </c>
-      <c r="P87">
-        <v>4.8</v>
-      </c>
-      <c r="Q87">
-        <v>1.95</v>
-      </c>
-      <c r="R87">
-        <v>2.74</v>
-      </c>
-      <c r="S87">
-        <v>1.2</v>
-      </c>
-      <c r="T87">
-        <v>3.9</v>
-      </c>
-      <c r="U87">
-        <v>2</v>
-      </c>
-      <c r="V87">
-        <v>1.73</v>
-      </c>
       <c r="W87">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X87">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y87">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="Z87">
-        <v>5.2</v>
+        <v>3.75</v>
       </c>
       <c r="AA87">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="AB87">
-        <v>2.56</v>
+        <v>2.05</v>
       </c>
       <c r="AC87">
-        <v>2.12</v>
+        <v>2.69</v>
       </c>
       <c r="AD87">
-        <v>1.72</v>
+        <v>1.36</v>
       </c>
       <c r="AE87">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AF87">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AG87">
-        <v>2.35</v>
+        <v>2.09</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK87">
-        <v>2.5</v>
+        <v>1.21</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="O88">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="P88">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="Q88">
-        <v>3.25</v>
+        <v>1.95</v>
       </c>
       <c r="R88">
-        <v>2.24</v>
+        <v>2.73</v>
       </c>
       <c r="S88">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="T88">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="U88">
-        <v>2.62</v>
+        <v>2</v>
       </c>
       <c r="V88">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="W88">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X88">
         <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="Z88">
-        <v>3.34</v>
+        <v>5.2</v>
       </c>
       <c r="AA88">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="AB88">
-        <v>1.86</v>
+        <v>2.56</v>
       </c>
       <c r="AC88">
-        <v>3.14</v>
+        <v>2.11</v>
       </c>
       <c r="AD88">
-        <v>1.27</v>
+        <v>1.68</v>
       </c>
       <c r="AE88">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="AF88">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="AG88">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK88">
-        <v>1.32</v>
+        <v>2.5</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O89">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P89">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="Q89">
-        <v>4.68</v>
+        <v>3.25</v>
       </c>
       <c r="R89">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="S89">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="T89">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="U89">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="V89">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W89">
         <v>1.1</v>
       </c>
       <c r="X89">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="Z89">
-        <v>3.75</v>
+        <v>3.34</v>
       </c>
       <c r="AA89">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="AB89">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AC89">
-        <v>2.69</v>
+        <v>3.14</v>
       </c>
       <c r="AD89">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AE89">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF89">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AG89">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AK89">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14988,16 +14988,16 @@
         <v>1.38</v>
       </c>
       <c r="Q90">
-        <v>5.5</v>
+        <v>4.25</v>
       </c>
       <c r="R90">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="S90">
         <v>1.22</v>
       </c>
       <c r="T90">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U90">
         <v>2.1</v>
@@ -15018,16 +15018,16 @@
         <v>5.6</v>
       </c>
       <c r="AA90">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AB90">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AC90">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="AD90">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AE90">
         <v>1.29</v>
@@ -15036,7 +15036,7 @@
         <v>1.55</v>
       </c>
       <c r="AG90">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15175,22 +15175,22 @@
         <v>1.02</v>
       </c>
       <c r="Y91">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="Z91">
         <v>4.8</v>
       </c>
       <c r="AA91">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AB91">
-        <v>2.24</v>
+        <v>2.35</v>
       </c>
       <c r="AC91">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="AD91">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="AE91">
         <v>1.16</v>
@@ -15199,7 +15199,7 @@
         <v>1.53</v>
       </c>
       <c r="AG91">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15320,7 +15320,7 @@
         <v>2.46</v>
       </c>
       <c r="S92">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T92">
         <v>3.52</v>
@@ -15332,10 +15332,10 @@
         <v>1.6</v>
       </c>
       <c r="W92">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X92">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y92">
         <v>1.15</v>
@@ -15378,7 +15378,7 @@
         <v>1.44</v>
       </c>
       <c r="AK92">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15477,10 +15477,10 @@
         <v>1.96</v>
       </c>
       <c r="Q93">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="R93">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="S93">
         <v>1.31</v>
@@ -15498,7 +15498,7 @@
         <v>1.11</v>
       </c>
       <c r="X93">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y93">
         <v>1.2</v>
@@ -15513,7 +15513,7 @@
         <v>1.98</v>
       </c>
       <c r="AC93">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AD93">
         <v>1.41</v>
@@ -15631,19 +15631,19 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.99</v>
+        <v>2.91</v>
       </c>
       <c r="O94">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P94">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="Q94">
-        <v>3.6</v>
+        <v>3.49</v>
       </c>
       <c r="R94">
-        <v>2.21</v>
+        <v>2.39</v>
       </c>
       <c r="S94">
         <v>1.29</v>
@@ -15661,34 +15661,34 @@
         <v>1.12</v>
       </c>
       <c r="X94">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y94">
         <v>1.19</v>
       </c>
       <c r="Z94">
-        <v>4.25</v>
+        <v>4.15</v>
       </c>
       <c r="AA94">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AB94">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="AC94">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="AD94">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AE94">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF94">
         <v>1.57</v>
       </c>
       <c r="AG94">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -16141,10 +16141,10 @@
         <v>3.08</v>
       </c>
       <c r="U97">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="V97">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W97">
         <v>1.11</v>
@@ -16156,19 +16156,19 @@
         <v>1.19</v>
       </c>
       <c r="Z97">
-        <v>4.02</v>
+        <v>3.78</v>
       </c>
       <c r="AA97">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB97">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="AC97">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="AD97">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE97">
         <v>1.1</v>
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O98">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q98">
         <v>2.49</v>
@@ -16301,7 +16301,7 @@
         <v>1.39</v>
       </c>
       <c r="T98">
-        <v>3.07</v>
+        <v>2.92</v>
       </c>
       <c r="U98">
         <v>2.89</v>
@@ -16455,10 +16455,10 @@
         <v>2.3</v>
       </c>
       <c r="Q99">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R99">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="S99">
         <v>1.36</v>
@@ -16488,7 +16488,7 @@
         <v>1.8</v>
       </c>
       <c r="AB99">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC99">
         <v>2.88</v>
@@ -16497,7 +16497,7 @@
         <v>1.32</v>
       </c>
       <c r="AE99">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF99">
         <v>1.65</v>
@@ -16618,16 +16618,16 @@
         <v>4</v>
       </c>
       <c r="Q100">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="R100">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="S100">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="T100">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="U100">
         <v>3.18</v>
@@ -16645,28 +16645,28 @@
         <v>1.4</v>
       </c>
       <c r="Z100">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="AA100">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AB100">
         <v>1.61</v>
       </c>
       <c r="AC100">
-        <v>4.16</v>
+        <v>4.2</v>
       </c>
       <c r="AD100">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE100">
         <v>1.02</v>
       </c>
       <c r="AF100">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AG100">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>1.25</v>
       </c>
       <c r="AK100">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16944,19 +16944,19 @@
         <v>1.3</v>
       </c>
       <c r="Q102">
-        <v>9.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="R102">
-        <v>2.59</v>
+        <v>2.52</v>
       </c>
       <c r="S102">
         <v>1.25</v>
       </c>
       <c r="T102">
-        <v>3.4</v>
+        <v>3.26</v>
       </c>
       <c r="U102">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="V102">
         <v>1.5</v>
@@ -16965,34 +16965,34 @@
         <v>1.08</v>
       </c>
       <c r="X102">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y102">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z102">
-        <v>4.03</v>
+        <v>3.82</v>
       </c>
       <c r="AA102">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AB102">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC102">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AD102">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AE102">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF102">
         <v>2.24</v>
       </c>
       <c r="AG102">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>3.63</v>
       </c>
       <c r="AA103">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AB103">
         <v>1.92</v>
@@ -17442,7 +17442,7 @@
         <v>1.44</v>
       </c>
       <c r="T105">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="U105">
         <v>2.9</v>
@@ -17466,7 +17466,7 @@
         <v>2.1</v>
       </c>
       <c r="AB105">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC105">
         <v>3.8</v>
@@ -17494,7 +17494,7 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK105">
         <v>1.57</v>
@@ -17596,16 +17596,16 @@
         <v>0</v>
       </c>
       <c r="Q106">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="R106">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="S106">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T106">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U106">
         <v>2.15</v>
@@ -17617,7 +17617,7 @@
         <v>1.13</v>
       </c>
       <c r="X106">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y106">
         <v>1.13</v>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK106">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17783,10 +17783,10 @@
         <v>1.06</v>
       </c>
       <c r="Y107">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="Z107">
-        <v>2.37</v>
+        <v>2.41</v>
       </c>
       <c r="AA107">
         <v>2.62</v>
@@ -17795,10 +17795,10 @@
         <v>1.38</v>
       </c>
       <c r="AC107">
-        <v>5.4</v>
+        <v>5.45</v>
       </c>
       <c r="AD107">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AE107">
         <v>1.04</v>
@@ -18106,25 +18106,25 @@
         <v>1.03</v>
       </c>
       <c r="X109">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Y109">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="Z109">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AA109">
-        <v>3.04</v>
+        <v>2.87</v>
       </c>
       <c r="AB109">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AC109">
-        <v>6.3</v>
+        <v>5.9</v>
       </c>
       <c r="AD109">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AE109">
         <v>1.03</v>

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="O20">
+        <v>3.6</v>
+      </c>
+      <c r="P20">
+        <v>3</v>
+      </c>
+      <c r="Q20">
+        <v>2.47</v>
+      </c>
+      <c r="R20">
+        <v>2.32</v>
+      </c>
+      <c r="S20">
+        <v>1.18</v>
+      </c>
+      <c r="T20">
         <v>3.85</v>
       </c>
-      <c r="P20">
-        <v>3.85</v>
-      </c>
-      <c r="Q20">
-        <v>2.2</v>
-      </c>
-      <c r="R20">
-        <v>2.5</v>
-      </c>
-      <c r="S20">
+      <c r="U20">
+        <v>2.02</v>
+      </c>
+      <c r="V20">
+        <v>1.68</v>
+      </c>
+      <c r="W20">
         <v>1.16</v>
-      </c>
-      <c r="T20">
-        <v>4.05</v>
-      </c>
-      <c r="U20">
-        <v>1.98</v>
-      </c>
-      <c r="V20">
-        <v>1.71</v>
-      </c>
-      <c r="W20">
-        <v>1.17</v>
       </c>
       <c r="X20">
         <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z20">
-        <v>5.55</v>
+        <v>5.35</v>
       </c>
       <c r="AA20">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AB20">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AC20">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AD20">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AE20">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF20">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AG20">
-        <v>2.69</v>
+        <v>2.74</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AK20">
-        <v>1.91</v>
+        <v>1.63</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3898,16 +3898,16 @@
         <v>1.12</v>
       </c>
       <c r="O22">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="P22">
         <v>15</v>
       </c>
       <c r="Q22">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="R22">
-        <v>3.46</v>
+        <v>3.22</v>
       </c>
       <c r="S22">
         <v>1.17</v>
@@ -3916,7 +3916,7 @@
         <v>4.4</v>
       </c>
       <c r="U22">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="V22">
         <v>1.91</v>
@@ -3928,10 +3928,10 @@
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Z22">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="AA22">
         <v>1.3</v>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AK22">
         <v>5.5</v>
@@ -4882,55 +4882,55 @@
         <v>0</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,31 +5036,31 @@
         </is>
       </c>
       <c r="N29">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="O29">
         <v>4.2</v>
       </c>
       <c r="P29">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Q29">
-        <v>7.49</v>
+        <v>6.5</v>
       </c>
       <c r="R29">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="S29">
         <v>1.34</v>
       </c>
       <c r="T29">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="U29">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="V29">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W29">
         <v>1.07</v>
@@ -5075,16 +5075,16 @@
         <v>3.48</v>
       </c>
       <c r="AA29">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AB29">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AC29">
-        <v>2.74</v>
+        <v>2.94</v>
       </c>
       <c r="AD29">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AE29">
         <v>1.11</v>
@@ -5093,7 +5093,7 @@
         <v>1.98</v>
       </c>
       <c r="AG29">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.16</v>
+        <v>2.55</v>
       </c>
       <c r="AK29">
         <v>1.02</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="O31">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P31">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5851,25 +5851,25 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="O34">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P34">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="Q34">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="R34">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="S34">
         <v>1.33</v>
       </c>
       <c r="T34">
-        <v>2.23</v>
+        <v>2.88</v>
       </c>
       <c r="U34">
         <v>2.29</v>
@@ -5884,16 +5884,16 @@
         <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z34">
         <v>2.63</v>
       </c>
       <c r="AA34">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AB34">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AC34">
         <v>2.75</v>
@@ -5902,7 +5902,7 @@
         <v>1.2</v>
       </c>
       <c r="AE34">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF34">
         <v>1.6</v>
@@ -5924,7 +5924,7 @@
         <v>1.1</v>
       </c>
       <c r="AK34">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6026,7 +6026,7 @@
         <v>2.19</v>
       </c>
       <c r="R35">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S35">
         <v>1.35</v>
@@ -6340,19 +6340,19 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Q37">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="R37">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="S37">
         <v>1.22</v>
@@ -6367,34 +6367,34 @@
         <v>1.67</v>
       </c>
       <c r="W37">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X37">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z37">
-        <v>5.2</v>
+        <v>4.65</v>
       </c>
       <c r="AA37">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AB37">
-        <v>2.49</v>
+        <v>2.28</v>
       </c>
       <c r="AC37">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="AD37">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AE37">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AF37">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG37">
         <v>2.2</v>
@@ -6413,7 +6413,7 @@
         <v>1.14</v>
       </c>
       <c r="AK37">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6515,16 +6515,16 @@
         <v>4.4</v>
       </c>
       <c r="R38">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="S38">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="T38">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="U38">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V38">
         <v>1.44</v>
@@ -6533,13 +6533,13 @@
         <v>1.1</v>
       </c>
       <c r="X38">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y38">
         <v>1.22</v>
       </c>
       <c r="Z38">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AA38">
         <v>1.8</v>
@@ -6554,13 +6554,13 @@
         <v>1.33</v>
       </c>
       <c r="AE38">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF38">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AG38">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6666,19 +6666,19 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="O39">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P39">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="Q39">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R39">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S39">
         <v>1.23</v>
@@ -6690,13 +6690,13 @@
         <v>2.19</v>
       </c>
       <c r="V39">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W39">
         <v>1.13</v>
       </c>
       <c r="X39">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
         <v>1.13</v>
@@ -6708,7 +6708,7 @@
         <v>1.53</v>
       </c>
       <c r="AB39">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="AC39">
         <v>2.28</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7001,7 +7001,7 @@
         <v>2.95</v>
       </c>
       <c r="Q41">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="R41">
         <v>2.38</v>
@@ -7010,7 +7010,7 @@
         <v>1.25</v>
       </c>
       <c r="T41">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="U41">
         <v>2.22</v>
@@ -7049,7 +7049,7 @@
         <v>1.5</v>
       </c>
       <c r="AG41">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK41">
         <v>1.67</v>
@@ -7164,28 +7164,28 @@
         <v>3.12</v>
       </c>
       <c r="Q42">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="R42">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="S42">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T42">
-        <v>2.63</v>
+        <v>2.48</v>
       </c>
       <c r="U42">
-        <v>3.2</v>
+        <v>3.06</v>
       </c>
       <c r="V42">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W42">
+        <v>1.02</v>
+      </c>
+      <c r="X42">
         <v>1.05</v>
-      </c>
-      <c r="X42">
-        <v>0</v>
       </c>
       <c r="Y42">
         <v>1.39</v>
@@ -7194,10 +7194,10 @@
         <v>2.59</v>
       </c>
       <c r="AA42">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="AB42">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AC42">
         <v>4.25</v>
@@ -7206,13 +7206,13 @@
         <v>1.15</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF42">
         <v>1.95</v>
       </c>
       <c r="AG42">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK42">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,19 +7318,19 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="O43">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P43">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="Q43">
         <v>2.72</v>
       </c>
       <c r="R43">
-        <v>2.13</v>
+        <v>1.98</v>
       </c>
       <c r="S43">
         <v>1.41</v>
@@ -7339,10 +7339,10 @@
         <v>2.79</v>
       </c>
       <c r="U43">
-        <v>3.09</v>
+        <v>3.02</v>
       </c>
       <c r="V43">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W43">
         <v>1.03</v>
@@ -7351,22 +7351,22 @@
         <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z43">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="AA43">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AB43">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AC43">
         <v>3.66</v>
       </c>
       <c r="AD43">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AE43">
         <v>1.03</v>
@@ -7375,7 +7375,7 @@
         <v>1.81</v>
       </c>
       <c r="AG43">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7807,19 +7807,19 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.33</v>
+        <v>2.05</v>
       </c>
       <c r="O46">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="P46">
-        <v>2.61</v>
+        <v>3.1</v>
       </c>
       <c r="Q46">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="R46">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="S46">
         <v>1.22</v>
@@ -7846,10 +7846,10 @@
         <v>5.72</v>
       </c>
       <c r="AA46">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AB46">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="AC46">
         <v>2.09</v>
@@ -7858,7 +7858,7 @@
         <v>1.64</v>
       </c>
       <c r="AE46">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AF46">
         <v>1.4</v>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK46">
         <v>1.71</v>
@@ -7985,7 +7985,7 @@
         <v>2.5</v>
       </c>
       <c r="S47">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T47">
         <v>3.5</v>
@@ -8009,7 +8009,7 @@
         <v>4.33</v>
       </c>
       <c r="AA47">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AB47">
         <v>2.24</v>
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AK47">
         <v>1.08</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="O48">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="P48">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q48">
         <v>2.51</v>
@@ -8163,7 +8163,7 @@
         <v>1.08</v>
       </c>
       <c r="X48">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y48">
         <v>1.15</v>
@@ -8190,7 +8190,7 @@
         <v>1.53</v>
       </c>
       <c r="AG48">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK48">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8305,7 +8305,7 @@
         <v>4.4</v>
       </c>
       <c r="Q49">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="R49">
         <v>2.23</v>
@@ -8326,7 +8326,7 @@
         <v>1.1</v>
       </c>
       <c r="X49">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y49">
         <v>1.18</v>
@@ -8369,7 +8369,7 @@
         <v>1.17</v>
       </c>
       <c r="AK49">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="O50">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P50">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="Q50">
         <v>3.14</v>
@@ -8486,10 +8486,10 @@
         <v>1.51</v>
       </c>
       <c r="W50">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X50">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
         <v>1.15</v>
@@ -8498,7 +8498,7 @@
         <v>4.25</v>
       </c>
       <c r="AA50">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AB50">
         <v>2.13</v>
@@ -8513,10 +8513,10 @@
         <v>1.12</v>
       </c>
       <c r="AF50">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AG50">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.21</v>
+        <v>1.46</v>
       </c>
       <c r="AK50">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8637,7 +8637,7 @@
         <v>2.28</v>
       </c>
       <c r="S51">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T51">
         <v>3.5</v>
@@ -8670,13 +8670,13 @@
         <v>2.42</v>
       </c>
       <c r="AD51">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE51">
         <v>1.15</v>
       </c>
       <c r="AF51">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AG51">
         <v>2.39</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="O52">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="P52">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -8972,10 +8972,10 @@
         <v>2</v>
       </c>
       <c r="V53">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="W53">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X53">
         <v>1.01</v>
@@ -8990,10 +8990,10 @@
         <v>1.37</v>
       </c>
       <c r="AB53">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="AC53">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AD53">
         <v>1.73</v>
@@ -9021,7 +9021,7 @@
         <v>1.14</v>
       </c>
       <c r="AK53">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9120,13 +9120,13 @@
         <v>2.2</v>
       </c>
       <c r="Q54">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="R54">
         <v>2.45</v>
       </c>
       <c r="S54">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T54">
         <v>4.5</v>
@@ -9150,19 +9150,19 @@
         <v>5.65</v>
       </c>
       <c r="AA54">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AB54">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="AC54">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AD54">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AE54">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AF54">
         <v>1.4</v>
@@ -9184,7 +9184,7 @@
         <v>1.58</v>
       </c>
       <c r="AK54">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9286,7 +9286,7 @@
         <v>3.36</v>
       </c>
       <c r="R55">
-        <v>2.43</v>
+        <v>2.51</v>
       </c>
       <c r="S55">
         <v>1.14</v>
@@ -9295,13 +9295,13 @@
         <v>4.2</v>
       </c>
       <c r="U55">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="V55">
         <v>1.82</v>
       </c>
       <c r="W55">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X55">
         <v>1.01</v>
@@ -9316,16 +9316,16 @@
         <v>1.3</v>
       </c>
       <c r="AB55">
-        <v>2.97</v>
+        <v>3.17</v>
       </c>
       <c r="AC55">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AD55">
         <v>1.97</v>
       </c>
       <c r="AE55">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AF55">
         <v>1.32</v>
@@ -9446,10 +9446,10 @@
         <v>2.28</v>
       </c>
       <c r="Q56">
-        <v>3.81</v>
+        <v>3.6</v>
       </c>
       <c r="R56">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S56">
         <v>1.33</v>
@@ -9476,13 +9476,13 @@
         <v>3.08</v>
       </c>
       <c r="AA56">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB56">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC56">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AD56">
         <v>1.25</v>
@@ -9491,10 +9491,10 @@
         <v>1.06</v>
       </c>
       <c r="AF56">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG56">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK56">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9609,49 +9609,49 @@
         <v>1.87</v>
       </c>
       <c r="Q57">
-        <v>3.6</v>
+        <v>3.83</v>
       </c>
       <c r="R57">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="S57">
         <v>1.22</v>
       </c>
       <c r="T57">
-        <v>4</v>
+        <v>3.74</v>
       </c>
       <c r="U57">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="V57">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W57">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X57">
         <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z57">
-        <v>5.5</v>
+        <v>5.35</v>
       </c>
       <c r="AA57">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AB57">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="AC57">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AD57">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AE57">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AF57">
         <v>1.4</v>
@@ -9673,7 +9673,7 @@
         <v>1.2</v>
       </c>
       <c r="AK57">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9772,16 +9772,16 @@
         <v>3.32</v>
       </c>
       <c r="Q58">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="R58">
         <v>2.38</v>
       </c>
       <c r="S58">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="T58">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="U58">
         <v>2.55</v>
@@ -9790,7 +9790,7 @@
         <v>1.45</v>
       </c>
       <c r="W58">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X58">
         <v>1</v>
@@ -9802,19 +9802,19 @@
         <v>3.8</v>
       </c>
       <c r="AA58">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AB58">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AC58">
         <v>2.8</v>
       </c>
       <c r="AD58">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AE58">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF58">
         <v>1.6</v>
@@ -9836,7 +9836,7 @@
         <v>1.24</v>
       </c>
       <c r="AK58">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10095,7 +10095,7 @@
         <v>4.45</v>
       </c>
       <c r="P60">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Q60">
         <v>4.53</v>
@@ -10104,7 +10104,7 @@
         <v>2.38</v>
       </c>
       <c r="S60">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T60">
         <v>4</v>
@@ -10125,13 +10125,13 @@
         <v>1.16</v>
       </c>
       <c r="Z60">
-        <v>5.01</v>
+        <v>5.1</v>
       </c>
       <c r="AA60">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB60">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AC60">
         <v>2.34</v>
@@ -10140,7 +10140,7 @@
         <v>1.59</v>
       </c>
       <c r="AE60">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AF60">
         <v>1.6</v>
@@ -10424,7 +10424,7 @@
         <v>7</v>
       </c>
       <c r="Q62">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="R62">
         <v>2.75</v>
@@ -10433,13 +10433,13 @@
         <v>1.2</v>
       </c>
       <c r="T62">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="U62">
         <v>2.05</v>
       </c>
       <c r="V62">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="W62">
         <v>1.18</v>
@@ -10451,13 +10451,13 @@
         <v>1.08</v>
       </c>
       <c r="Z62">
-        <v>6.54</v>
+        <v>6.65</v>
       </c>
       <c r="AA62">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AB62">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AC62">
         <v>2.07</v>
@@ -10472,7 +10472,7 @@
         <v>1.67</v>
       </c>
       <c r="AG62">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10750,22 +10750,22 @@
         <v>2.62</v>
       </c>
       <c r="Q64">
-        <v>2.67</v>
+        <v>2.48</v>
       </c>
       <c r="R64">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="S64">
         <v>1.22</v>
       </c>
       <c r="T64">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="U64">
         <v>2.2</v>
       </c>
       <c r="V64">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W64">
         <v>1.14</v>
@@ -10789,10 +10789,10 @@
         <v>2.25</v>
       </c>
       <c r="AD64">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AE64">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AF64">
         <v>1.44</v>
@@ -10811,7 +10811,7 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK64">
         <v>1.57</v>
@@ -10916,37 +10916,37 @@
         <v>3.02</v>
       </c>
       <c r="R65">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="S65">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T65">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="U65">
         <v>2.66</v>
       </c>
       <c r="V65">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W65">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X65">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y65">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z65">
         <v>3.4</v>
       </c>
       <c r="AA65">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="AB65">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AC65">
         <v>3.4</v>
@@ -10958,10 +10958,10 @@
         <v>1.06</v>
       </c>
       <c r="AF65">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG65">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -11076,10 +11076,10 @@
         <v>2.99</v>
       </c>
       <c r="Q66">
-        <v>2.57</v>
+        <v>2.69</v>
       </c>
       <c r="R66">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="S66">
         <v>1.36</v>
@@ -11097,25 +11097,25 @@
         <v>1.05</v>
       </c>
       <c r="X66">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y66">
         <v>1.28</v>
       </c>
       <c r="Z66">
-        <v>3.32</v>
+        <v>3.08</v>
       </c>
       <c r="AA66">
         <v>1.95</v>
       </c>
       <c r="AB66">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC66">
         <v>3.55</v>
       </c>
       <c r="AD66">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE66">
         <v>1.04</v>
@@ -11140,7 +11140,7 @@
         <v>1.28</v>
       </c>
       <c r="AK66">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11233,55 +11233,55 @@
         <v>2.13</v>
       </c>
       <c r="O67">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P67">
         <v>3.2</v>
       </c>
       <c r="Q67">
-        <v>2.46</v>
+        <v>2.63</v>
       </c>
       <c r="R67">
         <v>2.15</v>
       </c>
       <c r="S67">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T67">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="U67">
         <v>2.48</v>
       </c>
       <c r="V67">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W67">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X67">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z67">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA67">
         <v>1.8</v>
       </c>
       <c r="AB67">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AC67">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="AD67">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE67">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF67">
         <v>1.67</v>
@@ -11393,7 +11393,7 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="O68">
         <v>3</v>
@@ -11402,7 +11402,7 @@
         <v>2.6</v>
       </c>
       <c r="Q68">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="R68">
         <v>1.95</v>
@@ -11414,16 +11414,16 @@
         <v>2.39</v>
       </c>
       <c r="U68">
-        <v>3.33</v>
+        <v>3.1</v>
       </c>
       <c r="V68">
         <v>1.3</v>
       </c>
       <c r="W68">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X68">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y68">
         <v>1.41</v>
@@ -11432,10 +11432,10 @@
         <v>2.75</v>
       </c>
       <c r="AA68">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AB68">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC68">
         <v>4.15</v>
@@ -11444,7 +11444,7 @@
         <v>1.17</v>
       </c>
       <c r="AE68">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF68">
         <v>1.94</v>
@@ -11577,7 +11577,7 @@
         <v>3.3</v>
       </c>
       <c r="U69">
-        <v>2.53</v>
+        <v>2.34</v>
       </c>
       <c r="V69">
         <v>1.51</v>
@@ -11592,10 +11592,10 @@
         <v>1.21</v>
       </c>
       <c r="Z69">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="AA69">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB69">
         <v>2.15</v>
@@ -11604,7 +11604,7 @@
         <v>2.75</v>
       </c>
       <c r="AD69">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE69">
         <v>1.13</v>
@@ -11758,10 +11758,10 @@
         <v>0</v>
       </c>
       <c r="AA70">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB70">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC70">
         <v>0</v>
@@ -11891,10 +11891,10 @@
         <v>4.5</v>
       </c>
       <c r="Q71">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="R71">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="S71">
         <v>1.22</v>
@@ -11915,10 +11915,10 @@
         <v>1.01</v>
       </c>
       <c r="Y71">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z71">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AA71">
         <v>1.4</v>
@@ -11927,10 +11927,10 @@
         <v>2.88</v>
       </c>
       <c r="AC71">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AD71">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AE71">
         <v>1.31</v>
@@ -12709,10 +12709,10 @@
         <v>2.3</v>
       </c>
       <c r="R76">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S76">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T76">
         <v>3.2</v>
@@ -12736,10 +12736,10 @@
         <v>3.8</v>
       </c>
       <c r="AA76">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB76">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AC76">
         <v>3</v>
@@ -12751,7 +12751,7 @@
         <v>1.1</v>
       </c>
       <c r="AF76">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG76">
         <v>2.05</v>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK76">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12863,16 +12863,16 @@
         <v>2.15</v>
       </c>
       <c r="O77">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P77">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Q77">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="R77">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="S77">
         <v>1.33</v>
@@ -12893,16 +12893,16 @@
         <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z77">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AA77">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AB77">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AC77">
         <v>2.97</v>
@@ -12914,10 +12914,10 @@
         <v>1.08</v>
       </c>
       <c r="AF77">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG77">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>1.24</v>
       </c>
       <c r="AK77">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13035,19 +13035,19 @@
         <v>2.41</v>
       </c>
       <c r="R78">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="S78">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T78">
-        <v>3.03</v>
+        <v>2.8</v>
       </c>
       <c r="U78">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="V78">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W78">
         <v>1.06</v>
@@ -13056,25 +13056,25 @@
         <v>1.03</v>
       </c>
       <c r="Y78">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z78">
-        <v>3.48</v>
+        <v>3.6</v>
       </c>
       <c r="AA78">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AB78">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AC78">
         <v>3.22</v>
       </c>
       <c r="AD78">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE78">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF78">
         <v>1.75</v>
@@ -13096,7 +13096,7 @@
         <v>1.25</v>
       </c>
       <c r="AK78">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O79">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P79">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="Q79">
         <v>4.4</v>
       </c>
       <c r="R79">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="S79">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T79">
-        <v>2.76</v>
+        <v>2.87</v>
       </c>
       <c r="U79">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="V79">
         <v>1.44</v>
       </c>
       <c r="W79">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X79">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z79">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="AA79">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AB79">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AC79">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="AD79">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AE79">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF79">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG79">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK79">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13515,16 +13515,16 @@
         <v>2.24</v>
       </c>
       <c r="O81">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="P81">
         <v>2.95</v>
       </c>
       <c r="Q81">
-        <v>2.89</v>
+        <v>2.77</v>
       </c>
       <c r="R81">
-        <v>2.36</v>
+        <v>2.22</v>
       </c>
       <c r="S81">
         <v>1.29</v>
@@ -13533,13 +13533,13 @@
         <v>3.25</v>
       </c>
       <c r="U81">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="V81">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W81">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X81">
         <v>1.01</v>
@@ -13554,7 +13554,7 @@
         <v>1.67</v>
       </c>
       <c r="AB81">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="AC81">
         <v>2.86</v>
@@ -13585,7 +13585,7 @@
         <v>1.36</v>
       </c>
       <c r="AK81">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13687,7 +13687,7 @@
         <v>2.8</v>
       </c>
       <c r="R82">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S82">
         <v>1.3</v>
@@ -13696,7 +13696,7 @@
         <v>3.32</v>
       </c>
       <c r="U82">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="V82">
         <v>1.52</v>
@@ -13714,10 +13714,10 @@
         <v>4.33</v>
       </c>
       <c r="AA82">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AB82">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AC82">
         <v>2.52</v>
@@ -13726,10 +13726,10 @@
         <v>1.41</v>
       </c>
       <c r="AE82">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF82">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AG82">
         <v>2.3</v>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK82">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13847,25 +13847,25 @@
         <v>2.5</v>
       </c>
       <c r="Q83">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R83">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="S83">
         <v>1.4</v>
       </c>
       <c r="T83">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="U83">
         <v>2.9</v>
       </c>
       <c r="V83">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W83">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X83">
         <v>1.02</v>
@@ -13895,7 +13895,7 @@
         <v>1.82</v>
       </c>
       <c r="AG83">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>2.72</v>
       </c>
       <c r="Q85">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="R85">
         <v>2.1</v>
@@ -14209,7 +14209,7 @@
         <v>1.8</v>
       </c>
       <c r="AC85">
-        <v>3.28</v>
+        <v>3.59</v>
       </c>
       <c r="AD85">
         <v>1.25</v>
@@ -14336,7 +14336,7 @@
         <v>2.31</v>
       </c>
       <c r="Q86">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="R86">
         <v>2.25</v>
@@ -14351,7 +14351,7 @@
         <v>2.55</v>
       </c>
       <c r="V86">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W86">
         <v>1.11</v>
@@ -14372,7 +14372,7 @@
         <v>2.23</v>
       </c>
       <c r="AC86">
-        <v>2.61</v>
+        <v>2.88</v>
       </c>
       <c r="AD86">
         <v>1.42</v>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AK86">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.77</v>
+        <v>3.15</v>
       </c>
       <c r="O91">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P91">
-        <v>2.11</v>
+        <v>1.96</v>
       </c>
       <c r="Q91">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="R91">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="S91">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T91">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="U91">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="V91">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="W91">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X91">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y91">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z91">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="AA91">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AB91">
-        <v>2.35</v>
+        <v>1.98</v>
       </c>
       <c r="AC91">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="AD91">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="AE91">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="AF91">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG91">
-        <v>2.45</v>
+        <v>2.07</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
         <v>1.29</v>
       </c>
       <c r="AK91">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>3.15</v>
+        <v>2.77</v>
       </c>
       <c r="O93">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P93">
-        <v>1.96</v>
+        <v>2.11</v>
       </c>
       <c r="Q93">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="R93">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="S93">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T93">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="U93">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="V93">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="W93">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X93">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y93">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z93">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="AA93">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AB93">
-        <v>1.98</v>
+        <v>2.35</v>
       </c>
       <c r="AC93">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="AD93">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="AE93">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="AF93">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG93">
-        <v>2.07</v>
+        <v>2.45</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>1.29</v>
       </c>
       <c r="AK93">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15818,7 +15818,7 @@
         <v>2.25</v>
       </c>
       <c r="V95">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W95">
         <v>1.14</v>
@@ -15845,13 +15845,13 @@
         <v>1.76</v>
       </c>
       <c r="AE95">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF95">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG95">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK95">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15972,10 +15972,10 @@
         <v>2.25</v>
       </c>
       <c r="S96">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T96">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="U96">
         <v>2.23</v>
@@ -15987,7 +15987,7 @@
         <v>1.12</v>
       </c>
       <c r="X96">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y96">
         <v>1.13</v>
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="O98">
-        <v>3.37</v>
+        <v>3.48</v>
       </c>
       <c r="P98">
-        <v>3.08</v>
+        <v>3.46</v>
       </c>
       <c r="Q98">
         <v>2.49</v>
@@ -16304,34 +16304,34 @@
         <v>2.92</v>
       </c>
       <c r="U98">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="V98">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W98">
         <v>1.1</v>
       </c>
       <c r="X98">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y98">
         <v>1.25</v>
       </c>
       <c r="Z98">
-        <v>3.8</v>
+        <v>3.34</v>
       </c>
       <c r="AA98">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AB98">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AC98">
         <v>3.25</v>
       </c>
       <c r="AD98">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE98">
         <v>1.1</v>
@@ -16356,7 +16356,7 @@
         <v>1.3</v>
       </c>
       <c r="AK98">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16455,55 +16455,55 @@
         <v>2.3</v>
       </c>
       <c r="Q99">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R99">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="S99">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T99">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="U99">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="V99">
         <v>1.45</v>
       </c>
       <c r="W99">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X99">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y99">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="Z99">
         <v>3.3</v>
       </c>
       <c r="AA99">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB99">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC99">
-        <v>2.88</v>
+        <v>3.01</v>
       </c>
       <c r="AD99">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE99">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF99">
         <v>1.65</v>
       </c>
       <c r="AG99">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16609,25 +16609,25 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="O100">
         <v>3.2</v>
       </c>
       <c r="P100">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="Q100">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="R100">
-        <v>2.09</v>
+        <v>1.96</v>
       </c>
       <c r="S100">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="T100">
-        <v>2.61</v>
+        <v>2.44</v>
       </c>
       <c r="U100">
         <v>3.18</v>
@@ -16666,7 +16666,7 @@
         <v>2</v>
       </c>
       <c r="AG100">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -18085,10 +18085,10 @@
         <v>3.5</v>
       </c>
       <c r="Q109">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="R109">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="S109">
         <v>1.57</v>
@@ -18115,7 +18115,7 @@
         <v>2.13</v>
       </c>
       <c r="AA109">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="AB109">
         <v>1.33</v>
@@ -18149,7 +18149,7 @@
         <v>1.4</v>
       </c>
       <c r="AK109">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL109">
         <v>0</v>

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -3623,7 +3623,7 @@
         <v>1.25</v>
       </c>
       <c r="AF20">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AG20">
         <v>2.74</v>
@@ -3916,7 +3916,7 @@
         <v>4.4</v>
       </c>
       <c r="U22">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="V22">
         <v>1.91</v>
@@ -3940,10 +3940,10 @@
         <v>3.4</v>
       </c>
       <c r="AC22">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AD22">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AE22">
         <v>1.39</v>
@@ -4067,7 +4067,7 @@
         <v>2.73</v>
       </c>
       <c r="Q23">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R23">
         <v>1.95</v>
@@ -4079,7 +4079,7 @@
         <v>2.51</v>
       </c>
       <c r="U23">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="V23">
         <v>1.3</v>
@@ -5401,10 +5401,10 @@
         <v>0</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC31">
         <v>0</v>
@@ -5878,7 +5878,7 @@
         <v>1.31</v>
       </c>
       <c r="W34">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X34">
         <v>1.02</v>
@@ -5890,7 +5890,7 @@
         <v>2.63</v>
       </c>
       <c r="AA34">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AB34">
         <v>1.6</v>
@@ -5902,7 +5902,7 @@
         <v>1.2</v>
       </c>
       <c r="AE34">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF34">
         <v>1.6</v>
@@ -6340,19 +6340,19 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="O37">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="P37">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="Q37">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="R37">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="S37">
         <v>1.22</v>
@@ -6367,34 +6367,34 @@
         <v>1.67</v>
       </c>
       <c r="W37">
+        <v>1.13</v>
+      </c>
+      <c r="X37">
+        <v>1.02</v>
+      </c>
+      <c r="Y37">
         <v>1.1</v>
       </c>
-      <c r="X37">
-        <v>1.01</v>
-      </c>
-      <c r="Y37">
-        <v>1.12</v>
-      </c>
       <c r="Z37">
-        <v>4.65</v>
+        <v>5.15</v>
       </c>
       <c r="AA37">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AB37">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="AC37">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="AD37">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AE37">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF37">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AG37">
         <v>2.2</v>
@@ -6413,7 +6413,7 @@
         <v>1.14</v>
       </c>
       <c r="AK37">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6512,22 +6512,22 @@
         <v>1.8</v>
       </c>
       <c r="Q38">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="R38">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="S38">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="T38">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="U38">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V38">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W38">
         <v>1.1</v>
@@ -6545,7 +6545,7 @@
         <v>1.8</v>
       </c>
       <c r="AB38">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AC38">
         <v>2.83</v>
@@ -6557,10 +6557,10 @@
         <v>1.09</v>
       </c>
       <c r="AF38">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AG38">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.3</v>
       </c>
       <c r="AK38">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,7 +6666,7 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="O39">
         <v>3.6</v>
@@ -6675,52 +6675,52 @@
         <v>3.4</v>
       </c>
       <c r="Q39">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="R39">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="S39">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T39">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="U39">
-        <v>2.19</v>
+        <v>2.38</v>
       </c>
       <c r="V39">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="W39">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z39">
-        <v>4.6</v>
+        <v>4.25</v>
       </c>
       <c r="AA39">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AB39">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="AC39">
-        <v>2.28</v>
+        <v>2.43</v>
       </c>
       <c r="AD39">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE39">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF39">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AG39">
         <v>2.3</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK39">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6992,19 +6992,19 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="O41">
         <v>3.4</v>
       </c>
       <c r="P41">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="Q41">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="R41">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="S41">
         <v>1.25</v>
@@ -7013,7 +7013,7 @@
         <v>3.38</v>
       </c>
       <c r="U41">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="V41">
         <v>1.57</v>
@@ -7025,7 +7025,7 @@
         <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z41">
         <v>4.67</v>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK41">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7164,55 +7164,55 @@
         <v>3.12</v>
       </c>
       <c r="Q42">
-        <v>2.84</v>
+        <v>2.5</v>
       </c>
       <c r="R42">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="S42">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T42">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="U42">
-        <v>3.06</v>
+        <v>3.2</v>
       </c>
       <c r="V42">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W42">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X42">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="Z42">
-        <v>2.59</v>
+        <v>2.98</v>
       </c>
       <c r="AA42">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AB42">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="AC42">
-        <v>4.25</v>
+        <v>3.86</v>
       </c>
       <c r="AD42">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AE42">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF42">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG42">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AK42">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,7 +7318,7 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="O43">
         <v>3.15</v>
@@ -7333,49 +7333,49 @@
         <v>1.98</v>
       </c>
       <c r="S43">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="T43">
-        <v>2.79</v>
+        <v>2.69</v>
       </c>
       <c r="U43">
-        <v>3.02</v>
+        <v>3.12</v>
       </c>
       <c r="V43">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W43">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X43">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z43">
-        <v>2.92</v>
+        <v>2.81</v>
       </c>
       <c r="AA43">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
       <c r="AB43">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AC43">
-        <v>3.66</v>
+        <v>3.92</v>
       </c>
       <c r="AD43">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE43">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF43">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AG43">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7970,16 +7970,16 @@
         </is>
       </c>
       <c r="N47">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="O47">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="P47">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="Q47">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="R47">
         <v>2.5</v>
@@ -8000,7 +8000,7 @@
         <v>1.13</v>
       </c>
       <c r="X47">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y47">
         <v>1.19</v>
@@ -8012,7 +8012,7 @@
         <v>1.6</v>
       </c>
       <c r="AB47">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="AC47">
         <v>2.59</v>
@@ -8133,34 +8133,34 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="O48">
         <v>3.4</v>
       </c>
       <c r="P48">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="Q48">
-        <v>2.51</v>
+        <v>2.78</v>
       </c>
       <c r="R48">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="S48">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T48">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="U48">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="V48">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W48">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X48">
         <v>1.02</v>
@@ -8169,28 +8169,28 @@
         <v>1.15</v>
       </c>
       <c r="Z48">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AA48">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB48">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AC48">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="AD48">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE48">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF48">
         <v>1.53</v>
       </c>
       <c r="AG48">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK48">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,31 +8296,31 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="O49">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P49">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="Q49">
         <v>2.15</v>
       </c>
       <c r="R49">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="S49">
         <v>1.29</v>
       </c>
       <c r="T49">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="U49">
-        <v>2.34</v>
+        <v>2.27</v>
       </c>
       <c r="V49">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="W49">
         <v>1.1</v>
@@ -8329,31 +8329,31 @@
         <v>1.03</v>
       </c>
       <c r="Y49">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z49">
-        <v>3.92</v>
+        <v>4.1</v>
       </c>
       <c r="AA49">
         <v>1.66</v>
       </c>
       <c r="AB49">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC49">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="AD49">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AE49">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF49">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AG49">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8459,61 +8459,61 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="O50">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P50">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Q50">
-        <v>3.14</v>
+        <v>3.46</v>
       </c>
       <c r="R50">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="S50">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T50">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="U50">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="V50">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="W50">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z50">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="AA50">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AB50">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="AC50">
-        <v>2.52</v>
+        <v>2.43</v>
       </c>
       <c r="AD50">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE50">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF50">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AG50">
         <v>2.34</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="AK50">
         <v>1.44</v>
@@ -8788,7 +8788,7 @@
         <v>2.15</v>
       </c>
       <c r="O52">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P52">
         <v>2.85</v>
@@ -8969,7 +8969,7 @@
         <v>4</v>
       </c>
       <c r="U53">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="V53">
         <v>1.74</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="O57">
-        <v>3.52</v>
+        <v>3.7</v>
       </c>
       <c r="P57">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="Q57">
         <v>3.83</v>
@@ -9630,7 +9630,7 @@
         <v>1.15</v>
       </c>
       <c r="X57">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y57">
         <v>1.14</v>
@@ -9642,7 +9642,7 @@
         <v>1.44</v>
       </c>
       <c r="AB57">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="AC57">
         <v>2.09</v>
@@ -9769,7 +9769,7 @@
         <v>3.55</v>
       </c>
       <c r="P58">
-        <v>3.32</v>
+        <v>3.15</v>
       </c>
       <c r="Q58">
         <v>2.56</v>
@@ -9793,13 +9793,13 @@
         <v>1.1</v>
       </c>
       <c r="X58">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y58">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z58">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AA58">
         <v>1.78</v>
@@ -9817,10 +9817,10 @@
         <v>1.12</v>
       </c>
       <c r="AF58">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG58">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK59">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10122,7 +10122,7 @@
         <v>1.02</v>
       </c>
       <c r="Y60">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z60">
         <v>5.1</v>
@@ -10750,7 +10750,7 @@
         <v>2.62</v>
       </c>
       <c r="Q64">
-        <v>2.48</v>
+        <v>2.74</v>
       </c>
       <c r="R64">
         <v>2.32</v>
@@ -10774,7 +10774,7 @@
         <v>1.02</v>
       </c>
       <c r="Y64">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z64">
         <v>4.85</v>
@@ -10786,7 +10786,7 @@
         <v>2.55</v>
       </c>
       <c r="AC64">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD64">
         <v>1.58</v>
@@ -10811,7 +10811,7 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AK64">
         <v>1.57</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,80 +11067,80 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="O66">
+        <v>3.98</v>
+      </c>
+      <c r="P66">
+        <v>3.9</v>
+      </c>
+      <c r="Q66">
+        <v>2.25</v>
+      </c>
+      <c r="R66">
+        <v>2.2</v>
+      </c>
+      <c r="S66">
+        <v>1.3</v>
+      </c>
+      <c r="T66">
         <v>3.3</v>
       </c>
-      <c r="P66">
-        <v>2.99</v>
-      </c>
-      <c r="Q66">
-        <v>2.69</v>
-      </c>
-      <c r="R66">
-        <v>2.07</v>
-      </c>
-      <c r="S66">
-        <v>1.36</v>
-      </c>
-      <c r="T66">
-        <v>2.82</v>
-      </c>
       <c r="U66">
-        <v>2.8</v>
+        <v>2.34</v>
       </c>
       <c r="V66">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="W66">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X66">
         <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="Z66">
-        <v>3.08</v>
+        <v>4.3</v>
       </c>
       <c r="AA66">
+        <v>1.65</v>
+      </c>
+      <c r="AB66">
+        <v>2.15</v>
+      </c>
+      <c r="AC66">
+        <v>2.75</v>
+      </c>
+      <c r="AD66">
+        <v>1.42</v>
+      </c>
+      <c r="AE66">
+        <v>1.13</v>
+      </c>
+      <c r="AF66">
+        <v>1.62</v>
+      </c>
+      <c r="AG66">
+        <v>2.15</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ66">
+        <v>1.2</v>
+      </c>
+      <c r="AK66">
         <v>1.95</v>
-      </c>
-      <c r="AB66">
-        <v>1.75</v>
-      </c>
-      <c r="AC66">
-        <v>3.55</v>
-      </c>
-      <c r="AD66">
-        <v>1.25</v>
-      </c>
-      <c r="AE66">
-        <v>1.04</v>
-      </c>
-      <c r="AF66">
-        <v>1.79</v>
-      </c>
-      <c r="AG66">
-        <v>1.92</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ66">
-        <v>1.28</v>
-      </c>
-      <c r="AK66">
-        <v>1.7</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11393,7 +11393,7 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="O68">
         <v>3</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="O69">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="P69">
-        <v>3.9</v>
+        <v>2.99</v>
       </c>
       <c r="Q69">
-        <v>2.25</v>
+        <v>2.69</v>
       </c>
       <c r="R69">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="S69">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T69">
-        <v>3.3</v>
+        <v>2.82</v>
       </c>
       <c r="U69">
-        <v>2.34</v>
+        <v>2.8</v>
       </c>
       <c r="V69">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="W69">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X69">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y69">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="Z69">
-        <v>4.3</v>
+        <v>3.08</v>
       </c>
       <c r="AA69">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AB69">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AC69">
-        <v>2.75</v>
+        <v>3.55</v>
       </c>
       <c r="AD69">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AE69">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AF69">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="AG69">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK69">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11933,7 +11933,7 @@
         <v>1.76</v>
       </c>
       <c r="AE71">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AF71">
         <v>1.44</v>
@@ -12703,7 +12703,7 @@
         <v>3.4</v>
       </c>
       <c r="P76">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="Q76">
         <v>2.3</v>
@@ -12718,7 +12718,7 @@
         <v>3.2</v>
       </c>
       <c r="U76">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="V76">
         <v>1.45</v>
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O77">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P77">
         <v>2.9</v>
       </c>
       <c r="Q77">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="R77">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="S77">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T77">
-        <v>2.84</v>
+        <v>2.95</v>
       </c>
       <c r="U77">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="V77">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="W77">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X77">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y77">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z77">
-        <v>3.34</v>
+        <v>3.72</v>
       </c>
       <c r="AA77">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB77">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AC77">
-        <v>2.97</v>
+        <v>2.87</v>
       </c>
       <c r="AD77">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AE77">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF77">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AG77">
-        <v>2.01</v>
+        <v>2.16</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK77">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13023,19 +13023,19 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="O78">
         <v>3.4</v>
       </c>
       <c r="P78">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="Q78">
         <v>2.41</v>
       </c>
       <c r="R78">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S78">
         <v>1.34</v>
@@ -13044,7 +13044,7 @@
         <v>2.8</v>
       </c>
       <c r="U78">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="V78">
         <v>1.42</v>
@@ -13068,7 +13068,7 @@
         <v>1.87</v>
       </c>
       <c r="AC78">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="AD78">
         <v>1.3</v>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK78">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13240,7 +13240,7 @@
         <v>1.1</v>
       </c>
       <c r="AF79">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG79">
         <v>2.03</v>
@@ -13352,7 +13352,7 @@
         <v>2.2</v>
       </c>
       <c r="O80">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P80">
         <v>2.7</v>
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.24</v>
+        <v>2.29</v>
       </c>
       <c r="O81">
         <v>3.62</v>
       </c>
       <c r="P81">
-        <v>2.95</v>
+        <v>2.89</v>
       </c>
       <c r="Q81">
         <v>2.77</v>
@@ -13539,7 +13539,7 @@
         <v>1.51</v>
       </c>
       <c r="W81">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X81">
         <v>1.01</v>
@@ -13705,7 +13705,7 @@
         <v>1.11</v>
       </c>
       <c r="X82">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y82">
         <v>1.18</v>
@@ -13838,80 +13838,80 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O83">
         <v>3.1</v>
       </c>
       <c r="P83">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q83">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R83">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S83">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T83">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U83">
-        <v>2.9</v>
+        <v>2.71</v>
       </c>
       <c r="V83">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W83">
         <v>1.06</v>
       </c>
       <c r="X83">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y83">
+        <v>1.25</v>
+      </c>
+      <c r="Z83">
+        <v>3.6</v>
+      </c>
+      <c r="AA83">
+        <v>1.9</v>
+      </c>
+      <c r="AB83">
+        <v>1.87</v>
+      </c>
+      <c r="AC83">
+        <v>2.97</v>
+      </c>
+      <c r="AD83">
+        <v>1.3</v>
+      </c>
+      <c r="AE83">
+        <v>1.08</v>
+      </c>
+      <c r="AF83">
+        <v>1.64</v>
+      </c>
+      <c r="AG83">
+        <v>2.08</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ83">
+        <v>1.25</v>
+      </c>
+      <c r="AK83">
         <v>1.33</v>
-      </c>
-      <c r="Z83">
-        <v>2.83</v>
-      </c>
-      <c r="AA83">
-        <v>2.15</v>
-      </c>
-      <c r="AB83">
-        <v>1.63</v>
-      </c>
-      <c r="AC83">
-        <v>3.75</v>
-      </c>
-      <c r="AD83">
-        <v>1.19</v>
-      </c>
-      <c r="AE83">
-        <v>1.03</v>
-      </c>
-      <c r="AF83">
-        <v>1.82</v>
-      </c>
-      <c r="AG83">
-        <v>1.82</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ83">
-        <v>1.28</v>
-      </c>
-      <c r="AK83">
-        <v>1.38</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14025,7 +14025,7 @@
         <v>1.84</v>
       </c>
       <c r="V84">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="W84">
         <v>1.23</v>
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="O85">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P85">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="Q85">
         <v>2.97</v>
@@ -14182,7 +14182,7 @@
         <v>1.37</v>
       </c>
       <c r="T85">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="U85">
         <v>2.8</v>
@@ -14209,19 +14209,19 @@
         <v>1.8</v>
       </c>
       <c r="AC85">
-        <v>3.59</v>
+        <v>2.75</v>
       </c>
       <c r="AD85">
         <v>1.25</v>
       </c>
       <c r="AE85">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AF85">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AG85">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>1.3</v>
       </c>
       <c r="AK85">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>3.15</v>
+        <v>2.77</v>
       </c>
       <c r="O91">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P91">
-        <v>1.96</v>
+        <v>2.11</v>
       </c>
       <c r="Q91">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="R91">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="S91">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T91">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="U91">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="V91">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="W91">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X91">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y91">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z91">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="AA91">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AB91">
-        <v>1.98</v>
+        <v>2.35</v>
       </c>
       <c r="AC91">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="AD91">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="AE91">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="AF91">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG91">
-        <v>2.07</v>
+        <v>2.45</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
         <v>1.29</v>
       </c>
       <c r="AK91">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.77</v>
+        <v>3.15</v>
       </c>
       <c r="O93">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P93">
-        <v>2.11</v>
+        <v>1.96</v>
       </c>
       <c r="Q93">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="R93">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="S93">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T93">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="U93">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="V93">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="W93">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X93">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y93">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z93">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="AA93">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AB93">
-        <v>2.35</v>
+        <v>1.98</v>
       </c>
       <c r="AC93">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="AD93">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="AE93">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="AF93">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG93">
-        <v>2.45</v>
+        <v>2.07</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>1.29</v>
       </c>
       <c r="AK93">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15957,13 +15957,13 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="O96">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P96">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="Q96">
         <v>3.02</v>
@@ -16962,7 +16962,7 @@
         <v>1.5</v>
       </c>
       <c r="W102">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X102">
         <v>1</v>
@@ -16977,7 +16977,7 @@
         <v>1.69</v>
       </c>
       <c r="AB102">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AC102">
         <v>2.62</v>
@@ -17005,7 +17005,7 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.08</v>
+        <v>4</v>
       </c>
       <c r="AK102">
         <v>1.04</v>
@@ -17137,7 +17137,7 @@
         <v>3.63</v>
       </c>
       <c r="AA103">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AB103">
         <v>1.92</v>
@@ -17433,46 +17433,46 @@
         <v>2.8</v>
       </c>
       <c r="Q105">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="R105">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="S105">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T105">
-        <v>2.53</v>
+        <v>2.67</v>
       </c>
       <c r="U105">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="V105">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W105">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X105">
         <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="Z105">
-        <v>3.13</v>
+        <v>2.92</v>
       </c>
       <c r="AA105">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AB105">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AC105">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AD105">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE105">
         <v>1.03</v>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK105">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -18085,7 +18085,7 @@
         <v>3.5</v>
       </c>
       <c r="Q109">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="R109">
         <v>1.85</v>

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -650,13 +650,13 @@
         <v>2.1</v>
       </c>
       <c r="S2">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T2">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U2">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V2">
         <v>1.4</v>
@@ -668,7 +668,7 @@
         <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z2">
         <v>3.34</v>
@@ -798,10 +798,10 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="O3">
-        <v>3.7</v>
+        <v>3.53</v>
       </c>
       <c r="P3">
         <v>3.15</v>
@@ -837,7 +837,7 @@
         <v>4.33</v>
       </c>
       <c r="AA3">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AB3">
         <v>2.15</v>
@@ -846,7 +846,7 @@
         <v>2.7</v>
       </c>
       <c r="AD3">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AE3">
         <v>1.17</v>
@@ -1459,56 +1459,56 @@
         <v>2.69</v>
       </c>
       <c r="Q7">
-        <v>2.75</v>
+        <v>3.04</v>
       </c>
       <c r="R7">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S7">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T7">
         <v>3</v>
       </c>
       <c r="U7">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="V7">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W7">
+        <v>1.07</v>
+      </c>
+      <c r="X7">
+        <v>1</v>
+      </c>
+      <c r="Y7">
+        <v>1.21</v>
+      </c>
+      <c r="Z7">
+        <v>3.58</v>
+      </c>
+      <c r="AA7">
+        <v>1.64</v>
+      </c>
+      <c r="AB7">
+        <v>1.69</v>
+      </c>
+      <c r="AC7">
+        <v>2.88</v>
+      </c>
+      <c r="AD7">
+        <v>1.32</v>
+      </c>
+      <c r="AE7">
         <v>1.08</v>
       </c>
-      <c r="X7">
-        <v>1.04</v>
-      </c>
-      <c r="Y7">
-        <v>1.25</v>
-      </c>
-      <c r="Z7">
-        <v>3.8</v>
-      </c>
-      <c r="AA7">
+      <c r="AF7">
+        <v>1.5</v>
+      </c>
+      <c r="AG7">
         <v>1.87</v>
       </c>
-      <c r="AB7">
-        <v>1.9</v>
-      </c>
-      <c r="AC7">
-        <v>3.1</v>
-      </c>
-      <c r="AD7">
-        <v>1.36</v>
-      </c>
-      <c r="AE7">
-        <v>1.1</v>
-      </c>
-      <c r="AF7">
-        <v>1.67</v>
-      </c>
-      <c r="AG7">
-        <v>2.1</v>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK7">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q10">
         <v>3.28</v>
@@ -1960,10 +1960,10 @@
         <v>3</v>
       </c>
       <c r="U10">
-        <v>2.51</v>
+        <v>2.62</v>
       </c>
       <c r="V10">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W10">
         <v>1.1</v>
@@ -1972,31 +1972,31 @@
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z10">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA10">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="AB10">
         <v>1.88</v>
       </c>
       <c r="AC10">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="AD10">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE10">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF10">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG10">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>3.6</v>
       </c>
       <c r="P20">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Q20">
         <v>2.47</v>
@@ -3732,19 +3732,19 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q21">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="R21">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="S21">
         <v>1.29</v>
@@ -3762,34 +3762,34 @@
         <v>1.13</v>
       </c>
       <c r="X21">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z21">
-        <v>4.19</v>
+        <v>4.15</v>
       </c>
       <c r="AA21">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AB21">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC21">
-        <v>2.67</v>
+        <v>2.59</v>
       </c>
       <c r="AD21">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AE21">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF21">
         <v>1.53</v>
       </c>
       <c r="AG21">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK21">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3913,7 +3913,7 @@
         <v>1.17</v>
       </c>
       <c r="T22">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="U22">
         <v>1.85</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="O29">
         <v>4.2</v>
       </c>
       <c r="P29">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="O35">
         <v>3.7</v>
@@ -6343,7 +6343,7 @@
         <v>1.57</v>
       </c>
       <c r="O37">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P37">
         <v>4.33</v>
@@ -6367,34 +6367,34 @@
         <v>1.67</v>
       </c>
       <c r="W37">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X37">
         <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z37">
-        <v>5.15</v>
+        <v>5.45</v>
       </c>
       <c r="AA37">
         <v>1.43</v>
       </c>
       <c r="AB37">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="AC37">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="AD37">
+        <v>1.68</v>
+      </c>
+      <c r="AE37">
+        <v>1.25</v>
+      </c>
+      <c r="AF37">
         <v>1.62</v>
-      </c>
-      <c r="AE37">
-        <v>1.22</v>
-      </c>
-      <c r="AF37">
-        <v>1.49</v>
       </c>
       <c r="AG37">
         <v>2.2</v>
@@ -6672,16 +6672,16 @@
         <v>3.6</v>
       </c>
       <c r="P39">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q39">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R39">
         <v>2.3</v>
       </c>
       <c r="S39">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T39">
         <v>3.3</v>
@@ -6877,7 +6877,7 @@
         <v>2.11</v>
       </c>
       <c r="AD40">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AE40">
         <v>1.27</v>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.13</v>
+        <v>2.45</v>
       </c>
       <c r="AK40">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O41">
         <v>3.4</v>
@@ -7004,7 +7004,7 @@
         <v>2.47</v>
       </c>
       <c r="R41">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="S41">
         <v>1.25</v>
@@ -7013,7 +7013,7 @@
         <v>3.38</v>
       </c>
       <c r="U41">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="V41">
         <v>1.57</v>
@@ -8139,7 +8139,7 @@
         <v>3.4</v>
       </c>
       <c r="P48">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q48">
         <v>2.78</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.65</v>
+        <v>2.75</v>
       </c>
       <c r="O49">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P49">
-        <v>4.2</v>
+        <v>2.11</v>
       </c>
       <c r="Q49">
-        <v>2.15</v>
+        <v>3.46</v>
       </c>
       <c r="R49">
+        <v>2.21</v>
+      </c>
+      <c r="S49">
+        <v>1.32</v>
+      </c>
+      <c r="T49">
+        <v>3.38</v>
+      </c>
+      <c r="U49">
+        <v>2.34</v>
+      </c>
+      <c r="V49">
+        <v>1.56</v>
+      </c>
+      <c r="W49">
+        <v>1.14</v>
+      </c>
+      <c r="X49">
+        <v>1.01</v>
+      </c>
+      <c r="Y49">
+        <v>1.14</v>
+      </c>
+      <c r="Z49">
+        <v>4.4</v>
+      </c>
+      <c r="AA49">
+        <v>1.58</v>
+      </c>
+      <c r="AB49">
         <v>2.25</v>
       </c>
-      <c r="S49">
-        <v>1.29</v>
-      </c>
-      <c r="T49">
-        <v>3.3</v>
-      </c>
-      <c r="U49">
-        <v>2.27</v>
-      </c>
-      <c r="V49">
-        <v>1.51</v>
-      </c>
-      <c r="W49">
-        <v>1.1</v>
-      </c>
-      <c r="X49">
-        <v>1.03</v>
-      </c>
-      <c r="Y49">
-        <v>1.16</v>
-      </c>
-      <c r="Z49">
-        <v>4.1</v>
-      </c>
-      <c r="AA49">
-        <v>1.66</v>
-      </c>
-      <c r="AB49">
-        <v>2.1</v>
-      </c>
       <c r="AC49">
-        <v>2.52</v>
+        <v>2.43</v>
       </c>
       <c r="AD49">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE49">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF49">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG49">
-        <v>2.12</v>
+        <v>2.34</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.17</v>
+        <v>1.54</v>
       </c>
       <c r="AK49">
-        <v>2.1</v>
+        <v>1.36</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.75</v>
+        <v>1.65</v>
       </c>
       <c r="O50">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="P50">
+        <v>3.7</v>
+      </c>
+      <c r="Q50">
         <v>2.15</v>
       </c>
-      <c r="Q50">
-        <v>3.46</v>
-      </c>
       <c r="R50">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="S50">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="T50">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="U50">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="V50">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="W50">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y50">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z50">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AA50">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AB50">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AC50">
-        <v>2.43</v>
+        <v>2.52</v>
       </c>
       <c r="AD50">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AE50">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF50">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG50">
-        <v>2.34</v>
+        <v>2.12</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.54</v>
+        <v>1.17</v>
       </c>
       <c r="AK50">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -9452,16 +9452,16 @@
         <v>2.1</v>
       </c>
       <c r="S56">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T56">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="U56">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="V56">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W56">
         <v>1.05</v>
@@ -10261,7 +10261,7 @@
         <v>2.37</v>
       </c>
       <c r="Q61">
-        <v>3.05</v>
+        <v>3.42</v>
       </c>
       <c r="R61">
         <v>2.12</v>
@@ -10270,7 +10270,7 @@
         <v>1.3</v>
       </c>
       <c r="T61">
-        <v>3.21</v>
+        <v>3.02</v>
       </c>
       <c r="U61">
         <v>2.6</v>
@@ -10279,16 +10279,16 @@
         <v>1.45</v>
       </c>
       <c r="W61">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X61">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y61">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z61">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AA61">
         <v>1.8</v>
@@ -10297,16 +10297,16 @@
         <v>2</v>
       </c>
       <c r="AC61">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AD61">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE61">
         <v>1.1</v>
       </c>
       <c r="AF61">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG61">
         <v>2.15</v>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AK61">
         <v>1.4</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.65</v>
+        <v>2.15</v>
       </c>
       <c r="O68">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="P68">
-        <v>2.6</v>
+        <v>2.99</v>
       </c>
       <c r="Q68">
-        <v>3.4</v>
+        <v>2.69</v>
       </c>
       <c r="R68">
+        <v>2.07</v>
+      </c>
+      <c r="S68">
+        <v>1.36</v>
+      </c>
+      <c r="T68">
+        <v>2.82</v>
+      </c>
+      <c r="U68">
+        <v>2.8</v>
+      </c>
+      <c r="V68">
+        <v>1.4</v>
+      </c>
+      <c r="W68">
+        <v>1.05</v>
+      </c>
+      <c r="X68">
+        <v>1.02</v>
+      </c>
+      <c r="Y68">
+        <v>1.28</v>
+      </c>
+      <c r="Z68">
+        <v>3.08</v>
+      </c>
+      <c r="AA68">
         <v>1.95</v>
       </c>
-      <c r="S68">
-        <v>1.49</v>
-      </c>
-      <c r="T68">
-        <v>2.39</v>
-      </c>
-      <c r="U68">
-        <v>3.1</v>
-      </c>
-      <c r="V68">
-        <v>1.3</v>
-      </c>
-      <c r="W68">
+      <c r="AB68">
+        <v>1.75</v>
+      </c>
+      <c r="AC68">
+        <v>3.55</v>
+      </c>
+      <c r="AD68">
+        <v>1.25</v>
+      </c>
+      <c r="AE68">
         <v>1.04</v>
       </c>
-      <c r="X68">
-        <v>1.04</v>
-      </c>
-      <c r="Y68">
-        <v>1.41</v>
-      </c>
-      <c r="Z68">
-        <v>2.75</v>
-      </c>
-      <c r="AA68">
-        <v>2.3</v>
-      </c>
-      <c r="AB68">
-        <v>1.6</v>
-      </c>
-      <c r="AC68">
-        <v>4.15</v>
-      </c>
-      <c r="AD68">
-        <v>1.17</v>
-      </c>
-      <c r="AE68">
-        <v>1.02</v>
-      </c>
       <c r="AF68">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="AG68">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AK68">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,80 +11556,80 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.15</v>
+        <v>2.65</v>
       </c>
       <c r="O69">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="P69">
-        <v>2.99</v>
+        <v>2.6</v>
       </c>
       <c r="Q69">
-        <v>2.69</v>
+        <v>3.4</v>
       </c>
       <c r="R69">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="S69">
+        <v>1.49</v>
+      </c>
+      <c r="T69">
+        <v>2.39</v>
+      </c>
+      <c r="U69">
+        <v>3.1</v>
+      </c>
+      <c r="V69">
+        <v>1.3</v>
+      </c>
+      <c r="W69">
+        <v>1.04</v>
+      </c>
+      <c r="X69">
+        <v>1.04</v>
+      </c>
+      <c r="Y69">
+        <v>1.41</v>
+      </c>
+      <c r="Z69">
+        <v>2.75</v>
+      </c>
+      <c r="AA69">
+        <v>2.3</v>
+      </c>
+      <c r="AB69">
+        <v>1.6</v>
+      </c>
+      <c r="AC69">
+        <v>4.15</v>
+      </c>
+      <c r="AD69">
+        <v>1.17</v>
+      </c>
+      <c r="AE69">
+        <v>1.02</v>
+      </c>
+      <c r="AF69">
+        <v>1.94</v>
+      </c>
+      <c r="AG69">
+        <v>1.77</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ69">
         <v>1.36</v>
       </c>
-      <c r="T69">
-        <v>2.82</v>
-      </c>
-      <c r="U69">
-        <v>2.8</v>
-      </c>
-      <c r="V69">
+      <c r="AK69">
         <v>1.4</v>
-      </c>
-      <c r="W69">
-        <v>1.05</v>
-      </c>
-      <c r="X69">
-        <v>1.02</v>
-      </c>
-      <c r="Y69">
-        <v>1.28</v>
-      </c>
-      <c r="Z69">
-        <v>3.08</v>
-      </c>
-      <c r="AA69">
-        <v>1.95</v>
-      </c>
-      <c r="AB69">
-        <v>1.75</v>
-      </c>
-      <c r="AC69">
-        <v>3.55</v>
-      </c>
-      <c r="AD69">
-        <v>1.25</v>
-      </c>
-      <c r="AE69">
-        <v>1.04</v>
-      </c>
-      <c r="AF69">
-        <v>1.79</v>
-      </c>
-      <c r="AG69">
-        <v>1.92</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ69">
-        <v>1.28</v>
-      </c>
-      <c r="AK69">
-        <v>1.7</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -12045,7 +12045,7 @@
         </is>
       </c>
       <c r="N72">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O72">
         <v>3.5</v>
@@ -12057,19 +12057,19 @@
         <v>3.28</v>
       </c>
       <c r="R72">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S72">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T72">
         <v>3.7</v>
       </c>
       <c r="U72">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="V72">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W72">
         <v>1.13</v>
@@ -12078,7 +12078,7 @@
         <v>1.02</v>
       </c>
       <c r="Y72">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z72">
         <v>5.25</v>
@@ -12090,19 +12090,19 @@
         <v>2.55</v>
       </c>
       <c r="AC72">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="AD72">
         <v>1.57</v>
       </c>
       <c r="AE72">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF72">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AG72">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.18</v>
+        <v>1.79</v>
       </c>
       <c r="AK72">
         <v>1.29</v>
@@ -12208,25 +12208,25 @@
         </is>
       </c>
       <c r="N73">
-        <v>5.66</v>
+        <v>5.36</v>
       </c>
       <c r="O73">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="P73">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="Q73">
-        <v>4.18</v>
+        <v>5</v>
       </c>
       <c r="R73">
         <v>2.43</v>
       </c>
       <c r="S73">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="T73">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="U73">
         <v>2.06</v>
@@ -12241,10 +12241,10 @@
         <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z73">
-        <v>6.06</v>
+        <v>6.5</v>
       </c>
       <c r="AA73">
         <v>1.4</v>
@@ -12253,10 +12253,10 @@
         <v>2.88</v>
       </c>
       <c r="AC73">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AD73">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AE73">
         <v>1.3</v>
@@ -12281,7 +12281,7 @@
         <v>1.14</v>
       </c>
       <c r="AK73">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12374,16 +12374,16 @@
         <v>2.05</v>
       </c>
       <c r="O74">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="P74">
         <v>2.7</v>
       </c>
       <c r="Q74">
-        <v>2.52</v>
+        <v>2.33</v>
       </c>
       <c r="R74">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="S74">
         <v>1.17</v>
@@ -12392,10 +12392,10 @@
         <v>4.5</v>
       </c>
       <c r="U74">
+        <v>1.82</v>
+      </c>
+      <c r="V74">
         <v>1.86</v>
-      </c>
-      <c r="V74">
-        <v>1.8</v>
       </c>
       <c r="W74">
         <v>1.22</v>
@@ -12540,28 +12540,28 @@
         <v>3.9</v>
       </c>
       <c r="P75">
-        <v>3.85</v>
+        <v>4.04</v>
       </c>
       <c r="Q75">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="R75">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="S75">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T75">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="U75">
         <v>2.05</v>
       </c>
       <c r="V75">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="W75">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X75">
         <v>1.01</v>
@@ -12579,7 +12579,7 @@
         <v>3.1</v>
       </c>
       <c r="AC75">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AD75">
         <v>1.86</v>
@@ -12591,7 +12591,7 @@
         <v>1.36</v>
       </c>
       <c r="AG75">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>1.22</v>
       </c>
       <c r="AK75">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12751,7 +12751,7 @@
         <v>1.1</v>
       </c>
       <c r="AF76">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG76">
         <v>2.05</v>
@@ -12881,7 +12881,7 @@
         <v>2.95</v>
       </c>
       <c r="U77">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V77">
         <v>1.48</v>
@@ -12899,19 +12899,19 @@
         <v>3.72</v>
       </c>
       <c r="AA77">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB77">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC77">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="AD77">
         <v>1.38</v>
       </c>
       <c r="AE77">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF77">
         <v>1.57</v>
@@ -13838,31 +13838,31 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="O83">
         <v>3.1</v>
       </c>
       <c r="P83">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="Q83">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="R83">
         <v>2.1</v>
       </c>
       <c r="S83">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T83">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U83">
         <v>2.71</v>
       </c>
       <c r="V83">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W83">
         <v>1.06</v>
@@ -14058,7 +14058,7 @@
         <v>1.36</v>
       </c>
       <c r="AG84">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="O88">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="P88">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="Q88">
-        <v>1.95</v>
+        <v>3.25</v>
       </c>
       <c r="R88">
-        <v>2.73</v>
+        <v>2.25</v>
       </c>
       <c r="S88">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="T88">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="U88">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="V88">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="W88">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X88">
         <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="Z88">
-        <v>5.2</v>
+        <v>3.34</v>
       </c>
       <c r="AA88">
-        <v>1.4</v>
+        <v>1.88</v>
       </c>
       <c r="AB88">
-        <v>2.56</v>
+        <v>1.9</v>
       </c>
       <c r="AC88">
-        <v>2.11</v>
+        <v>3.14</v>
       </c>
       <c r="AD88">
-        <v>1.68</v>
+        <v>1.27</v>
       </c>
       <c r="AE88">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AF88">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="AG88">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK88">
-        <v>2.5</v>
+        <v>1.32</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="O89">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="P89">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="Q89">
-        <v>3.25</v>
+        <v>1.95</v>
       </c>
       <c r="R89">
-        <v>2.25</v>
+        <v>2.73</v>
       </c>
       <c r="S89">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="T89">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="U89">
-        <v>2.62</v>
+        <v>2</v>
       </c>
       <c r="V89">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="W89">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X89">
         <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="Z89">
-        <v>3.34</v>
+        <v>5.2</v>
       </c>
       <c r="AA89">
-        <v>1.88</v>
+        <v>1.4</v>
       </c>
       <c r="AB89">
-        <v>1.9</v>
+        <v>2.56</v>
       </c>
       <c r="AC89">
-        <v>3.14</v>
+        <v>2.11</v>
       </c>
       <c r="AD89">
-        <v>1.27</v>
+        <v>1.68</v>
       </c>
       <c r="AE89">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="AF89">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="AG89">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK89">
-        <v>1.32</v>
+        <v>2.5</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.3</v>
+        <v>3.15</v>
       </c>
       <c r="O92">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P92">
-        <v>2.55</v>
+        <v>1.96</v>
       </c>
       <c r="Q92">
-        <v>2.88</v>
+        <v>3.9</v>
       </c>
       <c r="R92">
-        <v>2.46</v>
+        <v>2.16</v>
       </c>
       <c r="S92">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="T92">
-        <v>3.52</v>
+        <v>3.1</v>
       </c>
       <c r="U92">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="V92">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="W92">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X92">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y92">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z92">
-        <v>4.98</v>
+        <v>3.7</v>
       </c>
       <c r="AA92">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AB92">
-        <v>2.4</v>
+        <v>1.98</v>
       </c>
       <c r="AC92">
-        <v>2.34</v>
+        <v>2.8</v>
       </c>
       <c r="AD92">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="AE92">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="AF92">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AG92">
-        <v>2.5</v>
+        <v>2.07</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AK92">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>3.15</v>
+        <v>2.3</v>
       </c>
       <c r="O93">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P93">
-        <v>1.96</v>
+        <v>2.55</v>
       </c>
       <c r="Q93">
-        <v>3.9</v>
+        <v>2.88</v>
       </c>
       <c r="R93">
-        <v>2.16</v>
+        <v>2.46</v>
       </c>
       <c r="S93">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="T93">
-        <v>3.1</v>
+        <v>3.52</v>
       </c>
       <c r="U93">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="V93">
+        <v>1.6</v>
+      </c>
+      <c r="W93">
+        <v>1.15</v>
+      </c>
+      <c r="X93">
+        <v>1.03</v>
+      </c>
+      <c r="Y93">
+        <v>1.15</v>
+      </c>
+      <c r="Z93">
+        <v>4.98</v>
+      </c>
+      <c r="AA93">
+        <v>1.53</v>
+      </c>
+      <c r="AB93">
+        <v>2.4</v>
+      </c>
+      <c r="AC93">
+        <v>2.34</v>
+      </c>
+      <c r="AD93">
+        <v>1.57</v>
+      </c>
+      <c r="AE93">
+        <v>1.23</v>
+      </c>
+      <c r="AF93">
         <v>1.44</v>
       </c>
-      <c r="W93">
-        <v>1.11</v>
-      </c>
-      <c r="X93">
-        <v>1.04</v>
-      </c>
-      <c r="Y93">
-        <v>1.2</v>
-      </c>
-      <c r="Z93">
-        <v>3.7</v>
-      </c>
-      <c r="AA93">
-        <v>1.75</v>
-      </c>
-      <c r="AB93">
-        <v>1.98</v>
-      </c>
-      <c r="AC93">
-        <v>2.8</v>
-      </c>
-      <c r="AD93">
-        <v>1.41</v>
-      </c>
-      <c r="AE93">
-        <v>1.08</v>
-      </c>
-      <c r="AF93">
-        <v>1.62</v>
-      </c>
       <c r="AG93">
-        <v>2.07</v>
+        <v>2.5</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AK93">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15815,7 +15815,7 @@
         <v>3.34</v>
       </c>
       <c r="U95">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V95">
         <v>1.66</v>
@@ -16516,7 +16516,7 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AK99">
         <v>1.36</v>

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -1293,74 +1293,74 @@
         <v>3.5</v>
       </c>
       <c r="P6">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="Q6">
+        <v>2.29</v>
+      </c>
+      <c r="R6">
         <v>2.16</v>
       </c>
-      <c r="R6">
-        <v>2.12</v>
-      </c>
       <c r="S6">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T6">
-        <v>3.11</v>
+        <v>2.73</v>
       </c>
       <c r="U6">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="V6">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W6">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="Z6">
-        <v>3.7</v>
+        <v>3.37</v>
       </c>
       <c r="AA6">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="AB6">
         <v>1.93</v>
       </c>
       <c r="AC6">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="AD6">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AE6">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF6">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG6">
+        <v>1.92</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6">
+        <v>1.25</v>
+      </c>
+      <c r="AK6">
         <v>1.95</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6">
-        <v>1.22</v>
-      </c>
-      <c r="AK6">
-        <v>1.82</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -3569,19 +3569,19 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="O20">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P20">
-        <v>2.9</v>
+        <v>3.12</v>
       </c>
       <c r="Q20">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="R20">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="S20">
         <v>1.18</v>
@@ -4067,7 +4067,7 @@
         <v>2.73</v>
       </c>
       <c r="Q23">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R23">
         <v>1.95</v>
@@ -5866,19 +5866,19 @@
         <v>2.09</v>
       </c>
       <c r="S34">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T34">
         <v>2.88</v>
       </c>
       <c r="U34">
-        <v>2.29</v>
+        <v>2.88</v>
       </c>
       <c r="V34">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X34">
         <v>1.02</v>
@@ -5890,10 +5890,10 @@
         <v>2.63</v>
       </c>
       <c r="AA34">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AB34">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC34">
         <v>2.75</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6524,10 +6524,10 @@
         <v>3.1</v>
       </c>
       <c r="U38">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V38">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W38">
         <v>1.1</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="O42">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="P42">
-        <v>3.12</v>
+        <v>3.23</v>
       </c>
       <c r="Q42">
         <v>2.5</v>
@@ -7182,7 +7182,7 @@
         <v>1.32</v>
       </c>
       <c r="W42">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X42">
         <v>1.03</v>
@@ -7209,10 +7209,10 @@
         <v>1.04</v>
       </c>
       <c r="AF42">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AG42">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>7.5</v>
       </c>
       <c r="R47">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="S47">
         <v>1.25</v>
@@ -9111,7 +9111,7 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="O54">
         <v>3.6</v>
@@ -9165,7 +9165,7 @@
         <v>1.26</v>
       </c>
       <c r="AF54">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AG54">
         <v>2.8</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.9</v>
+        <v>3.16</v>
       </c>
       <c r="O55">
         <v>4</v>
       </c>
       <c r="P55">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="Q55">
         <v>3.36</v>
@@ -9766,7 +9766,7 @@
         <v>2.09</v>
       </c>
       <c r="O58">
-        <v>3.55</v>
+        <v>3.66</v>
       </c>
       <c r="P58">
         <v>3.15</v>
@@ -10418,7 +10418,7 @@
         <v>1.3</v>
       </c>
       <c r="O62">
-        <v>5.25</v>
+        <v>5.6</v>
       </c>
       <c r="P62">
         <v>7</v>
@@ -10451,7 +10451,7 @@
         <v>1.08</v>
       </c>
       <c r="Z62">
-        <v>6.65</v>
+        <v>6.64</v>
       </c>
       <c r="AA62">
         <v>1.35</v>
@@ -10753,7 +10753,7 @@
         <v>2.74</v>
       </c>
       <c r="R64">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="S64">
         <v>1.22</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,65 +10904,65 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.7</v>
+        <v>2.13</v>
       </c>
       <c r="O65">
+        <v>3.3</v>
+      </c>
+      <c r="P65">
         <v>3.2</v>
       </c>
-      <c r="P65">
-        <v>2.37</v>
-      </c>
       <c r="Q65">
+        <v>2.63</v>
+      </c>
+      <c r="R65">
+        <v>2.15</v>
+      </c>
+      <c r="S65">
+        <v>1.32</v>
+      </c>
+      <c r="T65">
         <v>3.02</v>
       </c>
-      <c r="R65">
+      <c r="U65">
+        <v>2.48</v>
+      </c>
+      <c r="V65">
+        <v>1.46</v>
+      </c>
+      <c r="W65">
+        <v>1.09</v>
+      </c>
+      <c r="X65">
+        <v>1.01</v>
+      </c>
+      <c r="Y65">
+        <v>1.26</v>
+      </c>
+      <c r="Z65">
+        <v>3.5</v>
+      </c>
+      <c r="AA65">
+        <v>1.8</v>
+      </c>
+      <c r="AB65">
+        <v>1.88</v>
+      </c>
+      <c r="AC65">
+        <v>3.04</v>
+      </c>
+      <c r="AD65">
+        <v>1.32</v>
+      </c>
+      <c r="AE65">
+        <v>1.09</v>
+      </c>
+      <c r="AF65">
+        <v>1.67</v>
+      </c>
+      <c r="AG65">
         <v>2.1</v>
       </c>
-      <c r="S65">
-        <v>1.36</v>
-      </c>
-      <c r="T65">
-        <v>2.81</v>
-      </c>
-      <c r="U65">
-        <v>2.66</v>
-      </c>
-      <c r="V65">
-        <v>1.37</v>
-      </c>
-      <c r="W65">
-        <v>1.04</v>
-      </c>
-      <c r="X65">
-        <v>1</v>
-      </c>
-      <c r="Y65">
-        <v>1.28</v>
-      </c>
-      <c r="Z65">
-        <v>3.4</v>
-      </c>
-      <c r="AA65">
-        <v>1.92</v>
-      </c>
-      <c r="AB65">
-        <v>1.82</v>
-      </c>
-      <c r="AC65">
-        <v>3.4</v>
-      </c>
-      <c r="AD65">
-        <v>1.29</v>
-      </c>
-      <c r="AE65">
-        <v>1.06</v>
-      </c>
-      <c r="AF65">
-        <v>1.71</v>
-      </c>
-      <c r="AG65">
-        <v>2.02</v>
-      </c>
       <c r="AH65" t="inlineStr">
         <is>
           <t>[]</t>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AK65">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.73</v>
+        <v>2.65</v>
       </c>
       <c r="O66">
-        <v>3.98</v>
+        <v>3</v>
       </c>
       <c r="P66">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="Q66">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="R66">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="S66">
+        <v>1.49</v>
+      </c>
+      <c r="T66">
+        <v>2.39</v>
+      </c>
+      <c r="U66">
+        <v>3.1</v>
+      </c>
+      <c r="V66">
         <v>1.3</v>
       </c>
-      <c r="T66">
-        <v>3.3</v>
-      </c>
-      <c r="U66">
-        <v>2.34</v>
-      </c>
-      <c r="V66">
-        <v>1.51</v>
-      </c>
       <c r="W66">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X66">
+        <v>1.04</v>
+      </c>
+      <c r="Y66">
+        <v>1.41</v>
+      </c>
+      <c r="Z66">
+        <v>2.75</v>
+      </c>
+      <c r="AA66">
+        <v>2.3</v>
+      </c>
+      <c r="AB66">
+        <v>1.6</v>
+      </c>
+      <c r="AC66">
+        <v>4.15</v>
+      </c>
+      <c r="AD66">
+        <v>1.17</v>
+      </c>
+      <c r="AE66">
         <v>1.02</v>
       </c>
-      <c r="Y66">
-        <v>1.21</v>
-      </c>
-      <c r="Z66">
-        <v>4.3</v>
-      </c>
-      <c r="AA66">
-        <v>1.65</v>
-      </c>
-      <c r="AB66">
-        <v>2.15</v>
-      </c>
-      <c r="AC66">
-        <v>2.75</v>
-      </c>
-      <c r="AD66">
-        <v>1.42</v>
-      </c>
-      <c r="AE66">
-        <v>1.13</v>
-      </c>
       <c r="AF66">
-        <v>1.62</v>
+        <v>1.94</v>
       </c>
       <c r="AG66">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AK66">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.13</v>
+        <v>2.6</v>
       </c>
       <c r="O67">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P67">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q67">
-        <v>2.63</v>
+        <v>3.02</v>
       </c>
       <c r="R67">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S67">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="T67">
-        <v>3.02</v>
+        <v>2.8</v>
       </c>
       <c r="U67">
-        <v>2.48</v>
+        <v>2.66</v>
       </c>
       <c r="V67">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="W67">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X67">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y67">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z67">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA67">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AB67">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="AC67">
-        <v>3.04</v>
+        <v>3.4</v>
       </c>
       <c r="AD67">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AE67">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF67">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AG67">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AK67">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.65</v>
+        <v>1.73</v>
       </c>
       <c r="O69">
-        <v>3</v>
+        <v>3.98</v>
       </c>
       <c r="P69">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="Q69">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="R69">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="S69">
-        <v>1.49</v>
+        <v>1.29</v>
       </c>
       <c r="T69">
-        <v>2.39</v>
+        <v>3.46</v>
       </c>
       <c r="U69">
-        <v>3.1</v>
+        <v>2.33</v>
       </c>
       <c r="V69">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="W69">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X69">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y69">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="Z69">
-        <v>2.75</v>
+        <v>4.4</v>
       </c>
       <c r="AA69">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="AB69">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="AC69">
-        <v>4.15</v>
+        <v>2.7</v>
       </c>
       <c r="AD69">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AE69">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="AF69">
-        <v>1.94</v>
+        <v>1.62</v>
       </c>
       <c r="AG69">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AK69">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.05</v>
+        <v>1.69</v>
       </c>
       <c r="O74">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="P74">
-        <v>2.7</v>
+        <v>4.04</v>
       </c>
       <c r="Q74">
-        <v>2.33</v>
+        <v>2.13</v>
       </c>
       <c r="R74">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="S74">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T74">
         <v>4.5</v>
       </c>
       <c r="U74">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="V74">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="W74">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="X74">
         <v>1.01</v>
       </c>
       <c r="Y74">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Z74">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AA74">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AB74">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="AC74">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AD74">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="AE74">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AF74">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AG74">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK74">
-        <v>1.65</v>
+        <v>2.07</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.69</v>
+        <v>2.05</v>
       </c>
       <c r="O75">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="P75">
-        <v>4.04</v>
+        <v>2.7</v>
       </c>
       <c r="Q75">
-        <v>2.13</v>
+        <v>2.33</v>
       </c>
       <c r="R75">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="S75">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T75">
         <v>4.5</v>
       </c>
       <c r="U75">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="V75">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="W75">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X75">
         <v>1.01</v>
       </c>
       <c r="Y75">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Z75">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AA75">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AB75">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="AC75">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AD75">
-        <v>1.86</v>
+        <v>1.99</v>
       </c>
       <c r="AE75">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AF75">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AG75">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK75">
-        <v>2.07</v>
+        <v>1.65</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -13539,7 +13539,7 @@
         <v>1.51</v>
       </c>
       <c r="W81">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X81">
         <v>1.01</v>
@@ -13681,7 +13681,7 @@
         <v>3.4</v>
       </c>
       <c r="P82">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="Q82">
         <v>2.8</v>
@@ -14007,7 +14007,7 @@
         <v>4.2</v>
       </c>
       <c r="P84">
-        <v>2.95</v>
+        <v>3.36</v>
       </c>
       <c r="Q84">
         <v>2.4</v>
@@ -14037,7 +14037,7 @@
         <v>1.05</v>
       </c>
       <c r="Z84">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AA84">
         <v>1.36</v>
@@ -14046,7 +14046,7 @@
         <v>3.2</v>
       </c>
       <c r="AC84">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AD84">
         <v>1.9</v>
@@ -14511,7 +14511,7 @@
         <v>3.22</v>
       </c>
       <c r="U87">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V87">
         <v>1.5</v>
@@ -14520,7 +14520,7 @@
         <v>1.1</v>
       </c>
       <c r="X87">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y87">
         <v>1.19</v>
@@ -14547,7 +14547,7 @@
         <v>1.66</v>
       </c>
       <c r="AG87">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="O88">
         <v>3.2</v>
       </c>
       <c r="P88">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q88">
         <v>3.25</v>
@@ -14683,19 +14683,19 @@
         <v>1.1</v>
       </c>
       <c r="X88">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y88">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z88">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="AA88">
         <v>1.88</v>
       </c>
       <c r="AB88">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AC88">
         <v>3.14</v>
@@ -14864,13 +14864,13 @@
         <v>2.11</v>
       </c>
       <c r="AD89">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AE89">
         <v>1.25</v>
       </c>
       <c r="AF89">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG89">
         <v>2.35</v>
@@ -14889,7 +14889,7 @@
         <v>1.2</v>
       </c>
       <c r="AK89">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -15024,7 +15024,7 @@
         <v>2.88</v>
       </c>
       <c r="AC90">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AD90">
         <v>1.67</v>
@@ -15036,7 +15036,7 @@
         <v>1.55</v>
       </c>
       <c r="AG90">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15172,13 +15172,13 @@
         <v>1.15</v>
       </c>
       <c r="X91">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y91">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z91">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AA91">
         <v>1.57</v>
@@ -15187,19 +15187,19 @@
         <v>2.35</v>
       </c>
       <c r="AC91">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="AD91">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AE91">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AF91">
         <v>1.53</v>
       </c>
       <c r="AG91">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>3.15</v>
+        <v>2.3</v>
       </c>
       <c r="O92">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P92">
-        <v>1.96</v>
+        <v>2.55</v>
       </c>
       <c r="Q92">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="R92">
-        <v>2.16</v>
+        <v>2.46</v>
       </c>
       <c r="S92">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="T92">
-        <v>3.1</v>
+        <v>3.52</v>
       </c>
       <c r="U92">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="V92">
+        <v>1.6</v>
+      </c>
+      <c r="W92">
+        <v>1.15</v>
+      </c>
+      <c r="X92">
+        <v>1.01</v>
+      </c>
+      <c r="Y92">
+        <v>1.14</v>
+      </c>
+      <c r="Z92">
+        <v>5.5</v>
+      </c>
+      <c r="AA92">
+        <v>1.53</v>
+      </c>
+      <c r="AB92">
+        <v>2.4</v>
+      </c>
+      <c r="AC92">
+        <v>2.3</v>
+      </c>
+      <c r="AD92">
+        <v>1.6</v>
+      </c>
+      <c r="AE92">
+        <v>1.22</v>
+      </c>
+      <c r="AF92">
         <v>1.44</v>
       </c>
-      <c r="W92">
-        <v>1.11</v>
-      </c>
-      <c r="X92">
-        <v>1.04</v>
-      </c>
-      <c r="Y92">
-        <v>1.2</v>
-      </c>
-      <c r="Z92">
-        <v>3.7</v>
-      </c>
-      <c r="AA92">
-        <v>1.75</v>
-      </c>
-      <c r="AB92">
-        <v>1.98</v>
-      </c>
-      <c r="AC92">
-        <v>2.8</v>
-      </c>
-      <c r="AD92">
-        <v>1.41</v>
-      </c>
-      <c r="AE92">
-        <v>1.08</v>
-      </c>
-      <c r="AF92">
-        <v>1.62</v>
-      </c>
       <c r="AG92">
-        <v>2.07</v>
+        <v>2.5</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AK92">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.3</v>
+        <v>3.15</v>
       </c>
       <c r="O93">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P93">
-        <v>2.55</v>
+        <v>1.96</v>
       </c>
       <c r="Q93">
-        <v>2.88</v>
+        <v>3.9</v>
       </c>
       <c r="R93">
-        <v>2.46</v>
+        <v>2.16</v>
       </c>
       <c r="S93">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="T93">
-        <v>3.52</v>
+        <v>3.1</v>
       </c>
       <c r="U93">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="V93">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="W93">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X93">
         <v>1.03</v>
       </c>
       <c r="Y93">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z93">
-        <v>4.98</v>
+        <v>3.7</v>
       </c>
       <c r="AA93">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AB93">
-        <v>2.4</v>
+        <v>1.98</v>
       </c>
       <c r="AC93">
-        <v>2.34</v>
+        <v>2.8</v>
       </c>
       <c r="AD93">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="AE93">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="AF93">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AG93">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AK93">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15631,19 +15631,19 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="O94">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P94">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="Q94">
-        <v>3.49</v>
+        <v>3.42</v>
       </c>
       <c r="R94">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="S94">
         <v>1.29</v>
@@ -15652,7 +15652,7 @@
         <v>3.25</v>
       </c>
       <c r="U94">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="V94">
         <v>1.5</v>
@@ -15661,34 +15661,34 @@
         <v>1.12</v>
       </c>
       <c r="X94">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y94">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z94">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="AA94">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AB94">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="AC94">
-        <v>2.59</v>
+        <v>2.46</v>
       </c>
       <c r="AD94">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AE94">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF94">
         <v>1.57</v>
       </c>
       <c r="AG94">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>1.55</v>
       </c>
       <c r="O97">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P97">
         <v>5</v>
@@ -16150,7 +16150,7 @@
         <v>1.11</v>
       </c>
       <c r="X97">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y97">
         <v>1.19</v>
@@ -16171,7 +16171,7 @@
         <v>1.44</v>
       </c>
       <c r="AE97">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF97">
         <v>1.75</v>
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="O100">
         <v>3.2</v>
       </c>
       <c r="P100">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="Q100">
         <v>2.52</v>
@@ -17137,7 +17137,7 @@
         <v>3.63</v>
       </c>
       <c r="AA103">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AB103">
         <v>1.92</v>
@@ -17264,40 +17264,40 @@
         <v>1.67</v>
       </c>
       <c r="O104">
-        <v>3.94</v>
+        <v>3.8</v>
       </c>
       <c r="P104">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="Q104">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="R104">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S104">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T104">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U104">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="V104">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="W104">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X104">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y104">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z104">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AA104">
         <v>1.4</v>
@@ -17306,19 +17306,19 @@
         <v>2.75</v>
       </c>
       <c r="AC104">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AD104">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE104">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF104">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG104">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK104">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17445,7 +17445,7 @@
         <v>2.67</v>
       </c>
       <c r="U105">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="V105">
         <v>1.33</v>
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O106">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q106">
         <v>2.34</v>
@@ -17759,16 +17759,16 @@
         <v>2.75</v>
       </c>
       <c r="Q107">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R107">
         <v>1.83</v>
       </c>
       <c r="S107">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="T107">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="U107">
         <v>3.82</v>
@@ -17777,7 +17777,7 @@
         <v>1.22</v>
       </c>
       <c r="W107">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X107">
         <v>1.06</v>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK107">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17952,10 +17952,10 @@
         <v>0</v>
       </c>
       <c r="AA108">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB108">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC108">
         <v>0</v>

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="N20">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O20">
         <v>3.75</v>
@@ -3581,19 +3581,19 @@
         <v>2.45</v>
       </c>
       <c r="R20">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="S20">
         <v>1.18</v>
       </c>
       <c r="T20">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="U20">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="V20">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W20">
         <v>1.16</v>
@@ -3913,7 +3913,7 @@
         <v>1.17</v>
       </c>
       <c r="T22">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="U22">
         <v>1.85</v>
@@ -3940,13 +3940,13 @@
         <v>3.4</v>
       </c>
       <c r="AC22">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AD22">
         <v>1.98</v>
       </c>
       <c r="AE22">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AF22">
         <v>1.95</v>
@@ -5054,10 +5054,10 @@
         <v>1.34</v>
       </c>
       <c r="T29">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="U29">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="V29">
         <v>1.44</v>
@@ -5075,16 +5075,16 @@
         <v>3.48</v>
       </c>
       <c r="AA29">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AB29">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AC29">
-        <v>2.94</v>
+        <v>2.74</v>
       </c>
       <c r="AD29">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE29">
         <v>1.11</v>
@@ -5362,10 +5362,10 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O31">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="P31">
         <v>2.5</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="O34">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P34">
-        <v>2.9</v>
+        <v>3.16</v>
       </c>
       <c r="Q34">
         <v>2.5</v>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="O35">
         <v>3.7</v>
@@ -6050,7 +6050,7 @@
         <v>1.27</v>
       </c>
       <c r="Z35">
-        <v>3.63</v>
+        <v>3.65</v>
       </c>
       <c r="AA35">
         <v>1.86</v>
@@ -6373,22 +6373,22 @@
         <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z37">
-        <v>5.45</v>
+        <v>5.75</v>
       </c>
       <c r="AA37">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AB37">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="AC37">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AD37">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AE37">
         <v>1.25</v>
@@ -6515,7 +6515,7 @@
         <v>4.33</v>
       </c>
       <c r="R38">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="S38">
         <v>1.36</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="O39">
         <v>3.6</v>
       </c>
       <c r="P39">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="Q39">
         <v>2.4</v>
@@ -6684,13 +6684,13 @@
         <v>1.29</v>
       </c>
       <c r="T39">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U39">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="V39">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W39">
         <v>1.11</v>
@@ -6699,28 +6699,28 @@
         <v>1.02</v>
       </c>
       <c r="Y39">
+        <v>1.18</v>
+      </c>
+      <c r="Z39">
+        <v>4.4</v>
+      </c>
+      <c r="AA39">
+        <v>1.61</v>
+      </c>
+      <c r="AB39">
+        <v>2.13</v>
+      </c>
+      <c r="AC39">
+        <v>2.6</v>
+      </c>
+      <c r="AD39">
+        <v>1.45</v>
+      </c>
+      <c r="AE39">
         <v>1.15</v>
       </c>
-      <c r="Z39">
-        <v>4.25</v>
-      </c>
-      <c r="AA39">
-        <v>1.59</v>
-      </c>
-      <c r="AB39">
-        <v>2.35</v>
-      </c>
-      <c r="AC39">
-        <v>2.43</v>
-      </c>
-      <c r="AD39">
-        <v>1.44</v>
-      </c>
-      <c r="AE39">
-        <v>1.14</v>
-      </c>
       <c r="AF39">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG39">
         <v>2.3</v>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK39">
         <v>1.83</v>
@@ -6995,16 +6995,16 @@
         <v>2</v>
       </c>
       <c r="O41">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P41">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="Q41">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="R41">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S41">
         <v>1.25</v>
@@ -7025,22 +7025,22 @@
         <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z41">
-        <v>4.67</v>
+        <v>4.6</v>
       </c>
       <c r="AA41">
         <v>1.57</v>
       </c>
       <c r="AB41">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="AC41">
-        <v>2.49</v>
+        <v>2.36</v>
       </c>
       <c r="AD41">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE41">
         <v>1.15</v>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK41">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="O43">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P43">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="Q43">
         <v>2.72</v>
@@ -7982,7 +7982,7 @@
         <v>7.5</v>
       </c>
       <c r="R47">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="S47">
         <v>1.25</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O48">
         <v>3.4</v>
       </c>
       <c r="P48">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="Q48">
         <v>2.78</v>
@@ -8296,19 +8296,19 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.75</v>
+        <v>2.86</v>
       </c>
       <c r="O49">
         <v>3.5</v>
       </c>
       <c r="P49">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="Q49">
         <v>3.46</v>
       </c>
       <c r="R49">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="S49">
         <v>1.32</v>
@@ -8462,10 +8462,10 @@
         <v>1.65</v>
       </c>
       <c r="O50">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P50">
-        <v>3.7</v>
+        <v>4.47</v>
       </c>
       <c r="Q50">
         <v>2.15</v>
@@ -8498,7 +8498,7 @@
         <v>4.1</v>
       </c>
       <c r="AA50">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AB50">
         <v>2.1</v>
@@ -8661,7 +8661,7 @@
         <v>4.35</v>
       </c>
       <c r="AA51">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB51">
         <v>2.3</v>
@@ -8788,7 +8788,7 @@
         <v>2.15</v>
       </c>
       <c r="O52">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P52">
         <v>2.85</v>
@@ -8951,7 +8951,7 @@
         <v>1.5</v>
       </c>
       <c r="O53">
-        <v>4.33</v>
+        <v>4.55</v>
       </c>
       <c r="P53">
         <v>4.6</v>
@@ -9510,7 +9510,7 @@
         <v>1.25</v>
       </c>
       <c r="AK56">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,31 +9600,31 @@
         </is>
       </c>
       <c r="N57">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="O57">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P57">
         <v>1.85</v>
       </c>
       <c r="Q57">
-        <v>3.83</v>
+        <v>4.14</v>
       </c>
       <c r="R57">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="S57">
         <v>1.22</v>
       </c>
       <c r="T57">
-        <v>3.74</v>
+        <v>3.9</v>
       </c>
       <c r="U57">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="V57">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="W57">
         <v>1.15</v>
@@ -9636,7 +9636,7 @@
         <v>1.14</v>
       </c>
       <c r="Z57">
-        <v>5.35</v>
+        <v>5.5</v>
       </c>
       <c r="AA57">
         <v>1.44</v>
@@ -9645,13 +9645,13 @@
         <v>2.62</v>
       </c>
       <c r="AC57">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="AD57">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AE57">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AF57">
         <v>1.4</v>
@@ -9673,7 +9673,7 @@
         <v>1.2</v>
       </c>
       <c r="AK57">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,7 +9763,7 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="O58">
         <v>3.66</v>
@@ -9926,7 +9926,7 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="O59">
         <v>3.6</v>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>5.4</v>
+        <v>5.71</v>
       </c>
       <c r="O60">
         <v>4.45</v>
       </c>
       <c r="P60">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="Q60">
         <v>4.53</v>
@@ -10418,13 +10418,13 @@
         <v>1.3</v>
       </c>
       <c r="O62">
-        <v>5.6</v>
+        <v>5.25</v>
       </c>
       <c r="P62">
         <v>7</v>
       </c>
       <c r="Q62">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="R62">
         <v>2.75</v>
@@ -10433,7 +10433,7 @@
         <v>1.2</v>
       </c>
       <c r="T62">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="U62">
         <v>2.05</v>
@@ -10442,7 +10442,7 @@
         <v>1.72</v>
       </c>
       <c r="W62">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X62">
         <v>1.01</v>
@@ -10451,22 +10451,22 @@
         <v>1.08</v>
       </c>
       <c r="Z62">
-        <v>6.64</v>
+        <v>6.25</v>
       </c>
       <c r="AA62">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AB62">
         <v>2.9</v>
       </c>
       <c r="AC62">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AD62">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AE62">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AF62">
         <v>1.67</v>
@@ -10488,7 +10488,7 @@
         <v>1.04</v>
       </c>
       <c r="AK62">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="O65">
         <v>3.3</v>
       </c>
       <c r="P65">
-        <v>3.2</v>
+        <v>3.29</v>
       </c>
       <c r="Q65">
         <v>2.63</v>
@@ -10946,7 +10946,7 @@
         <v>1.8</v>
       </c>
       <c r="AB65">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AC65">
         <v>3.04</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.65</v>
+        <v>1.73</v>
       </c>
       <c r="O66">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="P66">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="Q66">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="R66">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="S66">
-        <v>1.49</v>
+        <v>1.29</v>
       </c>
       <c r="T66">
-        <v>2.39</v>
+        <v>3.46</v>
       </c>
       <c r="U66">
-        <v>3.1</v>
+        <v>2.33</v>
       </c>
       <c r="V66">
-        <v>1.3</v>
+        <v>1.52</v>
       </c>
       <c r="W66">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X66">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="Z66">
-        <v>2.75</v>
+        <v>4.4</v>
       </c>
       <c r="AA66">
-        <v>2.3</v>
+        <v>1.64</v>
       </c>
       <c r="AB66">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="AC66">
-        <v>4.15</v>
+        <v>2.7</v>
       </c>
       <c r="AD66">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AE66">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="AF66">
-        <v>1.94</v>
+        <v>1.62</v>
       </c>
       <c r="AG66">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AK66">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,80 +11230,80 @@
         </is>
       </c>
       <c r="N67">
+        <v>2.59</v>
+      </c>
+      <c r="O67">
+        <v>3</v>
+      </c>
+      <c r="P67">
         <v>2.6</v>
       </c>
-      <c r="O67">
-        <v>3.2</v>
-      </c>
-      <c r="P67">
-        <v>2.5</v>
-      </c>
       <c r="Q67">
-        <v>3.02</v>
+        <v>3.4</v>
       </c>
       <c r="R67">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="S67">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="T67">
-        <v>2.8</v>
+        <v>2.39</v>
       </c>
       <c r="U67">
-        <v>2.66</v>
+        <v>3.1</v>
       </c>
       <c r="V67">
+        <v>1.3</v>
+      </c>
+      <c r="W67">
+        <v>1.04</v>
+      </c>
+      <c r="X67">
+        <v>1.04</v>
+      </c>
+      <c r="Y67">
+        <v>1.41</v>
+      </c>
+      <c r="Z67">
+        <v>2.75</v>
+      </c>
+      <c r="AA67">
+        <v>2.3</v>
+      </c>
+      <c r="AB67">
+        <v>1.6</v>
+      </c>
+      <c r="AC67">
+        <v>4.15</v>
+      </c>
+      <c r="AD67">
+        <v>1.17</v>
+      </c>
+      <c r="AE67">
+        <v>1.02</v>
+      </c>
+      <c r="AF67">
+        <v>1.94</v>
+      </c>
+      <c r="AG67">
+        <v>1.77</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ67">
         <v>1.36</v>
       </c>
-      <c r="W67">
-        <v>1.08</v>
-      </c>
-      <c r="X67">
-        <v>1</v>
-      </c>
-      <c r="Y67">
-        <v>1.28</v>
-      </c>
-      <c r="Z67">
-        <v>3.4</v>
-      </c>
-      <c r="AA67">
-        <v>1.93</v>
-      </c>
-      <c r="AB67">
-        <v>1.81</v>
-      </c>
-      <c r="AC67">
-        <v>3.4</v>
-      </c>
-      <c r="AD67">
-        <v>1.29</v>
-      </c>
-      <c r="AE67">
-        <v>1.06</v>
-      </c>
-      <c r="AF67">
-        <v>1.71</v>
-      </c>
-      <c r="AG67">
-        <v>2.02</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ67">
-        <v>1.44</v>
-      </c>
       <c r="AK67">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11396,7 +11396,7 @@
         <v>2.15</v>
       </c>
       <c r="O68">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="P68">
         <v>2.99</v>
@@ -11405,7 +11405,7 @@
         <v>2.69</v>
       </c>
       <c r="R68">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S68">
         <v>1.36</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.73</v>
+        <v>2.6</v>
       </c>
       <c r="O69">
-        <v>3.98</v>
+        <v>3.25</v>
       </c>
       <c r="P69">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="Q69">
-        <v>2.25</v>
+        <v>3.02</v>
       </c>
       <c r="R69">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S69">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="T69">
-        <v>3.46</v>
+        <v>2.66</v>
       </c>
       <c r="U69">
-        <v>2.33</v>
+        <v>2.66</v>
       </c>
       <c r="V69">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="W69">
         <v>1.08</v>
       </c>
       <c r="X69">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y69">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="Z69">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="AA69">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="AB69">
-        <v>2.15</v>
+        <v>1.81</v>
       </c>
       <c r="AC69">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="AD69">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="AE69">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AF69">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AG69">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="AK69">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -13023,7 +13023,7 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="O78">
         <v>3.4</v>
@@ -13035,7 +13035,7 @@
         <v>2.41</v>
       </c>
       <c r="R78">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S78">
         <v>1.34</v>
@@ -13192,7 +13192,7 @@
         <v>3.6</v>
       </c>
       <c r="P79">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="Q79">
         <v>4.4</v>
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="O81">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="P81">
-        <v>2.89</v>
+        <v>2.93</v>
       </c>
       <c r="Q81">
         <v>2.77</v>
@@ -13678,7 +13678,7 @@
         <v>2.2</v>
       </c>
       <c r="O82">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P82">
         <v>2.75</v>
@@ -13687,7 +13687,7 @@
         <v>2.8</v>
       </c>
       <c r="R82">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S82">
         <v>1.3</v>
@@ -13859,13 +13859,13 @@
         <v>3</v>
       </c>
       <c r="U83">
-        <v>2.71</v>
+        <v>2.59</v>
       </c>
       <c r="V83">
         <v>1.4</v>
       </c>
       <c r="W83">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X83">
         <v>1</v>
@@ -13874,7 +13874,7 @@
         <v>1.25</v>
       </c>
       <c r="Z83">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA83">
         <v>1.9</v>
@@ -13892,10 +13892,10 @@
         <v>1.08</v>
       </c>
       <c r="AF83">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AG83">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>3.2</v>
       </c>
       <c r="P85">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="Q85">
         <v>2.97</v>
@@ -14330,10 +14330,10 @@
         <v>3.01</v>
       </c>
       <c r="O86">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P86">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="Q86">
         <v>3.58</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.3</v>
+        <v>3.15</v>
       </c>
       <c r="O92">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P92">
-        <v>2.55</v>
+        <v>1.96</v>
       </c>
       <c r="Q92">
+        <v>3.9</v>
+      </c>
+      <c r="R92">
+        <v>2.16</v>
+      </c>
+      <c r="S92">
+        <v>1.31</v>
+      </c>
+      <c r="T92">
+        <v>3.1</v>
+      </c>
+      <c r="U92">
+        <v>2.63</v>
+      </c>
+      <c r="V92">
+        <v>1.44</v>
+      </c>
+      <c r="W92">
+        <v>1.11</v>
+      </c>
+      <c r="X92">
+        <v>1.03</v>
+      </c>
+      <c r="Y92">
+        <v>1.2</v>
+      </c>
+      <c r="Z92">
+        <v>3.7</v>
+      </c>
+      <c r="AA92">
+        <v>1.75</v>
+      </c>
+      <c r="AB92">
+        <v>1.98</v>
+      </c>
+      <c r="AC92">
         <v>2.8</v>
       </c>
-      <c r="R92">
-        <v>2.46</v>
-      </c>
-      <c r="S92">
-        <v>1.22</v>
-      </c>
-      <c r="T92">
-        <v>3.52</v>
-      </c>
-      <c r="U92">
-        <v>2.15</v>
-      </c>
-      <c r="V92">
-        <v>1.6</v>
-      </c>
-      <c r="W92">
-        <v>1.15</v>
-      </c>
-      <c r="X92">
-        <v>1.01</v>
-      </c>
-      <c r="Y92">
-        <v>1.14</v>
-      </c>
-      <c r="Z92">
-        <v>5.5</v>
-      </c>
-      <c r="AA92">
-        <v>1.53</v>
-      </c>
-      <c r="AB92">
-        <v>2.4</v>
-      </c>
-      <c r="AC92">
-        <v>2.3</v>
-      </c>
       <c r="AD92">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="AE92">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AF92">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AG92">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AK92">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>3.15</v>
+        <v>2.3</v>
       </c>
       <c r="O93">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P93">
-        <v>1.96</v>
+        <v>2.55</v>
       </c>
       <c r="Q93">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="R93">
-        <v>2.16</v>
+        <v>2.46</v>
       </c>
       <c r="S93">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="T93">
-        <v>3.1</v>
+        <v>3.52</v>
       </c>
       <c r="U93">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="V93">
+        <v>1.6</v>
+      </c>
+      <c r="W93">
+        <v>1.15</v>
+      </c>
+      <c r="X93">
+        <v>1.01</v>
+      </c>
+      <c r="Y93">
+        <v>1.14</v>
+      </c>
+      <c r="Z93">
+        <v>5.5</v>
+      </c>
+      <c r="AA93">
+        <v>1.53</v>
+      </c>
+      <c r="AB93">
+        <v>2.4</v>
+      </c>
+      <c r="AC93">
+        <v>2.3</v>
+      </c>
+      <c r="AD93">
+        <v>1.6</v>
+      </c>
+      <c r="AE93">
+        <v>1.22</v>
+      </c>
+      <c r="AF93">
         <v>1.44</v>
       </c>
-      <c r="W93">
-        <v>1.11</v>
-      </c>
-      <c r="X93">
-        <v>1.03</v>
-      </c>
-      <c r="Y93">
-        <v>1.2</v>
-      </c>
-      <c r="Z93">
-        <v>3.7</v>
-      </c>
-      <c r="AA93">
-        <v>1.75</v>
-      </c>
-      <c r="AB93">
-        <v>1.98</v>
-      </c>
-      <c r="AC93">
-        <v>2.8</v>
-      </c>
-      <c r="AD93">
-        <v>1.41</v>
-      </c>
-      <c r="AE93">
-        <v>1.08</v>
-      </c>
-      <c r="AF93">
-        <v>1.62</v>
-      </c>
       <c r="AG93">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AK93">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15957,13 +15957,13 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="O96">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P96">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="Q96">
         <v>3.02</v>
@@ -16316,7 +16316,7 @@
         <v>1.01</v>
       </c>
       <c r="Y98">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z98">
         <v>3.34</v>
@@ -16452,7 +16452,7 @@
         <v>3.48</v>
       </c>
       <c r="P99">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="Q99">
         <v>3.3</v>
@@ -16516,7 +16516,7 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AK99">
         <v>1.36</v>
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="O100">
         <v>3.2</v>
       </c>
       <c r="P100">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="Q100">
         <v>2.52</v>
@@ -16645,7 +16645,7 @@
         <v>1.4</v>
       </c>
       <c r="Z100">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="AA100">
         <v>2.3</v>
@@ -16654,10 +16654,10 @@
         <v>1.61</v>
       </c>
       <c r="AC100">
-        <v>4.2</v>
+        <v>4.18</v>
       </c>
       <c r="AD100">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE100">
         <v>1.02</v>
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="O104">
         <v>3.8</v>
       </c>
       <c r="P104">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="Q104">
         <v>2.09</v>
@@ -17300,10 +17300,10 @@
         <v>6.1</v>
       </c>
       <c r="AA104">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AB104">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AC104">
         <v>1.99</v>
@@ -17759,16 +17759,16 @@
         <v>2.75</v>
       </c>
       <c r="Q107">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R107">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="S107">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="T107">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="U107">
         <v>3.82</v>

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -3898,16 +3898,16 @@
         <v>1.12</v>
       </c>
       <c r="O22">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
       <c r="P22">
-        <v>15</v>
+        <v>13.3</v>
       </c>
       <c r="Q22">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="R22">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="S22">
         <v>1.17</v>
@@ -3916,7 +3916,7 @@
         <v>4.4</v>
       </c>
       <c r="U22">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="V22">
         <v>1.91</v>
@@ -3940,10 +3940,10 @@
         <v>3.4</v>
       </c>
       <c r="AC22">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AD22">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AE22">
         <v>1.4</v>
@@ -4058,25 +4058,25 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="O23">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="P23">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="Q23">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R23">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="S23">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="T23">
-        <v>2.51</v>
+        <v>2.57</v>
       </c>
       <c r="U23">
         <v>3.2</v>
@@ -4088,34 +4088,34 @@
         <v>1.03</v>
       </c>
       <c r="X23">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y23">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z23">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AA23">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AB23">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AC23">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AD23">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AE23">
         <v>1.04</v>
       </c>
       <c r="AF23">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG23">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="O24">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P24">
-        <v>4.05</v>
+        <v>4.09</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -5109,7 +5109,7 @@
         <v>2.55</v>
       </c>
       <c r="AK29">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5205,19 +5205,19 @@
         <v>3</v>
       </c>
       <c r="P30">
-        <v>4.68</v>
+        <v>4.55</v>
       </c>
       <c r="Q30">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="R30">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="S30">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="T30">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="U30">
         <v>3.5</v>
@@ -5226,7 +5226,7 @@
         <v>1.22</v>
       </c>
       <c r="W30">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X30">
         <v>1.07</v>
@@ -5241,7 +5241,7 @@
         <v>2.43</v>
       </c>
       <c r="AB30">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AC30">
         <v>4.75</v>
@@ -5253,10 +5253,10 @@
         <v>1.01</v>
       </c>
       <c r="AF30">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AG30">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AK30">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="O32">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="P32">
-        <v>3.62</v>
+        <v>2.75</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5875,7 +5875,7 @@
         <v>2.88</v>
       </c>
       <c r="V34">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W34">
         <v>1.04</v>
@@ -6017,7 +6017,7 @@
         <v>1.63</v>
       </c>
       <c r="O35">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P35">
         <v>4.8</v>
@@ -6071,7 +6071,7 @@
         <v>1.8</v>
       </c>
       <c r="AG35">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK35">
         <v>2.15</v>
@@ -6382,7 +6382,7 @@
         <v>1.4</v>
       </c>
       <c r="AB37">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AC37">
         <v>2.04</v>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="N38">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="O38">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="P38">
         <v>1.8</v>
@@ -6518,7 +6518,7 @@
         <v>2.3</v>
       </c>
       <c r="S38">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T38">
         <v>3.1</v>
@@ -6557,7 +6557,7 @@
         <v>1.09</v>
       </c>
       <c r="AF38">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG38">
         <v>2.05</v>
@@ -6699,19 +6699,19 @@
         <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z39">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA39">
         <v>1.61</v>
       </c>
       <c r="AB39">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="AC39">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AD39">
         <v>1.45</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6995,7 +6995,7 @@
         <v>2</v>
       </c>
       <c r="O41">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P41">
         <v>3.05</v>
@@ -7007,13 +7007,13 @@
         <v>2.3</v>
       </c>
       <c r="S41">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T41">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="U41">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="V41">
         <v>1.57</v>
@@ -7028,16 +7028,16 @@
         <v>1.15</v>
       </c>
       <c r="Z41">
-        <v>4.6</v>
+        <v>4.72</v>
       </c>
       <c r="AA41">
         <v>1.57</v>
       </c>
       <c r="AB41">
-        <v>2.19</v>
+        <v>2.31</v>
       </c>
       <c r="AC41">
-        <v>2.36</v>
+        <v>2.51</v>
       </c>
       <c r="AD41">
         <v>1.5</v>
@@ -7164,55 +7164,55 @@
         <v>3.23</v>
       </c>
       <c r="Q42">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="R42">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="S42">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T42">
-        <v>2.58</v>
+        <v>2.15</v>
       </c>
       <c r="U42">
-        <v>3.2</v>
+        <v>2.39</v>
       </c>
       <c r="V42">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="W42">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X42">
         <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="Z42">
-        <v>2.98</v>
+        <v>2.38</v>
       </c>
       <c r="AA42">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AB42">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AC42">
-        <v>3.86</v>
+        <v>3</v>
       </c>
       <c r="AD42">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AE42">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF42">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AG42">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="AK42">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7324,7 +7324,7 @@
         <v>3.1</v>
       </c>
       <c r="P43">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="Q43">
         <v>2.72</v>
@@ -7336,13 +7336,13 @@
         <v>1.44</v>
       </c>
       <c r="T43">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="U43">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="V43">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W43">
         <v>1.02</v>
@@ -7351,22 +7351,22 @@
         <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="Z43">
-        <v>2.81</v>
+        <v>3.01</v>
       </c>
       <c r="AA43">
         <v>2.21</v>
       </c>
       <c r="AB43">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AC43">
-        <v>3.92</v>
+        <v>3.96</v>
       </c>
       <c r="AD43">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AE43">
         <v>1.02</v>
@@ -7391,7 +7391,7 @@
         <v>1.26</v>
       </c>
       <c r="AK43">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7831,7 +7831,7 @@
         <v>2.14</v>
       </c>
       <c r="V46">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W46">
         <v>1.13</v>
@@ -7840,10 +7840,10 @@
         <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z46">
-        <v>5.72</v>
+        <v>5.8</v>
       </c>
       <c r="AA46">
         <v>1.41</v>
@@ -7852,7 +7852,7 @@
         <v>2.52</v>
       </c>
       <c r="AC46">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="AD46">
         <v>1.64</v>
@@ -8003,19 +8003,19 @@
         <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z47">
-        <v>4.33</v>
+        <v>4.37</v>
       </c>
       <c r="AA47">
         <v>1.6</v>
       </c>
       <c r="AB47">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="AC47">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="AD47">
         <v>1.47</v>
@@ -8142,71 +8142,71 @@
         <v>2.69</v>
       </c>
       <c r="Q48">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="R48">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="S48">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T48">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="U48">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="V48">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="W48">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X48">
         <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z48">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AA48">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AB48">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AC48">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="AD48">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE48">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF48">
+        <v>1.5</v>
+      </c>
+      <c r="AG48">
+        <v>2.38</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48">
+        <v>1.25</v>
+      </c>
+      <c r="AK48">
         <v>1.53</v>
-      </c>
-      <c r="AG48">
-        <v>2.3</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ48">
-        <v>1.22</v>
-      </c>
-      <c r="AK48">
-        <v>1.51</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8305,10 +8305,10 @@
         <v>2.15</v>
       </c>
       <c r="Q49">
-        <v>3.46</v>
+        <v>3.56</v>
       </c>
       <c r="R49">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S49">
         <v>1.32</v>
@@ -8317,43 +8317,43 @@
         <v>3.38</v>
       </c>
       <c r="U49">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="V49">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W49">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X49">
         <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z49">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA49">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AB49">
         <v>2.25</v>
       </c>
       <c r="AC49">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="AD49">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE49">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF49">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG49">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="AK49">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8465,25 +8465,25 @@
         <v>3.7</v>
       </c>
       <c r="P50">
-        <v>4.47</v>
+        <v>3.6</v>
       </c>
       <c r="Q50">
         <v>2.15</v>
       </c>
       <c r="R50">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S50">
         <v>1.29</v>
       </c>
       <c r="T50">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U50">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="V50">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W50">
         <v>1.1</v>
@@ -8492,31 +8492,31 @@
         <v>1.03</v>
       </c>
       <c r="Y50">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z50">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AA50">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AB50">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AC50">
-        <v>2.52</v>
+        <v>2.63</v>
       </c>
       <c r="AD50">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE50">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF50">
         <v>1.62</v>
       </c>
       <c r="AG50">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK50">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8628,7 +8628,7 @@
         <v>3.6</v>
       </c>
       <c r="P51">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q51">
         <v>3.62</v>
@@ -8643,16 +8643,16 @@
         <v>3.5</v>
       </c>
       <c r="U51">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V51">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W51">
         <v>1.09</v>
       </c>
       <c r="X51">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y51">
         <v>1.14</v>
@@ -8661,19 +8661,19 @@
         <v>4.35</v>
       </c>
       <c r="AA51">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB51">
         <v>2.3</v>
       </c>
       <c r="AC51">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AD51">
         <v>1.44</v>
       </c>
       <c r="AE51">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AF51">
         <v>1.53</v>
@@ -8791,7 +8791,7 @@
         <v>3.4</v>
       </c>
       <c r="P52">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -8824,10 +8824,10 @@
         <v>0</v>
       </c>
       <c r="AA52">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB52">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC52">
         <v>0</v>
@@ -8990,10 +8990,10 @@
         <v>1.37</v>
       </c>
       <c r="AB53">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="AC53">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AD53">
         <v>1.73</v>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.58</v>
+        <v>1.23</v>
       </c>
       <c r="AK54">
         <v>1.37</v>
@@ -9298,7 +9298,7 @@
         <v>2.04</v>
       </c>
       <c r="V55">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="W55">
         <v>1.18</v>
@@ -9322,7 +9322,7 @@
         <v>1.83</v>
       </c>
       <c r="AD55">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AE55">
         <v>1.38</v>
@@ -9766,10 +9766,10 @@
         <v>2</v>
       </c>
       <c r="O58">
-        <v>3.66</v>
+        <v>3.55</v>
       </c>
       <c r="P58">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q58">
         <v>2.56</v>
@@ -9793,13 +9793,13 @@
         <v>1.1</v>
       </c>
       <c r="X58">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z58">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA58">
         <v>1.78</v>
@@ -9808,7 +9808,7 @@
         <v>2.14</v>
       </c>
       <c r="AC58">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AD58">
         <v>1.38</v>
@@ -9817,10 +9817,10 @@
         <v>1.12</v>
       </c>
       <c r="AF58">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG58">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9965,13 +9965,13 @@
         <v>4.5</v>
       </c>
       <c r="AA59">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AB59">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="AC59">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="AD59">
         <v>1.53</v>
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="N60">
-        <v>5.71</v>
+        <v>5</v>
       </c>
       <c r="O60">
         <v>4.45</v>
@@ -10134,7 +10134,7 @@
         <v>2.42</v>
       </c>
       <c r="AC60">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="AD60">
         <v>1.59</v>
@@ -10143,10 +10143,10 @@
         <v>1.19</v>
       </c>
       <c r="AF60">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG60">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10415,31 +10415,31 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="O62">
         <v>5.25</v>
       </c>
       <c r="P62">
-        <v>7</v>
+        <v>9.08</v>
       </c>
       <c r="Q62">
         <v>1.64</v>
       </c>
       <c r="R62">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="S62">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T62">
         <v>4.5</v>
       </c>
       <c r="U62">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="V62">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W62">
         <v>1.19</v>
@@ -10448,7 +10448,7 @@
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z62">
         <v>6.25</v>
@@ -10457,10 +10457,10 @@
         <v>1.33</v>
       </c>
       <c r="AB62">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AC62">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AD62">
         <v>1.79</v>
@@ -10485,7 +10485,7 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AK62">
         <v>3.4</v>
@@ -10747,7 +10747,7 @@
         <v>3.6</v>
       </c>
       <c r="P64">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="Q64">
         <v>2.74</v>
@@ -10765,7 +10765,7 @@
         <v>2.2</v>
       </c>
       <c r="V64">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W64">
         <v>1.14</v>
@@ -10949,7 +10949,7 @@
         <v>2</v>
       </c>
       <c r="AC65">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="AD65">
         <v>1.32</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.73</v>
+        <v>2.59</v>
       </c>
       <c r="O66">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="P66">
-        <v>3.9</v>
+        <v>2.59</v>
       </c>
       <c r="Q66">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="R66">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="S66">
-        <v>1.29</v>
+        <v>1.49</v>
       </c>
       <c r="T66">
-        <v>3.46</v>
+        <v>2.39</v>
       </c>
       <c r="U66">
-        <v>2.33</v>
+        <v>3.1</v>
       </c>
       <c r="V66">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="W66">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X66">
+        <v>1.04</v>
+      </c>
+      <c r="Y66">
+        <v>1.42</v>
+      </c>
+      <c r="Z66">
+        <v>2.75</v>
+      </c>
+      <c r="AA66">
+        <v>2.3</v>
+      </c>
+      <c r="AB66">
+        <v>1.61</v>
+      </c>
+      <c r="AC66">
+        <v>4.15</v>
+      </c>
+      <c r="AD66">
+        <v>1.17</v>
+      </c>
+      <c r="AE66">
         <v>1.02</v>
       </c>
-      <c r="Y66">
-        <v>1.2</v>
-      </c>
-      <c r="Z66">
-        <v>4.4</v>
-      </c>
-      <c r="AA66">
-        <v>1.64</v>
-      </c>
-      <c r="AB66">
-        <v>2.15</v>
-      </c>
-      <c r="AC66">
-        <v>2.7</v>
-      </c>
-      <c r="AD66">
-        <v>1.43</v>
-      </c>
-      <c r="AE66">
-        <v>1.14</v>
-      </c>
       <c r="AF66">
-        <v>1.62</v>
+        <v>1.94</v>
       </c>
       <c r="AG66">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AK66">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="O67">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P67">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q67">
+        <v>3.02</v>
+      </c>
+      <c r="R67">
+        <v>2.1</v>
+      </c>
+      <c r="S67">
+        <v>1.37</v>
+      </c>
+      <c r="T67">
+        <v>2.66</v>
+      </c>
+      <c r="U67">
+        <v>2.66</v>
+      </c>
+      <c r="V67">
+        <v>1.36</v>
+      </c>
+      <c r="W67">
+        <v>1.08</v>
+      </c>
+      <c r="X67">
+        <v>1</v>
+      </c>
+      <c r="Y67">
+        <v>1.28</v>
+      </c>
+      <c r="Z67">
         <v>3.4</v>
       </c>
-      <c r="R67">
-        <v>1.95</v>
-      </c>
-      <c r="S67">
-        <v>1.49</v>
-      </c>
-      <c r="T67">
-        <v>2.39</v>
-      </c>
-      <c r="U67">
-        <v>3.1</v>
-      </c>
-      <c r="V67">
-        <v>1.3</v>
-      </c>
-      <c r="W67">
-        <v>1.04</v>
-      </c>
-      <c r="X67">
-        <v>1.04</v>
-      </c>
-      <c r="Y67">
-        <v>1.41</v>
-      </c>
-      <c r="Z67">
-        <v>2.75</v>
-      </c>
       <c r="AA67">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="AB67">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="AC67">
-        <v>4.15</v>
+        <v>3.4</v>
       </c>
       <c r="AD67">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AE67">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF67">
-        <v>1.94</v>
+        <v>1.71</v>
       </c>
       <c r="AG67">
-        <v>1.77</v>
+        <v>2.02</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AK67">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11399,7 +11399,7 @@
         <v>3</v>
       </c>
       <c r="P68">
-        <v>2.99</v>
+        <v>3.4</v>
       </c>
       <c r="Q68">
         <v>2.69</v>
@@ -11411,7 +11411,7 @@
         <v>1.36</v>
       </c>
       <c r="T68">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="U68">
         <v>2.8</v>
@@ -11423,7 +11423,7 @@
         <v>1.05</v>
       </c>
       <c r="X68">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y68">
         <v>1.28</v>
@@ -11432,13 +11432,13 @@
         <v>3.08</v>
       </c>
       <c r="AA68">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AB68">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC68">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AD68">
         <v>1.25</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,80 +11556,80 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.6</v>
+        <v>1.73</v>
       </c>
       <c r="O69">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="P69">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="Q69">
-        <v>3.02</v>
+        <v>2.25</v>
       </c>
       <c r="R69">
+        <v>2.2</v>
+      </c>
+      <c r="S69">
+        <v>1.29</v>
+      </c>
+      <c r="T69">
+        <v>3.46</v>
+      </c>
+      <c r="U69">
+        <v>2.33</v>
+      </c>
+      <c r="V69">
+        <v>1.52</v>
+      </c>
+      <c r="W69">
+        <v>1.11</v>
+      </c>
+      <c r="X69">
+        <v>1.02</v>
+      </c>
+      <c r="Y69">
+        <v>1.21</v>
+      </c>
+      <c r="Z69">
+        <v>4.4</v>
+      </c>
+      <c r="AA69">
+        <v>1.65</v>
+      </c>
+      <c r="AB69">
+        <v>2.15</v>
+      </c>
+      <c r="AC69">
+        <v>2.7</v>
+      </c>
+      <c r="AD69">
+        <v>1.43</v>
+      </c>
+      <c r="AE69">
+        <v>1.14</v>
+      </c>
+      <c r="AF69">
+        <v>1.62</v>
+      </c>
+      <c r="AG69">
+        <v>2.15</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ69">
+        <v>1.2</v>
+      </c>
+      <c r="AK69">
         <v>2.1</v>
-      </c>
-      <c r="S69">
-        <v>1.37</v>
-      </c>
-      <c r="T69">
-        <v>2.66</v>
-      </c>
-      <c r="U69">
-        <v>2.66</v>
-      </c>
-      <c r="V69">
-        <v>1.36</v>
-      </c>
-      <c r="W69">
-        <v>1.08</v>
-      </c>
-      <c r="X69">
-        <v>1</v>
-      </c>
-      <c r="Y69">
-        <v>1.28</v>
-      </c>
-      <c r="Z69">
-        <v>3.4</v>
-      </c>
-      <c r="AA69">
-        <v>1.93</v>
-      </c>
-      <c r="AB69">
-        <v>1.81</v>
-      </c>
-      <c r="AC69">
-        <v>3.4</v>
-      </c>
-      <c r="AD69">
-        <v>1.29</v>
-      </c>
-      <c r="AE69">
-        <v>1.06</v>
-      </c>
-      <c r="AF69">
-        <v>1.71</v>
-      </c>
-      <c r="AG69">
-        <v>2.02</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ69">
-        <v>1.44</v>
-      </c>
-      <c r="AK69">
-        <v>1.44</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11903,7 +11903,7 @@
         <v>3.55</v>
       </c>
       <c r="U71">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="V71">
         <v>1.67</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.69</v>
+        <v>2.05</v>
       </c>
       <c r="O74">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="P74">
-        <v>4.04</v>
+        <v>2.7</v>
       </c>
       <c r="Q74">
-        <v>2.13</v>
+        <v>2.33</v>
       </c>
       <c r="R74">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="S74">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T74">
         <v>4.5</v>
       </c>
       <c r="U74">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="V74">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="W74">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X74">
         <v>1.01</v>
       </c>
       <c r="Y74">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Z74">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AA74">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AB74">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="AC74">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AD74">
-        <v>1.86</v>
+        <v>1.99</v>
       </c>
       <c r="AE74">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AF74">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AG74">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK74">
-        <v>2.07</v>
+        <v>1.65</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.05</v>
+        <v>1.69</v>
       </c>
       <c r="O75">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="P75">
-        <v>2.7</v>
+        <v>4.04</v>
       </c>
       <c r="Q75">
-        <v>2.33</v>
+        <v>2.13</v>
       </c>
       <c r="R75">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="S75">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T75">
         <v>4.5</v>
       </c>
       <c r="U75">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="V75">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="W75">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="X75">
         <v>1.01</v>
       </c>
       <c r="Y75">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Z75">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AA75">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AB75">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="AC75">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AD75">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="AE75">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AF75">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AG75">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK75">
-        <v>1.65</v>
+        <v>2.07</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12718,7 +12718,7 @@
         <v>3.2</v>
       </c>
       <c r="U76">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="V76">
         <v>1.45</v>
@@ -12736,7 +12736,7 @@
         <v>3.8</v>
       </c>
       <c r="AA76">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AB76">
         <v>1.93</v>
@@ -12863,55 +12863,55 @@
         <v>2.1</v>
       </c>
       <c r="O77">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P77">
         <v>2.9</v>
       </c>
       <c r="Q77">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="R77">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S77">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T77">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="U77">
         <v>2.4</v>
       </c>
       <c r="V77">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W77">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X77">
         <v>1.03</v>
       </c>
       <c r="Y77">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z77">
-        <v>3.72</v>
+        <v>3.84</v>
       </c>
       <c r="AA77">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AB77">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AC77">
         <v>2.75</v>
       </c>
       <c r="AD77">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE77">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF77">
         <v>1.57</v>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK77">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13029,7 +13029,7 @@
         <v>3.4</v>
       </c>
       <c r="P78">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="Q78">
         <v>2.41</v>
@@ -13515,10 +13515,10 @@
         <v>2.26</v>
       </c>
       <c r="O81">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P81">
-        <v>2.93</v>
+        <v>2.97</v>
       </c>
       <c r="Q81">
         <v>2.77</v>
@@ -13533,19 +13533,19 @@
         <v>3.25</v>
       </c>
       <c r="U81">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="V81">
         <v>1.51</v>
       </c>
       <c r="W81">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X81">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y81">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z81">
         <v>4.4</v>
@@ -13557,7 +13557,7 @@
         <v>2.15</v>
       </c>
       <c r="AC81">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="AD81">
         <v>1.43</v>
@@ -13678,7 +13678,7 @@
         <v>2.2</v>
       </c>
       <c r="O82">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P82">
         <v>2.75</v>
@@ -13696,7 +13696,7 @@
         <v>3.32</v>
       </c>
       <c r="U82">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="V82">
         <v>1.52</v>
@@ -13859,7 +13859,7 @@
         <v>3</v>
       </c>
       <c r="U83">
-        <v>2.59</v>
+        <v>2.72</v>
       </c>
       <c r="V83">
         <v>1.4</v>
@@ -13892,7 +13892,7 @@
         <v>1.08</v>
       </c>
       <c r="AF83">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG83">
         <v>2.1</v>
@@ -14058,7 +14058,7 @@
         <v>1.36</v>
       </c>
       <c r="AG84">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14197,16 +14197,16 @@
         <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z85">
         <v>3.08</v>
       </c>
       <c r="AA85">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB85">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC85">
         <v>2.75</v>
@@ -14221,7 +14221,7 @@
         <v>1.6</v>
       </c>
       <c r="AG85">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.87</v>
+        <v>1.5</v>
       </c>
       <c r="O88">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="P88">
-        <v>2.15</v>
+        <v>4.8</v>
       </c>
       <c r="Q88">
-        <v>3.25</v>
+        <v>1.95</v>
       </c>
       <c r="R88">
-        <v>2.25</v>
+        <v>2.73</v>
       </c>
       <c r="S88">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="T88">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="U88">
-        <v>2.62</v>
+        <v>2</v>
       </c>
       <c r="V88">
+        <v>1.73</v>
+      </c>
+      <c r="W88">
+        <v>1.17</v>
+      </c>
+      <c r="X88">
+        <v>1.01</v>
+      </c>
+      <c r="Y88">
+        <v>1.1</v>
+      </c>
+      <c r="Z88">
+        <v>5.2</v>
+      </c>
+      <c r="AA88">
         <v>1.4</v>
       </c>
-      <c r="W88">
-        <v>1.1</v>
-      </c>
-      <c r="X88">
-        <v>1.03</v>
-      </c>
-      <c r="Y88">
+      <c r="AB88">
+        <v>2.56</v>
+      </c>
+      <c r="AC88">
+        <v>2.11</v>
+      </c>
+      <c r="AD88">
+        <v>1.67</v>
+      </c>
+      <c r="AE88">
         <v>1.25</v>
       </c>
-      <c r="Z88">
-        <v>3.6</v>
-      </c>
-      <c r="AA88">
-        <v>1.88</v>
-      </c>
-      <c r="AB88">
-        <v>1.83</v>
-      </c>
-      <c r="AC88">
-        <v>3.14</v>
-      </c>
-      <c r="AD88">
-        <v>1.27</v>
-      </c>
-      <c r="AE88">
-        <v>1.06</v>
-      </c>
       <c r="AF88">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="AG88">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK88">
-        <v>1.32</v>
+        <v>2.4</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.5</v>
+        <v>2.87</v>
       </c>
       <c r="O89">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="P89">
-        <v>4.8</v>
+        <v>2.15</v>
       </c>
       <c r="Q89">
-        <v>1.95</v>
+        <v>3.25</v>
       </c>
       <c r="R89">
-        <v>2.73</v>
+        <v>2.25</v>
       </c>
       <c r="S89">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="T89">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="U89">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="V89">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="W89">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X89">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y89">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="Z89">
-        <v>5.2</v>
+        <v>3.6</v>
       </c>
       <c r="AA89">
-        <v>1.4</v>
+        <v>1.88</v>
       </c>
       <c r="AB89">
-        <v>2.56</v>
+        <v>1.83</v>
       </c>
       <c r="AC89">
-        <v>2.11</v>
+        <v>3.14</v>
       </c>
       <c r="AD89">
-        <v>1.67</v>
+        <v>1.27</v>
       </c>
       <c r="AE89">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AF89">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="AG89">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK89">
-        <v>2.4</v>
+        <v>1.32</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -15800,7 +15800,7 @@
         <v>3.75</v>
       </c>
       <c r="P95">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="Q95">
         <v>3.02</v>
@@ -15848,7 +15848,7 @@
         <v>1.25</v>
       </c>
       <c r="AF95">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG95">
         <v>3</v>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK95">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15957,10 +15957,10 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="O96">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P96">
         <v>2.42</v>
@@ -16283,10 +16283,10 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="O98">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="P98">
         <v>3.46</v>
@@ -16304,7 +16304,7 @@
         <v>2.92</v>
       </c>
       <c r="U98">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="V98">
         <v>1.41</v>
@@ -16319,7 +16319,7 @@
         <v>1.29</v>
       </c>
       <c r="Z98">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="AA98">
         <v>1.98</v>
@@ -16446,10 +16446,10 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="O99">
-        <v>3.48</v>
+        <v>3.6</v>
       </c>
       <c r="P99">
         <v>2.38</v>
@@ -16467,7 +16467,7 @@
         <v>3.1</v>
       </c>
       <c r="U99">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="V99">
         <v>1.45</v>
@@ -16491,16 +16491,16 @@
         <v>1.95</v>
       </c>
       <c r="AC99">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="AD99">
         <v>1.36</v>
       </c>
       <c r="AE99">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF99">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG99">
         <v>2.15</v>
@@ -16609,10 +16609,10 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="O100">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P100">
         <v>3.6</v>
@@ -16654,7 +16654,7 @@
         <v>1.61</v>
       </c>
       <c r="AC100">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
       <c r="AD100">
         <v>1.21</v>
@@ -17261,19 +17261,19 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="O104">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P104">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="Q104">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="R104">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="S104">
         <v>1.19</v>
@@ -17282,10 +17282,10 @@
         <v>4.2</v>
       </c>
       <c r="U104">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="V104">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="W104">
         <v>1.19</v>
@@ -17297,7 +17297,7 @@
         <v>1.06</v>
       </c>
       <c r="Z104">
-        <v>6.1</v>
+        <v>6.15</v>
       </c>
       <c r="AA104">
         <v>1.34</v>
@@ -17309,16 +17309,16 @@
         <v>1.99</v>
       </c>
       <c r="AD104">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AE104">
         <v>1.3</v>
       </c>
       <c r="AF104">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AG104">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AK104">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.65</v>
+        <v>2.35</v>
       </c>
       <c r="O107">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="P107">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="Q107">
         <v>3.1</v>
@@ -18130,7 +18130,7 @@
         <v>1.03</v>
       </c>
       <c r="AF109">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AG109">
         <v>1.52</v>
@@ -18278,10 +18278,10 @@
         <v>0</v>
       </c>
       <c r="AA110">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AB110">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="AC110">
         <v>0</v>

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -635,10 +635,10 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="O2">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="P2">
         <v>2.95</v>
@@ -653,7 +653,7 @@
         <v>1.35</v>
       </c>
       <c r="T2">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U2">
         <v>2.75</v>
@@ -665,16 +665,16 @@
         <v>1.08</v>
       </c>
       <c r="X2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y2">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z2">
         <v>3.34</v>
       </c>
       <c r="AA2">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AB2">
         <v>1.84</v>
@@ -689,7 +689,7 @@
         <v>1.07</v>
       </c>
       <c r="AF2">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG2">
         <v>2.05</v>
@@ -798,16 +798,16 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O3">
-        <v>3.53</v>
+        <v>3.55</v>
       </c>
       <c r="P3">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q3">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="R3">
         <v>2.3</v>
@@ -852,7 +852,7 @@
         <v>1.17</v>
       </c>
       <c r="AF3">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG3">
         <v>2.3</v>
@@ -979,7 +979,7 @@
         <v>1.37</v>
       </c>
       <c r="T4">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U4">
         <v>2.74</v>
@@ -1012,7 +1012,7 @@
         <v>1.29</v>
       </c>
       <c r="AE4">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF4">
         <v>1.73</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1450,16 +1450,16 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="O7">
-        <v>3.36</v>
+        <v>3.2</v>
       </c>
       <c r="P7">
-        <v>2.69</v>
+        <v>2.52</v>
       </c>
       <c r="Q7">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="R7">
         <v>2.25</v>
@@ -1489,10 +1489,10 @@
         <v>3.58</v>
       </c>
       <c r="AA7">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AB7">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AC7">
         <v>2.88</v>
@@ -1504,10 +1504,10 @@
         <v>1.08</v>
       </c>
       <c r="AF7">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG7">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AK7">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="O10">
         <v>3.25</v>
@@ -1957,13 +1957,13 @@
         <v>1.33</v>
       </c>
       <c r="T10">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="U10">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="V10">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W10">
         <v>1.1</v>
@@ -1975,10 +1975,10 @@
         <v>1.25</v>
       </c>
       <c r="Z10">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AA10">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AB10">
         <v>1.88</v>
@@ -1990,13 +1990,13 @@
         <v>1.36</v>
       </c>
       <c r="AE10">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF10">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG10">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2141,10 +2141,10 @@
         <v>0</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC11">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2304,10 +2304,10 @@
         <v>0</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC12">
         <v>0</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3445,10 +3445,10 @@
         <v>0</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC19">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="O20">
         <v>3.75</v>
       </c>
       <c r="P20">
-        <v>3.12</v>
+        <v>2.93</v>
       </c>
       <c r="Q20">
         <v>2.45</v>
@@ -3599,34 +3599,34 @@
         <v>1.16</v>
       </c>
       <c r="X20">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z20">
-        <v>5.35</v>
+        <v>6.5</v>
       </c>
       <c r="AA20">
         <v>1.42</v>
       </c>
       <c r="AB20">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="AC20">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AD20">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AE20">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AF20">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AG20">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3732,31 +3732,31 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="O21">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="P21">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="Q21">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="R21">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="S21">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T21">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U21">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V21">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W21">
         <v>1.13</v>
@@ -3765,31 +3765,31 @@
         <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z21">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
       <c r="AA21">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AB21">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AC21">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="AD21">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE21">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF21">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG21">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK21">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3898,7 +3898,7 @@
         <v>1.12</v>
       </c>
       <c r="O22">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="P22">
         <v>13.3</v>
@@ -3940,10 +3940,10 @@
         <v>3.4</v>
       </c>
       <c r="AC22">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AD22">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AE22">
         <v>1.4</v>
@@ -4251,34 +4251,34 @@
         <v>1.06</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y24">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z24">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA24">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AB24">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC24">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="AD24">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE24">
         <v>1.07</v>
       </c>
       <c r="AF24">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG24">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q28">
         <v>3.16</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="O29">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="P29">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Q29">
         <v>6.5</v>
@@ -5109,7 +5109,7 @@
         <v>2.55</v>
       </c>
       <c r="AK29">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="O30">
         <v>3</v>
@@ -5272,7 +5272,7 @@
         <v>1.36</v>
       </c>
       <c r="AK30">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5368,7 +5368,7 @@
         <v>3.85</v>
       </c>
       <c r="P31">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5525,61 +5525,61 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="O32">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P32">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="Q32">
         <v>2.86</v>
       </c>
       <c r="R32">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="S32">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T32">
-        <v>2.85</v>
+        <v>2.97</v>
       </c>
       <c r="U32">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="V32">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W32">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z32">
-        <v>3.58</v>
+        <v>4.1</v>
       </c>
       <c r="AA32">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB32">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AC32">
-        <v>2.83</v>
+        <v>2.93</v>
       </c>
       <c r="AD32">
         <v>1.33</v>
       </c>
       <c r="AE32">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF32">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG32">
         <v>2.15</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AK32">
         <v>1.49</v>
@@ -5875,10 +5875,10 @@
         <v>2.88</v>
       </c>
       <c r="V34">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W34">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X34">
         <v>1.02</v>
@@ -6186,55 +6186,55 @@
         <v>2.6</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="O37">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P37">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="Q37">
         <v>2</v>
@@ -6358,7 +6358,7 @@
         <v>1.22</v>
       </c>
       <c r="T37">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="U37">
         <v>2.1</v>
@@ -6373,10 +6373,10 @@
         <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z37">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AA37">
         <v>1.4</v>
@@ -6385,13 +6385,13 @@
         <v>2.75</v>
       </c>
       <c r="AC37">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="AD37">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AE37">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF37">
         <v>1.62</v>
@@ -6696,7 +6696,7 @@
         <v>1.11</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
         <v>1.17</v>
@@ -6832,7 +6832,7 @@
         <v>5</v>
       </c>
       <c r="O40">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="P40">
         <v>1.45</v>
@@ -6850,7 +6850,7 @@
         <v>4</v>
       </c>
       <c r="U40">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="V40">
         <v>1.68</v>
@@ -6865,19 +6865,19 @@
         <v>1.12</v>
       </c>
       <c r="Z40">
-        <v>5.72</v>
+        <v>5.8</v>
       </c>
       <c r="AA40">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AB40">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AC40">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AD40">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AE40">
         <v>1.27</v>
@@ -7013,10 +7013,10 @@
         <v>3.5</v>
       </c>
       <c r="U41">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="V41">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W41">
         <v>1.14</v>
@@ -7209,7 +7209,7 @@
         <v>1.03</v>
       </c>
       <c r="AF42">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AG42">
         <v>1.83</v>
@@ -7327,7 +7327,7 @@
         <v>2.7</v>
       </c>
       <c r="Q43">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="R43">
         <v>1.98</v>
@@ -7810,7 +7810,7 @@
         <v>2.05</v>
       </c>
       <c r="O46">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P46">
         <v>3.1</v>
@@ -7825,13 +7825,13 @@
         <v>1.22</v>
       </c>
       <c r="T46">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U46">
         <v>2.14</v>
       </c>
       <c r="V46">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W46">
         <v>1.13</v>
@@ -7843,7 +7843,7 @@
         <v>1.14</v>
       </c>
       <c r="Z46">
-        <v>5.8</v>
+        <v>5.79</v>
       </c>
       <c r="AA46">
         <v>1.41</v>
@@ -7970,16 +7970,16 @@
         </is>
       </c>
       <c r="N47">
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
       <c r="O47">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="P47">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Q47">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="R47">
         <v>2.5</v>
@@ -7991,10 +7991,10 @@
         <v>3.5</v>
       </c>
       <c r="U47">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="V47">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W47">
         <v>1.13</v>
@@ -8003,31 +8003,31 @@
         <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z47">
-        <v>4.37</v>
+        <v>4.23</v>
       </c>
       <c r="AA47">
         <v>1.6</v>
       </c>
       <c r="AB47">
-        <v>2.24</v>
+        <v>2.19</v>
       </c>
       <c r="AC47">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AD47">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AE47">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF47">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AG47">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
+        <v>2.86</v>
+      </c>
+      <c r="O48">
+        <v>3.55</v>
+      </c>
+      <c r="P48">
+        <v>2.15</v>
+      </c>
+      <c r="Q48">
+        <v>3.56</v>
+      </c>
+      <c r="R48">
         <v>2.3</v>
       </c>
-      <c r="O48">
-        <v>3.4</v>
-      </c>
-      <c r="P48">
-        <v>2.69</v>
-      </c>
-      <c r="Q48">
-        <v>2.88</v>
-      </c>
-      <c r="R48">
+      <c r="S48">
+        <v>1.32</v>
+      </c>
+      <c r="T48">
+        <v>3.38</v>
+      </c>
+      <c r="U48">
+        <v>2.24</v>
+      </c>
+      <c r="V48">
+        <v>1.55</v>
+      </c>
+      <c r="W48">
+        <v>1.11</v>
+      </c>
+      <c r="X48">
+        <v>1.01</v>
+      </c>
+      <c r="Y48">
+        <v>1.17</v>
+      </c>
+      <c r="Z48">
+        <v>4.6</v>
+      </c>
+      <c r="AA48">
+        <v>1.6</v>
+      </c>
+      <c r="AB48">
         <v>2.25</v>
       </c>
-      <c r="S48">
-        <v>1.29</v>
-      </c>
-      <c r="T48">
-        <v>3.3</v>
-      </c>
-      <c r="U48">
-        <v>2.32</v>
-      </c>
-      <c r="V48">
-        <v>1.52</v>
-      </c>
-      <c r="W48">
-        <v>1.13</v>
-      </c>
-      <c r="X48">
-        <v>1.02</v>
-      </c>
-      <c r="Y48">
-        <v>1.18</v>
-      </c>
-      <c r="Z48">
-        <v>4.4</v>
-      </c>
-      <c r="AA48">
-        <v>1.64</v>
-      </c>
-      <c r="AB48">
-        <v>2.09</v>
-      </c>
       <c r="AC48">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AD48">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE48">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF48">
         <v>1.5</v>
       </c>
       <c r="AG48">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="AK48">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.86</v>
+        <v>2.3</v>
       </c>
       <c r="O49">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P49">
-        <v>2.15</v>
+        <v>2.69</v>
       </c>
       <c r="Q49">
-        <v>3.56</v>
+        <v>2.88</v>
       </c>
       <c r="R49">
+        <v>2.25</v>
+      </c>
+      <c r="S49">
+        <v>1.29</v>
+      </c>
+      <c r="T49">
+        <v>3.4</v>
+      </c>
+      <c r="U49">
         <v>2.3</v>
       </c>
-      <c r="S49">
-        <v>1.32</v>
-      </c>
-      <c r="T49">
-        <v>3.38</v>
-      </c>
-      <c r="U49">
-        <v>2.24</v>
-      </c>
       <c r="V49">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="W49">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X49">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z49">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AA49">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AB49">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="AC49">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AD49">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AE49">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF49">
         <v>1.5</v>
       </c>
       <c r="AG49">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="AK49">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8489,7 +8489,7 @@
         <v>1.1</v>
       </c>
       <c r="X50">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
         <v>1.18</v>
@@ -8498,7 +8498,7 @@
         <v>4.4</v>
       </c>
       <c r="AA50">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AB50">
         <v>2.09</v>
@@ -8622,7 +8622,7 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="O51">
         <v>3.6</v>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK51">
         <v>1.35</v>
@@ -8791,7 +8791,7 @@
         <v>3.4</v>
       </c>
       <c r="P52">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -8990,10 +8990,10 @@
         <v>1.37</v>
       </c>
       <c r="AB53">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="AC53">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AD53">
         <v>1.73</v>
@@ -9005,7 +9005,7 @@
         <v>1.44</v>
       </c>
       <c r="AG53">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         <v>1.15</v>
       </c>
       <c r="X54">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
         <v>1.08</v>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.23</v>
+        <v>1.62</v>
       </c>
       <c r="AK54">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="O56">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="P56">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="Q56">
         <v>3.6</v>
@@ -9603,16 +9603,16 @@
         <v>3.4</v>
       </c>
       <c r="O57">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P57">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="Q57">
         <v>4.14</v>
       </c>
       <c r="R57">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="S57">
         <v>1.22</v>
@@ -9766,16 +9766,16 @@
         <v>2</v>
       </c>
       <c r="O58">
-        <v>3.55</v>
+        <v>3.66</v>
       </c>
       <c r="P58">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q58">
         <v>2.56</v>
       </c>
       <c r="R58">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="S58">
         <v>1.28</v>
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK58">
         <v>1.7</v>
@@ -9926,7 +9926,7 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="O59">
         <v>3.6</v>
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AK59">
         <v>1.58</v>
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="N60">
-        <v>5</v>
+        <v>5.71</v>
       </c>
       <c r="O60">
         <v>4.45</v>
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="O61">
         <v>3.5</v>
       </c>
       <c r="P61">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="Q61">
         <v>3.42</v>
@@ -10270,13 +10270,13 @@
         <v>1.3</v>
       </c>
       <c r="T61">
-        <v>3.02</v>
+        <v>3.23</v>
       </c>
       <c r="U61">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="V61">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W61">
         <v>1.07</v>
@@ -10436,10 +10436,10 @@
         <v>4.5</v>
       </c>
       <c r="U62">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V62">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="W62">
         <v>1.19</v>
@@ -10747,10 +10747,10 @@
         <v>3.6</v>
       </c>
       <c r="P64">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="Q64">
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="R64">
         <v>2.5</v>
@@ -10907,7 +10907,7 @@
         <v>2</v>
       </c>
       <c r="O65">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P65">
         <v>3.29</v>
@@ -11070,10 +11070,10 @@
         <v>2.59</v>
       </c>
       <c r="O66">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="P66">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="Q66">
         <v>3.4</v>
@@ -11088,7 +11088,7 @@
         <v>2.39</v>
       </c>
       <c r="U66">
-        <v>3.1</v>
+        <v>3.33</v>
       </c>
       <c r="V66">
         <v>1.3</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="O67">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P67">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q67">
-        <v>3.02</v>
+        <v>2.69</v>
       </c>
       <c r="R67">
         <v>2.1</v>
       </c>
       <c r="S67">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T67">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="U67">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="V67">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W67">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X67">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y67">
         <v>1.28</v>
       </c>
       <c r="Z67">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="AA67">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AB67">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AC67">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD67">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE67">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF67">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AG67">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AK67">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,80 +11393,80 @@
         </is>
       </c>
       <c r="N68">
+        <v>1.72</v>
+      </c>
+      <c r="O68">
+        <v>3.5</v>
+      </c>
+      <c r="P68">
+        <v>3.9</v>
+      </c>
+      <c r="Q68">
+        <v>2.25</v>
+      </c>
+      <c r="R68">
+        <v>2.2</v>
+      </c>
+      <c r="S68">
+        <v>1.29</v>
+      </c>
+      <c r="T68">
+        <v>3.46</v>
+      </c>
+      <c r="U68">
+        <v>2.33</v>
+      </c>
+      <c r="V68">
+        <v>1.52</v>
+      </c>
+      <c r="W68">
+        <v>1.11</v>
+      </c>
+      <c r="X68">
+        <v>1.02</v>
+      </c>
+      <c r="Y68">
+        <v>1.21</v>
+      </c>
+      <c r="Z68">
+        <v>4.4</v>
+      </c>
+      <c r="AA68">
+        <v>1.65</v>
+      </c>
+      <c r="AB68">
         <v>2.15</v>
       </c>
-      <c r="O68">
-        <v>3</v>
-      </c>
-      <c r="P68">
-        <v>3.4</v>
-      </c>
-      <c r="Q68">
-        <v>2.69</v>
-      </c>
-      <c r="R68">
+      <c r="AC68">
+        <v>2.7</v>
+      </c>
+      <c r="AD68">
+        <v>1.43</v>
+      </c>
+      <c r="AE68">
+        <v>1.14</v>
+      </c>
+      <c r="AF68">
+        <v>1.62</v>
+      </c>
+      <c r="AG68">
+        <v>2.15</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ68">
+        <v>1.17</v>
+      </c>
+      <c r="AK68">
         <v>2.1</v>
-      </c>
-      <c r="S68">
-        <v>1.36</v>
-      </c>
-      <c r="T68">
-        <v>2.88</v>
-      </c>
-      <c r="U68">
-        <v>2.8</v>
-      </c>
-      <c r="V68">
-        <v>1.4</v>
-      </c>
-      <c r="W68">
-        <v>1.05</v>
-      </c>
-      <c r="X68">
-        <v>1.04</v>
-      </c>
-      <c r="Y68">
-        <v>1.28</v>
-      </c>
-      <c r="Z68">
-        <v>3.08</v>
-      </c>
-      <c r="AA68">
-        <v>1.96</v>
-      </c>
-      <c r="AB68">
-        <v>1.73</v>
-      </c>
-      <c r="AC68">
-        <v>3.5</v>
-      </c>
-      <c r="AD68">
-        <v>1.25</v>
-      </c>
-      <c r="AE68">
-        <v>1.04</v>
-      </c>
-      <c r="AF68">
-        <v>1.79</v>
-      </c>
-      <c r="AG68">
-        <v>1.92</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ68">
-        <v>1.28</v>
-      </c>
-      <c r="AK68">
-        <v>1.7</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.73</v>
+        <v>2.65</v>
       </c>
       <c r="O69">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P69">
-        <v>3.9</v>
+        <v>2.45</v>
       </c>
       <c r="Q69">
-        <v>2.25</v>
+        <v>3.2</v>
       </c>
       <c r="R69">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S69">
+        <v>1.37</v>
+      </c>
+      <c r="T69">
+        <v>2.64</v>
+      </c>
+      <c r="U69">
+        <v>2.67</v>
+      </c>
+      <c r="V69">
+        <v>1.36</v>
+      </c>
+      <c r="W69">
+        <v>1.08</v>
+      </c>
+      <c r="X69">
+        <v>1</v>
+      </c>
+      <c r="Y69">
         <v>1.29</v>
       </c>
-      <c r="T69">
-        <v>3.46</v>
-      </c>
-      <c r="U69">
-        <v>2.33</v>
-      </c>
-      <c r="V69">
-        <v>1.52</v>
-      </c>
-      <c r="W69">
-        <v>1.11</v>
-      </c>
-      <c r="X69">
-        <v>1.02</v>
-      </c>
-      <c r="Y69">
-        <v>1.21</v>
-      </c>
       <c r="Z69">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="AA69">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="AB69">
-        <v>2.15</v>
+        <v>1.81</v>
       </c>
       <c r="AC69">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="AD69">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="AE69">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AF69">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AG69">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="AK69">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11882,10 +11882,10 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="O71">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="P71">
         <v>4.5</v>
@@ -11903,7 +11903,7 @@
         <v>3.55</v>
       </c>
       <c r="U71">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V71">
         <v>1.67</v>
@@ -11955,7 +11955,7 @@
         <v>1.22</v>
       </c>
       <c r="AK71">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12045,16 +12045,16 @@
         </is>
       </c>
       <c r="N72">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="O72">
         <v>3.5</v>
       </c>
       <c r="P72">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="Q72">
-        <v>3.28</v>
+        <v>3.63</v>
       </c>
       <c r="R72">
         <v>2.4</v>
@@ -12208,10 +12208,10 @@
         </is>
       </c>
       <c r="N73">
-        <v>5.36</v>
+        <v>5</v>
       </c>
       <c r="O73">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="P73">
         <v>1.48</v>
@@ -12220,7 +12220,7 @@
         <v>5</v>
       </c>
       <c r="R73">
-        <v>2.43</v>
+        <v>2.51</v>
       </c>
       <c r="S73">
         <v>1.18</v>
@@ -12229,10 +12229,10 @@
         <v>4.4</v>
       </c>
       <c r="U73">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="V73">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="W73">
         <v>1.17</v>
@@ -12259,7 +12259,7 @@
         <v>1.8</v>
       </c>
       <c r="AE73">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF73">
         <v>1.5</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.05</v>
+        <v>1.68</v>
       </c>
       <c r="O74">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="P74">
-        <v>2.7</v>
+        <v>3.58</v>
       </c>
       <c r="Q74">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="R74">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="S74">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T74">
         <v>4.5</v>
       </c>
       <c r="U74">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="V74">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="W74">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="X74">
         <v>1.01</v>
       </c>
       <c r="Y74">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Z74">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AA74">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AB74">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="AC74">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AD74">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="AE74">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AF74">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AG74">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK74">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.69</v>
+        <v>2.07</v>
       </c>
       <c r="O75">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="P75">
-        <v>4.04</v>
+        <v>2.7</v>
       </c>
       <c r="Q75">
-        <v>2.13</v>
+        <v>2.52</v>
       </c>
       <c r="R75">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="S75">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T75">
         <v>4.5</v>
       </c>
       <c r="U75">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="V75">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="W75">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X75">
         <v>1.01</v>
       </c>
       <c r="Y75">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Z75">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AA75">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AB75">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="AC75">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AD75">
-        <v>1.86</v>
+        <v>1.99</v>
       </c>
       <c r="AE75">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AF75">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AG75">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK75">
-        <v>2.07</v>
+        <v>1.65</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12718,7 +12718,7 @@
         <v>3.2</v>
       </c>
       <c r="U76">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="V76">
         <v>1.45</v>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK76">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -13512,7 +13512,7 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="O81">
         <v>3.45</v>
@@ -13533,13 +13533,13 @@
         <v>3.25</v>
       </c>
       <c r="U81">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="V81">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W81">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X81">
         <v>1.03</v>
@@ -13557,7 +13557,7 @@
         <v>2.15</v>
       </c>
       <c r="AC81">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="AD81">
         <v>1.43</v>
@@ -13585,7 +13585,7 @@
         <v>1.36</v>
       </c>
       <c r="AK81">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13705,7 +13705,7 @@
         <v>1.11</v>
       </c>
       <c r="X82">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y82">
         <v>1.18</v>
@@ -13853,13 +13853,13 @@
         <v>2.1</v>
       </c>
       <c r="S83">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T83">
         <v>3</v>
       </c>
       <c r="U83">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="V83">
         <v>1.4</v>
@@ -14010,7 +14010,7 @@
         <v>3.36</v>
       </c>
       <c r="Q84">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="R84">
         <v>2.53</v>
@@ -14019,16 +14019,16 @@
         <v>1.18</v>
       </c>
       <c r="T84">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="U84">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V84">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="W84">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X84">
         <v>1.01</v>
@@ -14040,7 +14040,7 @@
         <v>7.5</v>
       </c>
       <c r="AA84">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AB84">
         <v>3.2</v>
@@ -14052,7 +14052,7 @@
         <v>1.9</v>
       </c>
       <c r="AE84">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AF84">
         <v>1.36</v>
@@ -14182,7 +14182,7 @@
         <v>1.37</v>
       </c>
       <c r="T85">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="U85">
         <v>2.8</v>
@@ -14203,10 +14203,10 @@
         <v>3.08</v>
       </c>
       <c r="AA85">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB85">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC85">
         <v>2.75</v>
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="O86">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P86">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="Q86">
         <v>3.58</v>
@@ -14342,43 +14342,43 @@
         <v>2.25</v>
       </c>
       <c r="S86">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T86">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="U86">
         <v>2.55</v>
       </c>
       <c r="V86">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W86">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X86">
         <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z86">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="AA86">
         <v>1.76</v>
       </c>
       <c r="AB86">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="AC86">
         <v>2.88</v>
       </c>
       <c r="AD86">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE86">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF86">
         <v>1.53</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>3.15</v>
+        <v>2.3</v>
       </c>
       <c r="O92">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P92">
-        <v>1.96</v>
+        <v>2.55</v>
       </c>
       <c r="Q92">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="R92">
-        <v>2.16</v>
+        <v>2.46</v>
       </c>
       <c r="S92">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="T92">
-        <v>3.1</v>
+        <v>3.52</v>
       </c>
       <c r="U92">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="V92">
+        <v>1.6</v>
+      </c>
+      <c r="W92">
+        <v>1.15</v>
+      </c>
+      <c r="X92">
+        <v>1.01</v>
+      </c>
+      <c r="Y92">
+        <v>1.14</v>
+      </c>
+      <c r="Z92">
+        <v>5.5</v>
+      </c>
+      <c r="AA92">
+        <v>1.53</v>
+      </c>
+      <c r="AB92">
+        <v>2.4</v>
+      </c>
+      <c r="AC92">
+        <v>2.3</v>
+      </c>
+      <c r="AD92">
+        <v>1.6</v>
+      </c>
+      <c r="AE92">
+        <v>1.22</v>
+      </c>
+      <c r="AF92">
         <v>1.44</v>
       </c>
-      <c r="W92">
-        <v>1.11</v>
-      </c>
-      <c r="X92">
-        <v>1.03</v>
-      </c>
-      <c r="Y92">
-        <v>1.2</v>
-      </c>
-      <c r="Z92">
-        <v>3.7</v>
-      </c>
-      <c r="AA92">
-        <v>1.75</v>
-      </c>
-      <c r="AB92">
-        <v>1.98</v>
-      </c>
-      <c r="AC92">
-        <v>2.8</v>
-      </c>
-      <c r="AD92">
-        <v>1.41</v>
-      </c>
-      <c r="AE92">
-        <v>1.08</v>
-      </c>
-      <c r="AF92">
-        <v>1.62</v>
-      </c>
       <c r="AG92">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AK92">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.3</v>
+        <v>3.15</v>
       </c>
       <c r="O93">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P93">
-        <v>2.55</v>
+        <v>1.96</v>
       </c>
       <c r="Q93">
+        <v>3.9</v>
+      </c>
+      <c r="R93">
+        <v>2.16</v>
+      </c>
+      <c r="S93">
+        <v>1.31</v>
+      </c>
+      <c r="T93">
+        <v>3.1</v>
+      </c>
+      <c r="U93">
+        <v>2.63</v>
+      </c>
+      <c r="V93">
+        <v>1.44</v>
+      </c>
+      <c r="W93">
+        <v>1.11</v>
+      </c>
+      <c r="X93">
+        <v>1.03</v>
+      </c>
+      <c r="Y93">
+        <v>1.2</v>
+      </c>
+      <c r="Z93">
+        <v>3.7</v>
+      </c>
+      <c r="AA93">
+        <v>1.75</v>
+      </c>
+      <c r="AB93">
+        <v>1.98</v>
+      </c>
+      <c r="AC93">
         <v>2.8</v>
       </c>
-      <c r="R93">
-        <v>2.46</v>
-      </c>
-      <c r="S93">
-        <v>1.22</v>
-      </c>
-      <c r="T93">
-        <v>3.52</v>
-      </c>
-      <c r="U93">
-        <v>2.15</v>
-      </c>
-      <c r="V93">
-        <v>1.6</v>
-      </c>
-      <c r="W93">
-        <v>1.15</v>
-      </c>
-      <c r="X93">
-        <v>1.01</v>
-      </c>
-      <c r="Y93">
-        <v>1.14</v>
-      </c>
-      <c r="Z93">
-        <v>5.5</v>
-      </c>
-      <c r="AA93">
-        <v>1.53</v>
-      </c>
-      <c r="AB93">
-        <v>2.4</v>
-      </c>
-      <c r="AC93">
-        <v>2.3</v>
-      </c>
       <c r="AD93">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="AE93">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AF93">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AG93">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AK93">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15809,10 +15809,10 @@
         <v>2.38</v>
       </c>
       <c r="S95">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T95">
-        <v>3.34</v>
+        <v>3.48</v>
       </c>
       <c r="U95">
         <v>2.2</v>
@@ -15830,19 +15830,19 @@
         <v>1.13</v>
       </c>
       <c r="Z95">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="AA95">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AB95">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="AC95">
-        <v>2.24</v>
+        <v>2.05</v>
       </c>
       <c r="AD95">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AE95">
         <v>1.25</v>
@@ -15864,7 +15864,7 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK95">
         <v>1.5</v>
@@ -15960,10 +15960,10 @@
         <v>2.45</v>
       </c>
       <c r="O96">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P96">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="Q96">
         <v>3.02</v>
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="O98">
         <v>3.4</v>
       </c>
       <c r="P98">
-        <v>3.46</v>
+        <v>3.48</v>
       </c>
       <c r="Q98">
         <v>2.49</v>
@@ -16301,10 +16301,10 @@
         <v>1.39</v>
       </c>
       <c r="T98">
+        <v>2.99</v>
+      </c>
+      <c r="U98">
         <v>2.92</v>
-      </c>
-      <c r="U98">
-        <v>2.94</v>
       </c>
       <c r="V98">
         <v>1.41</v>
@@ -16319,13 +16319,13 @@
         <v>1.29</v>
       </c>
       <c r="Z98">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="AA98">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AB98">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="AC98">
         <v>3.25</v>
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="O99">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P99">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="Q99">
         <v>3.3</v>
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="O100">
         <v>3.35</v>
       </c>
       <c r="P100">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="Q100">
         <v>2.52</v>
@@ -16624,10 +16624,10 @@
         <v>1.96</v>
       </c>
       <c r="S100">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="T100">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="U100">
         <v>3.18</v>
@@ -16639,22 +16639,22 @@
         <v>1.05</v>
       </c>
       <c r="X100">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y100">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="Z100">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="AA100">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="AB100">
         <v>1.61</v>
       </c>
       <c r="AC100">
-        <v>4.17</v>
+        <v>4.21</v>
       </c>
       <c r="AD100">
         <v>1.21</v>
@@ -16935,61 +16935,61 @@
         </is>
       </c>
       <c r="N102">
-        <v>9.25</v>
+        <v>11</v>
       </c>
       <c r="O102">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="P102">
+        <v>1.08</v>
+      </c>
+      <c r="Q102">
+        <v>9.6</v>
+      </c>
+      <c r="R102">
+        <v>2.61</v>
+      </c>
+      <c r="S102">
         <v>1.3</v>
       </c>
-      <c r="Q102">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="R102">
-        <v>2.52</v>
-      </c>
-      <c r="S102">
-        <v>1.25</v>
-      </c>
       <c r="T102">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="U102">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="V102">
         <v>1.5</v>
       </c>
       <c r="W102">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X102">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y102">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z102">
-        <v>3.82</v>
+        <v>4.1</v>
       </c>
       <c r="AA102">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="AB102">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="AC102">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
       <c r="AD102">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AE102">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF102">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="AG102">
         <v>1.62</v>
@@ -17264,10 +17264,10 @@
         <v>1.57</v>
       </c>
       <c r="O104">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P104">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="Q104">
         <v>2.03</v>
@@ -17288,7 +17288,7 @@
         <v>1.77</v>
       </c>
       <c r="W104">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X104">
         <v>1.01</v>
@@ -17334,7 +17334,7 @@
         <v>1.14</v>
       </c>
       <c r="AK104">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17424,10 +17424,10 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="O105">
-        <v>3.2</v>
+        <v>3.07</v>
       </c>
       <c r="P105">
         <v>2.8</v>
@@ -17445,7 +17445,7 @@
         <v>2.67</v>
       </c>
       <c r="U105">
-        <v>2.9</v>
+        <v>3.13</v>
       </c>
       <c r="V105">
         <v>1.33</v>
@@ -17478,7 +17478,7 @@
         <v>1.03</v>
       </c>
       <c r="AF105">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG105">
         <v>1.9</v>
@@ -18085,7 +18085,7 @@
         <v>3.5</v>
       </c>
       <c r="Q109">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="R109">
         <v>1.85</v>

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -1015,10 +1015,10 @@
         <v>1.1</v>
       </c>
       <c r="AF4">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG4">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="O6">
         <v>3.5</v>
@@ -1323,13 +1323,13 @@
         <v>1.31</v>
       </c>
       <c r="Z6">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="AA6">
         <v>1.92</v>
       </c>
       <c r="AB6">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AC6">
         <v>3.05</v>
@@ -1341,7 +1341,7 @@
         <v>1.07</v>
       </c>
       <c r="AF6">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG6">
         <v>1.92</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.35</v>
+        <v>2.37</v>
       </c>
       <c r="O13">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="P13">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="Q13">
-        <v>1.57</v>
+        <v>2.83</v>
       </c>
       <c r="R13">
-        <v>2.88</v>
+        <v>2.21</v>
       </c>
       <c r="S13">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T13">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="U13">
-        <v>2.06</v>
+        <v>2.27</v>
       </c>
       <c r="V13">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="W13">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="Z13">
-        <v>5.3</v>
+        <v>4.15</v>
       </c>
       <c r="AA13">
+        <v>1.62</v>
+      </c>
+      <c r="AB13">
+        <v>2.11</v>
+      </c>
+      <c r="AC13">
+        <v>2.52</v>
+      </c>
+      <c r="AD13">
         <v>1.41</v>
       </c>
-      <c r="AB13">
-        <v>2.52</v>
-      </c>
-      <c r="AC13">
-        <v>2.06</v>
-      </c>
-      <c r="AD13">
-        <v>1.65</v>
-      </c>
       <c r="AE13">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AF13">
-        <v>1.85</v>
+        <v>1.51</v>
       </c>
       <c r="AG13">
-        <v>1.82</v>
+        <v>2.34</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AK13">
-        <v>4</v>
+        <v>1.47</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.37</v>
+        <v>1.35</v>
       </c>
       <c r="O14">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="P14">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="Q14">
-        <v>2.83</v>
+        <v>1.57</v>
       </c>
       <c r="R14">
-        <v>2.21</v>
+        <v>2.88</v>
       </c>
       <c r="S14">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T14">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="U14">
-        <v>2.27</v>
+        <v>2.06</v>
       </c>
       <c r="V14">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="W14">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X14">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="Z14">
-        <v>4.15</v>
+        <v>5.3</v>
       </c>
       <c r="AA14">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="AB14">
-        <v>2.11</v>
+        <v>2.52</v>
       </c>
       <c r="AC14">
-        <v>2.52</v>
+        <v>2.06</v>
       </c>
       <c r="AD14">
-        <v>1.41</v>
+        <v>1.65</v>
       </c>
       <c r="AE14">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AF14">
-        <v>1.51</v>
+        <v>1.85</v>
       </c>
       <c r="AG14">
-        <v>2.34</v>
+        <v>1.82</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AK14">
-        <v>1.47</v>
+        <v>4</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>2.03</v>
       </c>
       <c r="O20">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P20">
         <v>2.93</v>
@@ -3581,52 +3581,52 @@
         <v>2.45</v>
       </c>
       <c r="R20">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S20">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T20">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U20">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="V20">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="W20">
         <v>1.16</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z20">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA20">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AB20">
-        <v>2.88</v>
+        <v>2.58</v>
       </c>
       <c r="AC20">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AD20">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AE20">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AF20">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AG20">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3940,13 +3940,13 @@
         <v>3.4</v>
       </c>
       <c r="AC22">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AD22">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AE22">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AF22">
         <v>1.95</v>
@@ -4070,13 +4070,13 @@
         <v>3</v>
       </c>
       <c r="R23">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="S23">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="T23">
-        <v>2.57</v>
+        <v>2.64</v>
       </c>
       <c r="U23">
         <v>3.2</v>
@@ -4091,31 +4091,31 @@
         <v>1.03</v>
       </c>
       <c r="Y23">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z23">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AA23">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="AB23">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AC23">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AD23">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE23">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF23">
+        <v>1.83</v>
+      </c>
+      <c r="AG23">
         <v>1.85</v>
-      </c>
-      <c r="AG23">
-        <v>1.83</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>1.33</v>
       </c>
       <c r="AK23">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,19 +4873,19 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.49</v>
+        <v>2.75</v>
       </c>
       <c r="O28">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="P28">
-        <v>2.49</v>
+        <v>2.37</v>
       </c>
       <c r="Q28">
-        <v>3.16</v>
+        <v>3.5</v>
       </c>
       <c r="R28">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="S28">
         <v>1.36</v>
@@ -4912,25 +4912,25 @@
         <v>2.97</v>
       </c>
       <c r="AA28">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AB28">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AC28">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AD28">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE28">
         <v>1.05</v>
       </c>
       <c r="AF28">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AG28">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>1.25</v>
       </c>
       <c r="AK28">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="O30">
         <v>3</v>
@@ -5211,13 +5211,13 @@
         <v>2.5</v>
       </c>
       <c r="R30">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="S30">
         <v>1.5</v>
       </c>
       <c r="T30">
-        <v>2.37</v>
+        <v>2.42</v>
       </c>
       <c r="U30">
         <v>3.5</v>
@@ -5241,7 +5241,7 @@
         <v>2.43</v>
       </c>
       <c r="AB30">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AC30">
         <v>4.75</v>
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK30">
         <v>1.83</v>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="O31">
         <v>3.85</v>
@@ -6020,7 +6020,7 @@
         <v>3.6</v>
       </c>
       <c r="P35">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="Q35">
         <v>2.19</v>
@@ -6032,7 +6032,7 @@
         <v>1.35</v>
       </c>
       <c r="T35">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="U35">
         <v>2.75</v>
@@ -6340,10 +6340,10 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="O37">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P37">
         <v>4.2</v>
@@ -6355,19 +6355,19 @@
         <v>2.6</v>
       </c>
       <c r="S37">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T37">
-        <v>3.9</v>
+        <v>3.42</v>
       </c>
       <c r="U37">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="V37">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="W37">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X37">
         <v>1.02</v>
@@ -6376,28 +6376,28 @@
         <v>1.1</v>
       </c>
       <c r="Z37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA37">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB37">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AC37">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="AD37">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AE37">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AF37">
         <v>1.62</v>
       </c>
       <c r="AG37">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6684,13 +6684,13 @@
         <v>1.29</v>
       </c>
       <c r="T39">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U39">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="V39">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W39">
         <v>1.11</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="O42">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P42">
-        <v>3.23</v>
+        <v>3.62</v>
       </c>
       <c r="Q42">
         <v>2.38</v>
@@ -7330,7 +7330,7 @@
         <v>2.78</v>
       </c>
       <c r="R43">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="S43">
         <v>1.44</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -7520,10 +7520,10 @@
         <v>0</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC44">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>7.54</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>13.7</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -7683,10 +7683,10 @@
         <v>0</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC45">
         <v>0</v>
@@ -7970,10 +7970,10 @@
         </is>
       </c>
       <c r="N47">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="O47">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="P47">
         <v>1.36</v>
@@ -7994,7 +7994,7 @@
         <v>2.29</v>
       </c>
       <c r="V47">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="W47">
         <v>1.13</v>
@@ -8003,22 +8003,22 @@
         <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z47">
-        <v>4.23</v>
+        <v>4.48</v>
       </c>
       <c r="AA47">
         <v>1.6</v>
       </c>
       <c r="AB47">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
       <c r="AC47">
-        <v>2.67</v>
+        <v>2.55</v>
       </c>
       <c r="AD47">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AE47">
         <v>1.16</v>
@@ -8320,7 +8320,7 @@
         <v>2.3</v>
       </c>
       <c r="V49">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="W49">
         <v>1.13</v>
@@ -8480,10 +8480,10 @@
         <v>3.4</v>
       </c>
       <c r="U50">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="V50">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W50">
         <v>1.1</v>
@@ -9277,7 +9277,7 @@
         <v>3.16</v>
       </c>
       <c r="O55">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P55">
         <v>2.01</v>
@@ -9319,7 +9319,7 @@
         <v>3.17</v>
       </c>
       <c r="AC55">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AD55">
         <v>1.98</v>
@@ -9603,10 +9603,10 @@
         <v>3.4</v>
       </c>
       <c r="O57">
-        <v>3.9</v>
+        <v>3.93</v>
       </c>
       <c r="P57">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="Q57">
         <v>4.14</v>
@@ -11912,7 +11912,7 @@
         <v>1.14</v>
       </c>
       <c r="X71">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y71">
         <v>1.1</v>
@@ -11955,7 +11955,7 @@
         <v>1.22</v>
       </c>
       <c r="AK71">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -13023,7 +13023,7 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="O78">
         <v>3.4</v>
@@ -13192,7 +13192,7 @@
         <v>3.6</v>
       </c>
       <c r="P79">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="Q79">
         <v>4.4</v>
@@ -13204,13 +13204,13 @@
         <v>1.3</v>
       </c>
       <c r="T79">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="U79">
         <v>2.44</v>
       </c>
       <c r="V79">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W79">
         <v>1.09</v>
@@ -13219,16 +13219,16 @@
         <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z79">
         <v>3.58</v>
       </c>
       <c r="AA79">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB79">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC79">
         <v>2.74</v>
@@ -13240,7 +13240,7 @@
         <v>1.1</v>
       </c>
       <c r="AF79">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG79">
         <v>2.03</v>
@@ -14004,7 +14004,7 @@
         <v>1.92</v>
       </c>
       <c r="O84">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P84">
         <v>3.36</v>
@@ -14037,10 +14037,10 @@
         <v>1.05</v>
       </c>
       <c r="Z84">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AA84">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AB84">
         <v>3.2</v>
@@ -14170,7 +14170,7 @@
         <v>3.2</v>
       </c>
       <c r="P85">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="Q85">
         <v>2.97</v>
@@ -14182,7 +14182,7 @@
         <v>1.37</v>
       </c>
       <c r="T85">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="U85">
         <v>2.8</v>
@@ -14197,19 +14197,19 @@
         <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z85">
         <v>3.08</v>
       </c>
       <c r="AA85">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB85">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC85">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AD85">
         <v>1.25</v>
@@ -14493,10 +14493,10 @@
         <v>4</v>
       </c>
       <c r="O87">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P87">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="Q87">
         <v>4.33</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="O88">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="P88">
-        <v>4.8</v>
+        <v>2.15</v>
       </c>
       <c r="Q88">
-        <v>1.95</v>
+        <v>3.25</v>
       </c>
       <c r="R88">
-        <v>2.73</v>
+        <v>2.32</v>
       </c>
       <c r="S88">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="T88">
-        <v>3.9</v>
+        <v>2.82</v>
       </c>
       <c r="U88">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="V88">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="W88">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X88">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y88">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="Z88">
-        <v>5.2</v>
+        <v>3.58</v>
       </c>
       <c r="AA88">
-        <v>1.4</v>
+        <v>1.82</v>
       </c>
       <c r="AB88">
-        <v>2.56</v>
+        <v>2.06</v>
       </c>
       <c r="AC88">
-        <v>2.11</v>
+        <v>2.97</v>
       </c>
       <c r="AD88">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="AE88">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AF88">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AG88">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK88">
-        <v>2.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.87</v>
+        <v>1.45</v>
       </c>
       <c r="O89">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="P89">
-        <v>2.15</v>
+        <v>4.6</v>
       </c>
       <c r="Q89">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="R89">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="S89">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="T89">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="U89">
-        <v>2.62</v>
+        <v>2</v>
       </c>
       <c r="V89">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="W89">
+        <v>1.17</v>
+      </c>
+      <c r="X89">
+        <v>1.01</v>
+      </c>
+      <c r="Y89">
         <v>1.1</v>
       </c>
-      <c r="X89">
-        <v>1.03</v>
-      </c>
-      <c r="Y89">
+      <c r="Z89">
+        <v>5.2</v>
+      </c>
+      <c r="AA89">
+        <v>1.44</v>
+      </c>
+      <c r="AB89">
+        <v>2.7</v>
+      </c>
+      <c r="AC89">
+        <v>2.05</v>
+      </c>
+      <c r="AD89">
+        <v>1.66</v>
+      </c>
+      <c r="AE89">
         <v>1.25</v>
       </c>
-      <c r="Z89">
-        <v>3.6</v>
-      </c>
-      <c r="AA89">
-        <v>1.88</v>
-      </c>
-      <c r="AB89">
-        <v>1.83</v>
-      </c>
-      <c r="AC89">
-        <v>3.14</v>
-      </c>
-      <c r="AD89">
-        <v>1.27</v>
-      </c>
-      <c r="AE89">
-        <v>1.06</v>
-      </c>
       <c r="AF89">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="AG89">
-        <v>2.1</v>
+        <v>2.39</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK89">
-        <v>1.32</v>
+        <v>2.4</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14979,10 +14979,10 @@
         </is>
       </c>
       <c r="N90">
-        <v>5.6</v>
+        <v>5.72</v>
       </c>
       <c r="O90">
-        <v>4.55</v>
+        <v>4.75</v>
       </c>
       <c r="P90">
         <v>1.38</v>
@@ -14991,7 +14991,7 @@
         <v>4.25</v>
       </c>
       <c r="R90">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="S90">
         <v>1.22</v>
@@ -15015,7 +15015,7 @@
         <v>1.13</v>
       </c>
       <c r="Z90">
-        <v>5.6</v>
+        <v>5.67</v>
       </c>
       <c r="AA90">
         <v>1.4</v>
@@ -15142,19 +15142,19 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="O91">
         <v>3.4</v>
       </c>
       <c r="P91">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="Q91">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="R91">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="S91">
         <v>1.25</v>
@@ -15169,7 +15169,7 @@
         <v>1.57</v>
       </c>
       <c r="W91">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X91">
         <v>1.01</v>
@@ -15184,7 +15184,7 @@
         <v>1.57</v>
       </c>
       <c r="AB91">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="AC91">
         <v>2.55</v>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK91">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.3</v>
+        <v>3.15</v>
       </c>
       <c r="O92">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P92">
-        <v>2.55</v>
+        <v>1.92</v>
       </c>
       <c r="Q92">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="R92">
-        <v>2.46</v>
+        <v>2.16</v>
       </c>
       <c r="S92">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="T92">
-        <v>3.52</v>
+        <v>3.1</v>
       </c>
       <c r="U92">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="V92">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="W92">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X92">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y92">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z92">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
       <c r="AA92">
-        <v>1.53</v>
+        <v>1.76</v>
       </c>
       <c r="AB92">
-        <v>2.4</v>
+        <v>1.98</v>
       </c>
       <c r="AC92">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="AD92">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="AE92">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AF92">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AG92">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AK92">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>3.15</v>
+        <v>2.38</v>
       </c>
       <c r="O93">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P93">
-        <v>1.96</v>
+        <v>2.45</v>
       </c>
       <c r="Q93">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="R93">
-        <v>2.16</v>
+        <v>2.46</v>
       </c>
       <c r="S93">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="T93">
-        <v>3.1</v>
+        <v>3.52</v>
       </c>
       <c r="U93">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="V93">
+        <v>1.6</v>
+      </c>
+      <c r="W93">
+        <v>1.15</v>
+      </c>
+      <c r="X93">
+        <v>1.01</v>
+      </c>
+      <c r="Y93">
+        <v>1.14</v>
+      </c>
+      <c r="Z93">
+        <v>5.5</v>
+      </c>
+      <c r="AA93">
+        <v>1.53</v>
+      </c>
+      <c r="AB93">
+        <v>2.55</v>
+      </c>
+      <c r="AC93">
+        <v>2.3</v>
+      </c>
+      <c r="AD93">
+        <v>1.6</v>
+      </c>
+      <c r="AE93">
+        <v>1.22</v>
+      </c>
+      <c r="AF93">
         <v>1.44</v>
       </c>
-      <c r="W93">
-        <v>1.11</v>
-      </c>
-      <c r="X93">
-        <v>1.03</v>
-      </c>
-      <c r="Y93">
-        <v>1.2</v>
-      </c>
-      <c r="Z93">
-        <v>3.7</v>
-      </c>
-      <c r="AA93">
-        <v>1.75</v>
-      </c>
-      <c r="AB93">
-        <v>1.98</v>
-      </c>
-      <c r="AC93">
-        <v>2.8</v>
-      </c>
-      <c r="AD93">
-        <v>1.41</v>
-      </c>
-      <c r="AE93">
-        <v>1.08</v>
-      </c>
-      <c r="AF93">
-        <v>1.62</v>
-      </c>
       <c r="AG93">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AK93">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="O94">
         <v>3.5</v>
       </c>
       <c r="P94">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="Q94">
         <v>3.42</v>
@@ -15646,22 +15646,22 @@
         <v>2.43</v>
       </c>
       <c r="S94">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T94">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U94">
         <v>2.35</v>
       </c>
       <c r="V94">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W94">
         <v>1.12</v>
       </c>
       <c r="X94">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y94">
         <v>1.2</v>
@@ -15670,7 +15670,7 @@
         <v>4.5</v>
       </c>
       <c r="AA94">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AB94">
         <v>2.18</v>
@@ -15685,10 +15685,10 @@
         <v>1.14</v>
       </c>
       <c r="AF94">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG94">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         <v>2.2</v>
       </c>
       <c r="V95">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="W95">
         <v>1.14</v>
@@ -15836,13 +15836,13 @@
         <v>1.47</v>
       </c>
       <c r="AB95">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="AC95">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AD95">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AE95">
         <v>1.25</v>
@@ -15851,7 +15851,7 @@
         <v>1.4</v>
       </c>
       <c r="AG95">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="O97">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P97">
-        <v>5</v>
+        <v>5.15</v>
       </c>
       <c r="Q97">
         <v>2.05</v>
@@ -16135,7 +16135,7 @@
         <v>2.17</v>
       </c>
       <c r="S97">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T97">
         <v>3.08</v>
@@ -16153,10 +16153,10 @@
         <v>1.02</v>
       </c>
       <c r="Y97">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z97">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="AA97">
         <v>1.72</v>
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O101">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q101">
         <v>0</v>

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU110"/>
+  <dimension ref="A1:AU112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -961,22 +961,22 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="O4">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P4">
-        <v>4.19</v>
+        <v>4.1</v>
       </c>
       <c r="Q4">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="R4">
         <v>2.05</v>
       </c>
       <c r="S4">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T4">
         <v>3</v>
@@ -988,7 +988,7 @@
         <v>1.4</v>
       </c>
       <c r="W4">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X4">
         <v>1.03</v>
@@ -1003,7 +1003,7 @@
         <v>1.9</v>
       </c>
       <c r="AB4">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AC4">
         <v>3.4</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AK4">
-        <v>1.7</v>
+        <v>2.03</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="O9">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P9">
-        <v>4.03</v>
+        <v>3.85</v>
       </c>
       <c r="Q9">
         <v>2.48</v>
@@ -1815,10 +1815,10 @@
         <v>3.1</v>
       </c>
       <c r="AA9">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AB9">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC9">
         <v>3.4</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,80 +2591,80 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.35</v>
+        <v>2.37</v>
       </c>
       <c r="O14">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="P14">
-        <v>6</v>
+        <v>2.45</v>
       </c>
       <c r="Q14">
-        <v>1.57</v>
+        <v>2.96</v>
       </c>
       <c r="R14">
-        <v>2.88</v>
+        <v>2.23</v>
       </c>
       <c r="S14">
+        <v>1.24</v>
+      </c>
+      <c r="T14">
+        <v>3.38</v>
+      </c>
+      <c r="U14">
+        <v>2.34</v>
+      </c>
+      <c r="V14">
+        <v>1.48</v>
+      </c>
+      <c r="W14">
+        <v>1.1</v>
+      </c>
+      <c r="X14">
+        <v>1.02</v>
+      </c>
+      <c r="Y14">
+        <v>1.16</v>
+      </c>
+      <c r="Z14">
+        <v>4.1</v>
+      </c>
+      <c r="AA14">
+        <v>1.65</v>
+      </c>
+      <c r="AB14">
+        <v>2.06</v>
+      </c>
+      <c r="AC14">
+        <v>2.66</v>
+      </c>
+      <c r="AD14">
+        <v>1.37</v>
+      </c>
+      <c r="AE14">
+        <v>1.11</v>
+      </c>
+      <c r="AF14">
+        <v>1.54</v>
+      </c>
+      <c r="AG14">
+        <v>2.26</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14">
         <v>1.2</v>
       </c>
-      <c r="T14">
-        <v>4</v>
-      </c>
-      <c r="U14">
-        <v>2.06</v>
-      </c>
-      <c r="V14">
-        <v>1.65</v>
-      </c>
-      <c r="W14">
-        <v>1.17</v>
-      </c>
-      <c r="X14">
-        <v>1.01</v>
-      </c>
-      <c r="Y14">
-        <v>1.09</v>
-      </c>
-      <c r="Z14">
-        <v>5.3</v>
-      </c>
-      <c r="AA14">
-        <v>1.41</v>
-      </c>
-      <c r="AB14">
-        <v>2.52</v>
-      </c>
-      <c r="AC14">
-        <v>2.06</v>
-      </c>
-      <c r="AD14">
-        <v>1.65</v>
-      </c>
-      <c r="AE14">
-        <v>1.24</v>
-      </c>
-      <c r="AF14">
-        <v>1.85</v>
-      </c>
-      <c r="AG14">
-        <v>1.82</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14">
-        <v>1.08</v>
-      </c>
       <c r="AK14">
-        <v>4</v>
+        <v>1.43</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.37</v>
+        <v>1.35</v>
       </c>
       <c r="O15">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="P15">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="Q15">
-        <v>2.9</v>
+        <v>1.57</v>
       </c>
       <c r="R15">
-        <v>2.13</v>
+        <v>2.88</v>
       </c>
       <c r="S15">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U15">
-        <v>2.45</v>
+        <v>2.06</v>
       </c>
       <c r="V15">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="W15">
+        <v>1.17</v>
+      </c>
+      <c r="X15">
+        <v>1.01</v>
+      </c>
+      <c r="Y15">
         <v>1.09</v>
       </c>
-      <c r="X15">
-        <v>1</v>
-      </c>
-      <c r="Y15">
-        <v>1.21</v>
-      </c>
       <c r="Z15">
-        <v>3.58</v>
+        <v>5.3</v>
       </c>
       <c r="AA15">
-        <v>1.76</v>
+        <v>1.41</v>
       </c>
       <c r="AB15">
-        <v>1.92</v>
+        <v>2.52</v>
       </c>
       <c r="AC15">
-        <v>2.88</v>
+        <v>2.06</v>
       </c>
       <c r="AD15">
-        <v>1.32</v>
+        <v>1.65</v>
       </c>
       <c r="AE15">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="AF15">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AG15">
-        <v>2.13</v>
+        <v>1.82</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AK15">
-        <v>1.46</v>
+        <v>4</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G16">
@@ -2920,61 +2920,61 @@
         <v>2.37</v>
       </c>
       <c r="O16">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P16">
+        <v>2.5</v>
+      </c>
+      <c r="Q16">
+        <v>2.9</v>
+      </c>
+      <c r="R16">
+        <v>2.13</v>
+      </c>
+      <c r="S16">
+        <v>1.3</v>
+      </c>
+      <c r="T16">
+        <v>3</v>
+      </c>
+      <c r="U16">
         <v>2.45</v>
       </c>
-      <c r="Q16">
-        <v>2.96</v>
-      </c>
-      <c r="R16">
-        <v>2.23</v>
-      </c>
-      <c r="S16">
-        <v>1.24</v>
-      </c>
-      <c r="T16">
-        <v>3.38</v>
-      </c>
-      <c r="U16">
-        <v>2.34</v>
-      </c>
       <c r="V16">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W16">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X16">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y16">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z16">
-        <v>4.1</v>
+        <v>3.58</v>
       </c>
       <c r="AA16">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AB16">
-        <v>2.06</v>
+        <v>1.92</v>
       </c>
       <c r="AC16">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="AD16">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AE16">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF16">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="AG16">
-        <v>2.26</v>
+        <v>2.13</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK16">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3569,19 +3569,19 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="O20">
         <v>3.6</v>
       </c>
       <c r="P20">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="Q20">
+        <v>2.5</v>
+      </c>
+      <c r="R20">
         <v>2.45</v>
-      </c>
-      <c r="R20">
-        <v>2.4</v>
       </c>
       <c r="S20">
         <v>1.2</v>
@@ -3590,10 +3590,10 @@
         <v>3.9</v>
       </c>
       <c r="U20">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="V20">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W20">
         <v>1.16</v>
@@ -3608,25 +3608,25 @@
         <v>5.75</v>
       </c>
       <c r="AA20">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AB20">
-        <v>2.58</v>
+        <v>2.65</v>
       </c>
       <c r="AC20">
         <v>2.15</v>
       </c>
       <c r="AD20">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AE20">
         <v>1.29</v>
       </c>
       <c r="AF20">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG20">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -4058,34 +4058,34 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O23">
         <v>3.05</v>
       </c>
       <c r="P23">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="Q23">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="R23">
         <v>2.01</v>
       </c>
       <c r="S23">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="T23">
         <v>2.64</v>
       </c>
       <c r="U23">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="V23">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W23">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X23">
         <v>1.03</v>
@@ -4094,13 +4094,13 @@
         <v>1.3</v>
       </c>
       <c r="Z23">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AA23">
         <v>2.04</v>
       </c>
       <c r="AB23">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC23">
         <v>3.7</v>
@@ -4112,10 +4112,10 @@
         <v>1.05</v>
       </c>
       <c r="AF23">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG23">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>1.33</v>
       </c>
       <c r="AK23">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="O24">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P24">
-        <v>4.09</v>
+        <v>3.9</v>
       </c>
       <c r="Q24">
         <v>2.3</v>
@@ -5036,7 +5036,7 @@
         </is>
       </c>
       <c r="N29">
-        <v>6.3</v>
+        <v>6.75</v>
       </c>
       <c r="O29">
         <v>4.33</v>
@@ -5045,19 +5045,19 @@
         <v>1.4</v>
       </c>
       <c r="Q29">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="R29">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S29">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="T29">
-        <v>3.14</v>
+        <v>2.79</v>
       </c>
       <c r="U29">
-        <v>2.73</v>
+        <v>2.53</v>
       </c>
       <c r="V29">
         <v>1.44</v>
@@ -5066,31 +5066,31 @@
         <v>1.07</v>
       </c>
       <c r="X29">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y29">
         <v>1.22</v>
       </c>
       <c r="Z29">
-        <v>3.48</v>
+        <v>3.7</v>
       </c>
       <c r="AA29">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AB29">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AC29">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="AD29">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE29">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF29">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AG29">
         <v>1.7</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>2.55</v>
+        <v>1.13</v>
       </c>
       <c r="AK29">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="O30">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P30">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="Q30">
         <v>2.5</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.21</v>
+        <v>2.45</v>
       </c>
       <c r="O31">
         <v>3.85</v>
       </c>
       <c r="P31">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5525,58 +5525,58 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="O32">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P32">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="Q32">
-        <v>2.86</v>
+        <v>2.66</v>
       </c>
       <c r="R32">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="S32">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T32">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="U32">
-        <v>2.64</v>
+        <v>2.69</v>
       </c>
       <c r="V32">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W32">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X32">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y32">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z32">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AA32">
         <v>1.83</v>
       </c>
       <c r="AB32">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AC32">
-        <v>2.93</v>
+        <v>3.25</v>
       </c>
       <c r="AD32">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE32">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF32">
         <v>1.62</v>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AK32">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O34">
         <v>3.25</v>
       </c>
       <c r="P34">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="Q34">
         <v>2.5</v>
@@ -5878,22 +5878,22 @@
         <v>1.31</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X34">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
         <v>1.27</v>
       </c>
       <c r="Z34">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AA34">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AB34">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AC34">
         <v>2.75</v>
@@ -5905,10 +5905,10 @@
         <v>1.07</v>
       </c>
       <c r="AF34">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG34">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="O37">
         <v>3.8</v>
@@ -6352,22 +6352,22 @@
         <v>2</v>
       </c>
       <c r="R37">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="S37">
         <v>1.25</v>
       </c>
       <c r="T37">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="U37">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="V37">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W37">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X37">
         <v>1.02</v>
@@ -6385,10 +6385,10 @@
         <v>2.5</v>
       </c>
       <c r="AC37">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AD37">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AE37">
         <v>1.22</v>
@@ -6503,19 +6503,19 @@
         </is>
       </c>
       <c r="N38">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="O38">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P38">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Q38">
         <v>4.33</v>
       </c>
       <c r="R38">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="S38">
         <v>1.3</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="O39">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P39">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="Q39">
         <v>2.4</v>
@@ -6690,7 +6690,7 @@
         <v>2.27</v>
       </c>
       <c r="V39">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W39">
         <v>1.11</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK39">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="O42">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="P42">
-        <v>3.62</v>
+        <v>3.55</v>
       </c>
       <c r="Q42">
         <v>2.38</v>
@@ -7170,16 +7170,16 @@
         <v>1.91</v>
       </c>
       <c r="S42">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="T42">
-        <v>2.15</v>
+        <v>2.62</v>
       </c>
       <c r="U42">
         <v>2.39</v>
       </c>
       <c r="V42">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W42">
         <v>1.03</v>
@@ -7209,7 +7209,7 @@
         <v>1.03</v>
       </c>
       <c r="AF42">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG42">
         <v>1.83</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="AK42">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7807,16 +7807,16 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O46">
         <v>3.6</v>
       </c>
       <c r="P46">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="Q46">
-        <v>2.49</v>
+        <v>2.42</v>
       </c>
       <c r="R46">
         <v>2.4</v>
@@ -7831,10 +7831,10 @@
         <v>2.14</v>
       </c>
       <c r="V46">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="W46">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="X46">
         <v>1.02</v>
@@ -7843,7 +7843,7 @@
         <v>1.14</v>
       </c>
       <c r="Z46">
-        <v>5.79</v>
+        <v>5.87</v>
       </c>
       <c r="AA46">
         <v>1.41</v>
@@ -7973,10 +7973,10 @@
         <v>6.5</v>
       </c>
       <c r="O47">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="P47">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Q47">
         <v>7</v>
@@ -7994,10 +7994,10 @@
         <v>2.29</v>
       </c>
       <c r="V47">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W47">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X47">
         <v>1.01</v>
@@ -8006,22 +8006,22 @@
         <v>1.19</v>
       </c>
       <c r="Z47">
-        <v>4.48</v>
+        <v>5</v>
       </c>
       <c r="AA47">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB47">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AC47">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="AD47">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AE47">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AF47">
         <v>1.82</v>
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.13</v>
+        <v>3</v>
       </c>
       <c r="AK47">
         <v>1.08</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.86</v>
+        <v>2.35</v>
       </c>
       <c r="O48">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="P48">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="Q48">
-        <v>3.56</v>
+        <v>2.88</v>
       </c>
       <c r="R48">
+        <v>2.25</v>
+      </c>
+      <c r="S48">
+        <v>1.29</v>
+      </c>
+      <c r="T48">
+        <v>3.4</v>
+      </c>
+      <c r="U48">
         <v>2.3</v>
       </c>
-      <c r="S48">
-        <v>1.32</v>
-      </c>
-      <c r="T48">
-        <v>3.38</v>
-      </c>
-      <c r="U48">
-        <v>2.24</v>
-      </c>
       <c r="V48">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="W48">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X48">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z48">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AA48">
         <v>1.6</v>
       </c>
       <c r="AB48">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="AC48">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AD48">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AE48">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF48">
         <v>1.5</v>
       </c>
       <c r="AG48">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="AK48">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
+        <v>3.05</v>
+      </c>
+      <c r="O49">
+        <v>3.45</v>
+      </c>
+      <c r="P49">
+        <v>2.1</v>
+      </c>
+      <c r="Q49">
+        <v>3.56</v>
+      </c>
+      <c r="R49">
         <v>2.3</v>
       </c>
-      <c r="O49">
-        <v>3.4</v>
-      </c>
-      <c r="P49">
-        <v>2.69</v>
-      </c>
-      <c r="Q49">
-        <v>2.88</v>
-      </c>
-      <c r="R49">
+      <c r="S49">
+        <v>1.32</v>
+      </c>
+      <c r="T49">
+        <v>3.38</v>
+      </c>
+      <c r="U49">
+        <v>2.24</v>
+      </c>
+      <c r="V49">
+        <v>1.55</v>
+      </c>
+      <c r="W49">
+        <v>1.11</v>
+      </c>
+      <c r="X49">
+        <v>1.01</v>
+      </c>
+      <c r="Y49">
+        <v>1.17</v>
+      </c>
+      <c r="Z49">
+        <v>4.6</v>
+      </c>
+      <c r="AA49">
+        <v>1.6</v>
+      </c>
+      <c r="AB49">
         <v>2.25</v>
       </c>
-      <c r="S49">
-        <v>1.29</v>
-      </c>
-      <c r="T49">
-        <v>3.4</v>
-      </c>
-      <c r="U49">
-        <v>2.3</v>
-      </c>
-      <c r="V49">
+      <c r="AC49">
+        <v>2.55</v>
+      </c>
+      <c r="AD49">
+        <v>1.47</v>
+      </c>
+      <c r="AE49">
+        <v>1.17</v>
+      </c>
+      <c r="AF49">
         <v>1.53</v>
       </c>
-      <c r="W49">
-        <v>1.13</v>
-      </c>
-      <c r="X49">
-        <v>1.02</v>
-      </c>
-      <c r="Y49">
-        <v>1.18</v>
-      </c>
-      <c r="Z49">
-        <v>4.4</v>
-      </c>
-      <c r="AA49">
-        <v>1.64</v>
-      </c>
-      <c r="AB49">
-        <v>2.09</v>
-      </c>
-      <c r="AC49">
-        <v>2.63</v>
-      </c>
-      <c r="AD49">
-        <v>1.44</v>
-      </c>
-      <c r="AE49">
-        <v>1.14</v>
-      </c>
-      <c r="AF49">
-        <v>1.5</v>
-      </c>
       <c r="AG49">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="AK49">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="O50">
         <v>3.7</v>
       </c>
       <c r="P50">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="Q50">
         <v>2.15</v>
@@ -8480,10 +8480,10 @@
         <v>3.4</v>
       </c>
       <c r="U50">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="V50">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W50">
         <v>1.1</v>
@@ -8498,10 +8498,10 @@
         <v>4.4</v>
       </c>
       <c r="AA50">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB50">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AC50">
         <v>2.63</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.89</v>
+        <v>2.15</v>
       </c>
       <c r="O51">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P51">
-        <v>2.1</v>
+        <v>2.77</v>
       </c>
       <c r="Q51">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R51">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S51">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T51">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U51">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V51">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W51">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X51">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y51">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z51">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AA51">
         <v>1.61</v>
       </c>
       <c r="AB51">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC51">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD51">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE51">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF51">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG51">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK51">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.15</v>
+        <v>1.5</v>
       </c>
       <c r="O52">
-        <v>3.4</v>
+        <v>4.55</v>
       </c>
       <c r="P52">
-        <v>2.85</v>
+        <v>4.6</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA52">
-        <v>1.61</v>
+        <v>1.37</v>
       </c>
       <c r="AB52">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.5</v>
+        <v>2.89</v>
       </c>
       <c r="O53">
-        <v>4.55</v>
+        <v>3.6</v>
       </c>
       <c r="P53">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="Q53">
-        <v>1.93</v>
+        <v>3.62</v>
       </c>
       <c r="R53">
-        <v>2.57</v>
+        <v>2.28</v>
       </c>
       <c r="S53">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="T53">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U53">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="V53">
-        <v>1.74</v>
+        <v>1.55</v>
       </c>
       <c r="W53">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="X53">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y53">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z53">
-        <v>5.45</v>
+        <v>4.35</v>
       </c>
       <c r="AA53">
-        <v>1.37</v>
+        <v>1.61</v>
       </c>
       <c r="AB53">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="AC53">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="AD53">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="AE53">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AF53">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AG53">
-        <v>2.63</v>
+        <v>2.39</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AK53">
-        <v>2.42</v>
+        <v>1.35</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9114,13 +9114,13 @@
         <v>2.8</v>
       </c>
       <c r="O54">
-        <v>3.6</v>
+        <v>3.88</v>
       </c>
       <c r="P54">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q54">
-        <v>3.2</v>
+        <v>2.89</v>
       </c>
       <c r="R54">
         <v>2.45</v>
@@ -9135,7 +9135,7 @@
         <v>2.09</v>
       </c>
       <c r="V54">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="W54">
         <v>1.15</v>
@@ -9150,13 +9150,13 @@
         <v>5.65</v>
       </c>
       <c r="AA54">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AB54">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AC54">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AD54">
         <v>1.72</v>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.62</v>
+        <v>1.23</v>
       </c>
       <c r="AK54">
         <v>1.33</v>
@@ -9277,10 +9277,10 @@
         <v>3.16</v>
       </c>
       <c r="O55">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P55">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="Q55">
         <v>3.36</v>
@@ -9292,7 +9292,7 @@
         <v>1.14</v>
       </c>
       <c r="T55">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="U55">
         <v>2.04</v>
@@ -9319,7 +9319,7 @@
         <v>3.17</v>
       </c>
       <c r="AC55">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AD55">
         <v>1.98</v>
@@ -9763,25 +9763,25 @@
         </is>
       </c>
       <c r="N58">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="O58">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="P58">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="Q58">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
       <c r="R58">
-        <v>2.37</v>
+        <v>2.41</v>
       </c>
       <c r="S58">
         <v>1.28</v>
       </c>
       <c r="T58">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="U58">
         <v>2.55</v>
@@ -9802,7 +9802,7 @@
         <v>4.33</v>
       </c>
       <c r="AA58">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="AB58">
         <v>2.14</v>
@@ -9811,7 +9811,7 @@
         <v>2.82</v>
       </c>
       <c r="AD58">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE58">
         <v>1.12</v>
@@ -9820,7 +9820,7 @@
         <v>1.6</v>
       </c>
       <c r="AG58">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK58">
         <v>1.7</v>
@@ -9932,7 +9932,7 @@
         <v>3.6</v>
       </c>
       <c r="P59">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -10047,7 +10047,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>5.71</v>
+        <v>2.4</v>
       </c>
       <c r="O60">
-        <v>4.45</v>
+        <v>3.55</v>
       </c>
       <c r="P60">
-        <v>1.46</v>
+        <v>2.4</v>
       </c>
       <c r="Q60">
-        <v>4.53</v>
+        <v>2.95</v>
       </c>
       <c r="R60">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="S60">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T60">
         <v>4</v>
       </c>
       <c r="U60">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="V60">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="W60">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X60">
         <v>1.02</v>
       </c>
       <c r="Y60">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z60">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AA60">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AB60">
-        <v>2.42</v>
+        <v>2.88</v>
       </c>
       <c r="AC60">
-        <v>2.37</v>
+        <v>2.05</v>
       </c>
       <c r="AD60">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="AE60">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AF60">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AG60">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>1.2</v>
       </c>
       <c r="AK60">
-        <v>1.11</v>
+        <v>1.47</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10210,22 +10210,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Horsens</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.7</v>
+        <v>5.71</v>
       </c>
       <c r="O61">
-        <v>3.5</v>
+        <v>4.45</v>
       </c>
       <c r="P61">
-        <v>2.3</v>
+        <v>1.46</v>
       </c>
       <c r="Q61">
-        <v>3.42</v>
+        <v>4.49</v>
       </c>
       <c r="R61">
-        <v>2.12</v>
+        <v>2.39</v>
       </c>
       <c r="S61">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="T61">
-        <v>3.23</v>
+        <v>4</v>
       </c>
       <c r="U61">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="V61">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="W61">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X61">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y61">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="Z61">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="AA61">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="AB61">
-        <v>2</v>
+        <v>2.42</v>
       </c>
       <c r="AC61">
-        <v>2.9</v>
+        <v>2.37</v>
       </c>
       <c r="AD61">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="AE61">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="AF61">
         <v>1.62</v>
       </c>
       <c r="AG61">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK61">
-        <v>1.4</v>
+        <v>1.11</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10368,12 +10368,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Horsens</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,80 +10415,80 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.25</v>
+        <v>2.7</v>
       </c>
       <c r="O62">
-        <v>5.25</v>
+        <v>3.5</v>
       </c>
       <c r="P62">
-        <v>9.08</v>
+        <v>2.3</v>
       </c>
       <c r="Q62">
-        <v>1.64</v>
+        <v>3.42</v>
       </c>
       <c r="R62">
-        <v>2.8</v>
+        <v>2.12</v>
       </c>
       <c r="S62">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="T62">
-        <v>4.5</v>
+        <v>3.23</v>
       </c>
       <c r="U62">
-        <v>1.94</v>
+        <v>2.46</v>
       </c>
       <c r="V62">
-        <v>1.74</v>
+        <v>1.46</v>
       </c>
       <c r="W62">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="X62">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y62">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="Z62">
-        <v>6.25</v>
+        <v>4.1</v>
       </c>
       <c r="AA62">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="AB62">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="AC62">
-        <v>1.87</v>
+        <v>2.9</v>
       </c>
       <c r="AD62">
-        <v>1.79</v>
+        <v>1.4</v>
       </c>
       <c r="AE62">
+        <v>1.1</v>
+      </c>
+      <c r="AF62">
+        <v>1.62</v>
+      </c>
+      <c r="AG62">
+        <v>2.15</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ62">
         <v>1.28</v>
       </c>
-      <c r="AF62">
-        <v>1.67</v>
-      </c>
-      <c r="AG62">
-        <v>2.1</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ62">
-        <v>1.03</v>
-      </c>
       <c r="AK62">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>2026-10-16 14:30:00</t>
+          <t>2026-10-16 14:00:00</t>
         </is>
       </c>
     </row>
@@ -10531,12 +10531,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="O63">
-        <v>3.95</v>
+        <v>5.25</v>
       </c>
       <c r="P63">
-        <v>3.5</v>
+        <v>9.08</v>
       </c>
       <c r="Q63">
-        <v>2.28</v>
+        <v>1.64</v>
       </c>
       <c r="R63">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="S63">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T63">
-        <v>3.94</v>
+        <v>4.5</v>
       </c>
       <c r="U63">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="V63">
         <v>1.74</v>
       </c>
       <c r="W63">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X63">
         <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="Z63">
-        <v>5.89</v>
+        <v>6.25</v>
       </c>
       <c r="AA63">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB63">
         <v>3.1</v>
       </c>
       <c r="AC63">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AD63">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AE63">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AF63">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="AG63">
-        <v>2.71</v>
+        <v>2.1</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.22</v>
+        <v>1.03</v>
       </c>
       <c r="AK63">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10682,7 +10682,7 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>2026-10-16 15:00:00</t>
+          <t>2026-10-16 14:30:00</t>
         </is>
       </c>
     </row>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,80 +10741,80 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="O64">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="P64">
-        <v>2.61</v>
+        <v>3.5</v>
       </c>
       <c r="Q64">
-        <v>2.79</v>
+        <v>2.28</v>
       </c>
       <c r="R64">
         <v>2.5</v>
       </c>
       <c r="S64">
+        <v>1.17</v>
+      </c>
+      <c r="T64">
+        <v>3.94</v>
+      </c>
+      <c r="U64">
+        <v>2.02</v>
+      </c>
+      <c r="V64">
+        <v>1.74</v>
+      </c>
+      <c r="W64">
+        <v>1.2</v>
+      </c>
+      <c r="X64">
+        <v>1.01</v>
+      </c>
+      <c r="Y64">
+        <v>1.12</v>
+      </c>
+      <c r="Z64">
+        <v>5.89</v>
+      </c>
+      <c r="AA64">
+        <v>1.36</v>
+      </c>
+      <c r="AB64">
+        <v>3.1</v>
+      </c>
+      <c r="AC64">
+        <v>1.98</v>
+      </c>
+      <c r="AD64">
+        <v>1.74</v>
+      </c>
+      <c r="AE64">
+        <v>1.32</v>
+      </c>
+      <c r="AF64">
+        <v>1.38</v>
+      </c>
+      <c r="AG64">
+        <v>2.71</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ64">
         <v>1.22</v>
       </c>
-      <c r="T64">
-        <v>3.7</v>
-      </c>
-      <c r="U64">
-        <v>2.2</v>
-      </c>
-      <c r="V64">
-        <v>1.64</v>
-      </c>
-      <c r="W64">
-        <v>1.14</v>
-      </c>
-      <c r="X64">
-        <v>1.02</v>
-      </c>
-      <c r="Y64">
-        <v>1.14</v>
-      </c>
-      <c r="Z64">
-        <v>4.85</v>
-      </c>
-      <c r="AA64">
-        <v>1.5</v>
-      </c>
-      <c r="AB64">
-        <v>2.55</v>
-      </c>
-      <c r="AC64">
-        <v>2.3</v>
-      </c>
-      <c r="AD64">
-        <v>1.58</v>
-      </c>
-      <c r="AE64">
-        <v>1.21</v>
-      </c>
-      <c r="AF64">
-        <v>1.44</v>
-      </c>
-      <c r="AG64">
-        <v>2.5</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ64">
-        <v>1.35</v>
-      </c>
       <c r="AK64">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10862,7 +10862,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="O65">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P65">
-        <v>3.29</v>
+        <v>2.61</v>
       </c>
       <c r="Q65">
-        <v>2.63</v>
+        <v>2.48</v>
       </c>
       <c r="R65">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="S65">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="T65">
-        <v>3.02</v>
+        <v>3.7</v>
       </c>
       <c r="U65">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="V65">
-        <v>1.46</v>
+        <v>1.64</v>
       </c>
       <c r="W65">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X65">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="Z65">
-        <v>3.5</v>
+        <v>4.85</v>
       </c>
       <c r="AA65">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AB65">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="AC65">
-        <v>3.06</v>
+        <v>2.3</v>
       </c>
       <c r="AD65">
-        <v>1.32</v>
+        <v>1.58</v>
       </c>
       <c r="AE65">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="AF65">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AG65">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK65">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,80 +11067,80 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.59</v>
+        <v>2</v>
       </c>
       <c r="O66">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="P66">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q66">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="R66">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="S66">
-        <v>1.49</v>
+        <v>1.32</v>
       </c>
       <c r="T66">
-        <v>2.39</v>
+        <v>3.02</v>
       </c>
       <c r="U66">
-        <v>3.33</v>
+        <v>2.48</v>
       </c>
       <c r="V66">
+        <v>1.46</v>
+      </c>
+      <c r="W66">
+        <v>1.09</v>
+      </c>
+      <c r="X66">
+        <v>1.01</v>
+      </c>
+      <c r="Y66">
+        <v>1.27</v>
+      </c>
+      <c r="Z66">
+        <v>3.5</v>
+      </c>
+      <c r="AA66">
+        <v>1.85</v>
+      </c>
+      <c r="AB66">
+        <v>2</v>
+      </c>
+      <c r="AC66">
+        <v>3.09</v>
+      </c>
+      <c r="AD66">
+        <v>1.38</v>
+      </c>
+      <c r="AE66">
+        <v>1.14</v>
+      </c>
+      <c r="AF66">
+        <v>1.67</v>
+      </c>
+      <c r="AG66">
+        <v>2.1</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ66">
         <v>1.3</v>
       </c>
-      <c r="W66">
-        <v>1.04</v>
-      </c>
-      <c r="X66">
-        <v>1.04</v>
-      </c>
-      <c r="Y66">
-        <v>1.42</v>
-      </c>
-      <c r="Z66">
-        <v>2.75</v>
-      </c>
-      <c r="AA66">
-        <v>2.3</v>
-      </c>
-      <c r="AB66">
-        <v>1.61</v>
-      </c>
-      <c r="AC66">
-        <v>4.15</v>
-      </c>
-      <c r="AD66">
-        <v>1.17</v>
-      </c>
-      <c r="AE66">
-        <v>1.02</v>
-      </c>
-      <c r="AF66">
-        <v>1.94</v>
-      </c>
-      <c r="AG66">
-        <v>1.77</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ66">
-        <v>1.36</v>
-      </c>
       <c r="AK66">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11233,16 +11233,16 @@
         <v>2.15</v>
       </c>
       <c r="O67">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P67">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="Q67">
-        <v>2.69</v>
+        <v>2.78</v>
       </c>
       <c r="R67">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S67">
         <v>1.36</v>
@@ -11251,7 +11251,7 @@
         <v>2.88</v>
       </c>
       <c r="U67">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="V67">
         <v>1.4</v>
@@ -11269,10 +11269,10 @@
         <v>3.08</v>
       </c>
       <c r="AA67">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="AB67">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AC67">
         <v>3.5</v>
@@ -11281,7 +11281,7 @@
         <v>1.25</v>
       </c>
       <c r="AE67">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF67">
         <v>1.8</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.72</v>
+        <v>2.63</v>
       </c>
       <c r="O68">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P68">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="Q68">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="R68">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="S68">
-        <v>1.29</v>
+        <v>1.49</v>
       </c>
       <c r="T68">
-        <v>3.46</v>
+        <v>2.39</v>
       </c>
       <c r="U68">
-        <v>2.33</v>
+        <v>3.33</v>
       </c>
       <c r="V68">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="W68">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X68">
+        <v>1.04</v>
+      </c>
+      <c r="Y68">
+        <v>1.43</v>
+      </c>
+      <c r="Z68">
+        <v>2.85</v>
+      </c>
+      <c r="AA68">
+        <v>2.3</v>
+      </c>
+      <c r="AB68">
+        <v>1.6</v>
+      </c>
+      <c r="AC68">
+        <v>4.15</v>
+      </c>
+      <c r="AD68">
+        <v>1.17</v>
+      </c>
+      <c r="AE68">
         <v>1.02</v>
       </c>
-      <c r="Y68">
-        <v>1.21</v>
-      </c>
-      <c r="Z68">
-        <v>4.4</v>
-      </c>
-      <c r="AA68">
-        <v>1.65</v>
-      </c>
-      <c r="AB68">
-        <v>2.15</v>
-      </c>
-      <c r="AC68">
-        <v>2.7</v>
-      </c>
-      <c r="AD68">
-        <v>1.43</v>
-      </c>
-      <c r="AE68">
-        <v>1.14</v>
-      </c>
       <c r="AF68">
-        <v>1.62</v>
+        <v>1.94</v>
       </c>
       <c r="AG68">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AK68">
-        <v>2.1</v>
+        <v>1.41</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,80 +11556,80 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.65</v>
+        <v>1.73</v>
       </c>
       <c r="O69">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="P69">
-        <v>2.45</v>
+        <v>4.4</v>
       </c>
       <c r="Q69">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="R69">
+        <v>2.24</v>
+      </c>
+      <c r="S69">
+        <v>1.29</v>
+      </c>
+      <c r="T69">
+        <v>3.46</v>
+      </c>
+      <c r="U69">
+        <v>2.4</v>
+      </c>
+      <c r="V69">
+        <v>1.52</v>
+      </c>
+      <c r="W69">
+        <v>1.12</v>
+      </c>
+      <c r="X69">
+        <v>1.02</v>
+      </c>
+      <c r="Y69">
+        <v>1.21</v>
+      </c>
+      <c r="Z69">
+        <v>4.4</v>
+      </c>
+      <c r="AA69">
+        <v>1.65</v>
+      </c>
+      <c r="AB69">
+        <v>2.19</v>
+      </c>
+      <c r="AC69">
+        <v>2.7</v>
+      </c>
+      <c r="AD69">
+        <v>1.43</v>
+      </c>
+      <c r="AE69">
+        <v>1.14</v>
+      </c>
+      <c r="AF69">
+        <v>1.62</v>
+      </c>
+      <c r="AG69">
+        <v>2.15</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ69">
+        <v>1.17</v>
+      </c>
+      <c r="AK69">
         <v>2.1</v>
-      </c>
-      <c r="S69">
-        <v>1.37</v>
-      </c>
-      <c r="T69">
-        <v>2.64</v>
-      </c>
-      <c r="U69">
-        <v>2.67</v>
-      </c>
-      <c r="V69">
-        <v>1.36</v>
-      </c>
-      <c r="W69">
-        <v>1.08</v>
-      </c>
-      <c r="X69">
-        <v>1</v>
-      </c>
-      <c r="Y69">
-        <v>1.29</v>
-      </c>
-      <c r="Z69">
-        <v>3.4</v>
-      </c>
-      <c r="AA69">
-        <v>1.93</v>
-      </c>
-      <c r="AB69">
-        <v>1.81</v>
-      </c>
-      <c r="AC69">
-        <v>3.4</v>
-      </c>
-      <c r="AD69">
-        <v>1.29</v>
-      </c>
-      <c r="AE69">
-        <v>1.06</v>
-      </c>
-      <c r="AF69">
-        <v>1.71</v>
-      </c>
-      <c r="AG69">
-        <v>2.02</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ69">
-        <v>1.44</v>
-      </c>
-      <c r="AK69">
-        <v>1.44</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11677,7 +11677,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.44</v>
+        <v>2.55</v>
       </c>
       <c r="O70">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="P70">
-        <v>5.8</v>
+        <v>2.6</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T70">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U70">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="V70">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W70">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y70">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z70">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA70">
-        <v>1.72</v>
+        <v>2.03</v>
       </c>
       <c r="AB70">
-        <v>2.07</v>
+        <v>1.81</v>
       </c>
       <c r="AC70">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD70">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE70">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF70">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK70">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11840,7 +11840,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="O71">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="P71">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="Q71">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="R71">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S71">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T71">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="U71">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V71">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="W71">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X71">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y71">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z71">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA71">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="AB71">
-        <v>2.88</v>
+        <v>2.07</v>
       </c>
       <c r="AC71">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD71">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AE71">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF71">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG71">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK71">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12003,7 +12003,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>3.38</v>
+        <v>1.67</v>
       </c>
       <c r="O72">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="P72">
-        <v>1.86</v>
+        <v>4.5</v>
       </c>
       <c r="Q72">
-        <v>3.63</v>
+        <v>2.16</v>
       </c>
       <c r="R72">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="S72">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T72">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="U72">
-        <v>2.21</v>
+        <v>2.02</v>
       </c>
       <c r="V72">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="W72">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X72">
         <v>1.02</v>
       </c>
       <c r="Y72">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z72">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="AA72">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AB72">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="AC72">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AD72">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="AE72">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AF72">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG72">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.79</v>
+        <v>1.22</v>
       </c>
       <c r="AK72">
-        <v>1.29</v>
+        <v>2.14</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>5</v>
+        <v>3.38</v>
       </c>
       <c r="O73">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="P73">
-        <v>1.48</v>
+        <v>1.86</v>
       </c>
       <c r="Q73">
-        <v>5</v>
+        <v>3.63</v>
       </c>
       <c r="R73">
-        <v>2.51</v>
+        <v>2.4</v>
       </c>
       <c r="S73">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="T73">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="U73">
-        <v>1.93</v>
+        <v>2.21</v>
       </c>
       <c r="V73">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="W73">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X73">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y73">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z73">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA73">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AB73">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="AC73">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AD73">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AE73">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AF73">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG73">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.14</v>
+        <v>1.79</v>
       </c>
       <c r="AK73">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.68</v>
+        <v>5</v>
       </c>
       <c r="O74">
-        <v>3.9</v>
+        <v>4.75</v>
       </c>
       <c r="P74">
-        <v>3.58</v>
+        <v>1.48</v>
       </c>
       <c r="Q74">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="R74">
-        <v>2.56</v>
+        <v>2.51</v>
       </c>
       <c r="S74">
         <v>1.18</v>
       </c>
       <c r="T74">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="U74">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="V74">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="W74">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="X74">
         <v>1.01</v>
       </c>
       <c r="Y74">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z74">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AA74">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB74">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AC74">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AD74">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AE74">
         <v>1.33</v>
       </c>
       <c r="AF74">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AG74">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK74">
-        <v>2.05</v>
+        <v>1.15</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.07</v>
+        <v>1.68</v>
       </c>
       <c r="O75">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P75">
-        <v>2.7</v>
+        <v>3.58</v>
       </c>
       <c r="Q75">
-        <v>2.52</v>
+        <v>2.1</v>
       </c>
       <c r="R75">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="S75">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T75">
         <v>4.5</v>
       </c>
       <c r="U75">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="V75">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="W75">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="X75">
         <v>1.01</v>
       </c>
       <c r="Y75">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Z75">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AA75">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AB75">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="AC75">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AD75">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="AE75">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AF75">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AG75">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK75">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12650,12 +12650,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
+        <v>2.07</v>
+      </c>
+      <c r="O76">
+        <v>3.75</v>
+      </c>
+      <c r="P76">
+        <v>2.7</v>
+      </c>
+      <c r="Q76">
+        <v>2.52</v>
+      </c>
+      <c r="R76">
+        <v>2.6</v>
+      </c>
+      <c r="S76">
+        <v>1.17</v>
+      </c>
+      <c r="T76">
+        <v>4.5</v>
+      </c>
+      <c r="U76">
         <v>1.82</v>
       </c>
-      <c r="O76">
-        <v>3.4</v>
-      </c>
-      <c r="P76">
-        <v>4.1</v>
-      </c>
-      <c r="Q76">
-        <v>2.3</v>
-      </c>
-      <c r="R76">
-        <v>2.3</v>
-      </c>
-      <c r="S76">
+      <c r="V76">
+        <v>1.86</v>
+      </c>
+      <c r="W76">
+        <v>1.22</v>
+      </c>
+      <c r="X76">
+        <v>1.01</v>
+      </c>
+      <c r="Y76">
+        <v>1.03</v>
+      </c>
+      <c r="Z76">
+        <v>7.2</v>
+      </c>
+      <c r="AA76">
+        <v>1.29</v>
+      </c>
+      <c r="AB76">
+        <v>3.5</v>
+      </c>
+      <c r="AC76">
+        <v>1.82</v>
+      </c>
+      <c r="AD76">
+        <v>1.99</v>
+      </c>
+      <c r="AE76">
+        <v>1.39</v>
+      </c>
+      <c r="AF76">
         <v>1.3</v>
       </c>
-      <c r="T76">
-        <v>3.2</v>
-      </c>
-      <c r="U76">
-        <v>2.72</v>
-      </c>
-      <c r="V76">
-        <v>1.45</v>
-      </c>
-      <c r="W76">
-        <v>1.07</v>
-      </c>
-      <c r="X76">
-        <v>1.02</v>
-      </c>
-      <c r="Y76">
-        <v>1.22</v>
-      </c>
-      <c r="Z76">
-        <v>3.8</v>
-      </c>
-      <c r="AA76">
-        <v>1.74</v>
-      </c>
-      <c r="AB76">
-        <v>1.93</v>
-      </c>
-      <c r="AC76">
-        <v>3</v>
-      </c>
-      <c r="AD76">
-        <v>1.33</v>
-      </c>
-      <c r="AE76">
-        <v>1.1</v>
-      </c>
-      <c r="AF76">
-        <v>1.67</v>
-      </c>
       <c r="AG76">
-        <v>2.05</v>
+        <v>3.5</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AK76">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12801,7 +12801,7 @@
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>2026-10-16 15:30:00</t>
+          <t>2026-10-16 15:00:00</t>
         </is>
       </c>
     </row>
@@ -12818,7 +12818,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="O77">
         <v>3.4</v>
       </c>
       <c r="P77">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q77">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="R77">
         <v>2.3</v>
       </c>
       <c r="S77">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T77">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U77">
-        <v>2.4</v>
+        <v>2.72</v>
       </c>
       <c r="V77">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="W77">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X77">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y77">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z77">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="AA77">
+        <v>1.74</v>
+      </c>
+      <c r="AB77">
+        <v>1.93</v>
+      </c>
+      <c r="AC77">
+        <v>3</v>
+      </c>
+      <c r="AD77">
+        <v>1.33</v>
+      </c>
+      <c r="AE77">
+        <v>1.1</v>
+      </c>
+      <c r="AF77">
         <v>1.67</v>
       </c>
-      <c r="AB77">
-        <v>2.15</v>
-      </c>
-      <c r="AC77">
-        <v>2.75</v>
-      </c>
-      <c r="AD77">
-        <v>1.4</v>
-      </c>
-      <c r="AE77">
-        <v>1.17</v>
-      </c>
-      <c r="AF77">
-        <v>1.57</v>
-      </c>
       <c r="AG77">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK77">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12981,7 +12981,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="O78">
         <v>3.4</v>
       </c>
       <c r="P78">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="Q78">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="R78">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S78">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="T78">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="U78">
-        <v>2.59</v>
+        <v>2.4</v>
       </c>
       <c r="V78">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="W78">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X78">
         <v>1.03</v>
       </c>
       <c r="Y78">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z78">
-        <v>3.6</v>
+        <v>3.84</v>
       </c>
       <c r="AA78">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AB78">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="AC78">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="AD78">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AE78">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AF78">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AG78">
-        <v>1.95</v>
+        <v>2.16</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK78">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13144,7 +13144,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>4</v>
+        <v>1.83</v>
       </c>
       <c r="O79">
+        <v>3.4</v>
+      </c>
+      <c r="P79">
         <v>3.6</v>
       </c>
-      <c r="P79">
-        <v>1.7</v>
-      </c>
       <c r="Q79">
-        <v>4.4</v>
+        <v>2.41</v>
       </c>
       <c r="R79">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="S79">
+        <v>1.34</v>
+      </c>
+      <c r="T79">
+        <v>2.8</v>
+      </c>
+      <c r="U79">
+        <v>2.59</v>
+      </c>
+      <c r="V79">
+        <v>1.42</v>
+      </c>
+      <c r="W79">
+        <v>1.06</v>
+      </c>
+      <c r="X79">
+        <v>1.03</v>
+      </c>
+      <c r="Y79">
+        <v>1.25</v>
+      </c>
+      <c r="Z79">
+        <v>3.6</v>
+      </c>
+      <c r="AA79">
+        <v>1.9</v>
+      </c>
+      <c r="AB79">
+        <v>1.87</v>
+      </c>
+      <c r="AC79">
+        <v>3.25</v>
+      </c>
+      <c r="AD79">
         <v>1.3</v>
       </c>
-      <c r="T79">
-        <v>2.88</v>
-      </c>
-      <c r="U79">
-        <v>2.44</v>
-      </c>
-      <c r="V79">
-        <v>1.5</v>
-      </c>
-      <c r="W79">
-        <v>1.09</v>
-      </c>
-      <c r="X79">
-        <v>1.01</v>
-      </c>
-      <c r="Y79">
-        <v>1.24</v>
-      </c>
-      <c r="Z79">
-        <v>3.58</v>
-      </c>
-      <c r="AA79">
+      <c r="AE79">
+        <v>1.08</v>
+      </c>
+      <c r="AF79">
         <v>1.75</v>
       </c>
-      <c r="AB79">
-        <v>2.05</v>
-      </c>
-      <c r="AC79">
-        <v>2.74</v>
-      </c>
-      <c r="AD79">
-        <v>1.35</v>
-      </c>
-      <c r="AE79">
-        <v>1.1</v>
-      </c>
-      <c r="AF79">
-        <v>1.67</v>
-      </c>
       <c r="AG79">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK79">
-        <v>1.14</v>
+        <v>1.93</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13307,7 +13307,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="O80">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P80">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="Q80">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S80">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T80">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U80">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V80">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W80">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X80">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y80">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z80">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA80">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AB80">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AC80">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD80">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG80">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK80">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13470,7 +13470,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="O81">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P81">
-        <v>2.97</v>
+        <v>2.7</v>
       </c>
       <c r="Q81">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="R81">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S81">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T81">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U81">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="V81">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W81">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X81">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y81">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z81">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA81">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB81">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC81">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD81">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE81">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF81">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG81">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK81">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13633,7 +13633,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G82">
@@ -13678,58 +13678,58 @@
         <v>2.2</v>
       </c>
       <c r="O82">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P82">
-        <v>2.75</v>
+        <v>2.97</v>
       </c>
       <c r="Q82">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="R82">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="S82">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T82">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="U82">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="V82">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W82">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X82">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y82">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z82">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AA82">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AB82">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AC82">
-        <v>2.52</v>
+        <v>2.88</v>
       </c>
       <c r="AD82">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AE82">
         <v>1.14</v>
       </c>
       <c r="AF82">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG82">
         <v>2.3</v>
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK82">
         <v>1.57</v>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="O83">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P83">
-        <v>2.37</v>
+        <v>2.85</v>
       </c>
       <c r="Q83">
-        <v>3.45</v>
+        <v>2.8</v>
       </c>
       <c r="R83">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S83">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T83">
-        <v>3</v>
+        <v>3.32</v>
       </c>
       <c r="U83">
-        <v>2.78</v>
+        <v>2.31</v>
       </c>
       <c r="V83">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="W83">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X83">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z83">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA83">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="AB83">
-        <v>1.87</v>
+        <v>2.14</v>
       </c>
       <c r="AC83">
-        <v>2.97</v>
+        <v>2.52</v>
       </c>
       <c r="AD83">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AE83">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF83">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AG83">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>1.25</v>
       </c>
       <c r="AK83">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13959,7 +13959,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.92</v>
+        <v>2.7</v>
       </c>
       <c r="O84">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="P84">
-        <v>3.36</v>
+        <v>2.37</v>
       </c>
       <c r="Q84">
-        <v>2.26</v>
+        <v>3.45</v>
       </c>
       <c r="R84">
-        <v>2.53</v>
+        <v>2.1</v>
       </c>
       <c r="S84">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="T84">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="U84">
-        <v>1.86</v>
+        <v>2.78</v>
       </c>
       <c r="V84">
-        <v>1.81</v>
+        <v>1.4</v>
       </c>
       <c r="W84">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="X84">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y84">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="Z84">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="AA84">
-        <v>1.36</v>
+        <v>1.9</v>
       </c>
       <c r="AB84">
-        <v>3.2</v>
+        <v>1.87</v>
       </c>
       <c r="AC84">
-        <v>1.87</v>
+        <v>2.97</v>
       </c>
       <c r="AD84">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="AE84">
-        <v>1.38</v>
+        <v>1.08</v>
       </c>
       <c r="AF84">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AG84">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
         <v>1.25</v>
       </c>
       <c r="AK84">
-        <v>1.91</v>
+        <v>1.33</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14117,12 +14117,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,80 +14164,80 @@
         </is>
       </c>
       <c r="N85">
+        <v>1.84</v>
+      </c>
+      <c r="O85">
+        <v>4</v>
+      </c>
+      <c r="P85">
+        <v>3.5</v>
+      </c>
+      <c r="Q85">
         <v>2.25</v>
       </c>
-      <c r="O85">
-        <v>3.2</v>
-      </c>
-      <c r="P85">
-        <v>2.87</v>
-      </c>
-      <c r="Q85">
-        <v>2.97</v>
-      </c>
       <c r="R85">
-        <v>2.1</v>
+        <v>2.53</v>
       </c>
       <c r="S85">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="T85">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="U85">
-        <v>2.8</v>
+        <v>1.86</v>
       </c>
       <c r="V85">
-        <v>1.36</v>
+        <v>1.81</v>
       </c>
       <c r="W85">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="X85">
         <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>1.31</v>
+        <v>1.05</v>
       </c>
       <c r="Z85">
-        <v>3.08</v>
+        <v>7.5</v>
       </c>
       <c r="AA85">
-        <v>2.05</v>
+        <v>1.36</v>
       </c>
       <c r="AB85">
-        <v>1.75</v>
+        <v>3.2</v>
       </c>
       <c r="AC85">
-        <v>2.8</v>
+        <v>1.87</v>
       </c>
       <c r="AD85">
+        <v>1.9</v>
+      </c>
+      <c r="AE85">
+        <v>1.38</v>
+      </c>
+      <c r="AF85">
+        <v>1.36</v>
+      </c>
+      <c r="AG85">
+        <v>3</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ85">
         <v>1.25</v>
       </c>
-      <c r="AE85">
-        <v>1.04</v>
-      </c>
-      <c r="AF85">
-        <v>1.6</v>
-      </c>
-      <c r="AG85">
-        <v>2.05</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI85" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ85">
-        <v>1.3</v>
-      </c>
       <c r="AK85">
-        <v>1.47</v>
+        <v>1.91</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14268,7 +14268,7 @@
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>2026-10-16 15:45:00</t>
+          <t>2026-10-16 15:30:00</t>
         </is>
       </c>
     </row>
@@ -14285,7 +14285,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,80 +14327,80 @@
         </is>
       </c>
       <c r="N86">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="O86">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="P86">
-        <v>2.31</v>
+        <v>2.87</v>
       </c>
       <c r="Q86">
-        <v>3.58</v>
+        <v>2.97</v>
       </c>
       <c r="R86">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S86">
+        <v>1.37</v>
+      </c>
+      <c r="T86">
+        <v>2.2</v>
+      </c>
+      <c r="U86">
+        <v>2.8</v>
+      </c>
+      <c r="V86">
+        <v>1.36</v>
+      </c>
+      <c r="W86">
+        <v>1.05</v>
+      </c>
+      <c r="X86">
+        <v>1.01</v>
+      </c>
+      <c r="Y86">
+        <v>1.31</v>
+      </c>
+      <c r="Z86">
+        <v>3.08</v>
+      </c>
+      <c r="AA86">
+        <v>2.05</v>
+      </c>
+      <c r="AB86">
+        <v>1.75</v>
+      </c>
+      <c r="AC86">
+        <v>2.8</v>
+      </c>
+      <c r="AD86">
+        <v>1.25</v>
+      </c>
+      <c r="AE86">
+        <v>1.04</v>
+      </c>
+      <c r="AF86">
+        <v>1.6</v>
+      </c>
+      <c r="AG86">
+        <v>2.05</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ86">
         <v>1.3</v>
       </c>
-      <c r="T86">
-        <v>3.18</v>
-      </c>
-      <c r="U86">
-        <v>2.55</v>
-      </c>
-      <c r="V86">
-        <v>1.53</v>
-      </c>
-      <c r="W86">
-        <v>1.12</v>
-      </c>
-      <c r="X86">
-        <v>1.02</v>
-      </c>
-      <c r="Y86">
-        <v>1.19</v>
-      </c>
-      <c r="Z86">
-        <v>4.25</v>
-      </c>
-      <c r="AA86">
-        <v>1.76</v>
-      </c>
-      <c r="AB86">
-        <v>2.16</v>
-      </c>
-      <c r="AC86">
-        <v>2.88</v>
-      </c>
-      <c r="AD86">
-        <v>1.44</v>
-      </c>
-      <c r="AE86">
-        <v>1.14</v>
-      </c>
-      <c r="AF86">
-        <v>1.53</v>
-      </c>
-      <c r="AG86">
-        <v>2.32</v>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI86" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ86">
-        <v>1.57</v>
-      </c>
       <c r="AK86">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14448,22 +14448,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,34 +14490,34 @@
         </is>
       </c>
       <c r="N87">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O87">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="P87">
-        <v>1.72</v>
+        <v>2.31</v>
       </c>
       <c r="Q87">
-        <v>4.33</v>
+        <v>3.58</v>
       </c>
       <c r="R87">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="S87">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T87">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="U87">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="V87">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W87">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X87">
         <v>1.02</v>
@@ -14526,28 +14526,28 @@
         <v>1.19</v>
       </c>
       <c r="Z87">
-        <v>3.75</v>
+        <v>4.25</v>
       </c>
       <c r="AA87">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AB87">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="AC87">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="AD87">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE87">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF87">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AG87">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="AK87">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,61 +14653,61 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="O88">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="P88">
-        <v>2.15</v>
+        <v>1.72</v>
       </c>
       <c r="Q88">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="R88">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="S88">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T88">
-        <v>2.82</v>
+        <v>3.22</v>
       </c>
       <c r="U88">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V88">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W88">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X88">
         <v>1.02</v>
       </c>
       <c r="Y88">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z88">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="AA88">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AB88">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AC88">
-        <v>2.97</v>
+        <v>2.69</v>
       </c>
       <c r="AD88">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE88">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF88">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AG88">
         <v>2.1</v>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK88">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,65 +14979,65 @@
         </is>
       </c>
       <c r="N90">
-        <v>5.72</v>
+        <v>2.9</v>
       </c>
       <c r="O90">
-        <v>4.75</v>
+        <v>3.25</v>
       </c>
       <c r="P90">
-        <v>1.38</v>
+        <v>2.15</v>
       </c>
       <c r="Q90">
-        <v>4.25</v>
+        <v>3.25</v>
       </c>
       <c r="R90">
-        <v>2.62</v>
+        <v>2.32</v>
       </c>
       <c r="S90">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T90">
-        <v>4</v>
+        <v>2.82</v>
       </c>
       <c r="U90">
+        <v>2.5</v>
+      </c>
+      <c r="V90">
+        <v>1.44</v>
+      </c>
+      <c r="W90">
+        <v>1.11</v>
+      </c>
+      <c r="X90">
+        <v>1.02</v>
+      </c>
+      <c r="Y90">
+        <v>1.21</v>
+      </c>
+      <c r="Z90">
+        <v>3.58</v>
+      </c>
+      <c r="AA90">
+        <v>1.82</v>
+      </c>
+      <c r="AB90">
+        <v>2.06</v>
+      </c>
+      <c r="AC90">
+        <v>2.97</v>
+      </c>
+      <c r="AD90">
+        <v>1.3</v>
+      </c>
+      <c r="AE90">
+        <v>1.07</v>
+      </c>
+      <c r="AF90">
+        <v>1.65</v>
+      </c>
+      <c r="AG90">
         <v>2.1</v>
       </c>
-      <c r="V90">
-        <v>1.75</v>
-      </c>
-      <c r="W90">
-        <v>1.17</v>
-      </c>
-      <c r="X90">
-        <v>1.01</v>
-      </c>
-      <c r="Y90">
-        <v>1.13</v>
-      </c>
-      <c r="Z90">
-        <v>5.67</v>
-      </c>
-      <c r="AA90">
-        <v>1.4</v>
-      </c>
-      <c r="AB90">
-        <v>2.88</v>
-      </c>
-      <c r="AC90">
-        <v>2.15</v>
-      </c>
-      <c r="AD90">
-        <v>1.67</v>
-      </c>
-      <c r="AE90">
-        <v>1.29</v>
-      </c>
-      <c r="AF90">
-        <v>1.55</v>
-      </c>
-      <c r="AG90">
-        <v>2.25</v>
-      </c>
       <c r="AH90" t="inlineStr">
         <is>
           <t>[]</t>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>2.8</v>
+        <v>1.28</v>
       </c>
       <c r="AK90">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.7</v>
+        <v>5.72</v>
       </c>
       <c r="O91">
-        <v>3.4</v>
+        <v>4.75</v>
       </c>
       <c r="P91">
-        <v>2.15</v>
+        <v>1.38</v>
       </c>
       <c r="Q91">
-        <v>3.3</v>
+        <v>4.25</v>
       </c>
       <c r="R91">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="S91">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T91">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U91">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="V91">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="W91">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X91">
         <v>1.01</v>
       </c>
       <c r="Y91">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z91">
-        <v>5</v>
+        <v>5.67</v>
       </c>
       <c r="AA91">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AB91">
-        <v>2.36</v>
+        <v>2.88</v>
       </c>
       <c r="AC91">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="AD91">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AE91">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AF91">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG91">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.25</v>
+        <v>2.8</v>
       </c>
       <c r="AK91">
-        <v>1.4</v>
+        <v>1.11</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="O92">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P92">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="Q92">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="R92">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="S92">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T92">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="U92">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="V92">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="W92">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X92">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y92">
+        <v>1.17</v>
+      </c>
+      <c r="Z92">
+        <v>5</v>
+      </c>
+      <c r="AA92">
+        <v>1.57</v>
+      </c>
+      <c r="AB92">
+        <v>2.36</v>
+      </c>
+      <c r="AC92">
+        <v>2.55</v>
+      </c>
+      <c r="AD92">
+        <v>1.5</v>
+      </c>
+      <c r="AE92">
         <v>1.2</v>
       </c>
-      <c r="Z92">
-        <v>3.7</v>
-      </c>
-      <c r="AA92">
-        <v>1.76</v>
-      </c>
-      <c r="AB92">
-        <v>1.98</v>
-      </c>
-      <c r="AC92">
-        <v>2.88</v>
-      </c>
-      <c r="AD92">
-        <v>1.41</v>
-      </c>
-      <c r="AE92">
-        <v>1.08</v>
-      </c>
       <c r="AF92">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG92">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK92">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.38</v>
+        <v>3.15</v>
       </c>
       <c r="O93">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P93">
-        <v>2.45</v>
+        <v>1.92</v>
       </c>
       <c r="Q93">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="R93">
-        <v>2.46</v>
+        <v>2.16</v>
       </c>
       <c r="S93">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="T93">
-        <v>3.52</v>
+        <v>3.1</v>
       </c>
       <c r="U93">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="V93">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="W93">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X93">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y93">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z93">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
       <c r="AA93">
-        <v>1.53</v>
+        <v>1.76</v>
       </c>
       <c r="AB93">
-        <v>2.55</v>
+        <v>1.98</v>
       </c>
       <c r="AC93">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="AD93">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="AE93">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AF93">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AG93">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AK93">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,61 +15631,61 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.9</v>
+        <v>2.38</v>
       </c>
       <c r="O94">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P94">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="Q94">
-        <v>3.42</v>
+        <v>2.8</v>
       </c>
       <c r="R94">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="S94">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T94">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="U94">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="V94">
+        <v>1.6</v>
+      </c>
+      <c r="W94">
+        <v>1.15</v>
+      </c>
+      <c r="X94">
+        <v>1.01</v>
+      </c>
+      <c r="Y94">
+        <v>1.14</v>
+      </c>
+      <c r="Z94">
+        <v>5.5</v>
+      </c>
+      <c r="AA94">
         <v>1.53</v>
       </c>
-      <c r="W94">
-        <v>1.12</v>
-      </c>
-      <c r="X94">
-        <v>1.02</v>
-      </c>
-      <c r="Y94">
-        <v>1.2</v>
-      </c>
-      <c r="Z94">
-        <v>4.5</v>
-      </c>
-      <c r="AA94">
+      <c r="AB94">
+        <v>2.55</v>
+      </c>
+      <c r="AC94">
+        <v>2.3</v>
+      </c>
+      <c r="AD94">
         <v>1.6</v>
       </c>
-      <c r="AB94">
-        <v>2.18</v>
-      </c>
-      <c r="AC94">
-        <v>2.46</v>
-      </c>
-      <c r="AD94">
-        <v>1.43</v>
-      </c>
       <c r="AE94">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AF94">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG94">
         <v>2.5</v>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AK94">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15752,22 +15752,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.53</v>
+        <v>2.9</v>
       </c>
       <c r="O95">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P95">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="Q95">
-        <v>3.02</v>
+        <v>3.42</v>
       </c>
       <c r="R95">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="S95">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T95">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="U95">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="V95">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="W95">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X95">
         <v>1.02</v>
       </c>
       <c r="Y95">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="Z95">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AA95">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AB95">
-        <v>2.85</v>
+        <v>2.18</v>
       </c>
       <c r="AC95">
-        <v>2.15</v>
+        <v>2.46</v>
       </c>
       <c r="AD95">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AE95">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AF95">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AG95">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK95">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15910,27 +15910,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,34 +15957,34 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="O96">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P96">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="Q96">
         <v>3.02</v>
       </c>
       <c r="R96">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S96">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T96">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="U96">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="V96">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="W96">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X96">
         <v>1.02</v>
@@ -15993,28 +15993,28 @@
         <v>1.13</v>
       </c>
       <c r="Z96">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AA96">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AB96">
-        <v>2.2</v>
+        <v>2.85</v>
       </c>
       <c r="AC96">
-        <v>2.43</v>
+        <v>2.15</v>
       </c>
       <c r="AD96">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AE96">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AF96">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AG96">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK96">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16061,7 +16061,7 @@
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>2026-10-16 16:00:00</t>
+          <t>2026-10-16 15:45:00</t>
         </is>
       </c>
     </row>
@@ -16078,7 +16078,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.52</v>
+        <v>2.43</v>
       </c>
       <c r="O97">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="P97">
-        <v>5.15</v>
+        <v>2.4</v>
       </c>
       <c r="Q97">
-        <v>2.05</v>
+        <v>3.02</v>
       </c>
       <c r="R97">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="S97">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T97">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="U97">
-        <v>2.55</v>
+        <v>2.23</v>
       </c>
       <c r="V97">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W97">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X97">
         <v>1.02</v>
       </c>
       <c r="Y97">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="Z97">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AA97">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AB97">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AC97">
-        <v>2.74</v>
+        <v>2.43</v>
       </c>
       <c r="AD97">
         <v>1.44</v>
       </c>
       <c r="AE97">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF97">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="AG97">
-        <v>1.97</v>
+        <v>2.45</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AK97">
-        <v>2.26</v>
+        <v>1.42</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16241,22 +16241,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,65 +16283,65 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.11</v>
+        <v>1.52</v>
       </c>
       <c r="O98">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="P98">
-        <v>3.48</v>
+        <v>5.15</v>
       </c>
       <c r="Q98">
-        <v>2.49</v>
+        <v>2.05</v>
       </c>
       <c r="R98">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="S98">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="T98">
-        <v>2.99</v>
+        <v>3.08</v>
       </c>
       <c r="U98">
-        <v>2.92</v>
+        <v>2.55</v>
       </c>
       <c r="V98">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W98">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X98">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y98">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="Z98">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="AA98">
+        <v>1.72</v>
+      </c>
+      <c r="AB98">
+        <v>2.02</v>
+      </c>
+      <c r="AC98">
+        <v>2.74</v>
+      </c>
+      <c r="AD98">
+        <v>1.44</v>
+      </c>
+      <c r="AE98">
+        <v>1.11</v>
+      </c>
+      <c r="AF98">
+        <v>1.75</v>
+      </c>
+      <c r="AG98">
         <v>1.97</v>
       </c>
-      <c r="AB98">
-        <v>1.92</v>
-      </c>
-      <c r="AC98">
-        <v>3.25</v>
-      </c>
-      <c r="AD98">
-        <v>1.32</v>
-      </c>
-      <c r="AE98">
-        <v>1.1</v>
-      </c>
-      <c r="AF98">
-        <v>1.7</v>
-      </c>
-      <c r="AG98">
-        <v>2</v>
-      </c>
       <c r="AH98" t="inlineStr">
         <is>
           <t>[]</t>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AK98">
-        <v>1.77</v>
+        <v>2.26</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16404,7 +16404,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.85</v>
+        <v>2.11</v>
       </c>
       <c r="O99">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P99">
-        <v>2.37</v>
+        <v>3.48</v>
       </c>
       <c r="Q99">
-        <v>3.3</v>
+        <v>2.49</v>
       </c>
       <c r="R99">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="S99">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="T99">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="U99">
-        <v>2.69</v>
+        <v>2.92</v>
       </c>
       <c r="V99">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="W99">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X99">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y99">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="Z99">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="AA99">
-        <v>1.79</v>
+        <v>1.97</v>
       </c>
       <c r="AB99">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AC99">
-        <v>3.02</v>
+        <v>3.25</v>
       </c>
       <c r="AD99">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE99">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF99">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG99">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AK99">
-        <v>1.36</v>
+        <v>1.77</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16562,27 +16562,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.86</v>
+        <v>2.85</v>
       </c>
       <c r="O100">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P100">
-        <v>3.65</v>
+        <v>2.35</v>
       </c>
       <c r="Q100">
-        <v>2.52</v>
+        <v>3.3</v>
       </c>
       <c r="R100">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="S100">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="T100">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
       <c r="U100">
-        <v>3.18</v>
+        <v>2.69</v>
       </c>
       <c r="V100">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="W100">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X100">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y100">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="Z100">
-        <v>2.84</v>
+        <v>3.3</v>
       </c>
       <c r="AA100">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AB100">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="AC100">
-        <v>4.21</v>
+        <v>3.02</v>
       </c>
       <c r="AD100">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AE100">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="AF100">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AG100">
-        <v>1.72</v>
+        <v>2.15</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AK100">
-        <v>1.76</v>
+        <v>1.36</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16713,7 +16713,7 @@
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>2026-10-16 17:30:00</t>
+          <t>2026-10-16 16:00:00</t>
         </is>
       </c>
     </row>
@@ -16725,12 +16725,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>2</v>
+        <v>3.68</v>
       </c>
       <c r="O101">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="P101">
-        <v>3.3</v>
+        <v>1.65</v>
       </c>
       <c r="Q101">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R101">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="S101">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T101">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="U101">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="V101">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="W101">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X101">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y101">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z101">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA101">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AB101">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC101">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD101">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AE101">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF101">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AG101">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK101">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16876,7 +16876,7 @@
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>2026-10-16 18:00:00</t>
+          <t>2026-10-16 16:15:00</t>
         </is>
       </c>
     </row>
@@ -16888,12 +16888,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>11</v>
+        <v>1.86</v>
       </c>
       <c r="O102">
-        <v>5.8</v>
+        <v>3.35</v>
       </c>
       <c r="P102">
-        <v>1.08</v>
+        <v>3.65</v>
       </c>
       <c r="Q102">
-        <v>9.6</v>
+        <v>2.52</v>
       </c>
       <c r="R102">
-        <v>2.61</v>
+        <v>1.96</v>
       </c>
       <c r="S102">
+        <v>1.47</v>
+      </c>
+      <c r="T102">
+        <v>2.63</v>
+      </c>
+      <c r="U102">
+        <v>3.18</v>
+      </c>
+      <c r="V102">
+        <v>1.27</v>
+      </c>
+      <c r="W102">
+        <v>1.05</v>
+      </c>
+      <c r="X102">
+        <v>1.04</v>
+      </c>
+      <c r="Y102">
         <v>1.3</v>
       </c>
-      <c r="T102">
-        <v>3.25</v>
-      </c>
-      <c r="U102">
-        <v>2.26</v>
-      </c>
-      <c r="V102">
-        <v>1.5</v>
-      </c>
-      <c r="W102">
-        <v>1.08</v>
-      </c>
-      <c r="X102">
+      <c r="Z102">
+        <v>2.84</v>
+      </c>
+      <c r="AA102">
+        <v>1.92</v>
+      </c>
+      <c r="AB102">
+        <v>1.61</v>
+      </c>
+      <c r="AC102">
+        <v>4.21</v>
+      </c>
+      <c r="AD102">
+        <v>1.21</v>
+      </c>
+      <c r="AE102">
         <v>1.02</v>
       </c>
-      <c r="Y102">
-        <v>1.16</v>
-      </c>
-      <c r="Z102">
-        <v>4.1</v>
-      </c>
-      <c r="AA102">
-        <v>1.63</v>
-      </c>
-      <c r="AB102">
-        <v>2.17</v>
-      </c>
-      <c r="AC102">
-        <v>2.46</v>
-      </c>
-      <c r="AD102">
-        <v>1.46</v>
-      </c>
-      <c r="AE102">
-        <v>1.15</v>
-      </c>
       <c r="AF102">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AG102">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>4</v>
+        <v>1.25</v>
       </c>
       <c r="AK102">
-        <v>1.04</v>
+        <v>1.76</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17039,7 +17039,7 @@
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>2026-10-16 19:30:00</t>
+          <t>2026-10-16 17:30:00</t>
         </is>
       </c>
     </row>
@@ -17051,12 +17051,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="O103">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="P103">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q103">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R103">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S103">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T103">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U103">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="V103">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W103">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X103">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y103">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z103">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="AA103">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB103">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC103">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD103">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE103">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF103">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG103">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK103">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17202,7 +17202,7 @@
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>2026-10-16 20:00:00</t>
+          <t>2026-10-16 18:00:00</t>
         </is>
       </c>
     </row>
@@ -17214,12 +17214,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,80 +17261,80 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.57</v>
+        <v>11</v>
       </c>
       <c r="O104">
+        <v>5.8</v>
+      </c>
+      <c r="P104">
+        <v>1.08</v>
+      </c>
+      <c r="Q104">
+        <v>9.6</v>
+      </c>
+      <c r="R104">
+        <v>2.61</v>
+      </c>
+      <c r="S104">
+        <v>1.3</v>
+      </c>
+      <c r="T104">
+        <v>3.25</v>
+      </c>
+      <c r="U104">
+        <v>2.26</v>
+      </c>
+      <c r="V104">
+        <v>1.5</v>
+      </c>
+      <c r="W104">
+        <v>1.08</v>
+      </c>
+      <c r="X104">
+        <v>1.02</v>
+      </c>
+      <c r="Y104">
+        <v>1.16</v>
+      </c>
+      <c r="Z104">
+        <v>4.1</v>
+      </c>
+      <c r="AA104">
+        <v>1.63</v>
+      </c>
+      <c r="AB104">
+        <v>2.17</v>
+      </c>
+      <c r="AC104">
+        <v>2.46</v>
+      </c>
+      <c r="AD104">
+        <v>1.46</v>
+      </c>
+      <c r="AE104">
+        <v>1.15</v>
+      </c>
+      <c r="AF104">
+        <v>2.38</v>
+      </c>
+      <c r="AG104">
+        <v>1.62</v>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ104">
         <v>4</v>
       </c>
-      <c r="P104">
-        <v>4.2</v>
-      </c>
-      <c r="Q104">
-        <v>2.03</v>
-      </c>
-      <c r="R104">
-        <v>2.45</v>
-      </c>
-      <c r="S104">
-        <v>1.19</v>
-      </c>
-      <c r="T104">
-        <v>4.2</v>
-      </c>
-      <c r="U104">
-        <v>2.02</v>
-      </c>
-      <c r="V104">
-        <v>1.77</v>
-      </c>
-      <c r="W104">
-        <v>1.2</v>
-      </c>
-      <c r="X104">
-        <v>1.01</v>
-      </c>
-      <c r="Y104">
-        <v>1.06</v>
-      </c>
-      <c r="Z104">
-        <v>6.15</v>
-      </c>
-      <c r="AA104">
-        <v>1.34</v>
-      </c>
-      <c r="AB104">
-        <v>2.78</v>
-      </c>
-      <c r="AC104">
-        <v>1.99</v>
-      </c>
-      <c r="AD104">
-        <v>1.8</v>
-      </c>
-      <c r="AE104">
-        <v>1.3</v>
-      </c>
-      <c r="AF104">
-        <v>1.41</v>
-      </c>
-      <c r="AG104">
-        <v>2.62</v>
-      </c>
-      <c r="AH104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ104">
-        <v>1.14</v>
-      </c>
       <c r="AK104">
-        <v>2.25</v>
+        <v>1.04</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17365,7 +17365,7 @@
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>2026-10-16 20:00:00</t>
+          <t>2026-10-16 19:30:00</t>
         </is>
       </c>
     </row>
@@ -17377,12 +17377,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="O105">
-        <v>3.07</v>
+        <v>3.35</v>
       </c>
       <c r="P105">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="Q105">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="R105">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="S105">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T105">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="U105">
-        <v>3.13</v>
+        <v>2.57</v>
       </c>
       <c r="V105">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W105">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X105">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y105">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="Z105">
-        <v>2.92</v>
+        <v>3.63</v>
       </c>
       <c r="AA105">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="AB105">
+        <v>1.92</v>
+      </c>
+      <c r="AC105">
+        <v>3.28</v>
+      </c>
+      <c r="AD105">
+        <v>1.29</v>
+      </c>
+      <c r="AE105">
+        <v>1.12</v>
+      </c>
+      <c r="AF105">
         <v>1.7</v>
       </c>
-      <c r="AC105">
-        <v>3.58</v>
-      </c>
-      <c r="AD105">
-        <v>1.22</v>
-      </c>
-      <c r="AE105">
-        <v>1.03</v>
-      </c>
-      <c r="AF105">
-        <v>1.83</v>
-      </c>
       <c r="AG105">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AK105">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17528,7 +17528,7 @@
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>2026-10-16 20:30:00</t>
+          <t>2026-10-16 20:00:00</t>
         </is>
       </c>
     </row>
@@ -17540,12 +17540,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="O106">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="P106">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="Q106">
-        <v>2.34</v>
+        <v>1.94</v>
       </c>
       <c r="R106">
-        <v>2.33</v>
+        <v>2.49</v>
       </c>
       <c r="S106">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="T106">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="U106">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="V106">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="W106">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X106">
         <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="Z106">
-        <v>4.55</v>
+        <v>6.25</v>
       </c>
       <c r="AA106">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="AB106">
-        <v>2.31</v>
+        <v>2.83</v>
       </c>
       <c r="AC106">
-        <v>2.28</v>
+        <v>1.97</v>
       </c>
       <c r="AD106">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AE106">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AF106">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AG106">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK106">
-        <v>1.78</v>
+        <v>2.4</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17691,7 +17691,7 @@
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>2026-10-16 21:00:00</t>
+          <t>2026-10-16 20:00:00</t>
         </is>
       </c>
     </row>
@@ -17703,12 +17703,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="O107">
-        <v>2.9</v>
+        <v>3.07</v>
       </c>
       <c r="P107">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="Q107">
         <v>3.1</v>
       </c>
       <c r="R107">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="S107">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="T107">
-        <v>2.38</v>
+        <v>2.67</v>
       </c>
       <c r="U107">
-        <v>3.82</v>
+        <v>3.13</v>
       </c>
       <c r="V107">
+        <v>1.33</v>
+      </c>
+      <c r="W107">
+        <v>1.03</v>
+      </c>
+      <c r="X107">
+        <v>1.01</v>
+      </c>
+      <c r="Y107">
+        <v>1.31</v>
+      </c>
+      <c r="Z107">
+        <v>2.92</v>
+      </c>
+      <c r="AA107">
+        <v>2.06</v>
+      </c>
+      <c r="AB107">
+        <v>1.7</v>
+      </c>
+      <c r="AC107">
+        <v>3.58</v>
+      </c>
+      <c r="AD107">
         <v>1.22</v>
       </c>
-      <c r="W107">
-        <v>1.04</v>
-      </c>
-      <c r="X107">
-        <v>1.06</v>
-      </c>
-      <c r="Y107">
-        <v>1.54</v>
-      </c>
-      <c r="Z107">
-        <v>2.41</v>
-      </c>
-      <c r="AA107">
-        <v>2.62</v>
-      </c>
-      <c r="AB107">
-        <v>1.38</v>
-      </c>
-      <c r="AC107">
-        <v>5.45</v>
-      </c>
-      <c r="AD107">
-        <v>1.08</v>
-      </c>
       <c r="AE107">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF107">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AG107">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK107">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17854,7 +17854,7 @@
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>2026-10-16 21:00:00</t>
+          <t>2026-10-16 20:30:00</t>
         </is>
       </c>
     </row>
@@ -17871,7 +17871,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
+        <v>1.82</v>
+      </c>
+      <c r="O108">
+        <v>3.6</v>
+      </c>
+      <c r="P108">
+        <v>3.4</v>
+      </c>
+      <c r="Q108">
+        <v>2.34</v>
+      </c>
+      <c r="R108">
+        <v>2.33</v>
+      </c>
+      <c r="S108">
+        <v>1.22</v>
+      </c>
+      <c r="T108">
+        <v>3.75</v>
+      </c>
+      <c r="U108">
+        <v>2.15</v>
+      </c>
+      <c r="V108">
+        <v>1.6</v>
+      </c>
+      <c r="W108">
+        <v>1.13</v>
+      </c>
+      <c r="X108">
+        <v>1.01</v>
+      </c>
+      <c r="Y108">
+        <v>1.13</v>
+      </c>
+      <c r="Z108">
+        <v>4.55</v>
+      </c>
+      <c r="AA108">
+        <v>1.52</v>
+      </c>
+      <c r="AB108">
+        <v>2.31</v>
+      </c>
+      <c r="AC108">
+        <v>2.28</v>
+      </c>
+      <c r="AD108">
         <v>1.5</v>
       </c>
-      <c r="O108">
-        <v>4.15</v>
-      </c>
-      <c r="P108">
-        <v>4.96</v>
-      </c>
-      <c r="Q108">
-        <v>0</v>
-      </c>
-      <c r="R108">
-        <v>0</v>
-      </c>
-      <c r="S108">
-        <v>0</v>
-      </c>
-      <c r="T108">
-        <v>0</v>
-      </c>
-      <c r="U108">
-        <v>0</v>
-      </c>
-      <c r="V108">
-        <v>0</v>
-      </c>
-      <c r="W108">
-        <v>0</v>
-      </c>
-      <c r="X108">
-        <v>0</v>
-      </c>
-      <c r="Y108">
-        <v>0</v>
-      </c>
-      <c r="Z108">
-        <v>0</v>
-      </c>
-      <c r="AA108">
-        <v>1.53</v>
-      </c>
-      <c r="AB108">
-        <v>2.37</v>
-      </c>
-      <c r="AC108">
-        <v>0</v>
-      </c>
-      <c r="AD108">
-        <v>0</v>
-      </c>
       <c r="AE108">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF108">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG108">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK108">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18029,7 +18029,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,65 +18076,65 @@
         </is>
       </c>
       <c r="N109">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="O109">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="P109">
-        <v>3.5</v>
+        <v>2.67</v>
       </c>
       <c r="Q109">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="R109">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="S109">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="T109">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="U109">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
       <c r="V109">
         <v>1.22</v>
       </c>
       <c r="W109">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X109">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Y109">
+        <v>1.55</v>
+      </c>
+      <c r="Z109">
+        <v>2.42</v>
+      </c>
+      <c r="AA109">
+        <v>2.62</v>
+      </c>
+      <c r="AB109">
+        <v>1.38</v>
+      </c>
+      <c r="AC109">
+        <v>5.45</v>
+      </c>
+      <c r="AD109">
+        <v>1.08</v>
+      </c>
+      <c r="AE109">
+        <v>1.04</v>
+      </c>
+      <c r="AF109">
+        <v>2.15</v>
+      </c>
+      <c r="AG109">
         <v>1.61</v>
       </c>
-      <c r="Z109">
-        <v>2.13</v>
-      </c>
-      <c r="AA109">
-        <v>2.83</v>
-      </c>
-      <c r="AB109">
-        <v>1.33</v>
-      </c>
-      <c r="AC109">
-        <v>5.9</v>
-      </c>
-      <c r="AD109">
-        <v>1.07</v>
-      </c>
-      <c r="AE109">
-        <v>1.03</v>
-      </c>
-      <c r="AF109">
-        <v>2.3</v>
-      </c>
-      <c r="AG109">
-        <v>1.52</v>
-      </c>
       <c r="AH109" t="inlineStr">
         <is>
           <t>[]</t>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AK109">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18180,7 +18180,7 @@
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>2026-10-16 22:00:00</t>
+          <t>2026-10-16 21:00:00</t>
         </is>
       </c>
     </row>
@@ -18192,156 +18192,482 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Boston Legacy W</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Racing Louisville</t>
+        </is>
+      </c>
+      <c r="G110">
+        <v>0</v>
+      </c>
+      <c r="H110">
+        <v>0</v>
+      </c>
+      <c r="I110">
+        <v>0</v>
+      </c>
+      <c r="J110">
+        <v>0</v>
+      </c>
+      <c r="K110">
+        <v>0</v>
+      </c>
+      <c r="L110">
+        <v>0</v>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N110">
+        <v>1.5</v>
+      </c>
+      <c r="O110">
+        <v>4.15</v>
+      </c>
+      <c r="P110">
+        <v>4.96</v>
+      </c>
+      <c r="Q110">
+        <v>0</v>
+      </c>
+      <c r="R110">
+        <v>0</v>
+      </c>
+      <c r="S110">
+        <v>0</v>
+      </c>
+      <c r="T110">
+        <v>0</v>
+      </c>
+      <c r="U110">
+        <v>0</v>
+      </c>
+      <c r="V110">
+        <v>0</v>
+      </c>
+      <c r="W110">
+        <v>0</v>
+      </c>
+      <c r="X110">
+        <v>0</v>
+      </c>
+      <c r="Y110">
+        <v>0</v>
+      </c>
+      <c r="Z110">
+        <v>0</v>
+      </c>
+      <c r="AA110">
+        <v>1.53</v>
+      </c>
+      <c r="AB110">
+        <v>2.37</v>
+      </c>
+      <c r="AC110">
+        <v>0</v>
+      </c>
+      <c r="AD110">
+        <v>0</v>
+      </c>
+      <c r="AE110">
+        <v>0</v>
+      </c>
+      <c r="AF110">
+        <v>0</v>
+      </c>
+      <c r="AG110">
+        <v>0</v>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ110">
+        <v>0</v>
+      </c>
+      <c r="AK110">
+        <v>0</v>
+      </c>
+      <c r="AL110">
+        <v>0</v>
+      </c>
+      <c r="AM110">
+        <v>-1</v>
+      </c>
+      <c r="AN110">
+        <v>-1</v>
+      </c>
+      <c r="AO110">
+        <v>-1</v>
+      </c>
+      <c r="AP110">
+        <v>-1</v>
+      </c>
+      <c r="AQ110">
+        <v>0</v>
+      </c>
+      <c r="AR110">
+        <v>0</v>
+      </c>
+      <c r="AS110">
+        <v>0</v>
+      </c>
+      <c r="AT110">
+        <v>0</v>
+      </c>
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Gimnasia y Tiro</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="G111">
+        <v>0</v>
+      </c>
+      <c r="H111">
+        <v>0</v>
+      </c>
+      <c r="I111">
+        <v>0</v>
+      </c>
+      <c r="J111">
+        <v>0</v>
+      </c>
+      <c r="K111">
+        <v>0</v>
+      </c>
+      <c r="L111">
+        <v>0</v>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N111">
+        <v>2.1</v>
+      </c>
+      <c r="O111">
+        <v>2.85</v>
+      </c>
+      <c r="P111">
+        <v>3.5</v>
+      </c>
+      <c r="Q111">
+        <v>3</v>
+      </c>
+      <c r="R111">
+        <v>1.83</v>
+      </c>
+      <c r="S111">
+        <v>1.57</v>
+      </c>
+      <c r="T111">
+        <v>2.25</v>
+      </c>
+      <c r="U111">
+        <v>3.9</v>
+      </c>
+      <c r="V111">
+        <v>1.22</v>
+      </c>
+      <c r="W111">
+        <v>1.03</v>
+      </c>
+      <c r="X111">
+        <v>1.11</v>
+      </c>
+      <c r="Y111">
+        <v>1.62</v>
+      </c>
+      <c r="Z111">
+        <v>2.12</v>
+      </c>
+      <c r="AA111">
+        <v>2.9</v>
+      </c>
+      <c r="AB111">
+        <v>1.36</v>
+      </c>
+      <c r="AC111">
+        <v>7</v>
+      </c>
+      <c r="AD111">
+        <v>1.07</v>
+      </c>
+      <c r="AE111">
+        <v>1.03</v>
+      </c>
+      <c r="AF111">
+        <v>2.3</v>
+      </c>
+      <c r="AG111">
+        <v>1.5</v>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ111">
+        <v>1.36</v>
+      </c>
+      <c r="AK111">
+        <v>1.6</v>
+      </c>
+      <c r="AL111">
+        <v>0</v>
+      </c>
+      <c r="AM111">
+        <v>-1</v>
+      </c>
+      <c r="AN111">
+        <v>-1</v>
+      </c>
+      <c r="AO111">
+        <v>-1</v>
+      </c>
+      <c r="AP111">
+        <v>-1</v>
+      </c>
+      <c r="AQ111">
+        <v>0</v>
+      </c>
+      <c r="AR111">
+        <v>0</v>
+      </c>
+      <c r="AS111">
+        <v>0</v>
+      </c>
+      <c r="AT111">
+        <v>0</v>
+      </c>
+      <c r="AU111" t="inlineStr">
+        <is>
+          <t>2026-10-16 22:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="C112" t="inlineStr">
         <is>
           <t>Canada Canadian Premier League</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
+      <c r="D112" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
+      <c r="E112" t="inlineStr">
         <is>
           <t>Vancouver FC</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
+      <c r="F112" t="inlineStr">
         <is>
           <t>HFX Wanderers FC</t>
         </is>
       </c>
-      <c r="G110">
-        <v>0</v>
-      </c>
-      <c r="H110">
-        <v>0</v>
-      </c>
-      <c r="I110">
-        <v>0</v>
-      </c>
-      <c r="J110">
-        <v>0</v>
-      </c>
-      <c r="K110">
-        <v>0</v>
-      </c>
-      <c r="L110">
-        <v>0</v>
-      </c>
-      <c r="M110" t="inlineStr">
+      <c r="G112">
+        <v>0</v>
+      </c>
+      <c r="H112">
+        <v>0</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+      <c r="J112">
+        <v>0</v>
+      </c>
+      <c r="K112">
+        <v>0</v>
+      </c>
+      <c r="L112">
+        <v>0</v>
+      </c>
+      <c r="M112" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N110">
-        <v>2.02</v>
-      </c>
-      <c r="O110">
-        <v>3.44</v>
-      </c>
-      <c r="P110">
-        <v>3.1</v>
-      </c>
-      <c r="Q110">
-        <v>0</v>
-      </c>
-      <c r="R110">
-        <v>0</v>
-      </c>
-      <c r="S110">
-        <v>0</v>
-      </c>
-      <c r="T110">
-        <v>0</v>
-      </c>
-      <c r="U110">
-        <v>0</v>
-      </c>
-      <c r="V110">
-        <v>0</v>
-      </c>
-      <c r="W110">
-        <v>0</v>
-      </c>
-      <c r="X110">
-        <v>0</v>
-      </c>
-      <c r="Y110">
-        <v>0</v>
-      </c>
-      <c r="Z110">
-        <v>0</v>
-      </c>
-      <c r="AA110">
-        <v>1.6</v>
-      </c>
-      <c r="AB110">
-        <v>2.3</v>
-      </c>
-      <c r="AC110">
-        <v>0</v>
-      </c>
-      <c r="AD110">
-        <v>0</v>
-      </c>
-      <c r="AE110">
-        <v>0</v>
-      </c>
-      <c r="AF110">
-        <v>0</v>
-      </c>
-      <c r="AG110">
-        <v>0</v>
-      </c>
-      <c r="AH110" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI110" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ110">
-        <v>0</v>
-      </c>
-      <c r="AK110">
-        <v>0</v>
-      </c>
-      <c r="AL110">
-        <v>0</v>
-      </c>
-      <c r="AM110">
-        <v>-1</v>
-      </c>
-      <c r="AN110">
-        <v>-1</v>
-      </c>
-      <c r="AO110">
-        <v>-1</v>
-      </c>
-      <c r="AP110">
-        <v>-1</v>
-      </c>
-      <c r="AQ110">
-        <v>0</v>
-      </c>
-      <c r="AR110">
-        <v>0</v>
-      </c>
-      <c r="AS110">
-        <v>0</v>
-      </c>
-      <c r="AT110">
-        <v>0</v>
-      </c>
-      <c r="AU110" t="inlineStr">
+      <c r="N112">
+        <v>2.15</v>
+      </c>
+      <c r="O112">
+        <v>3.6</v>
+      </c>
+      <c r="P112">
+        <v>2.75</v>
+      </c>
+      <c r="Q112">
+        <v>0</v>
+      </c>
+      <c r="R112">
+        <v>0</v>
+      </c>
+      <c r="S112">
+        <v>0</v>
+      </c>
+      <c r="T112">
+        <v>0</v>
+      </c>
+      <c r="U112">
+        <v>0</v>
+      </c>
+      <c r="V112">
+        <v>0</v>
+      </c>
+      <c r="W112">
+        <v>0</v>
+      </c>
+      <c r="X112">
+        <v>0</v>
+      </c>
+      <c r="Y112">
+        <v>0</v>
+      </c>
+      <c r="Z112">
+        <v>0</v>
+      </c>
+      <c r="AA112">
+        <v>1.53</v>
+      </c>
+      <c r="AB112">
+        <v>2.37</v>
+      </c>
+      <c r="AC112">
+        <v>0</v>
+      </c>
+      <c r="AD112">
+        <v>0</v>
+      </c>
+      <c r="AE112">
+        <v>0</v>
+      </c>
+      <c r="AF112">
+        <v>0</v>
+      </c>
+      <c r="AG112">
+        <v>0</v>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ112">
+        <v>0</v>
+      </c>
+      <c r="AK112">
+        <v>0</v>
+      </c>
+      <c r="AL112">
+        <v>0</v>
+      </c>
+      <c r="AM112">
+        <v>-1</v>
+      </c>
+      <c r="AN112">
+        <v>-1</v>
+      </c>
+      <c r="AO112">
+        <v>-1</v>
+      </c>
+      <c r="AP112">
+        <v>-1</v>
+      </c>
+      <c r="AQ112">
+        <v>0</v>
+      </c>
+      <c r="AR112">
+        <v>0</v>
+      </c>
+      <c r="AS112">
+        <v>0</v>
+      </c>
+      <c r="AT112">
+        <v>0</v>
+      </c>
+      <c r="AU112" t="inlineStr">
         <is>
           <t>2026-10-16 23:00:00</t>
         </is>

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -1622,55 +1622,55 @@
         <v>2.65</v>
       </c>
       <c r="Q8">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="R8">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="S8">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="T8">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="U8">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="V8">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="W8">
+        <v>1.02</v>
+      </c>
+      <c r="X8">
+        <v>1.14</v>
+      </c>
+      <c r="Y8">
+        <v>1.73</v>
+      </c>
+      <c r="Z8">
+        <v>1.96</v>
+      </c>
+      <c r="AA8">
+        <v>3.3</v>
+      </c>
+      <c r="AB8">
+        <v>1.29</v>
+      </c>
+      <c r="AC8">
+        <v>7.5</v>
+      </c>
+      <c r="AD8">
+        <v>1.03</v>
+      </c>
+      <c r="AE8">
         <v>1.01</v>
       </c>
-      <c r="X8">
-        <v>1.11</v>
-      </c>
-      <c r="Y8">
-        <v>1.63</v>
-      </c>
-      <c r="Z8">
-        <v>2.1</v>
-      </c>
-      <c r="AA8">
-        <v>3</v>
-      </c>
-      <c r="AB8">
-        <v>1.33</v>
-      </c>
-      <c r="AC8">
-        <v>7</v>
-      </c>
-      <c r="AD8">
-        <v>1.07</v>
-      </c>
-      <c r="AE8">
-        <v>1.02</v>
-      </c>
       <c r="AF8">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AG8">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>1.36</v>
       </c>
       <c r="AK8">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.84</v>
+        <v>3.3</v>
       </c>
       <c r="O19">
-        <v>2.74</v>
+        <v>2.45</v>
       </c>
       <c r="P19">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3445,10 +3445,10 @@
         <v>0</v>
       </c>
       <c r="AA19">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AB19">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC19">
         <v>0</v>
@@ -3590,7 +3590,7 @@
         <v>3.9</v>
       </c>
       <c r="U20">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="V20">
         <v>1.67</v>
@@ -3895,19 +3895,19 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="O22">
         <v>8</v>
       </c>
       <c r="P22">
-        <v>13.3</v>
+        <v>14</v>
       </c>
       <c r="Q22">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="R22">
-        <v>3.2</v>
+        <v>3.06</v>
       </c>
       <c r="S22">
         <v>1.17</v>
@@ -3919,7 +3919,7 @@
         <v>1.84</v>
       </c>
       <c r="V22">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="W22">
         <v>1.22</v>
@@ -3940,13 +3940,13 @@
         <v>3.4</v>
       </c>
       <c r="AC22">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AD22">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="AE22">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AF22">
         <v>1.95</v>
@@ -4873,19 +4873,19 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="O28">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P28">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="Q28">
         <v>3.5</v>
       </c>
       <c r="R28">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="S28">
         <v>1.36</v>
@@ -4894,13 +4894,13 @@
         <v>2.73</v>
       </c>
       <c r="U28">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="V28">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W28">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X28">
         <v>1.02</v>
@@ -4927,10 +4927,10 @@
         <v>1.05</v>
       </c>
       <c r="AF28">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG28">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AK28">
         <v>1.36</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>6.75</v>
+        <v>7.25</v>
       </c>
       <c r="O29">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="P29">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Q29">
         <v>7</v>
@@ -5054,7 +5054,7 @@
         <v>1.37</v>
       </c>
       <c r="T29">
-        <v>2.79</v>
+        <v>3</v>
       </c>
       <c r="U29">
         <v>2.53</v>
@@ -5075,7 +5075,7 @@
         <v>3.7</v>
       </c>
       <c r="AA29">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AB29">
         <v>1.91</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AK29">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="O35">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P35">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="Q35">
         <v>2.19</v>
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="O36">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="P36">
         <v>2.6</v>
       </c>
       <c r="Q36">
-        <v>3.64</v>
+        <v>3.75</v>
       </c>
       <c r="R36">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="S36">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="T36">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="U36">
-        <v>3.42</v>
+        <v>3.68</v>
       </c>
       <c r="V36">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="W36">
+        <v>1.01</v>
+      </c>
+      <c r="X36">
+        <v>1.13</v>
+      </c>
+      <c r="Y36">
+        <v>1.66</v>
+      </c>
+      <c r="Z36">
+        <v>2.05</v>
+      </c>
+      <c r="AA36">
+        <v>3.1</v>
+      </c>
+      <c r="AB36">
+        <v>1.33</v>
+      </c>
+      <c r="AC36">
+        <v>7.5</v>
+      </c>
+      <c r="AD36">
+        <v>1.06</v>
+      </c>
+      <c r="AE36">
         <v>1.02</v>
       </c>
-      <c r="X36">
-        <v>1.08</v>
-      </c>
-      <c r="Y36">
-        <v>1.55</v>
-      </c>
-      <c r="Z36">
-        <v>2.24</v>
-      </c>
-      <c r="AA36">
-        <v>2.62</v>
-      </c>
-      <c r="AB36">
-        <v>1.38</v>
-      </c>
-      <c r="AC36">
-        <v>5.2</v>
-      </c>
-      <c r="AD36">
-        <v>1.1</v>
-      </c>
-      <c r="AE36">
-        <v>1.01</v>
-      </c>
       <c r="AF36">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="AG36">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AK36">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6992,34 +6992,34 @@
         </is>
       </c>
       <c r="N41">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O41">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P41">
         <v>3.05</v>
       </c>
       <c r="Q41">
-        <v>2.63</v>
+        <v>2.47</v>
       </c>
       <c r="R41">
         <v>2.3</v>
       </c>
       <c r="S41">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T41">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U41">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="V41">
         <v>1.56</v>
       </c>
       <c r="W41">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X41">
         <v>1.01</v>
@@ -7028,16 +7028,16 @@
         <v>1.15</v>
       </c>
       <c r="Z41">
-        <v>4.72</v>
+        <v>4.77</v>
       </c>
       <c r="AA41">
         <v>1.57</v>
       </c>
       <c r="AB41">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AC41">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="AD41">
         <v>1.5</v>
@@ -7330,19 +7330,19 @@
         <v>2.78</v>
       </c>
       <c r="R43">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="S43">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T43">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="U43">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="V43">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W43">
         <v>1.02</v>
@@ -7354,19 +7354,19 @@
         <v>1.37</v>
       </c>
       <c r="Z43">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="AA43">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="AB43">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC43">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="AD43">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE43">
         <v>1.02</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.35</v>
+        <v>3.05</v>
       </c>
       <c r="O48">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P48">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="Q48">
-        <v>2.88</v>
+        <v>3.56</v>
       </c>
       <c r="R48">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S48">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T48">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="U48">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="V48">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="W48">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X48">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z48">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA48">
         <v>1.6</v>
       </c>
       <c r="AB48">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="AC48">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AD48">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE48">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF48">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG48">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="AK48">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>3.05</v>
+        <v>2.35</v>
       </c>
       <c r="O49">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P49">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="Q49">
-        <v>3.56</v>
+        <v>2.88</v>
       </c>
       <c r="R49">
+        <v>2.25</v>
+      </c>
+      <c r="S49">
+        <v>1.29</v>
+      </c>
+      <c r="T49">
+        <v>3.4</v>
+      </c>
+      <c r="U49">
         <v>2.3</v>
       </c>
-      <c r="S49">
-        <v>1.32</v>
-      </c>
-      <c r="T49">
-        <v>3.38</v>
-      </c>
-      <c r="U49">
-        <v>2.24</v>
-      </c>
       <c r="V49">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="W49">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X49">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z49">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AA49">
         <v>1.6</v>
       </c>
       <c r="AB49">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="AC49">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AD49">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AE49">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF49">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG49">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="AK49">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O51">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P51">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.5</v>
+        <v>3.05</v>
       </c>
       <c r="O52">
-        <v>4.55</v>
+        <v>3.45</v>
       </c>
       <c r="P52">
-        <v>4.6</v>
+        <v>2.15</v>
       </c>
       <c r="Q52">
-        <v>1.93</v>
+        <v>3.08</v>
       </c>
       <c r="R52">
-        <v>2.57</v>
+        <v>2.22</v>
       </c>
       <c r="S52">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="T52">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U52">
-        <v>2.1</v>
+        <v>2.41</v>
       </c>
       <c r="V52">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="W52">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="X52">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y52">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z52">
-        <v>5.45</v>
+        <v>4.35</v>
       </c>
       <c r="AA52">
-        <v>1.37</v>
+        <v>1.61</v>
       </c>
       <c r="AB52">
-        <v>2.88</v>
+        <v>2.31</v>
       </c>
       <c r="AC52">
-        <v>2</v>
+        <v>2.56</v>
       </c>
       <c r="AD52">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="AE52">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AF52">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AG52">
-        <v>2.63</v>
+        <v>2.39</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AK52">
-        <v>2.42</v>
+        <v>1.35</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,80 +8948,80 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.89</v>
+        <v>1.53</v>
       </c>
       <c r="O53">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="P53">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="Q53">
-        <v>3.62</v>
+        <v>2.06</v>
       </c>
       <c r="R53">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="S53">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="T53">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="U53">
+        <v>2.13</v>
+      </c>
+      <c r="V53">
+        <v>1.7</v>
+      </c>
+      <c r="W53">
+        <v>1.18</v>
+      </c>
+      <c r="X53">
+        <v>1.01</v>
+      </c>
+      <c r="Y53">
+        <v>1.08</v>
+      </c>
+      <c r="Z53">
+        <v>5.45</v>
+      </c>
+      <c r="AA53">
+        <v>1.4</v>
+      </c>
+      <c r="AB53">
+        <v>2.88</v>
+      </c>
+      <c r="AC53">
+        <v>2</v>
+      </c>
+      <c r="AD53">
+        <v>1.71</v>
+      </c>
+      <c r="AE53">
+        <v>1.29</v>
+      </c>
+      <c r="AF53">
+        <v>1.44</v>
+      </c>
+      <c r="AG53">
+        <v>2.63</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ53">
+        <v>1.14</v>
+      </c>
+      <c r="AK53">
         <v>2.4</v>
-      </c>
-      <c r="V53">
-        <v>1.55</v>
-      </c>
-      <c r="W53">
-        <v>1.09</v>
-      </c>
-      <c r="X53">
-        <v>1.03</v>
-      </c>
-      <c r="Y53">
-        <v>1.14</v>
-      </c>
-      <c r="Z53">
-        <v>4.35</v>
-      </c>
-      <c r="AA53">
-        <v>1.61</v>
-      </c>
-      <c r="AB53">
-        <v>2.3</v>
-      </c>
-      <c r="AC53">
-        <v>2.55</v>
-      </c>
-      <c r="AD53">
-        <v>1.44</v>
-      </c>
-      <c r="AE53">
-        <v>1.19</v>
-      </c>
-      <c r="AF53">
-        <v>1.53</v>
-      </c>
-      <c r="AG53">
-        <v>2.39</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ53">
-        <v>1.29</v>
-      </c>
-      <c r="AK53">
-        <v>1.35</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O56">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="P56">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="Q56">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="R56">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S56">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="T56">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="U56">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="V56">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W56">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X56">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y56">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="Z56">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AA56">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AB56">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC56">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AD56">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE56">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF56">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AG56">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK56">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,28 +9600,28 @@
         </is>
       </c>
       <c r="N57">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="O57">
-        <v>3.93</v>
+        <v>3.7</v>
       </c>
       <c r="P57">
-        <v>1.58</v>
+        <v>1.79</v>
       </c>
       <c r="Q57">
-        <v>4.14</v>
+        <v>4.23</v>
       </c>
       <c r="R57">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="S57">
         <v>1.22</v>
       </c>
       <c r="T57">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="U57">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="V57">
         <v>1.68</v>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.2</v>
+        <v>1.91</v>
       </c>
       <c r="AK57">
         <v>1.25</v>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O59">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P59">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -9953,7 +9953,7 @@
         <v>1.57</v>
       </c>
       <c r="W59">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X59">
         <v>1.01</v>
@@ -9965,13 +9965,13 @@
         <v>4.5</v>
       </c>
       <c r="AA59">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AB59">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="AC59">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="AD59">
         <v>1.53</v>
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AK59">
         <v>1.58</v>
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="O60">
         <v>3.55</v>
@@ -10113,7 +10113,7 @@
         <v>2.05</v>
       </c>
       <c r="V60">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="W60">
         <v>1.15</v>
@@ -10146,7 +10146,7 @@
         <v>1.36</v>
       </c>
       <c r="AG60">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10252,34 +10252,34 @@
         </is>
       </c>
       <c r="N61">
-        <v>5.71</v>
+        <v>5.75</v>
       </c>
       <c r="O61">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="P61">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="Q61">
-        <v>4.49</v>
+        <v>4.58</v>
       </c>
       <c r="R61">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="S61">
         <v>1.18</v>
       </c>
       <c r="T61">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="U61">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="V61">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="W61">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X61">
         <v>1.02</v>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AK61">
         <v>1.11</v>
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="O63">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="P63">
-        <v>9.08</v>
+        <v>7.5</v>
       </c>
       <c r="Q63">
         <v>1.64</v>
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="O65">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P65">
-        <v>2.61</v>
+        <v>2.75</v>
       </c>
       <c r="Q65">
         <v>2.48</v>
@@ -10943,7 +10943,7 @@
         <v>4.85</v>
       </c>
       <c r="AA65">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AB65">
         <v>2.55</v>
@@ -10977,7 +10977,7 @@
         <v>1.2</v>
       </c>
       <c r="AK65">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="O67">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P67">
-        <v>3.35</v>
+        <v>2.7</v>
       </c>
       <c r="Q67">
-        <v>2.78</v>
+        <v>3.4</v>
       </c>
       <c r="R67">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="S67">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="T67">
-        <v>2.88</v>
+        <v>2.39</v>
       </c>
       <c r="U67">
-        <v>2.88</v>
+        <v>3.33</v>
       </c>
       <c r="V67">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W67">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X67">
         <v>1.04</v>
       </c>
       <c r="Y67">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="Z67">
-        <v>3.08</v>
+        <v>2.85</v>
       </c>
       <c r="AA67">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="AB67">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AC67">
-        <v>3.5</v>
+        <v>4.15</v>
       </c>
       <c r="AD67">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AE67">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="AF67">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AG67">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK67">
-        <v>1.7</v>
+        <v>1.41</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="O68">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="P68">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="Q68">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="R68">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="S68">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="T68">
-        <v>2.39</v>
+        <v>2.94</v>
       </c>
       <c r="U68">
-        <v>3.33</v>
+        <v>2.68</v>
       </c>
       <c r="V68">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W68">
         <v>1.04</v>
       </c>
       <c r="X68">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y68">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="Z68">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="AA68">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="AB68">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="AC68">
-        <v>4.15</v>
+        <v>3.4</v>
       </c>
       <c r="AD68">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AE68">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF68">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AG68">
-        <v>1.77</v>
+        <v>2.01</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK68">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
+        <v>2.15</v>
+      </c>
+      <c r="O69">
+        <v>3.05</v>
+      </c>
+      <c r="P69">
+        <v>3.35</v>
+      </c>
+      <c r="Q69">
+        <v>2.78</v>
+      </c>
+      <c r="R69">
+        <v>2.06</v>
+      </c>
+      <c r="S69">
+        <v>1.36</v>
+      </c>
+      <c r="T69">
+        <v>2.88</v>
+      </c>
+      <c r="U69">
+        <v>2.88</v>
+      </c>
+      <c r="V69">
+        <v>1.4</v>
+      </c>
+      <c r="W69">
+        <v>1.05</v>
+      </c>
+      <c r="X69">
+        <v>1.04</v>
+      </c>
+      <c r="Y69">
+        <v>1.28</v>
+      </c>
+      <c r="Z69">
+        <v>3.08</v>
+      </c>
+      <c r="AA69">
+        <v>2.06</v>
+      </c>
+      <c r="AB69">
         <v>1.73</v>
       </c>
-      <c r="O69">
-        <v>3.55</v>
-      </c>
-      <c r="P69">
-        <v>4.4</v>
-      </c>
-      <c r="Q69">
-        <v>2.25</v>
-      </c>
-      <c r="R69">
-        <v>2.24</v>
-      </c>
-      <c r="S69">
-        <v>1.29</v>
-      </c>
-      <c r="T69">
-        <v>3.46</v>
-      </c>
-      <c r="U69">
-        <v>2.4</v>
-      </c>
-      <c r="V69">
-        <v>1.52</v>
-      </c>
-      <c r="W69">
-        <v>1.12</v>
-      </c>
-      <c r="X69">
-        <v>1.02</v>
-      </c>
-      <c r="Y69">
-        <v>1.21</v>
-      </c>
-      <c r="Z69">
-        <v>4.4</v>
-      </c>
-      <c r="AA69">
-        <v>1.65</v>
-      </c>
-      <c r="AB69">
-        <v>2.19</v>
-      </c>
       <c r="AC69">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AD69">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AE69">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF69">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AG69">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AK69">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,80 +11719,80 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.55</v>
+        <v>1.73</v>
       </c>
       <c r="O70">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="P70">
-        <v>2.6</v>
+        <v>4.4</v>
       </c>
       <c r="Q70">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="R70">
+        <v>2.24</v>
+      </c>
+      <c r="S70">
+        <v>1.29</v>
+      </c>
+      <c r="T70">
+        <v>3.46</v>
+      </c>
+      <c r="U70">
+        <v>2.4</v>
+      </c>
+      <c r="V70">
+        <v>1.52</v>
+      </c>
+      <c r="W70">
+        <v>1.12</v>
+      </c>
+      <c r="X70">
+        <v>1.02</v>
+      </c>
+      <c r="Y70">
+        <v>1.21</v>
+      </c>
+      <c r="Z70">
+        <v>4.4</v>
+      </c>
+      <c r="AA70">
+        <v>1.65</v>
+      </c>
+      <c r="AB70">
+        <v>2.19</v>
+      </c>
+      <c r="AC70">
+        <v>2.7</v>
+      </c>
+      <c r="AD70">
+        <v>1.43</v>
+      </c>
+      <c r="AE70">
+        <v>1.14</v>
+      </c>
+      <c r="AF70">
+        <v>1.62</v>
+      </c>
+      <c r="AG70">
+        <v>2.15</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ70">
+        <v>1.17</v>
+      </c>
+      <c r="AK70">
         <v>2.1</v>
-      </c>
-      <c r="S70">
-        <v>1.37</v>
-      </c>
-      <c r="T70">
-        <v>2.94</v>
-      </c>
-      <c r="U70">
-        <v>2.68</v>
-      </c>
-      <c r="V70">
-        <v>1.36</v>
-      </c>
-      <c r="W70">
-        <v>1.04</v>
-      </c>
-      <c r="X70">
-        <v>1</v>
-      </c>
-      <c r="Y70">
-        <v>1.3</v>
-      </c>
-      <c r="Z70">
-        <v>3.4</v>
-      </c>
-      <c r="AA70">
-        <v>2.03</v>
-      </c>
-      <c r="AB70">
-        <v>1.81</v>
-      </c>
-      <c r="AC70">
-        <v>3.4</v>
-      </c>
-      <c r="AD70">
-        <v>1.3</v>
-      </c>
-      <c r="AE70">
-        <v>1.06</v>
-      </c>
-      <c r="AF70">
-        <v>1.75</v>
-      </c>
-      <c r="AG70">
-        <v>2.01</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ70">
-        <v>1.4</v>
-      </c>
-      <c r="AK70">
-        <v>1.5</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11885,10 +11885,10 @@
         <v>1.44</v>
       </c>
       <c r="O71">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="P71">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -11921,10 +11921,10 @@
         <v>0</v>
       </c>
       <c r="AA71">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB71">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC71">
         <v>0</v>
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="O72">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="P72">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q72">
         <v>2.16</v>
@@ -12066,10 +12066,10 @@
         <v>3.55</v>
       </c>
       <c r="U72">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="V72">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="W72">
         <v>1.14</v>
@@ -12102,7 +12102,7 @@
         <v>1.44</v>
       </c>
       <c r="AG72">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AK72">
         <v>2.14</v>
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="O77">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P77">
-        <v>3.8</v>
+        <v>4.06</v>
       </c>
       <c r="Q77">
         <v>2.3</v>
@@ -12881,7 +12881,7 @@
         <v>3.2</v>
       </c>
       <c r="U77">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="V77">
         <v>1.45</v>
@@ -12899,16 +12899,16 @@
         <v>3.8</v>
       </c>
       <c r="AA77">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="AB77">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="AC77">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AD77">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE77">
         <v>1.1</v>
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O78">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P78">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
       <c r="Q78">
         <v>2.5</v>
@@ -13038,13 +13038,13 @@
         <v>2.25</v>
       </c>
       <c r="S78">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T78">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U78">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="V78">
         <v>1.49</v>
@@ -13062,10 +13062,10 @@
         <v>3.84</v>
       </c>
       <c r="AA78">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AB78">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC78">
         <v>2.75</v>
@@ -13186,31 +13186,31 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="O79">
         <v>3.4</v>
       </c>
       <c r="P79">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="Q79">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="R79">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S79">
         <v>1.34</v>
       </c>
       <c r="T79">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="U79">
         <v>2.59</v>
       </c>
       <c r="V79">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W79">
         <v>1.06</v>
@@ -13228,10 +13228,10 @@
         <v>1.9</v>
       </c>
       <c r="AB79">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AC79">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="AD79">
         <v>1.3</v>
@@ -13352,16 +13352,16 @@
         <v>4</v>
       </c>
       <c r="O80">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P80">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="Q80">
-        <v>4.4</v>
+        <v>4.85</v>
       </c>
       <c r="R80">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="S80">
         <v>1.3</v>
@@ -13376,13 +13376,13 @@
         <v>1.5</v>
       </c>
       <c r="W80">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X80">
         <v>1.01</v>
       </c>
       <c r="Y80">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z80">
         <v>3.58</v>
@@ -13394,7 +13394,7 @@
         <v>2.05</v>
       </c>
       <c r="AC80">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="AD80">
         <v>1.35</v>
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="O81">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P81">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13675,19 +13675,19 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="O82">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="P82">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="Q82">
         <v>2.77</v>
       </c>
       <c r="R82">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="S82">
         <v>1.29</v>
@@ -13696,13 +13696,13 @@
         <v>3.25</v>
       </c>
       <c r="U82">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="V82">
         <v>1.5</v>
       </c>
       <c r="W82">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X82">
         <v>1.03</v>
@@ -13711,16 +13711,16 @@
         <v>1.22</v>
       </c>
       <c r="Z82">
-        <v>4.4</v>
+        <v>4.43</v>
       </c>
       <c r="AA82">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AB82">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC82">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AD82">
         <v>1.43</v>
@@ -13838,7 +13838,7 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="O83">
         <v>3.4</v>
@@ -13850,7 +13850,7 @@
         <v>2.8</v>
       </c>
       <c r="R83">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="S83">
         <v>1.3</v>
@@ -13883,7 +13883,7 @@
         <v>2.14</v>
       </c>
       <c r="AC83">
-        <v>2.52</v>
+        <v>2.75</v>
       </c>
       <c r="AD83">
         <v>1.41</v>
@@ -13911,7 +13911,7 @@
         <v>1.25</v>
       </c>
       <c r="AK83">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="O84">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P84">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="Q84">
         <v>3.45</v>
@@ -14040,10 +14040,10 @@
         <v>3.5</v>
       </c>
       <c r="AA84">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB84">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AC84">
         <v>2.97</v>
@@ -14330,10 +14330,10 @@
         <v>2.25</v>
       </c>
       <c r="O86">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P86">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="Q86">
         <v>2.97</v>
@@ -14490,16 +14490,16 @@
         </is>
       </c>
       <c r="N87">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="O87">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P87">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="Q87">
-        <v>3.58</v>
+        <v>3.17</v>
       </c>
       <c r="R87">
         <v>2.21</v>
@@ -14532,7 +14532,7 @@
         <v>1.76</v>
       </c>
       <c r="AB87">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AC87">
         <v>2.88</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.45</v>
+        <v>2.9</v>
       </c>
       <c r="O89">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="P89">
-        <v>4.6</v>
+        <v>2.15</v>
       </c>
       <c r="Q89">
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="R89">
-        <v>2.7</v>
+        <v>2.32</v>
       </c>
       <c r="S89">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="T89">
-        <v>3.9</v>
+        <v>2.82</v>
       </c>
       <c r="U89">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="V89">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="W89">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X89">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y89">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="Z89">
-        <v>5.2</v>
+        <v>3.58</v>
       </c>
       <c r="AA89">
-        <v>1.44</v>
+        <v>1.82</v>
       </c>
       <c r="AB89">
-        <v>2.7</v>
+        <v>2.06</v>
       </c>
       <c r="AC89">
-        <v>2.05</v>
+        <v>2.97</v>
       </c>
       <c r="AD89">
-        <v>1.66</v>
+        <v>1.3</v>
       </c>
       <c r="AE89">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AF89">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AG89">
-        <v>2.39</v>
+        <v>2.1</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK89">
-        <v>2.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.9</v>
+        <v>1.45</v>
       </c>
       <c r="O90">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="P90">
-        <v>2.15</v>
+        <v>4.6</v>
       </c>
       <c r="Q90">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="R90">
-        <v>2.32</v>
+        <v>2.7</v>
       </c>
       <c r="S90">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="T90">
-        <v>2.82</v>
+        <v>3.9</v>
       </c>
       <c r="U90">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="V90">
+        <v>1.73</v>
+      </c>
+      <c r="W90">
+        <v>1.17</v>
+      </c>
+      <c r="X90">
+        <v>1.01</v>
+      </c>
+      <c r="Y90">
+        <v>1.1</v>
+      </c>
+      <c r="Z90">
+        <v>5.2</v>
+      </c>
+      <c r="AA90">
         <v>1.44</v>
       </c>
-      <c r="W90">
-        <v>1.11</v>
-      </c>
-      <c r="X90">
-        <v>1.02</v>
-      </c>
-      <c r="Y90">
-        <v>1.21</v>
-      </c>
-      <c r="Z90">
-        <v>3.58</v>
-      </c>
-      <c r="AA90">
-        <v>1.82</v>
-      </c>
       <c r="AB90">
-        <v>2.06</v>
+        <v>2.7</v>
       </c>
       <c r="AC90">
-        <v>2.97</v>
+        <v>2.05</v>
       </c>
       <c r="AD90">
-        <v>1.3</v>
+        <v>1.66</v>
       </c>
       <c r="AE90">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AF90">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AG90">
-        <v>2.1</v>
+        <v>2.39</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK90">
-        <v>1.36</v>
+        <v>2.4</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>3.15</v>
+        <v>2.38</v>
       </c>
       <c r="O93">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P93">
-        <v>1.92</v>
+        <v>2.45</v>
       </c>
       <c r="Q93">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="R93">
-        <v>2.16</v>
+        <v>2.46</v>
       </c>
       <c r="S93">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="T93">
-        <v>3.1</v>
+        <v>3.52</v>
       </c>
       <c r="U93">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="V93">
+        <v>1.6</v>
+      </c>
+      <c r="W93">
+        <v>1.15</v>
+      </c>
+      <c r="X93">
+        <v>1.01</v>
+      </c>
+      <c r="Y93">
+        <v>1.14</v>
+      </c>
+      <c r="Z93">
+        <v>5.5</v>
+      </c>
+      <c r="AA93">
+        <v>1.53</v>
+      </c>
+      <c r="AB93">
+        <v>2.55</v>
+      </c>
+      <c r="AC93">
+        <v>2.3</v>
+      </c>
+      <c r="AD93">
+        <v>1.6</v>
+      </c>
+      <c r="AE93">
+        <v>1.22</v>
+      </c>
+      <c r="AF93">
         <v>1.44</v>
       </c>
-      <c r="W93">
-        <v>1.11</v>
-      </c>
-      <c r="X93">
-        <v>1.03</v>
-      </c>
-      <c r="Y93">
-        <v>1.2</v>
-      </c>
-      <c r="Z93">
-        <v>3.7</v>
-      </c>
-      <c r="AA93">
-        <v>1.76</v>
-      </c>
-      <c r="AB93">
-        <v>1.98</v>
-      </c>
-      <c r="AC93">
-        <v>2.88</v>
-      </c>
-      <c r="AD93">
-        <v>1.41</v>
-      </c>
-      <c r="AE93">
-        <v>1.08</v>
-      </c>
-      <c r="AF93">
-        <v>1.62</v>
-      </c>
       <c r="AG93">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AK93">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.38</v>
+        <v>3.15</v>
       </c>
       <c r="O94">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P94">
-        <v>2.45</v>
+        <v>1.92</v>
       </c>
       <c r="Q94">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="R94">
-        <v>2.46</v>
+        <v>2.16</v>
       </c>
       <c r="S94">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="T94">
-        <v>3.52</v>
+        <v>3.1</v>
       </c>
       <c r="U94">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="V94">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="W94">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X94">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y94">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z94">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
       <c r="AA94">
-        <v>1.53</v>
+        <v>1.76</v>
       </c>
       <c r="AB94">
-        <v>2.55</v>
+        <v>1.98</v>
       </c>
       <c r="AC94">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="AD94">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="AE94">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AF94">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AG94">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AK94">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15960,10 +15960,10 @@
         <v>2.53</v>
       </c>
       <c r="O96">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="P96">
-        <v>2.65</v>
+        <v>2.38</v>
       </c>
       <c r="Q96">
         <v>3.02</v>
@@ -15999,7 +15999,7 @@
         <v>1.47</v>
       </c>
       <c r="AB96">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="AC96">
         <v>2.15</v>
@@ -16120,10 +16120,10 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="O97">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P97">
         <v>2.4</v>
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="O99">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P99">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="Q99">
         <v>2.49</v>
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="O101">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="P101">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Q101">
         <v>3.75</v>
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="O102">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P102">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="Q102">
         <v>2.52</v>
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O103">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P103">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17427,7 +17427,7 @@
         <v>2.2</v>
       </c>
       <c r="O105">
-        <v>3.35</v>
+        <v>3.01</v>
       </c>
       <c r="P105">
         <v>2.83</v>
@@ -18118,7 +18118,7 @@
         <v>2.62</v>
       </c>
       <c r="AB109">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AC109">
         <v>5.45</v>
@@ -18146,7 +18146,7 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK109">
         <v>1.53</v>
@@ -18420,7 +18420,7 @@
         <v>1.57</v>
       </c>
       <c r="T111">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="U111">
         <v>3.9</v>
@@ -18441,7 +18441,7 @@
         <v>2.12</v>
       </c>
       <c r="AA111">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AB111">
         <v>1.36</v>
@@ -18472,7 +18472,7 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK111">
         <v>1.6</v>

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -647,10 +647,10 @@
         <v>2.8</v>
       </c>
       <c r="R2">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="S2">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T2">
         <v>3</v>
@@ -801,13 +801,13 @@
         <v>2.25</v>
       </c>
       <c r="O3">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P3">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q3">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="R3">
         <v>2.3</v>
@@ -819,7 +819,7 @@
         <v>3.25</v>
       </c>
       <c r="U3">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="V3">
         <v>1.47</v>
@@ -828,16 +828,16 @@
         <v>1.12</v>
       </c>
       <c r="X3">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y3">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z3">
         <v>4.33</v>
       </c>
       <c r="AA3">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AB3">
         <v>2.15</v>
@@ -846,7 +846,7 @@
         <v>2.7</v>
       </c>
       <c r="AD3">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AE3">
         <v>1.17</v>
@@ -855,7 +855,7 @@
         <v>1.57</v>
       </c>
       <c r="AG3">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>1.33</v>
       </c>
       <c r="AK3">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="O4">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="P4">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="Q4">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="R4">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="S4">
         <v>1.36</v>
@@ -1003,7 +1003,7 @@
         <v>1.9</v>
       </c>
       <c r="AB4">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AC4">
         <v>3.4</v>
@@ -1034,7 +1034,7 @@
         <v>1.18</v>
       </c>
       <c r="AK4">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.7</v>
+        <v>3.63</v>
       </c>
       <c r="O5">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P5">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="Q5">
-        <v>4.18</v>
+        <v>4</v>
       </c>
       <c r="R5">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="S5">
         <v>1.2</v>
@@ -1145,37 +1145,37 @@
         <v>3.9</v>
       </c>
       <c r="U5">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="V5">
         <v>1.67</v>
       </c>
       <c r="W5">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X5">
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z5">
-        <v>5.65</v>
+        <v>5.75</v>
       </c>
       <c r="AA5">
         <v>1.44</v>
       </c>
       <c r="AB5">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AC5">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AD5">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AE5">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AF5">
         <v>1.4</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.16</v>
+        <v>1.91</v>
       </c>
       <c r="AK5">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1450,16 +1450,16 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="O7">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P7">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="Q7">
-        <v>2.88</v>
+        <v>3.09</v>
       </c>
       <c r="R7">
         <v>2.25</v>
@@ -1782,7 +1782,7 @@
         <v>3.45</v>
       </c>
       <c r="P9">
-        <v>3.85</v>
+        <v>3.66</v>
       </c>
       <c r="Q9">
         <v>2.48</v>
@@ -1942,10 +1942,10 @@
         <v>2.59</v>
       </c>
       <c r="O10">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P10">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="Q10">
         <v>3.28</v>
@@ -1957,13 +1957,13 @@
         <v>1.33</v>
       </c>
       <c r="T10">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="U10">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="V10">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W10">
         <v>1.1</v>
@@ -1984,16 +1984,16 @@
         <v>1.88</v>
       </c>
       <c r="AC10">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AD10">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE10">
         <v>1.08</v>
       </c>
       <c r="AF10">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG10">
         <v>2.1</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="AK10">
         <v>1.4</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="O11">
-        <v>3.22</v>
+        <v>3.35</v>
       </c>
       <c r="P11">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2141,10 +2141,10 @@
         <v>0</v>
       </c>
       <c r="AA11">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB11">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC11">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="O12">
         <v>3.5</v>
       </c>
       <c r="P12">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2428,34 +2428,34 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="O13">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P13">
         <v>2.5</v>
       </c>
       <c r="Q13">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="R13">
-        <v>2.21</v>
+        <v>2.14</v>
       </c>
       <c r="S13">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T13">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U13">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="V13">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W13">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X13">
         <v>1.02</v>
@@ -2464,13 +2464,13 @@
         <v>1.16</v>
       </c>
       <c r="Z13">
-        <v>4.15</v>
+        <v>4.05</v>
       </c>
       <c r="AA13">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AB13">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="AC13">
         <v>2.52</v>
@@ -2482,10 +2482,10 @@
         <v>1.13</v>
       </c>
       <c r="AF13">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AG13">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK13">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,31 +2591,31 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="O14">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P14">
         <v>2.45</v>
       </c>
       <c r="Q14">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="R14">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S14">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T14">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="U14">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="V14">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="W14">
         <v>1.1</v>
@@ -2624,31 +2624,31 @@
         <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z14">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA14">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AB14">
-        <v>2.06</v>
+        <v>2.17</v>
       </c>
       <c r="AC14">
-        <v>2.66</v>
+        <v>2.49</v>
       </c>
       <c r="AD14">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AE14">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF14">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AG14">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.2</v>
+        <v>1.53</v>
       </c>
       <c r="AK14">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2757,61 +2757,61 @@
         <v>1.35</v>
       </c>
       <c r="O15">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="P15">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="Q15">
+        <v>1.75</v>
+      </c>
+      <c r="R15">
+        <v>2.6</v>
+      </c>
+      <c r="S15">
+        <v>1.24</v>
+      </c>
+      <c r="T15">
+        <v>3.75</v>
+      </c>
+      <c r="U15">
+        <v>2.13</v>
+      </c>
+      <c r="V15">
+        <v>1.61</v>
+      </c>
+      <c r="W15">
+        <v>1.14</v>
+      </c>
+      <c r="X15">
+        <v>1.02</v>
+      </c>
+      <c r="Y15">
+        <v>1.11</v>
+      </c>
+      <c r="Z15">
+        <v>4.95</v>
+      </c>
+      <c r="AA15">
+        <v>1.48</v>
+      </c>
+      <c r="AB15">
+        <v>2.55</v>
+      </c>
+      <c r="AC15">
+        <v>2.22</v>
+      </c>
+      <c r="AD15">
         <v>1.57</v>
       </c>
-      <c r="R15">
-        <v>2.88</v>
-      </c>
-      <c r="S15">
-        <v>1.2</v>
-      </c>
-      <c r="T15">
-        <v>4</v>
-      </c>
-      <c r="U15">
-        <v>2.06</v>
-      </c>
-      <c r="V15">
-        <v>1.65</v>
-      </c>
-      <c r="W15">
-        <v>1.17</v>
-      </c>
-      <c r="X15">
-        <v>1.01</v>
-      </c>
-      <c r="Y15">
-        <v>1.09</v>
-      </c>
-      <c r="Z15">
-        <v>5.3</v>
-      </c>
-      <c r="AA15">
-        <v>1.41</v>
-      </c>
-      <c r="AB15">
-        <v>2.52</v>
-      </c>
-      <c r="AC15">
-        <v>2.06</v>
-      </c>
-      <c r="AD15">
-        <v>1.65</v>
-      </c>
       <c r="AE15">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AF15">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AG15">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AK15">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="O16">
         <v>3.3</v>
       </c>
       <c r="P16">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="Q16">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="R16">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="S16">
         <v>1.3</v>
       </c>
       <c r="T16">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="U16">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="V16">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W16">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X16">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z16">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AA16">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AB16">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AC16">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AD16">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AE16">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF16">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG16">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK16">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,25 +3080,25 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="O17">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P17">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="Q17">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="R17">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="S17">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T17">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="U17">
         <v>2.45</v>
@@ -3116,13 +3116,13 @@
         <v>1.18</v>
       </c>
       <c r="Z17">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="AA17">
         <v>1.67</v>
       </c>
       <c r="AB17">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AC17">
         <v>2.66</v>
@@ -3134,10 +3134,10 @@
         <v>1.11</v>
       </c>
       <c r="AF17">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG17">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>1.18</v>
       </c>
       <c r="AK17">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>6.75</v>
+        <v>6.25</v>
       </c>
       <c r="O18">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="P18">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>6.72</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3735,7 +3735,7 @@
         <v>2.12</v>
       </c>
       <c r="O21">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="P21">
         <v>2.7</v>
@@ -3753,10 +3753,10 @@
         <v>3.5</v>
       </c>
       <c r="U21">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V21">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W21">
         <v>1.13</v>
@@ -3901,13 +3901,13 @@
         <v>8</v>
       </c>
       <c r="P22">
-        <v>14</v>
+        <v>13.3</v>
       </c>
       <c r="Q22">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="R22">
-        <v>3.06</v>
+        <v>3.22</v>
       </c>
       <c r="S22">
         <v>1.17</v>
@@ -3940,13 +3940,13 @@
         <v>3.4</v>
       </c>
       <c r="AC22">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AD22">
         <v>1.93</v>
       </c>
       <c r="AE22">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AF22">
         <v>1.95</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="O23">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="P23">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="Q23">
         <v>2.75</v>
@@ -4079,7 +4079,7 @@
         <v>2.64</v>
       </c>
       <c r="U23">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="V23">
         <v>1.36</v>
@@ -4097,10 +4097,10 @@
         <v>3.1</v>
       </c>
       <c r="AA23">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="AB23">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC23">
         <v>3.7</v>
@@ -4876,10 +4876,10 @@
         <v>3</v>
       </c>
       <c r="O28">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="P28">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Q28">
         <v>3.5</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="AK28">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>7.25</v>
+        <v>7</v>
       </c>
       <c r="O29">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="P29">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="Q29">
         <v>7</v>
@@ -5054,7 +5054,7 @@
         <v>1.37</v>
       </c>
       <c r="T29">
-        <v>3</v>
+        <v>2.79</v>
       </c>
       <c r="U29">
         <v>2.53</v>
@@ -5093,7 +5093,7 @@
         <v>2</v>
       </c>
       <c r="AG29">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK29">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="O30">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="P30">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="Q30">
         <v>2.5</v>
@@ -5217,7 +5217,7 @@
         <v>1.5</v>
       </c>
       <c r="T30">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="U30">
         <v>3.5</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="O31">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="P31">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O34">
         <v>3.25</v>
       </c>
       <c r="P34">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="Q34">
         <v>2.5</v>
@@ -5893,7 +5893,7 @@
         <v>1.76</v>
       </c>
       <c r="AB34">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AC34">
         <v>2.75</v>
@@ -6340,7 +6340,7 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="O37">
         <v>3.8</v>
@@ -6509,7 +6509,7 @@
         <v>3.3</v>
       </c>
       <c r="P38">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="Q38">
         <v>4.33</v>
@@ -6576,7 +6576,7 @@
         <v>1.3</v>
       </c>
       <c r="AK38">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6835,13 +6835,13 @@
         <v>4.4</v>
       </c>
       <c r="P40">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="Q40">
-        <v>5.65</v>
+        <v>5.76</v>
       </c>
       <c r="R40">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="S40">
         <v>1.2</v>
@@ -6853,7 +6853,7 @@
         <v>2.14</v>
       </c>
       <c r="V40">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W40">
         <v>1.17</v>
@@ -6862,25 +6862,25 @@
         <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Z40">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="AA40">
         <v>1.44</v>
       </c>
       <c r="AB40">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AC40">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AD40">
         <v>1.71</v>
       </c>
       <c r="AE40">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AF40">
         <v>1.53</v>
@@ -7013,7 +7013,7 @@
         <v>3.4</v>
       </c>
       <c r="U41">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="V41">
         <v>1.56</v>
@@ -7028,16 +7028,16 @@
         <v>1.15</v>
       </c>
       <c r="Z41">
-        <v>4.77</v>
+        <v>4.75</v>
       </c>
       <c r="AA41">
         <v>1.57</v>
       </c>
       <c r="AB41">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC41">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="AD41">
         <v>1.5</v>
@@ -7164,7 +7164,7 @@
         <v>3.55</v>
       </c>
       <c r="Q42">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R42">
         <v>1.91</v>
@@ -7209,7 +7209,7 @@
         <v>1.03</v>
       </c>
       <c r="AF42">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AG42">
         <v>1.83</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="O47">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="P47">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Q47">
         <v>7</v>
@@ -7994,7 +7994,7 @@
         <v>2.29</v>
       </c>
       <c r="V47">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W47">
         <v>1.14</v>
@@ -8015,7 +8015,7 @@
         <v>2.25</v>
       </c>
       <c r="AC47">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="AD47">
         <v>1.52</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="O48">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P48">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q48">
         <v>3.56</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="O49">
         <v>3.3</v>
       </c>
       <c r="P49">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="Q49">
         <v>2.88</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O51">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P51">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,80 +8785,80 @@
         </is>
       </c>
       <c r="N52">
-        <v>3.05</v>
+        <v>1.53</v>
       </c>
       <c r="O52">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="P52">
-        <v>2.15</v>
+        <v>4.6</v>
       </c>
       <c r="Q52">
-        <v>3.08</v>
+        <v>1.95</v>
       </c>
       <c r="R52">
-        <v>2.22</v>
+        <v>2.6</v>
       </c>
       <c r="S52">
+        <v>1.2</v>
+      </c>
+      <c r="T52">
+        <v>4.1</v>
+      </c>
+      <c r="U52">
+        <v>2</v>
+      </c>
+      <c r="V52">
+        <v>1.73</v>
+      </c>
+      <c r="W52">
+        <v>1.18</v>
+      </c>
+      <c r="X52">
+        <v>1.01</v>
+      </c>
+      <c r="Y52">
+        <v>1.08</v>
+      </c>
+      <c r="Z52">
+        <v>5.45</v>
+      </c>
+      <c r="AA52">
+        <v>1.4</v>
+      </c>
+      <c r="AB52">
+        <v>2.88</v>
+      </c>
+      <c r="AC52">
+        <v>2</v>
+      </c>
+      <c r="AD52">
+        <v>1.71</v>
+      </c>
+      <c r="AE52">
         <v>1.29</v>
       </c>
-      <c r="T52">
-        <v>3.5</v>
-      </c>
-      <c r="U52">
-        <v>2.41</v>
-      </c>
-      <c r="V52">
-        <v>1.56</v>
-      </c>
-      <c r="W52">
-        <v>1.12</v>
-      </c>
-      <c r="X52">
-        <v>1.03</v>
-      </c>
-      <c r="Y52">
+      <c r="AF52">
+        <v>1.5</v>
+      </c>
+      <c r="AG52">
+        <v>2.38</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ52">
         <v>1.14</v>
       </c>
-      <c r="Z52">
-        <v>4.35</v>
-      </c>
-      <c r="AA52">
-        <v>1.61</v>
-      </c>
-      <c r="AB52">
-        <v>2.31</v>
-      </c>
-      <c r="AC52">
-        <v>2.56</v>
-      </c>
-      <c r="AD52">
-        <v>1.44</v>
-      </c>
-      <c r="AE52">
-        <v>1.19</v>
-      </c>
-      <c r="AF52">
-        <v>1.53</v>
-      </c>
-      <c r="AG52">
-        <v>2.39</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ52">
-        <v>1.24</v>
-      </c>
       <c r="AK52">
-        <v>1.35</v>
+        <v>2.4</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
+        <v>3</v>
+      </c>
+      <c r="O53">
+        <v>3.4</v>
+      </c>
+      <c r="P53">
+        <v>2.2</v>
+      </c>
+      <c r="Q53">
+        <v>3.62</v>
+      </c>
+      <c r="R53">
+        <v>2.28</v>
+      </c>
+      <c r="S53">
+        <v>1.25</v>
+      </c>
+      <c r="T53">
+        <v>3.5</v>
+      </c>
+      <c r="U53">
+        <v>2.41</v>
+      </c>
+      <c r="V53">
+        <v>1.56</v>
+      </c>
+      <c r="W53">
+        <v>1.15</v>
+      </c>
+      <c r="X53">
+        <v>1.03</v>
+      </c>
+      <c r="Y53">
+        <v>1.14</v>
+      </c>
+      <c r="Z53">
+        <v>4.35</v>
+      </c>
+      <c r="AA53">
+        <v>1.61</v>
+      </c>
+      <c r="AB53">
+        <v>2.31</v>
+      </c>
+      <c r="AC53">
+        <v>2.56</v>
+      </c>
+      <c r="AD53">
+        <v>1.44</v>
+      </c>
+      <c r="AE53">
+        <v>1.19</v>
+      </c>
+      <c r="AF53">
         <v>1.53</v>
       </c>
-      <c r="O53">
-        <v>4.4</v>
-      </c>
-      <c r="P53">
-        <v>4.6</v>
-      </c>
-      <c r="Q53">
-        <v>2.06</v>
-      </c>
-      <c r="R53">
-        <v>2.35</v>
-      </c>
-      <c r="S53">
-        <v>1.2</v>
-      </c>
-      <c r="T53">
-        <v>4.1</v>
-      </c>
-      <c r="U53">
-        <v>2.13</v>
-      </c>
-      <c r="V53">
-        <v>1.7</v>
-      </c>
-      <c r="W53">
-        <v>1.18</v>
-      </c>
-      <c r="X53">
-        <v>1.01</v>
-      </c>
-      <c r="Y53">
-        <v>1.08</v>
-      </c>
-      <c r="Z53">
-        <v>5.45</v>
-      </c>
-      <c r="AA53">
-        <v>1.4</v>
-      </c>
-      <c r="AB53">
-        <v>2.88</v>
-      </c>
-      <c r="AC53">
-        <v>2</v>
-      </c>
-      <c r="AD53">
-        <v>1.71</v>
-      </c>
-      <c r="AE53">
-        <v>1.29</v>
-      </c>
-      <c r="AF53">
-        <v>1.44</v>
-      </c>
       <c r="AG53">
-        <v>2.63</v>
+        <v>2.39</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AK53">
-        <v>2.4</v>
+        <v>1.35</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="O54">
-        <v>3.88</v>
+        <v>3.83</v>
       </c>
       <c r="P54">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q54">
         <v>2.89</v>
@@ -9150,10 +9150,10 @@
         <v>5.65</v>
       </c>
       <c r="AA54">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AB54">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AC54">
         <v>2.08</v>
@@ -9277,7 +9277,7 @@
         <v>3.16</v>
       </c>
       <c r="O55">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="P55">
         <v>2</v>
@@ -9298,7 +9298,7 @@
         <v>2.04</v>
       </c>
       <c r="V55">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="W55">
         <v>1.18</v>
@@ -9319,7 +9319,7 @@
         <v>3.17</v>
       </c>
       <c r="AC55">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AD55">
         <v>1.98</v>
@@ -9437,25 +9437,25 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="O56">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P56">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="Q56">
         <v>3.3</v>
       </c>
       <c r="R56">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S56">
         <v>1.4</v>
       </c>
       <c r="T56">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="U56">
         <v>3</v>
@@ -9464,7 +9464,7 @@
         <v>1.35</v>
       </c>
       <c r="W56">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X56">
         <v>1.06</v>
@@ -9476,7 +9476,7 @@
         <v>3.1</v>
       </c>
       <c r="AA56">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB56">
         <v>1.65</v>
@@ -9507,7 +9507,7 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AK56">
         <v>1.4</v>
@@ -9600,10 +9600,10 @@
         </is>
       </c>
       <c r="N57">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O57">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P57">
         <v>1.79</v>
@@ -9763,16 +9763,16 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="O58">
         <v>3.6</v>
       </c>
       <c r="P58">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q58">
-        <v>2.42</v>
+        <v>2.47</v>
       </c>
       <c r="R58">
         <v>2.41</v>
@@ -9793,7 +9793,7 @@
         <v>1.1</v>
       </c>
       <c r="X58">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y58">
         <v>1.2</v>
@@ -9817,7 +9817,7 @@
         <v>1.12</v>
       </c>
       <c r="AF58">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG58">
         <v>2.2</v>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="O59">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P59">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="Q59">
         <v>2.63</v>
@@ -9953,7 +9953,7 @@
         <v>1.57</v>
       </c>
       <c r="W59">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X59">
         <v>1.01</v>
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>5.75</v>
+        <v>5.71</v>
       </c>
       <c r="O61">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="P61">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="Q61">
         <v>4.58</v>
@@ -10415,34 +10415,34 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="O62">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P62">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q62">
         <v>3.42</v>
       </c>
       <c r="R62">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="S62">
         <v>1.3</v>
       </c>
       <c r="T62">
-        <v>3.23</v>
+        <v>3.27</v>
       </c>
       <c r="U62">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="V62">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W62">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X62">
         <v>1.03</v>
@@ -10457,7 +10457,7 @@
         <v>1.8</v>
       </c>
       <c r="AB62">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC62">
         <v>2.9</v>
@@ -10472,7 +10472,7 @@
         <v>1.62</v>
       </c>
       <c r="AG62">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10578,10 +10578,10 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="O63">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="P63">
         <v>7.5</v>
@@ -10651,7 +10651,7 @@
         <v>1.03</v>
       </c>
       <c r="AK63">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10925,31 +10925,31 @@
         <v>3.7</v>
       </c>
       <c r="U65">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="V65">
         <v>1.64</v>
       </c>
       <c r="W65">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X65">
         <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z65">
         <v>4.85</v>
       </c>
       <c r="AA65">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AB65">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AC65">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AD65">
         <v>1.58</v>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK65">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="O66">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P66">
-        <v>3.4</v>
+        <v>2.91</v>
       </c>
       <c r="Q66">
         <v>2.63</v>
@@ -11100,22 +11100,22 @@
         <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z66">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="AA66">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AB66">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AC66">
-        <v>3.09</v>
+        <v>2.88</v>
       </c>
       <c r="AD66">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE66">
         <v>1.14</v>
@@ -11140,7 +11140,7 @@
         <v>1.3</v>
       </c>
       <c r="AK66">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.63</v>
+        <v>1.73</v>
       </c>
       <c r="O67">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="P67">
+        <v>4.4</v>
+      </c>
+      <c r="Q67">
+        <v>2.25</v>
+      </c>
+      <c r="R67">
+        <v>2.24</v>
+      </c>
+      <c r="S67">
+        <v>1.29</v>
+      </c>
+      <c r="T67">
+        <v>3.46</v>
+      </c>
+      <c r="U67">
+        <v>2.4</v>
+      </c>
+      <c r="V67">
+        <v>1.52</v>
+      </c>
+      <c r="W67">
+        <v>1.12</v>
+      </c>
+      <c r="X67">
+        <v>1.02</v>
+      </c>
+      <c r="Y67">
+        <v>1.21</v>
+      </c>
+      <c r="Z67">
+        <v>4.4</v>
+      </c>
+      <c r="AA67">
+        <v>1.65</v>
+      </c>
+      <c r="AB67">
+        <v>2.2</v>
+      </c>
+      <c r="AC67">
         <v>2.7</v>
       </c>
-      <c r="Q67">
-        <v>3.4</v>
-      </c>
-      <c r="R67">
-        <v>1.95</v>
-      </c>
-      <c r="S67">
-        <v>1.49</v>
-      </c>
-      <c r="T67">
-        <v>2.39</v>
-      </c>
-      <c r="U67">
-        <v>3.33</v>
-      </c>
-      <c r="V67">
-        <v>1.3</v>
-      </c>
-      <c r="W67">
-        <v>1.04</v>
-      </c>
-      <c r="X67">
-        <v>1.04</v>
-      </c>
-      <c r="Y67">
+      <c r="AD67">
         <v>1.43</v>
       </c>
-      <c r="Z67">
-        <v>2.85</v>
-      </c>
-      <c r="AA67">
-        <v>2.3</v>
-      </c>
-      <c r="AB67">
-        <v>1.6</v>
-      </c>
-      <c r="AC67">
-        <v>4.15</v>
-      </c>
-      <c r="AD67">
-        <v>1.17</v>
-      </c>
       <c r="AE67">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="AF67">
-        <v>1.94</v>
+        <v>1.62</v>
       </c>
       <c r="AG67">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AK67">
-        <v>1.41</v>
+        <v>2.1</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.55</v>
+        <v>2.04</v>
       </c>
       <c r="O68">
         <v>3.35</v>
       </c>
       <c r="P68">
-        <v>2.6</v>
+        <v>3.55</v>
       </c>
       <c r="Q68">
-        <v>3</v>
+        <v>2.79</v>
       </c>
       <c r="R68">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="S68">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T68">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="U68">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="V68">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W68">
+        <v>1.05</v>
+      </c>
+      <c r="X68">
         <v>1.04</v>
       </c>
-      <c r="X68">
-        <v>1</v>
-      </c>
       <c r="Y68">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z68">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="AA68">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="AB68">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AC68">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD68">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE68">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF68">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AG68">
-        <v>2.01</v>
+        <v>1.92</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AK68">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.15</v>
+        <v>2.59</v>
       </c>
       <c r="O69">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="P69">
-        <v>3.35</v>
+        <v>2.5</v>
       </c>
       <c r="Q69">
-        <v>2.78</v>
+        <v>3.4</v>
       </c>
       <c r="R69">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="S69">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="T69">
-        <v>2.88</v>
+        <v>2.39</v>
       </c>
       <c r="U69">
-        <v>2.88</v>
+        <v>3.33</v>
       </c>
       <c r="V69">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W69">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X69">
         <v>1.04</v>
       </c>
       <c r="Y69">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="Z69">
-        <v>3.08</v>
+        <v>2.85</v>
       </c>
       <c r="AA69">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="AB69">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AC69">
-        <v>3.5</v>
+        <v>4.15</v>
       </c>
       <c r="AD69">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AE69">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="AF69">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AG69">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AK69">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.73</v>
+        <v>2.55</v>
       </c>
       <c r="O70">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="P70">
-        <v>4.4</v>
+        <v>2.6</v>
       </c>
       <c r="Q70">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="R70">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="S70">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="T70">
-        <v>3.46</v>
+        <v>2.93</v>
       </c>
       <c r="U70">
-        <v>2.4</v>
+        <v>2.68</v>
       </c>
       <c r="V70">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="W70">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="X70">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y70">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="Z70">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="AA70">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AB70">
-        <v>2.19</v>
+        <v>1.81</v>
       </c>
       <c r="AC70">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="AD70">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AE70">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF70">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AG70">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="AK70">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11888,7 +11888,7 @@
         <v>4.33</v>
       </c>
       <c r="P71">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AK72">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12208,16 +12208,16 @@
         </is>
       </c>
       <c r="N73">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="O73">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P73">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="Q73">
-        <v>3.63</v>
+        <v>4</v>
       </c>
       <c r="R73">
         <v>2.4</v>
@@ -12256,7 +12256,7 @@
         <v>2.3</v>
       </c>
       <c r="AD73">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AE73">
         <v>1.2</v>
@@ -12265,7 +12265,7 @@
         <v>1.47</v>
       </c>
       <c r="AG73">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.79</v>
+        <v>1.2</v>
       </c>
       <c r="AK73">
         <v>1.29</v>
@@ -12374,25 +12374,25 @@
         <v>5</v>
       </c>
       <c r="O74">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="P74">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Q74">
         <v>5</v>
       </c>
       <c r="R74">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="S74">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T74">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="U74">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="V74">
         <v>1.85</v>
@@ -12416,10 +12416,10 @@
         <v>2.88</v>
       </c>
       <c r="AC74">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AD74">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AE74">
         <v>1.33</v>
@@ -12441,7 +12441,7 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AK74">
         <v>1.15</v>
@@ -12534,31 +12534,31 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="O75">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="P75">
-        <v>3.58</v>
+        <v>4.1</v>
       </c>
       <c r="Q75">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="R75">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="S75">
         <v>1.18</v>
       </c>
       <c r="T75">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="U75">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="V75">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="W75">
         <v>1.19</v>
@@ -12579,7 +12579,7 @@
         <v>3.1</v>
       </c>
       <c r="AC75">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AD75">
         <v>1.86</v>
@@ -12697,16 +12697,16 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="O76">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P76">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q76">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="R76">
         <v>2.6</v>
@@ -12718,7 +12718,7 @@
         <v>4.5</v>
       </c>
       <c r="U76">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="V76">
         <v>1.86</v>
@@ -12742,7 +12742,7 @@
         <v>3.5</v>
       </c>
       <c r="AC76">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AD76">
         <v>1.99</v>
@@ -12754,7 +12754,7 @@
         <v>1.3</v>
       </c>
       <c r="AG76">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK76">
         <v>1.65</v>
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="O77">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P77">
-        <v>4.06</v>
+        <v>3.8</v>
       </c>
       <c r="Q77">
         <v>2.3</v>
@@ -12884,7 +12884,7 @@
         <v>2.73</v>
       </c>
       <c r="V77">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W77">
         <v>1.07</v>
@@ -12899,10 +12899,10 @@
         <v>3.8</v>
       </c>
       <c r="AA77">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AB77">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="AC77">
         <v>2.9</v>
@@ -12930,7 +12930,7 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK77">
         <v>1.98</v>
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="O78">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P78">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="Q78">
         <v>2.5</v>
@@ -13062,7 +13062,7 @@
         <v>3.84</v>
       </c>
       <c r="AA78">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB78">
         <v>2.1</v>
@@ -13186,31 +13186,31 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="O79">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P79">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="Q79">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="R79">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S79">
         <v>1.34</v>
       </c>
       <c r="T79">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="U79">
         <v>2.59</v>
       </c>
       <c r="V79">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W79">
         <v>1.06</v>
@@ -13225,13 +13225,13 @@
         <v>3.6</v>
       </c>
       <c r="AA79">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB79">
         <v>1.85</v>
       </c>
       <c r="AC79">
-        <v>3.27</v>
+        <v>3.31</v>
       </c>
       <c r="AD79">
         <v>1.3</v>
@@ -13352,13 +13352,13 @@
         <v>4</v>
       </c>
       <c r="O80">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P80">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="Q80">
-        <v>4.85</v>
+        <v>4.96</v>
       </c>
       <c r="R80">
         <v>2.25</v>
@@ -13394,7 +13394,7 @@
         <v>2.05</v>
       </c>
       <c r="AC80">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AD80">
         <v>1.35</v>
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="O81">
         <v>3.4</v>
       </c>
       <c r="P81">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13675,19 +13675,19 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O82">
         <v>3.25</v>
       </c>
       <c r="P82">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="Q82">
         <v>2.77</v>
       </c>
       <c r="R82">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="S82">
         <v>1.29</v>
@@ -13838,10 +13838,10 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O83">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P83">
         <v>2.85</v>
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="O84">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P84">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="Q84">
         <v>3.45</v>
@@ -14164,19 +14164,19 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="O85">
         <v>4</v>
       </c>
       <c r="P85">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q85">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="R85">
-        <v>2.53</v>
+        <v>2.48</v>
       </c>
       <c r="S85">
         <v>1.18</v>
@@ -14360,19 +14360,19 @@
         <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z86">
         <v>3.08</v>
       </c>
       <c r="AA86">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AB86">
         <v>1.75</v>
       </c>
       <c r="AC86">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AD86">
         <v>1.25</v>
@@ -14511,7 +14511,7 @@
         <v>3.18</v>
       </c>
       <c r="U87">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="V87">
         <v>1.53</v>
@@ -14520,7 +14520,7 @@
         <v>1.12</v>
       </c>
       <c r="X87">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y87">
         <v>1.19</v>
@@ -14532,16 +14532,16 @@
         <v>1.76</v>
       </c>
       <c r="AB87">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AC87">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="AD87">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AE87">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF87">
         <v>1.53</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.9</v>
+        <v>1.45</v>
       </c>
       <c r="O89">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="P89">
-        <v>2.15</v>
+        <v>4.6</v>
       </c>
       <c r="Q89">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="R89">
-        <v>2.32</v>
+        <v>2.7</v>
       </c>
       <c r="S89">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="T89">
-        <v>2.82</v>
+        <v>3.9</v>
       </c>
       <c r="U89">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="V89">
+        <v>1.73</v>
+      </c>
+      <c r="W89">
+        <v>1.17</v>
+      </c>
+      <c r="X89">
+        <v>1.01</v>
+      </c>
+      <c r="Y89">
+        <v>1.1</v>
+      </c>
+      <c r="Z89">
+        <v>5.2</v>
+      </c>
+      <c r="AA89">
         <v>1.44</v>
       </c>
-      <c r="W89">
-        <v>1.11</v>
-      </c>
-      <c r="X89">
-        <v>1.02</v>
-      </c>
-      <c r="Y89">
-        <v>1.21</v>
-      </c>
-      <c r="Z89">
-        <v>3.58</v>
-      </c>
-      <c r="AA89">
-        <v>1.82</v>
-      </c>
       <c r="AB89">
-        <v>2.06</v>
+        <v>2.7</v>
       </c>
       <c r="AC89">
-        <v>2.97</v>
+        <v>2.05</v>
       </c>
       <c r="AD89">
-        <v>1.3</v>
+        <v>1.66</v>
       </c>
       <c r="AE89">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AF89">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AG89">
-        <v>2.1</v>
+        <v>2.39</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK89">
-        <v>1.36</v>
+        <v>2.4</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.45</v>
+        <v>2.9</v>
       </c>
       <c r="O90">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="P90">
-        <v>4.6</v>
+        <v>2.15</v>
       </c>
       <c r="Q90">
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="R90">
-        <v>2.7</v>
+        <v>2.32</v>
       </c>
       <c r="S90">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="T90">
-        <v>3.9</v>
+        <v>2.82</v>
       </c>
       <c r="U90">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="V90">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="W90">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X90">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y90">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="Z90">
-        <v>5.2</v>
+        <v>3.58</v>
       </c>
       <c r="AA90">
-        <v>1.44</v>
+        <v>1.82</v>
       </c>
       <c r="AB90">
-        <v>2.7</v>
+        <v>2.06</v>
       </c>
       <c r="AC90">
-        <v>2.05</v>
+        <v>2.97</v>
       </c>
       <c r="AD90">
-        <v>1.66</v>
+        <v>1.3</v>
       </c>
       <c r="AE90">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AF90">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AG90">
-        <v>2.39</v>
+        <v>2.1</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK90">
-        <v>2.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15960,7 +15960,7 @@
         <v>2.53</v>
       </c>
       <c r="O96">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="P96">
         <v>2.38</v>
@@ -15969,7 +15969,7 @@
         <v>3.02</v>
       </c>
       <c r="R96">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S96">
         <v>1.28</v>
@@ -15981,7 +15981,7 @@
         <v>2.2</v>
       </c>
       <c r="V96">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W96">
         <v>1.14</v>
@@ -15999,7 +15999,7 @@
         <v>1.47</v>
       </c>
       <c r="AB96">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="AC96">
         <v>2.15</v>
@@ -16008,10 +16008,10 @@
         <v>1.67</v>
       </c>
       <c r="AE96">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF96">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AG96">
         <v>3.1</v>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK96">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16129,10 +16129,10 @@
         <v>2.4</v>
       </c>
       <c r="Q97">
-        <v>3.02</v>
+        <v>2.69</v>
       </c>
       <c r="R97">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="S97">
         <v>1.25</v>
@@ -16141,37 +16141,37 @@
         <v>3.5</v>
       </c>
       <c r="U97">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="V97">
         <v>1.53</v>
       </c>
       <c r="W97">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X97">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y97">
         <v>1.13</v>
       </c>
       <c r="Z97">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="AA97">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AB97">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AC97">
-        <v>2.43</v>
+        <v>2.63</v>
       </c>
       <c r="AD97">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE97">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF97">
         <v>1.48</v>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK97">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16455,10 +16455,10 @@
         <v>3.5</v>
       </c>
       <c r="Q99">
-        <v>2.49</v>
+        <v>2.59</v>
       </c>
       <c r="R99">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="S99">
         <v>1.39</v>
@@ -16467,10 +16467,10 @@
         <v>2.99</v>
       </c>
       <c r="U99">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="V99">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W99">
         <v>1.1</v>
@@ -16482,19 +16482,19 @@
         <v>1.29</v>
       </c>
       <c r="Z99">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AA99">
+        <v>1.92</v>
+      </c>
+      <c r="AB99">
         <v>1.97</v>
-      </c>
-      <c r="AB99">
-        <v>1.92</v>
       </c>
       <c r="AC99">
         <v>3.25</v>
       </c>
       <c r="AD99">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE99">
         <v>1.1</v>
@@ -16618,10 +16618,10 @@
         <v>2.35</v>
       </c>
       <c r="Q100">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="R100">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="S100">
         <v>1.33</v>
@@ -16630,10 +16630,10 @@
         <v>3.1</v>
       </c>
       <c r="U100">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="V100">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W100">
         <v>1.06</v>
@@ -16654,7 +16654,7 @@
         <v>1.95</v>
       </c>
       <c r="AC100">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="AD100">
         <v>1.36</v>
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>3.65</v>
+        <v>3.68</v>
       </c>
       <c r="O101">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="P101">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Q101">
         <v>3.75</v>
@@ -16938,22 +16938,22 @@
         <v>1.83</v>
       </c>
       <c r="O102">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P102">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="Q102">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="R102">
-        <v>1.96</v>
+        <v>2.11</v>
       </c>
       <c r="S102">
         <v>1.47</v>
       </c>
       <c r="T102">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="U102">
         <v>3.18</v>
@@ -16971,7 +16971,7 @@
         <v>1.3</v>
       </c>
       <c r="Z102">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="AA102">
         <v>1.92</v>
@@ -16980,7 +16980,7 @@
         <v>1.61</v>
       </c>
       <c r="AC102">
-        <v>4.21</v>
+        <v>4.25</v>
       </c>
       <c r="AD102">
         <v>1.21</v>
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="O103">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="P103">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17137,10 +17137,10 @@
         <v>0</v>
       </c>
       <c r="AA103">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB103">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC103">
         <v>0</v>
@@ -17261,19 +17261,19 @@
         </is>
       </c>
       <c r="N104">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O104">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="P104">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="Q104">
-        <v>9.6</v>
+        <v>6.28</v>
       </c>
       <c r="R104">
-        <v>2.61</v>
+        <v>2.44</v>
       </c>
       <c r="S104">
         <v>1.3</v>
@@ -17282,7 +17282,7 @@
         <v>3.25</v>
       </c>
       <c r="U104">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="V104">
         <v>1.5</v>
@@ -17291,50 +17291,50 @@
         <v>1.08</v>
       </c>
       <c r="X104">
+        <v>1.01</v>
+      </c>
+      <c r="Y104">
+        <v>1.2</v>
+      </c>
+      <c r="Z104">
+        <v>3.72</v>
+      </c>
+      <c r="AA104">
+        <v>1.72</v>
+      </c>
+      <c r="AB104">
+        <v>2.03</v>
+      </c>
+      <c r="AC104">
+        <v>2.69</v>
+      </c>
+      <c r="AD104">
+        <v>1.36</v>
+      </c>
+      <c r="AE104">
+        <v>1.11</v>
+      </c>
+      <c r="AF104">
+        <v>2.15</v>
+      </c>
+      <c r="AG104">
+        <v>1.67</v>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ104">
+        <v>1.13</v>
+      </c>
+      <c r="AK104">
         <v>1.02</v>
-      </c>
-      <c r="Y104">
-        <v>1.16</v>
-      </c>
-      <c r="Z104">
-        <v>4.1</v>
-      </c>
-      <c r="AA104">
-        <v>1.63</v>
-      </c>
-      <c r="AB104">
-        <v>2.17</v>
-      </c>
-      <c r="AC104">
-        <v>2.46</v>
-      </c>
-      <c r="AD104">
-        <v>1.46</v>
-      </c>
-      <c r="AE104">
-        <v>1.15</v>
-      </c>
-      <c r="AF104">
-        <v>2.38</v>
-      </c>
-      <c r="AG104">
-        <v>1.62</v>
-      </c>
-      <c r="AH104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ104">
-        <v>4</v>
-      </c>
-      <c r="AK104">
-        <v>1.04</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17424,10 +17424,10 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O105">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="P105">
         <v>2.83</v>
@@ -17657,7 +17657,7 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AK106">
         <v>2.4</v>
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.23</v>
+        <v>2.31</v>
       </c>
       <c r="O107">
         <v>3.07</v>
       </c>
       <c r="P107">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="Q107">
         <v>3.1</v>
@@ -17771,7 +17771,7 @@
         <v>2.67</v>
       </c>
       <c r="U107">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="V107">
         <v>1.33</v>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK107">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -18079,10 +18079,10 @@
         <v>2.23</v>
       </c>
       <c r="O109">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="P109">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="Q109">
         <v>3.1</v>
@@ -18112,13 +18112,13 @@
         <v>1.55</v>
       </c>
       <c r="Z109">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="AA109">
         <v>2.62</v>
       </c>
       <c r="AB109">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AC109">
         <v>5.45</v>
@@ -18438,13 +18438,13 @@
         <v>1.62</v>
       </c>
       <c r="Z111">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AA111">
         <v>3.1</v>
       </c>
       <c r="AB111">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC111">
         <v>7</v>
@@ -18453,7 +18453,7 @@
         <v>1.07</v>
       </c>
       <c r="AE111">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF111">
         <v>2.3</v>
@@ -18565,7 +18565,7 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="O112">
         <v>3.6</v>

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="O4">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P4">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="Q4">
         <v>2.45</v>
@@ -1293,7 +1293,7 @@
         <v>3.5</v>
       </c>
       <c r="P6">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="Q6">
         <v>2.29</v>
@@ -1305,10 +1305,10 @@
         <v>1.35</v>
       </c>
       <c r="T6">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="U6">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="V6">
         <v>1.38</v>
@@ -1320,16 +1320,16 @@
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z6">
-        <v>3.38</v>
+        <v>3.41</v>
       </c>
       <c r="AA6">
         <v>1.92</v>
       </c>
       <c r="AB6">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AC6">
         <v>3.05</v>
@@ -1360,7 +1360,7 @@
         <v>1.25</v>
       </c>
       <c r="AK6">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="O9">
         <v>3.45</v>
@@ -1785,22 +1785,22 @@
         <v>3.66</v>
       </c>
       <c r="Q9">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="R9">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="S9">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T9">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="U9">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="V9">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W9">
         <v>1.05</v>
@@ -1809,19 +1809,19 @@
         <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z9">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AA9">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AB9">
         <v>1.75</v>
       </c>
       <c r="AC9">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="AD9">
         <v>1.25</v>
@@ -1830,10 +1830,10 @@
         <v>1.07</v>
       </c>
       <c r="AF9">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AG9">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AK9">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -3898,13 +3898,13 @@
         <v>1.11</v>
       </c>
       <c r="O22">
-        <v>8</v>
+        <v>8.9</v>
       </c>
       <c r="P22">
         <v>13.3</v>
       </c>
       <c r="Q22">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="R22">
         <v>3.22</v>
@@ -3916,10 +3916,10 @@
         <v>4.4</v>
       </c>
       <c r="U22">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V22">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="W22">
         <v>1.22</v>
@@ -3940,10 +3940,10 @@
         <v>3.4</v>
       </c>
       <c r="AC22">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AD22">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="AE22">
         <v>1.43</v>
@@ -4061,10 +4061,10 @@
         <v>2.3</v>
       </c>
       <c r="O23">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P23">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="Q23">
         <v>2.75</v>
@@ -4097,7 +4097,7 @@
         <v>3.1</v>
       </c>
       <c r="AA23">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AB23">
         <v>1.67</v>
@@ -4221,19 +4221,19 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="O24">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="P24">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="Q24">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="R24">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="S24">
         <v>1.36</v>
@@ -4242,7 +4242,7 @@
         <v>2.72</v>
       </c>
       <c r="U24">
-        <v>2.72</v>
+        <v>2.85</v>
       </c>
       <c r="V24">
         <v>1.36</v>
@@ -4251,7 +4251,7 @@
         <v>1.06</v>
       </c>
       <c r="X24">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
         <v>1.29</v>
@@ -4275,10 +4275,10 @@
         <v>1.07</v>
       </c>
       <c r="AF24">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG24">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK24">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="O25">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P25">
-        <v>2.34</v>
+        <v>2.15</v>
       </c>
       <c r="Q25">
-        <v>3.35</v>
+        <v>3.56</v>
       </c>
       <c r="R25">
         <v>2.09</v>
       </c>
       <c r="S25">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T25">
         <v>3.3</v>
       </c>
       <c r="U25">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="V25">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W25">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X25">
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z25">
-        <v>3.84</v>
+        <v>3.98</v>
       </c>
       <c r="AA25">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AB25">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="AC25">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="AD25">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE25">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF25">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AG25">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4547,22 +4547,22 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="O26">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="P26">
-        <v>3.29</v>
+        <v>3.15</v>
       </c>
       <c r="Q26">
         <v>2.8</v>
       </c>
       <c r="R26">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S26">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T26">
         <v>2.57</v>
@@ -4586,10 +4586,10 @@
         <v>2.95</v>
       </c>
       <c r="AA26">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB26">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC26">
         <v>3.46</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,19 +4710,19 @@
         </is>
       </c>
       <c r="N27">
-        <v>4.98</v>
+        <v>4.7</v>
       </c>
       <c r="O27">
-        <v>3.93</v>
+        <v>3.75</v>
       </c>
       <c r="P27">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="Q27">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="R27">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="S27">
         <v>1.38</v>
@@ -4731,7 +4731,7 @@
         <v>2.9</v>
       </c>
       <c r="U27">
-        <v>2.58</v>
+        <v>2.78</v>
       </c>
       <c r="V27">
         <v>1.4</v>
@@ -4740,34 +4740,34 @@
         <v>1.06</v>
       </c>
       <c r="X27">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z27">
-        <v>3.8</v>
+        <v>3.42</v>
       </c>
       <c r="AA27">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB27">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AC27">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AD27">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE27">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF27">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AG27">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.22</v>
+        <v>2.2</v>
       </c>
       <c r="AK27">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O32">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P32">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="Q32">
         <v>2.66</v>
@@ -5573,7 +5573,7 @@
         <v>3.25</v>
       </c>
       <c r="AD32">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE32">
         <v>1.1</v>
@@ -5854,13 +5854,13 @@
         <v>2.1</v>
       </c>
       <c r="O34">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P34">
-        <v>3.16</v>
+        <v>2.95</v>
       </c>
       <c r="Q34">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="R34">
         <v>2.09</v>
@@ -5875,7 +5875,7 @@
         <v>2.88</v>
       </c>
       <c r="V34">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W34">
         <v>1.07</v>
@@ -5890,16 +5890,16 @@
         <v>2.5</v>
       </c>
       <c r="AA34">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AB34">
         <v>1.58</v>
       </c>
       <c r="AC34">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AD34">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE34">
         <v>1.07</v>
@@ -6029,7 +6029,7 @@
         <v>2.2</v>
       </c>
       <c r="S35">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T35">
         <v>2.76</v>
@@ -6047,10 +6047,10 @@
         <v>1.03</v>
       </c>
       <c r="Y35">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z35">
-        <v>3.65</v>
+        <v>3.71</v>
       </c>
       <c r="AA35">
         <v>1.86</v>
@@ -6062,7 +6062,7 @@
         <v>3.05</v>
       </c>
       <c r="AD35">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE35">
         <v>1.07</v>
@@ -6349,7 +6349,7 @@
         <v>4.2</v>
       </c>
       <c r="Q37">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="R37">
         <v>2.4</v>
@@ -6358,16 +6358,16 @@
         <v>1.25</v>
       </c>
       <c r="T37">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="U37">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V37">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W37">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X37">
         <v>1.02</v>
@@ -6382,13 +6382,13 @@
         <v>1.44</v>
       </c>
       <c r="AB37">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AC37">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AD37">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AE37">
         <v>1.22</v>
@@ -6515,10 +6515,10 @@
         <v>4.33</v>
       </c>
       <c r="R38">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="S38">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T38">
         <v>3.1</v>
@@ -6687,7 +6687,7 @@
         <v>3.3</v>
       </c>
       <c r="U39">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="V39">
         <v>1.53</v>
@@ -6699,19 +6699,19 @@
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z39">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA39">
         <v>1.61</v>
       </c>
       <c r="AB39">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AC39">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AD39">
         <v>1.45</v>
@@ -7013,7 +7013,7 @@
         <v>3.4</v>
       </c>
       <c r="U41">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="V41">
         <v>1.56</v>
@@ -7028,7 +7028,7 @@
         <v>1.15</v>
       </c>
       <c r="Z41">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="AA41">
         <v>1.57</v>
@@ -7037,7 +7037,7 @@
         <v>2.2</v>
       </c>
       <c r="AC41">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="AD41">
         <v>1.5</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="O42">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P42">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="Q42">
         <v>2.4</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O44">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="P44">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="O45">
-        <v>7.54</v>
+        <v>6.75</v>
       </c>
       <c r="P45">
-        <v>13.7</v>
+        <v>13.5</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -7683,10 +7683,10 @@
         <v>0</v>
       </c>
       <c r="AA45">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB45">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AC45">
         <v>0</v>
@@ -7843,7 +7843,7 @@
         <v>1.14</v>
       </c>
       <c r="Z46">
-        <v>5.87</v>
+        <v>5.92</v>
       </c>
       <c r="AA46">
         <v>1.41</v>
@@ -7970,7 +7970,7 @@
         </is>
       </c>
       <c r="N47">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="O47">
         <v>4.5</v>
@@ -8136,7 +8136,7 @@
         <v>2.75</v>
       </c>
       <c r="O48">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="P48">
         <v>2.2</v>
@@ -8154,10 +8154,10 @@
         <v>3.38</v>
       </c>
       <c r="U48">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V48">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W48">
         <v>1.11</v>
@@ -8314,10 +8314,10 @@
         <v>1.29</v>
       </c>
       <c r="T49">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="U49">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="V49">
         <v>1.52</v>
@@ -8332,28 +8332,28 @@
         <v>1.18</v>
       </c>
       <c r="Z49">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AA49">
         <v>1.6</v>
       </c>
       <c r="AB49">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AC49">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AD49">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE49">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF49">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG49">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK49">
         <v>1.55</v>
@@ -8480,10 +8480,10 @@
         <v>3.4</v>
       </c>
       <c r="U50">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="V50">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W50">
         <v>1.1</v>
@@ -8513,7 +8513,7 @@
         <v>1.14</v>
       </c>
       <c r="AF50">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG50">
         <v>2.15</v>
@@ -9114,7 +9114,7 @@
         <v>2.9</v>
       </c>
       <c r="O54">
-        <v>3.83</v>
+        <v>3.88</v>
       </c>
       <c r="P54">
         <v>2.2</v>
@@ -9141,7 +9141,7 @@
         <v>1.15</v>
       </c>
       <c r="X54">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y54">
         <v>1.08</v>
@@ -9165,7 +9165,7 @@
         <v>1.26</v>
       </c>
       <c r="AF54">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AG54">
         <v>2.8</v>
@@ -9277,7 +9277,7 @@
         <v>3.16</v>
       </c>
       <c r="O55">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="P55">
         <v>2</v>
@@ -9292,13 +9292,13 @@
         <v>1.14</v>
       </c>
       <c r="T55">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="U55">
         <v>2.04</v>
       </c>
       <c r="V55">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="W55">
         <v>1.18</v>
@@ -9316,13 +9316,13 @@
         <v>1.3</v>
       </c>
       <c r="AB55">
-        <v>3.17</v>
+        <v>3.22</v>
       </c>
       <c r="AC55">
         <v>1.82</v>
       </c>
       <c r="AD55">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AE55">
         <v>1.38</v>
@@ -9642,7 +9642,7 @@
         <v>1.44</v>
       </c>
       <c r="AB57">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="AC57">
         <v>2.07</v>
@@ -9657,7 +9657,7 @@
         <v>1.4</v>
       </c>
       <c r="AG57">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>1.91</v>
       </c>
       <c r="AK57">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,19 +9763,19 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="O58">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P58">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="Q58">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="R58">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="S58">
         <v>1.28</v>
@@ -9790,7 +9790,7 @@
         <v>1.45</v>
       </c>
       <c r="W58">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X58">
         <v>1</v>
@@ -9805,13 +9805,13 @@
         <v>1.69</v>
       </c>
       <c r="AB58">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AC58">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="AD58">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE58">
         <v>1.12</v>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK58">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10297,7 +10297,7 @@
         <v>2.42</v>
       </c>
       <c r="AC61">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="AD61">
         <v>1.59</v>
@@ -11076,7 +11076,7 @@
         <v>2.91</v>
       </c>
       <c r="Q66">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="R66">
         <v>2.15</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.73</v>
+        <v>2.55</v>
       </c>
       <c r="O67">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="P67">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q67">
-        <v>2.25</v>
+        <v>3.2</v>
       </c>
       <c r="R67">
-        <v>2.24</v>
+        <v>2.05</v>
       </c>
       <c r="S67">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T67">
-        <v>3.46</v>
+        <v>2.93</v>
       </c>
       <c r="U67">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="V67">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="W67">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="X67">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="Z67">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA67">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AB67">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="AC67">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AD67">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AE67">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF67">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AG67">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="AK67">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11405,7 +11405,7 @@
         <v>2.79</v>
       </c>
       <c r="R68">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S68">
         <v>1.36</v>
@@ -11595,7 +11595,7 @@
         <v>2.85</v>
       </c>
       <c r="AA69">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AB69">
         <v>1.61</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,80 +11719,80 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.55</v>
+        <v>1.75</v>
       </c>
       <c r="O70">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P70">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="Q70">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="R70">
+        <v>2.24</v>
+      </c>
+      <c r="S70">
+        <v>1.32</v>
+      </c>
+      <c r="T70">
+        <v>3.46</v>
+      </c>
+      <c r="U70">
+        <v>2.5</v>
+      </c>
+      <c r="V70">
+        <v>1.52</v>
+      </c>
+      <c r="W70">
+        <v>1.11</v>
+      </c>
+      <c r="X70">
+        <v>1.02</v>
+      </c>
+      <c r="Y70">
+        <v>1.2</v>
+      </c>
+      <c r="Z70">
+        <v>4.4</v>
+      </c>
+      <c r="AA70">
+        <v>1.66</v>
+      </c>
+      <c r="AB70">
+        <v>2.12</v>
+      </c>
+      <c r="AC70">
+        <v>2.75</v>
+      </c>
+      <c r="AD70">
+        <v>1.43</v>
+      </c>
+      <c r="AE70">
+        <v>1.14</v>
+      </c>
+      <c r="AF70">
+        <v>1.62</v>
+      </c>
+      <c r="AG70">
+        <v>2.15</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ70">
+        <v>1.13</v>
+      </c>
+      <c r="AK70">
         <v>2.1</v>
-      </c>
-      <c r="S70">
-        <v>1.37</v>
-      </c>
-      <c r="T70">
-        <v>2.93</v>
-      </c>
-      <c r="U70">
-        <v>2.68</v>
-      </c>
-      <c r="V70">
-        <v>1.36</v>
-      </c>
-      <c r="W70">
-        <v>1.04</v>
-      </c>
-      <c r="X70">
-        <v>1</v>
-      </c>
-      <c r="Y70">
-        <v>1.31</v>
-      </c>
-      <c r="Z70">
-        <v>3.25</v>
-      </c>
-      <c r="AA70">
-        <v>2</v>
-      </c>
-      <c r="AB70">
-        <v>1.81</v>
-      </c>
-      <c r="AC70">
-        <v>3.6</v>
-      </c>
-      <c r="AD70">
-        <v>1.25</v>
-      </c>
-      <c r="AE70">
-        <v>1.1</v>
-      </c>
-      <c r="AF70">
-        <v>1.72</v>
-      </c>
-      <c r="AG70">
-        <v>2</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ70">
-        <v>1.4</v>
-      </c>
-      <c r="AK70">
-        <v>1.5</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -12045,19 +12045,19 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="O72">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="P72">
         <v>4.6</v>
       </c>
       <c r="Q72">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="R72">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="S72">
         <v>1.22</v>
@@ -12072,7 +12072,7 @@
         <v>1.72</v>
       </c>
       <c r="W72">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X72">
         <v>1.02</v>
@@ -12090,10 +12090,10 @@
         <v>2.88</v>
       </c>
       <c r="AC72">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AD72">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AE72">
         <v>1.3</v>
@@ -12102,7 +12102,7 @@
         <v>1.44</v>
       </c>
       <c r="AG72">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>1.22</v>
       </c>
       <c r="AK72">
-        <v>2.15</v>
+        <v>2.27</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="O73">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="P73">
-        <v>1.95</v>
+        <v>1.47</v>
       </c>
       <c r="Q73">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R73">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="S73">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T73">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="U73">
-        <v>2.21</v>
+        <v>1.97</v>
       </c>
       <c r="V73">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="W73">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X73">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z73">
-        <v>5.25</v>
+        <v>6.5</v>
       </c>
       <c r="AA73">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AB73">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="AC73">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="AD73">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="AE73">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AF73">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG73">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AK73">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="O74">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="P74">
-        <v>1.47</v>
+        <v>4.1</v>
       </c>
       <c r="Q74">
-        <v>5</v>
+        <v>2.15</v>
       </c>
       <c r="R74">
-        <v>2.49</v>
+        <v>2.8</v>
       </c>
       <c r="S74">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T74">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="U74">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="V74">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="W74">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="X74">
         <v>1.01</v>
       </c>
       <c r="Y74">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z74">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AA74">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB74">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AC74">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AD74">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="AE74">
         <v>1.33</v>
       </c>
       <c r="AF74">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AG74">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AK74">
-        <v>1.15</v>
+        <v>2.05</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="O75">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="P75">
-        <v>4.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q75">
-        <v>2.15</v>
+        <v>4</v>
       </c>
       <c r="R75">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="S75">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="T75">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="U75">
-        <v>1.95</v>
+        <v>2.21</v>
       </c>
       <c r="V75">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="W75">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="X75">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y75">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="Z75">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="AA75">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AB75">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="AC75">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AD75">
-        <v>1.86</v>
+        <v>1.58</v>
       </c>
       <c r="AE75">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AF75">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AG75">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK75">
-        <v>2.05</v>
+        <v>1.29</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="N80">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O80">
         <v>3.85</v>
@@ -13358,7 +13358,7 @@
         <v>1.71</v>
       </c>
       <c r="Q80">
-        <v>4.96</v>
+        <v>4.9</v>
       </c>
       <c r="R80">
         <v>2.25</v>
@@ -13367,13 +13367,13 @@
         <v>1.3</v>
       </c>
       <c r="T80">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="U80">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="V80">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W80">
         <v>1.07</v>
@@ -13419,7 +13419,7 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK80">
         <v>1.14</v>
@@ -14004,7 +14004,7 @@
         <v>2.7</v>
       </c>
       <c r="O84">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P84">
         <v>2.37</v>
@@ -14170,7 +14170,7 @@
         <v>4</v>
       </c>
       <c r="P85">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q85">
         <v>2.32</v>
@@ -14179,16 +14179,16 @@
         <v>2.48</v>
       </c>
       <c r="S85">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="T85">
         <v>4.5</v>
       </c>
       <c r="U85">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="V85">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="W85">
         <v>1.22</v>
@@ -14197,7 +14197,7 @@
         <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z85">
         <v>7.5</v>
@@ -14215,13 +14215,13 @@
         <v>1.9</v>
       </c>
       <c r="AE85">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AF85">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AG85">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK85">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14659,7 +14659,7 @@
         <v>3.75</v>
       </c>
       <c r="P88">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -14668,10 +14668,10 @@
         <v>2.26</v>
       </c>
       <c r="S88">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T88">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="U88">
         <v>2.38</v>
@@ -14695,7 +14695,7 @@
         <v>1.72</v>
       </c>
       <c r="AB88">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AC88">
         <v>2.69</v>
@@ -14723,7 +14723,7 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.24</v>
+        <v>2.08</v>
       </c>
       <c r="AK88">
         <v>1.21</v>
@@ -14816,19 +14816,19 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="O89">
         <v>4.6</v>
       </c>
       <c r="P89">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="Q89">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R89">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="S89">
         <v>1.17</v>
@@ -14846,7 +14846,7 @@
         <v>1.17</v>
       </c>
       <c r="X89">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y89">
         <v>1.1</v>
@@ -14855,7 +14855,7 @@
         <v>5.2</v>
       </c>
       <c r="AA89">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB89">
         <v>2.7</v>
@@ -14889,7 +14889,7 @@
         <v>1.2</v>
       </c>
       <c r="AK89">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14988,52 +14988,52 @@
         <v>2.15</v>
       </c>
       <c r="Q90">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R90">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="S90">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T90">
-        <v>2.82</v>
+        <v>3.02</v>
       </c>
       <c r="U90">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="V90">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W90">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X90">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y90">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z90">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AA90">
+        <v>1.86</v>
+      </c>
+      <c r="AB90">
         <v>1.82</v>
       </c>
-      <c r="AB90">
-        <v>2.06</v>
-      </c>
       <c r="AC90">
-        <v>2.97</v>
+        <v>3.32</v>
       </c>
       <c r="AD90">
         <v>1.3</v>
       </c>
       <c r="AE90">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF90">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG90">
         <v>2.1</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,80 +15142,80 @@
         </is>
       </c>
       <c r="N91">
-        <v>5.72</v>
+        <v>3.1</v>
       </c>
       <c r="O91">
-        <v>4.75</v>
+        <v>3.35</v>
       </c>
       <c r="P91">
-        <v>1.38</v>
+        <v>2</v>
       </c>
       <c r="Q91">
-        <v>4.25</v>
+        <v>3.9</v>
       </c>
       <c r="R91">
-        <v>2.62</v>
+        <v>2.16</v>
       </c>
       <c r="S91">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="T91">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="U91">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="V91">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="W91">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X91">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y91">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="Z91">
-        <v>5.67</v>
+        <v>3.7</v>
       </c>
       <c r="AA91">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AB91">
+        <v>2</v>
+      </c>
+      <c r="AC91">
         <v>2.88</v>
       </c>
-      <c r="AC91">
-        <v>2.15</v>
-      </c>
       <c r="AD91">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="AE91">
+        <v>1.08</v>
+      </c>
+      <c r="AF91">
+        <v>1.62</v>
+      </c>
+      <c r="AG91">
+        <v>2.2</v>
+      </c>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ91">
         <v>1.29</v>
       </c>
-      <c r="AF91">
-        <v>1.55</v>
-      </c>
-      <c r="AG91">
-        <v>2.25</v>
-      </c>
-      <c r="AH91" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI91" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ91">
-        <v>2.8</v>
-      </c>
       <c r="AK91">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15308,31 +15308,31 @@
         <v>2.7</v>
       </c>
       <c r="O92">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P92">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="Q92">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="R92">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="S92">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T92">
         <v>3.5</v>
       </c>
       <c r="U92">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="V92">
         <v>1.57</v>
       </c>
       <c r="W92">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X92">
         <v>1.01</v>
@@ -15341,19 +15341,19 @@
         <v>1.17</v>
       </c>
       <c r="Z92">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AA92">
         <v>1.57</v>
       </c>
       <c r="AB92">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="AC92">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="AD92">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AE92">
         <v>1.2</v>
@@ -15362,7 +15362,7 @@
         <v>1.53</v>
       </c>
       <c r="AG92">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK92">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15468,19 +15468,19 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="O93">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P93">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="Q93">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="R93">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="S93">
         <v>1.22</v>
@@ -15513,7 +15513,7 @@
         <v>2.55</v>
       </c>
       <c r="AC93">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AD93">
         <v>1.6</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,80 +15631,80 @@
         </is>
       </c>
       <c r="N94">
-        <v>3.15</v>
+        <v>5.75</v>
       </c>
       <c r="O94">
-        <v>3.55</v>
+        <v>4.7</v>
       </c>
       <c r="P94">
-        <v>1.92</v>
+        <v>1.38</v>
       </c>
       <c r="Q94">
-        <v>3.9</v>
+        <v>4.25</v>
       </c>
       <c r="R94">
-        <v>2.16</v>
+        <v>2.62</v>
       </c>
       <c r="S94">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="T94">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="U94">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="V94">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="W94">
+        <v>1.17</v>
+      </c>
+      <c r="X94">
+        <v>1.01</v>
+      </c>
+      <c r="Y94">
+        <v>1.13</v>
+      </c>
+      <c r="Z94">
+        <v>5.67</v>
+      </c>
+      <c r="AA94">
+        <v>1.4</v>
+      </c>
+      <c r="AB94">
+        <v>2.75</v>
+      </c>
+      <c r="AC94">
+        <v>2.15</v>
+      </c>
+      <c r="AD94">
+        <v>1.67</v>
+      </c>
+      <c r="AE94">
+        <v>1.29</v>
+      </c>
+      <c r="AF94">
+        <v>1.55</v>
+      </c>
+      <c r="AG94">
+        <v>2.25</v>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ94">
+        <v>2.75</v>
+      </c>
+      <c r="AK94">
         <v>1.11</v>
-      </c>
-      <c r="X94">
-        <v>1.03</v>
-      </c>
-      <c r="Y94">
-        <v>1.2</v>
-      </c>
-      <c r="Z94">
-        <v>3.7</v>
-      </c>
-      <c r="AA94">
-        <v>1.76</v>
-      </c>
-      <c r="AB94">
-        <v>1.98</v>
-      </c>
-      <c r="AC94">
-        <v>2.88</v>
-      </c>
-      <c r="AD94">
-        <v>1.41</v>
-      </c>
-      <c r="AE94">
-        <v>1.08</v>
-      </c>
-      <c r="AF94">
-        <v>1.62</v>
-      </c>
-      <c r="AG94">
-        <v>2.2</v>
-      </c>
-      <c r="AH94" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI94" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ94">
-        <v>1.29</v>
-      </c>
-      <c r="AK94">
-        <v>1.3</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15794,19 +15794,19 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="O95">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P95">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q95">
-        <v>3.42</v>
+        <v>3.1</v>
       </c>
       <c r="R95">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="S95">
         <v>1.25</v>
@@ -15815,43 +15815,43 @@
         <v>3.5</v>
       </c>
       <c r="U95">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="V95">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W95">
         <v>1.12</v>
       </c>
       <c r="X95">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y95">
+        <v>1.14</v>
+      </c>
+      <c r="Z95">
+        <v>5</v>
+      </c>
+      <c r="AA95">
+        <v>1.57</v>
+      </c>
+      <c r="AB95">
+        <v>2.33</v>
+      </c>
+      <c r="AC95">
+        <v>2.63</v>
+      </c>
+      <c r="AD95">
+        <v>1.44</v>
+      </c>
+      <c r="AE95">
         <v>1.2</v>
-      </c>
-      <c r="Z95">
-        <v>4.5</v>
-      </c>
-      <c r="AA95">
-        <v>1.6</v>
-      </c>
-      <c r="AB95">
-        <v>2.18</v>
-      </c>
-      <c r="AC95">
-        <v>2.46</v>
-      </c>
-      <c r="AD95">
-        <v>1.43</v>
-      </c>
-      <c r="AE95">
-        <v>1.14</v>
       </c>
       <c r="AF95">
         <v>1.5</v>
       </c>
       <c r="AG95">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.29</v>
+        <v>1.47</v>
       </c>
       <c r="AK95">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15972,19 +15972,19 @@
         <v>2.3</v>
       </c>
       <c r="S96">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T96">
         <v>3.48</v>
       </c>
       <c r="U96">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="V96">
         <v>1.67</v>
       </c>
       <c r="W96">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X96">
         <v>1.02</v>
@@ -16129,10 +16129,10 @@
         <v>2.4</v>
       </c>
       <c r="Q97">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="R97">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="S97">
         <v>1.25</v>
@@ -16150,7 +16150,7 @@
         <v>1.11</v>
       </c>
       <c r="X97">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y97">
         <v>1.13</v>
@@ -16159,16 +16159,16 @@
         <v>4.55</v>
       </c>
       <c r="AA97">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AB97">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AC97">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AD97">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AE97">
         <v>1.15</v>
@@ -16193,7 +16193,7 @@
         <v>1.22</v>
       </c>
       <c r="AK97">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16283,22 +16283,22 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="O98">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P98">
-        <v>5.15</v>
+        <v>5</v>
       </c>
       <c r="Q98">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="R98">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="S98">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T98">
         <v>3.08</v>
@@ -16319,10 +16319,10 @@
         <v>1.2</v>
       </c>
       <c r="Z98">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA98">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AB98">
         <v>2.02</v>
@@ -16331,7 +16331,7 @@
         <v>2.74</v>
       </c>
       <c r="AD98">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE98">
         <v>1.11</v>
@@ -16340,7 +16340,7 @@
         <v>1.75</v>
       </c>
       <c r="AG98">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -17608,10 +17608,10 @@
         <v>4.3</v>
       </c>
       <c r="U106">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="V106">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="W106">
         <v>1.2</v>
@@ -17629,7 +17629,7 @@
         <v>1.33</v>
       </c>
       <c r="AB106">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="AC106">
         <v>1.97</v>
@@ -17913,31 +17913,31 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="O108">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P108">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="Q108">
-        <v>2.34</v>
+        <v>2.15</v>
       </c>
       <c r="R108">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="S108">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T108">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U108">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="V108">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W108">
         <v>1.13</v>
@@ -17946,31 +17946,31 @@
         <v>1.01</v>
       </c>
       <c r="Y108">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z108">
-        <v>4.55</v>
+        <v>4.8</v>
       </c>
       <c r="AA108">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AB108">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="AC108">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="AD108">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AE108">
         <v>1.18</v>
       </c>
       <c r="AF108">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG108">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK108">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="O110">
-        <v>4.15</v>
+        <v>3.96</v>
       </c>
       <c r="P110">
-        <v>4.96</v>
+        <v>4.2</v>
       </c>
       <c r="Q110">
         <v>0</v>
@@ -18574,34 +18574,34 @@
         <v>2.75</v>
       </c>
       <c r="Q112">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R112">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S112">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T112">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U112">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V112">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W112">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X112">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z112">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA112">
         <v>1.53</v>
@@ -18610,19 +18610,19 @@
         <v>2.37</v>
       </c>
       <c r="AC112">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD112">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE112">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF112">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG112">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK112">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL112">
         <v>0</v>

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -961,37 +961,37 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="O4">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P4">
-        <v>3.9</v>
+        <v>4.41</v>
       </c>
       <c r="Q4">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="R4">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S4">
+        <v>1.35</v>
+      </c>
+      <c r="T4">
+        <v>2.88</v>
+      </c>
+      <c r="U4">
+        <v>2.89</v>
+      </c>
+      <c r="V4">
         <v>1.36</v>
       </c>
-      <c r="T4">
-        <v>3</v>
-      </c>
-      <c r="U4">
-        <v>2.74</v>
-      </c>
-      <c r="V4">
-        <v>1.4</v>
-      </c>
       <c r="W4">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
         <v>1.37</v>
@@ -1000,10 +1000,10 @@
         <v>2.77</v>
       </c>
       <c r="AA4">
+        <v>1.88</v>
+      </c>
+      <c r="AB4">
         <v>1.9</v>
-      </c>
-      <c r="AB4">
-        <v>1.88</v>
       </c>
       <c r="AC4">
         <v>3.4</v>
@@ -1649,7 +1649,7 @@
         <v>1.73</v>
       </c>
       <c r="Z8">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AA8">
         <v>3.3</v>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Halaba Ketema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.75</v>
+        <v>3.3</v>
       </c>
       <c r="O9">
-        <v>3.45</v>
+        <v>2.45</v>
       </c>
       <c r="P9">
-        <v>3.66</v>
+        <v>2.4</v>
       </c>
       <c r="Q9">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="R9">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W9">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y9">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z9">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <v>1.93</v>
+        <v>3.25</v>
       </c>
       <c r="AB9">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="AC9">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD9">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK9">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.59</v>
+        <v>1.53</v>
       </c>
       <c r="O10">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="P10">
-        <v>2.19</v>
+        <v>4.9</v>
       </c>
       <c r="Q10">
-        <v>3.28</v>
+        <v>2</v>
       </c>
       <c r="R10">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S10">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T10">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U10">
-        <v>2.65</v>
+        <v>2.76</v>
       </c>
       <c r="V10">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W10">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
+        <v>1.28</v>
+      </c>
+      <c r="Z10">
+        <v>3.08</v>
+      </c>
+      <c r="AA10">
+        <v>1.93</v>
+      </c>
+      <c r="AB10">
+        <v>1.75</v>
+      </c>
+      <c r="AC10">
+        <v>3.3</v>
+      </c>
+      <c r="AD10">
         <v>1.25</v>
-      </c>
-      <c r="Z10">
-        <v>3.6</v>
-      </c>
-      <c r="AA10">
-        <v>1.88</v>
-      </c>
-      <c r="AB10">
-        <v>1.88</v>
-      </c>
-      <c r="AC10">
-        <v>2.97</v>
-      </c>
-      <c r="AD10">
-        <v>1.3</v>
       </c>
       <c r="AE10">
         <v>1.08</v>
       </c>
       <c r="AF10">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AG10">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK10">
-        <v>1.4</v>
+        <v>1.86</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.9</v>
+        <v>2.59</v>
       </c>
       <c r="O11">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="P11">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA11">
-        <v>1.61</v>
+        <v>1.88</v>
       </c>
       <c r="AB11">
-        <v>2.25</v>
+        <v>1.88</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Adhyaksa</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.83</v>
+        <v>2.9</v>
       </c>
       <c r="O12">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P12">
-        <v>3.8</v>
+        <v>2.25</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2304,10 +2304,10 @@
         <v>0</v>
       </c>
       <c r="AA12">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AB12">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AC12">
         <v>0</v>
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Adhyaksa</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.35</v>
+        <v>1.83</v>
       </c>
       <c r="O13">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P13">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="Q13">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R13">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S13">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T13">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U13">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V13">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W13">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X13">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y13">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z13">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AA13">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB13">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AC13">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AD13">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE13">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF13">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG13">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK13">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-10-16 10:00:00</t>
+          <t>2026-10-16 09:00:00</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,80 +2591,80 @@
         </is>
       </c>
       <c r="N14">
+        <v>2.4</v>
+      </c>
+      <c r="O14">
+        <v>3.3</v>
+      </c>
+      <c r="P14">
         <v>2.5</v>
       </c>
-      <c r="O14">
-        <v>3.45</v>
-      </c>
-      <c r="P14">
-        <v>2.45</v>
-      </c>
       <c r="Q14">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="R14">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="S14">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T14">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U14">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="V14">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W14">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X14">
         <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z14">
-        <v>4.33</v>
+        <v>3.86</v>
       </c>
       <c r="AA14">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="AB14">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AC14">
-        <v>2.49</v>
+        <v>2.66</v>
       </c>
       <c r="AD14">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AE14">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF14">
+        <v>1.55</v>
+      </c>
+      <c r="AG14">
+        <v>2.3</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14">
+        <v>1.24</v>
+      </c>
+      <c r="AK14">
         <v>1.5</v>
-      </c>
-      <c r="AG14">
-        <v>2.36</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14">
-        <v>1.53</v>
-      </c>
-      <c r="AK14">
-        <v>1.4</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.35</v>
+        <v>2.45</v>
       </c>
       <c r="O15">
-        <v>4.7</v>
+        <v>3.45</v>
       </c>
       <c r="P15">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q15">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="R15">
-        <v>2.6</v>
+        <v>2.24</v>
       </c>
       <c r="S15">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T15">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="U15">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="V15">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="W15">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X15">
         <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z15">
-        <v>4.95</v>
+        <v>4.33</v>
       </c>
       <c r="AA15">
-        <v>1.48</v>
+        <v>1.66</v>
       </c>
       <c r="AB15">
-        <v>2.55</v>
+        <v>2.17</v>
       </c>
       <c r="AC15">
-        <v>2.22</v>
+        <v>2.49</v>
       </c>
       <c r="AD15">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="AE15">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AF15">
-        <v>1.73</v>
+        <v>1.49</v>
       </c>
       <c r="AG15">
-        <v>2</v>
+        <v>2.39</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="AK15">
-        <v>3.1</v>
+        <v>1.44</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2923,16 +2923,16 @@
         <v>3.3</v>
       </c>
       <c r="P16">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="Q16">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="R16">
         <v>2.08</v>
       </c>
       <c r="S16">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T16">
         <v>2.95</v>
@@ -2947,7 +2947,7 @@
         <v>1.1</v>
       </c>
       <c r="X16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y16">
         <v>1.22</v>
@@ -2990,7 +2990,7 @@
         <v>1.24</v>
       </c>
       <c r="AK16">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.77</v>
+        <v>1.35</v>
       </c>
       <c r="O17">
-        <v>3.65</v>
+        <v>4.7</v>
       </c>
       <c r="P17">
-        <v>3.85</v>
+        <v>7.5</v>
       </c>
       <c r="Q17">
-        <v>2.28</v>
+        <v>1.75</v>
       </c>
       <c r="R17">
-        <v>2.22</v>
+        <v>2.6</v>
       </c>
       <c r="S17">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="T17">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="U17">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="V17">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="W17">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X17">
         <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="Z17">
-        <v>3.92</v>
+        <v>4.95</v>
       </c>
       <c r="AA17">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="AB17">
-        <v>2.04</v>
+        <v>2.55</v>
       </c>
       <c r="AC17">
-        <v>2.66</v>
+        <v>2.22</v>
       </c>
       <c r="AD17">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="AE17">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AF17">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AG17">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AK17">
-        <v>1.87</v>
+        <v>3.1</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kelantan Red Warrior</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>6.25</v>
+        <v>1.77</v>
       </c>
       <c r="O18">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="P18">
-        <v>1.4</v>
+        <v>3.85</v>
       </c>
       <c r="Q18">
-        <v>6.72</v>
+        <v>2.28</v>
       </c>
       <c r="R18">
-        <v>2.8</v>
+        <v>2.22</v>
       </c>
       <c r="S18">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="T18">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="U18">
-        <v>2.02</v>
+        <v>2.45</v>
       </c>
       <c r="V18">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="W18">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="Z18">
-        <v>5.55</v>
+        <v>3.92</v>
       </c>
       <c r="AA18">
-        <v>1.39</v>
+        <v>1.7</v>
       </c>
       <c r="AB18">
-        <v>2.59</v>
+        <v>2.1</v>
       </c>
       <c r="AC18">
-        <v>2.01</v>
+        <v>2.66</v>
       </c>
       <c r="AD18">
-        <v>1.69</v>
+        <v>1.37</v>
       </c>
       <c r="AE18">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="AF18">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AG18">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AK18">
-        <v>1.02</v>
+        <v>1.87</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Halaba Ketema</t>
+          <t>Kelantan Red Warrior</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.3</v>
+        <v>6.25</v>
       </c>
       <c r="O19">
-        <v>2.45</v>
+        <v>4.5</v>
       </c>
       <c r="P19">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>6.72</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA19">
-        <v>3.25</v>
+        <v>1.39</v>
       </c>
       <c r="AB19">
-        <v>1.33</v>
+        <v>2.59</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,58 +3569,58 @@
         </is>
       </c>
       <c r="N20">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="O20">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P20">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="Q20">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="R20">
         <v>2.45</v>
       </c>
       <c r="S20">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T20">
         <v>3.9</v>
       </c>
       <c r="U20">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="V20">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W20">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X20">
         <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z20">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AA20">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AB20">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="AC20">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AD20">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AE20">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AF20">
         <v>1.4</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AK20">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4067,55 +4067,55 @@
         <v>3.05</v>
       </c>
       <c r="Q23">
+        <v>2.85</v>
+      </c>
+      <c r="R23">
+        <v>2</v>
+      </c>
+      <c r="S23">
+        <v>1.44</v>
+      </c>
+      <c r="T23">
+        <v>2.45</v>
+      </c>
+      <c r="U23">
+        <v>3.2</v>
+      </c>
+      <c r="V23">
+        <v>1.3</v>
+      </c>
+      <c r="W23">
+        <v>1.05</v>
+      </c>
+      <c r="X23">
+        <v>1.04</v>
+      </c>
+      <c r="Y23">
+        <v>1.36</v>
+      </c>
+      <c r="Z23">
         <v>2.75</v>
       </c>
-      <c r="R23">
-        <v>2.01</v>
-      </c>
-      <c r="S23">
-        <v>1.36</v>
-      </c>
-      <c r="T23">
-        <v>2.64</v>
-      </c>
-      <c r="U23">
-        <v>2.88</v>
-      </c>
-      <c r="V23">
-        <v>1.36</v>
-      </c>
-      <c r="W23">
-        <v>1.07</v>
-      </c>
-      <c r="X23">
+      <c r="AA23">
+        <v>2.21</v>
+      </c>
+      <c r="AB23">
+        <v>1.56</v>
+      </c>
+      <c r="AC23">
+        <v>4.25</v>
+      </c>
+      <c r="AD23">
+        <v>1.15</v>
+      </c>
+      <c r="AE23">
         <v>1.03</v>
       </c>
-      <c r="Y23">
-        <v>1.3</v>
-      </c>
-      <c r="Z23">
-        <v>3.1</v>
-      </c>
-      <c r="AA23">
-        <v>2.04</v>
-      </c>
-      <c r="AB23">
-        <v>1.67</v>
-      </c>
-      <c r="AC23">
-        <v>3.7</v>
-      </c>
-      <c r="AD23">
-        <v>1.2</v>
-      </c>
-      <c r="AE23">
-        <v>1.05</v>
-      </c>
       <c r="AF23">
+        <v>1.91</v>
+      </c>
+      <c r="AG23">
         <v>1.75</v>
-      </c>
-      <c r="AG23">
-        <v>1.95</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>1.33</v>
       </c>
       <c r="AK23">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,31 +4221,31 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="O24">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P24">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="Q24">
-        <v>2.44</v>
+        <v>2.27</v>
       </c>
       <c r="R24">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S24">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T24">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="U24">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="V24">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W24">
         <v>1.06</v>
@@ -4254,10 +4254,10 @@
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z24">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="AA24">
         <v>1.91</v>
@@ -4266,7 +4266,7 @@
         <v>1.8</v>
       </c>
       <c r="AC24">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="AD24">
         <v>1.29</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK24">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="N28">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="O28">
         <v>3.15</v>
@@ -4882,7 +4882,7 @@
         <v>2.15</v>
       </c>
       <c r="Q28">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R28">
         <v>2.1</v>
@@ -4891,7 +4891,7 @@
         <v>1.36</v>
       </c>
       <c r="T28">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="U28">
         <v>2.88</v>
@@ -4906,13 +4906,13 @@
         <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z28">
         <v>2.97</v>
       </c>
       <c r="AA28">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AB28">
         <v>1.72</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AK28">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,65 +5036,65 @@
         </is>
       </c>
       <c r="N29">
-        <v>7</v>
+        <v>7.75</v>
       </c>
       <c r="O29">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="P29">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Q29">
         <v>7</v>
       </c>
       <c r="R29">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S29">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="T29">
-        <v>2.79</v>
+        <v>3.4</v>
       </c>
       <c r="U29">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="V29">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="W29">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X29">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y29">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="Z29">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="AA29">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AB29">
+        <v>2.18</v>
+      </c>
+      <c r="AC29">
+        <v>2.31</v>
+      </c>
+      <c r="AD29">
+        <v>1.48</v>
+      </c>
+      <c r="AE29">
+        <v>1.17</v>
+      </c>
+      <c r="AF29">
+        <v>1.83</v>
+      </c>
+      <c r="AG29">
         <v>1.91</v>
       </c>
-      <c r="AC29">
-        <v>2.9</v>
-      </c>
-      <c r="AD29">
-        <v>1.33</v>
-      </c>
-      <c r="AE29">
-        <v>1.09</v>
-      </c>
-      <c r="AF29">
-        <v>2</v>
-      </c>
-      <c r="AG29">
-        <v>1.75</v>
-      </c>
       <c r="AH29" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK29">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,25 +5199,25 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="O30">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="P30">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="Q30">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="R30">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="S30">
         <v>1.5</v>
       </c>
       <c r="T30">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="U30">
         <v>3.5</v>
@@ -5229,16 +5229,16 @@
         <v>1.05</v>
       </c>
       <c r="X30">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y30">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Z30">
-        <v>2.41</v>
+        <v>2.55</v>
       </c>
       <c r="AA30">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="AB30">
         <v>1.5</v>
@@ -5247,7 +5247,7 @@
         <v>4.75</v>
       </c>
       <c r="AD30">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AE30">
         <v>1.01</v>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK30">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5371,10 +5371,10 @@
         <v>2.53</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -5383,10 +5383,10 @@
         <v>0</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W31">
         <v>0</v>
@@ -5395,25 +5395,25 @@
         <v>0</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>6.27</v>
       </c>
       <c r="AA31">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB31">
-        <v>2.37</v>
+        <v>2.8</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF31">
         <v>0</v>
@@ -5534,10 +5534,10 @@
         <v>2.75</v>
       </c>
       <c r="Q32">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="R32">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S32">
         <v>1.36</v>
@@ -5564,7 +5564,7 @@
         <v>3.8</v>
       </c>
       <c r="AA32">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB32">
         <v>1.93</v>
@@ -5573,7 +5573,7 @@
         <v>3.25</v>
       </c>
       <c r="AD32">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE32">
         <v>1.1</v>
@@ -5582,7 +5582,7 @@
         <v>1.62</v>
       </c>
       <c r="AG32">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5860,19 +5860,19 @@
         <v>2.95</v>
       </c>
       <c r="Q34">
-        <v>2.55</v>
+        <v>2.72</v>
       </c>
       <c r="R34">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="S34">
         <v>1.36</v>
       </c>
       <c r="T34">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="U34">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V34">
         <v>1.3</v>
@@ -5890,13 +5890,13 @@
         <v>2.5</v>
       </c>
       <c r="AA34">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AB34">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AC34">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="AD34">
         <v>1.18</v>
@@ -5908,7 +5908,7 @@
         <v>1.62</v>
       </c>
       <c r="AG34">
-        <v>1.73</v>
+        <v>1.97</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AK34">
         <v>1.66</v>
@@ -6014,19 +6014,19 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="O35">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="P35">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Q35">
         <v>2.19</v>
       </c>
       <c r="R35">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="S35">
         <v>1.33</v>
@@ -6035,40 +6035,40 @@
         <v>2.76</v>
       </c>
       <c r="U35">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V35">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W35">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X35">
         <v>1.03</v>
       </c>
       <c r="Y35">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z35">
-        <v>3.71</v>
+        <v>3.29</v>
       </c>
       <c r="AA35">
         <v>1.86</v>
       </c>
       <c r="AB35">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AC35">
         <v>3.05</v>
       </c>
       <c r="AD35">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE35">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF35">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AG35">
         <v>1.91</v>
@@ -6180,22 +6180,22 @@
         <v>2.75</v>
       </c>
       <c r="O36">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="P36">
         <v>2.6</v>
       </c>
       <c r="Q36">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="R36">
         <v>1.75</v>
       </c>
       <c r="S36">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="T36">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="U36">
         <v>3.68</v>
@@ -6352,16 +6352,16 @@
         <v>2.1</v>
       </c>
       <c r="R37">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S37">
         <v>1.25</v>
       </c>
       <c r="T37">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="U37">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="V37">
         <v>1.62</v>
@@ -6373,19 +6373,19 @@
         <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z37">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AA37">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AB37">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AC37">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AD37">
         <v>1.65</v>
@@ -6397,7 +6397,7 @@
         <v>1.62</v>
       </c>
       <c r="AG37">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AK37">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6530,16 +6530,16 @@
         <v>1.44</v>
       </c>
       <c r="W38">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X38">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y38">
         <v>1.22</v>
       </c>
       <c r="Z38">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA38">
         <v>1.8</v>
@@ -6551,10 +6551,10 @@
         <v>2.83</v>
       </c>
       <c r="AD38">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE38">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF38">
         <v>1.67</v>
@@ -6666,19 +6666,19 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="O39">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P39">
         <v>3.5</v>
       </c>
       <c r="Q39">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="R39">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="S39">
         <v>1.29</v>
@@ -6693,7 +6693,7 @@
         <v>1.53</v>
       </c>
       <c r="W39">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X39">
         <v>1.01</v>
@@ -6708,10 +6708,10 @@
         <v>1.61</v>
       </c>
       <c r="AB39">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC39">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AD39">
         <v>1.45</v>
@@ -6720,7 +6720,7 @@
         <v>1.15</v>
       </c>
       <c r="AF39">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG39">
         <v>2.3</v>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK39">
         <v>1.85</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O42">
         <v>3.1</v>
       </c>
       <c r="P42">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q42">
         <v>2.4</v>
@@ -7170,19 +7170,19 @@
         <v>1.91</v>
       </c>
       <c r="S42">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T42">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="U42">
-        <v>2.39</v>
+        <v>3</v>
       </c>
       <c r="V42">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W42">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X42">
         <v>1.03</v>
@@ -7194,16 +7194,16 @@
         <v>2.38</v>
       </c>
       <c r="AA42">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AB42">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="AC42">
-        <v>3</v>
+        <v>3.86</v>
       </c>
       <c r="AD42">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AE42">
         <v>1.03</v>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="AK42">
         <v>1.62</v>
@@ -7327,19 +7327,19 @@
         <v>2.7</v>
       </c>
       <c r="Q43">
-        <v>2.78</v>
+        <v>2.93</v>
       </c>
       <c r="R43">
         <v>2.1</v>
       </c>
       <c r="S43">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T43">
         <v>2.71</v>
       </c>
       <c r="U43">
-        <v>3.27</v>
+        <v>3.31</v>
       </c>
       <c r="V43">
         <v>1.33</v>
@@ -7351,19 +7351,19 @@
         <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Z43">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="AA43">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="AB43">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC43">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="AD43">
         <v>1.24</v>
@@ -7391,7 +7391,7 @@
         <v>1.26</v>
       </c>
       <c r="AK43">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7816,55 +7816,55 @@
         <v>3.05</v>
       </c>
       <c r="Q46">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="R46">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="S46">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T46">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="U46">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="V46">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="W46">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X46">
         <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z46">
-        <v>5.92</v>
+        <v>5.24</v>
       </c>
       <c r="AA46">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="AB46">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="AC46">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AD46">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="AE46">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AF46">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG46">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK46">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7979,10 +7979,10 @@
         <v>1.35</v>
       </c>
       <c r="Q47">
-        <v>7</v>
+        <v>7.54</v>
       </c>
       <c r="R47">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="S47">
         <v>1.25</v>
@@ -8015,10 +8015,10 @@
         <v>2.25</v>
       </c>
       <c r="AC47">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="AD47">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AE47">
         <v>1.2</v>
@@ -8136,25 +8136,25 @@
         <v>2.75</v>
       </c>
       <c r="O48">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P48">
         <v>2.2</v>
       </c>
       <c r="Q48">
-        <v>3.56</v>
+        <v>3.32</v>
       </c>
       <c r="R48">
         <v>2.3</v>
       </c>
       <c r="S48">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T48">
         <v>3.38</v>
       </c>
       <c r="U48">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="V48">
         <v>1.54</v>
@@ -8178,13 +8178,13 @@
         <v>2.25</v>
       </c>
       <c r="AC48">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="AD48">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AE48">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF48">
         <v>1.53</v>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.58</v>
+        <v>1.21</v>
       </c>
       <c r="AK48">
         <v>1.33</v>
@@ -8305,7 +8305,7 @@
         <v>3</v>
       </c>
       <c r="Q49">
-        <v>2.88</v>
+        <v>2.69</v>
       </c>
       <c r="R49">
         <v>2.25</v>
@@ -8314,7 +8314,7 @@
         <v>1.29</v>
       </c>
       <c r="T49">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="U49">
         <v>2.39</v>
@@ -8329,10 +8329,10 @@
         <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z49">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AA49">
         <v>1.6</v>
@@ -8347,7 +8347,7 @@
         <v>1.4</v>
       </c>
       <c r="AE49">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF49">
         <v>1.53</v>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK49">
         <v>1.55</v>
@@ -8486,16 +8486,16 @@
         <v>1.52</v>
       </c>
       <c r="W50">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y50">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z50">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AA50">
         <v>1.65</v>
@@ -8504,16 +8504,16 @@
         <v>2.1</v>
       </c>
       <c r="AC50">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AD50">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AE50">
         <v>1.14</v>
       </c>
       <c r="AF50">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG50">
         <v>2.15</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AK50">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
+        <v>2.89</v>
+      </c>
+      <c r="O52">
+        <v>3.4</v>
+      </c>
+      <c r="P52">
+        <v>2.2</v>
+      </c>
+      <c r="Q52">
+        <v>3.62</v>
+      </c>
+      <c r="R52">
+        <v>2.28</v>
+      </c>
+      <c r="S52">
+        <v>1.25</v>
+      </c>
+      <c r="T52">
+        <v>3.5</v>
+      </c>
+      <c r="U52">
+        <v>2.41</v>
+      </c>
+      <c r="V52">
+        <v>1.56</v>
+      </c>
+      <c r="W52">
+        <v>1.15</v>
+      </c>
+      <c r="X52">
+        <v>1.03</v>
+      </c>
+      <c r="Y52">
+        <v>1.14</v>
+      </c>
+      <c r="Z52">
+        <v>4.35</v>
+      </c>
+      <c r="AA52">
+        <v>1.61</v>
+      </c>
+      <c r="AB52">
+        <v>2.31</v>
+      </c>
+      <c r="AC52">
+        <v>2.56</v>
+      </c>
+      <c r="AD52">
+        <v>1.44</v>
+      </c>
+      <c r="AE52">
+        <v>1.19</v>
+      </c>
+      <c r="AF52">
         <v>1.53</v>
       </c>
-      <c r="O52">
-        <v>4.4</v>
-      </c>
-      <c r="P52">
-        <v>4.6</v>
-      </c>
-      <c r="Q52">
-        <v>1.95</v>
-      </c>
-      <c r="R52">
-        <v>2.6</v>
-      </c>
-      <c r="S52">
-        <v>1.2</v>
-      </c>
-      <c r="T52">
-        <v>4.1</v>
-      </c>
-      <c r="U52">
-        <v>2</v>
-      </c>
-      <c r="V52">
-        <v>1.73</v>
-      </c>
-      <c r="W52">
-        <v>1.18</v>
-      </c>
-      <c r="X52">
-        <v>1.01</v>
-      </c>
-      <c r="Y52">
-        <v>1.08</v>
-      </c>
-      <c r="Z52">
-        <v>5.45</v>
-      </c>
-      <c r="AA52">
-        <v>1.4</v>
-      </c>
-      <c r="AB52">
-        <v>2.88</v>
-      </c>
-      <c r="AC52">
-        <v>2</v>
-      </c>
-      <c r="AD52">
-        <v>1.71</v>
-      </c>
-      <c r="AE52">
-        <v>1.29</v>
-      </c>
-      <c r="AF52">
-        <v>1.5</v>
-      </c>
       <c r="AG52">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AK52">
-        <v>2.4</v>
+        <v>1.35</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,80 +8948,80 @@
         </is>
       </c>
       <c r="N53">
-        <v>3</v>
+        <v>1.53</v>
       </c>
       <c r="O53">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="P53">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="Q53">
-        <v>3.62</v>
+        <v>1.85</v>
       </c>
       <c r="R53">
-        <v>2.28</v>
+        <v>2.62</v>
       </c>
       <c r="S53">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T53">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="U53">
-        <v>2.41</v>
+        <v>2</v>
       </c>
       <c r="V53">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="W53">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X53">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y53">
+        <v>1.08</v>
+      </c>
+      <c r="Z53">
+        <v>5.45</v>
+      </c>
+      <c r="AA53">
+        <v>1.4</v>
+      </c>
+      <c r="AB53">
+        <v>2.88</v>
+      </c>
+      <c r="AC53">
+        <v>2</v>
+      </c>
+      <c r="AD53">
+        <v>1.71</v>
+      </c>
+      <c r="AE53">
+        <v>1.29</v>
+      </c>
+      <c r="AF53">
+        <v>1.5</v>
+      </c>
+      <c r="AG53">
+        <v>2.45</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ53">
         <v>1.14</v>
       </c>
-      <c r="Z53">
-        <v>4.35</v>
-      </c>
-      <c r="AA53">
-        <v>1.61</v>
-      </c>
-      <c r="AB53">
-        <v>2.31</v>
-      </c>
-      <c r="AC53">
-        <v>2.56</v>
-      </c>
-      <c r="AD53">
-        <v>1.44</v>
-      </c>
-      <c r="AE53">
-        <v>1.19</v>
-      </c>
-      <c r="AF53">
-        <v>1.53</v>
-      </c>
-      <c r="AG53">
-        <v>2.39</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ53">
-        <v>1.24</v>
-      </c>
       <c r="AK53">
-        <v>1.35</v>
+        <v>2.4</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9114,34 +9114,34 @@
         <v>2.9</v>
       </c>
       <c r="O54">
-        <v>3.88</v>
+        <v>3.93</v>
       </c>
       <c r="P54">
         <v>2.2</v>
       </c>
       <c r="Q54">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="R54">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S54">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T54">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="U54">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="V54">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="W54">
         <v>1.15</v>
       </c>
       <c r="X54">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
         <v>1.08</v>
@@ -9156,16 +9156,16 @@
         <v>2.66</v>
       </c>
       <c r="AC54">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="AD54">
         <v>1.72</v>
       </c>
       <c r="AE54">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AF54">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG54">
         <v>2.8</v>
@@ -9184,7 +9184,7 @@
         <v>1.23</v>
       </c>
       <c r="AK54">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9274,58 +9274,58 @@
         </is>
       </c>
       <c r="N55">
-        <v>3.16</v>
+        <v>3.85</v>
       </c>
       <c r="O55">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="P55">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="Q55">
-        <v>3.36</v>
+        <v>3.74</v>
       </c>
       <c r="R55">
-        <v>2.51</v>
+        <v>2.82</v>
       </c>
       <c r="S55">
         <v>1.14</v>
       </c>
       <c r="T55">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="U55">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="V55">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="W55">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="X55">
         <v>1.01</v>
       </c>
       <c r="Y55">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Z55">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AA55">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AB55">
-        <v>3.22</v>
+        <v>3.33</v>
       </c>
       <c r="AC55">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AD55">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AE55">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AF55">
         <v>1.32</v>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
+        <v>1.2</v>
+      </c>
+      <c r="AK55">
         <v>1.25</v>
-      </c>
-      <c r="AK55">
-        <v>1.36</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9458,10 +9458,10 @@
         <v>2.61</v>
       </c>
       <c r="U56">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V56">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W56">
         <v>1.05</v>
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="O58">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P58">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="Q58">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="R58">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="S58">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T58">
         <v>3.23</v>
       </c>
       <c r="U58">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="V58">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W58">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X58">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y58">
         <v>1.2</v>
       </c>
       <c r="Z58">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AA58">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AB58">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AC58">
-        <v>2.78</v>
+        <v>2.69</v>
       </c>
       <c r="AD58">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AE58">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF58">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AG58">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK58">
         <v>1.85</v>
@@ -10098,7 +10098,7 @@
         <v>2.4</v>
       </c>
       <c r="Q60">
-        <v>2.95</v>
+        <v>3.07</v>
       </c>
       <c r="R60">
         <v>2.37</v>
@@ -10110,7 +10110,7 @@
         <v>4</v>
       </c>
       <c r="U60">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V60">
         <v>1.7</v>
@@ -10128,10 +10128,10 @@
         <v>5.7</v>
       </c>
       <c r="AA60">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AB60">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AC60">
         <v>2.05</v>
@@ -10140,7 +10140,7 @@
         <v>1.75</v>
       </c>
       <c r="AE60">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AF60">
         <v>1.36</v>
@@ -10255,31 +10255,31 @@
         <v>5.71</v>
       </c>
       <c r="O61">
-        <v>4.55</v>
+        <v>4.65</v>
       </c>
       <c r="P61">
         <v>1.46</v>
       </c>
       <c r="Q61">
-        <v>4.58</v>
+        <v>4.73</v>
       </c>
       <c r="R61">
-        <v>2.37</v>
+        <v>2.41</v>
       </c>
       <c r="S61">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T61">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="U61">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="V61">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="W61">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X61">
         <v>1.02</v>
@@ -10288,7 +10288,7 @@
         <v>1.14</v>
       </c>
       <c r="Z61">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AA61">
         <v>1.44</v>
@@ -10297,7 +10297,7 @@
         <v>2.42</v>
       </c>
       <c r="AC61">
-        <v>2.39</v>
+        <v>2.27</v>
       </c>
       <c r="AD61">
         <v>1.59</v>
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="O63">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="P63">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="Q63">
         <v>1.64</v>
@@ -10599,10 +10599,10 @@
         <v>4.5</v>
       </c>
       <c r="U63">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="V63">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W63">
         <v>1.19</v>
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O65">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P65">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q65">
         <v>2.48</v>
@@ -11076,13 +11076,13 @@
         <v>2.91</v>
       </c>
       <c r="Q66">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="R66">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="S66">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T66">
         <v>3.02</v>
@@ -11106,7 +11106,7 @@
         <v>3.48</v>
       </c>
       <c r="AA66">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AB66">
         <v>1.97</v>
@@ -11115,7 +11115,7 @@
         <v>2.88</v>
       </c>
       <c r="AD66">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE66">
         <v>1.14</v>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK66">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,16 +11230,16 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="O67">
         <v>3.35</v>
       </c>
       <c r="P67">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q67">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R67">
         <v>2.05</v>
@@ -11251,7 +11251,7 @@
         <v>2.93</v>
       </c>
       <c r="U67">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="V67">
         <v>1.35</v>
@@ -11260,10 +11260,10 @@
         <v>1.04</v>
       </c>
       <c r="X67">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y67">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z67">
         <v>3.3</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.04</v>
+        <v>1.75</v>
       </c>
       <c r="O68">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="P68">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="Q68">
-        <v>2.79</v>
+        <v>2.25</v>
       </c>
       <c r="R68">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="S68">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T68">
-        <v>2.88</v>
+        <v>3.31</v>
       </c>
       <c r="U68">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="V68">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W68">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X68">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="Z68">
-        <v>3.08</v>
+        <v>4.4</v>
       </c>
       <c r="AA68">
-        <v>2.06</v>
+        <v>1.66</v>
       </c>
       <c r="AB68">
-        <v>1.73</v>
+        <v>2.27</v>
       </c>
       <c r="AC68">
-        <v>3.5</v>
+        <v>2.46</v>
       </c>
       <c r="AD68">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="AE68">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF68">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="AG68">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AK68">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.59</v>
+        <v>2.04</v>
       </c>
       <c r="O69">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
       <c r="P69">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="Q69">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="R69">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="S69">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="T69">
-        <v>2.39</v>
+        <v>2.88</v>
       </c>
       <c r="U69">
-        <v>3.33</v>
+        <v>2.8</v>
       </c>
       <c r="V69">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="W69">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X69">
         <v>1.04</v>
       </c>
       <c r="Y69">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="Z69">
-        <v>2.85</v>
+        <v>3.08</v>
       </c>
       <c r="AA69">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="AB69">
-        <v>1.61</v>
+        <v>1.79</v>
       </c>
       <c r="AC69">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="AD69">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AE69">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="AF69">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="AG69">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AK69">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.75</v>
+        <v>2.59</v>
       </c>
       <c r="O70">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="P70">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q70">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="R70">
-        <v>2.24</v>
+        <v>1.95</v>
       </c>
       <c r="S70">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="T70">
-        <v>3.46</v>
+        <v>2.59</v>
       </c>
       <c r="U70">
-        <v>2.5</v>
+        <v>3.33</v>
       </c>
       <c r="V70">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="W70">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X70">
+        <v>1.04</v>
+      </c>
+      <c r="Y70">
+        <v>1.44</v>
+      </c>
+      <c r="Z70">
+        <v>2.85</v>
+      </c>
+      <c r="AA70">
+        <v>2.35</v>
+      </c>
+      <c r="AB70">
+        <v>1.61</v>
+      </c>
+      <c r="AC70">
+        <v>4.15</v>
+      </c>
+      <c r="AD70">
+        <v>1.17</v>
+      </c>
+      <c r="AE70">
         <v>1.02</v>
       </c>
-      <c r="Y70">
-        <v>1.2</v>
-      </c>
-      <c r="Z70">
-        <v>4.4</v>
-      </c>
-      <c r="AA70">
-        <v>1.66</v>
-      </c>
-      <c r="AB70">
-        <v>2.12</v>
-      </c>
-      <c r="AC70">
-        <v>2.75</v>
-      </c>
-      <c r="AD70">
-        <v>1.43</v>
-      </c>
-      <c r="AE70">
-        <v>1.14</v>
-      </c>
       <c r="AF70">
-        <v>1.62</v>
+        <v>1.94</v>
       </c>
       <c r="AG70">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AK70">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -12881,7 +12881,7 @@
         <v>3.2</v>
       </c>
       <c r="U77">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="V77">
         <v>1.46</v>
@@ -12902,7 +12902,7 @@
         <v>1.83</v>
       </c>
       <c r="AB77">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AC77">
         <v>2.9</v>
@@ -13512,7 +13512,7 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O81">
         <v>3.4</v>
@@ -13675,22 +13675,22 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O82">
         <v>3.25</v>
       </c>
       <c r="P82">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="Q82">
-        <v>2.77</v>
+        <v>3.02</v>
       </c>
       <c r="R82">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="S82">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T82">
         <v>3.25</v>
@@ -13705,7 +13705,7 @@
         <v>1.11</v>
       </c>
       <c r="X82">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y82">
         <v>1.22</v>
@@ -13720,16 +13720,16 @@
         <v>2.1</v>
       </c>
       <c r="AC82">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="AD82">
         <v>1.43</v>
       </c>
       <c r="AE82">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF82">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AG82">
         <v>2.3</v>
@@ -13748,7 +13748,7 @@
         <v>1.36</v>
       </c>
       <c r="AK82">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13838,10 +13838,10 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="O83">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P83">
         <v>2.85</v>
@@ -13859,7 +13859,7 @@
         <v>3.32</v>
       </c>
       <c r="U83">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="V83">
         <v>1.52</v>
@@ -14164,19 +14164,19 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="O85">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="P85">
         <v>3.5</v>
       </c>
       <c r="Q85">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="R85">
-        <v>2.48</v>
+        <v>2.53</v>
       </c>
       <c r="S85">
         <v>1.14</v>
@@ -14188,7 +14188,7 @@
         <v>1.91</v>
       </c>
       <c r="V85">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="W85">
         <v>1.22</v>
@@ -14197,22 +14197,22 @@
         <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z85">
-        <v>7.5</v>
+        <v>6.85</v>
       </c>
       <c r="AA85">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AB85">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AC85">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AD85">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AE85">
         <v>1.4</v>
@@ -14234,7 +14234,7 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK85">
         <v>1.98</v>
@@ -14499,10 +14499,10 @@
         <v>2.28</v>
       </c>
       <c r="Q87">
-        <v>3.17</v>
+        <v>3.24</v>
       </c>
       <c r="R87">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="S87">
         <v>1.3</v>
@@ -14532,7 +14532,7 @@
         <v>1.76</v>
       </c>
       <c r="AB87">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="AC87">
         <v>2.63</v>
@@ -14547,7 +14547,7 @@
         <v>1.53</v>
       </c>
       <c r="AG87">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.46</v>
+        <v>2.9</v>
       </c>
       <c r="O89">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="P89">
-        <v>6</v>
+        <v>2.15</v>
       </c>
       <c r="Q89">
-        <v>2.02</v>
+        <v>3.2</v>
       </c>
       <c r="R89">
-        <v>2.73</v>
+        <v>2.25</v>
       </c>
       <c r="S89">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="T89">
-        <v>3.9</v>
+        <v>3.02</v>
       </c>
       <c r="U89">
-        <v>2</v>
+        <v>2.88</v>
       </c>
       <c r="V89">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="W89">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X89">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y89">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="Z89">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA89">
-        <v>1.4</v>
+        <v>1.86</v>
       </c>
       <c r="AB89">
-        <v>2.7</v>
+        <v>1.82</v>
       </c>
       <c r="AC89">
-        <v>2.05</v>
+        <v>3.32</v>
       </c>
       <c r="AD89">
-        <v>1.66</v>
+        <v>1.3</v>
       </c>
       <c r="AE89">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AF89">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AG89">
-        <v>2.39</v>
+        <v>2.1</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK89">
-        <v>2.3</v>
+        <v>1.36</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.9</v>
+        <v>1.46</v>
       </c>
       <c r="O90">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="P90">
-        <v>2.15</v>
+        <v>6</v>
       </c>
       <c r="Q90">
-        <v>3.2</v>
+        <v>2.02</v>
       </c>
       <c r="R90">
-        <v>2.25</v>
+        <v>2.73</v>
       </c>
       <c r="S90">
-        <v>1.37</v>
+        <v>1.17</v>
       </c>
       <c r="T90">
-        <v>3.02</v>
+        <v>3.9</v>
       </c>
       <c r="U90">
-        <v>2.88</v>
+        <v>2</v>
       </c>
       <c r="V90">
+        <v>1.73</v>
+      </c>
+      <c r="W90">
+        <v>1.17</v>
+      </c>
+      <c r="X90">
+        <v>1.02</v>
+      </c>
+      <c r="Y90">
+        <v>1.1</v>
+      </c>
+      <c r="Z90">
+        <v>5.2</v>
+      </c>
+      <c r="AA90">
         <v>1.4</v>
       </c>
-      <c r="W90">
-        <v>1.1</v>
-      </c>
-      <c r="X90">
-        <v>1.03</v>
-      </c>
-      <c r="Y90">
-        <v>1.24</v>
-      </c>
-      <c r="Z90">
-        <v>3.5</v>
-      </c>
-      <c r="AA90">
-        <v>1.86</v>
-      </c>
       <c r="AB90">
-        <v>1.82</v>
+        <v>2.7</v>
       </c>
       <c r="AC90">
-        <v>3.32</v>
+        <v>2.05</v>
       </c>
       <c r="AD90">
-        <v>1.3</v>
+        <v>1.66</v>
       </c>
       <c r="AE90">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="AF90">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AG90">
-        <v>2.1</v>
+        <v>2.39</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK90">
-        <v>1.36</v>
+        <v>2.3</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>3.1</v>
+        <v>5.75</v>
       </c>
       <c r="O91">
-        <v>3.35</v>
+        <v>4.7</v>
       </c>
       <c r="P91">
-        <v>2</v>
+        <v>1.38</v>
       </c>
       <c r="Q91">
-        <v>3.9</v>
+        <v>4.25</v>
       </c>
       <c r="R91">
-        <v>2.16</v>
+        <v>2.62</v>
       </c>
       <c r="S91">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="T91">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="U91">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="V91">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="W91">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X91">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y91">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="Z91">
-        <v>3.7</v>
+        <v>5.67</v>
       </c>
       <c r="AA91">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AB91">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="AC91">
-        <v>2.88</v>
+        <v>2.15</v>
       </c>
       <c r="AD91">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="AE91">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="AF91">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AG91">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.29</v>
+        <v>2.75</v>
       </c>
       <c r="AK91">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,80 +15631,80 @@
         </is>
       </c>
       <c r="N94">
-        <v>5.75</v>
+        <v>3.1</v>
       </c>
       <c r="O94">
-        <v>4.7</v>
+        <v>3.35</v>
       </c>
       <c r="P94">
-        <v>1.38</v>
+        <v>2</v>
       </c>
       <c r="Q94">
-        <v>4.25</v>
+        <v>3.9</v>
       </c>
       <c r="R94">
-        <v>2.62</v>
+        <v>2.16</v>
       </c>
       <c r="S94">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="T94">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="U94">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="V94">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="W94">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X94">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y94">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="Z94">
-        <v>5.67</v>
+        <v>3.7</v>
       </c>
       <c r="AA94">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AB94">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="AC94">
-        <v>2.15</v>
+        <v>2.88</v>
       </c>
       <c r="AD94">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="AE94">
+        <v>1.08</v>
+      </c>
+      <c r="AF94">
+        <v>1.62</v>
+      </c>
+      <c r="AG94">
+        <v>2.2</v>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ94">
         <v>1.29</v>
       </c>
-      <c r="AF94">
-        <v>1.55</v>
-      </c>
-      <c r="AG94">
-        <v>2.25</v>
-      </c>
-      <c r="AH94" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI94" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ94">
-        <v>2.75</v>
-      </c>
       <c r="AK94">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -16467,10 +16467,10 @@
         <v>2.99</v>
       </c>
       <c r="U99">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="V99">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W99">
         <v>1.1</v>
@@ -16482,19 +16482,19 @@
         <v>1.29</v>
       </c>
       <c r="Z99">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AA99">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AB99">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AC99">
         <v>3.25</v>
       </c>
       <c r="AD99">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE99">
         <v>1.1</v>
@@ -16615,10 +16615,10 @@
         <v>3.5</v>
       </c>
       <c r="P100">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Q100">
-        <v>3.12</v>
+        <v>3.54</v>
       </c>
       <c r="R100">
         <v>2.33</v>
@@ -16630,7 +16630,7 @@
         <v>3.1</v>
       </c>
       <c r="U100">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="V100">
         <v>1.46</v>
@@ -16645,7 +16645,7 @@
         <v>1.21</v>
       </c>
       <c r="Z100">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AA100">
         <v>1.79</v>
@@ -16654,7 +16654,7 @@
         <v>1.95</v>
       </c>
       <c r="AC100">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="AD100">
         <v>1.36</v>
@@ -16778,19 +16778,19 @@
         <v>4.5</v>
       </c>
       <c r="P101">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="Q101">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="R101">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="S101">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T101">
-        <v>5.35</v>
+        <v>4.75</v>
       </c>
       <c r="U101">
         <v>1.76</v>
@@ -16808,7 +16808,7 @@
         <v>1.03</v>
       </c>
       <c r="Z101">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="AA101">
         <v>1.24</v>
@@ -16820,7 +16820,7 @@
         <v>1.73</v>
       </c>
       <c r="AD101">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="AE101">
         <v>1.33</v>
@@ -16842,7 +16842,7 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK101">
         <v>1.25</v>
@@ -16941,58 +16941,58 @@
         <v>3.35</v>
       </c>
       <c r="P102">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="Q102">
-        <v>2.53</v>
+        <v>2.43</v>
       </c>
       <c r="R102">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="S102">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="T102">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="U102">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="V102">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W102">
         <v>1.05</v>
       </c>
       <c r="X102">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y102">
         <v>1.3</v>
       </c>
       <c r="Z102">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="AA102">
-        <v>1.92</v>
+        <v>2.17</v>
       </c>
       <c r="AB102">
         <v>1.61</v>
       </c>
       <c r="AC102">
-        <v>4.25</v>
+        <v>4.18</v>
       </c>
       <c r="AD102">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE102">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF102">
         <v>2</v>
       </c>
       <c r="AG102">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK102">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17427,7 +17427,7 @@
         <v>2.15</v>
       </c>
       <c r="O105">
-        <v>3.02</v>
+        <v>3.19</v>
       </c>
       <c r="P105">
         <v>2.83</v>
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="O109">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="P109">
-        <v>2.65</v>
+        <v>3.05</v>
       </c>
       <c r="Q109">
         <v>3.1</v>
@@ -18109,10 +18109,10 @@
         <v>1.06</v>
       </c>
       <c r="Y109">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="Z109">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="AA109">
         <v>2.62</v>
@@ -18435,10 +18435,10 @@
         <v>1.11</v>
       </c>
       <c r="Y111">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Z111">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AA111">
         <v>3.1</v>
@@ -18565,19 +18565,19 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="O112">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P112">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q112">
-        <v>2.68</v>
+        <v>2.63</v>
       </c>
       <c r="R112">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="S112">
         <v>1.22</v>
@@ -18622,7 +18622,7 @@
         <v>1.44</v>
       </c>
       <c r="AG112">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK112">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL112">
         <v>0</v>

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -624,14 +624,14 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
@@ -641,19 +641,19 @@
         <v>3.45</v>
       </c>
       <c r="P2">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="Q2">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="R2">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="S2">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T2">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="U2">
         <v>2.75</v>
@@ -662,25 +662,25 @@
         <v>1.4</v>
       </c>
       <c r="W2">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X2">
         <v>1.04</v>
       </c>
       <c r="Y2">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="Z2">
         <v>3.34</v>
       </c>
       <c r="AA2">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AB2">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AC2">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="AD2">
         <v>1.28</v>
@@ -696,46 +696,46 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["82"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["50", "66"]</t>
         </is>
       </c>
       <c r="AJ2">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK2">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -794,20 +794,20 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="O3">
         <v>3.6</v>
       </c>
       <c r="P3">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="Q3">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="R3">
         <v>2.3</v>
@@ -822,19 +822,19 @@
         <v>2.45</v>
       </c>
       <c r="V3">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W3">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X3">
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z3">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AA3">
         <v>1.71</v>
@@ -843,19 +843,19 @@
         <v>2.15</v>
       </c>
       <c r="AC3">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AD3">
-        <v>1.39</v>
+        <v>1.54</v>
       </c>
       <c r="AE3">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF3">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG3">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -877,28 +877,28 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Halaba Ketema</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
+        <v>1.53</v>
+      </c>
+      <c r="O9">
+        <v>3.7</v>
+      </c>
+      <c r="P9">
+        <v>4.9</v>
+      </c>
+      <c r="Q9">
+        <v>2</v>
+      </c>
+      <c r="R9">
+        <v>2.3</v>
+      </c>
+      <c r="S9">
+        <v>1.36</v>
+      </c>
+      <c r="T9">
+        <v>3.2</v>
+      </c>
+      <c r="U9">
+        <v>2.76</v>
+      </c>
+      <c r="V9">
+        <v>1.4</v>
+      </c>
+      <c r="W9">
+        <v>1.07</v>
+      </c>
+      <c r="X9">
+        <v>1.03</v>
+      </c>
+      <c r="Y9">
+        <v>1.28</v>
+      </c>
+      <c r="Z9">
+        <v>3.08</v>
+      </c>
+      <c r="AA9">
+        <v>1.93</v>
+      </c>
+      <c r="AB9">
+        <v>1.75</v>
+      </c>
+      <c r="AC9">
         <v>3.3</v>
       </c>
-      <c r="O9">
-        <v>2.45</v>
-      </c>
-      <c r="P9">
-        <v>2.4</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>0</v>
-      </c>
-      <c r="V9">
-        <v>0</v>
-      </c>
-      <c r="W9">
-        <v>0</v>
-      </c>
-      <c r="X9">
-        <v>0</v>
-      </c>
-      <c r="Y9">
-        <v>0</v>
-      </c>
-      <c r="Z9">
-        <v>0</v>
-      </c>
-      <c r="AA9">
-        <v>3.25</v>
-      </c>
-      <c r="AB9">
-        <v>1.33</v>
-      </c>
-      <c r="AC9">
-        <v>0</v>
-      </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,80 +1939,80 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.53</v>
+        <v>2.59</v>
       </c>
       <c r="O10">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P10">
-        <v>4.9</v>
+        <v>2.31</v>
       </c>
       <c r="Q10">
-        <v>2</v>
+        <v>3.28</v>
       </c>
       <c r="R10">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S10">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T10">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U10">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="V10">
+        <v>1.44</v>
+      </c>
+      <c r="W10">
+        <v>1.1</v>
+      </c>
+      <c r="X10">
+        <v>1.01</v>
+      </c>
+      <c r="Y10">
+        <v>1.25</v>
+      </c>
+      <c r="Z10">
+        <v>3.75</v>
+      </c>
+      <c r="AA10">
+        <v>1.82</v>
+      </c>
+      <c r="AB10">
+        <v>1.96</v>
+      </c>
+      <c r="AC10">
+        <v>2.93</v>
+      </c>
+      <c r="AD10">
+        <v>1.3</v>
+      </c>
+      <c r="AE10">
+        <v>1.1</v>
+      </c>
+      <c r="AF10">
+        <v>1.62</v>
+      </c>
+      <c r="AG10">
+        <v>2.1</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10">
+        <v>1.25</v>
+      </c>
+      <c r="AK10">
         <v>1.4</v>
-      </c>
-      <c r="W10">
-        <v>1.07</v>
-      </c>
-      <c r="X10">
-        <v>1.03</v>
-      </c>
-      <c r="Y10">
-        <v>1.28</v>
-      </c>
-      <c r="Z10">
-        <v>3.08</v>
-      </c>
-      <c r="AA10">
-        <v>1.93</v>
-      </c>
-      <c r="AB10">
-        <v>1.75</v>
-      </c>
-      <c r="AC10">
-        <v>3.3</v>
-      </c>
-      <c r="AD10">
-        <v>1.25</v>
-      </c>
-      <c r="AE10">
-        <v>1.08</v>
-      </c>
-      <c r="AF10">
-        <v>1.85</v>
-      </c>
-      <c r="AG10">
-        <v>1.85</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10">
-        <v>1.15</v>
-      </c>
-      <c r="AK10">
-        <v>1.86</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.59</v>
+        <v>3.2</v>
       </c>
       <c r="O11">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="P11">
-        <v>2.19</v>
+        <v>1.99</v>
       </c>
       <c r="Q11">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R11">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="V11">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W11">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y11">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z11">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA11">
-        <v>1.88</v>
+        <v>1.57</v>
       </c>
       <c r="AB11">
-        <v>1.88</v>
+        <v>2.35</v>
       </c>
       <c r="AC11">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AD11">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE11">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF11">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG11">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK11">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Adhyaksa</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.9</v>
+        <v>1.85</v>
       </c>
       <c r="O12">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P12">
-        <v>2.25</v>
+        <v>3.8</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2304,10 +2304,10 @@
         <v>0</v>
       </c>
       <c r="AA12">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AB12">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AC12">
         <v>0</v>
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Adhyaksa</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.83</v>
+        <v>2.4</v>
       </c>
       <c r="O13">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P13">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AA13">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB13">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-10-16 09:00:00</t>
+          <t>2026-10-16 10:00:00</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O14">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P14">
         <v>2.5</v>
       </c>
       <c r="Q14">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="R14">
-        <v>2.11</v>
+        <v>2.24</v>
       </c>
       <c r="S14">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T14">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U14">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="V14">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W14">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X14">
         <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z14">
-        <v>3.86</v>
+        <v>4.33</v>
       </c>
       <c r="AA14">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB14">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AC14">
-        <v>2.66</v>
+        <v>2.49</v>
       </c>
       <c r="AD14">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AE14">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF14">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AG14">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AK14">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="O15">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P15">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="Q15">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="R15">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="S15">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T15">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="U15">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="V15">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="W15">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X15">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z15">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="AA15">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="AB15">
-        <v>2.17</v>
+        <v>1.88</v>
       </c>
       <c r="AC15">
-        <v>2.49</v>
+        <v>2.92</v>
       </c>
       <c r="AD15">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AE15">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF15">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="AG15">
-        <v>2.39</v>
+        <v>2.1</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="AK15">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,80 +2917,80 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.25</v>
+        <v>1.35</v>
       </c>
       <c r="O16">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="P16">
-        <v>2.62</v>
+        <v>7.5</v>
       </c>
       <c r="Q16">
-        <v>2.87</v>
+        <v>1.75</v>
       </c>
       <c r="R16">
-        <v>2.08</v>
+        <v>2.6</v>
       </c>
       <c r="S16">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="T16">
-        <v>2.95</v>
+        <v>3.7</v>
       </c>
       <c r="U16">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="V16">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="W16">
+        <v>1.15</v>
+      </c>
+      <c r="X16">
+        <v>1.02</v>
+      </c>
+      <c r="Y16">
+        <v>1.11</v>
+      </c>
+      <c r="Z16">
+        <v>4.95</v>
+      </c>
+      <c r="AA16">
+        <v>1.48</v>
+      </c>
+      <c r="AB16">
+        <v>2.55</v>
+      </c>
+      <c r="AC16">
+        <v>2.22</v>
+      </c>
+      <c r="AD16">
+        <v>1.57</v>
+      </c>
+      <c r="AE16">
+        <v>1.19</v>
+      </c>
+      <c r="AF16">
+        <v>1.73</v>
+      </c>
+      <c r="AG16">
+        <v>2</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16">
         <v>1.1</v>
       </c>
-      <c r="X16">
-        <v>1.04</v>
-      </c>
-      <c r="Y16">
-        <v>1.22</v>
-      </c>
-      <c r="Z16">
-        <v>3.5</v>
-      </c>
-      <c r="AA16">
-        <v>1.79</v>
-      </c>
-      <c r="AB16">
-        <v>1.88</v>
-      </c>
-      <c r="AC16">
-        <v>2.92</v>
-      </c>
-      <c r="AD16">
-        <v>1.31</v>
-      </c>
-      <c r="AE16">
-        <v>1.08</v>
-      </c>
-      <c r="AF16">
-        <v>1.62</v>
-      </c>
-      <c r="AG16">
-        <v>2.1</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16">
-        <v>1.24</v>
-      </c>
       <c r="AK16">
-        <v>1.57</v>
+        <v>3.1</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.35</v>
+        <v>1.77</v>
       </c>
       <c r="O17">
-        <v>4.7</v>
+        <v>3.65</v>
       </c>
       <c r="P17">
-        <v>7.5</v>
+        <v>3.85</v>
       </c>
       <c r="Q17">
-        <v>1.75</v>
+        <v>2.28</v>
       </c>
       <c r="R17">
-        <v>2.6</v>
+        <v>2.22</v>
       </c>
       <c r="S17">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="T17">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="U17">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="V17">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="W17">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X17">
         <v>1.02</v>
       </c>
       <c r="Y17">
+        <v>1.18</v>
+      </c>
+      <c r="Z17">
+        <v>3.92</v>
+      </c>
+      <c r="AA17">
+        <v>1.7</v>
+      </c>
+      <c r="AB17">
+        <v>2.1</v>
+      </c>
+      <c r="AC17">
+        <v>2.66</v>
+      </c>
+      <c r="AD17">
+        <v>1.37</v>
+      </c>
+      <c r="AE17">
         <v>1.11</v>
       </c>
-      <c r="Z17">
-        <v>4.95</v>
-      </c>
-      <c r="AA17">
-        <v>1.48</v>
-      </c>
-      <c r="AB17">
-        <v>2.55</v>
-      </c>
-      <c r="AC17">
-        <v>2.22</v>
-      </c>
-      <c r="AD17">
-        <v>1.57</v>
-      </c>
-      <c r="AE17">
-        <v>1.19</v>
-      </c>
       <c r="AF17">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AG17">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AK17">
-        <v>3.1</v>
+        <v>1.87</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Kelantan Red Warrior</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,80 +3243,80 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.77</v>
+        <v>6.25</v>
       </c>
       <c r="O18">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="P18">
-        <v>3.85</v>
+        <v>1.4</v>
       </c>
       <c r="Q18">
-        <v>2.28</v>
+        <v>6.72</v>
       </c>
       <c r="R18">
-        <v>2.22</v>
+        <v>2.8</v>
       </c>
       <c r="S18">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="T18">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="U18">
-        <v>2.45</v>
+        <v>2.02</v>
       </c>
       <c r="V18">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="W18">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X18">
+        <v>1.01</v>
+      </c>
+      <c r="Y18">
+        <v>1.08</v>
+      </c>
+      <c r="Z18">
+        <v>5.55</v>
+      </c>
+      <c r="AA18">
+        <v>1.39</v>
+      </c>
+      <c r="AB18">
+        <v>2.59</v>
+      </c>
+      <c r="AC18">
+        <v>2.01</v>
+      </c>
+      <c r="AD18">
+        <v>1.69</v>
+      </c>
+      <c r="AE18">
+        <v>1.26</v>
+      </c>
+      <c r="AF18">
+        <v>1.59</v>
+      </c>
+      <c r="AG18">
+        <v>2.15</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
+        <v>1.12</v>
+      </c>
+      <c r="AK18">
         <v>1.02</v>
-      </c>
-      <c r="Y18">
-        <v>1.18</v>
-      </c>
-      <c r="Z18">
-        <v>3.92</v>
-      </c>
-      <c r="AA18">
-        <v>1.7</v>
-      </c>
-      <c r="AB18">
-        <v>2.1</v>
-      </c>
-      <c r="AC18">
-        <v>2.66</v>
-      </c>
-      <c r="AD18">
-        <v>1.37</v>
-      </c>
-      <c r="AE18">
-        <v>1.11</v>
-      </c>
-      <c r="AF18">
-        <v>1.62</v>
-      </c>
-      <c r="AG18">
-        <v>2.12</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.18</v>
-      </c>
-      <c r="AK18">
-        <v>1.87</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kelantan Red Warrior</t>
+          <t>Halaba Ketema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>6.25</v>
+        <v>3.3</v>
       </c>
       <c r="O19">
-        <v>4.5</v>
+        <v>2.45</v>
       </c>
       <c r="P19">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="Q19">
-        <v>6.72</v>
+        <v>0</v>
       </c>
       <c r="R19">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S19">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="T19">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="U19">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V19">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="W19">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X19">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y19">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z19">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="AA19">
-        <v>1.39</v>
+        <v>3.25</v>
       </c>
       <c r="AB19">
-        <v>2.59</v>
+        <v>1.33</v>
       </c>
       <c r="AC19">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AD19">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AE19">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AF19">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AG19">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK19">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,55 +3569,55 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="O20">
-        <v>3.7</v>
+        <v>3.63</v>
       </c>
       <c r="P20">
-        <v>3.2</v>
+        <v>3.01</v>
       </c>
       <c r="Q20">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="R20">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S20">
         <v>1.17</v>
       </c>
       <c r="T20">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="U20">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="V20">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="W20">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X20">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
         <v>1.1</v>
       </c>
       <c r="Z20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA20">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AB20">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AC20">
         <v>2</v>
       </c>
       <c r="AD20">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AE20">
         <v>1.33</v>
@@ -3626,7 +3626,7 @@
         <v>1.4</v>
       </c>
       <c r="AG20">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AK20">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3898,31 +3898,31 @@
         <v>1.11</v>
       </c>
       <c r="O22">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="P22">
-        <v>13.3</v>
+        <v>14.39</v>
       </c>
       <c r="Q22">
         <v>1.4</v>
       </c>
       <c r="R22">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="S22">
         <v>1.17</v>
       </c>
       <c r="T22">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="U22">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="V22">
         <v>1.92</v>
       </c>
       <c r="W22">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X22">
         <v>1.01</v>
@@ -3934,25 +3934,25 @@
         <v>8</v>
       </c>
       <c r="AA22">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AB22">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AC22">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AD22">
         <v>2.03</v>
       </c>
       <c r="AE22">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AF22">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AG22">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AK22">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="O28">
         <v>3.15</v>
@@ -4885,7 +4885,7 @@
         <v>3.25</v>
       </c>
       <c r="R28">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S28">
         <v>1.36</v>
@@ -4906,22 +4906,22 @@
         <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z28">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="AA28">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AB28">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC28">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AD28">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE28">
         <v>1.05</v>
@@ -4930,7 +4930,7 @@
         <v>1.75</v>
       </c>
       <c r="AG28">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AK28">
         <v>1.4</v>
@@ -5036,19 +5036,19 @@
         </is>
       </c>
       <c r="N29">
-        <v>7.75</v>
+        <v>7.5</v>
       </c>
       <c r="O29">
-        <v>4.8</v>
+        <v>5.05</v>
       </c>
       <c r="P29">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Q29">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="R29">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="S29">
         <v>1.25</v>
@@ -5057,43 +5057,43 @@
         <v>3.4</v>
       </c>
       <c r="U29">
-        <v>2.45</v>
+        <v>2.19</v>
       </c>
       <c r="V29">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="W29">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X29">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z29">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AA29">
         <v>1.53</v>
       </c>
       <c r="AB29">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="AC29">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="AD29">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="AE29">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF29">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG29">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>1.18</v>
       </c>
       <c r="AK29">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5365,77 +5365,77 @@
         <v>2.2</v>
       </c>
       <c r="O31">
-        <v>3.75</v>
+        <v>3.48</v>
       </c>
       <c r="P31">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="Q31">
-        <v>2.99</v>
+        <v>2.76</v>
       </c>
       <c r="R31">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U31">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="V31">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Z31">
-        <v>6.27</v>
+        <v>5.25</v>
       </c>
       <c r="AA31">
+        <v>1.4</v>
+      </c>
+      <c r="AB31">
+        <v>2.56</v>
+      </c>
+      <c r="AC31">
+        <v>2.06</v>
+      </c>
+      <c r="AD31">
+        <v>1.66</v>
+      </c>
+      <c r="AE31">
+        <v>1.25</v>
+      </c>
+      <c r="AF31">
+        <v>1.39</v>
+      </c>
+      <c r="AG31">
+        <v>2.88</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31">
+        <v>1.22</v>
+      </c>
+      <c r="AK31">
         <v>1.5</v>
-      </c>
-      <c r="AB31">
-        <v>2.8</v>
-      </c>
-      <c r="AC31">
-        <v>2.15</v>
-      </c>
-      <c r="AD31">
-        <v>1.71</v>
-      </c>
-      <c r="AE31">
-        <v>1.29</v>
-      </c>
-      <c r="AF31">
-        <v>0</v>
-      </c>
-      <c r="AG31">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31">
-        <v>0</v>
-      </c>
-      <c r="AK31">
-        <v>0</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -6023,25 +6023,25 @@
         <v>4.9</v>
       </c>
       <c r="Q35">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="R35">
         <v>2.17</v>
       </c>
       <c r="S35">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T35">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="U35">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="V35">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W35">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X35">
         <v>1.03</v>
@@ -6050,16 +6050,16 @@
         <v>1.3</v>
       </c>
       <c r="Z35">
-        <v>3.29</v>
+        <v>3.14</v>
       </c>
       <c r="AA35">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="AB35">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AC35">
-        <v>3.05</v>
+        <v>3.28</v>
       </c>
       <c r="AD35">
         <v>1.3</v>
@@ -6068,10 +6068,10 @@
         <v>1.05</v>
       </c>
       <c r="AF35">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG35">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>1.19</v>
       </c>
       <c r="AK35">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,19 +6177,19 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O36">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="P36">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="Q36">
-        <v>3.9</v>
+        <v>4.11</v>
       </c>
       <c r="R36">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="S36">
         <v>1.63</v>
@@ -6207,16 +6207,16 @@
         <v>1.01</v>
       </c>
       <c r="X36">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Y36">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="Z36">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AA36">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AB36">
         <v>1.33</v>
@@ -6225,7 +6225,7 @@
         <v>7.5</v>
       </c>
       <c r="AD36">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AE36">
         <v>1.02</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK36">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="O37">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="P37">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q37">
         <v>2.1</v>
@@ -6355,16 +6355,16 @@
         <v>2.45</v>
       </c>
       <c r="S37">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T37">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="U37">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="V37">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W37">
         <v>1.14</v>
@@ -6373,31 +6373,31 @@
         <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z37">
         <v>5.1</v>
       </c>
       <c r="AA37">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AB37">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AC37">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD37">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AE37">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF37">
         <v>1.62</v>
       </c>
       <c r="AG37">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>2.24</v>
       </c>
       <c r="S39">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T39">
         <v>3.3</v>
@@ -6693,7 +6693,7 @@
         <v>1.53</v>
       </c>
       <c r="W39">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X39">
         <v>1.01</v>
@@ -6711,7 +6711,7 @@
         <v>2.2</v>
       </c>
       <c r="AC39">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AD39">
         <v>1.45</v>
@@ -6720,7 +6720,7 @@
         <v>1.15</v>
       </c>
       <c r="AF39">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG39">
         <v>2.3</v>
@@ -6992,19 +6992,19 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O41">
         <v>3.4</v>
       </c>
       <c r="P41">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="Q41">
-        <v>2.47</v>
+        <v>2.57</v>
       </c>
       <c r="R41">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S41">
         <v>1.25</v>
@@ -7013,10 +7013,10 @@
         <v>3.4</v>
       </c>
       <c r="U41">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="V41">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W41">
         <v>1.12</v>
@@ -7028,7 +7028,7 @@
         <v>1.15</v>
       </c>
       <c r="Z41">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AA41">
         <v>1.57</v>
@@ -7040,7 +7040,7 @@
         <v>2.5</v>
       </c>
       <c r="AD41">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE41">
         <v>1.15</v>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK41">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7327,22 +7327,22 @@
         <v>2.7</v>
       </c>
       <c r="Q43">
-        <v>2.93</v>
+        <v>3.07</v>
       </c>
       <c r="R43">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S43">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="T43">
-        <v>2.71</v>
+        <v>2.83</v>
       </c>
       <c r="U43">
-        <v>3.31</v>
+        <v>3.14</v>
       </c>
       <c r="V43">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W43">
         <v>1.02</v>
@@ -7351,22 +7351,22 @@
         <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="Z43">
-        <v>3.04</v>
+        <v>3.27</v>
       </c>
       <c r="AA43">
-        <v>2.26</v>
+        <v>2.13</v>
       </c>
       <c r="AB43">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AC43">
-        <v>4.06</v>
+        <v>3.76</v>
       </c>
       <c r="AD43">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE43">
         <v>1.02</v>
@@ -7391,7 +7391,7 @@
         <v>1.26</v>
       </c>
       <c r="AK43">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7979,10 +7979,10 @@
         <v>1.35</v>
       </c>
       <c r="Q47">
-        <v>7.54</v>
+        <v>6.61</v>
       </c>
       <c r="R47">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="S47">
         <v>1.25</v>
@@ -7994,31 +7994,31 @@
         <v>2.29</v>
       </c>
       <c r="V47">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="W47">
         <v>1.14</v>
       </c>
       <c r="X47">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y47">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z47">
         <v>5</v>
       </c>
       <c r="AA47">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AB47">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AC47">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="AD47">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AE47">
         <v>1.2</v>
@@ -8043,7 +8043,7 @@
         <v>3</v>
       </c>
       <c r="AK47">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.75</v>
+        <v>2.08</v>
       </c>
       <c r="O48">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P48">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="Q48">
-        <v>3.32</v>
+        <v>2.69</v>
       </c>
       <c r="R48">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S48">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T48">
-        <v>3.38</v>
+        <v>3.08</v>
       </c>
       <c r="U48">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="V48">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="W48">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X48">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z48">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AA48">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AB48">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC48">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="AD48">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="AE48">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AF48">
         <v>1.53</v>
       </c>
       <c r="AG48">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AK48">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.08</v>
+        <v>3.05</v>
       </c>
       <c r="O49">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P49">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="Q49">
-        <v>2.69</v>
+        <v>3.32</v>
       </c>
       <c r="R49">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S49">
         <v>1.29</v>
       </c>
       <c r="T49">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="U49">
-        <v>2.39</v>
+        <v>2.26</v>
       </c>
       <c r="V49">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="W49">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X49">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z49">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AA49">
         <v>1.6</v>
       </c>
       <c r="AB49">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC49">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AD49">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AE49">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AF49">
         <v>1.53</v>
       </c>
       <c r="AG49">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AK49">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="O50">
         <v>3.7</v>
       </c>
       <c r="P50">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="Q50">
         <v>2.15</v>
@@ -8480,10 +8480,10 @@
         <v>3.4</v>
       </c>
       <c r="U50">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="V50">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="W50">
         <v>1.13</v>
@@ -8492,25 +8492,25 @@
         <v>1.03</v>
       </c>
       <c r="Y50">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z50">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="AA50">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AB50">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="AC50">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AD50">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AE50">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF50">
         <v>1.62</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AK50">
         <v>1.96</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="O51">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P51">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8661,10 +8661,10 @@
         <v>0</v>
       </c>
       <c r="AA51">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AB51">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AC51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,80 +8785,80 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.89</v>
+        <v>1.55</v>
       </c>
       <c r="O52">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="P52">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="Q52">
-        <v>3.62</v>
+        <v>1.95</v>
       </c>
       <c r="R52">
-        <v>2.28</v>
+        <v>2.52</v>
       </c>
       <c r="S52">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T52">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="U52">
-        <v>2.41</v>
+        <v>2.1</v>
       </c>
       <c r="V52">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="W52">
+        <v>1.17</v>
+      </c>
+      <c r="X52">
+        <v>1.01</v>
+      </c>
+      <c r="Y52">
         <v>1.15</v>
       </c>
-      <c r="X52">
-        <v>1.03</v>
-      </c>
-      <c r="Y52">
+      <c r="Z52">
+        <v>5.25</v>
+      </c>
+      <c r="AA52">
+        <v>1.4</v>
+      </c>
+      <c r="AB52">
+        <v>2.75</v>
+      </c>
+      <c r="AC52">
+        <v>2.15</v>
+      </c>
+      <c r="AD52">
+        <v>1.68</v>
+      </c>
+      <c r="AE52">
+        <v>1.27</v>
+      </c>
+      <c r="AF52">
+        <v>1.5</v>
+      </c>
+      <c r="AG52">
+        <v>2.45</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ52">
         <v>1.14</v>
       </c>
-      <c r="Z52">
-        <v>4.35</v>
-      </c>
-      <c r="AA52">
-        <v>1.61</v>
-      </c>
-      <c r="AB52">
-        <v>2.31</v>
-      </c>
-      <c r="AC52">
-        <v>2.56</v>
-      </c>
-      <c r="AD52">
-        <v>1.44</v>
-      </c>
-      <c r="AE52">
-        <v>1.19</v>
-      </c>
-      <c r="AF52">
-        <v>1.53</v>
-      </c>
-      <c r="AG52">
-        <v>2.39</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ52">
-        <v>1.24</v>
-      </c>
       <c r="AK52">
-        <v>1.35</v>
+        <v>2.4</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.53</v>
+        <v>2.89</v>
       </c>
       <c r="O53">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="P53">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="Q53">
-        <v>1.85</v>
+        <v>3.62</v>
       </c>
       <c r="R53">
-        <v>2.62</v>
+        <v>2.32</v>
       </c>
       <c r="S53">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="T53">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="U53">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="V53">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="W53">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X53">
         <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z53">
-        <v>5.45</v>
+        <v>4.4</v>
       </c>
       <c r="AA53">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AB53">
-        <v>2.88</v>
+        <v>2.24</v>
       </c>
       <c r="AC53">
-        <v>2</v>
+        <v>2.68</v>
       </c>
       <c r="AD53">
-        <v>1.71</v>
+        <v>1.47</v>
       </c>
       <c r="AE53">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AF53">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG53">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AK53">
-        <v>2.4</v>
+        <v>1.35</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9455,7 +9455,7 @@
         <v>1.4</v>
       </c>
       <c r="T56">
-        <v>2.61</v>
+        <v>2.55</v>
       </c>
       <c r="U56">
         <v>2.9</v>
@@ -9476,7 +9476,7 @@
         <v>3.1</v>
       </c>
       <c r="AA56">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB56">
         <v>1.65</v>
@@ -9510,7 +9510,7 @@
         <v>1.44</v>
       </c>
       <c r="AK56">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>1.79</v>
       </c>
       <c r="Q57">
-        <v>4.23</v>
+        <v>4.26</v>
       </c>
       <c r="R57">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="S57">
         <v>1.22</v>
@@ -9621,22 +9621,22 @@
         <v>3.75</v>
       </c>
       <c r="U57">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="V57">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W57">
         <v>1.15</v>
       </c>
       <c r="X57">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y57">
         <v>1.14</v>
       </c>
       <c r="Z57">
-        <v>5.5</v>
+        <v>5.69</v>
       </c>
       <c r="AA57">
         <v>1.44</v>
@@ -9645,19 +9645,19 @@
         <v>2.52</v>
       </c>
       <c r="AC57">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AD57">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AE57">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AF57">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG57">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>1.91</v>
       </c>
       <c r="AK57">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9932,19 +9932,19 @@
         <v>3.6</v>
       </c>
       <c r="P59">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="Q59">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="R59">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="S59">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T59">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U59">
         <v>2.22</v>
@@ -9959,16 +9959,16 @@
         <v>1.01</v>
       </c>
       <c r="Y59">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z59">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA59">
         <v>1.58</v>
       </c>
       <c r="AB59">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AC59">
         <v>2.41</v>
@@ -9977,13 +9977,13 @@
         <v>1.53</v>
       </c>
       <c r="AE59">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF59">
         <v>1.46</v>
       </c>
       <c r="AG59">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AK59">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10098,10 +10098,10 @@
         <v>2.4</v>
       </c>
       <c r="Q60">
-        <v>3.07</v>
+        <v>2.93</v>
       </c>
       <c r="R60">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="S60">
         <v>1.2</v>
@@ -10140,7 +10140,7 @@
         <v>1.75</v>
       </c>
       <c r="AE60">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AF60">
         <v>1.36</v>
@@ -10596,13 +10596,13 @@
         <v>1.18</v>
       </c>
       <c r="T63">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="U63">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V63">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="W63">
         <v>1.19</v>
@@ -10620,16 +10620,16 @@
         <v>1.33</v>
       </c>
       <c r="AB63">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AC63">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AD63">
         <v>1.79</v>
       </c>
       <c r="AE63">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AF63">
         <v>1.67</v>
@@ -10904,43 +10904,43 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="O65">
         <v>3.5</v>
       </c>
       <c r="P65">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="Q65">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="R65">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="S65">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T65">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="U65">
         <v>2.1</v>
       </c>
       <c r="V65">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="W65">
         <v>1.17</v>
       </c>
       <c r="X65">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y65">
         <v>1.13</v>
       </c>
       <c r="Z65">
-        <v>4.85</v>
+        <v>6</v>
       </c>
       <c r="AA65">
         <v>1.44</v>
@@ -10949,19 +10949,19 @@
         <v>2.6</v>
       </c>
       <c r="AC65">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AD65">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AE65">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF65">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AG65">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>1.25</v>
       </c>
       <c r="AK65">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,49 +11230,49 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.65</v>
+        <v>2.04</v>
       </c>
       <c r="O67">
         <v>3.35</v>
       </c>
       <c r="P67">
-        <v>2.3</v>
+        <v>3.55</v>
       </c>
       <c r="Q67">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="R67">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S67">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T67">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="U67">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="V67">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W67">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X67">
         <v>1.04</v>
       </c>
       <c r="Y67">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z67">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="AA67">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB67">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AC67">
         <v>3.5</v>
@@ -11284,10 +11284,10 @@
         <v>1.1</v>
       </c>
       <c r="AF67">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AG67">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AK67">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.04</v>
+        <v>2.59</v>
       </c>
       <c r="O69">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="P69">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q69">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="R69">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="S69">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="T69">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="U69">
-        <v>2.8</v>
+        <v>3.33</v>
       </c>
       <c r="V69">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W69">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X69">
         <v>1.04</v>
       </c>
       <c r="Y69">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="Z69">
-        <v>3.08</v>
+        <v>2.85</v>
       </c>
       <c r="AA69">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="AB69">
-        <v>1.79</v>
+        <v>1.61</v>
       </c>
       <c r="AC69">
-        <v>3.5</v>
+        <v>4.15</v>
       </c>
       <c r="AD69">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AE69">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="AF69">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="AG69">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AK69">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,31 +11719,31 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="O70">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="P70">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q70">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R70">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="S70">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="T70">
-        <v>2.59</v>
+        <v>2.93</v>
       </c>
       <c r="U70">
-        <v>3.33</v>
+        <v>2.88</v>
       </c>
       <c r="V70">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W70">
         <v>1.04</v>
@@ -11752,47 +11752,47 @@
         <v>1.04</v>
       </c>
       <c r="Y70">
+        <v>1.32</v>
+      </c>
+      <c r="Z70">
+        <v>3.3</v>
+      </c>
+      <c r="AA70">
+        <v>2</v>
+      </c>
+      <c r="AB70">
+        <v>1.78</v>
+      </c>
+      <c r="AC70">
+        <v>3.5</v>
+      </c>
+      <c r="AD70">
+        <v>1.25</v>
+      </c>
+      <c r="AE70">
+        <v>1.1</v>
+      </c>
+      <c r="AF70">
+        <v>1.74</v>
+      </c>
+      <c r="AG70">
+        <v>1.98</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ70">
         <v>1.44</v>
       </c>
-      <c r="Z70">
-        <v>2.85</v>
-      </c>
-      <c r="AA70">
-        <v>2.35</v>
-      </c>
-      <c r="AB70">
-        <v>1.61</v>
-      </c>
-      <c r="AC70">
-        <v>4.15</v>
-      </c>
-      <c r="AD70">
-        <v>1.17</v>
-      </c>
-      <c r="AE70">
-        <v>1.02</v>
-      </c>
-      <c r="AF70">
-        <v>1.94</v>
-      </c>
-      <c r="AG70">
-        <v>1.77</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ70">
-        <v>1.36</v>
-      </c>
       <c r="AK70">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11885,10 +11885,10 @@
         <v>1.44</v>
       </c>
       <c r="O71">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="P71">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -11921,10 +11921,10 @@
         <v>0</v>
       </c>
       <c r="AA71">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AB71">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AC71">
         <v>0</v>
@@ -12045,16 +12045,16 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="O72">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="P72">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="Q72">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="R72">
         <v>2.36</v>
@@ -12066,22 +12066,22 @@
         <v>3.55</v>
       </c>
       <c r="U72">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="V72">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="W72">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X72">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y72">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z72">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA72">
         <v>1.4</v>
@@ -12090,19 +12090,19 @@
         <v>2.88</v>
       </c>
       <c r="AC72">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="AD72">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AE72">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AF72">
         <v>1.44</v>
       </c>
       <c r="AG72">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>1.22</v>
       </c>
       <c r="AK72">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,80 +12208,80 @@
         </is>
       </c>
       <c r="N73">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="O73">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="P73">
+        <v>1.95</v>
+      </c>
+      <c r="Q73">
+        <v>4</v>
+      </c>
+      <c r="R73">
+        <v>2.4</v>
+      </c>
+      <c r="S73">
+        <v>1.23</v>
+      </c>
+      <c r="T73">
+        <v>3.7</v>
+      </c>
+      <c r="U73">
+        <v>2.21</v>
+      </c>
+      <c r="V73">
+        <v>1.6</v>
+      </c>
+      <c r="W73">
+        <v>1.13</v>
+      </c>
+      <c r="X73">
+        <v>1.02</v>
+      </c>
+      <c r="Y73">
+        <v>1.14</v>
+      </c>
+      <c r="Z73">
+        <v>5.25</v>
+      </c>
+      <c r="AA73">
+        <v>1.53</v>
+      </c>
+      <c r="AB73">
+        <v>2.55</v>
+      </c>
+      <c r="AC73">
+        <v>2.3</v>
+      </c>
+      <c r="AD73">
+        <v>1.58</v>
+      </c>
+      <c r="AE73">
+        <v>1.2</v>
+      </c>
+      <c r="AF73">
         <v>1.47</v>
       </c>
-      <c r="Q73">
-        <v>5</v>
-      </c>
-      <c r="R73">
-        <v>2.49</v>
-      </c>
-      <c r="S73">
+      <c r="AG73">
+        <v>2.55</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ73">
         <v>1.2</v>
       </c>
-      <c r="T73">
-        <v>4.2</v>
-      </c>
-      <c r="U73">
-        <v>1.97</v>
-      </c>
-      <c r="V73">
-        <v>1.85</v>
-      </c>
-      <c r="W73">
-        <v>1.17</v>
-      </c>
-      <c r="X73">
-        <v>1.01</v>
-      </c>
-      <c r="Y73">
-        <v>1.1</v>
-      </c>
-      <c r="Z73">
-        <v>6.5</v>
-      </c>
-      <c r="AA73">
-        <v>1.4</v>
-      </c>
-      <c r="AB73">
-        <v>2.88</v>
-      </c>
-      <c r="AC73">
-        <v>2.12</v>
-      </c>
-      <c r="AD73">
-        <v>1.71</v>
-      </c>
-      <c r="AE73">
-        <v>1.33</v>
-      </c>
-      <c r="AF73">
-        <v>1.5</v>
-      </c>
-      <c r="AG73">
-        <v>2.45</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ73">
-        <v>1.15</v>
-      </c>
       <c r="AK73">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="O75">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="P75">
-        <v>1.95</v>
+        <v>1.47</v>
       </c>
       <c r="Q75">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R75">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="S75">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T75">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="U75">
-        <v>2.21</v>
+        <v>1.97</v>
       </c>
       <c r="V75">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="W75">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X75">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y75">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z75">
-        <v>5.25</v>
+        <v>6.5</v>
       </c>
       <c r="AA75">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AB75">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="AC75">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="AD75">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="AE75">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AF75">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG75">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AK75">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -13029,13 +13029,13 @@
         <v>3.25</v>
       </c>
       <c r="P78">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="Q78">
         <v>2.5</v>
       </c>
       <c r="R78">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S78">
         <v>1.3</v>
@@ -13074,7 +13074,7 @@
         <v>1.4</v>
       </c>
       <c r="AE78">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF78">
         <v>1.57</v>
@@ -13186,7 +13186,7 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="O79">
         <v>3.5</v>
@@ -13195,25 +13195,25 @@
         <v>3.75</v>
       </c>
       <c r="Q79">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="R79">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="S79">
         <v>1.34</v>
       </c>
       <c r="T79">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="U79">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="V79">
         <v>1.42</v>
       </c>
       <c r="W79">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X79">
         <v>1.03</v>
@@ -13222,7 +13222,7 @@
         <v>1.25</v>
       </c>
       <c r="Z79">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="AA79">
         <v>1.85</v>
@@ -13231,13 +13231,13 @@
         <v>1.85</v>
       </c>
       <c r="AC79">
-        <v>3.31</v>
+        <v>3.33</v>
       </c>
       <c r="AD79">
         <v>1.3</v>
       </c>
       <c r="AE79">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF79">
         <v>1.75</v>
@@ -13259,7 +13259,7 @@
         <v>1.29</v>
       </c>
       <c r="AK79">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13358,34 +13358,34 @@
         <v>1.71</v>
       </c>
       <c r="Q80">
-        <v>4.9</v>
+        <v>4.94</v>
       </c>
       <c r="R80">
         <v>2.25</v>
       </c>
       <c r="S80">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T80">
-        <v>2.84</v>
+        <v>3.3</v>
       </c>
       <c r="U80">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="V80">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W80">
         <v>1.07</v>
       </c>
       <c r="X80">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y80">
         <v>1.25</v>
       </c>
       <c r="Z80">
-        <v>3.58</v>
+        <v>4.1</v>
       </c>
       <c r="AA80">
         <v>1.75</v>
@@ -13394,19 +13394,19 @@
         <v>2.05</v>
       </c>
       <c r="AC80">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="AD80">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AE80">
         <v>1.1</v>
       </c>
       <c r="AF80">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG80">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK80">
         <v>1.14</v>
@@ -13512,7 +13512,7 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O81">
         <v>3.4</v>
@@ -13551,10 +13551,10 @@
         <v>0</v>
       </c>
       <c r="AA81">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB81">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC81">
         <v>0</v>
@@ -13675,31 +13675,31 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O82">
         <v>3.25</v>
       </c>
       <c r="P82">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q82">
-        <v>3.02</v>
+        <v>3.11</v>
       </c>
       <c r="R82">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="S82">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T82">
         <v>3.25</v>
       </c>
       <c r="U82">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="V82">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W82">
         <v>1.11</v>
@@ -13711,28 +13711,28 @@
         <v>1.22</v>
       </c>
       <c r="Z82">
-        <v>4.43</v>
+        <v>4.53</v>
       </c>
       <c r="AA82">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AB82">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC82">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="AD82">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AE82">
         <v>1.13</v>
       </c>
       <c r="AF82">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AG82">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AK82">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13841,61 +13841,61 @@
         <v>2.2</v>
       </c>
       <c r="O83">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P83">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="Q83">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R83">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="S83">
         <v>1.3</v>
       </c>
       <c r="T83">
-        <v>3.32</v>
+        <v>3.22</v>
       </c>
       <c r="U83">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V83">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W83">
+        <v>1.1</v>
+      </c>
+      <c r="X83">
+        <v>1.02</v>
+      </c>
+      <c r="Y83">
+        <v>1.19</v>
+      </c>
+      <c r="Z83">
+        <v>3.8</v>
+      </c>
+      <c r="AA83">
+        <v>1.73</v>
+      </c>
+      <c r="AB83">
+        <v>2.1</v>
+      </c>
+      <c r="AC83">
+        <v>2.97</v>
+      </c>
+      <c r="AD83">
+        <v>1.37</v>
+      </c>
+      <c r="AE83">
         <v>1.11</v>
       </c>
-      <c r="X83">
-        <v>1.01</v>
-      </c>
-      <c r="Y83">
-        <v>1.18</v>
-      </c>
-      <c r="Z83">
-        <v>4.33</v>
-      </c>
-      <c r="AA83">
-        <v>1.64</v>
-      </c>
-      <c r="AB83">
-        <v>2.14</v>
-      </c>
-      <c r="AC83">
-        <v>2.75</v>
-      </c>
-      <c r="AD83">
-        <v>1.41</v>
-      </c>
-      <c r="AE83">
-        <v>1.14</v>
-      </c>
       <c r="AF83">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="AG83">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,7 +13908,7 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK83">
         <v>1.55</v>
@@ -14001,7 +14001,7 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="O84">
         <v>3</v>
@@ -14010,7 +14010,7 @@
         <v>2.37</v>
       </c>
       <c r="Q84">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="R84">
         <v>2.1</v>
@@ -14037,7 +14037,7 @@
         <v>1.25</v>
       </c>
       <c r="Z84">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AA84">
         <v>1.85</v>
@@ -14055,7 +14055,7 @@
         <v>1.08</v>
       </c>
       <c r="AF84">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AG84">
         <v>2.1</v>
@@ -14363,13 +14363,13 @@
         <v>1.32</v>
       </c>
       <c r="Z86">
-        <v>3.08</v>
+        <v>3.35</v>
       </c>
       <c r="AA86">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AB86">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AC86">
         <v>2.75</v>
@@ -14499,10 +14499,10 @@
         <v>2.28</v>
       </c>
       <c r="Q87">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="R87">
-        <v>2.24</v>
+        <v>2.29</v>
       </c>
       <c r="S87">
         <v>1.3</v>
@@ -14523,7 +14523,7 @@
         <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z87">
         <v>4.25</v>
@@ -14532,7 +14532,7 @@
         <v>1.76</v>
       </c>
       <c r="AB87">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AC87">
         <v>2.63</v>
@@ -14547,7 +14547,7 @@
         <v>1.53</v>
       </c>
       <c r="AG87">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.9</v>
+        <v>1.46</v>
       </c>
       <c r="O89">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="P89">
-        <v>2.15</v>
+        <v>6</v>
       </c>
       <c r="Q89">
-        <v>3.2</v>
+        <v>2.02</v>
       </c>
       <c r="R89">
-        <v>2.25</v>
+        <v>2.73</v>
       </c>
       <c r="S89">
-        <v>1.37</v>
+        <v>1.17</v>
       </c>
       <c r="T89">
-        <v>3.02</v>
+        <v>3.9</v>
       </c>
       <c r="U89">
-        <v>2.88</v>
+        <v>2</v>
       </c>
       <c r="V89">
+        <v>1.73</v>
+      </c>
+      <c r="W89">
+        <v>1.17</v>
+      </c>
+      <c r="X89">
+        <v>1.02</v>
+      </c>
+      <c r="Y89">
+        <v>1.1</v>
+      </c>
+      <c r="Z89">
+        <v>5.2</v>
+      </c>
+      <c r="AA89">
         <v>1.4</v>
       </c>
-      <c r="W89">
-        <v>1.1</v>
-      </c>
-      <c r="X89">
-        <v>1.03</v>
-      </c>
-      <c r="Y89">
-        <v>1.24</v>
-      </c>
-      <c r="Z89">
-        <v>3.5</v>
-      </c>
-      <c r="AA89">
-        <v>1.86</v>
-      </c>
       <c r="AB89">
-        <v>1.82</v>
+        <v>2.7</v>
       </c>
       <c r="AC89">
-        <v>3.32</v>
+        <v>2.05</v>
       </c>
       <c r="AD89">
-        <v>1.3</v>
+        <v>1.66</v>
       </c>
       <c r="AE89">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="AF89">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AG89">
-        <v>2.1</v>
+        <v>2.39</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK89">
-        <v>1.36</v>
+        <v>2.3</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.46</v>
+        <v>2.9</v>
       </c>
       <c r="O90">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="P90">
-        <v>6</v>
+        <v>2.15</v>
       </c>
       <c r="Q90">
-        <v>2.02</v>
+        <v>3.2</v>
       </c>
       <c r="R90">
-        <v>2.73</v>
+        <v>2.25</v>
       </c>
       <c r="S90">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="T90">
-        <v>3.9</v>
+        <v>3.02</v>
       </c>
       <c r="U90">
-        <v>2</v>
+        <v>2.88</v>
       </c>
       <c r="V90">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="W90">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X90">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y90">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="Z90">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA90">
-        <v>1.4</v>
+        <v>1.86</v>
       </c>
       <c r="AB90">
-        <v>2.7</v>
+        <v>1.82</v>
       </c>
       <c r="AC90">
-        <v>2.05</v>
+        <v>3.32</v>
       </c>
       <c r="AD90">
-        <v>1.66</v>
+        <v>1.3</v>
       </c>
       <c r="AE90">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AF90">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AG90">
-        <v>2.39</v>
+        <v>2.1</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK90">
-        <v>2.3</v>
+        <v>1.36</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,80 +15305,80 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.7</v>
+        <v>2.14</v>
       </c>
       <c r="O92">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P92">
-        <v>2.17</v>
+        <v>2.75</v>
       </c>
       <c r="Q92">
-        <v>3.27</v>
+        <v>2.96</v>
       </c>
       <c r="R92">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="S92">
         <v>1.22</v>
       </c>
       <c r="T92">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="U92">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="V92">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W92">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X92">
         <v>1.01</v>
       </c>
       <c r="Y92">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z92">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA92">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB92">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="AC92">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="AD92">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AE92">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF92">
+        <v>1.44</v>
+      </c>
+      <c r="AG92">
+        <v>2.5</v>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ92">
+        <v>1.44</v>
+      </c>
+      <c r="AK92">
         <v>1.53</v>
-      </c>
-      <c r="AG92">
-        <v>2.47</v>
-      </c>
-      <c r="AH92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ92">
-        <v>1.29</v>
-      </c>
-      <c r="AK92">
-        <v>1.44</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,80 +15468,80 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.14</v>
+        <v>2.7</v>
       </c>
       <c r="O93">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P93">
-        <v>2.75</v>
+        <v>2.17</v>
       </c>
       <c r="Q93">
-        <v>2.96</v>
+        <v>3.27</v>
       </c>
       <c r="R93">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="S93">
         <v>1.22</v>
       </c>
       <c r="T93">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="U93">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="V93">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W93">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X93">
         <v>1.01</v>
       </c>
       <c r="Y93">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z93">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="AA93">
+        <v>1.57</v>
+      </c>
+      <c r="AB93">
+        <v>2.35</v>
+      </c>
+      <c r="AC93">
+        <v>2.35</v>
+      </c>
+      <c r="AD93">
+        <v>1.47</v>
+      </c>
+      <c r="AE93">
+        <v>1.2</v>
+      </c>
+      <c r="AF93">
         <v>1.53</v>
       </c>
-      <c r="AB93">
-        <v>2.55</v>
-      </c>
-      <c r="AC93">
-        <v>2.37</v>
-      </c>
-      <c r="AD93">
-        <v>1.6</v>
-      </c>
-      <c r="AE93">
-        <v>1.22</v>
-      </c>
-      <c r="AF93">
+      <c r="AG93">
+        <v>2.47</v>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ93">
+        <v>1.29</v>
+      </c>
+      <c r="AK93">
         <v>1.44</v>
-      </c>
-      <c r="AG93">
-        <v>2.5</v>
-      </c>
-      <c r="AH93" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI93" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ93">
-        <v>1.44</v>
-      </c>
-      <c r="AK93">
-        <v>1.53</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15957,16 +15957,16 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.53</v>
+        <v>2.42</v>
       </c>
       <c r="O96">
         <v>3.8</v>
       </c>
       <c r="P96">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="Q96">
-        <v>3.02</v>
+        <v>2.78</v>
       </c>
       <c r="R96">
         <v>2.3</v>
@@ -15975,13 +15975,13 @@
         <v>1.25</v>
       </c>
       <c r="T96">
-        <v>3.48</v>
+        <v>3.58</v>
       </c>
       <c r="U96">
         <v>2.15</v>
       </c>
       <c r="V96">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="W96">
         <v>1.18</v>
@@ -15990,25 +15990,25 @@
         <v>1.02</v>
       </c>
       <c r="Y96">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z96">
-        <v>5</v>
+        <v>5.35</v>
       </c>
       <c r="AA96">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AB96">
-        <v>2.81</v>
+        <v>2.94</v>
       </c>
       <c r="AC96">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AD96">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AE96">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF96">
         <v>1.33</v>
@@ -16030,7 +16030,7 @@
         <v>1.25</v>
       </c>
       <c r="AK96">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16129,10 +16129,10 @@
         <v>2.4</v>
       </c>
       <c r="Q97">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="R97">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="S97">
         <v>1.25</v>
@@ -16141,43 +16141,43 @@
         <v>3.5</v>
       </c>
       <c r="U97">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="V97">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W97">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X97">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y97">
         <v>1.13</v>
       </c>
       <c r="Z97">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="AA97">
         <v>1.55</v>
       </c>
       <c r="AB97">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AC97">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="AD97">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AE97">
         <v>1.15</v>
       </c>
       <c r="AF97">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AG97">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16193,7 +16193,7 @@
         <v>1.22</v>
       </c>
       <c r="AK97">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16446,19 +16446,19 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="O99">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P99">
         <v>3.5</v>
       </c>
       <c r="Q99">
-        <v>2.59</v>
+        <v>2.68</v>
       </c>
       <c r="R99">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="S99">
         <v>1.39</v>
@@ -16467,10 +16467,10 @@
         <v>2.99</v>
       </c>
       <c r="U99">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="V99">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="W99">
         <v>1.1</v>
@@ -16482,25 +16482,25 @@
         <v>1.29</v>
       </c>
       <c r="Z99">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="AA99">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AB99">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AC99">
         <v>3.25</v>
       </c>
       <c r="AD99">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE99">
         <v>1.1</v>
       </c>
       <c r="AF99">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG99">
         <v>2</v>
@@ -16519,7 +16519,7 @@
         <v>1.3</v>
       </c>
       <c r="AK99">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16609,16 +16609,16 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="O100">
         <v>3.5</v>
       </c>
       <c r="P100">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="Q100">
-        <v>3.54</v>
+        <v>3.78</v>
       </c>
       <c r="R100">
         <v>2.33</v>
@@ -16627,10 +16627,10 @@
         <v>1.33</v>
       </c>
       <c r="T100">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U100">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="V100">
         <v>1.46</v>
@@ -16645,7 +16645,7 @@
         <v>1.21</v>
       </c>
       <c r="Z100">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AA100">
         <v>1.79</v>
@@ -16679,7 +16679,7 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AK100">
         <v>1.36</v>
@@ -16772,28 +16772,28 @@
         </is>
       </c>
       <c r="N101">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="O101">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="P101">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="Q101">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="R101">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="S101">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T101">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="U101">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="V101">
         <v>1.91</v>
@@ -16805,31 +16805,31 @@
         <v>1.01</v>
       </c>
       <c r="Y101">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Z101">
-        <v>7.7</v>
+        <v>6.75</v>
       </c>
       <c r="AA101">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AB101">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AC101">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AD101">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AE101">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF101">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AG101">
-        <v>3.08</v>
+        <v>2.6</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.14</v>
+        <v>2.3</v>
       </c>
       <c r="AK101">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16959,7 +16959,7 @@
         <v>3.12</v>
       </c>
       <c r="V102">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W102">
         <v>1.05</v>
@@ -16977,7 +16977,7 @@
         <v>2.17</v>
       </c>
       <c r="AB102">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AC102">
         <v>4.18</v>
@@ -16992,7 +16992,7 @@
         <v>2</v>
       </c>
       <c r="AG102">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17104,7 +17104,7 @@
         <v>3.24</v>
       </c>
       <c r="P103">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17424,10 +17424,10 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O105">
-        <v>3.19</v>
+        <v>3.3</v>
       </c>
       <c r="P105">
         <v>2.83</v>
@@ -17460,16 +17460,16 @@
         <v>1.29</v>
       </c>
       <c r="Z105">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="AA105">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AB105">
         <v>1.92</v>
       </c>
       <c r="AC105">
-        <v>3.28</v>
+        <v>3.37</v>
       </c>
       <c r="AD105">
         <v>1.29</v>
@@ -17587,25 +17587,25 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="O106">
+        <v>3.65</v>
+      </c>
+      <c r="P106">
+        <v>3.7</v>
+      </c>
+      <c r="Q106">
+        <v>2.24</v>
+      </c>
+      <c r="R106">
+        <v>2.25</v>
+      </c>
+      <c r="S106">
+        <v>1.19</v>
+      </c>
+      <c r="T106">
         <v>4.2</v>
-      </c>
-      <c r="P106">
-        <v>4.6</v>
-      </c>
-      <c r="Q106">
-        <v>1.94</v>
-      </c>
-      <c r="R106">
-        <v>2.49</v>
-      </c>
-      <c r="S106">
-        <v>1.18</v>
-      </c>
-      <c r="T106">
-        <v>4.3</v>
       </c>
       <c r="U106">
         <v>1.95</v>
@@ -17620,31 +17620,31 @@
         <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z106">
-        <v>6.25</v>
+        <v>5.9</v>
       </c>
       <c r="AA106">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB106">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AC106">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="AD106">
         <v>1.8</v>
       </c>
       <c r="AE106">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF106">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AG106">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AK106">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17922,10 +17922,10 @@
         <v>3.7</v>
       </c>
       <c r="Q108">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="R108">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="S108">
         <v>1.25</v>
@@ -17952,10 +17952,10 @@
         <v>4.8</v>
       </c>
       <c r="AA108">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AB108">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="AC108">
         <v>2.33</v>
@@ -17970,7 +17970,7 @@
         <v>1.53</v>
       </c>
       <c r="AG108">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK108">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18079,7 +18079,7 @@
         <v>2.35</v>
       </c>
       <c r="O109">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="P109">
         <v>3.05</v>
@@ -18149,7 +18149,7 @@
         <v>1.4</v>
       </c>
       <c r="AK109">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18408,7 +18408,7 @@
         <v>2.85</v>
       </c>
       <c r="P111">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="Q111">
         <v>3</v>
@@ -18435,16 +18435,16 @@
         <v>1.11</v>
       </c>
       <c r="Y111">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="Z111">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AA111">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AB111">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC111">
         <v>7</v>
@@ -18459,7 +18459,7 @@
         <v>2.3</v>
       </c>
       <c r="AG111">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>1.4</v>
       </c>
       <c r="AK111">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18568,34 +18568,34 @@
         <v>2.15</v>
       </c>
       <c r="O112">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P112">
+        <v>2.9</v>
+      </c>
+      <c r="Q112">
         <v>2.7</v>
       </c>
-      <c r="Q112">
-        <v>2.63</v>
-      </c>
       <c r="R112">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S112">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="T112">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="U112">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="V112">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="W112">
         <v>1.17</v>
       </c>
       <c r="X112">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y112">
         <v>1.12</v>
@@ -18604,25 +18604,25 @@
         <v>4.7</v>
       </c>
       <c r="AA112">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AB112">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="AC112">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AD112">
         <v>1.54</v>
       </c>
       <c r="AE112">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF112">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AG112">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AK112">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AL112">
         <v>0</v>

--- a/jogos_2026-10-16.xlsx
+++ b/jogos_2026-10-16.xlsx
@@ -938,26 +938,26 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["65", "81", "90+5"]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5", "56"]</t>
         </is>
       </c>
       <c r="AJ4">
@@ -1040,28 +1040,28 @@
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1101,10 +1101,10 @@
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1113,18 +1113,18 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
-        <v>3.63</v>
+        <v>3.32</v>
       </c>
       <c r="O5">
         <v>3.8</v>
@@ -1145,13 +1145,13 @@
         <v>3.9</v>
       </c>
       <c r="U5">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V5">
         <v>1.67</v>
       </c>
       <c r="W5">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X5">
         <v>1.01</v>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["57", "62"]</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["71"]</t>
         </is>
       </c>
       <c r="AJ5">
@@ -1203,28 +1203,28 @@
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1267,13 +1267,13 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -1283,35 +1283,35 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="O6">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P6">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="Q6">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="R6">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="S6">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T6">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="U6">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="V6">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W6">
         <v>1.06</v>
@@ -1320,31 +1320,31 @@
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z6">
-        <v>3.41</v>
+        <v>3.08</v>
       </c>
       <c r="AA6">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="AB6">
         <v>1.85</v>
       </c>
       <c r="AC6">
-        <v>3.05</v>
+        <v>3.28</v>
       </c>
       <c r="AD6">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AE6">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF6">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG6">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1353,41 +1353,41 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["27"]</t>
         </is>
       </c>
       <c r="AJ6">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK6">
+        <v>1.87</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>3</v>
+      </c>
+      <c r="AN6">
         <v>2</v>
       </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>-1</v>
-      </c>
-      <c r="AN6">
-        <v>-1</v>
-      </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1442,21 +1442,21 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="O7">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P7">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="Q7">
         <v>3.09</v>
@@ -1468,16 +1468,16 @@
         <v>1.3</v>
       </c>
       <c r="T7">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U7">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="V7">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W7">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X7">
         <v>1</v>
@@ -1489,10 +1489,10 @@
         <v>3.58</v>
       </c>
       <c r="AA7">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB7">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AC7">
         <v>2.88</v>
@@ -1507,7 +1507,7 @@
         <v>1.47</v>
       </c>
       <c r="AG7">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["62", "75"]</t>
         </is>
       </c>
       <c r="AJ7">
@@ -1529,28 +1529,28 @@
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
@@ -1692,28 +1692,28 @@
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -1765,14 +1765,14 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["83"]</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -1855,28 +1855,28 @@
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -1916,26 +1916,26 @@
         </is>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["51", "78", "90"]</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["26", "71", "90+2"]</t>
         </is>
       </c>
       <c r="AJ10">
@@ -2018,28 +2018,28 @@
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2079,26 +2079,26 @@
         </is>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["14", "78", "90+8"]</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["59", "90+9"]</t>
         </is>
       </c>
       <c r="AJ11">
@@ -2181,28 +2181,28 @@
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN11">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2245,13 +2245,13 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["21"]</t>
         </is>
       </c>
       <c r="AJ12">
@@ -2344,28 +2344,28 @@
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -2408,23 +2408,23 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
@@ -2437,7 +2437,7 @@
         <v>2.5</v>
       </c>
       <c r="Q13">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="R13">
         <v>2.11</v>
@@ -2449,10 +2449,10 @@
         <v>3.4</v>
       </c>
       <c r="U13">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="V13">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W13">
         <v>1.11</v>
@@ -2461,22 +2461,22 @@
         <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z13">
         <v>3.86</v>
       </c>
       <c r="AA13">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AB13">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AC13">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="AD13">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AE13">
         <v>1.11</v>
@@ -2494,41 +2494,41 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["36", "78", "83", "87"]</t>
         </is>
       </c>
       <c r="AJ13">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="AK13">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -2571,36 +2571,36 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14">
         <v>2.45</v>
       </c>
       <c r="O14">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P14">
         <v>2.5</v>
       </c>
       <c r="Q14">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="R14">
         <v>2.24</v>
@@ -2615,28 +2615,28 @@
         <v>2.25</v>
       </c>
       <c r="V14">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W14">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X14">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
         <v>1.14</v>
       </c>
       <c r="Z14">
-        <v>4.33</v>
+        <v>3.13</v>
       </c>
       <c r="AA14">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="AB14">
         <v>2.17</v>
       </c>
       <c r="AC14">
-        <v>2.49</v>
+        <v>2.15</v>
       </c>
       <c r="AD14">
         <v>1.42</v>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+1", "74"]</t>
         </is>
       </c>
       <c r="AJ14">
@@ -2670,28 +2670,28 @@
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN14">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO14">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G15">
@@ -2750,111 +2750,111 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
-        <v>2.25</v>
+        <v>1.35</v>
       </c>
       <c r="O15">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="P15">
-        <v>2.62</v>
+        <v>7.5</v>
       </c>
       <c r="Q15">
-        <v>2.87</v>
+        <v>1.75</v>
       </c>
       <c r="R15">
-        <v>2.08</v>
+        <v>2.43</v>
       </c>
       <c r="S15">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="T15">
-        <v>2.95</v>
+        <v>3.7</v>
       </c>
       <c r="U15">
-        <v>2.48</v>
+        <v>2.22</v>
       </c>
       <c r="V15">
-        <v>1.43</v>
+        <v>1.64</v>
       </c>
       <c r="W15">
+        <v>1.15</v>
+      </c>
+      <c r="X15">
+        <v>1.02</v>
+      </c>
+      <c r="Y15">
+        <v>1.11</v>
+      </c>
+      <c r="Z15">
+        <v>4.95</v>
+      </c>
+      <c r="AA15">
+        <v>1.47</v>
+      </c>
+      <c r="AB15">
+        <v>2.53</v>
+      </c>
+      <c r="AC15">
+        <v>2.22</v>
+      </c>
+      <c r="AD15">
+        <v>1.57</v>
+      </c>
+      <c r="AE15">
+        <v>1.19</v>
+      </c>
+      <c r="AF15">
+        <v>1.73</v>
+      </c>
+      <c r="AG15">
+        <v>2</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15">
         <v>1.1</v>
       </c>
-      <c r="X15">
-        <v>1.04</v>
-      </c>
-      <c r="Y15">
-        <v>1.22</v>
-      </c>
-      <c r="Z15">
-        <v>3.5</v>
-      </c>
-      <c r="AA15">
-        <v>1.79</v>
-      </c>
-      <c r="AB15">
-        <v>1.88</v>
-      </c>
-      <c r="AC15">
-        <v>2.92</v>
-      </c>
-      <c r="AD15">
-        <v>1.31</v>
-      </c>
-      <c r="AE15">
-        <v>1.08</v>
-      </c>
-      <c r="AF15">
-        <v>1.62</v>
-      </c>
-      <c r="AG15">
-        <v>2.1</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15">
-        <v>1.24</v>
-      </c>
       <c r="AK15">
-        <v>1.57</v>
+        <v>2.88</v>
       </c>
       <c r="AL15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN15">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G16">
@@ -2913,68 +2913,68 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
-        <v>1.35</v>
+        <v>2.2</v>
       </c>
       <c r="O16">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="P16">
-        <v>7.5</v>
+        <v>2.7</v>
       </c>
       <c r="Q16">
-        <v>1.75</v>
+        <v>2.87</v>
       </c>
       <c r="R16">
-        <v>2.6</v>
+        <v>2.08</v>
       </c>
       <c r="S16">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="T16">
-        <v>3.7</v>
+        <v>2.95</v>
       </c>
       <c r="U16">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="V16">
+        <v>1.43</v>
+      </c>
+      <c r="W16">
+        <v>1.1</v>
+      </c>
+      <c r="X16">
+        <v>1.01</v>
+      </c>
+      <c r="Y16">
+        <v>1.22</v>
+      </c>
+      <c r="Z16">
+        <v>3.5</v>
+      </c>
+      <c r="AA16">
+        <v>1.84</v>
+      </c>
+      <c r="AB16">
+        <v>1.88</v>
+      </c>
+      <c r="AC16">
+        <v>2.92</v>
+      </c>
+      <c r="AD16">
+        <v>1.25</v>
+      </c>
+      <c r="AE16">
+        <v>1.08</v>
+      </c>
+      <c r="AF16">
         <v>1.62</v>
       </c>
-      <c r="W16">
-        <v>1.15</v>
-      </c>
-      <c r="X16">
-        <v>1.02</v>
-      </c>
-      <c r="Y16">
-        <v>1.11</v>
-      </c>
-      <c r="Z16">
-        <v>4.95</v>
-      </c>
-      <c r="AA16">
-        <v>1.48</v>
-      </c>
-      <c r="AB16">
-        <v>2.55</v>
-      </c>
-      <c r="AC16">
-        <v>2.22</v>
-      </c>
-      <c r="AD16">
-        <v>1.57</v>
-      </c>
-      <c r="AE16">
-        <v>1.19</v>
-      </c>
-      <c r="AF16">
-        <v>1.73</v>
-      </c>
       <c r="AG16">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2990,34 +2990,34 @@
         <v>1.1</v>
       </c>
       <c r="AK16">
-        <v>3.1</v>
+        <v>1.57</v>
       </c>
       <c r="AL16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP16">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3057,16 +3057,16 @@
         </is>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -3076,14 +3076,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
         <v>1.77</v>
       </c>
       <c r="O17">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P17">
         <v>3.85</v>
@@ -3092,16 +3092,16 @@
         <v>2.28</v>
       </c>
       <c r="R17">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="S17">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T17">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="U17">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="V17">
         <v>1.44</v>
@@ -3110,25 +3110,25 @@
         <v>1.11</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z17">
-        <v>3.92</v>
+        <v>3</v>
       </c>
       <c r="AA17">
         <v>1.7</v>
       </c>
       <c r="AB17">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AC17">
         <v>2.66</v>
       </c>
       <c r="AD17">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AE17">
         <v>1.11</v>
@@ -3137,20 +3137,20 @@
         <v>1.62</v>
       </c>
       <c r="AG17">
-        <v>2.12</v>
+        <v>1.9</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["6", "18"]</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["41"]</t>
         </is>
       </c>
       <c r="AJ17">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AK17">
         <v>1.87</v>
@@ -3159,28 +3159,28 @@
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP17">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -3220,130 +3220,130 @@
         </is>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18">
-        <v>6.25</v>
+        <v>5</v>
       </c>
       <c r="O18">
-        <v>4.5</v>
+        <v>4.02</v>
       </c>
       <c r="P18">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="Q18">
-        <v>6.72</v>
+        <v>4.8</v>
       </c>
       <c r="R18">
-        <v>2.8</v>
+        <v>2.47</v>
       </c>
       <c r="S18">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T18">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="U18">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V18">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="W18">
         <v>1.17</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
         <v>1.08</v>
       </c>
       <c r="Z18">
-        <v>5.55</v>
+        <v>5.5</v>
       </c>
       <c r="AA18">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AB18">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="AC18">
-        <v>2.01</v>
+        <v>2.14</v>
       </c>
       <c r="AD18">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AE18">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF18">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AG18">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["52", "69"]</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13", "45", "45+5", "60", "90+6"]</t>
         </is>
       </c>
       <c r="AJ18">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AK18">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="AL18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO18">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         </is>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19">
         <v>0</v>
@@ -3395,14 +3395,14 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N19">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["48"]</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
@@ -3485,28 +3485,28 @@
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN19">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP19">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
@@ -3546,26 +3546,26 @@
         </is>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20">
         <v>0</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N20">
@@ -3630,12 +3630,12 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["55", "72"]</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["32"]</t>
         </is>
       </c>
       <c r="AJ20">
@@ -3648,28 +3648,28 @@
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN20">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO20">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
@@ -3709,130 +3709,130 @@
         </is>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N21">
-        <v>2.12</v>
+        <v>2.72</v>
       </c>
       <c r="O21">
-        <v>3.5</v>
+        <v>3.26</v>
       </c>
       <c r="P21">
-        <v>2.7</v>
+        <v>2.23</v>
       </c>
       <c r="Q21">
-        <v>2.74</v>
+        <v>3.14</v>
       </c>
       <c r="R21">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="S21">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T21">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U21">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="V21">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="W21">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X21">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y21">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z21">
-        <v>4.25</v>
+        <v>4.05</v>
       </c>
       <c r="AA21">
+        <v>1.65</v>
+      </c>
+      <c r="AB21">
+        <v>2.04</v>
+      </c>
+      <c r="AC21">
+        <v>2.75</v>
+      </c>
+      <c r="AD21">
+        <v>1.37</v>
+      </c>
+      <c r="AE21">
+        <v>1.11</v>
+      </c>
+      <c r="AF21">
+        <v>1.53</v>
+      </c>
+      <c r="AG21">
+        <v>2.27</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>["33", "41", "48", "68", "90+1"]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>["40"]</t>
+        </is>
+      </c>
+      <c r="AJ21">
+        <v>1.21</v>
+      </c>
+      <c r="AK21">
+        <v>1.39</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>8</v>
+      </c>
+      <c r="AN21">
+        <v>8</v>
+      </c>
+      <c r="AO21">
+        <v>11</v>
+      </c>
+      <c r="AP21">
+        <v>20</v>
+      </c>
+      <c r="AQ21">
         <v>1.61</v>
       </c>
-      <c r="AB21">
-        <v>2.13</v>
-      </c>
-      <c r="AC21">
-        <v>2.6</v>
-      </c>
-      <c r="AD21">
-        <v>1.4</v>
-      </c>
-      <c r="AE21">
-        <v>1.12</v>
-      </c>
-      <c r="AF21">
-        <v>1.52</v>
-      </c>
-      <c r="AG21">
-        <v>2.4</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21">
-        <v>1.25</v>
-      </c>
-      <c r="AK21">
-        <v>1.62</v>
-      </c>
-      <c r="AL21">
-        <v>0</v>
-      </c>
-      <c r="AM21">
-        <v>-1</v>
-      </c>
-      <c r="AN21">
-        <v>-1</v>
-      </c>
-      <c r="AO21">
-        <v>-1</v>
-      </c>
-      <c r="AP21">
-        <v>-1</v>
-      </c>
-      <c r="AQ21">
-        <v>0</v>
-      </c>
       <c r="AR21">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
@@ -3872,33 +3872,33 @@
         </is>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N22">
         <v>1.11</v>
       </c>
       <c r="O22">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="P22">
         <v>14.39</v>
@@ -3907,95 +3907,95 @@
         <v>1.4</v>
       </c>
       <c r="R22">
-        <v>3.34</v>
+        <v>3.44</v>
       </c>
       <c r="S22">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="T22">
-        <v>5.3</v>
+        <v>5.55</v>
       </c>
       <c r="U22">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="V22">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="W22">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X22">
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Z22">
         <v>8</v>
       </c>
       <c r="AA22">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AB22">
         <v>3.5</v>
       </c>
       <c r="AC22">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AD22">
-        <v>2.03</v>
+        <v>2.17</v>
       </c>
       <c r="AE22">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="AF22">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AG22">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["30", "69"]</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+5"]</t>
         </is>
       </c>
       <c r="AJ22">
         <v>1</v>
       </c>
       <c r="AK22">
-        <v>5.75</v>
+        <v>5.95</v>
       </c>
       <c r="AL22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN22">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -4047,39 +4047,39 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23">
         <v>0</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N23">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="O23">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="P23">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="Q23">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="R23">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S23">
         <v>1.44</v>
       </c>
       <c r="T23">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
       <c r="U23">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="V23">
         <v>1.3</v>
@@ -4091,22 +4091,22 @@
         <v>1.04</v>
       </c>
       <c r="Y23">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z23">
         <v>2.75</v>
       </c>
       <c r="AA23">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AB23">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AC23">
-        <v>4.25</v>
+        <v>3.92</v>
       </c>
       <c r="AD23">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AE23">
         <v>1.03</v>
@@ -4119,7 +4119,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["61"]</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
@@ -4131,34 +4131,34 @@
         <v>1.33</v>
       </c>
       <c r="AK23">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AL23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN23">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO23">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AP23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24">
         <v>0</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -4217,35 +4217,35 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N24">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="O24">
-        <v>3.4</v>
+        <v>3.21</v>
       </c>
       <c r="P24">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="Q24">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="R24">
         <v>2.1</v>
       </c>
       <c r="S24">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T24">
-        <v>2.78</v>
+        <v>2.69</v>
       </c>
       <c r="U24">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="V24">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W24">
         <v>1.06</v>
@@ -4254,10 +4254,10 @@
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z24">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="AA24">
         <v>1.91</v>
@@ -4266,7 +4266,7 @@
         <v>1.8</v>
       </c>
       <c r="AC24">
-        <v>3.14</v>
+        <v>3.34</v>
       </c>
       <c r="AD24">
         <v>1.29</v>
@@ -4287,11 +4287,11 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["33"]</t>
         </is>
       </c>
       <c r="AJ24">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AK24">
         <v>1.91</v>
@@ -4300,28 +4300,28 @@
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN24">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
@@ -4384,22 +4384,22 @@
         </is>
       </c>
       <c r="N25">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="O25">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P25">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q25">
         <v>3.56</v>
       </c>
       <c r="R25">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="S25">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T25">
         <v>3.3</v>
@@ -4411,7 +4411,7 @@
         <v>1.45</v>
       </c>
       <c r="W25">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X25">
         <v>1.01</v>
@@ -4426,7 +4426,7 @@
         <v>1.7</v>
       </c>
       <c r="AB25">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AC25">
         <v>2.56</v>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AK25">
         <v>1.36</v>
@@ -4547,16 +4547,16 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O26">
         <v>3.25</v>
       </c>
       <c r="P26">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="Q26">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="R26">
         <v>2.1</v>
@@ -4565,46 +4565,46 @@
         <v>1.36</v>
       </c>
       <c r="T26">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="U26">
         <v>2.8</v>
       </c>
       <c r="V26">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="W26">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X26">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y26">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z26">
-        <v>2.95</v>
+        <v>3.18</v>
       </c>
       <c r="AA26">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AB26">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AC26">
-        <v>3.46</v>
+        <v>3.24</v>
       </c>
       <c r="AD26">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE26">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF26">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AG26">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK26">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4719,10 +4719,10 @@
         <v>1.6</v>
       </c>
       <c r="Q27">
-        <v>5.4</v>
+        <v>5.45</v>
       </c>
       <c r="R27">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S27">
         <v>1.38</v>
@@ -4731,7 +4731,7 @@
         <v>2.9</v>
       </c>
       <c r="U27">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="V27">
         <v>1.4</v>
@@ -4743,31 +4743,31 @@
         <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z27">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="AA27">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB27">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AC27">
         <v>3.08</v>
       </c>
       <c r="AD27">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE27">
         <v>1.07</v>
       </c>
       <c r="AF27">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AG27">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AK27">
         <v>1.11</v>
@@ -4850,26 +4850,26 @@
         </is>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K28">
         <v>0</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N28">
@@ -4934,12 +4934,12 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["9"]</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["22", "33", "58", "83", "87"]</t>
         </is>
       </c>
       <c r="AJ28">
@@ -4952,28 +4952,28 @@
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO28">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP28">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
@@ -5013,13 +5013,13 @@
         </is>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -5028,11 +5028,11 @@
         <v>0</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N29">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["23"]</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["56", "60"]</t>
         </is>
       </c>
       <c r="AJ29">
@@ -5115,28 +5115,28 @@
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AO29">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP29">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AQ29">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AR29">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AS29">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AT29">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
@@ -5202,52 +5202,52 @@
         <v>1.95</v>
       </c>
       <c r="O30">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="P30">
-        <v>4.1</v>
+        <v>3.77</v>
       </c>
       <c r="Q30">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="R30">
         <v>1.83</v>
       </c>
       <c r="S30">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T30">
         <v>2.5</v>
       </c>
       <c r="U30">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="V30">
         <v>1.22</v>
       </c>
       <c r="W30">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X30">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y30">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Z30">
         <v>2.55</v>
       </c>
       <c r="AA30">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="AB30">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AC30">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="AD30">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AE30">
         <v>1.01</v>
@@ -5272,7 +5272,7 @@
         <v>1.29</v>
       </c>
       <c r="AK30">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5540,22 +5540,22 @@
         <v>2.1</v>
       </c>
       <c r="S32">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T32">
-        <v>2.92</v>
+        <v>2.76</v>
       </c>
       <c r="U32">
-        <v>2.69</v>
+        <v>2.64</v>
       </c>
       <c r="V32">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="W32">
         <v>1.1</v>
       </c>
       <c r="X32">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
         <v>1.25</v>
@@ -5570,13 +5570,13 @@
         <v>1.93</v>
       </c>
       <c r="AC32">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="AD32">
         <v>1.31</v>
       </c>
       <c r="AE32">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF32">
         <v>1.62</v>
@@ -5857,25 +5857,25 @@
         <v>3.1</v>
       </c>
       <c r="P34">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="Q34">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="R34">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="S34">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T34">
-        <v>2.2</v>
+        <v>2.68</v>
       </c>
       <c r="U34">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="V34">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W34">
         <v>1.07</v>
@@ -5884,31 +5884,31 @@
         <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z34">
-        <v>2.5</v>
+        <v>3.13</v>
       </c>
       <c r="AA34">
-        <v>1.78</v>
+        <v>2.02</v>
       </c>
       <c r="AB34">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="AC34">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="AD34">
         <v>1.18</v>
       </c>
       <c r="AE34">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF34">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AG34">
-        <v>1.97</v>
+        <v>1.7</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AK34">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6506,7 +6506,7 @@
         <v>3.35</v>
       </c>
       <c r="O38">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P38">
         <v>1.92</v>
@@ -6515,7 +6515,7 @@
         <v>4.33</v>
       </c>
       <c r="R38">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="S38">
         <v>1.36</v>
@@ -6533,13 +6533,13 @@
         <v>1.07</v>
       </c>
       <c r="X38">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
         <v>1.22</v>
       </c>
       <c r="Z38">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AA38">
         <v>1.8</v>
@@ -6551,16 +6551,16 @@
         <v>2.83</v>
       </c>
       <c r="AD38">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE38">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF38">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG38">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.3</v>
       </c>
       <c r="AK38">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="O40">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="P40">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="Q40">
-        <v>5.76</v>
+        <v>5.85</v>
       </c>
       <c r="R40">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="S40">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T40">
         <v>4</v>
       </c>
       <c r="U40">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="V40">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="W40">
         <v>1.17</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z40">
         <v>6.5</v>
       </c>
       <c r="AA40">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB40">
-        <v>2.82</v>
+        <v>3.02</v>
       </c>
       <c r="AC40">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="AD40">
         <v>1.71</v>
       </c>
       <c r="AE40">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AF40">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG40">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AK40">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7158,7 +7158,7 @@
         <v>2</v>
       </c>
       <c r="O42">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P42">
         <v>3.4</v>
@@ -7167,16 +7167,16 @@
         <v>2.4</v>
       </c>
       <c r="R42">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="S42">
         <v>1.4</v>
       </c>
       <c r="T42">
-        <v>2.75</v>
+        <v>2.58</v>
       </c>
       <c r="U42">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="V42">
         <v>1.35</v>
@@ -7188,31 +7188,31 @@
         <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="Z42">
-        <v>2.38</v>
+        <v>2.78</v>
       </c>
       <c r="AA42">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AB42">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC42">
-        <v>3.86</v>
+        <v>3</v>
       </c>
       <c r="AD42">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AE42">
         <v>1.03</v>
       </c>
       <c r="AF42">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AG42">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AK42">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,16 +7318,16 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="O43">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P43">
         <v>2.7</v>
       </c>
       <c r="Q43">
-        <v>3.07</v>
+        <v>3.3</v>
       </c>
       <c r="R43">
         <v>2.15</v>
@@ -7357,16 +7357,16 @@
         <v>3.27</v>
       </c>
       <c r="AA43">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="AB43">
         <v>1.73</v>
       </c>
       <c r="AC43">
-        <v>3.76</v>
+        <v>3.84</v>
       </c>
       <c r="AD43">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AE43">
         <v>1.02</v>
@@ -7375,7 +7375,7 @@
         <v>1.85</v>
       </c>
       <c r="AG43">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7810,10 +7810,10 @@
         <v>2.1</v>
       </c>
       <c r="O46">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P46">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="Q46">
         <v>2.45</v>
@@ -7825,16 +7825,16 @@
         <v>1.2</v>
       </c>
       <c r="T46">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="U46">
         <v>2.21</v>
       </c>
       <c r="V46">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="W46">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X46">
         <v>1.02</v>
@@ -7843,13 +7843,13 @@
         <v>1.17</v>
       </c>
       <c r="Z46">
-        <v>5.24</v>
+        <v>5</v>
       </c>
       <c r="AA46">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AB46">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="AC46">
         <v>2.25</v>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK46">
         <v>1.73</v>
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O51">
         <v>3.3</v>
       </c>
       <c r="P51">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="AA51">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AB51">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.55</v>
+        <v>3.08</v>
       </c>
       <c r="O52">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="P52">
-        <v>4.8</v>
+        <v>2.25</v>
       </c>
       <c r="Q52">
-        <v>1.95</v>
+        <v>3.69</v>
       </c>
       <c r="R52">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="S52">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="T52">
-        <v>3.9</v>
+        <v>3.08</v>
       </c>
       <c r="U52">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="V52">
+        <v>1.51</v>
+      </c>
+      <c r="W52">
+        <v>1.12</v>
+      </c>
+      <c r="X52">
+        <v>1.03</v>
+      </c>
+      <c r="Y52">
+        <v>1.18</v>
+      </c>
+      <c r="Z52">
+        <v>3.84</v>
+      </c>
+      <c r="AA52">
         <v>1.7</v>
       </c>
-      <c r="W52">
-        <v>1.17</v>
-      </c>
-      <c r="X52">
-        <v>1.01</v>
-      </c>
-      <c r="Y52">
-        <v>1.15</v>
-      </c>
-      <c r="Z52">
-        <v>5.25</v>
-      </c>
-      <c r="AA52">
-        <v>1.4</v>
-      </c>
       <c r="AB52">
-        <v>2.75</v>
+        <v>2.07</v>
       </c>
       <c r="AC52">
-        <v>2.15</v>
+        <v>2.89</v>
       </c>
       <c r="AD52">
-        <v>1.68</v>
+        <v>1.41</v>
       </c>
       <c r="AE52">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="AF52">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AG52">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.14</v>
+        <v>1.64</v>
       </c>
       <c r="AK52">
-        <v>2.4</v>
+        <v>1.33</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,80 +8948,80 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.89</v>
+        <v>1.53</v>
       </c>
       <c r="O53">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="P53">
-        <v>2.2</v>
+        <v>5.25</v>
       </c>
       <c r="Q53">
-        <v>3.62</v>
+        <v>1.85</v>
       </c>
       <c r="R53">
-        <v>2.32</v>
+        <v>2.7</v>
       </c>
       <c r="S53">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="T53">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="U53">
-        <v>2.43</v>
+        <v>2.1</v>
       </c>
       <c r="V53">
-        <v>1.56</v>
+        <v>1.81</v>
       </c>
       <c r="W53">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X53">
         <v>1.01</v>
       </c>
       <c r="Y53">
+        <v>1.08</v>
+      </c>
+      <c r="Z53">
+        <v>5.35</v>
+      </c>
+      <c r="AA53">
+        <v>1.4</v>
+      </c>
+      <c r="AB53">
+        <v>2.59</v>
+      </c>
+      <c r="AC53">
+        <v>2.05</v>
+      </c>
+      <c r="AD53">
+        <v>1.71</v>
+      </c>
+      <c r="AE53">
+        <v>1.26</v>
+      </c>
+      <c r="AF53">
+        <v>1.52</v>
+      </c>
+      <c r="AG53">
+        <v>2.37</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ53">
         <v>1.14</v>
       </c>
-      <c r="Z53">
-        <v>4.4</v>
-      </c>
-      <c r="AA53">
-        <v>1.67</v>
-      </c>
-      <c r="AB53">
-        <v>2.24</v>
-      </c>
-      <c r="AC53">
-        <v>2.68</v>
-      </c>
-      <c r="AD53">
-        <v>1.47</v>
-      </c>
-      <c r="AE53">
-        <v>1.18</v>
-      </c>
-      <c r="AF53">
-        <v>1.53</v>
-      </c>
-      <c r="AG53">
-        <v>2.39</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ53">
-        <v>1.18</v>
-      </c>
       <c r="AK53">
-        <v>1.35</v>
+        <v>2.5</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,19 +9111,19 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="O54">
-        <v>3.93</v>
+        <v>3.83</v>
       </c>
       <c r="P54">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="Q54">
         <v>3</v>
       </c>
       <c r="R54">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="S54">
         <v>1.17</v>
@@ -9135,10 +9135,10 @@
         <v>2.12</v>
       </c>
       <c r="V54">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="W54">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X54">
         <v>1.01</v>
@@ -9147,28 +9147,28 @@
         <v>1.08</v>
       </c>
       <c r="Z54">
-        <v>5.65</v>
+        <v>6.86</v>
       </c>
       <c r="AA54">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AB54">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="AC54">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AD54">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AE54">
+        <v>1.28</v>
+      </c>
+      <c r="AF54">
         <v>1.35</v>
       </c>
-      <c r="AF54">
-        <v>1.4</v>
-      </c>
       <c r="AG54">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.23</v>
+        <v>1.62</v>
       </c>
       <c r="AK54">
         <v>1.34</v>
@@ -9274,19 +9274,19 @@
         </is>
       </c>
       <c r="N55">
-        <v>3.85</v>
+        <v>3.61</v>
       </c>
       <c r="O55">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="P55">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Q55">
         <v>3.74</v>
       </c>
       <c r="R55">
-        <v>2.82</v>
+        <v>2.63</v>
       </c>
       <c r="S55">
         <v>1.14</v>
@@ -9298,7 +9298,7 @@
         <v>2.01</v>
       </c>
       <c r="V55">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="W55">
         <v>1.21</v>
@@ -9316,10 +9316,10 @@
         <v>1.27</v>
       </c>
       <c r="AB55">
-        <v>3.33</v>
+        <v>3.36</v>
       </c>
       <c r="AC55">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AD55">
         <v>2.04</v>
@@ -9344,7 +9344,7 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.2</v>
+        <v>1.91</v>
       </c>
       <c r="AK55">
         <v>1.25</v>
@@ -9437,16 +9437,16 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="O56">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P56">
-        <v>2.32</v>
+        <v>2.07</v>
       </c>
       <c r="Q56">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="R56">
         <v>2</v>
@@ -9455,7 +9455,7 @@
         <v>1.4</v>
       </c>
       <c r="T56">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="U56">
         <v>2.9</v>
@@ -9464,10 +9464,10 @@
         <v>1.36</v>
       </c>
       <c r="W56">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X56">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y56">
         <v>1.36</v>
@@ -9485,7 +9485,7 @@
         <v>4.1</v>
       </c>
       <c r="AD56">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE56">
         <v>1.04</v>
@@ -9507,7 +9507,7 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AK56">
         <v>1.36</v>
@@ -9600,7 +9600,7 @@
         </is>
       </c>
       <c r="N57">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="O57">
         <v>3.65</v>
@@ -9609,10 +9609,10 @@
         <v>1.79</v>
       </c>
       <c r="Q57">
-        <v>4.26</v>
+        <v>4.21</v>
       </c>
       <c r="R57">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="S57">
         <v>1.22</v>
@@ -9621,10 +9621,10 @@
         <v>3.75</v>
       </c>
       <c r="U57">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="V57">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="W57">
         <v>1.15</v>
@@ -9633,31 +9633,31 @@
         <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z57">
-        <v>5.69</v>
+        <v>5.75</v>
       </c>
       <c r="AA57">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AB57">
         <v>2.52</v>
       </c>
       <c r="AC57">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AD57">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AE57">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AF57">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AG57">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AK57">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,16 +9763,16 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O58">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P58">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q58">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="R58">
         <v>2.48</v>
@@ -9781,16 +9781,16 @@
         <v>1.29</v>
       </c>
       <c r="T58">
-        <v>3.23</v>
+        <v>3.32</v>
       </c>
       <c r="U58">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="V58">
         <v>1.5</v>
       </c>
       <c r="W58">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X58">
         <v>1.01</v>
@@ -9805,22 +9805,22 @@
         <v>1.71</v>
       </c>
       <c r="AB58">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AC58">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="AD58">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="AE58">
         <v>1.14</v>
       </c>
       <c r="AF58">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AG58">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK58">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9938,7 +9938,7 @@
         <v>2.7</v>
       </c>
       <c r="R59">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="S59">
         <v>1.22</v>
@@ -9962,7 +9962,7 @@
         <v>1.14</v>
       </c>
       <c r="Z59">
-        <v>5.5</v>
+        <v>4.98</v>
       </c>
       <c r="AA59">
         <v>1.58</v>
@@ -9983,7 +9983,7 @@
         <v>1.46</v>
       </c>
       <c r="AG59">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK59">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10089,34 +10089,34 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="O60">
         <v>3.55</v>
       </c>
       <c r="P60">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="Q60">
-        <v>2.93</v>
+        <v>3.32</v>
       </c>
       <c r="R60">
         <v>2.4</v>
       </c>
       <c r="S60">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T60">
         <v>4</v>
       </c>
       <c r="U60">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="V60">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="W60">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X60">
         <v>1.02</v>
@@ -10125,28 +10125,28 @@
         <v>1.08</v>
       </c>
       <c r="Z60">
-        <v>5.7</v>
+        <v>5.45</v>
       </c>
       <c r="AA60">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AB60">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="AC60">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AD60">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AE60">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AF60">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AG60">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AK60">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10294,16 +10294,16 @@
         <v>1.44</v>
       </c>
       <c r="AB61">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="AC61">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="AD61">
         <v>1.59</v>
       </c>
       <c r="AE61">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF61">
         <v>1.62</v>
@@ -10424,25 +10424,25 @@
         <v>2.4</v>
       </c>
       <c r="Q62">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="R62">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="S62">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T62">
-        <v>3.27</v>
+        <v>3.29</v>
       </c>
       <c r="U62">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="V62">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="W62">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X62">
         <v>1.03</v>
@@ -10454,25 +10454,25 @@
         <v>4.1</v>
       </c>
       <c r="AA62">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AB62">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="AC62">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AD62">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AE62">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF62">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AG62">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK62">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,16 +10578,16 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="O63">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="P63">
-        <v>8.5</v>
+        <v>9.08</v>
       </c>
       <c r="Q63">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="R63">
         <v>2.8</v>
@@ -10596,13 +10596,13 @@
         <v>1.18</v>
       </c>
       <c r="T63">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U63">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V63">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="W63">
         <v>1.19</v>
@@ -10614,28 +10614,28 @@
         <v>1.07</v>
       </c>
       <c r="Z63">
-        <v>6.25</v>
+        <v>6.15</v>
       </c>
       <c r="AA63">
         <v>1.33</v>
       </c>
       <c r="AB63">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AC63">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AD63">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="AE63">
         <v>1.33</v>
       </c>
       <c r="AF63">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG63">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AK63">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10904,7 +10904,7 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="O65">
         <v>3.5</v>
@@ -10949,7 +10949,7 @@
         <v>2.6</v>
       </c>
       <c r="AC65">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="AD65">
         <v>1.65</v>
@@ -11082,13 +11082,13 @@
         <v>2.14</v>
       </c>
       <c r="S66">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T66">
         <v>3.02</v>
       </c>
       <c r="U66">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V66">
         <v>1.46</v>
@@ -11106,7 +11106,7 @@
         <v>3.48</v>
       </c>
       <c r="AA66">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AB66">
         <v>1.97</v>
@@ -11115,10 +11115,10 @@
         <v>2.88</v>
       </c>
       <c r="AD66">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE66">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF66">
         <v>1.67</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
       <c r="O67">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="P67">
-        <v>3.55</v>
+        <v>4.12</v>
       </c>
       <c r="Q67">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="R67">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="S67">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T67">
-        <v>2.88</v>
+        <v>3.46</v>
       </c>
       <c r="U67">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="V67">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="W67">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X67">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="Z67">
-        <v>3.08</v>
+        <v>4.45</v>
       </c>
       <c r="AA67">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="AB67">
-        <v>1.79</v>
+        <v>2.25</v>
       </c>
       <c r="AC67">
-        <v>3.5</v>
+        <v>2.42</v>
       </c>
       <c r="AD67">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="AE67">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF67">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="AG67">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AK67">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,65 +11393,65 @@
         </is>
       </c>
       <c r="N68">
+        <v>2.74</v>
+      </c>
+      <c r="O68">
+        <v>2.9</v>
+      </c>
+      <c r="P68">
+        <v>2.5</v>
+      </c>
+      <c r="Q68">
+        <v>3.63</v>
+      </c>
+      <c r="R68">
+        <v>1.95</v>
+      </c>
+      <c r="S68">
+        <v>1.5</v>
+      </c>
+      <c r="T68">
+        <v>2.56</v>
+      </c>
+      <c r="U68">
+        <v>3.14</v>
+      </c>
+      <c r="V68">
+        <v>1.3</v>
+      </c>
+      <c r="W68">
+        <v>1.04</v>
+      </c>
+      <c r="X68">
+        <v>1.11</v>
+      </c>
+      <c r="Y68">
+        <v>1.45</v>
+      </c>
+      <c r="Z68">
+        <v>2.52</v>
+      </c>
+      <c r="AA68">
+        <v>2.45</v>
+      </c>
+      <c r="AB68">
+        <v>1.58</v>
+      </c>
+      <c r="AC68">
+        <v>4.25</v>
+      </c>
+      <c r="AD68">
+        <v>1.17</v>
+      </c>
+      <c r="AE68">
+        <v>1.01</v>
+      </c>
+      <c r="AF68">
+        <v>1.97</v>
+      </c>
+      <c r="AG68">
         <v>1.75</v>
       </c>
-      <c r="O68">
-        <v>3.55</v>
-      </c>
-      <c r="P68">
-        <v>4.3</v>
-      </c>
-      <c r="Q68">
-        <v>2.25</v>
-      </c>
-      <c r="R68">
-        <v>2.26</v>
-      </c>
-      <c r="S68">
-        <v>1.32</v>
-      </c>
-      <c r="T68">
-        <v>3.31</v>
-      </c>
-      <c r="U68">
-        <v>2.5</v>
-      </c>
-      <c r="V68">
-        <v>1.5</v>
-      </c>
-      <c r="W68">
-        <v>1.11</v>
-      </c>
-      <c r="X68">
-        <v>1.01</v>
-      </c>
-      <c r="Y68">
-        <v>1.2</v>
-      </c>
-      <c r="Z68">
-        <v>4.4</v>
-      </c>
-      <c r="AA68">
-        <v>1.66</v>
-      </c>
-      <c r="AB68">
-        <v>2.27</v>
-      </c>
-      <c r="AC68">
-        <v>2.46</v>
-      </c>
-      <c r="AD68">
-        <v>1.47</v>
-      </c>
-      <c r="AE68">
-        <v>1.14</v>
-      </c>
-      <c r="AF68">
-        <v>1.6</v>
-      </c>
-      <c r="AG68">
-        <v>2.3</v>
-      </c>
       <c r="AH68" t="inlineStr">
         <is>
           <t>[]</t>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="AK68">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.59</v>
+        <v>1.98</v>
       </c>
       <c r="O69">
         <v>3</v>
       </c>
       <c r="P69">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="Q69">
-        <v>3.4</v>
+        <v>2.78</v>
       </c>
       <c r="R69">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="S69">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="T69">
-        <v>2.59</v>
+        <v>2.82</v>
       </c>
       <c r="U69">
-        <v>3.33</v>
+        <v>2.8</v>
       </c>
       <c r="V69">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="W69">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X69">
         <v>1.04</v>
       </c>
       <c r="Y69">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="Z69">
-        <v>2.85</v>
+        <v>3.08</v>
       </c>
       <c r="AA69">
-        <v>2.35</v>
+        <v>2.04</v>
       </c>
       <c r="AB69">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AC69">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="AD69">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AE69">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AF69">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AG69">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AK69">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11728,7 +11728,7 @@
         <v>2.3</v>
       </c>
       <c r="Q70">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R70">
         <v>2.05</v>
@@ -11737,7 +11737,7 @@
         <v>1.38</v>
       </c>
       <c r="T70">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="U70">
         <v>2.88</v>
@@ -11749,13 +11749,13 @@
         <v>1.04</v>
       </c>
       <c r="X70">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y70">
         <v>1.32</v>
       </c>
       <c r="Z70">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AA70">
         <v>2</v>
@@ -11764,19 +11764,19 @@
         <v>1.78</v>
       </c>
       <c r="AC70">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD70">
         <v>1.25</v>
       </c>
       <c r="AE70">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF70">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG70">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AK70">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11888,58 +11888,58 @@
         <v>4.5</v>
       </c>
       <c r="P71">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="Q71">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R71">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S71">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T71">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U71">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V71">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W71">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X71">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y71">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z71">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA71">
         <v>1.57</v>
       </c>
       <c r="AB71">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="AC71">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD71">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE71">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF71">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG71">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK71">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12051,37 +12051,37 @@
         <v>4.5</v>
       </c>
       <c r="P72">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="Q72">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R72">
-        <v>2.36</v>
+        <v>2.49</v>
       </c>
       <c r="S72">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="T72">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="U72">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="V72">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="W72">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="X72">
         <v>1.01</v>
       </c>
       <c r="Y72">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Z72">
-        <v>6.5</v>
+        <v>6.05</v>
       </c>
       <c r="AA72">
         <v>1.4</v>
@@ -12090,13 +12090,13 @@
         <v>2.88</v>
       </c>
       <c r="AC72">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AD72">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AE72">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AF72">
         <v>1.44</v>
@@ -12115,7 +12115,7 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK72">
         <v>2.26</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="O73">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="P73">
-        <v>1.95</v>
+        <v>3</v>
       </c>
       <c r="Q73">
-        <v>4</v>
+        <v>2.41</v>
       </c>
       <c r="R73">
-        <v>2.4</v>
+        <v>2.61</v>
       </c>
       <c r="S73">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="T73">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="U73">
-        <v>2.21</v>
+        <v>1.92</v>
       </c>
       <c r="V73">
-        <v>1.6</v>
+        <v>1.86</v>
       </c>
       <c r="W73">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="X73">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="Z73">
-        <v>5.25</v>
+        <v>7.4</v>
       </c>
       <c r="AA73">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="AB73">
-        <v>2.55</v>
+        <v>3.5</v>
       </c>
       <c r="AC73">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AD73">
-        <v>1.58</v>
+        <v>1.99</v>
       </c>
       <c r="AE73">
-        <v>1.2</v>
+        <v>1.39</v>
       </c>
       <c r="AF73">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="AG73">
-        <v>2.55</v>
+        <v>3.26</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="AK73">
-        <v>1.29</v>
+        <v>1.75</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="O74">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="P74">
+        <v>4.5</v>
+      </c>
+      <c r="Q74">
+        <v>2.06</v>
+      </c>
+      <c r="R74">
+        <v>2.75</v>
+      </c>
+      <c r="S74">
+        <v>1.2</v>
+      </c>
+      <c r="T74">
         <v>4.1</v>
       </c>
-      <c r="Q74">
-        <v>2.15</v>
-      </c>
-      <c r="R74">
-        <v>2.8</v>
-      </c>
-      <c r="S74">
+      <c r="U74">
+        <v>1.97</v>
+      </c>
+      <c r="V74">
+        <v>1.71</v>
+      </c>
+      <c r="W74">
         <v>1.18</v>
-      </c>
-      <c r="T74">
-        <v>4.4</v>
-      </c>
-      <c r="U74">
-        <v>1.95</v>
-      </c>
-      <c r="V74">
-        <v>1.79</v>
-      </c>
-      <c r="W74">
-        <v>1.19</v>
       </c>
       <c r="X74">
         <v>1.01</v>
       </c>
       <c r="Y74">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Z74">
-        <v>7</v>
+        <v>6.22</v>
       </c>
       <c r="AA74">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB74">
         <v>3.1</v>
       </c>
       <c r="AC74">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AD74">
-        <v>1.86</v>
+        <v>1.72</v>
       </c>
       <c r="AE74">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AF74">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AG74">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,80 +12534,80 @@
         </is>
       </c>
       <c r="N75">
-        <v>5</v>
+        <v>3.05</v>
       </c>
       <c r="O75">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="P75">
-        <v>1.47</v>
+        <v>2.1</v>
       </c>
       <c r="Q75">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="R75">
-        <v>2.49</v>
+        <v>2.38</v>
       </c>
       <c r="S75">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T75">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="U75">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="V75">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="W75">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X75">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y75">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z75">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA75">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AB75">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="AC75">
-        <v>2.12</v>
+        <v>2.21</v>
       </c>
       <c r="AD75">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AE75">
+        <v>1.21</v>
+      </c>
+      <c r="AF75">
+        <v>1.44</v>
+      </c>
+      <c r="AG75">
+        <v>2.55</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ75">
+        <v>1.22</v>
+      </c>
+      <c r="AK75">
         <v>1.33</v>
-      </c>
-      <c r="AF75">
-        <v>1.5</v>
-      </c>
-      <c r="AG75">
-        <v>2.45</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ75">
-        <v>1.15</v>
-      </c>
-      <c r="AK75">
-        <v>1.15</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.15</v>
+        <v>4.75</v>
       </c>
       <c r="O76">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="P76">
-        <v>2.8</v>
+        <v>1.55</v>
       </c>
       <c r="Q76">
+        <v>5</v>
+      </c>
+      <c r="R76">
         <v>2.54</v>
       </c>
-      <c r="R76">
-        <v>2.6</v>
-      </c>
       <c r="S76">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="T76">
-        <v>4.5</v>
+        <v>3.84</v>
       </c>
       <c r="U76">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="V76">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="W76">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="X76">
         <v>1.01</v>
       </c>
       <c r="Y76">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="Z76">
-        <v>7.2</v>
+        <v>6.1</v>
       </c>
       <c r="AA76">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="AB76">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="AC76">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="AD76">
-        <v>1.99</v>
+        <v>1.71</v>
       </c>
       <c r="AE76">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="AF76">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AG76">
-        <v>3.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
+        <v>1.15</v>
+      </c>
+      <c r="AK76">
         <v>1.17</v>
-      </c>
-      <c r="AK76">
-        <v>1.65</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12863,7 +12863,7 @@
         <v>1.79</v>
       </c>
       <c r="O77">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="P77">
         <v>3.8</v>
@@ -12872,22 +12872,22 @@
         <v>2.3</v>
       </c>
       <c r="R77">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S77">
         <v>1.3</v>
       </c>
       <c r="T77">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="U77">
-        <v>2.72</v>
+        <v>2.77</v>
       </c>
       <c r="V77">
         <v>1.46</v>
       </c>
       <c r="W77">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X77">
         <v>1.02</v>
@@ -12896,28 +12896,28 @@
         <v>1.22</v>
       </c>
       <c r="Z77">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="AA77">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB77">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AC77">
-        <v>2.9</v>
+        <v>2.66</v>
       </c>
       <c r="AD77">
         <v>1.38</v>
       </c>
       <c r="AE77">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF77">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG77">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,7 +12930,7 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK77">
         <v>1.98</v>
@@ -13032,34 +13032,34 @@
         <v>3.25</v>
       </c>
       <c r="Q78">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="R78">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S78">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T78">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="U78">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="V78">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W78">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X78">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y78">
         <v>1.2</v>
       </c>
       <c r="Z78">
-        <v>3.84</v>
+        <v>3.5</v>
       </c>
       <c r="AA78">
         <v>1.75</v>
@@ -13068,19 +13068,19 @@
         <v>2.1</v>
       </c>
       <c r="AC78">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="AD78">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE78">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF78">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AG78">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK78">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13186,7 +13186,7 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="O79">
         <v>3.5</v>
@@ -13195,7 +13195,7 @@
         <v>3.75</v>
       </c>
       <c r="Q79">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="R79">
         <v>2.14</v>
@@ -13204,13 +13204,13 @@
         <v>1.34</v>
       </c>
       <c r="T79">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="U79">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V79">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W79">
         <v>1.08</v>
@@ -13219,7 +13219,7 @@
         <v>1.03</v>
       </c>
       <c r="Y79">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z79">
         <v>3.34</v>
@@ -13231,10 +13231,10 @@
         <v>1.85</v>
       </c>
       <c r="AC79">
-        <v>3.33</v>
+        <v>3.34</v>
       </c>
       <c r="AD79">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE79">
         <v>1.1</v>
@@ -13349,31 +13349,31 @@
         </is>
       </c>
       <c r="N80">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="O80">
         <v>3.85</v>
       </c>
       <c r="P80">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="Q80">
-        <v>4.94</v>
+        <v>5.13</v>
       </c>
       <c r="R80">
         <v>2.25</v>
       </c>
       <c r="S80">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T80">
         <v>3.3</v>
       </c>
       <c r="U80">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="V80">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W80">
         <v>1.07</v>
@@ -13382,31 +13382,31 @@
         <v>1</v>
       </c>
       <c r="Y80">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z80">
-        <v>4.1</v>
+        <v>3.82</v>
       </c>
       <c r="AA80">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AB80">
+        <v>2.02</v>
+      </c>
+      <c r="AC80">
+        <v>2.79</v>
+      </c>
+      <c r="AD80">
+        <v>1.38</v>
+      </c>
+      <c r="AE80">
+        <v>1.12</v>
+      </c>
+      <c r="AF80">
+        <v>1.67</v>
+      </c>
+      <c r="AG80">
         <v>2.05</v>
-      </c>
-      <c r="AC80">
-        <v>2.89</v>
-      </c>
-      <c r="AD80">
-        <v>1.41</v>
-      </c>
-      <c r="AE80">
-        <v>1.1</v>
-      </c>
-      <c r="AF80">
-        <v>1.65</v>
-      </c>
-      <c r="AG80">
-        <v>2.1</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>1.2</v>
       </c>
       <c r="AK80">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13521,56 +13521,56 @@
         <v>2.75</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T81">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U81">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V81">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W81">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X81">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z81">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA81">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="AB81">
+        <v>1.89</v>
+      </c>
+      <c r="AC81">
+        <v>3.1</v>
+      </c>
+      <c r="AD81">
+        <v>1.35</v>
+      </c>
+      <c r="AE81">
+        <v>1.08</v>
+      </c>
+      <c r="AF81">
+        <v>1.62</v>
+      </c>
+      <c r="AG81">
         <v>2.15</v>
       </c>
-      <c r="AC81">
-        <v>0</v>
-      </c>
-      <c r="AD81">
-        <v>0</v>
-      </c>
-      <c r="AE81">
-        <v>0</v>
-      </c>
-      <c r="AF81">
-        <v>0</v>
-      </c>
-      <c r="AG81">
-        <v>0</v>
-      </c>
       <c r="AH81" t="inlineStr">
         <is>
           <t>[]</t>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK81">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13675,31 +13675,31 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O82">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P82">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="Q82">
         <v>3.11</v>
       </c>
       <c r="R82">
-        <v>2.23</v>
+        <v>2.33</v>
       </c>
       <c r="S82">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T82">
         <v>3.25</v>
       </c>
       <c r="U82">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="V82">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W82">
         <v>1.11</v>
@@ -13708,25 +13708,25 @@
         <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z82">
-        <v>4.53</v>
+        <v>4.09</v>
       </c>
       <c r="AA82">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AB82">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="AC82">
-        <v>2.87</v>
+        <v>3.13</v>
       </c>
       <c r="AD82">
         <v>1.47</v>
       </c>
       <c r="AE82">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF82">
         <v>1.5</v>
@@ -13853,16 +13853,16 @@
         <v>2.21</v>
       </c>
       <c r="S83">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T83">
-        <v>3.22</v>
+        <v>2.86</v>
       </c>
       <c r="U83">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="V83">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W83">
         <v>1.1</v>
@@ -13877,22 +13877,22 @@
         <v>3.8</v>
       </c>
       <c r="AA83">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AB83">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC83">
-        <v>2.97</v>
+        <v>2.66</v>
       </c>
       <c r="AD83">
         <v>1.37</v>
       </c>
       <c r="AE83">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF83">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG83">
         <v>2.2</v>
@@ -13911,7 +13911,7 @@
         <v>1.29</v>
       </c>
       <c r="AK83">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14007,19 +14007,19 @@
         <v>3</v>
       </c>
       <c r="P84">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="Q84">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="R84">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="S84">
         <v>1.35</v>
       </c>
       <c r="T84">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="U84">
         <v>2.78</v>
@@ -14040,7 +14040,7 @@
         <v>3.42</v>
       </c>
       <c r="AA84">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AB84">
         <v>1.85</v>
@@ -14058,7 +14058,7 @@
         <v>1.64</v>
       </c>
       <c r="AG84">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AK84">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14164,16 +14164,16 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="O85">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="P85">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="Q85">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="R85">
         <v>2.53</v>
@@ -14185,10 +14185,10 @@
         <v>4.5</v>
       </c>
       <c r="U85">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="V85">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="W85">
         <v>1.22</v>
@@ -14212,7 +14212,7 @@
         <v>1.91</v>
       </c>
       <c r="AD85">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AE85">
         <v>1.4</v>
@@ -14333,37 +14333,37 @@
         <v>3.15</v>
       </c>
       <c r="P86">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q86">
         <v>2.97</v>
       </c>
       <c r="R86">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="S86">
         <v>1.37</v>
       </c>
       <c r="T86">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="U86">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="V86">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W86">
         <v>1.05</v>
       </c>
       <c r="X86">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y86">
         <v>1.32</v>
       </c>
       <c r="Z86">
-        <v>3.35</v>
+        <v>3.08</v>
       </c>
       <c r="AA86">
         <v>1.75</v>
@@ -14375,7 +14375,7 @@
         <v>2.75</v>
       </c>
       <c r="AD86">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE86">
         <v>1.04</v>
@@ -14505,7 +14505,7 @@
         <v>2.29</v>
       </c>
       <c r="S87">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T87">
         <v>3.18</v>
@@ -14529,22 +14529,22 @@
         <v>4.25</v>
       </c>
       <c r="AA87">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AB87">
         <v>2.2</v>
       </c>
       <c r="AC87">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="AD87">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AE87">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF87">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG87">
         <v>2.32</v>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AK87">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.46</v>
+        <v>2.9</v>
       </c>
       <c r="O89">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="P89">
-        <v>6</v>
+        <v>2.15</v>
       </c>
       <c r="Q89">
-        <v>2.02</v>
+        <v>3.2</v>
       </c>
       <c r="R89">
-        <v>2.73</v>
+        <v>2.25</v>
       </c>
       <c r="S89">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="T89">
-        <v>3.9</v>
+        <v>3.02</v>
       </c>
       <c r="U89">
-        <v>2</v>
+        <v>2.88</v>
       </c>
       <c r="V89">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="W89">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X89">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y89">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="Z89">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA89">
-        <v>1.4</v>
+        <v>1.86</v>
       </c>
       <c r="AB89">
-        <v>2.7</v>
+        <v>1.82</v>
       </c>
       <c r="AC89">
-        <v>2.05</v>
+        <v>3.32</v>
       </c>
       <c r="AD89">
-        <v>1.66</v>
+        <v>1.3</v>
       </c>
       <c r="AE89">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AF89">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AG89">
-        <v>2.39</v>
+        <v>2.1</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK89">
-        <v>2.3</v>
+        <v>1.36</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.9</v>
+        <v>1.46</v>
       </c>
       <c r="O90">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="P90">
-        <v>2.15</v>
+        <v>6</v>
       </c>
       <c r="Q90">
-        <v>3.2</v>
+        <v>2.02</v>
       </c>
       <c r="R90">
-        <v>2.25</v>
+        <v>2.73</v>
       </c>
       <c r="S90">
-        <v>1.37</v>
+        <v>1.17</v>
       </c>
       <c r="T90">
-        <v>3.02</v>
+        <v>3.9</v>
       </c>
       <c r="U90">
-        <v>2.88</v>
+        <v>2</v>
       </c>
       <c r="V90">
+        <v>1.73</v>
+      </c>
+      <c r="W90">
+        <v>1.17</v>
+      </c>
+      <c r="X90">
+        <v>1.02</v>
+      </c>
+      <c r="Y90">
+        <v>1.1</v>
+      </c>
+      <c r="Z90">
+        <v>5.2</v>
+      </c>
+      <c r="AA90">
         <v>1.4</v>
       </c>
-      <c r="W90">
-        <v>1.1</v>
-      </c>
-      <c r="X90">
-        <v>1.03</v>
-      </c>
-      <c r="Y90">
-        <v>1.24</v>
-      </c>
-      <c r="Z90">
-        <v>3.5</v>
-      </c>
-      <c r="AA90">
-        <v>1.86</v>
-      </c>
       <c r="AB90">
-        <v>1.82</v>
+        <v>2.7</v>
       </c>
       <c r="AC90">
-        <v>3.32</v>
+        <v>2.05</v>
       </c>
       <c r="AD90">
-        <v>1.3</v>
+        <v>1.66</v>
       </c>
       <c r="AE90">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="AF90">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AG90">
-        <v>2.1</v>
+        <v>2.39</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK90">
-        <v>1.36</v>
+        <v>2.3</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>5.75</v>
+        <v>2.14</v>
       </c>
       <c r="O91">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="P91">
-        <v>1.38</v>
+        <v>2.75</v>
       </c>
       <c r="Q91">
-        <v>4.25</v>
+        <v>2.96</v>
       </c>
       <c r="R91">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="S91">
         <v>1.22</v>
       </c>
       <c r="T91">
-        <v>4</v>
+        <v>3.52</v>
       </c>
       <c r="U91">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="V91">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="W91">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X91">
         <v>1.01</v>
       </c>
       <c r="Y91">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z91">
-        <v>5.67</v>
+        <v>5.5</v>
       </c>
       <c r="AA91">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AB91">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="AC91">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="AD91">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AE91">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AF91">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AG91">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>2.75</v>
+        <v>1.44</v>
       </c>
       <c r="AK91">
-        <v>1.11</v>
+        <v>1.53</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.14</v>
+        <v>3.1</v>
       </c>
       <c r="O92">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P92">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="Q92">
-        <v>2.96</v>
+        <v>3.9</v>
       </c>
       <c r="R92">
-        <v>2.48</v>
+        <v>2.16</v>
       </c>
       <c r="S92">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="T92">
-        <v>3.52</v>
+        <v>3.1</v>
       </c>
       <c r="U92">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="V92">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="W92">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X92">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y92">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z92">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
       <c r="AA92">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AB92">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="AC92">
-        <v>2.37</v>
+        <v>2.88</v>
       </c>
       <c r="AD92">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="AE92">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AF92">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AG92">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AK92">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>3.1</v>
+        <v>5.75</v>
       </c>
       <c r="O94">
-        <v>3.35</v>
+        <v>4.7</v>
       </c>
       <c r="P94">
-        <v>2</v>
+        <v>1.38</v>
       </c>
       <c r="Q94">
-        <v>3.9</v>
+        <v>4.25</v>
       </c>
       <c r="R94">
-        <v>2.16</v>
+        <v>2.62</v>
       </c>
       <c r="S94">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="T94">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="U94">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="V94">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="W94">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X94">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y94">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="Z94">
-        <v>3.7</v>
+        <v>5.67</v>
       </c>
       <c r="AA94">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AB94">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="AC94">
-        <v>2.88</v>
+        <v>2.15</v>
       </c>
       <c r="AD94">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="AE94">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="AF94">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AG94">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.29</v>
+        <v>2.75</v>
       </c>
       <c r="AK94">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15963,7 +15963,7 @@
         <v>3.8</v>
       </c>
       <c r="P96">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="Q96">
         <v>2.78</v>
@@ -15972,19 +15972,19 @@
         <v>2.3</v>
       </c>
       <c r="S96">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T96">
         <v>3.58</v>
       </c>
       <c r="U96">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="V96">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="W96">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X96">
         <v>1.02</v>
@@ -15993,28 +15993,28 @@
         <v>1.1</v>
       </c>
       <c r="Z96">
-        <v>5.35</v>
+        <v>5.45</v>
       </c>
       <c r="AA96">
         <v>1.42</v>
       </c>
       <c r="AB96">
-        <v>2.94</v>
+        <v>2.87</v>
       </c>
       <c r="AC96">
         <v>2.05</v>
       </c>
       <c r="AD96">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="AE96">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AF96">
         <v>1.33</v>
       </c>
       <c r="AG96">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>1.25</v>
       </c>
       <c r="AK96">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16120,10 +16120,10 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="O97">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P97">
         <v>2.4</v>
@@ -16132,7 +16132,7 @@
         <v>2.81</v>
       </c>
       <c r="R97">
-        <v>2.24</v>
+        <v>2.19</v>
       </c>
       <c r="S97">
         <v>1.25</v>
@@ -16141,43 +16141,43 @@
         <v>3.5</v>
       </c>
       <c r="U97">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="V97">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W97">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X97">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y97">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z97">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AA97">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AB97">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AC97">
-        <v>2.35</v>
+        <v>2.56</v>
       </c>
       <c r="AD97">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AE97">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF97">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AG97">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="AK97">
         <v>1.44</v>
@@ -16446,10 +16446,10 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="O99">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P99">
         <v>3.5</v>
@@ -16458,7 +16458,7 @@
         <v>2.68</v>
       </c>
       <c r="R99">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="S99">
         <v>1.39</v>
@@ -16467,7 +16467,7 @@
         <v>2.99</v>
       </c>
       <c r="U99">
-        <v>2.91</v>
+        <v>2.59</v>
       </c>
       <c r="V99">
         <v>1.46</v>
@@ -16479,31 +16479,31 @@
         <v>1.01</v>
       </c>
       <c r="Y99">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z99">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="AA99">
         <v>1.92</v>
       </c>
       <c r="AB99">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AC99">
         <v>3.25</v>
       </c>
       <c r="AD99">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE99">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF99">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AG99">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AK99">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16615,58 +16615,58 @@
         <v>3.5</v>
       </c>
       <c r="P100">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q100">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="R100">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="S100">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T100">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="U100">
         <v>2.69</v>
       </c>
       <c r="V100">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W100">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X100">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y100">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z100">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AA100">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AB100">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AC100">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="AD100">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE100">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF100">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG100">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,7 +16679,7 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="AK100">
         <v>1.36</v>
@@ -16775,7 +16775,7 @@
         <v>3.65</v>
       </c>
       <c r="O101">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="P101">
         <v>1.6</v>
@@ -16787,25 +16787,25 @@
         <v>2.74</v>
       </c>
       <c r="S101">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="T101">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="U101">
         <v>1.78</v>
       </c>
       <c r="V101">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="W101">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="X101">
         <v>1.01</v>
       </c>
       <c r="Y101">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="Z101">
         <v>6.75</v>
@@ -16823,13 +16823,13 @@
         <v>2.05</v>
       </c>
       <c r="AE101">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AF101">
         <v>1.37</v>
       </c>
       <c r="AG101">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16935,43 +16935,43 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="O102">
         <v>3.35</v>
       </c>
       <c r="P102">
-        <v>3.6</v>
+        <v>4.17</v>
       </c>
       <c r="Q102">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
       <c r="R102">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="S102">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T102">
-        <v>2.66</v>
+        <v>2.45</v>
       </c>
       <c r="U102">
-        <v>3.12</v>
+        <v>2.46</v>
       </c>
       <c r="V102">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="W102">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X102">
         <v>1.03</v>
       </c>
       <c r="Y102">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z102">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="AA102">
         <v>2.17</v>
@@ -16980,10 +16980,10 @@
         <v>1.57</v>
       </c>
       <c r="AC102">
-        <v>4.18</v>
+        <v>3.98</v>
       </c>
       <c r="AD102">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE102">
         <v>1.03</v>
@@ -16992,7 +16992,7 @@
         <v>2</v>
       </c>
       <c r="AG102">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="AK102">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="O103">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="P103">
         <v>2.88</v>
       </c>
       <c r="Q103">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R103">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S103">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T103">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U103">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V103">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W103">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X103">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y103">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z103">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA103">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AB103">
+        <v>1.74</v>
+      </c>
+      <c r="AC103">
+        <v>3.34</v>
+      </c>
+      <c r="AD103">
+        <v>1.24</v>
+      </c>
+      <c r="AE103">
+        <v>1.04</v>
+      </c>
+      <c r="AF103">
         <v>1.8</v>
       </c>
-      <c r="AC103">
-        <v>0</v>
-      </c>
-      <c r="AD103">
-        <v>0</v>
-      </c>
-      <c r="AE103">
-        <v>0</v>
-      </c>
-      <c r="AF103">
-        <v>0</v>
-      </c>
       <c r="AG103">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK103">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17261,19 +17261,19 @@
         </is>
       </c>
       <c r="N104">
-        <v>8.800000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="O104">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="P104">
         <v>1.3</v>
       </c>
       <c r="Q104">
-        <v>6.28</v>
+        <v>6.57</v>
       </c>
       <c r="R104